--- a/tools/languages.xlsx
+++ b/tools/languages.xlsx
@@ -1,21 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macbook/projects/hieunm/xiangqi/Tools/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9235CB5D-365A-A846-8C6B-5186B6E28F9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="Calc"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="23760" windowHeight="13480" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -25,283 +20,304 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="88">
-  <si>
-    <t>Key</t>
-  </si>
-  <si>
-    <t>English</t>
-  </si>
-  <si>
-    <t>Vietnamese</t>
-  </si>
-  <si>
-    <t>page.home.title</t>
-  </si>
-  <si>
-    <t>Home</t>
-  </si>
-  <si>
-    <t>Trang chủ</t>
-  </si>
-  <si>
-    <t>page.history.title</t>
-  </si>
-  <si>
-    <t>History</t>
-  </si>
-  <si>
-    <t>Lịch sử</t>
-  </si>
-  <si>
-    <t>page.about.title</t>
-  </si>
-  <si>
-    <t>About</t>
-  </si>
-  <si>
-    <t>Thông tin</t>
-  </si>
-  <si>
-    <t>menu.setting.button</t>
-  </si>
-  <si>
-    <t>Settings</t>
-  </si>
-  <si>
-    <t>Cài đặt</t>
-  </si>
-  <si>
-    <t>menu.app-name</t>
-  </si>
-  <si>
-    <t>Xiangqi</t>
-  </si>
-  <si>
-    <t>Cờ tướng</t>
-  </si>
-  <si>
-    <t>menu.home</t>
-  </si>
-  <si>
-    <t>menu.users</t>
-  </si>
-  <si>
-    <t>Users</t>
-  </si>
-  <si>
-    <t>Người dùng</t>
-  </si>
-  <si>
-    <t>menu.analytics</t>
-  </si>
-  <si>
-    <t>Analytic</t>
-  </si>
-  <si>
-    <t>Phân tích</t>
-  </si>
-  <si>
-    <t>menu.logout</t>
-  </si>
-  <si>
-    <t>Logout</t>
-  </si>
-  <si>
-    <t>Đăng xuất</t>
-  </si>
-  <si>
-    <t>settings.header</t>
-  </si>
-  <si>
-    <t>settings.language</t>
-  </si>
-  <si>
-    <t>Language</t>
-  </si>
-  <si>
-    <t>Ngôn ngữ</t>
-  </si>
-  <si>
-    <t>settings.dark-mode</t>
-  </si>
-  <si>
-    <t>Dark mode</t>
-  </si>
-  <si>
-    <t>Chế độ tối</t>
-  </si>
-  <si>
-    <t>settings.close</t>
-  </si>
-  <si>
-    <t>Close</t>
-  </si>
-  <si>
-    <t>Đóng</t>
-  </si>
-  <si>
-    <t>popup.confirm.ok</t>
-  </si>
-  <si>
-    <t>Ok</t>
-  </si>
-  <si>
-    <t>popup.confirm.cancel</t>
-  </si>
-  <si>
-    <t>Cancel</t>
-  </si>
-  <si>
-    <t>Huỷ</t>
-  </si>
-  <si>
-    <t>home.turn.title</t>
-  </si>
-  <si>
-    <t>Turn</t>
-  </si>
-  <si>
-    <t>Lượt đánh</t>
-  </si>
-  <si>
-    <t>game.general.captured</t>
-  </si>
-  <si>
-    <t>General has been captured. Game over</t>
-  </si>
-  <si>
-    <t>Tướng đã bị bắt. Game kết thúc</t>
-  </si>
-  <si>
-    <t>game.general.in-check</t>
-  </si>
-  <si>
-    <t>login.form.title</t>
-  </si>
-  <si>
-    <t>Login</t>
-  </si>
-  <si>
-    <t>Đăng nhập</t>
-  </si>
-  <si>
-    <t>login.username.label</t>
-  </si>
-  <si>
-    <t>User name</t>
-  </si>
-  <si>
-    <t>Tên người dùng</t>
-  </si>
-  <si>
-    <t>login.username.placeholder</t>
-  </si>
-  <si>
-    <t>login.username.error1</t>
-  </si>
-  <si>
-    <t>User name is required</t>
-  </si>
-  <si>
-    <t>Tên người dùng bắt buộc nhập</t>
-  </si>
-  <si>
-    <t>login.password.label</t>
-  </si>
-  <si>
-    <t>Password</t>
-  </si>
-  <si>
-    <t>Mật khẩu</t>
-  </si>
-  <si>
-    <t>login.password.placeholder</t>
-  </si>
-  <si>
-    <t>login.password.error1</t>
-  </si>
-  <si>
-    <t>Password is required</t>
-  </si>
-  <si>
-    <t>Mật khẩu bắt buộc nhập</t>
-  </si>
-  <si>
-    <t>login.password.show</t>
-  </si>
-  <si>
-    <t>Show password</t>
-  </si>
-  <si>
-    <t>Hiện mật khẩu</t>
-  </si>
-  <si>
-    <t>login.password.hide</t>
-  </si>
-  <si>
-    <t>Hide password</t>
-  </si>
-  <si>
-    <t>Ẩn mật khẩu</t>
-  </si>
-  <si>
-    <t>login.form.error1</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="89">
+  <si>
+    <t xml:space="preserve">Key</t>
+  </si>
+  <si>
+    <t xml:space="preserve">English</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vietnamese</t>
+  </si>
+  <si>
+    <t xml:space="preserve">page.home.title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trang chủ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">page.history.title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">History</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lịch sử</t>
+  </si>
+  <si>
+    <t xml:space="preserve">page.about.title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">About</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thông tin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">menu.setting.button</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Settings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cài đặt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">menu.app-name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xiangqi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cờ tướng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">menu.home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">menu.users</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Users</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Người dùng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">menu.analytics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analytic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phân tích</t>
+  </si>
+  <si>
+    <t xml:space="preserve">menu.logout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đăng xuất</t>
+  </si>
+  <si>
+    <t xml:space="preserve">settings.header</t>
+  </si>
+  <si>
+    <t xml:space="preserve">settings.language</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Language</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ngôn ngữ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">settings.dark-mode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dark mode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chế độ tối</t>
+  </si>
+  <si>
+    <t xml:space="preserve">settings.close</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Close</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đóng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">popup.alert.title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Warning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cảnh báo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">popup.confirm.ok</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ok</t>
+  </si>
+  <si>
+    <t xml:space="preserve">popup.confirm.cancel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cancel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Huỷ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">home.turn.title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Turn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lượt đánh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">game.general.captured</t>
+  </si>
+  <si>
+    <t xml:space="preserve">General has been captured. Game over</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tướng đã bị bắt. Game kết thúc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">game.general.in-check</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your general is under attack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tướng của bạn đang bị chiếu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">login.page.title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Login</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đăng nhập</t>
+  </si>
+  <si>
+    <t xml:space="preserve">login.form.title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">login.username.label</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tên người dùng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">login.username.placeholder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">login.username.error1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User name is required</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tên người dùng bắt buộc nhập</t>
+  </si>
+  <si>
+    <t xml:space="preserve">login.password.label</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Password</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mật khẩu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">login.password.placeholder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">login.password.error1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Password is required</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mật khẩu bắt buộc nhập</t>
+  </si>
+  <si>
+    <t xml:space="preserve">login.password.show</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Show password</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hiện mật khẩu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">login.password.hide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hide password</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ẩn mật khẩu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">login.form.error1</t>
   </si>
   <si>
     <t xml:space="preserve">Login failed. Please check your credentials </t>
   </si>
   <si>
-    <t>Đăng nhập không thành công. Hãy kiểm tra lại</t>
-  </si>
-  <si>
-    <t>login.form.forgot-password</t>
-  </si>
-  <si>
-    <t>Forgot password</t>
-  </si>
-  <si>
-    <t>Quên mật khẩu</t>
-  </si>
-  <si>
-    <t>login.form.register</t>
-  </si>
-  <si>
-    <t>Register</t>
-  </si>
-  <si>
-    <t>Đăng ký</t>
-  </si>
-  <si>
-    <t>login.form.submit</t>
-  </si>
-  <si>
-    <t>popup.alert.title</t>
-  </si>
-  <si>
-    <t>Warning</t>
-  </si>
-  <si>
-    <t>Cảnh báo</t>
-  </si>
-  <si>
-    <t>Your general is under attack</t>
-  </si>
-  <si>
-    <t>Tướng của bạn đang bị chiếu</t>
+    <t xml:space="preserve">Đăng nhập không thành công. Hãy kiểm tra lại</t>
+  </si>
+  <si>
+    <t xml:space="preserve">login.form.forgot-password</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forgot password</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quên mật khẩu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">login.form.register</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Register</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đăng ký</t>
+  </si>
+  <si>
+    <t xml:space="preserve">login.form.submit</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="General"/>
+  </numFmts>
+  <fonts count="6">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
     </font>
     <font>
       <sz val="13"/>
@@ -327,7 +343,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -335,92 +351,117 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="0e2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="e8e8e8"/>
       </a:lt2>
       <a:accent1>
         <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="e97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="196b24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="0f9ed5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="a02b93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="4ea72e"/>
       </a:accent6>
       <a:hlink>
         <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="96607d"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -452,7 +493,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -476,7 +517,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -536,27 +577,28 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C481"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:C482"/>
+  <sheetFormatPr defaultColWidth="11.5078125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="35.5" style="1" customWidth="1"/>
-    <col min="2" max="2" width="41.6640625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="42.1640625" style="2" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="35.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="41.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="42.17"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -567,7 +609,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+    <row r="2" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
         <v>3</v>
       </c>
@@ -578,7 +620,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+    <row r="3" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
@@ -589,7 +631,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+    <row r="4" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
         <v>9</v>
       </c>
@@ -600,7 +642,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+    <row r="5" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
         <v>12</v>
       </c>
@@ -611,7 +653,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+    <row r="6" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
         <v>15</v>
       </c>
@@ -622,7 +664,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+    <row r="7" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
         <v>18</v>
       </c>
@@ -633,7 +675,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+    <row r="8" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
         <v>19</v>
       </c>
@@ -644,7 +686,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+    <row r="9" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
         <v>22</v>
       </c>
@@ -655,7 +697,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+    <row r="10" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
         <v>25</v>
       </c>
@@ -666,12 +708,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="11" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
     </row>
-    <row r="12" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+    <row r="12" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
         <v>28</v>
       </c>
@@ -682,7 +724,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+    <row r="13" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
         <v>29</v>
       </c>
@@ -693,7 +735,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+    <row r="14" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
         <v>32</v>
       </c>
@@ -704,7 +746,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+    <row r="15" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
         <v>35</v>
       </c>
@@ -715,2452 +757,2468 @@
         <v>37</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+    <row r="16" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>84</v>
+        <v>39</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3"/>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
     </row>
-    <row r="23" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+    <row r="23" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B36" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B25" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="18" x14ac:dyDescent="0.2">
-      <c r="A26" s="3" t="s">
+      <c r="C36" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B26" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="18" x14ac:dyDescent="0.2">
-      <c r="A27" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="18" x14ac:dyDescent="0.2">
-      <c r="A28" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" ht="18" x14ac:dyDescent="0.2">
-      <c r="A29" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="18" x14ac:dyDescent="0.2">
-      <c r="A30" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="18" x14ac:dyDescent="0.2">
-      <c r="A31" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="36" x14ac:dyDescent="0.2">
-      <c r="A32" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="18" x14ac:dyDescent="0.2">
-      <c r="A33" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="18" x14ac:dyDescent="0.2">
-      <c r="A34" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="18" x14ac:dyDescent="0.2">
-      <c r="A35" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A36" s="3"/>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-    </row>
-    <row r="37" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="37" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3"/>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
     </row>
-    <row r="38" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="38" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3"/>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
     </row>
-    <row r="39" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="39" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3"/>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
     </row>
-    <row r="40" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="40" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
     </row>
-    <row r="41" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="41" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="3"/>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
     </row>
-    <row r="42" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="42" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="3"/>
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
     </row>
-    <row r="43" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="43" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="3"/>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
     </row>
-    <row r="44" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="44" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="3"/>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
     </row>
-    <row r="45" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="45" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="3"/>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
     </row>
-    <row r="46" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="46" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="3"/>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
     </row>
-    <row r="47" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="47" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="3"/>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
     </row>
-    <row r="48" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="48" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="3"/>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
     </row>
-    <row r="49" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="49" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="3"/>
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
     </row>
-    <row r="50" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="50" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="3"/>
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
     </row>
-    <row r="51" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="51" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="3"/>
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
     </row>
-    <row r="52" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="52" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="3"/>
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
     </row>
-    <row r="53" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="53" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="3"/>
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
     </row>
-    <row r="54" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="54" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="3"/>
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
     </row>
-    <row r="55" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="55" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="3"/>
       <c r="B55" s="4"/>
       <c r="C55" s="4"/>
     </row>
-    <row r="56" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="56" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="3"/>
       <c r="B56" s="4"/>
       <c r="C56" s="4"/>
     </row>
-    <row r="57" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="57" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="3"/>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
     </row>
-    <row r="58" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="58" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="3"/>
       <c r="B58" s="4"/>
       <c r="C58" s="4"/>
     </row>
-    <row r="59" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="59" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="3"/>
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
     </row>
-    <row r="60" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="60" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="3"/>
       <c r="B60" s="4"/>
       <c r="C60" s="4"/>
     </row>
-    <row r="61" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="61" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="3"/>
       <c r="B61" s="4"/>
       <c r="C61" s="4"/>
     </row>
-    <row r="62" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="62" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="3"/>
       <c r="B62" s="4"/>
       <c r="C62" s="4"/>
     </row>
-    <row r="63" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="63" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="3"/>
       <c r="B63" s="4"/>
       <c r="C63" s="4"/>
     </row>
-    <row r="64" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="64" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="3"/>
       <c r="B64" s="4"/>
       <c r="C64" s="4"/>
     </row>
-    <row r="65" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="65" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="3"/>
       <c r="B65" s="4"/>
       <c r="C65" s="4"/>
     </row>
-    <row r="66" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="66" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="3"/>
       <c r="B66" s="4"/>
       <c r="C66" s="4"/>
     </row>
-    <row r="67" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="67" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="3"/>
       <c r="B67" s="4"/>
       <c r="C67" s="4"/>
     </row>
-    <row r="68" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="68" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="3"/>
       <c r="B68" s="4"/>
       <c r="C68" s="4"/>
     </row>
-    <row r="69" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="69" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="3"/>
       <c r="B69" s="4"/>
       <c r="C69" s="4"/>
     </row>
-    <row r="70" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="70" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="3"/>
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
     </row>
-    <row r="71" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="71" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="3"/>
       <c r="B71" s="4"/>
       <c r="C71" s="4"/>
     </row>
-    <row r="72" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="72" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="3"/>
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
     </row>
-    <row r="73" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="73" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="3"/>
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
     </row>
-    <row r="74" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="74" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="3"/>
       <c r="B74" s="4"/>
       <c r="C74" s="4"/>
     </row>
-    <row r="75" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="75" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="3"/>
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
     </row>
-    <row r="76" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="76" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="3"/>
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
     </row>
-    <row r="77" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="77" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="3"/>
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
     </row>
-    <row r="78" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="78" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="3"/>
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
     </row>
-    <row r="79" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="79" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="3"/>
       <c r="B79" s="4"/>
       <c r="C79" s="4"/>
     </row>
-    <row r="80" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="80" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="3"/>
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
     </row>
-    <row r="81" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="81" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="3"/>
       <c r="B81" s="4"/>
       <c r="C81" s="4"/>
     </row>
-    <row r="82" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="82" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="3"/>
       <c r="B82" s="4"/>
       <c r="C82" s="4"/>
     </row>
-    <row r="83" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="83" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="3"/>
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
     </row>
-    <row r="84" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="84" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="3"/>
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
     </row>
-    <row r="85" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="85" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="3"/>
       <c r="B85" s="4"/>
       <c r="C85" s="4"/>
     </row>
-    <row r="86" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="86" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="3"/>
       <c r="B86" s="4"/>
       <c r="C86" s="4"/>
     </row>
-    <row r="87" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="87" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="3"/>
       <c r="B87" s="4"/>
       <c r="C87" s="4"/>
     </row>
-    <row r="88" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="88" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="3"/>
       <c r="B88" s="4"/>
       <c r="C88" s="4"/>
     </row>
-    <row r="89" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="89" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="3"/>
       <c r="B89" s="4"/>
       <c r="C89" s="4"/>
     </row>
-    <row r="90" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="90" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="3"/>
       <c r="B90" s="4"/>
       <c r="C90" s="4"/>
     </row>
-    <row r="91" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="91" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="3"/>
       <c r="B91" s="4"/>
       <c r="C91" s="4"/>
     </row>
-    <row r="92" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="92" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="3"/>
       <c r="B92" s="4"/>
       <c r="C92" s="4"/>
     </row>
-    <row r="93" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="93" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="3"/>
       <c r="B93" s="4"/>
       <c r="C93" s="4"/>
     </row>
-    <row r="94" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="94" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="3"/>
       <c r="B94" s="4"/>
       <c r="C94" s="4"/>
     </row>
-    <row r="95" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="95" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="3"/>
       <c r="B95" s="4"/>
       <c r="C95" s="4"/>
     </row>
-    <row r="96" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="96" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="3"/>
       <c r="B96" s="4"/>
       <c r="C96" s="4"/>
     </row>
-    <row r="97" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="97" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="3"/>
       <c r="B97" s="4"/>
       <c r="C97" s="4"/>
     </row>
-    <row r="98" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="98" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="3"/>
       <c r="B98" s="4"/>
       <c r="C98" s="4"/>
     </row>
-    <row r="99" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="99" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="3"/>
       <c r="B99" s="4"/>
       <c r="C99" s="4"/>
     </row>
-    <row r="100" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="100" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="3"/>
       <c r="B100" s="4"/>
       <c r="C100" s="4"/>
     </row>
-    <row r="101" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="101" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="3"/>
       <c r="B101" s="4"/>
       <c r="C101" s="4"/>
     </row>
-    <row r="102" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="102" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="3"/>
       <c r="B102" s="4"/>
       <c r="C102" s="4"/>
     </row>
-    <row r="103" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="103" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="3"/>
       <c r="B103" s="4"/>
       <c r="C103" s="4"/>
     </row>
-    <row r="104" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="104" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="3"/>
       <c r="B104" s="4"/>
       <c r="C104" s="4"/>
     </row>
-    <row r="105" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="105" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="3"/>
       <c r="B105" s="4"/>
       <c r="C105" s="4"/>
     </row>
-    <row r="106" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="106" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="3"/>
       <c r="B106" s="4"/>
       <c r="C106" s="4"/>
     </row>
-    <row r="107" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="107" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="3"/>
       <c r="B107" s="4"/>
       <c r="C107" s="4"/>
     </row>
-    <row r="108" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="108" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="3"/>
       <c r="B108" s="4"/>
       <c r="C108" s="4"/>
     </row>
-    <row r="109" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="109" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="3"/>
       <c r="B109" s="4"/>
       <c r="C109" s="4"/>
     </row>
-    <row r="110" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="110" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="3"/>
       <c r="B110" s="4"/>
       <c r="C110" s="4"/>
     </row>
-    <row r="111" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="111" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="3"/>
       <c r="B111" s="4"/>
       <c r="C111" s="4"/>
     </row>
-    <row r="112" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A112" s="4"/>
+    <row r="112" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="3"/>
       <c r="B112" s="4"/>
       <c r="C112" s="4"/>
     </row>
-    <row r="113" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="113" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="4"/>
       <c r="B113" s="4"/>
       <c r="C113" s="4"/>
     </row>
-    <row r="114" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A114" s="3"/>
+    <row r="114" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="4"/>
       <c r="B114" s="4"/>
       <c r="C114" s="4"/>
     </row>
-    <row r="115" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="115" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="3"/>
       <c r="B115" s="4"/>
       <c r="C115" s="4"/>
     </row>
-    <row r="116" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="116" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="3"/>
       <c r="B116" s="4"/>
       <c r="C116" s="4"/>
     </row>
-    <row r="117" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="117" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="3"/>
       <c r="B117" s="4"/>
       <c r="C117" s="4"/>
     </row>
-    <row r="118" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="118" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="3"/>
       <c r="B118" s="4"/>
       <c r="C118" s="4"/>
     </row>
-    <row r="119" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="119" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="3"/>
       <c r="B119" s="4"/>
       <c r="C119" s="4"/>
     </row>
-    <row r="120" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="120" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="3"/>
       <c r="B120" s="4"/>
       <c r="C120" s="4"/>
     </row>
-    <row r="121" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="121" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="3"/>
       <c r="B121" s="4"/>
       <c r="C121" s="4"/>
     </row>
-    <row r="122" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="122" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="3"/>
       <c r="B122" s="4"/>
       <c r="C122" s="4"/>
     </row>
-    <row r="123" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="123" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="3"/>
       <c r="B123" s="4"/>
       <c r="C123" s="4"/>
     </row>
-    <row r="124" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="124" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="3"/>
       <c r="B124" s="4"/>
       <c r="C124" s="4"/>
     </row>
-    <row r="125" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="125" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="3"/>
       <c r="B125" s="4"/>
       <c r="C125" s="4"/>
     </row>
-    <row r="126" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="126" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="3"/>
       <c r="B126" s="4"/>
       <c r="C126" s="4"/>
     </row>
-    <row r="127" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="127" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="3"/>
       <c r="B127" s="4"/>
       <c r="C127" s="4"/>
     </row>
-    <row r="128" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="128" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="3"/>
       <c r="B128" s="4"/>
       <c r="C128" s="4"/>
     </row>
-    <row r="129" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="129" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="3"/>
       <c r="B129" s="4"/>
       <c r="C129" s="4"/>
     </row>
-    <row r="130" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="130" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="3"/>
       <c r="B130" s="4"/>
       <c r="C130" s="4"/>
     </row>
-    <row r="131" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="131" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="3"/>
       <c r="B131" s="4"/>
       <c r="C131" s="4"/>
     </row>
-    <row r="132" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="132" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="3"/>
       <c r="B132" s="4"/>
       <c r="C132" s="4"/>
     </row>
-    <row r="133" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="133" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="3"/>
       <c r="B133" s="4"/>
       <c r="C133" s="4"/>
     </row>
-    <row r="134" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="134" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="3"/>
       <c r="B134" s="4"/>
       <c r="C134" s="4"/>
     </row>
-    <row r="135" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="135" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="3"/>
       <c r="B135" s="4"/>
       <c r="C135" s="4"/>
     </row>
-    <row r="136" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="136" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="3"/>
       <c r="B136" s="4"/>
       <c r="C136" s="4"/>
     </row>
-    <row r="137" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="137" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="3"/>
       <c r="B137" s="4"/>
       <c r="C137" s="4"/>
     </row>
-    <row r="138" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="138" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="3"/>
       <c r="B138" s="4"/>
       <c r="C138" s="4"/>
     </row>
-    <row r="139" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="139" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="3"/>
       <c r="B139" s="4"/>
       <c r="C139" s="4"/>
     </row>
-    <row r="140" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="140" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="3"/>
       <c r="B140" s="4"/>
       <c r="C140" s="4"/>
     </row>
-    <row r="141" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="141" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="3"/>
       <c r="B141" s="4"/>
       <c r="C141" s="4"/>
     </row>
-    <row r="142" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="142" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="3"/>
       <c r="B142" s="4"/>
       <c r="C142" s="4"/>
     </row>
-    <row r="143" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="143" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="3"/>
       <c r="B143" s="4"/>
       <c r="C143" s="4"/>
     </row>
-    <row r="144" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="144" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="3"/>
       <c r="B144" s="4"/>
       <c r="C144" s="4"/>
     </row>
-    <row r="145" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="145" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="3"/>
       <c r="B145" s="4"/>
       <c r="C145" s="4"/>
     </row>
-    <row r="146" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="146" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="3"/>
       <c r="B146" s="4"/>
       <c r="C146" s="4"/>
     </row>
-    <row r="147" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="147" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="3"/>
       <c r="B147" s="4"/>
       <c r="C147" s="4"/>
     </row>
-    <row r="148" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="148" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="3"/>
       <c r="B148" s="4"/>
       <c r="C148" s="4"/>
     </row>
-    <row r="149" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="149" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="3"/>
       <c r="B149" s="4"/>
       <c r="C149" s="4"/>
     </row>
-    <row r="150" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="150" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="3"/>
       <c r="B150" s="4"/>
       <c r="C150" s="4"/>
     </row>
-    <row r="151" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="151" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="3"/>
       <c r="B151" s="4"/>
       <c r="C151" s="4"/>
     </row>
-    <row r="152" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="152" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="3"/>
       <c r="B152" s="4"/>
       <c r="C152" s="4"/>
     </row>
-    <row r="153" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="153" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="3"/>
       <c r="B153" s="4"/>
       <c r="C153" s="4"/>
     </row>
-    <row r="154" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="154" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="3"/>
       <c r="B154" s="4"/>
       <c r="C154" s="4"/>
     </row>
-    <row r="155" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="155" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="3"/>
       <c r="B155" s="4"/>
       <c r="C155" s="4"/>
     </row>
-    <row r="156" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="156" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="3"/>
       <c r="B156" s="4"/>
       <c r="C156" s="4"/>
     </row>
-    <row r="157" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="157" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="3"/>
       <c r="B157" s="4"/>
       <c r="C157" s="4"/>
     </row>
-    <row r="158" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="158" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="3"/>
       <c r="B158" s="4"/>
       <c r="C158" s="4"/>
     </row>
-    <row r="159" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="159" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="3"/>
       <c r="B159" s="4"/>
       <c r="C159" s="4"/>
     </row>
-    <row r="160" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="160" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="3"/>
       <c r="B160" s="4"/>
       <c r="C160" s="4"/>
     </row>
-    <row r="161" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="161" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="3"/>
       <c r="B161" s="4"/>
       <c r="C161" s="4"/>
     </row>
-    <row r="162" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="162" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="3"/>
       <c r="B162" s="4"/>
       <c r="C162" s="4"/>
     </row>
-    <row r="163" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="163" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="3"/>
       <c r="B163" s="4"/>
       <c r="C163" s="4"/>
     </row>
-    <row r="164" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="164" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="3"/>
       <c r="B164" s="4"/>
       <c r="C164" s="4"/>
     </row>
-    <row r="165" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="165" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="3"/>
       <c r="B165" s="4"/>
       <c r="C165" s="4"/>
     </row>
-    <row r="166" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="166" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="3"/>
       <c r="B166" s="4"/>
       <c r="C166" s="4"/>
     </row>
-    <row r="167" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="167" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="3"/>
       <c r="B167" s="4"/>
       <c r="C167" s="4"/>
     </row>
-    <row r="168" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="168" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="3"/>
       <c r="B168" s="4"/>
       <c r="C168" s="4"/>
     </row>
-    <row r="169" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="169" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="3"/>
       <c r="B169" s="4"/>
       <c r="C169" s="4"/>
     </row>
-    <row r="170" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="170" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="3"/>
       <c r="B170" s="4"/>
       <c r="C170" s="4"/>
     </row>
-    <row r="171" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="171" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="3"/>
       <c r="B171" s="4"/>
       <c r="C171" s="4"/>
     </row>
-    <row r="172" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="172" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="3"/>
       <c r="B172" s="4"/>
       <c r="C172" s="4"/>
     </row>
-    <row r="173" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="173" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="3"/>
       <c r="B173" s="4"/>
       <c r="C173" s="4"/>
     </row>
-    <row r="174" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="174" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="3"/>
       <c r="B174" s="4"/>
       <c r="C174" s="4"/>
     </row>
-    <row r="175" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="175" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="3"/>
       <c r="B175" s="4"/>
       <c r="C175" s="4"/>
     </row>
-    <row r="176" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="176" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="3"/>
       <c r="B176" s="4"/>
       <c r="C176" s="4"/>
     </row>
-    <row r="177" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="177" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="3"/>
       <c r="B177" s="4"/>
       <c r="C177" s="4"/>
     </row>
-    <row r="178" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="178" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="3"/>
       <c r="B178" s="4"/>
       <c r="C178" s="4"/>
     </row>
-    <row r="179" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="179" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="3"/>
       <c r="B179" s="4"/>
       <c r="C179" s="4"/>
     </row>
-    <row r="180" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="180" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="3"/>
-      <c r="B180" s="5"/>
-      <c r="C180" s="5"/>
-    </row>
-    <row r="181" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B180" s="4"/>
+      <c r="C180" s="4"/>
+    </row>
+    <row r="181" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="3"/>
       <c r="B181" s="5"/>
       <c r="C181" s="5"/>
     </row>
-    <row r="182" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="182" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="3"/>
       <c r="B182" s="5"/>
       <c r="C182" s="5"/>
     </row>
-    <row r="183" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="183" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="3"/>
       <c r="B183" s="5"/>
       <c r="C183" s="5"/>
     </row>
-    <row r="184" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="184" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="3"/>
       <c r="B184" s="5"/>
       <c r="C184" s="5"/>
     </row>
-    <row r="185" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="185" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="3"/>
-      <c r="B185" s="4"/>
-      <c r="C185" s="4"/>
-    </row>
-    <row r="186" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B185" s="5"/>
+      <c r="C185" s="5"/>
+    </row>
+    <row r="186" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="3"/>
       <c r="B186" s="4"/>
       <c r="C186" s="4"/>
     </row>
-    <row r="187" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="187" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="3"/>
       <c r="B187" s="4"/>
       <c r="C187" s="4"/>
     </row>
-    <row r="188" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="188" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="3"/>
       <c r="B188" s="4"/>
       <c r="C188" s="4"/>
     </row>
-    <row r="189" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="189" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="3"/>
       <c r="B189" s="4"/>
       <c r="C189" s="4"/>
     </row>
-    <row r="190" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="190" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="3"/>
       <c r="B190" s="4"/>
       <c r="C190" s="4"/>
     </row>
-    <row r="191" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="191" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="3"/>
       <c r="B191" s="4"/>
       <c r="C191" s="4"/>
     </row>
-    <row r="192" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="192" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="3"/>
       <c r="B192" s="4"/>
       <c r="C192" s="4"/>
     </row>
-    <row r="193" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="193" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="3"/>
-      <c r="B193" s="5"/>
-      <c r="C193" s="5"/>
-    </row>
-    <row r="194" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B193" s="4"/>
+      <c r="C193" s="4"/>
+    </row>
+    <row r="194" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="3"/>
       <c r="B194" s="5"/>
       <c r="C194" s="5"/>
     </row>
-    <row r="195" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="195" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="3"/>
       <c r="B195" s="5"/>
       <c r="C195" s="5"/>
     </row>
-    <row r="196" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="196" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="3"/>
       <c r="B196" s="5"/>
       <c r="C196" s="5"/>
     </row>
-    <row r="197" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="197" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="3"/>
       <c r="B197" s="5"/>
       <c r="C197" s="5"/>
     </row>
-    <row r="198" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="198" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="3"/>
-      <c r="B198" s="4"/>
-      <c r="C198" s="4"/>
-    </row>
-    <row r="199" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B198" s="5"/>
+      <c r="C198" s="5"/>
+    </row>
+    <row r="199" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="3"/>
       <c r="B199" s="4"/>
       <c r="C199" s="4"/>
     </row>
-    <row r="200" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="200" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="3"/>
       <c r="B200" s="4"/>
       <c r="C200" s="4"/>
     </row>
-    <row r="201" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="201" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="3"/>
       <c r="B201" s="4"/>
       <c r="C201" s="4"/>
     </row>
-    <row r="202" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="202" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="3"/>
       <c r="B202" s="4"/>
       <c r="C202" s="4"/>
     </row>
-    <row r="203" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="203" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="3"/>
       <c r="B203" s="4"/>
       <c r="C203" s="4"/>
     </row>
-    <row r="204" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="204" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="3"/>
       <c r="B204" s="4"/>
       <c r="C204" s="4"/>
     </row>
-    <row r="205" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="205" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="3"/>
       <c r="B205" s="4"/>
       <c r="C205" s="4"/>
     </row>
-    <row r="206" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="206" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="3"/>
       <c r="B206" s="4"/>
       <c r="C206" s="4"/>
     </row>
-    <row r="207" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="207" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="3"/>
       <c r="B207" s="4"/>
       <c r="C207" s="4"/>
     </row>
-    <row r="208" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="208" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="3"/>
       <c r="B208" s="4"/>
       <c r="C208" s="4"/>
     </row>
-    <row r="209" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="209" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="3"/>
       <c r="B209" s="4"/>
       <c r="C209" s="4"/>
     </row>
-    <row r="210" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="210" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="3"/>
       <c r="B210" s="4"/>
       <c r="C210" s="4"/>
     </row>
-    <row r="211" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="211" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="3"/>
       <c r="B211" s="4"/>
       <c r="C211" s="4"/>
     </row>
-    <row r="212" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="212" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="3"/>
       <c r="B212" s="4"/>
       <c r="C212" s="4"/>
     </row>
-    <row r="213" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="213" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="3"/>
       <c r="B213" s="4"/>
       <c r="C213" s="4"/>
     </row>
-    <row r="214" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="214" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="3"/>
       <c r="B214" s="4"/>
       <c r="C214" s="4"/>
     </row>
-    <row r="215" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="215" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="3"/>
       <c r="B215" s="4"/>
       <c r="C215" s="4"/>
     </row>
-    <row r="216" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="216" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="3"/>
       <c r="B216" s="4"/>
       <c r="C216" s="4"/>
     </row>
-    <row r="217" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="217" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="3"/>
       <c r="B217" s="4"/>
       <c r="C217" s="4"/>
     </row>
-    <row r="218" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="218" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="3"/>
       <c r="B218" s="4"/>
       <c r="C218" s="4"/>
     </row>
-    <row r="219" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="219" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="3"/>
       <c r="B219" s="4"/>
       <c r="C219" s="4"/>
     </row>
-    <row r="220" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="220" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="3"/>
       <c r="B220" s="4"/>
       <c r="C220" s="4"/>
     </row>
-    <row r="221" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="221" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="3"/>
       <c r="B221" s="4"/>
       <c r="C221" s="4"/>
     </row>
-    <row r="222" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="222" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="3"/>
       <c r="B222" s="4"/>
       <c r="C222" s="4"/>
     </row>
-    <row r="223" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="223" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="3"/>
       <c r="B223" s="4"/>
       <c r="C223" s="4"/>
     </row>
-    <row r="224" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="224" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="3"/>
       <c r="B224" s="4"/>
       <c r="C224" s="4"/>
     </row>
-    <row r="225" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="225" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="3"/>
       <c r="B225" s="4"/>
       <c r="C225" s="4"/>
     </row>
-    <row r="226" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="226" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="3"/>
       <c r="B226" s="4"/>
       <c r="C226" s="4"/>
     </row>
-    <row r="227" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="227" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="3"/>
       <c r="B227" s="4"/>
       <c r="C227" s="4"/>
     </row>
-    <row r="228" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="228" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="3"/>
       <c r="B228" s="4"/>
       <c r="C228" s="4"/>
     </row>
-    <row r="229" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="229" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="3"/>
       <c r="B229" s="4"/>
       <c r="C229" s="4"/>
     </row>
-    <row r="230" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="230" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="3"/>
       <c r="B230" s="4"/>
       <c r="C230" s="4"/>
     </row>
-    <row r="231" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="231" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="3"/>
       <c r="B231" s="4"/>
       <c r="C231" s="4"/>
     </row>
-    <row r="232" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="232" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="3"/>
       <c r="B232" s="4"/>
       <c r="C232" s="4"/>
     </row>
-    <row r="233" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="233" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="3"/>
       <c r="B233" s="4"/>
       <c r="C233" s="4"/>
     </row>
-    <row r="234" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="234" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="3"/>
       <c r="B234" s="4"/>
       <c r="C234" s="4"/>
     </row>
-    <row r="235" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="235" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="3"/>
       <c r="B235" s="4"/>
       <c r="C235" s="4"/>
     </row>
-    <row r="236" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="236" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="3"/>
       <c r="B236" s="4"/>
       <c r="C236" s="4"/>
     </row>
-    <row r="237" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="237" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="3"/>
       <c r="B237" s="4"/>
       <c r="C237" s="4"/>
     </row>
-    <row r="238" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="238" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="3"/>
       <c r="B238" s="4"/>
       <c r="C238" s="4"/>
     </row>
-    <row r="239" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="239" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="3"/>
       <c r="B239" s="4"/>
       <c r="C239" s="4"/>
     </row>
-    <row r="240" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="240" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="3"/>
       <c r="B240" s="4"/>
       <c r="C240" s="4"/>
     </row>
-    <row r="241" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="241" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="3"/>
       <c r="B241" s="4"/>
       <c r="C241" s="4"/>
     </row>
-    <row r="242" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="242" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="3"/>
       <c r="B242" s="4"/>
       <c r="C242" s="4"/>
     </row>
-    <row r="243" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="243" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="3"/>
       <c r="B243" s="4"/>
       <c r="C243" s="4"/>
     </row>
-    <row r="244" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="244" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="3"/>
       <c r="B244" s="4"/>
       <c r="C244" s="4"/>
     </row>
-    <row r="245" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="245" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="3"/>
       <c r="B245" s="4"/>
       <c r="C245" s="4"/>
     </row>
-    <row r="246" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="246" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="3"/>
       <c r="B246" s="4"/>
       <c r="C246" s="4"/>
     </row>
-    <row r="247" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="247" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="3"/>
       <c r="B247" s="4"/>
       <c r="C247" s="4"/>
     </row>
-    <row r="248" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="248" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="3"/>
       <c r="B248" s="4"/>
       <c r="C248" s="4"/>
     </row>
-    <row r="249" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="249" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="3"/>
       <c r="B249" s="4"/>
       <c r="C249" s="4"/>
     </row>
-    <row r="250" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="250" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="3"/>
       <c r="B250" s="4"/>
       <c r="C250" s="4"/>
     </row>
-    <row r="251" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="251" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="3"/>
       <c r="B251" s="4"/>
       <c r="C251" s="4"/>
     </row>
-    <row r="252" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="252" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="3"/>
       <c r="B252" s="4"/>
       <c r="C252" s="4"/>
     </row>
-    <row r="253" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="253" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="3"/>
       <c r="B253" s="4"/>
       <c r="C253" s="4"/>
     </row>
-    <row r="254" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="254" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="3"/>
       <c r="B254" s="4"/>
       <c r="C254" s="4"/>
     </row>
-    <row r="255" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="255" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="3"/>
       <c r="B255" s="4"/>
       <c r="C255" s="4"/>
     </row>
-    <row r="256" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="256" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A256" s="3"/>
       <c r="B256" s="4"/>
       <c r="C256" s="4"/>
     </row>
-    <row r="257" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="257" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="3"/>
       <c r="B257" s="4"/>
       <c r="C257" s="4"/>
     </row>
-    <row r="258" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="258" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="3"/>
       <c r="B258" s="4"/>
       <c r="C258" s="4"/>
     </row>
-    <row r="259" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="259" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="3"/>
       <c r="B259" s="4"/>
       <c r="C259" s="4"/>
     </row>
-    <row r="260" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="260" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="3"/>
       <c r="B260" s="4"/>
       <c r="C260" s="4"/>
     </row>
-    <row r="261" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="261" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="3"/>
       <c r="B261" s="4"/>
       <c r="C261" s="4"/>
     </row>
-    <row r="262" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="262" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="3"/>
       <c r="B262" s="4"/>
       <c r="C262" s="4"/>
     </row>
-    <row r="263" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="263" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="3"/>
       <c r="B263" s="4"/>
       <c r="C263" s="4"/>
     </row>
-    <row r="264" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="264" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A264" s="3"/>
       <c r="B264" s="4"/>
       <c r="C264" s="4"/>
     </row>
-    <row r="265" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="265" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A265" s="3"/>
       <c r="B265" s="4"/>
       <c r="C265" s="4"/>
     </row>
-    <row r="266" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="266" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A266" s="3"/>
       <c r="B266" s="4"/>
       <c r="C266" s="4"/>
     </row>
-    <row r="267" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="267" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A267" s="3"/>
       <c r="B267" s="4"/>
       <c r="C267" s="4"/>
     </row>
-    <row r="268" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="268" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A268" s="3"/>
       <c r="B268" s="4"/>
       <c r="C268" s="4"/>
     </row>
-    <row r="269" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="269" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A269" s="3"/>
       <c r="B269" s="4"/>
       <c r="C269" s="4"/>
     </row>
-    <row r="270" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="270" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A270" s="3"/>
       <c r="B270" s="4"/>
       <c r="C270" s="4"/>
     </row>
-    <row r="271" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="271" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A271" s="3"/>
       <c r="B271" s="4"/>
       <c r="C271" s="4"/>
     </row>
-    <row r="272" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="272" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A272" s="3"/>
       <c r="B272" s="4"/>
       <c r="C272" s="4"/>
     </row>
-    <row r="273" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="273" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A273" s="3"/>
       <c r="B273" s="4"/>
       <c r="C273" s="4"/>
     </row>
-    <row r="274" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="274" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A274" s="3"/>
       <c r="B274" s="4"/>
       <c r="C274" s="4"/>
     </row>
-    <row r="275" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="275" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A275" s="3"/>
       <c r="B275" s="4"/>
       <c r="C275" s="4"/>
     </row>
-    <row r="276" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="276" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A276" s="3"/>
       <c r="B276" s="4"/>
       <c r="C276" s="4"/>
     </row>
-    <row r="277" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="277" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A277" s="3"/>
       <c r="B277" s="4"/>
       <c r="C277" s="4"/>
     </row>
-    <row r="278" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="278" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A278" s="3"/>
       <c r="B278" s="4"/>
       <c r="C278" s="4"/>
     </row>
-    <row r="279" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="279" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A279" s="3"/>
       <c r="B279" s="4"/>
       <c r="C279" s="4"/>
     </row>
-    <row r="280" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="280" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A280" s="3"/>
       <c r="B280" s="4"/>
       <c r="C280" s="4"/>
     </row>
-    <row r="281" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="281" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A281" s="3"/>
       <c r="B281" s="4"/>
       <c r="C281" s="4"/>
     </row>
-    <row r="282" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="282" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A282" s="3"/>
       <c r="B282" s="4"/>
       <c r="C282" s="4"/>
     </row>
-    <row r="283" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="283" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A283" s="3"/>
       <c r="B283" s="4"/>
       <c r="C283" s="4"/>
     </row>
-    <row r="284" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="284" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A284" s="3"/>
       <c r="B284" s="4"/>
       <c r="C284" s="4"/>
     </row>
-    <row r="285" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="285" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A285" s="3"/>
       <c r="B285" s="4"/>
       <c r="C285" s="4"/>
     </row>
-    <row r="286" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="286" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A286" s="3"/>
       <c r="B286" s="4"/>
       <c r="C286" s="4"/>
     </row>
-    <row r="287" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="287" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A287" s="3"/>
       <c r="B287" s="4"/>
       <c r="C287" s="4"/>
     </row>
-    <row r="288" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="288" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A288" s="3"/>
       <c r="B288" s="4"/>
       <c r="C288" s="4"/>
     </row>
-    <row r="289" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="289" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A289" s="3"/>
       <c r="B289" s="4"/>
       <c r="C289" s="4"/>
     </row>
-    <row r="290" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="290" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A290" s="3"/>
       <c r="B290" s="4"/>
       <c r="C290" s="4"/>
     </row>
-    <row r="291" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="291" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A291" s="3"/>
       <c r="B291" s="4"/>
       <c r="C291" s="4"/>
     </row>
-    <row r="292" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="292" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A292" s="3"/>
       <c r="B292" s="4"/>
       <c r="C292" s="4"/>
     </row>
-    <row r="293" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="293" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A293" s="3"/>
       <c r="B293" s="4"/>
       <c r="C293" s="4"/>
     </row>
-    <row r="294" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="294" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A294" s="3"/>
       <c r="B294" s="4"/>
       <c r="C294" s="4"/>
     </row>
-    <row r="295" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="295" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A295" s="3"/>
       <c r="B295" s="4"/>
       <c r="C295" s="4"/>
     </row>
-    <row r="296" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="296" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A296" s="3"/>
       <c r="B296" s="4"/>
       <c r="C296" s="4"/>
     </row>
-    <row r="297" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="297" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A297" s="3"/>
       <c r="B297" s="4"/>
       <c r="C297" s="4"/>
     </row>
-    <row r="298" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="298" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A298" s="3"/>
       <c r="B298" s="4"/>
       <c r="C298" s="4"/>
     </row>
-    <row r="299" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="299" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A299" s="3"/>
       <c r="B299" s="4"/>
       <c r="C299" s="4"/>
     </row>
-    <row r="300" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="300" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A300" s="3"/>
       <c r="B300" s="4"/>
       <c r="C300" s="4"/>
     </row>
-    <row r="301" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="301" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A301" s="3"/>
       <c r="B301" s="4"/>
       <c r="C301" s="4"/>
     </row>
-    <row r="302" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="302" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A302" s="3"/>
       <c r="B302" s="4"/>
       <c r="C302" s="4"/>
     </row>
-    <row r="303" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="303" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A303" s="3"/>
       <c r="B303" s="4"/>
       <c r="C303" s="4"/>
     </row>
-    <row r="304" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="304" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A304" s="3"/>
       <c r="B304" s="4"/>
       <c r="C304" s="4"/>
     </row>
-    <row r="305" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="305" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A305" s="3"/>
       <c r="B305" s="4"/>
       <c r="C305" s="4"/>
     </row>
-    <row r="306" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="306" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A306" s="3"/>
       <c r="B306" s="4"/>
       <c r="C306" s="4"/>
     </row>
-    <row r="307" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="307" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A307" s="3"/>
       <c r="B307" s="4"/>
       <c r="C307" s="4"/>
     </row>
-    <row r="308" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="308" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A308" s="3"/>
       <c r="B308" s="4"/>
       <c r="C308" s="4"/>
     </row>
-    <row r="309" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="309" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A309" s="3"/>
       <c r="B309" s="4"/>
       <c r="C309" s="4"/>
     </row>
-    <row r="310" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="310" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A310" s="3"/>
       <c r="B310" s="4"/>
       <c r="C310" s="4"/>
     </row>
-    <row r="311" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="311" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A311" s="3"/>
       <c r="B311" s="4"/>
       <c r="C311" s="4"/>
     </row>
-    <row r="312" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="312" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A312" s="3"/>
       <c r="B312" s="4"/>
       <c r="C312" s="4"/>
     </row>
-    <row r="313" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="313" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A313" s="3"/>
       <c r="B313" s="4"/>
       <c r="C313" s="4"/>
     </row>
-    <row r="314" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="314" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A314" s="3"/>
       <c r="B314" s="4"/>
       <c r="C314" s="4"/>
     </row>
-    <row r="315" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="315" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A315" s="3"/>
       <c r="B315" s="4"/>
       <c r="C315" s="4"/>
     </row>
-    <row r="316" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="316" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A316" s="3"/>
       <c r="B316" s="4"/>
       <c r="C316" s="4"/>
     </row>
-    <row r="317" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="317" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A317" s="3"/>
       <c r="B317" s="4"/>
       <c r="C317" s="4"/>
     </row>
-    <row r="318" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="318" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A318" s="3"/>
       <c r="B318" s="4"/>
       <c r="C318" s="4"/>
     </row>
-    <row r="319" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="319" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A319" s="3"/>
       <c r="B319" s="4"/>
       <c r="C319" s="4"/>
     </row>
-    <row r="320" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="320" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A320" s="3"/>
       <c r="B320" s="4"/>
       <c r="C320" s="4"/>
     </row>
-    <row r="321" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="321" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A321" s="3"/>
       <c r="B321" s="4"/>
       <c r="C321" s="4"/>
     </row>
-    <row r="322" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="322" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A322" s="3"/>
       <c r="B322" s="4"/>
       <c r="C322" s="4"/>
     </row>
-    <row r="323" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="323" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A323" s="3"/>
       <c r="B323" s="4"/>
       <c r="C323" s="4"/>
     </row>
-    <row r="324" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="324" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A324" s="3"/>
       <c r="B324" s="4"/>
       <c r="C324" s="4"/>
     </row>
-    <row r="325" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="325" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A325" s="3"/>
       <c r="B325" s="4"/>
       <c r="C325" s="4"/>
     </row>
-    <row r="326" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="326" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A326" s="3"/>
       <c r="B326" s="4"/>
       <c r="C326" s="4"/>
     </row>
-    <row r="327" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="327" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A327" s="3"/>
       <c r="B327" s="4"/>
       <c r="C327" s="4"/>
     </row>
-    <row r="328" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="328" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A328" s="3"/>
       <c r="B328" s="4"/>
       <c r="C328" s="4"/>
     </row>
-    <row r="329" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="329" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A329" s="3"/>
       <c r="B329" s="4"/>
       <c r="C329" s="4"/>
     </row>
-    <row r="330" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="330" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A330" s="3"/>
       <c r="B330" s="4"/>
       <c r="C330" s="4"/>
     </row>
-    <row r="331" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="331" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A331" s="3"/>
       <c r="B331" s="4"/>
       <c r="C331" s="4"/>
     </row>
-    <row r="332" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="332" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A332" s="3"/>
       <c r="B332" s="4"/>
       <c r="C332" s="4"/>
     </row>
-    <row r="333" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="333" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A333" s="3"/>
       <c r="B333" s="4"/>
       <c r="C333" s="4"/>
     </row>
-    <row r="334" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="334" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A334" s="3"/>
       <c r="B334" s="4"/>
       <c r="C334" s="4"/>
     </row>
-    <row r="335" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="335" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A335" s="3"/>
       <c r="B335" s="4"/>
       <c r="C335" s="4"/>
     </row>
-    <row r="336" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="336" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A336" s="3"/>
       <c r="B336" s="4"/>
       <c r="C336" s="4"/>
     </row>
-    <row r="337" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="337" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A337" s="3"/>
-      <c r="B337" s="3"/>
+      <c r="B337" s="4"/>
       <c r="C337" s="4"/>
     </row>
-    <row r="338" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="338" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A338" s="3"/>
-      <c r="B338" s="4"/>
+      <c r="B338" s="3"/>
       <c r="C338" s="4"/>
     </row>
-    <row r="339" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="339" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A339" s="3"/>
       <c r="B339" s="4"/>
       <c r="C339" s="4"/>
     </row>
-    <row r="340" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="340" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A340" s="3"/>
       <c r="B340" s="4"/>
       <c r="C340" s="4"/>
     </row>
-    <row r="341" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="341" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A341" s="3"/>
       <c r="B341" s="4"/>
       <c r="C341" s="4"/>
     </row>
-    <row r="342" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="342" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A342" s="3"/>
       <c r="B342" s="4"/>
       <c r="C342" s="4"/>
     </row>
-    <row r="343" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="343" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A343" s="3"/>
       <c r="B343" s="4"/>
       <c r="C343" s="4"/>
     </row>
-    <row r="344" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="344" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A344" s="3"/>
       <c r="B344" s="4"/>
       <c r="C344" s="4"/>
     </row>
-    <row r="345" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="345" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A345" s="3"/>
       <c r="B345" s="4"/>
       <c r="C345" s="4"/>
     </row>
-    <row r="346" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="346" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A346" s="3"/>
       <c r="B346" s="4"/>
       <c r="C346" s="4"/>
     </row>
-    <row r="347" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="347" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A347" s="3"/>
       <c r="B347" s="4"/>
       <c r="C347" s="4"/>
     </row>
-    <row r="348" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="348" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A348" s="3"/>
       <c r="B348" s="4"/>
       <c r="C348" s="4"/>
     </row>
-    <row r="349" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="349" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A349" s="3"/>
       <c r="B349" s="4"/>
       <c r="C349" s="4"/>
     </row>
-    <row r="350" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="350" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A350" s="3"/>
       <c r="B350" s="4"/>
       <c r="C350" s="4"/>
     </row>
-    <row r="351" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="351" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A351" s="3"/>
       <c r="B351" s="4"/>
       <c r="C351" s="4"/>
     </row>
-    <row r="352" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="352" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A352" s="3"/>
       <c r="B352" s="4"/>
       <c r="C352" s="4"/>
     </row>
-    <row r="353" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="353" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A353" s="3"/>
       <c r="B353" s="4"/>
       <c r="C353" s="4"/>
     </row>
-    <row r="354" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="354" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A354" s="3"/>
       <c r="B354" s="4"/>
       <c r="C354" s="4"/>
     </row>
-    <row r="355" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="355" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A355" s="3"/>
       <c r="B355" s="4"/>
       <c r="C355" s="4"/>
     </row>
-    <row r="356" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="356" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A356" s="3"/>
       <c r="B356" s="4"/>
       <c r="C356" s="4"/>
     </row>
-    <row r="357" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="357" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A357" s="3"/>
       <c r="B357" s="4"/>
       <c r="C357" s="4"/>
     </row>
-    <row r="358" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="358" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A358" s="3"/>
       <c r="B358" s="4"/>
       <c r="C358" s="4"/>
     </row>
-    <row r="359" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="359" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A359" s="3"/>
       <c r="B359" s="4"/>
       <c r="C359" s="4"/>
     </row>
-    <row r="360" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="360" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A360" s="3"/>
       <c r="B360" s="4"/>
       <c r="C360" s="4"/>
     </row>
-    <row r="361" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="361" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A361" s="3"/>
       <c r="B361" s="4"/>
       <c r="C361" s="4"/>
     </row>
-    <row r="362" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="362" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A362" s="3"/>
       <c r="B362" s="4"/>
       <c r="C362" s="4"/>
     </row>
-    <row r="363" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="363" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A363" s="3"/>
       <c r="B363" s="4"/>
       <c r="C363" s="4"/>
     </row>
-    <row r="364" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="364" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A364" s="3"/>
       <c r="B364" s="4"/>
       <c r="C364" s="4"/>
     </row>
-    <row r="365" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="365" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A365" s="3"/>
       <c r="B365" s="4"/>
       <c r="C365" s="4"/>
     </row>
-    <row r="366" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="366" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A366" s="3"/>
       <c r="B366" s="4"/>
       <c r="C366" s="4"/>
     </row>
-    <row r="367" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="367" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A367" s="3"/>
       <c r="B367" s="4"/>
       <c r="C367" s="4"/>
     </row>
-    <row r="368" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="368" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A368" s="3"/>
       <c r="B368" s="4"/>
       <c r="C368" s="4"/>
     </row>
-    <row r="369" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="369" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A369" s="3"/>
       <c r="B369" s="4"/>
       <c r="C369" s="4"/>
     </row>
-    <row r="370" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="370" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A370" s="3"/>
       <c r="B370" s="4"/>
       <c r="C370" s="4"/>
     </row>
-    <row r="371" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="371" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A371" s="3"/>
       <c r="B371" s="4"/>
       <c r="C371" s="4"/>
     </row>
-    <row r="372" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="372" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A372" s="3"/>
-      <c r="B372" s="3"/>
+      <c r="B372" s="4"/>
       <c r="C372" s="4"/>
     </row>
-    <row r="373" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="373" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A373" s="3"/>
       <c r="B373" s="3"/>
       <c r="C373" s="4"/>
     </row>
-    <row r="374" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="374" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A374" s="3"/>
-      <c r="B374" s="4"/>
+      <c r="B374" s="3"/>
       <c r="C374" s="4"/>
     </row>
-    <row r="375" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="375" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A375" s="3"/>
       <c r="B375" s="4"/>
       <c r="C375" s="4"/>
     </row>
-    <row r="376" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="376" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A376" s="3"/>
       <c r="B376" s="4"/>
       <c r="C376" s="4"/>
     </row>
-    <row r="377" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="377" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A377" s="3"/>
       <c r="B377" s="4"/>
       <c r="C377" s="4"/>
     </row>
-    <row r="378" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="378" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A378" s="3"/>
       <c r="B378" s="4"/>
       <c r="C378" s="4"/>
     </row>
-    <row r="379" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="379" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A379" s="3"/>
       <c r="B379" s="4"/>
       <c r="C379" s="4"/>
     </row>
-    <row r="380" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="380" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A380" s="3"/>
       <c r="B380" s="4"/>
       <c r="C380" s="4"/>
     </row>
-    <row r="381" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="381" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A381" s="3"/>
       <c r="B381" s="4"/>
       <c r="C381" s="4"/>
     </row>
-    <row r="382" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="382" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A382" s="3"/>
       <c r="B382" s="4"/>
       <c r="C382" s="4"/>
     </row>
-    <row r="383" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="383" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A383" s="3"/>
       <c r="B383" s="4"/>
       <c r="C383" s="4"/>
     </row>
-    <row r="384" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="384" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A384" s="3"/>
       <c r="B384" s="4"/>
       <c r="C384" s="4"/>
     </row>
-    <row r="385" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="385" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A385" s="3"/>
       <c r="B385" s="4"/>
       <c r="C385" s="4"/>
     </row>
-    <row r="386" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="386" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A386" s="3"/>
       <c r="B386" s="4"/>
       <c r="C386" s="4"/>
     </row>
-    <row r="387" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="387" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A387" s="3"/>
       <c r="B387" s="4"/>
       <c r="C387" s="4"/>
     </row>
-    <row r="388" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="388" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A388" s="3"/>
       <c r="B388" s="4"/>
       <c r="C388" s="4"/>
     </row>
-    <row r="389" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="389" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A389" s="3"/>
       <c r="B389" s="4"/>
       <c r="C389" s="4"/>
     </row>
-    <row r="390" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="390" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A390" s="3"/>
       <c r="B390" s="4"/>
       <c r="C390" s="4"/>
     </row>
-    <row r="391" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="391" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A391" s="3"/>
       <c r="B391" s="4"/>
       <c r="C391" s="4"/>
     </row>
-    <row r="392" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="392" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A392" s="3"/>
       <c r="B392" s="4"/>
       <c r="C392" s="4"/>
     </row>
-    <row r="393" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="393" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A393" s="3"/>
       <c r="B393" s="4"/>
       <c r="C393" s="4"/>
     </row>
-    <row r="394" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="394" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A394" s="3"/>
       <c r="B394" s="4"/>
       <c r="C394" s="4"/>
     </row>
-    <row r="395" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="395" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A395" s="3"/>
       <c r="B395" s="4"/>
       <c r="C395" s="4"/>
     </row>
-    <row r="396" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="396" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A396" s="3"/>
       <c r="B396" s="4"/>
       <c r="C396" s="4"/>
     </row>
-    <row r="397" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="397" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A397" s="3"/>
       <c r="B397" s="4"/>
       <c r="C397" s="4"/>
     </row>
-    <row r="398" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="398" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A398" s="3"/>
       <c r="B398" s="4"/>
       <c r="C398" s="4"/>
     </row>
-    <row r="399" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="399" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A399" s="3"/>
       <c r="B399" s="4"/>
       <c r="C399" s="4"/>
     </row>
-    <row r="400" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="400" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A400" s="3"/>
       <c r="B400" s="4"/>
       <c r="C400" s="4"/>
     </row>
-    <row r="401" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="401" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A401" s="3"/>
       <c r="B401" s="4"/>
       <c r="C401" s="4"/>
     </row>
-    <row r="402" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="402" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A402" s="3"/>
       <c r="B402" s="4"/>
       <c r="C402" s="4"/>
     </row>
-    <row r="403" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="403" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A403" s="3"/>
       <c r="B403" s="4"/>
       <c r="C403" s="4"/>
     </row>
-    <row r="404" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="404" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A404" s="3"/>
       <c r="B404" s="4"/>
       <c r="C404" s="4"/>
     </row>
-    <row r="405" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="405" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A405" s="3"/>
       <c r="B405" s="4"/>
       <c r="C405" s="4"/>
     </row>
-    <row r="406" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="406" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A406" s="3"/>
       <c r="B406" s="4"/>
       <c r="C406" s="4"/>
     </row>
-    <row r="407" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="407" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A407" s="3"/>
       <c r="B407" s="4"/>
       <c r="C407" s="4"/>
     </row>
-    <row r="408" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="408" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A408" s="3"/>
       <c r="B408" s="4"/>
       <c r="C408" s="4"/>
     </row>
-    <row r="409" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="409" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A409" s="3"/>
       <c r="B409" s="4"/>
       <c r="C409" s="4"/>
     </row>
-    <row r="410" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="410" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A410" s="3"/>
       <c r="B410" s="4"/>
       <c r="C410" s="4"/>
     </row>
-    <row r="411" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="411" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A411" s="3"/>
       <c r="B411" s="4"/>
       <c r="C411" s="4"/>
     </row>
-    <row r="412" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="412" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A412" s="3"/>
       <c r="B412" s="4"/>
       <c r="C412" s="4"/>
     </row>
-    <row r="413" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="413" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A413" s="3"/>
       <c r="B413" s="4"/>
       <c r="C413" s="4"/>
     </row>
-    <row r="414" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="414" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A414" s="3"/>
       <c r="B414" s="4"/>
       <c r="C414" s="4"/>
     </row>
-    <row r="415" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="415" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A415" s="3"/>
       <c r="B415" s="4"/>
       <c r="C415" s="4"/>
     </row>
-    <row r="416" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="416" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A416" s="3"/>
       <c r="B416" s="4"/>
       <c r="C416" s="4"/>
     </row>
-    <row r="417" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="417" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A417" s="3"/>
       <c r="B417" s="4"/>
       <c r="C417" s="4"/>
     </row>
-    <row r="418" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="418" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A418" s="3"/>
       <c r="B418" s="4"/>
       <c r="C418" s="4"/>
     </row>
-    <row r="419" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="419" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A419" s="3"/>
       <c r="B419" s="4"/>
       <c r="C419" s="4"/>
     </row>
-    <row r="420" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="420" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A420" s="3"/>
       <c r="B420" s="4"/>
       <c r="C420" s="4"/>
     </row>
-    <row r="421" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="421" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A421" s="3"/>
       <c r="B421" s="4"/>
       <c r="C421" s="4"/>
     </row>
-    <row r="422" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="422" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A422" s="3"/>
       <c r="B422" s="4"/>
       <c r="C422" s="4"/>
     </row>
-    <row r="423" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="423" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A423" s="3"/>
       <c r="B423" s="4"/>
       <c r="C423" s="4"/>
     </row>
-    <row r="424" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="424" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A424" s="3"/>
       <c r="B424" s="4"/>
       <c r="C424" s="4"/>
     </row>
-    <row r="425" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="425" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A425" s="3"/>
       <c r="B425" s="4"/>
       <c r="C425" s="4"/>
     </row>
-    <row r="426" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="426" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A426" s="3"/>
       <c r="B426" s="4"/>
       <c r="C426" s="4"/>
     </row>
-    <row r="427" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="427" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A427" s="3"/>
       <c r="B427" s="4"/>
       <c r="C427" s="4"/>
     </row>
-    <row r="428" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="428" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A428" s="3"/>
       <c r="B428" s="4"/>
       <c r="C428" s="4"/>
     </row>
-    <row r="429" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="429" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A429" s="3"/>
       <c r="B429" s="4"/>
       <c r="C429" s="4"/>
     </row>
-    <row r="430" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="430" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A430" s="3"/>
       <c r="B430" s="4"/>
       <c r="C430" s="4"/>
     </row>
-    <row r="431" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="431" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A431" s="3"/>
       <c r="B431" s="4"/>
       <c r="C431" s="4"/>
     </row>
-    <row r="432" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="432" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A432" s="3"/>
       <c r="B432" s="4"/>
       <c r="C432" s="4"/>
     </row>
-    <row r="433" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="433" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A433" s="3"/>
       <c r="B433" s="4"/>
       <c r="C433" s="4"/>
     </row>
-    <row r="434" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="434" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A434" s="3"/>
       <c r="B434" s="4"/>
       <c r="C434" s="4"/>
     </row>
-    <row r="435" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="435" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A435" s="3"/>
       <c r="B435" s="4"/>
       <c r="C435" s="4"/>
     </row>
-    <row r="436" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="436" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A436" s="3"/>
       <c r="B436" s="4"/>
       <c r="C436" s="4"/>
     </row>
-    <row r="437" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="437" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A437" s="3"/>
       <c r="B437" s="4"/>
       <c r="C437" s="4"/>
     </row>
-    <row r="438" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="438" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A438" s="3"/>
       <c r="B438" s="4"/>
       <c r="C438" s="4"/>
     </row>
-    <row r="439" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="439" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A439" s="3"/>
       <c r="B439" s="4"/>
       <c r="C439" s="4"/>
     </row>
-    <row r="440" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="440" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A440" s="3"/>
       <c r="B440" s="4"/>
       <c r="C440" s="4"/>
     </row>
-    <row r="441" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="441" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A441" s="3"/>
       <c r="B441" s="4"/>
       <c r="C441" s="4"/>
     </row>
-    <row r="442" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="442" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A442" s="3"/>
       <c r="B442" s="4"/>
       <c r="C442" s="4"/>
     </row>
-    <row r="443" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="443" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A443" s="3"/>
       <c r="B443" s="4"/>
       <c r="C443" s="4"/>
     </row>
-    <row r="444" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="444" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A444" s="3"/>
       <c r="B444" s="4"/>
       <c r="C444" s="4"/>
     </row>
-    <row r="445" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="445" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A445" s="3"/>
       <c r="B445" s="4"/>
       <c r="C445" s="4"/>
     </row>
-    <row r="446" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="446" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A446" s="3"/>
       <c r="B446" s="4"/>
       <c r="C446" s="4"/>
     </row>
-    <row r="447" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="447" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A447" s="3"/>
-      <c r="B447" s="3"/>
-      <c r="C447" s="3"/>
-    </row>
-    <row r="448" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B447" s="4"/>
+      <c r="C447" s="4"/>
+    </row>
+    <row r="448" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A448" s="3"/>
-      <c r="B448" s="4"/>
-      <c r="C448" s="4"/>
-    </row>
-    <row r="449" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B448" s="3"/>
+      <c r="C448" s="3"/>
+    </row>
+    <row r="449" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A449" s="3"/>
       <c r="B449" s="4"/>
       <c r="C449" s="4"/>
     </row>
-    <row r="450" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="450" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A450" s="3"/>
       <c r="B450" s="4"/>
       <c r="C450" s="4"/>
     </row>
-    <row r="451" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="451" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A451" s="3"/>
       <c r="B451" s="4"/>
       <c r="C451" s="4"/>
     </row>
-    <row r="452" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="452" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A452" s="3"/>
       <c r="B452" s="4"/>
       <c r="C452" s="4"/>
     </row>
-    <row r="453" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="453" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A453" s="3"/>
       <c r="B453" s="4"/>
       <c r="C453" s="4"/>
     </row>
-    <row r="454" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="454" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A454" s="3"/>
       <c r="B454" s="4"/>
       <c r="C454" s="4"/>
     </row>
-    <row r="455" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="455" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A455" s="3"/>
       <c r="B455" s="4"/>
       <c r="C455" s="4"/>
     </row>
-    <row r="456" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="456" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A456" s="3"/>
       <c r="B456" s="4"/>
       <c r="C456" s="4"/>
     </row>
-    <row r="457" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="457" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A457" s="3"/>
       <c r="B457" s="4"/>
       <c r="C457" s="4"/>
     </row>
-    <row r="458" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="458" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A458" s="3"/>
       <c r="B458" s="4"/>
       <c r="C458" s="4"/>
     </row>
-    <row r="459" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="459" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A459" s="3"/>
       <c r="B459" s="4"/>
       <c r="C459" s="4"/>
     </row>
-    <row r="460" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="460" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A460" s="3"/>
-      <c r="B460" s="3"/>
-      <c r="C460" s="3"/>
-    </row>
-    <row r="461" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B460" s="4"/>
+      <c r="C460" s="4"/>
+    </row>
+    <row r="461" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A461" s="3"/>
       <c r="B461" s="3"/>
       <c r="C461" s="3"/>
     </row>
-    <row r="462" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="462" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A462" s="3"/>
       <c r="B462" s="3"/>
       <c r="C462" s="3"/>
     </row>
-    <row r="463" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="463" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A463" s="3"/>
       <c r="B463" s="3"/>
       <c r="C463" s="3"/>
     </row>
-    <row r="464" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="464" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A464" s="3"/>
       <c r="B464" s="3"/>
       <c r="C464" s="3"/>
     </row>
-    <row r="465" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="465" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A465" s="3"/>
-      <c r="B465" s="4"/>
-      <c r="C465" s="4"/>
-    </row>
-    <row r="466" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B465" s="3"/>
+      <c r="C465" s="3"/>
+    </row>
+    <row r="466" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A466" s="3"/>
       <c r="B466" s="4"/>
       <c r="C466" s="4"/>
     </row>
-    <row r="467" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="467" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A467" s="3"/>
       <c r="B467" s="4"/>
       <c r="C467" s="4"/>
     </row>
-    <row r="468" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="468" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A468" s="3"/>
       <c r="B468" s="4"/>
       <c r="C468" s="4"/>
     </row>
-    <row r="469" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="469" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A469" s="3"/>
       <c r="B469" s="4"/>
       <c r="C469" s="4"/>
     </row>
-    <row r="470" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="470" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A470" s="3"/>
       <c r="B470" s="4"/>
       <c r="C470" s="4"/>
     </row>
-    <row r="471" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="471" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A471" s="3"/>
       <c r="B471" s="4"/>
       <c r="C471" s="4"/>
     </row>
-    <row r="472" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="472" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A472" s="3"/>
       <c r="B472" s="4"/>
       <c r="C472" s="4"/>
     </row>
-    <row r="473" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="473" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A473" s="3"/>
       <c r="B473" s="4"/>
       <c r="C473" s="4"/>
     </row>
-    <row r="474" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="474" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A474" s="3"/>
       <c r="B474" s="4"/>
       <c r="C474" s="4"/>
     </row>
-    <row r="475" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="475" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A475" s="3"/>
       <c r="B475" s="4"/>
       <c r="C475" s="4"/>
     </row>
-    <row r="476" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="476" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A476" s="3"/>
       <c r="B476" s="4"/>
       <c r="C476" s="4"/>
     </row>
-    <row r="477" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="477" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A477" s="3"/>
       <c r="B477" s="4"/>
       <c r="C477" s="4"/>
     </row>
-    <row r="478" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="478" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A478" s="3"/>
       <c r="B478" s="4"/>
       <c r="C478" s="4"/>
     </row>
-    <row r="479" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="479" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A479" s="3"/>
       <c r="B479" s="4"/>
       <c r="C479" s="4"/>
     </row>
-    <row r="480" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="480" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A480" s="3"/>
-      <c r="B480" s="3"/>
-      <c r="C480" s="3"/>
-    </row>
-    <row r="481" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B480" s="4"/>
+      <c r="C480" s="4"/>
+    </row>
+    <row r="481" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A481" s="3"/>
       <c r="B481" s="3"/>
       <c r="C481" s="3"/>
     </row>
+    <row r="482" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A482" s="3"/>
+      <c r="B482" s="3"/>
+      <c r="C482" s="3"/>
+    </row>
   </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/tools/languages.xlsx
+++ b/tools/languages.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macbook/projects/hieunm/xiangqi/Tools/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24C1AFBA-3AF9-2C49-AC72-E3C8A74393EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE7EE2C6-BCB0-804D-8121-32BDDF94284C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15880" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,16 +16,11 @@
     <sheet name="languages" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0" iterateDelta="1E-4"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="418">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="443">
   <si>
     <t>Key</t>
   </si>
@@ -327,6 +322,15 @@
     <t>Đóng</t>
   </si>
   <si>
+    <t>settings.change-password</t>
+  </si>
+  <si>
+    <t>Change password</t>
+  </si>
+  <si>
+    <t>Đổi mật khẩu</t>
+  </si>
+  <si>
     <t>popup.alert.title</t>
   </si>
   <si>
@@ -396,36 +400,42 @@
     <t>Thoát phòng</t>
   </si>
   <si>
+    <t>room.actions.confirm-leave</t>
+  </si>
+  <si>
+    <t>Are you sure you want to leave room?</t>
+  </si>
+  <si>
+    <t>Bạn có chắc muốn rời bàn chơi?</t>
+  </si>
+  <si>
+    <t>room.info.waiting-user</t>
+  </si>
+  <si>
+    <t>Waiting player…</t>
+  </si>
+  <si>
+    <t>Đang chờ người chơi…</t>
+  </si>
+  <si>
+    <t>game.general.captured</t>
+  </si>
+  <si>
     <t>General has been captured. Room over</t>
   </si>
   <si>
     <t>Tướng đã bị bắt. Game kết thúc</t>
   </si>
   <si>
+    <t>game.general.in-check</t>
+  </si>
+  <si>
     <t>Your general is under attack</t>
   </si>
   <si>
     <t>Tướng của bạn đang bị chiếu</t>
   </si>
   <si>
-    <t>room.actions.confirm-leave</t>
-  </si>
-  <si>
-    <t>Are you sure you want to leave room?</t>
-  </si>
-  <si>
-    <t>Bạn có chắc muốn rời bàn chơi?</t>
-  </si>
-  <si>
-    <t>room.info.waiting-user</t>
-  </si>
-  <si>
-    <t>Waiting player…</t>
-  </si>
-  <si>
-    <t>Đang chờ người chơi…</t>
-  </si>
-  <si>
     <t>login.page.title</t>
   </si>
   <si>
@@ -1122,6 +1132,15 @@
     <t>Thiếu cookie token làm mới</t>
   </si>
   <si>
+    <t>refresh-token.messages.mismatch-or-expired</t>
+  </si>
+  <si>
+    <t>Refresh token mismatch or expired</t>
+  </si>
+  <si>
+    <t>Thiếu refresh token hoặc đã hết hạn</t>
+  </si>
+  <si>
     <t>refresh-token.messages.success</t>
   </si>
   <si>
@@ -1257,28 +1276,79 @@
     <t>Token hợp lệ</t>
   </si>
   <si>
-    <t>refresh-token.messages.mismatch-or-expired</t>
-  </si>
-  <si>
-    <t>Refresh token mismatch or expired</t>
-  </si>
-  <si>
-    <t>Thiếu refresh token hoặc đã hết hạn</t>
-  </si>
-  <si>
-    <t>settings.change-password</t>
-  </si>
-  <si>
-    <t>Change password</t>
-  </si>
-  <si>
-    <t>Đổi mật khẩu</t>
-  </si>
-  <si>
-    <t>game.general.in-check</t>
-  </si>
-  <si>
-    <t>game.general.captured</t>
+    <t>room.actions.confirm-surrender</t>
+  </si>
+  <si>
+    <t>Are you sure you want to surrender?</t>
+  </si>
+  <si>
+    <t>Bạn có chắc chắn muốn đầu hàng không?</t>
+  </si>
+  <si>
+    <t>surrender.messages.game-already-finished</t>
+  </si>
+  <si>
+    <t>Game is already finished</t>
+  </si>
+  <si>
+    <t>Trò chơi đã kết thúc</t>
+  </si>
+  <si>
+    <t>surrender.messages.game-history-not-found</t>
+  </si>
+  <si>
+    <t>Game history not found</t>
+  </si>
+  <si>
+    <t>Không tìm thấy lịch sử trò chơi</t>
+  </si>
+  <si>
+    <t>surrender.messages.game-not-found</t>
+  </si>
+  <si>
+    <t>Game not found</t>
+  </si>
+  <si>
+    <t>Không tìm thấy trò chơi</t>
+  </si>
+  <si>
+    <t>surrender.messages.internal-server-error</t>
+  </si>
+  <si>
+    <t>surrender.messages.invalid-game-id</t>
+  </si>
+  <si>
+    <t>Invalid game ID</t>
+  </si>
+  <si>
+    <t>ID trò chơi không hợp lệ</t>
+  </si>
+  <si>
+    <t>surrender.messages.invalid-surrender-player</t>
+  </si>
+  <si>
+    <t>You are not a player in this game</t>
+  </si>
+  <si>
+    <t>Bạn không phải là người chơi trong trò chơi này</t>
+  </si>
+  <si>
+    <t>surrender.messages.opponent-not-found</t>
+  </si>
+  <si>
+    <t>Opponent not found</t>
+  </si>
+  <si>
+    <t>Không tìm thấy đối thủ</t>
+  </si>
+  <si>
+    <t>surrender.messages.success</t>
+  </si>
+  <si>
+    <t>Surrendered</t>
+  </si>
+  <si>
+    <t>Đã đầu hàng</t>
   </si>
 </sst>
 </file>
@@ -1938,13 +2008,13 @@
     </row>
     <row r="39" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
-        <v>413</v>
+        <v>100</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>414</v>
+        <v>101</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>415</v>
+        <v>102</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1954,112 +2024,112 @@
     </row>
     <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B49" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="B49" s="4" t="s">
+      <c r="C49" s="4" t="s">
         <v>128</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B50" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="B50" s="4" t="s">
+      <c r="C50" s="4" t="s">
         <v>131</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -2069,24 +2139,24 @@
     </row>
     <row r="52" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="3" t="s">
-        <v>417</v>
+        <v>132</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
-        <v>416</v>
+        <v>135</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -2096,145 +2166,145 @@
     </row>
     <row r="55" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="3" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="3" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="57" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="3" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="3" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="3" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
     </row>
     <row r="61" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="3" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
     </row>
     <row r="62" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="3" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="3" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
     </row>
     <row r="65" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
     </row>
     <row r="66" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="3" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
     </row>
     <row r="67" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="3" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="68" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -2244,321 +2314,322 @@
     </row>
     <row r="69" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="3" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
     </row>
     <row r="70" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="3" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="71" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
     </row>
     <row r="72" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="3" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>175</v>
-      </c>
-    </row>
+        <v>180</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" ht="16" x14ac:dyDescent="0.2"/>
     <row r="74" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="3" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
     </row>
     <row r="75" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="3" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
     </row>
     <row r="76" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="3" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
     </row>
     <row r="77" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="3" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
     </row>
     <row r="78" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="3" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
     </row>
     <row r="79" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="3" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
     </row>
     <row r="80" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="3" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
     </row>
     <row r="81" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="3" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
     </row>
     <row r="82" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="3" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
     </row>
     <row r="83" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="3" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
     </row>
     <row r="84" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="3" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
     </row>
     <row r="85" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="3" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
     </row>
     <row r="86" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="3" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
     </row>
     <row r="87" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="3" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
     </row>
     <row r="88" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="3" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
     </row>
     <row r="89" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="3" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
     </row>
     <row r="90" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="3" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
     </row>
     <row r="91" spans="1:3" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="3" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
     </row>
     <row r="92" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="3" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
     </row>
     <row r="93" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="3" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
     </row>
     <row r="94" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
     </row>
     <row r="95" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="3" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
     </row>
     <row r="96" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="3" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
     </row>
     <row r="97" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="3" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
     </row>
     <row r="98" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="3" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
     </row>
     <row r="99" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -2568,68 +2639,68 @@
     </row>
     <row r="100" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="3" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
     </row>
     <row r="101" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="3" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
     </row>
     <row r="102" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="3" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
     </row>
     <row r="103" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="3" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
     </row>
     <row r="104" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="4" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
     </row>
     <row r="105" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="4" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
     </row>
     <row r="106" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -2639,90 +2710,90 @@
     </row>
     <row r="107" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="4" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
     </row>
     <row r="108" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="4" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
     </row>
     <row r="109" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="B109" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="B109" s="4" t="s">
-        <v>238</v>
-      </c>
       <c r="C109" s="4" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
     </row>
     <row r="110" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="4" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
     </row>
     <row r="111" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="4" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
     </row>
     <row r="112" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="4" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
     </row>
     <row r="113" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="4" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
     </row>
     <row r="114" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="4" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
     </row>
     <row r="115" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -2730,686 +2801,686 @@
       <c r="B115" s="4"/>
       <c r="C115" s="4"/>
     </row>
-    <row r="116" spans="1:3" ht="36" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="4" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3" ht="36" x14ac:dyDescent="0.2">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="4" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="4" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="4" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="4" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3" ht="36" x14ac:dyDescent="0.2">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="4" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3" ht="36" x14ac:dyDescent="0.2">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="4" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="4" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="C123" s="4" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="124" spans="1:3" ht="36" x14ac:dyDescent="0.2">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="4" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="125" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="4" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="126" spans="1:3" ht="36" x14ac:dyDescent="0.2">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="4" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="127" spans="1:3" ht="36" x14ac:dyDescent="0.2">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="4" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="128" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="4" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="C128" s="4" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="129" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="4" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="C129" s="4" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="130" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="4" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="B131" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="C131" s="4" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A132" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="B132" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="C132" s="4" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A133" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="B133" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="C133" s="4" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A134" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="B134" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="B131" s="4" t="s">
+      <c r="C134" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="C131" s="4" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="132" spans="1:3" ht="18" x14ac:dyDescent="0.2">
-      <c r="A132" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="B132" s="4" t="s">
-        <v>306</v>
-      </c>
-      <c r="C132" s="4" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="133" spans="1:3" ht="36" x14ac:dyDescent="0.2">
-      <c r="A133" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="B133" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="C133" s="4" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="134" spans="1:3" ht="36" x14ac:dyDescent="0.2">
-      <c r="A134" s="4" t="s">
-        <v>311</v>
-      </c>
-      <c r="B134" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="C134" s="4" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="135" spans="1:3" ht="36" x14ac:dyDescent="0.2">
+    </row>
+    <row r="135" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="4" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="C135" s="4" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="136" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="4" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="137" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="4" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="C137" s="4" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="138" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="4" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="139" spans="1:3" ht="36" x14ac:dyDescent="0.2">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="4" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="C139" s="4" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="140" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="4" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="141" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="B141" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="C141" s="4" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A142" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="B142" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="C142" s="4" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A143" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="B143" s="4" t="s">
         <v>326</v>
       </c>
-      <c r="B141" s="4" t="s">
+      <c r="C143" s="4" t="s">
         <v>327</v>
       </c>
-      <c r="C141" s="4" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="142" spans="1:3" ht="18" x14ac:dyDescent="0.2">
-      <c r="A142" s="4" t="s">
+    </row>
+    <row r="144" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A144" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="B144" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="C144" s="4" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A145" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="B145" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="C145" s="4" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A146" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="B146" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="C146" s="4" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A147" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="B147" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="C147" s="4" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A148" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="B148" s="4" t="s">
         <v>329</v>
       </c>
-      <c r="B142" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="C142" s="4" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="143" spans="1:3" ht="36" x14ac:dyDescent="0.2">
-      <c r="A143" s="4" t="s">
+      <c r="C148" s="4" t="s">
         <v>330</v>
       </c>
-      <c r="B143" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="C143" s="4" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="144" spans="1:3" ht="18" x14ac:dyDescent="0.2">
-      <c r="A144" s="4" t="s">
-        <v>331</v>
-      </c>
-      <c r="B144" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="C144" s="4" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="145" spans="1:3" ht="18" x14ac:dyDescent="0.2">
-      <c r="A145" s="4" t="s">
-        <v>334</v>
-      </c>
-      <c r="B145" s="4" t="s">
-        <v>335</v>
-      </c>
-      <c r="C145" s="4" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="146" spans="1:3" ht="18" x14ac:dyDescent="0.2">
-      <c r="A146" s="4" t="s">
-        <v>337</v>
-      </c>
-      <c r="B146" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="C146" s="4" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="147" spans="1:3" ht="18" x14ac:dyDescent="0.2">
-      <c r="A147" s="4" t="s">
-        <v>338</v>
-      </c>
-      <c r="B147" s="4" t="s">
-        <v>339</v>
-      </c>
-      <c r="C147" s="4" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="148" spans="1:3" ht="18" x14ac:dyDescent="0.2">
-      <c r="A148" s="4" t="s">
-        <v>341</v>
-      </c>
-      <c r="B148" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="C148" s="4" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="149" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="149" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="4" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="C149" s="4" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="150" spans="1:3" ht="36" x14ac:dyDescent="0.2">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="4" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="151" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="4" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="C151" s="4" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="152" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="4" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="C152" s="4" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="153" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="4" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="C153" s="4" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="154" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="4" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="155" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="4" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="C155" s="4" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="156" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="4" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="157" spans="1:3" ht="36" x14ac:dyDescent="0.2">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="4" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="158" spans="1:3" ht="36" x14ac:dyDescent="0.2">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="B158" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="C158" s="4" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A159" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="B159" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="C159" s="4" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A160" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="B160" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="C160" s="4" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A161" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="B161" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="C161" s="4" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A162" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="B162" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="C162" s="4" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A163" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="B163" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="C163" s="4" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A164" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="B164" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="C164" s="4" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A165" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="B165" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="C165" s="4" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A166" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B166" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="C166" s="4" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A167" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="B167" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="C167" s="4" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A168" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="B168" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="C168" s="4" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A169" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="B169" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="C169" s="4" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A170" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="B170" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="C170" s="4" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A171" s="4" t="s">
+        <v>403</v>
+      </c>
+      <c r="B171" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="C171" s="4" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A172" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="B172" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="C172" s="4" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A173" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="B173" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="C173" s="4" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A174" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="B174" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="C174" s="4" t="s">
         <v>410</v>
       </c>
-      <c r="B158" s="4" t="s">
+    </row>
+    <row r="175" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A175" s="4" t="s">
         <v>411</v>
       </c>
-      <c r="C158" s="4" t="s">
+      <c r="B175" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="C175" s="4" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A176" s="4" t="s">
         <v>412</v>
       </c>
-    </row>
-    <row r="159" spans="1:3" ht="18" x14ac:dyDescent="0.2">
-      <c r="A159" s="4" t="s">
-        <v>365</v>
-      </c>
-      <c r="B159" s="4" t="s">
-        <v>366</v>
-      </c>
-      <c r="C159" s="4" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="160" spans="1:3" ht="18" x14ac:dyDescent="0.2">
-      <c r="A160" s="4" t="s">
-        <v>368</v>
-      </c>
-      <c r="B160" s="4" t="s">
-        <v>369</v>
-      </c>
-      <c r="C160" s="4" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="161" spans="1:3" ht="18" x14ac:dyDescent="0.2">
-      <c r="A161" s="4" t="s">
-        <v>371</v>
-      </c>
-      <c r="B161" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="C161" s="4" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="162" spans="1:3" ht="36" x14ac:dyDescent="0.2">
-      <c r="A162" s="4" t="s">
-        <v>372</v>
-      </c>
-      <c r="B162" s="4" t="s">
-        <v>373</v>
-      </c>
-      <c r="C162" s="4" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="163" spans="1:3" ht="18" x14ac:dyDescent="0.2">
-      <c r="A163" s="4" t="s">
-        <v>375</v>
-      </c>
-      <c r="B163" s="4" t="s">
-        <v>376</v>
-      </c>
-      <c r="C163" s="4" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="164" spans="1:3" ht="18" x14ac:dyDescent="0.2">
-      <c r="A164" s="4" t="s">
-        <v>378</v>
-      </c>
-      <c r="B164" s="4" t="s">
-        <v>379</v>
-      </c>
-      <c r="C164" s="4" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="165" spans="1:3" ht="36" x14ac:dyDescent="0.2">
-      <c r="A165" s="4" t="s">
-        <v>381</v>
-      </c>
-      <c r="B165" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="C165" s="4" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="166" spans="1:3" ht="36" x14ac:dyDescent="0.2">
-      <c r="A166" s="4" t="s">
-        <v>382</v>
-      </c>
-      <c r="B166" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="C166" s="4" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="167" spans="1:3" ht="18" x14ac:dyDescent="0.2">
-      <c r="A167" s="4" t="s">
-        <v>383</v>
-      </c>
-      <c r="B167" s="4" t="s">
-        <v>384</v>
-      </c>
-      <c r="C167" s="4" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="168" spans="1:3" ht="36" x14ac:dyDescent="0.2">
-      <c r="A168" s="4" t="s">
-        <v>386</v>
-      </c>
-      <c r="B168" s="4" t="s">
-        <v>387</v>
-      </c>
-      <c r="C168" s="4" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="169" spans="1:3" ht="36" x14ac:dyDescent="0.2">
-      <c r="A169" s="4" t="s">
-        <v>389</v>
-      </c>
-      <c r="B169" s="4" t="s">
-        <v>390</v>
-      </c>
-      <c r="C169" s="4" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="170" spans="1:3" ht="18" x14ac:dyDescent="0.2">
-      <c r="A170" s="4" t="s">
-        <v>392</v>
-      </c>
-      <c r="B170" s="4" t="s">
-        <v>393</v>
-      </c>
-      <c r="C170" s="4" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="171" spans="1:3" ht="18" x14ac:dyDescent="0.2">
-      <c r="A171" s="4" t="s">
-        <v>395</v>
-      </c>
-      <c r="B171" s="4" t="s">
-        <v>396</v>
-      </c>
-      <c r="C171" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="172" spans="1:3" ht="36" x14ac:dyDescent="0.2">
-      <c r="A172" s="4" t="s">
-        <v>398</v>
-      </c>
-      <c r="B172" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="C172" s="4" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="173" spans="1:3" ht="36" x14ac:dyDescent="0.2">
-      <c r="A173" s="4" t="s">
-        <v>399</v>
-      </c>
-      <c r="B173" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="C173" s="4" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="174" spans="1:3" ht="18" x14ac:dyDescent="0.2">
-      <c r="A174" s="4" t="s">
-        <v>400</v>
-      </c>
-      <c r="B174" s="4" t="s">
-        <v>401</v>
-      </c>
-      <c r="C174" s="4" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="175" spans="1:3" ht="18" x14ac:dyDescent="0.2">
-      <c r="A175" s="4" t="s">
-        <v>403</v>
-      </c>
-      <c r="B175" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="C175" s="4" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="176" spans="1:3" ht="18" x14ac:dyDescent="0.2">
-      <c r="A176" s="4" t="s">
-        <v>404</v>
-      </c>
       <c r="B176" s="4" t="s">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="C176" s="4" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="177" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="4" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
     </row>
     <row r="178" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3417,62 +3488,116 @@
       <c r="B178" s="4"/>
       <c r="C178" s="4"/>
     </row>
-    <row r="179" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A179" s="4"/>
-      <c r="B179" s="4"/>
-      <c r="C179" s="4"/>
-    </row>
-    <row r="180" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A180" s="4"/>
-      <c r="B180" s="4"/>
-      <c r="C180" s="4"/>
-    </row>
-    <row r="181" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A181" s="4"/>
-      <c r="B181" s="4"/>
-      <c r="C181" s="4"/>
-    </row>
-    <row r="182" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A182" s="4"/>
-      <c r="B182" s="4"/>
-      <c r="C182" s="4"/>
-    </row>
-    <row r="183" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A183" s="4"/>
-      <c r="B183" s="4"/>
-      <c r="C183" s="4"/>
-    </row>
-    <row r="184" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A184" s="4"/>
-      <c r="B184" s="4"/>
-      <c r="C184" s="4"/>
-    </row>
-    <row r="185" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A185" s="4"/>
-      <c r="B185" s="4"/>
-      <c r="C185" s="4"/>
-    </row>
-    <row r="186" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A186" s="4"/>
-      <c r="B186" s="4"/>
-      <c r="C186" s="4"/>
-    </row>
-    <row r="187" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A187" s="4"/>
-      <c r="B187" s="4"/>
-      <c r="C187" s="4"/>
-    </row>
-    <row r="188" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+      <c r="A179" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="B179" s="4" t="s">
+        <v>419</v>
+      </c>
+      <c r="C179" s="4" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+      <c r="A180" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="B180" s="4" t="s">
+        <v>422</v>
+      </c>
+      <c r="C180" s="4" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" ht="36" x14ac:dyDescent="0.2">
+      <c r="A181" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="B181" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="C181" s="4" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+      <c r="A182" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="B182" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="C182" s="4" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+      <c r="A183" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="B183" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="C183" s="4" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+      <c r="A184" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="B184" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="C184" s="4" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" ht="36" x14ac:dyDescent="0.2">
+      <c r="A185" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="B185" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="C185" s="4" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+      <c r="A186" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="B186" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="C186" s="4" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+      <c r="A187" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="B187" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="C187" s="4" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A188" s="4"/>
       <c r="B188" s="4"/>
       <c r="C188" s="4"/>
     </row>
-    <row r="189" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A189" s="4"/>
       <c r="B189" s="4"/>
       <c r="C189" s="4"/>
     </row>
-    <row r="190" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A190" s="4"/>
       <c r="B190" s="4"/>
       <c r="C190" s="4"/>
@@ -3747,6 +3872,15 @@
       <c r="B244" s="4"/>
       <c r="C244" s="4"/>
     </row>
+    <row r="245" spans="1:3" ht="16" x14ac:dyDescent="0.2"/>
+    <row r="246" spans="1:3" ht="16" x14ac:dyDescent="0.2"/>
+    <row r="247" spans="1:3" ht="16" x14ac:dyDescent="0.2"/>
+    <row r="248" spans="1:3" ht="16" x14ac:dyDescent="0.2"/>
+    <row r="249" spans="1:3" ht="16" x14ac:dyDescent="0.2"/>
+    <row r="250" spans="1:3" ht="16" x14ac:dyDescent="0.2"/>
+    <row r="251" spans="1:3" ht="16" x14ac:dyDescent="0.2"/>
+    <row r="252" spans="1:3" ht="16" x14ac:dyDescent="0.2"/>
+    <row r="253" spans="1:3" ht="16" x14ac:dyDescent="0.2"/>
     <row r="1048118" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="1048119" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="1048120" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>

--- a/tools/languages.xlsx
+++ b/tools/languages.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macbook/projects/hieunm/xiangqi/Tools/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\xiangqi\tools\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE7EE2C6-BCB0-804D-8121-32BDDF94284C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16BD24EA-3C6B-4918-999A-F39828FF7C84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15880" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="languages" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="449">
   <si>
     <t>Key</t>
   </si>
@@ -1349,6 +1349,24 @@
   </si>
   <si>
     <t>Đã đầu hàng</t>
+  </si>
+  <si>
+    <t>room.actions.draw</t>
+  </si>
+  <si>
+    <t>Draw</t>
+  </si>
+  <si>
+    <t>Hòa</t>
+  </si>
+  <si>
+    <t>room.actions.confirm-draw</t>
+  </si>
+  <si>
+    <t>Are you sure you want to draw?</t>
+  </si>
+  <si>
+    <t>Bạn có chắc chắn muốn hòa không?</t>
   </si>
 </sst>
 </file>
@@ -1598,15 +1616,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C1048121"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:C1048123"/>
+  <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="40.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="41.6640625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="42.1640625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="40.625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="41.625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="42.125" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1617,7 +1635,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>3</v>
       </c>
@@ -1628,7 +1646,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
@@ -1639,7 +1657,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>9</v>
       </c>
@@ -1650,7 +1668,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>12</v>
       </c>
@@ -1661,7 +1679,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>15</v>
       </c>
@@ -1672,7 +1690,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>18</v>
       </c>
@@ -1683,12 +1701,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="4"/>
       <c r="C8" s="3"/>
     </row>
-    <row r="9" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>21</v>
       </c>
@@ -1699,7 +1717,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>24</v>
       </c>
@@ -1710,7 +1728,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>27</v>
       </c>
@@ -1721,7 +1739,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>30</v>
       </c>
@@ -1732,7 +1750,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>33</v>
       </c>
@@ -1743,7 +1761,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>36</v>
       </c>
@@ -1754,7 +1772,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>37</v>
       </c>
@@ -1765,7 +1783,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>40</v>
       </c>
@@ -1776,7 +1794,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>43</v>
       </c>
@@ -1787,7 +1805,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>46</v>
       </c>
@@ -1798,12 +1816,12 @@
         <v>48</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
     </row>
-    <row r="20" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>49</v>
       </c>
@@ -1814,7 +1832,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>52</v>
       </c>
@@ -1825,7 +1843,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>55</v>
       </c>
@@ -1836,7 +1854,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>58</v>
       </c>
@@ -1847,7 +1865,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>61</v>
       </c>
@@ -1858,7 +1876,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>64</v>
       </c>
@@ -1869,7 +1887,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>67</v>
       </c>
@@ -1880,7 +1898,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>70</v>
       </c>
@@ -1891,7 +1909,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>73</v>
       </c>
@@ -1902,7 +1920,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>76</v>
       </c>
@@ -1913,7 +1931,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>79</v>
       </c>
@@ -1924,7 +1942,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>82</v>
       </c>
@@ -1935,7 +1953,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>85</v>
       </c>
@@ -1946,7 +1964,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>88</v>
       </c>
@@ -1957,12 +1975,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3"/>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
     </row>
-    <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>90</v>
       </c>
@@ -1973,7 +1991,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>91</v>
       </c>
@@ -1984,7 +2002,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>94</v>
       </c>
@@ -1995,7 +2013,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>97</v>
       </c>
@@ -2006,7 +2024,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>100</v>
       </c>
@@ -2017,12 +2035,12 @@
         <v>102</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
     </row>
-    <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>103</v>
       </c>
@@ -2033,7 +2051,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>106</v>
       </c>
@@ -2044,7 +2062,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>109</v>
       </c>
@@ -2055,7 +2073,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>111</v>
       </c>
@@ -2066,7 +2084,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>114</v>
       </c>
@@ -2077,7 +2095,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>117</v>
       </c>
@@ -2088,7 +2106,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>120</v>
       </c>
@@ -2099,7 +2117,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>123</v>
       </c>
@@ -2110,7 +2128,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>126</v>
       </c>
@@ -2121,7 +2139,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>129</v>
       </c>
@@ -2132,12 +2150,12 @@
         <v>131</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3"/>
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
     </row>
-    <row r="52" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>132</v>
       </c>
@@ -2148,7 +2166,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
         <v>135</v>
       </c>
@@ -2159,12 +2177,12 @@
         <v>137</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3"/>
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
     </row>
-    <row r="55" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
         <v>138</v>
       </c>
@@ -2175,7 +2193,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
         <v>141</v>
       </c>
@@ -2186,7 +2204,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
         <v>142</v>
       </c>
@@ -2197,7 +2215,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
         <v>145</v>
       </c>
@@ -2208,7 +2226,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
         <v>146</v>
       </c>
@@ -2219,7 +2237,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
         <v>149</v>
       </c>
@@ -2230,7 +2248,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
         <v>150</v>
       </c>
@@ -2241,7 +2259,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
         <v>153</v>
       </c>
@@ -2252,7 +2270,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
         <v>156</v>
       </c>
@@ -2263,7 +2281,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
         <v>159</v>
       </c>
@@ -2274,7 +2292,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
         <v>162</v>
       </c>
@@ -2285,7 +2303,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
         <v>165</v>
       </c>
@@ -2296,7 +2314,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
         <v>168</v>
       </c>
@@ -2307,12 +2325,12 @@
         <v>140</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="3"/>
       <c r="B68" s="4"/>
       <c r="C68" s="4"/>
     </row>
-    <row r="69" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
         <v>169</v>
       </c>
@@ -2323,7 +2341,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
         <v>172</v>
       </c>
@@ -2334,7 +2352,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
         <v>175</v>
       </c>
@@ -2345,7 +2363,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
         <v>178</v>
       </c>
@@ -2356,8 +2374,8 @@
         <v>180</v>
       </c>
     </row>
-    <row r="73" spans="1:3" ht="16" x14ac:dyDescent="0.2"/>
-    <row r="74" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
         <v>181</v>
       </c>
@@ -2368,7 +2386,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="75" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
         <v>184</v>
       </c>
@@ -2379,7 +2397,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
         <v>187</v>
       </c>
@@ -2390,7 +2408,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
         <v>188</v>
       </c>
@@ -2401,7 +2419,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
         <v>191</v>
       </c>
@@ -2412,7 +2430,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="79" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
         <v>192</v>
       </c>
@@ -2423,7 +2441,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
         <v>195</v>
       </c>
@@ -2434,7 +2452,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="81" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
         <v>197</v>
       </c>
@@ -2445,7 +2463,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="82" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
         <v>198</v>
       </c>
@@ -2456,7 +2474,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
         <v>201</v>
       </c>
@@ -2467,7 +2485,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="84" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
         <v>202</v>
       </c>
@@ -2478,7 +2496,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="85" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
         <v>205</v>
       </c>
@@ -2489,7 +2507,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="86" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
         <v>206</v>
       </c>
@@ -2500,7 +2518,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="87" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
         <v>209</v>
       </c>
@@ -2511,7 +2529,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="88" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
         <v>212</v>
       </c>
@@ -2522,7 +2540,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
         <v>215</v>
       </c>
@@ -2533,7 +2551,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="90" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
         <v>218</v>
       </c>
@@ -2544,7 +2562,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="91" spans="1:3" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:3" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
         <v>219</v>
       </c>
@@ -2555,7 +2573,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="92" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
         <v>222</v>
       </c>
@@ -2566,7 +2584,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="93" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
         <v>223</v>
       </c>
@@ -2577,7 +2595,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="94" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
         <v>224</v>
       </c>
@@ -2588,7 +2606,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="95" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
         <v>225</v>
       </c>
@@ -2599,7 +2617,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="96" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
         <v>226</v>
       </c>
@@ -2610,7 +2628,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="97" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
         <v>229</v>
       </c>
@@ -2621,7 +2639,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="98" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
         <v>230</v>
       </c>
@@ -2632,12 +2650,12 @@
         <v>144</v>
       </c>
     </row>
-    <row r="99" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="3"/>
       <c r="B99" s="4"/>
       <c r="C99" s="4"/>
     </row>
-    <row r="100" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
         <v>231</v>
       </c>
@@ -2648,7 +2666,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="101" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
         <v>233</v>
       </c>
@@ -2659,7 +2677,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="102" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
         <v>234</v>
       </c>
@@ -2670,7 +2688,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="103" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
         <v>235</v>
       </c>
@@ -2681,7 +2699,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="104" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
         <v>236</v>
       </c>
@@ -2692,7 +2710,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="105" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
         <v>239</v>
       </c>
@@ -2703,12 +2721,12 @@
         <v>241</v>
       </c>
     </row>
-    <row r="106" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="4"/>
       <c r="B106" s="4"/>
       <c r="C106" s="4"/>
     </row>
-    <row r="107" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="4" t="s">
         <v>242</v>
       </c>
@@ -2719,7 +2737,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="108" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
         <v>245</v>
       </c>
@@ -2730,7 +2748,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="109" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="4" t="s">
         <v>248</v>
       </c>
@@ -2741,7 +2759,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="110" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
         <v>249</v>
       </c>
@@ -2752,7 +2770,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="111" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
         <v>252</v>
       </c>
@@ -2763,7 +2781,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="112" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
         <v>255</v>
       </c>
@@ -2774,7 +2792,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="113" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="4" t="s">
         <v>258</v>
       </c>
@@ -2785,7 +2803,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="114" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
         <v>260</v>
       </c>
@@ -2796,12 +2814,12 @@
         <v>244</v>
       </c>
     </row>
-    <row r="115" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="4"/>
       <c r="B115" s="4"/>
       <c r="C115" s="4"/>
     </row>
-    <row r="116" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
         <v>262</v>
       </c>
@@ -2812,7 +2830,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="117" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="4" t="s">
         <v>265</v>
       </c>
@@ -2823,7 +2841,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="118" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
         <v>268</v>
       </c>
@@ -2834,7 +2852,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="119" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="4" t="s">
         <v>271</v>
       </c>
@@ -2845,7 +2863,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="120" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
         <v>274</v>
       </c>
@@ -2856,7 +2874,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="121" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="4" t="s">
         <v>277</v>
       </c>
@@ -2867,7 +2885,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="122" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
         <v>280</v>
       </c>
@@ -2878,7 +2896,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="123" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="4" t="s">
         <v>283</v>
       </c>
@@ -2889,7 +2907,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="124" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
         <v>286</v>
       </c>
@@ -2900,7 +2918,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="125" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="4" t="s">
         <v>289</v>
       </c>
@@ -2911,7 +2929,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="126" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
         <v>292</v>
       </c>
@@ -2922,7 +2940,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="127" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="4" t="s">
         <v>295</v>
       </c>
@@ -2933,7 +2951,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="128" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
         <v>298</v>
       </c>
@@ -2944,7 +2962,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="129" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="4" t="s">
         <v>301</v>
       </c>
@@ -2955,7 +2973,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="130" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
         <v>304</v>
       </c>
@@ -2966,7 +2984,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="131" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="4" t="s">
         <v>307</v>
       </c>
@@ -2977,7 +2995,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="132" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
         <v>310</v>
       </c>
@@ -2988,7 +3006,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="133" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="4" t="s">
         <v>313</v>
       </c>
@@ -2999,7 +3017,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="134" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
         <v>316</v>
       </c>
@@ -3010,7 +3028,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="135" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="4" t="s">
         <v>317</v>
       </c>
@@ -3021,7 +3039,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="136" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
         <v>318</v>
       </c>
@@ -3032,7 +3050,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="137" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="4" t="s">
         <v>321</v>
       </c>
@@ -3043,7 +3061,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="138" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
         <v>324</v>
       </c>
@@ -3054,7 +3072,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="139" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="4" t="s">
         <v>325</v>
       </c>
@@ -3065,7 +3083,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="140" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
         <v>328</v>
       </c>
@@ -3076,7 +3094,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="141" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="4" t="s">
         <v>331</v>
       </c>
@@ -3087,7 +3105,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="142" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
         <v>334</v>
       </c>
@@ -3098,7 +3116,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="143" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="4" t="s">
         <v>335</v>
       </c>
@@ -3109,7 +3127,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="144" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
         <v>336</v>
       </c>
@@ -3120,7 +3138,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="145" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="4" t="s">
         <v>339</v>
       </c>
@@ -3131,7 +3149,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="146" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
         <v>342</v>
       </c>
@@ -3142,7 +3160,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="147" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="4" t="s">
         <v>343</v>
       </c>
@@ -3153,7 +3171,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="148" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
         <v>346</v>
       </c>
@@ -3164,7 +3182,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="149" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="4" t="s">
         <v>347</v>
       </c>
@@ -3175,7 +3193,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="150" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
         <v>350</v>
       </c>
@@ -3186,7 +3204,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="151" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="4" t="s">
         <v>353</v>
       </c>
@@ -3197,7 +3215,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="152" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
         <v>354</v>
       </c>
@@ -3208,7 +3226,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="153" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="4" t="s">
         <v>357</v>
       </c>
@@ -3219,7 +3237,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="154" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
         <v>360</v>
       </c>
@@ -3230,7 +3248,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="155" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="4" t="s">
         <v>363</v>
       </c>
@@ -3241,7 +3259,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="156" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
         <v>364</v>
       </c>
@@ -3252,7 +3270,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="157" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="4" t="s">
         <v>367</v>
       </c>
@@ -3263,7 +3281,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="158" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
         <v>370</v>
       </c>
@@ -3274,7 +3292,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="159" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="4" t="s">
         <v>373</v>
       </c>
@@ -3285,7 +3303,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="160" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
         <v>376</v>
       </c>
@@ -3296,7 +3314,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="161" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="4" t="s">
         <v>379</v>
       </c>
@@ -3307,7 +3325,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="162" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
         <v>380</v>
       </c>
@@ -3318,7 +3336,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="163" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="4" t="s">
         <v>383</v>
       </c>
@@ -3329,7 +3347,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="164" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
         <v>386</v>
       </c>
@@ -3340,7 +3358,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="165" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="4" t="s">
         <v>389</v>
       </c>
@@ -3351,7 +3369,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="166" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
         <v>390</v>
       </c>
@@ -3362,7 +3380,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="167" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="4" t="s">
         <v>391</v>
       </c>
@@ -3373,7 +3391,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="168" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
         <v>394</v>
       </c>
@@ -3384,7 +3402,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="169" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="4" t="s">
         <v>397</v>
       </c>
@@ -3395,7 +3413,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="170" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
         <v>400</v>
       </c>
@@ -3406,7 +3424,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="171" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="4" t="s">
         <v>403</v>
       </c>
@@ -3417,7 +3435,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="172" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
         <v>406</v>
       </c>
@@ -3428,7 +3446,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="173" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="4" t="s">
         <v>407</v>
       </c>
@@ -3439,7 +3457,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="174" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
         <v>408</v>
       </c>
@@ -3450,7 +3468,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="175" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="4" t="s">
         <v>411</v>
       </c>
@@ -3461,7 +3479,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="176" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
         <v>412</v>
       </c>
@@ -3472,7 +3490,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="177" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="4" t="s">
         <v>415</v>
       </c>
@@ -3483,12 +3501,12 @@
         <v>417</v>
       </c>
     </row>
-    <row r="178" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="4"/>
       <c r="B178" s="4"/>
       <c r="C178" s="4"/>
     </row>
-    <row r="179" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="4" t="s">
         <v>418</v>
       </c>
@@ -3499,392 +3517,406 @@
         <v>420</v>
       </c>
     </row>
-    <row r="180" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="B180" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="C180" s="4" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A181" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="B181" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="C181" s="4" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A182" s="4" t="s">
         <v>421</v>
       </c>
-      <c r="B180" s="4" t="s">
+      <c r="B182" s="4" t="s">
         <v>422</v>
       </c>
-      <c r="C180" s="4" t="s">
+      <c r="C182" s="4" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="181" spans="1:3" ht="36" x14ac:dyDescent="0.2">
-      <c r="A181" s="4" t="s">
+    <row r="183" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A183" s="4" t="s">
         <v>424</v>
       </c>
-      <c r="B181" s="4" t="s">
+      <c r="B183" s="4" t="s">
         <v>425</v>
       </c>
-      <c r="C181" s="4" t="s">
+      <c r="C183" s="4" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="182" spans="1:3" ht="18" x14ac:dyDescent="0.2">
-      <c r="A182" s="4" t="s">
+    <row r="184" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A184" s="4" t="s">
         <v>427</v>
       </c>
-      <c r="B182" s="4" t="s">
+      <c r="B184" s="4" t="s">
         <v>428</v>
       </c>
-      <c r="C182" s="4" t="s">
+      <c r="C184" s="4" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="183" spans="1:3" ht="18" x14ac:dyDescent="0.2">
-      <c r="A183" s="4" t="s">
+    <row r="185" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A185" s="4" t="s">
         <v>430</v>
       </c>
-      <c r="B183" s="4" t="s">
+      <c r="B185" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="C183" s="4" t="s">
+      <c r="C185" s="4" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="184" spans="1:3" ht="18" x14ac:dyDescent="0.2">
-      <c r="A184" s="4" t="s">
+    <row r="186" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A186" s="4" t="s">
         <v>431</v>
       </c>
-      <c r="B184" s="4" t="s">
+      <c r="B186" s="4" t="s">
         <v>432</v>
       </c>
-      <c r="C184" s="4" t="s">
+      <c r="C186" s="4" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="185" spans="1:3" ht="36" x14ac:dyDescent="0.2">
-      <c r="A185" s="4" t="s">
+    <row r="187" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A187" s="4" t="s">
         <v>434</v>
       </c>
-      <c r="B185" s="4" t="s">
+      <c r="B187" s="4" t="s">
         <v>435</v>
       </c>
-      <c r="C185" s="4" t="s">
+      <c r="C187" s="4" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="186" spans="1:3" ht="18" x14ac:dyDescent="0.2">
-      <c r="A186" s="4" t="s">
+    <row r="188" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A188" s="4" t="s">
         <v>437</v>
       </c>
-      <c r="B186" s="4" t="s">
+      <c r="B188" s="4" t="s">
         <v>438</v>
       </c>
-      <c r="C186" s="4" t="s">
+      <c r="C188" s="4" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="187" spans="1:3" ht="18" x14ac:dyDescent="0.2">
-      <c r="A187" s="4" t="s">
+    <row r="189" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A189" s="4" t="s">
         <v>440</v>
       </c>
-      <c r="B187" s="4" t="s">
+      <c r="B189" s="4" t="s">
         <v>441</v>
       </c>
-      <c r="C187" s="4" t="s">
+      <c r="C189" s="4" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="188" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A188" s="4"/>
-      <c r="B188" s="4"/>
-      <c r="C188" s="4"/>
-    </row>
-    <row r="189" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A189" s="4"/>
-      <c r="B189" s="4"/>
-      <c r="C189" s="4"/>
-    </row>
-    <row r="190" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="4"/>
       <c r="B190" s="4"/>
       <c r="C190" s="4"/>
     </row>
-    <row r="191" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A191" s="4"/>
-      <c r="B191" s="4"/>
-      <c r="C191" s="4"/>
-    </row>
-    <row r="192" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A192" s="4"/>
-      <c r="B192" s="4"/>
-      <c r="C192" s="4"/>
-    </row>
-    <row r="193" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="193" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="4"/>
       <c r="B193" s="4"/>
       <c r="C193" s="4"/>
     </row>
-    <row r="194" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="4"/>
       <c r="B194" s="4"/>
       <c r="C194" s="4"/>
     </row>
-    <row r="195" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="4"/>
       <c r="B195" s="4"/>
       <c r="C195" s="4"/>
     </row>
-    <row r="196" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="4"/>
       <c r="B196" s="4"/>
       <c r="C196" s="4"/>
     </row>
-    <row r="197" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="4"/>
       <c r="B197" s="4"/>
       <c r="C197" s="4"/>
     </row>
-    <row r="198" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="4"/>
       <c r="B198" s="4"/>
       <c r="C198" s="4"/>
     </row>
-    <row r="199" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="4"/>
       <c r="B199" s="4"/>
       <c r="C199" s="4"/>
     </row>
-    <row r="200" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="4"/>
       <c r="B200" s="4"/>
       <c r="C200" s="4"/>
     </row>
-    <row r="201" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="4"/>
       <c r="B201" s="4"/>
       <c r="C201" s="4"/>
     </row>
-    <row r="202" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="4"/>
       <c r="B202" s="4"/>
       <c r="C202" s="4"/>
     </row>
-    <row r="203" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="4"/>
       <c r="B203" s="4"/>
       <c r="C203" s="4"/>
     </row>
-    <row r="204" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="4"/>
       <c r="B204" s="4"/>
       <c r="C204" s="4"/>
     </row>
-    <row r="205" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="4"/>
       <c r="B205" s="4"/>
       <c r="C205" s="4"/>
     </row>
-    <row r="206" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="4"/>
       <c r="B206" s="4"/>
       <c r="C206" s="4"/>
     </row>
-    <row r="207" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="4"/>
       <c r="B207" s="4"/>
       <c r="C207" s="4"/>
     </row>
-    <row r="208" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="4"/>
       <c r="B208" s="4"/>
       <c r="C208" s="4"/>
     </row>
-    <row r="209" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="4"/>
       <c r="B209" s="4"/>
       <c r="C209" s="4"/>
     </row>
-    <row r="210" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="4"/>
       <c r="B210" s="4"/>
       <c r="C210" s="4"/>
     </row>
-    <row r="211" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="4"/>
       <c r="B211" s="4"/>
       <c r="C211" s="4"/>
     </row>
-    <row r="212" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="4"/>
       <c r="B212" s="4"/>
       <c r="C212" s="4"/>
     </row>
-    <row r="213" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="4"/>
       <c r="B213" s="4"/>
       <c r="C213" s="4"/>
     </row>
-    <row r="214" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="4"/>
       <c r="B214" s="4"/>
       <c r="C214" s="4"/>
     </row>
-    <row r="215" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="4"/>
       <c r="B215" s="4"/>
       <c r="C215" s="4"/>
     </row>
-    <row r="216" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="4"/>
       <c r="B216" s="4"/>
       <c r="C216" s="4"/>
     </row>
-    <row r="217" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="4"/>
       <c r="B217" s="4"/>
       <c r="C217" s="4"/>
     </row>
-    <row r="218" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="4"/>
       <c r="B218" s="4"/>
       <c r="C218" s="4"/>
     </row>
-    <row r="219" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="4"/>
       <c r="B219" s="4"/>
       <c r="C219" s="4"/>
     </row>
-    <row r="220" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="4"/>
       <c r="B220" s="4"/>
       <c r="C220" s="4"/>
     </row>
-    <row r="221" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="4"/>
       <c r="B221" s="4"/>
       <c r="C221" s="4"/>
     </row>
-    <row r="222" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="4"/>
       <c r="B222" s="4"/>
       <c r="C222" s="4"/>
     </row>
-    <row r="223" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="4"/>
       <c r="B223" s="4"/>
       <c r="C223" s="4"/>
     </row>
-    <row r="224" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="4"/>
       <c r="B224" s="4"/>
       <c r="C224" s="4"/>
     </row>
-    <row r="225" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="4"/>
       <c r="B225" s="4"/>
       <c r="C225" s="4"/>
     </row>
-    <row r="226" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="4"/>
       <c r="B226" s="4"/>
       <c r="C226" s="4"/>
     </row>
-    <row r="227" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="4"/>
       <c r="B227" s="4"/>
       <c r="C227" s="4"/>
     </row>
-    <row r="228" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="4"/>
       <c r="B228" s="4"/>
       <c r="C228" s="4"/>
     </row>
-    <row r="229" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="4"/>
       <c r="B229" s="4"/>
       <c r="C229" s="4"/>
     </row>
-    <row r="230" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="4"/>
       <c r="B230" s="4"/>
       <c r="C230" s="4"/>
     </row>
-    <row r="231" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="4"/>
       <c r="B231" s="4"/>
       <c r="C231" s="4"/>
     </row>
-    <row r="232" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="4"/>
       <c r="B232" s="4"/>
       <c r="C232" s="4"/>
     </row>
-    <row r="233" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="4"/>
       <c r="B233" s="4"/>
       <c r="C233" s="4"/>
     </row>
-    <row r="234" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="4"/>
       <c r="B234" s="4"/>
       <c r="C234" s="4"/>
     </row>
-    <row r="235" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="4"/>
       <c r="B235" s="4"/>
       <c r="C235" s="4"/>
     </row>
-    <row r="236" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="4"/>
       <c r="B236" s="4"/>
       <c r="C236" s="4"/>
     </row>
-    <row r="237" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="4"/>
       <c r="B237" s="4"/>
       <c r="C237" s="4"/>
     </row>
-    <row r="238" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="4"/>
       <c r="B238" s="4"/>
       <c r="C238" s="4"/>
     </row>
-    <row r="239" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="4"/>
       <c r="B239" s="4"/>
       <c r="C239" s="4"/>
     </row>
-    <row r="240" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="4"/>
       <c r="B240" s="4"/>
       <c r="C240" s="4"/>
     </row>
-    <row r="241" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="4"/>
       <c r="B241" s="4"/>
       <c r="C241" s="4"/>
     </row>
-    <row r="242" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="4"/>
       <c r="B242" s="4"/>
       <c r="C242" s="4"/>
     </row>
-    <row r="243" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="4"/>
       <c r="B243" s="4"/>
       <c r="C243" s="4"/>
     </row>
-    <row r="244" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="4"/>
       <c r="B244" s="4"/>
       <c r="C244" s="4"/>
     </row>
-    <row r="245" spans="1:3" ht="16" x14ac:dyDescent="0.2"/>
-    <row r="246" spans="1:3" ht="16" x14ac:dyDescent="0.2"/>
-    <row r="247" spans="1:3" ht="16" x14ac:dyDescent="0.2"/>
-    <row r="248" spans="1:3" ht="16" x14ac:dyDescent="0.2"/>
-    <row r="249" spans="1:3" ht="16" x14ac:dyDescent="0.2"/>
-    <row r="250" spans="1:3" ht="16" x14ac:dyDescent="0.2"/>
-    <row r="251" spans="1:3" ht="16" x14ac:dyDescent="0.2"/>
-    <row r="252" spans="1:3" ht="16" x14ac:dyDescent="0.2"/>
-    <row r="253" spans="1:3" ht="16" x14ac:dyDescent="0.2"/>
-    <row r="1048118" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1048119" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1048120" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1048121" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="245" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A245" s="4"/>
+      <c r="B245" s="4"/>
+      <c r="C245" s="4"/>
+    </row>
+    <row r="246" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A246" s="4"/>
+      <c r="B246" s="4"/>
+      <c r="C246" s="4"/>
+    </row>
+    <row r="247" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="248" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="249" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="250" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="251" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="252" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="253" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="254" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="255" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1048120" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1048121" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1048122" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1048123" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/tools/languages.xlsx
+++ b/tools/languages.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\xiangqi\Tools\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macbook/projects/hieunm/xiangqi/Tools/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81A2B38B-B4E7-4F7D-8910-6323141D19CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BB9B2B3-C6FB-3049-A7FA-075D073916E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="languages" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="471">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="477">
   <si>
     <t>Key</t>
   </si>
@@ -1433,6 +1433,24 @@
   </si>
   <si>
     <t>Trang cá nhân</t>
+  </si>
+  <si>
+    <t>dashboard.popup.pve-mode</t>
+  </si>
+  <si>
+    <t>PVE mode</t>
+  </si>
+  <si>
+    <t>Chơi với máy</t>
+  </si>
+  <si>
+    <t>menu.expired</t>
+  </si>
+  <si>
+    <t>Set expired</t>
+  </si>
+  <si>
+    <t>Hết hạn token</t>
   </si>
 </sst>
 </file>
@@ -1670,14 +1688,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C188"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C190"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
     <col min="2" max="3" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1688,7 +1706,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1699,7 +1717,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -1710,7 +1728,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -1721,7 +1739,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
@@ -1732,7 +1750,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -1743,7 +1761,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
@@ -1754,7 +1772,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>21</v>
       </c>
@@ -1765,7 +1783,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>24</v>
       </c>
@@ -1776,7 +1794,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>27</v>
       </c>
@@ -1787,7 +1805,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>30</v>
       </c>
@@ -1798,7 +1816,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>33</v>
       </c>
@@ -1809,7 +1827,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>36</v>
       </c>
@@ -1820,7 +1838,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>468</v>
       </c>
@@ -1831,669 +1849,669 @@
         <v>470</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B16" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C16" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
+    <row r="17" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B17" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C17" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
+    <row r="18" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B18" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C18" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
+    <row r="19" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B19" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C19" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
+    <row r="20" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B20" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C20" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
+    <row r="21" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B21" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C21" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
+    <row r="22" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B22" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C22" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
+    <row r="23" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B23" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C23" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
+    <row r="24" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B24" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C24" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
+    <row r="25" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B25" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C25" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
+    <row r="26" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B26" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C26" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
+    <row r="27" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B27" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C27" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
+    <row r="28" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B28" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C28" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
+    <row r="29" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B30" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C30" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
+    <row r="31" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B31" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C31" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
+    <row r="32" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B32" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C32" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
+    <row r="33" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B33" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C33" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
+    <row r="34" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B34" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C34" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
+    <row r="35" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B35" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C35" s="1" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
+    <row r="36" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B36" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C36" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
+    <row r="37" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B37" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C37" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
+    <row r="38" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B38" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C38" s="1" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
+    <row r="39" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B39" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C39" s="1" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
+    <row r="40" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B40" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C40" s="1" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
+    <row r="41" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B41" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C41" s="1" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
+    <row r="42" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="B42" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C42" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
+    <row r="43" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B43" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C43" s="1" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
+    <row r="44" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B44" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="C44" s="1" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
+    <row r="45" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="B45" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C45" s="1" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
+    <row r="46" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="B46" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="C46" s="1" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
+    <row r="47" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="B47" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="C47" s="1" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
+    <row r="48" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="B48" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C48" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
+    <row r="49" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="B49" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="C49" s="1" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
+    <row r="50" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="B50" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="C50" s="1" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
+    <row r="51" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="B51" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="C51" s="1" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
+    <row r="52" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="B52" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="C52" s="1" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
+    <row r="53" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="B53" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="C53" s="1" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
+    <row r="54" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="B54" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="C54" s="1" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
+    <row r="55" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="B55" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="C55" s="1" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
+    <row r="56" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="B56" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="C56" s="1" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
+    <row r="57" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="B57" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="C57" s="1" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
+    <row r="58" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="B58" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="C58" s="1" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
+    <row r="59" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="B59" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="C59" s="1" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
+    <row r="60" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="B60" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="C60" s="1" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
+    <row r="61" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="B61" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="C61" s="1" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
+    <row r="62" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="B62" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C60" s="1" t="s">
+      <c r="C62" s="1" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
+    <row r="63" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="B63" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="C61" s="1" t="s">
+      <c r="C63" s="1" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
+    <row r="64" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="B64" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="C62" s="1" t="s">
+      <c r="C64" s="1" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
+    <row r="65" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="B65" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="C65" s="1" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="1" t="s">
+    <row r="66" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="B66" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="C64" s="1" t="s">
+      <c r="C66" s="1" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
+    <row r="67" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="B67" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="C65" s="1" t="s">
+      <c r="C67" s="1" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
+    <row r="68" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="B68" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="C66" s="1" t="s">
+      <c r="C68" s="1" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
+    <row r="69" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="B69" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="C67" s="1" t="s">
+      <c r="C69" s="1" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="1" t="s">
+    <row r="70" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="B68" s="1" t="s">
+      <c r="B70" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="C68" s="1" t="s">
+      <c r="C70" s="1" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="1" t="s">
+    <row r="71" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="B69" s="1" t="s">
+      <c r="B71" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="C69" s="1" t="s">
+      <c r="C71" s="1" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="1" t="s">
+    <row r="72" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="B72" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="C70" s="1" t="s">
+      <c r="C72" s="1" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="1" t="s">
+    <row r="73" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="B71" s="1" t="s">
+      <c r="B73" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="C71" s="1" t="s">
+      <c r="C73" s="1" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="1" t="s">
+    <row r="74" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="B72" s="1" t="s">
+      <c r="B74" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="C72" s="1" t="s">
+      <c r="C74" s="1" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="73" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="1" t="s">
+    <row r="75" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="1" t="s">
         <v>192</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="1" t="s">
-        <v>196</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>157</v>
@@ -2502,240 +2520,240 @@
         <v>158</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B76" s="1" t="s">
+      <c r="B78" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="C76" s="1" t="s">
+      <c r="C78" s="1" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="1" t="s">
+    <row r="79" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="B77" s="1" t="s">
+      <c r="B79" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="C77" s="1" t="s">
+      <c r="C79" s="1" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="1" t="s">
+    <row r="80" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B78" s="1" t="s">
+      <c r="B80" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="C78" s="1" t="s">
+      <c r="C80" s="1" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="79" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="1" t="s">
+    <row r="81" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B79" s="1" t="s">
+      <c r="B81" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="C79" s="1" t="s">
+      <c r="C81" s="1" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="1" t="s">
+    <row r="82" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B80" s="1" t="s">
+      <c r="B82" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="C80" s="1" t="s">
+      <c r="C82" s="1" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="81" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="1" t="s">
+    <row r="83" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="B81" s="1" t="s">
+      <c r="B83" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="C81" s="1" t="s">
+      <c r="C83" s="1" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="82" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="1" t="s">
+    <row r="84" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="B82" s="1" t="s">
+      <c r="B84" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="C82" s="1" t="s">
+      <c r="C84" s="1" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="1" t="s">
+    <row r="85" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A85" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="B83" s="1" t="s">
+      <c r="B85" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="C83" s="1" t="s">
+      <c r="C85" s="1" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="84" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="1" t="s">
+    <row r="86" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="B84" s="1" t="s">
+      <c r="B86" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="C84" s="1" t="s">
+      <c r="C86" s="1" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="85" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="1" t="s">
+    <row r="87" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="B85" s="1" t="s">
+      <c r="B87" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="C85" s="1" t="s">
+      <c r="C87" s="1" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="86" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="1" t="s">
+    <row r="88" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A88" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="B86" s="1" t="s">
+      <c r="B88" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="C86" s="1" t="s">
+      <c r="C88" s="1" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="87" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="1" t="s">
+    <row r="89" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A89" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="B87" s="1" t="s">
+      <c r="B89" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C87" s="1" t="s">
+      <c r="C89" s="1" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="88" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="1" t="s">
+    <row r="90" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="B88" s="1" t="s">
+      <c r="B90" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C88" s="1" t="s">
+      <c r="C90" s="1" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="1" t="s">
+    <row r="91" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A91" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B89" s="1" t="s">
+      <c r="B91" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="C89" s="1" t="s">
+      <c r="C91" s="1" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="90" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="1" t="s">
+    <row r="92" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A92" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="B90" s="1" t="s">
+      <c r="B92" s="1" t="s">
         <v>223</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>154</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="93" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A95" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="B93" s="1" t="s">
+      <c r="B95" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="C93" s="1" t="s">
+      <c r="C95" s="1" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="94" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="1" t="s">
+    <row r="96" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A96" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="B94" s="1" t="s">
+      <c r="B96" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="C94" s="1" t="s">
+      <c r="C96" s="1" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="95" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="1" t="s">
+    <row r="97" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A97" s="1" t="s">
         <v>233</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="1" t="s">
-        <v>239</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>234</v>
@@ -2744,1004 +2762,1026 @@
         <v>235</v>
       </c>
     </row>
-    <row r="98" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A99" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A100" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="B98" s="1" t="s">
+      <c r="B100" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="C98" s="1" t="s">
+      <c r="C100" s="1" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="99" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="1" t="s">
+    <row r="101" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A101" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="B99" s="1" t="s">
+      <c r="B101" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="C99" s="1" t="s">
+      <c r="C101" s="1" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="100" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="1" t="s">
+    <row r="102" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A102" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="B100" s="1" t="s">
+      <c r="B102" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="C100" s="1" t="s">
+      <c r="C102" s="1" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="101" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="1" t="s">
+    <row r="103" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A103" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="B101" s="1" t="s">
+      <c r="B103" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="C101" s="1" t="s">
+      <c r="C103" s="1" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="102" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="1" t="s">
+    <row r="104" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A104" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="B102" s="1" t="s">
+      <c r="B104" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="C102" s="1" t="s">
+      <c r="C104" s="1" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="103" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="1" t="s">
+    <row r="105" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A105" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="B103" s="1" t="s">
+      <c r="B105" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="C103" s="1" t="s">
+      <c r="C105" s="1" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="104" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="1" t="s">
+    <row r="106" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A106" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="B104" s="1" t="s">
+      <c r="B106" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="C104" s="1" t="s">
+      <c r="C106" s="1" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="105" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="1" t="s">
+    <row r="107" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A107" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="B105" s="1" t="s">
+      <c r="B107" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C105" s="1" t="s">
+      <c r="C107" s="1" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="106" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="1" t="s">
+    <row r="108" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A108" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="B106" s="1" t="s">
+      <c r="B108" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="C106" s="1" t="s">
+      <c r="C108" s="1" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="107" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="1" t="s">
+    <row r="109" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A109" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="B107" s="1" t="s">
+      <c r="B109" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="C107" s="1" t="s">
+      <c r="C109" s="1" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="108" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="1" t="s">
+    <row r="110" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A110" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="B108" s="1" t="s">
+      <c r="B110" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="C108" s="1" t="s">
+      <c r="C110" s="1" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="109" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="1" t="s">
+    <row r="111" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A111" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="B109" s="1" t="s">
+      <c r="B111" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="C109" s="1" t="s">
+      <c r="C111" s="1" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="110" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="1" t="s">
+    <row r="112" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A112" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="B110" s="1" t="s">
+      <c r="B112" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="C110" s="1" t="s">
+      <c r="C112" s="1" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="111" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="1" t="s">
+    <row r="113" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A113" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="B111" s="1" t="s">
+      <c r="B113" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="C111" s="1" t="s">
+      <c r="C113" s="1" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="112" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="1" t="s">
+    <row r="114" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A114" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="B112" s="1" t="s">
+      <c r="B114" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="C112" s="1" t="s">
+      <c r="C114" s="1" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="113" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="1" t="s">
+    <row r="115" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A115" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="B113" s="1" t="s">
+      <c r="B115" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="C113" s="1" t="s">
+      <c r="C115" s="1" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="114" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="1" t="s">
+    <row r="116" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A116" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="B114" s="1" t="s">
+      <c r="B116" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="C114" s="1" t="s">
+      <c r="C116" s="1" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="115" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="1" t="s">
+    <row r="117" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A117" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="B115" s="1" t="s">
+      <c r="B117" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="C115" s="1" t="s">
+      <c r="C117" s="1" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="116" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="1" t="s">
+    <row r="118" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A118" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="B116" s="1" t="s">
+      <c r="B118" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="C116" s="1" t="s">
+      <c r="C118" s="1" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="117" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="1" t="s">
+    <row r="119" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A119" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="B117" s="1" t="s">
+      <c r="B119" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="C117" s="1" t="s">
+      <c r="C119" s="1" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="118" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="1" t="s">
+    <row r="120" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A120" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="B118" s="1" t="s">
+      <c r="B120" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="C118" s="1" t="s">
+      <c r="C120" s="1" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="119" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="1" t="s">
+    <row r="121" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A121" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="B119" s="1" t="s">
+      <c r="B121" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="C119" s="1" t="s">
+      <c r="C121" s="1" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="120" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="1" t="s">
+    <row r="122" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A122" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="B120" s="1" t="s">
+      <c r="B122" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="C120" s="1" t="s">
+      <c r="C122" s="1" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="121" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="1" t="s">
+    <row r="123" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A123" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="B121" s="1" t="s">
+      <c r="B123" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="C121" s="1" t="s">
+      <c r="C123" s="1" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="122" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="1" t="s">
+    <row r="124" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A124" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="B122" s="1" t="s">
+      <c r="B124" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="C122" s="1" t="s">
+      <c r="C124" s="1" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="123" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="1" t="s">
+    <row r="125" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A125" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="B123" s="1" t="s">
+      <c r="B125" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="C123" s="1" t="s">
+      <c r="C125" s="1" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="124" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="1" t="s">
+    <row r="126" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A126" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="B124" s="1" t="s">
+      <c r="B126" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="C124" s="1" t="s">
+      <c r="C126" s="1" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="125" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="1" t="s">
+    <row r="127" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A127" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="B125" s="1" t="s">
+      <c r="B127" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="C125" s="1" t="s">
+      <c r="C127" s="1" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="126" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="1" t="s">
+    <row r="128" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A128" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="B126" s="1" t="s">
+      <c r="B128" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="C126" s="1" t="s">
+      <c r="C128" s="1" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="127" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="1" t="s">
+    <row r="129" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A129" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="B127" s="1" t="s">
+      <c r="B129" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="C127" s="1" t="s">
+      <c r="C129" s="1" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="128" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="1" t="s">
+    <row r="130" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A130" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="B128" s="1" t="s">
+      <c r="B130" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="C128" s="1" t="s">
+      <c r="C130" s="1" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="129" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="1" t="s">
+    <row r="131" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A131" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="B129" s="1" t="s">
+      <c r="B131" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="C129" s="1" t="s">
+      <c r="C131" s="1" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="130" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="1" t="s">
+    <row r="132" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A132" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="B130" s="1" t="s">
+      <c r="B132" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="C130" s="1" t="s">
+      <c r="C132" s="1" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="131" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="1" t="s">
+    <row r="133" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A133" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="B131" s="1" t="s">
+      <c r="B133" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="C131" s="1" t="s">
+      <c r="C133" s="1" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="132" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="1" t="s">
+    <row r="134" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A134" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="B132" s="1" t="s">
+      <c r="B134" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="C132" s="1" t="s">
+      <c r="C134" s="1" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="133" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="1" t="s">
+    <row r="135" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A135" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="B133" s="1" t="s">
+      <c r="B135" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="C133" s="1" t="s">
+      <c r="C135" s="1" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="134" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="1" t="s">
+    <row r="136" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A136" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="B134" s="1" t="s">
+      <c r="B136" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="C134" s="1" t="s">
+      <c r="C136" s="1" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="135" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="1" t="s">
+    <row r="137" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A137" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="B135" s="1" t="s">
+      <c r="B137" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="C135" s="1" t="s">
+      <c r="C137" s="1" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="136" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="1" t="s">
+    <row r="138" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A138" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="B136" s="1" t="s">
+      <c r="B138" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="C136" s="1" t="s">
+      <c r="C138" s="1" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="137" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A137" s="1" t="s">
+    <row r="139" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A139" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="B137" s="1" t="s">
+      <c r="B139" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="C137" s="1" t="s">
+      <c r="C139" s="1" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="138" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A138" s="1" t="s">
+    <row r="140" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A140" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="B138" s="1" t="s">
+      <c r="B140" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="C138" s="1" t="s">
+      <c r="C140" s="1" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="139" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="1" t="s">
+    <row r="141" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A141" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="B139" s="1" t="s">
+      <c r="B141" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="C139" s="1" t="s">
+      <c r="C141" s="1" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="140" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="1" t="s">
+    <row r="142" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A142" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="B140" s="1" t="s">
+      <c r="B142" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="C140" s="1" t="s">
+      <c r="C142" s="1" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="141" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="1" t="s">
+    <row r="143" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A143" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="B141" s="1" t="s">
+      <c r="B143" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="C141" s="1" t="s">
+      <c r="C143" s="1" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="142" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A142" s="1" t="s">
+    <row r="144" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A144" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="B142" s="1" t="s">
+      <c r="B144" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="C142" s="1" t="s">
+      <c r="C144" s="1" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="143" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="1" t="s">
+    <row r="145" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A145" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="B143" s="1" t="s">
+      <c r="B145" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="C143" s="1" t="s">
+      <c r="C145" s="1" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="144" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="1" t="s">
+    <row r="146" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A146" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="B144" s="1" t="s">
+      <c r="B146" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="C144" s="1" t="s">
+      <c r="C146" s="1" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="145" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="1" t="s">
+    <row r="147" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A147" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="B145" s="1" t="s">
+      <c r="B147" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="C145" s="1" t="s">
+      <c r="C147" s="1" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="146" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A146" s="1" t="s">
+    <row r="148" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A148" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="B146" s="1" t="s">
+      <c r="B148" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="C146" s="1" t="s">
+      <c r="C148" s="1" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="147" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="1" t="s">
+    <row r="149" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A149" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="B147" s="1" t="s">
+      <c r="B149" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="C147" s="1" t="s">
+      <c r="C149" s="1" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="148" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="1" t="s">
+    <row r="150" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A150" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="B148" s="1" t="s">
+      <c r="B150" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="C148" s="1" t="s">
+      <c r="C150" s="1" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="149" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="1" t="s">
+    <row r="151" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A151" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="B149" s="1" t="s">
+      <c r="B151" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="C149" s="1" t="s">
+      <c r="C151" s="1" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="150" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A150" s="1" t="s">
+    <row r="152" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A152" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="B150" s="1" t="s">
+      <c r="B152" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="C150" s="1" t="s">
+      <c r="C152" s="1" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="151" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="1" t="s">
+    <row r="153" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A153" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="B151" s="1" t="s">
+      <c r="B153" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="C151" s="1" t="s">
+      <c r="C153" s="1" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="152" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="1" t="s">
+    <row r="154" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A154" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="B152" s="1" t="s">
+      <c r="B154" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="C152" s="1" t="s">
+      <c r="C154" s="1" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="153" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="1" t="s">
+    <row r="155" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A155" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="B153" s="1" t="s">
+      <c r="B155" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="C153" s="1" t="s">
+      <c r="C155" s="1" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="154" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A154" s="1" t="s">
+    <row r="156" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A156" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="B154" s="1" t="s">
+      <c r="B156" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="C154" s="1" t="s">
+      <c r="C156" s="1" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="155" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="1" t="s">
+    <row r="157" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A157" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="B155" s="1" t="s">
+      <c r="B157" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="C155" s="1" t="s">
+      <c r="C157" s="1" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="156" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A156" s="1" t="s">
+    <row r="158" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A158" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="B156" s="1" t="s">
+      <c r="B158" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="C156" s="1" t="s">
+      <c r="C158" s="1" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="157" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A157" s="1" t="s">
+    <row r="159" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A159" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="B157" s="1" t="s">
+      <c r="B159" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="C157" s="1" t="s">
+      <c r="C159" s="1" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="158" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="1" t="s">
+    <row r="160" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A160" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="B158" s="1" t="s">
+      <c r="B160" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="C158" s="1" t="s">
+      <c r="C160" s="1" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="159" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A159" s="1" t="s">
+    <row r="161" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A161" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="B159" s="1" t="s">
+      <c r="B161" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="C159" s="1" t="s">
+      <c r="C161" s="1" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="160" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A160" s="1" t="s">
+    <row r="162" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A162" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="B160" s="1" t="s">
+      <c r="B162" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="C160" s="1" t="s">
+      <c r="C162" s="1" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="161" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A161" s="1" t="s">
+    <row r="163" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A163" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="B161" s="1" t="s">
+      <c r="B163" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="C161" s="1" t="s">
+      <c r="C163" s="1" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="162" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A162" s="1" t="s">
+    <row r="164" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A164" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="B162" s="1" t="s">
+      <c r="B164" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="C162" s="1" t="s">
+      <c r="C164" s="1" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="163" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A163" s="1" t="s">
+    <row r="165" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A165" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="B163" s="1" t="s">
+      <c r="B165" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="C163" s="1" t="s">
+      <c r="C165" s="1" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="164" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A164" s="1" t="s">
+    <row r="166" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A166" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="B164" s="1" t="s">
+      <c r="B166" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="C164" s="1" t="s">
+      <c r="C166" s="1" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="165" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A165" s="1" t="s">
+    <row r="167" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A167" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="B165" s="1" t="s">
+      <c r="B167" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="C165" s="1" t="s">
+      <c r="C167" s="1" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="166" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A166" s="1" t="s">
+    <row r="168" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A168" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="B166" s="1" t="s">
+      <c r="B168" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="C166" s="1" t="s">
+      <c r="C168" s="1" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="167" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="1" t="s">
+    <row r="169" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A169" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="B167" s="1" t="s">
+      <c r="B169" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="C167" s="1" t="s">
+      <c r="C169" s="1" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="168" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A168" s="1" t="s">
+    <row r="170" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A170" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="B168" s="1" t="s">
+      <c r="B170" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="C168" s="1" t="s">
+      <c r="C170" s="1" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="169" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="1" t="s">
+    <row r="171" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A171" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="B169" s="1" t="s">
+      <c r="B171" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="C169" s="1" t="s">
+      <c r="C171" s="1" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="170" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A170" s="1" t="s">
+    <row r="172" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A172" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="B170" s="1" t="s">
+      <c r="B172" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="C170" s="1" t="s">
+      <c r="C172" s="1" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="171" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A171" s="1" t="s">
+    <row r="173" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A173" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="B171" s="1" t="s">
+      <c r="B173" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="C171" s="1" t="s">
+      <c r="C173" s="1" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="172" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A172" s="1" t="s">
+    <row r="174" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A174" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="B172" s="1" t="s">
+      <c r="B174" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="C172" s="1" t="s">
+      <c r="C174" s="1" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="173" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A173" s="1" t="s">
+    <row r="175" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A175" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="B173" s="1" t="s">
+      <c r="B175" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="C173" s="1" t="s">
+      <c r="C175" s="1" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="174" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A174" s="1" t="s">
+    <row r="176" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A176" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="B174" s="1" t="s">
+      <c r="B176" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="C174" s="1" t="s">
+      <c r="C176" s="1" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="175" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A175" s="1" t="s">
+    <row r="177" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A177" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="B175" s="1" t="s">
+      <c r="B177" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="C175" s="1" t="s">
+      <c r="C177" s="1" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="176" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A176" s="1" t="s">
+    <row r="178" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A178" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="B176" s="1" t="s">
+      <c r="B178" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="C176" s="1" t="s">
+      <c r="C178" s="1" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="177" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A177" s="1" t="s">
+    <row r="179" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A179" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="B177" s="1" t="s">
+      <c r="B179" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="C177" s="1" t="s">
+      <c r="C179" s="1" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="178" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A178" s="1" t="s">
+    <row r="180" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A180" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="B178" s="1" t="s">
+      <c r="B180" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="C178" s="1" t="s">
+      <c r="C180" s="1" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="179" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A179" s="1" t="s">
+    <row r="181" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A181" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="B179" s="1" t="s">
+      <c r="B181" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="C179" s="1" t="s">
+      <c r="C181" s="1" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="180" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A180" s="1" t="s">
+    <row r="182" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A182" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="B180" s="1" t="s">
+      <c r="B182" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="C180" s="1" t="s">
+      <c r="C182" s="1" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="181" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A181" s="1" t="s">
+    <row r="183" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A183" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="B181" s="1" t="s">
+      <c r="B183" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="C181" s="1" t="s">
+      <c r="C183" s="1" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="182" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A182" s="1" t="s">
+    <row r="184" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A184" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="B182" s="1" t="s">
+      <c r="B184" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="C182" s="1" t="s">
+      <c r="C184" s="1" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A183" t="s">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A185" t="s">
         <v>454</v>
       </c>
-      <c r="B183" t="s">
+      <c r="B185" t="s">
         <v>293</v>
       </c>
-      <c r="C183" t="s">
+      <c r="C185" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A184" t="s">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A186" t="s">
         <v>455</v>
       </c>
-      <c r="B184" t="s">
+      <c r="B186" t="s">
         <v>434</v>
       </c>
-      <c r="C184" t="s">
+      <c r="C186" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A185" t="s">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A187" t="s">
         <v>456</v>
       </c>
-      <c r="B185" t="s">
+      <c r="B187" t="s">
         <v>457</v>
       </c>
-      <c r="C185" t="s">
+      <c r="C187" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A186" t="s">
+    <row r="188" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A188" t="s">
         <v>459</v>
       </c>
-      <c r="B186" t="s">
+      <c r="B188" t="s">
         <v>460</v>
       </c>
-      <c r="C186" t="s">
+      <c r="C188" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A187" t="s">
+    <row r="189" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A189" t="s">
         <v>462</v>
       </c>
-      <c r="B187" t="s">
+      <c r="B189" t="s">
         <v>463</v>
       </c>
-      <c r="C187" t="s">
+      <c r="C189" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A188" t="s">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A190" t="s">
         <v>465</v>
       </c>
-      <c r="B188" t="s">
+      <c r="B190" t="s">
         <v>466</v>
       </c>
-      <c r="C188" t="s">
+      <c r="C190" t="s">
         <v>467</v>
       </c>
     </row>

--- a/tools/languages.xlsx
+++ b/tools/languages.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macbook/projects/hieunm/xiangqi/Tools/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BB9B2B3-C6FB-3049-A7FA-075D073916E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E57FDA59-661A-3745-9248-53AB46318061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="477">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="505">
   <si>
     <t>Key</t>
   </si>
@@ -133,6 +133,24 @@
     <t>menu.home</t>
   </si>
   <si>
+    <t>menu.profile</t>
+  </si>
+  <si>
+    <t>Profile</t>
+  </si>
+  <si>
+    <t>Trang cá nhân</t>
+  </si>
+  <si>
+    <t>menu.expired</t>
+  </si>
+  <si>
+    <t>Set expired</t>
+  </si>
+  <si>
+    <t>Hết hạn token</t>
+  </si>
+  <si>
     <t>menu.logout</t>
   </si>
   <si>
@@ -250,6 +268,15 @@
     <t>Đỏ tiên</t>
   </si>
   <si>
+    <t>dashboard.popup.pve-mode</t>
+  </si>
+  <si>
+    <t>PVE mode</t>
+  </si>
+  <si>
+    <t>Chơi với máy</t>
+  </si>
+  <si>
     <t>dashboard.popup.bet-amount</t>
   </si>
   <si>
@@ -1321,6 +1348,81 @@
     <t>Hòa cờ thành công</t>
   </si>
   <si>
+    <t>room.actions.settings</t>
+  </si>
+  <si>
+    <t>Room settings</t>
+  </si>
+  <si>
+    <t>Cài đặt phòng</t>
+  </si>
+  <si>
+    <t>room.settings.title</t>
+  </si>
+  <si>
+    <t>Room Settings</t>
+  </si>
+  <si>
+    <t>room.settings.room-name</t>
+  </si>
+  <si>
+    <t>Room name</t>
+  </si>
+  <si>
+    <t>Tên phòng</t>
+  </si>
+  <si>
+    <t>room.settings.save</t>
+  </si>
+  <si>
+    <t>Save</t>
+  </si>
+  <si>
+    <t>Lưu</t>
+  </si>
+  <si>
+    <t>update-room.messages.success</t>
+  </si>
+  <si>
+    <t>Room updated successfully</t>
+  </si>
+  <si>
+    <t>Cập nhật phòng thành công</t>
+  </si>
+  <si>
+    <t>update-room.messages.internal-server-error</t>
+  </si>
+  <si>
+    <t>update-room.messages.invalid-room-id</t>
+  </si>
+  <si>
+    <t>Invalid room ID</t>
+  </si>
+  <si>
+    <t>ID phòng không hợp lệ</t>
+  </si>
+  <si>
+    <t>update-room.messages.name-required</t>
+  </si>
+  <si>
+    <t>Room name is required</t>
+  </si>
+  <si>
+    <t>Tên phòng không được để trống</t>
+  </si>
+  <si>
+    <t>update-room.messages.room-not-found</t>
+  </si>
+  <si>
+    <t>update-room.messages.forbidden</t>
+  </si>
+  <si>
+    <t>You are not the host of this room</t>
+  </si>
+  <si>
+    <t>Bạn không phải chủ phòng</t>
+  </si>
+  <si>
     <t>draw-game.messages.invalid-game-id</t>
   </si>
   <si>
@@ -1426,31 +1528,13 @@
     <t>Token hợp lệ</t>
   </si>
   <si>
-    <t>menu.profile</t>
-  </si>
-  <si>
-    <t>Profile</t>
-  </si>
-  <si>
-    <t>Trang cá nhân</t>
-  </si>
-  <si>
-    <t>dashboard.popup.pve-mode</t>
-  </si>
-  <si>
-    <t>PVE mode</t>
-  </si>
-  <si>
-    <t>Chơi với máy</t>
-  </si>
-  <si>
-    <t>menu.expired</t>
-  </si>
-  <si>
-    <t>Set expired</t>
-  </si>
-  <si>
-    <t>Hết hạn token</t>
+    <t>dashboard.popup.join-room</t>
+  </si>
+  <si>
+    <t>Join room</t>
+  </si>
+  <si>
+    <t>Vào phòng</t>
   </si>
 </sst>
 </file>
@@ -1688,7 +1772,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C190"/>
+  <dimension ref="A1:C201"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -1840,1949 +1924,2070 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>468</v>
+        <v>37</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>469</v>
+        <v>38</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>470</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>474</v>
+        <v>40</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>475</v>
+        <v>41</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>476</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>471</v>
+        <v>82</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>472</v>
+        <v>83</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>473</v>
+        <v>84</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>84</v>
+        <v>502</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>31</v>
+        <v>503</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>32</v>
+        <v>504</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>86</v>
+        <v>31</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>87</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
     </row>
     <row r="57" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
     </row>
     <row r="61" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>130</v>
+        <v>166</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>131</v>
+        <v>167</v>
       </c>
     </row>
     <row r="62" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>161</v>
+        <v>139</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>162</v>
+        <v>140</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="65" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="66" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
     </row>
     <row r="67" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
     </row>
     <row r="68" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
     </row>
     <row r="69" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
     </row>
     <row r="70" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
     </row>
     <row r="71" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
     </row>
     <row r="72" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
     </row>
     <row r="73" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
     </row>
     <row r="74" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
     </row>
     <row r="75" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>157</v>
+        <v>199</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>158</v>
+        <v>200</v>
       </c>
     </row>
     <row r="76" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>194</v>
+        <v>166</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>195</v>
+        <v>167</v>
       </c>
     </row>
     <row r="77" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>157</v>
+        <v>203</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>158</v>
+        <v>204</v>
       </c>
     </row>
     <row r="78" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>198</v>
+        <v>166</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>199</v>
+        <v>167</v>
       </c>
     </row>
     <row r="79" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
     </row>
     <row r="80" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
     </row>
     <row r="81" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
     </row>
     <row r="82" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>157</v>
+        <v>216</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>158</v>
+        <v>217</v>
       </c>
     </row>
     <row r="83" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>211</v>
+        <v>166</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>212</v>
+        <v>167</v>
       </c>
     </row>
     <row r="84" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>148</v>
+        <v>220</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>149</v>
+        <v>221</v>
       </c>
     </row>
     <row r="85" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>138</v>
+        <v>157</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>139</v>
+        <v>158</v>
       </c>
     </row>
     <row r="86" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
     </row>
     <row r="87" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="88" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>218</v>
+        <v>154</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>219</v>
+        <v>155</v>
       </c>
     </row>
     <row r="89" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>134</v>
+        <v>227</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>135</v>
+        <v>228</v>
       </c>
     </row>
     <row r="90" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
     </row>
     <row r="91" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>223</v>
+        <v>143</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
     </row>
     <row r="92" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
     </row>
     <row r="93" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>190</v>
+        <v>232</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>191</v>
+        <v>164</v>
       </c>
     </row>
     <row r="94" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>154</v>
+        <v>199</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>155</v>
+        <v>200</v>
       </c>
     </row>
     <row r="95" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>228</v>
+        <v>163</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>229</v>
+        <v>164</v>
       </c>
     </row>
     <row r="96" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
     </row>
     <row r="97" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
     </row>
     <row r="98" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
     </row>
     <row r="99" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
     </row>
     <row r="100" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="101" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
     </row>
     <row r="102" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
     </row>
     <row r="103" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>190</v>
+        <v>256</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
     </row>
     <row r="104" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>252</v>
+        <v>199</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>235</v>
+        <v>259</v>
       </c>
     </row>
     <row r="105" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="106" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
     </row>
     <row r="107" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="108" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
     </row>
     <row r="109" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
     </row>
     <row r="110" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
     </row>
     <row r="111" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
     </row>
     <row r="112" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
     </row>
     <row r="113" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
     </row>
     <row r="114" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
     </row>
     <row r="115" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
     </row>
     <row r="116" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
     </row>
     <row r="117" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
     </row>
     <row r="118" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="119" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
     </row>
     <row r="120" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
     </row>
     <row r="121" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
     </row>
     <row r="122" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="123" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>293</v>
+        <v>314</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
     </row>
     <row r="124" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>184</v>
+        <v>302</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>185</v>
+        <v>303</v>
       </c>
     </row>
     <row r="125" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>310</v>
+        <v>193</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>311</v>
+        <v>194</v>
       </c>
     </row>
     <row r="126" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="1" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
     </row>
     <row r="127" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>293</v>
+        <v>322</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>294</v>
+        <v>323</v>
       </c>
     </row>
     <row r="128" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>317</v>
+        <v>302</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>318</v>
+        <v>303</v>
       </c>
     </row>
     <row r="129" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
     </row>
     <row r="130" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
     </row>
     <row r="131" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>293</v>
+        <v>332</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>294</v>
+        <v>333</v>
       </c>
     </row>
     <row r="132" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="1" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>317</v>
+        <v>302</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>318</v>
+        <v>303</v>
       </c>
     </row>
     <row r="133" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="C133" s="1" t="s">
         <v>327</v>
-      </c>
-      <c r="B133" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="C133" s="1" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="134" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="1" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
     </row>
     <row r="135" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="1" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>293</v>
+        <v>340</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>294</v>
+        <v>341</v>
       </c>
     </row>
     <row r="136" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="1" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>335</v>
+        <v>302</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>336</v>
+        <v>303</v>
       </c>
     </row>
     <row r="137" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>320</v>
+        <v>344</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>321</v>
+        <v>345</v>
       </c>
     </row>
     <row r="138" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="1" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>340</v>
+        <v>330</v>
       </c>
     </row>
     <row r="139" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="1" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
     </row>
     <row r="140" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="1" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>293</v>
+        <v>351</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>294</v>
+        <v>352</v>
       </c>
     </row>
     <row r="141" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="1" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>346</v>
+        <v>302</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>347</v>
+        <v>303</v>
       </c>
     </row>
     <row r="142" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="1" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
     </row>
     <row r="143" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="1" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
     </row>
     <row r="144" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="1" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>293</v>
+        <v>361</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>294</v>
+        <v>362</v>
       </c>
     </row>
     <row r="145" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="1" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>356</v>
+        <v>302</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>357</v>
+        <v>303</v>
       </c>
     </row>
     <row r="146" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="1" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
     </row>
     <row r="147" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="1" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
     </row>
     <row r="148" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="1" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
     </row>
     <row r="149" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="1" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
     </row>
     <row r="150" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="1" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>293</v>
+        <v>377</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>294</v>
+        <v>378</v>
       </c>
     </row>
     <row r="151" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="1" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>372</v>
+        <v>302</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>373</v>
+        <v>303</v>
       </c>
     </row>
     <row r="152" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="1" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
     </row>
     <row r="153" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="1" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
     </row>
     <row r="154" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="1" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>293</v>
+        <v>387</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>294</v>
+        <v>388</v>
       </c>
     </row>
     <row r="155" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="1" t="s">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>244</v>
+        <v>302</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>245</v>
+        <v>303</v>
       </c>
     </row>
     <row r="156" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="1" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>383</v>
+        <v>253</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>384</v>
+        <v>254</v>
       </c>
     </row>
     <row r="157" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="1" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
     </row>
     <row r="158" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="1" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
     </row>
     <row r="159" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="1" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
     </row>
     <row r="160" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="1" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
     </row>
     <row r="161" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="1" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>293</v>
+        <v>404</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>294</v>
+        <v>405</v>
       </c>
     </row>
     <row r="162" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="1" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>317</v>
+        <v>302</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>318</v>
+        <v>303</v>
       </c>
     </row>
     <row r="163" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="1" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>400</v>
+        <v>326</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>401</v>
+        <v>327</v>
       </c>
     </row>
     <row r="164" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="1" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>320</v>
+        <v>409</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>321</v>
+        <v>410</v>
       </c>
     </row>
     <row r="165" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="1" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>404</v>
+        <v>329</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>405</v>
+        <v>330</v>
       </c>
     </row>
     <row r="166" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="1" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
     </row>
     <row r="167" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="1" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
     </row>
     <row r="168" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="1" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
     </row>
     <row r="169" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="1" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
     </row>
     <row r="170" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="1" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
     </row>
     <row r="171" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="1" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
     </row>
     <row r="172" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="1" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
     </row>
     <row r="173" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="1" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
     </row>
     <row r="174" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="1" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
     </row>
     <row r="175" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="1" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
     </row>
     <row r="176" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="1" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
     </row>
     <row r="177" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="1" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="178" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="1" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
     </row>
     <row r="179" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="1" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
     </row>
     <row r="180" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="1" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>432</v>
+        <v>455</v>
       </c>
     </row>
     <row r="181" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="1" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
     </row>
     <row r="182" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="1" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>446</v>
+        <v>458</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>447</v>
+        <v>459</v>
       </c>
     </row>
     <row r="183" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="1" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>443</v>
+        <v>461</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>444</v>
+        <v>462</v>
       </c>
     </row>
     <row r="184" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="1" t="s">
-        <v>453</v>
+        <v>463</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>437</v>
+        <v>329</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A185" t="s">
-        <v>454</v>
-      </c>
-      <c r="B185" t="s">
-        <v>293</v>
-      </c>
-      <c r="C185" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A186" t="s">
-        <v>455</v>
-      </c>
-      <c r="B186" t="s">
-        <v>434</v>
-      </c>
-      <c r="C186" t="s">
-        <v>435</v>
+        <v>330</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A185" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="B185" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="C185" s="1" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A186" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="C186" s="1" t="s">
+        <v>469</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
-        <v>456</v>
+        <v>470</v>
       </c>
       <c r="B187" t="s">
-        <v>457</v>
+        <v>471</v>
       </c>
       <c r="C187" t="s">
-        <v>458</v>
+        <v>472</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
-        <v>459</v>
+        <v>473</v>
       </c>
       <c r="B188" t="s">
-        <v>460</v>
+        <v>474</v>
       </c>
       <c r="C188" t="s">
-        <v>461</v>
+        <v>475</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
-        <v>462</v>
+        <v>476</v>
       </c>
       <c r="B189" t="s">
-        <v>463</v>
+        <v>477</v>
       </c>
       <c r="C189" t="s">
-        <v>464</v>
+        <v>478</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
-        <v>465</v>
+        <v>479</v>
       </c>
       <c r="B190" t="s">
-        <v>466</v>
+        <v>480</v>
       </c>
       <c r="C190" t="s">
-        <v>467</v>
+        <v>481</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A191" t="s">
+        <v>482</v>
+      </c>
+      <c r="B191" t="s">
+        <v>483</v>
+      </c>
+      <c r="C191" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A192" t="s">
+        <v>484</v>
+      </c>
+      <c r="B192" t="s">
+        <v>302</v>
+      </c>
+      <c r="C192" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A193" t="s">
+        <v>485</v>
+      </c>
+      <c r="B193" t="s">
+        <v>480</v>
+      </c>
+      <c r="C193" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A194" t="s">
+        <v>486</v>
+      </c>
+      <c r="B194" t="s">
+        <v>477</v>
+      </c>
+      <c r="C194" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A195" t="s">
+        <v>487</v>
+      </c>
+      <c r="B195" t="s">
+        <v>471</v>
+      </c>
+      <c r="C195" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A196" t="s">
+        <v>488</v>
+      </c>
+      <c r="B196" t="s">
+        <v>302</v>
+      </c>
+      <c r="C196" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A197" t="s">
+        <v>489</v>
+      </c>
+      <c r="B197" t="s">
+        <v>468</v>
+      </c>
+      <c r="C197" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A198" t="s">
+        <v>490</v>
+      </c>
+      <c r="B198" t="s">
+        <v>491</v>
+      </c>
+      <c r="C198" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A199" t="s">
+        <v>493</v>
+      </c>
+      <c r="B199" t="s">
+        <v>494</v>
+      </c>
+      <c r="C199" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A200" t="s">
+        <v>496</v>
+      </c>
+      <c r="B200" t="s">
+        <v>497</v>
+      </c>
+      <c r="C200" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A201" t="s">
+        <v>499</v>
+      </c>
+      <c r="B201" t="s">
+        <v>500</v>
+      </c>
+      <c r="C201" t="s">
+        <v>501</v>
       </c>
     </row>
   </sheetData>

--- a/tools/languages.xlsx
+++ b/tools/languages.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15840" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15820" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="languages" sheetId="1" state="visible" r:id="rId1"/>
@@ -325,7 +325,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C288"/>
+  <dimension ref="A1:C294"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -948,364 +948,364 @@
     <row r="37" ht="17" customHeight="1">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>dashboard.popup.join-room</t>
+          <t>dashboard.popup.play</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Join room</t>
+          <t>Play</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Vào phòng</t>
+          <t>Chơi</t>
         </is>
       </c>
     </row>
     <row r="38" ht="17" customHeight="1">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>settings.header</t>
+          <t>dashboard.popup.view</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>View</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Cài đặt</t>
+          <t>Xem</t>
         </is>
       </c>
     </row>
     <row r="39" ht="17" customHeight="1">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>settings.language</t>
+          <t>settings.header</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Ngôn ngữ</t>
+          <t>Cài đặt</t>
         </is>
       </c>
     </row>
     <row r="40" ht="17" customHeight="1">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>settings.dark-mode</t>
+          <t>settings.language</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Dark mode</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Chế độ tối</t>
+          <t>Ngôn ngữ</t>
         </is>
       </c>
     </row>
     <row r="41" ht="17" customHeight="1">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>settings.debug-mode</t>
+          <t>settings.dark-mode</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Debug mode</t>
+          <t>Dark mode</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Chế độ test</t>
+          <t>Chế độ tối</t>
         </is>
       </c>
     </row>
     <row r="42" ht="17" customHeight="1">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>settings.close</t>
+          <t>settings.debug-mode</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Close</t>
+          <t>Debug mode</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Đóng</t>
+          <t>Chế độ test</t>
         </is>
       </c>
     </row>
     <row r="43" ht="17" customHeight="1">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>settings.change-password</t>
+          <t>settings.close</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Change password</t>
+          <t>Close</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Đổi mật khẩu</t>
+          <t>Đóng</t>
         </is>
       </c>
     </row>
     <row r="44" ht="17" customHeight="1">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>popup.alert.title</t>
+          <t>settings.change-password</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Change password</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Cảnh báo</t>
+          <t>Đổi mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="45" ht="17" customHeight="1">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>popup.confirm.title</t>
+          <t>popup.alert.title</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Confirm</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Xác nhận</t>
+          <t>Cảnh báo</t>
         </is>
       </c>
     </row>
     <row r="46" ht="17" customHeight="1">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>popup.confirm.ok</t>
+          <t>popup.confirm.title</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Ok</t>
+          <t>Confirm</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Ok</t>
+          <t>Xác nhận</t>
         </is>
       </c>
     </row>
     <row r="47" ht="17" customHeight="1">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>popup.confirm.cancel</t>
+          <t>popup.confirm.ok</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Ok</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Huỷ</t>
+          <t>Ok</t>
         </is>
       </c>
     </row>
     <row r="48" ht="17" customHeight="1">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>home.turn.title</t>
+          <t>popup.confirm.cancel</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Turn</t>
+          <t>Cancel</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Lượt đánh</t>
+          <t>Huỷ</t>
         </is>
       </c>
     </row>
     <row r="49" ht="17" customHeight="1">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>game.general.captured</t>
+          <t>home.turn.title</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>General has been captured. Room over</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>Tướng đã bị bắt. Game kết thúc</t>
+          <t>Turn</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Lượt đánh</t>
         </is>
       </c>
     </row>
     <row r="50" ht="17" customHeight="1">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>game.general.in-check</t>
+          <t>game.general.captured</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Your general is under attack</t>
+          <t>General has been captured. Room over</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Tướng của bạn đang bị chiếu</t>
+          <t>Tướng đã bị bắt. Game kết thúc</t>
         </is>
       </c>
     </row>
     <row r="51" ht="17" customHeight="1">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>room.bot-difficulty.title</t>
+          <t>game.general.in-check</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Select Bot Difficulty</t>
+          <t>Your general is under attack</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Chọn độ khó của Bot</t>
+          <t>Tướng của bạn đang bị chiếu</t>
         </is>
       </c>
     </row>
     <row r="52" ht="17" customHeight="1">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>room.bot-difficulty.beginner</t>
+          <t>room.bot-difficulty.title</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Beginner</t>
+          <t>Select Bot Difficulty</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>Mới bắt đầu</t>
+          <t>Chọn độ khó của Bot</t>
         </is>
       </c>
     </row>
     <row r="53" ht="17" customHeight="1">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>room.bot-difficulty.amateur</t>
+          <t>room.bot-difficulty.beginner</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Amateur</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>Nghiệp dư</t>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>Mới bắt đầu</t>
         </is>
       </c>
     </row>
     <row r="54" ht="17" customHeight="1">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>room.bot-difficulty.intermediate</t>
+          <t>room.bot-difficulty.amateur</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Intermediate</t>
+          <t>Amateur</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Trung bình</t>
+          <t>Nghiệp dư</t>
         </is>
       </c>
     </row>
     <row r="55" ht="17" customHeight="1">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>room.bot-difficulty.advanced</t>
+          <t>room.bot-difficulty.intermediate</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Advanced</t>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Nâng cao</t>
+          <t>Trung bình</t>
         </is>
       </c>
     </row>
     <row r="56" ht="17" customHeight="1">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>room.bot-difficulty.master</t>
+          <t>room.bot-difficulty.advanced</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Master</t>
+          <t>Advanced</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Lão luyện</t>
+          <t>Nâng cao</t>
         </is>
       </c>
     </row>
     <row r="57" ht="17" customHeight="1">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>login.page.title</t>
+          <t>room.bot-difficulty.master</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Login</t>
+          <t>Master</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập</t>
+          <t>Lão luyện</t>
         </is>
       </c>
     </row>
     <row r="58" ht="17" customHeight="1">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>login.form.title</t>
+          <t>login.page.title</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -1322,24 +1322,24 @@
     <row r="59" ht="17" customHeight="1">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>login.username.label</t>
+          <t>login.form.title</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>User name</t>
+          <t>Login</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Tên người dùng</t>
+          <t>Đăng nhập</t>
         </is>
       </c>
     </row>
     <row r="60" ht="17" customHeight="1">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>login.username.placeholder</t>
+          <t>login.username.label</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -1356,24 +1356,24 @@
     <row r="61" ht="17" customHeight="1">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>login.password.label</t>
+          <t>login.username.placeholder</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Password</t>
+          <t>User name</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Mật khẩu</t>
+          <t>Tên người dùng</t>
         </is>
       </c>
     </row>
     <row r="62" ht="17" customHeight="1">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>login.password.placeholder</t>
+          <t>login.password.label</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -1390,228 +1390,228 @@
     <row r="63" ht="17" customHeight="1">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>login.password.error1</t>
+          <t>login.password.placeholder</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Password is required</t>
+          <t>Password</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Mật khẩu bắt buộc nhập</t>
+          <t>Mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="64" ht="17" customHeight="1">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>login.password.show</t>
+          <t>login.password.error1</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Show password</t>
+          <t>Password is required</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Hiện mật khẩu</t>
+          <t>Mật khẩu bắt buộc nhập</t>
         </is>
       </c>
     </row>
     <row r="65" ht="17" customHeight="1">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>login.password.hide</t>
+          <t>login.password.show</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Hide password</t>
+          <t>Show password</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Ẩn mật khẩu</t>
+          <t>Hiện mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="66" ht="17" customHeight="1">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>login.form.error1</t>
+          <t>login.password.hide</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Login failed. Please check your credentials </t>
+          <t>Hide password</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập không thành công. Hãy kiểm tra lại</t>
+          <t>Ẩn mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="67" ht="17" customHeight="1">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>login.form.forgot-password</t>
+          <t>login.form.error1</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Forgot password</t>
+          <t xml:space="preserve">Login failed. Please check your credentials </t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Quên mật khẩu</t>
+          <t>Đăng nhập không thành công. Hãy kiểm tra lại</t>
         </is>
       </c>
     </row>
     <row r="68" ht="17" customHeight="1">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>login.form.register</t>
+          <t>login.form.forgot-password</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Register</t>
+          <t>Forgot password</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Đăng ký</t>
+          <t>Quên mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="69" ht="17" customHeight="1">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>login.form.submit</t>
+          <t>login.form.register</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Login</t>
+          <t>Register</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập</t>
+          <t>Đăng ký</t>
         </is>
       </c>
     </row>
     <row r="70" ht="17" customHeight="1">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>notfound.title</t>
+          <t>login.form.submit</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Page Not Found</t>
+          <t>Login</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Trang không tìm thấy</t>
+          <t>Đăng nhập</t>
         </is>
       </c>
     </row>
     <row r="71" ht="17" customHeight="1">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>notfound.description</t>
+          <t>notfound.title</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>The page you are looking for does not exist or has been moved.</t>
+          <t>Page Not Found</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Trang bạn tìm kiếm không tồn tại hoặc đã được di chuyển.</t>
+          <t>Trang không tìm thấy</t>
         </is>
       </c>
     </row>
     <row r="72" ht="17" customHeight="1">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>notfound.home</t>
+          <t>notfound.description</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Go to Home</t>
+          <t>The page you are looking for does not exist or has been moved.</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Về trang chủ</t>
+          <t>Trang bạn tìm kiếm không tồn tại hoặc đã được di chuyển.</t>
         </is>
       </c>
     </row>
     <row r="73" ht="17" customHeight="1">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>notfound.back</t>
+          <t>notfound.home</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Go Back</t>
+          <t>Go to Home</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Quay lại</t>
+          <t>Về trang chủ</t>
         </is>
       </c>
     </row>
     <row r="74" ht="17" customHeight="1">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>register.confirm-password.error1</t>
+          <t>notfound.back</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Confirm password does not match password</t>
+          <t>Go Back</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Mật khẩu xác nhận không khớp với mật khẩu</t>
+          <t>Quay lại</t>
         </is>
       </c>
     </row>
     <row r="75" ht="17" customHeight="1">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>register.confirm-password.label</t>
+          <t>register.confirm-password.error1</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Confirm Password</t>
+          <t>Confirm password does not match password</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Xác nhận mật khẩu</t>
+          <t>Mật khẩu xác nhận không khớp với mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="76" ht="17" customHeight="1">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>register.confirm-password.placeholder</t>
+          <t>register.confirm-password.label</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -1628,24 +1628,24 @@
     <row r="77" ht="17" customHeight="1">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>register.display-name.label</t>
+          <t>register.confirm-password.placeholder</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Display name</t>
+          <t>Confirm Password</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Tên hiển thị</t>
+          <t>Xác nhận mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="78" ht="17" customHeight="1">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>register.display-name.placeholder</t>
+          <t>register.display-name.label</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -1662,41 +1662,41 @@
     <row r="79" ht="17" customHeight="1">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>register.email.error1</t>
+          <t>register.display-name.placeholder</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Invalid email format</t>
+          <t>Display name</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Định dạng email không hợp lệ</t>
+          <t>Tên hiển thị</t>
         </is>
       </c>
     </row>
     <row r="80" ht="17" customHeight="1">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>register.email.label</t>
+          <t>register.email.error1</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Invalid email format</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Định dạng email không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="81" ht="17" customHeight="1">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>register.email.placeholder</t>
+          <t>register.email.label</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -1713,211 +1713,211 @@
     <row r="82" ht="17" customHeight="1">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>register.form.login</t>
+          <t>register.email.placeholder</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Back to login</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Về trang đăng nhập</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="83" ht="17" customHeight="1">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>register.form.submit</t>
+          <t>register.form.login</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Register</t>
+          <t>Back to login</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Đăng ký</t>
+          <t>Về trang đăng nhập</t>
         </is>
       </c>
     </row>
     <row r="84" ht="17" customHeight="1">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>register.form.success</t>
+          <t>register.form.submit</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Registration successful. Redirecting to login...</t>
+          <t>Register</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Đăng ký thành công. Đang chuyển hướng...</t>
+          <t>Đăng ký</t>
         </is>
       </c>
     </row>
     <row r="85" ht="17" customHeight="1">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>register.form.title</t>
+          <t>register.form.success</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Register</t>
+          <t>Registration successful. Redirecting to login...</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Đăng ký</t>
+          <t>Đăng ký thành công. Đang chuyển hướng...</t>
         </is>
       </c>
     </row>
     <row r="86" ht="17" customHeight="1">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>register.gender.female</t>
+          <t>register.form.title</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Register</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Nữ</t>
+          <t>Đăng ký</t>
         </is>
       </c>
     </row>
     <row r="87" ht="17" customHeight="1">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>register.gender.label</t>
+          <t>register.gender.female</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Gender</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Giới tính</t>
+          <t>Nữ</t>
         </is>
       </c>
     </row>
     <row r="88" ht="17" customHeight="1">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>register.gender.male</t>
+          <t>register.gender.label</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Gender</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Nam</t>
+          <t>Giới tính</t>
         </is>
       </c>
     </row>
     <row r="89" ht="17" customHeight="1">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>register.gender.select</t>
+          <t>register.gender.male</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Select gender</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Chọn giới tính</t>
+          <t>Nam</t>
         </is>
       </c>
     </row>
     <row r="90" ht="17" customHeight="1">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>register.page.title</t>
+          <t>register.gender.select</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Register</t>
+          <t>Select gender</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Đăng ký</t>
+          <t>Chọn giới tính</t>
         </is>
       </c>
     </row>
     <row r="91" ht="17" customHeight="1">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>register.password.error1</t>
+          <t>register.page.title</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Password must be at least 8 characters and contain uppercase, lowercase, number, and special character</t>
+          <t>Register</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Mật khẩu phải có ít nhất 8 ký tự và chứa chữ hoa, chữ thường, số và ký tự đặc biệt</t>
+          <t>Đăng ký</t>
         </is>
       </c>
     </row>
     <row r="92" ht="17" customHeight="1">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>register.password.hide</t>
+          <t>register.password.error1</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Hide password</t>
+          <t>Password must be at least 8 characters and contain uppercase, lowercase, number, and special character</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Ẩn mật khẩu</t>
+          <t>Mật khẩu phải có ít nhất 8 ký tự và chứa chữ hoa, chữ thường, số và ký tự đặc biệt</t>
         </is>
       </c>
     </row>
     <row r="93" ht="17" customHeight="1">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>register.password.label</t>
+          <t>register.password.hide</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Password</t>
+          <t>Hide password</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Mật khẩu</t>
+          <t>Ẩn mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="94" ht="17" customHeight="1">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>register.password.placeholder</t>
+          <t>register.password.label</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -1934,58 +1934,58 @@
     <row r="95" ht="17" customHeight="1">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>register.password.show</t>
+          <t>register.password.placeholder</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Show password</t>
+          <t>Password</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Hiện mật khẩu</t>
+          <t>Mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="96" ht="17" customHeight="1">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>register.username.error1</t>
+          <t>register.password.show</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>User name must contain only alphanumeric characters, underscore, and dot</t>
+          <t>Show password</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Tên người dùng chỉ chứa ký tự chữ số, dấu gạch dưới và dấu chấm</t>
+          <t>Hiện mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="97" ht="17" customHeight="1">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>register.username.label</t>
+          <t>register.username.error1</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>User name</t>
+          <t>User name must contain only alphanumeric characters, underscore, and dot</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Tên người dùng</t>
+          <t>Tên người dùng chỉ chứa ký tự chữ số, dấu gạch dưới và dấu chấm</t>
         </is>
       </c>
     </row>
     <row r="98" ht="17" customHeight="1">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>register.username.placeholder</t>
+          <t>register.username.label</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -2002,24 +2002,24 @@
     <row r="99" ht="17" customHeight="1">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.page.title</t>
+          <t>register.username.placeholder</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Forgot Password</t>
+          <t>User name</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Quên mật khẩu</t>
+          <t>Tên người dùng</t>
         </is>
       </c>
     </row>
     <row r="100" ht="17" customHeight="1">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.form.title</t>
+          <t>forgot-password.page.title</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -2036,2013 +2036,2013 @@
     <row r="101" ht="17" customHeight="1">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.form.login</t>
+          <t>forgot-password.form.title</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Back to login</t>
+          <t>Forgot Password</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Về trang đăng nhập</t>
+          <t>Quên mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="102" ht="17" customHeight="1">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.form.submit</t>
+          <t>forgot-password.form.login</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Forgot password</t>
+          <t>Back to login</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Quên mật khẩu</t>
+          <t>Về trang đăng nhập</t>
         </is>
       </c>
     </row>
     <row r="103" ht="17" customHeight="1">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.form.success</t>
+          <t>forgot-password.form.submit</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Check your email for reset password details.</t>
+          <t>Forgot password</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Hãy kiểm tra email để xem thông tin đặt lại mật khẩu.</t>
+          <t>Quên mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="104" ht="17" customHeight="1">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.form.error1</t>
+          <t>forgot-password.form.success</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Forgot password failed.</t>
+          <t>Check your email for reset password details.</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Quên mật khẩu không thành công.</t>
+          <t>Hãy kiểm tra email để xem thông tin đặt lại mật khẩu.</t>
         </is>
       </c>
     </row>
     <row r="105" ht="17" customHeight="1">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>reset-password.page.title</t>
+          <t>forgot-password.form.error1</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Reset Password</t>
+          <t>Forgot password failed.</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Đặt lại mật khẩu</t>
+          <t>Quên mật khẩu không thành công.</t>
         </is>
       </c>
     </row>
     <row r="106" ht="17" customHeight="1">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>reset-password.form.title</t>
+          <t>reset-password.page.title</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Reset your password</t>
+          <t>Reset Password</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Đặt lại mật khẩu của bạn</t>
+          <t>Đặt lại mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="107" ht="17" customHeight="1">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>reset-password.form.submit</t>
+          <t>reset-password.form.title</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Reset Password</t>
+          <t>Reset your password</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Đặt lại mật khẩu</t>
+          <t>Đặt lại mật khẩu của bạn</t>
         </is>
       </c>
     </row>
     <row r="108" ht="17" customHeight="1">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>reset-password.form.error1</t>
+          <t>reset-password.form.submit</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>An error occurred while resetting your password. Please try again.</t>
+          <t>Reset Password</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Có lỗi xảy ra khi đặt lại mật khẩu. Vui lòng thử lại.</t>
+          <t>Đặt lại mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="109" ht="17" customHeight="1">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>reset-password.form.invalid-token</t>
+          <t>reset-password.form.error1</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Invalid or expired reset password token</t>
+          <t>An error occurred while resetting your password. Please try again.</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Token đặt lại mật khẩu không hợp lệ hoặc đã hết hạn</t>
+          <t>Có lỗi xảy ra khi đặt lại mật khẩu. Vui lòng thử lại.</t>
         </is>
       </c>
     </row>
     <row r="110" ht="17" customHeight="1">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>reset-password.form.success</t>
+          <t>reset-password.form.invalid-token</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Password reset successfully. Redirecting to login...</t>
+          <t>Invalid or expired reset password token</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Đặt lại mật khẩu thành công. Đang chuyển hướng đến đăng nhập...</t>
+          <t>Token đặt lại mật khẩu không hợp lệ hoặc đã hết hạn</t>
         </is>
       </c>
     </row>
     <row r="111" ht="17" customHeight="1">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>reset-password.action.back-to-login</t>
+          <t>reset-password.form.success</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Back to login</t>
+          <t>Password reset successfully. Redirecting to login...</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Quay lại trang chủ</t>
+          <t>Đặt lại mật khẩu thành công. Đang chuyển hướng đến đăng nhập...</t>
         </is>
       </c>
     </row>
     <row r="112" ht="17" customHeight="1">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>reset-password.action.submit</t>
+          <t>reset-password.action.back-to-login</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Reset password</t>
+          <t>Back to login</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Đặt lại mật khẩu</t>
+          <t>Quay lại trang chủ</t>
         </is>
       </c>
     </row>
     <row r="113" ht="17" customHeight="1">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>auth-middleware.messages.invalid-token-payload</t>
+          <t>reset-password.action.submit</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Invalid token payload</t>
+          <t>Reset password</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Payload của token không hợp lệ</t>
+          <t>Đặt lại mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="114" ht="17" customHeight="1">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>auth-middleware.messages.session-not-found</t>
+          <t>auth-middleware.messages.invalid-token-payload</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Session not found</t>
+          <t>Invalid token payload</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy phiên</t>
+          <t>Payload của token không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="115" ht="17" customHeight="1">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>auth-middleware.messages.token-expired</t>
+          <t>auth-middleware.messages.session-not-found</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Token is expired</t>
+          <t>Session not found</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Token đã hết hạn</t>
+          <t>Không tìm thấy phiên</t>
         </is>
       </c>
     </row>
     <row r="116" ht="17" customHeight="1">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>auth-middleware.messages.token-invalid</t>
+          <t>auth-middleware.messages.token-expired</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Token is invalid</t>
+          <t>Token is expired</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Token không hợp lệ</t>
+          <t>Token đã hết hạn</t>
         </is>
       </c>
     </row>
     <row r="117" ht="17" customHeight="1">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>auth-middleware.messages.token-required</t>
+          <t>auth-middleware.messages.token-invalid</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Token not provided</t>
+          <t>Token is invalid</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Token không được cung cấp</t>
+          <t>Token không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="118" ht="17" customHeight="1">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>auth-middleware.messages.token-subject-mismatch</t>
+          <t>auth-middleware.messages.token-required</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Token subject mismatch</t>
+          <t>Token not provided</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Token chủ đề không khớp</t>
+          <t>Token không được cung cấp</t>
         </is>
       </c>
     </row>
     <row r="119" ht="17" customHeight="1">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>auth-middleware.messages.token-validation-failed</t>
+          <t>auth-middleware.messages.token-subject-mismatch</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Token validation failed</t>
+          <t>Token subject mismatch</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Xác thực token không thành công</t>
+          <t>Token chủ đề không khớp</t>
         </is>
       </c>
     </row>
     <row r="120" ht="17" customHeight="1">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.internal-server-error</t>
+          <t>auth-middleware.messages.token-validation-failed</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Internal server error while creating room</t>
+          <t>Token validation failed</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ khi tạo phòng</t>
+          <t>Xác thực token không thành công</t>
         </is>
       </c>
     </row>
     <row r="121" ht="17" customHeight="1">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.invalid-bet-amount</t>
+          <t>create-room.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Bet amount is required and must be one of the acceptable values</t>
+          <t>Internal server error while creating room</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Số tiền cược là bắt buộc và phải là một trong các giá trị được chấp nhận</t>
+          <t>Lỗi máy chủ nội bộ khi tạo phòng</t>
         </is>
       </c>
     </row>
     <row r="122" ht="17" customHeight="1">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.invalid-redFirst</t>
+          <t>create-room.messages.invalid-bet-amount</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>'redFirst' must be a boolean</t>
+          <t>Bet amount is required and must be one of the acceptable values</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>'redFirst' phải là giá trị boolean</t>
+          <t>Số tiền cược là bắt buộc và phải là một trong các giá trị được chấp nhận</t>
         </is>
       </c>
     </row>
     <row r="123" ht="17" customHeight="1">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.invalid-team-name</t>
+          <t>create-room.messages.invalid-redFirst</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>Team name must be either 'red', 'black', or null</t>
+          <t>'redFirst' must be a boolean</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>Tên đội phải là 'red', 'black' hoặc null</t>
+          <t>'redFirst' phải là giá trị boolean</t>
         </is>
       </c>
     </row>
     <row r="124" ht="17" customHeight="1">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.name-required</t>
+          <t>create-room.messages.invalid-team-name</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Room name (tableName) is required and must not be empty</t>
+          <t>Team name must be either 'red', 'black', or null</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Tên phòng (tableName) là bắt buộc và không được để trống</t>
+          <t>Tên đội phải là 'red', 'black' hoặc null</t>
         </is>
       </c>
     </row>
     <row r="125" ht="17" customHeight="1">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.room-created</t>
+          <t>create-room.messages.name-required</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>Room created successfully</t>
+          <t>Room name (tableName) is required and must not be empty</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Phòng được tạo thành công</t>
+          <t>Tên phòng (tableName) là bắt buộc và không được để trống</t>
         </is>
       </c>
     </row>
     <row r="126" ht="17" customHeight="1">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>fetch-rooms.messages.internal-server-error</t>
+          <t>create-room.messages.room-created</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Room created successfully</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Phòng được tạo thành công</t>
         </is>
       </c>
     </row>
     <row r="127" ht="17" customHeight="1">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>fetch-rooms.messages.invalid-status</t>
+          <t>fetch-rooms.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>Query parameter 'status' must be an integer</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Tham số truy vấn 'status' phải là số nguyên</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="128" ht="17" customHeight="1">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>fetch-rooms.messages.success</t>
+          <t>fetch-rooms.messages.invalid-status</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Fetch rooms successfully</t>
+          <t>Query parameter 'status' must be an integer</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Lấy phòng thành công</t>
+          <t>Tham số truy vấn 'status' phải là số nguyên</t>
         </is>
       </c>
     </row>
     <row r="129" ht="17" customHeight="1">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.messages.email-not-found</t>
+          <t>fetch-rooms.messages.success</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>Email does not exist</t>
+          <t>Fetch rooms successfully</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Email không tồn tại</t>
+          <t>Lấy phòng thành công</t>
         </is>
       </c>
     </row>
     <row r="130" ht="17" customHeight="1">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.messages.email-service-not-configured</t>
+          <t>forgot-password.messages.email-not-found</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Email service is not configured</t>
+          <t>Email does not exist</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Dịch vụ email chưa được cấu hình</t>
+          <t>Email không tồn tại</t>
         </is>
       </c>
     </row>
     <row r="131" ht="17" customHeight="1">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.messages.internal-server-error</t>
+          <t>forgot-password.messages.email-service-not-configured</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Email service is not configured</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Dịch vụ email chưa được cấu hình</t>
         </is>
       </c>
     </row>
     <row r="132" ht="17" customHeight="1">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.messages.invalid-email-format</t>
+          <t>forgot-password.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Invalid email format</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Định dạng email không hợp lệ</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="133" ht="17" customHeight="1">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.messages.missing-email</t>
+          <t>forgot-password.messages.invalid-email-format</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>Email is required</t>
+          <t>Invalid email format</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>Email là bắt buộc</t>
+          <t>Định dạng email không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="134" ht="17" customHeight="1">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.messages.success</t>
+          <t>forgot-password.messages.missing-email</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Forgot password email sent</t>
+          <t>Email is required</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Email đặt lại mật khẩu đã được gửi</t>
+          <t>Email là bắt buộc</t>
         </is>
       </c>
     </row>
     <row r="135" ht="17" customHeight="1">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>join-room.messages.internal-server-error</t>
+          <t>forgot-password.messages.success</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Forgot password email sent</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Email đặt lại mật khẩu đã được gửi</t>
         </is>
       </c>
     </row>
     <row r="136" ht="17" customHeight="1">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>join-room.messages.invalid-room-id</t>
+          <t>join-room.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Field 'id' is required and must be a positive integer</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="137" ht="17" customHeight="1">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>join-room.messages.room-not-found</t>
+          <t>join-room.messages.invalid-team</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>Room not found</t>
+          <t>Field 'team' must be 'red', 'black', null, or undefined</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy phòng</t>
+          <t>Trường 'team' phải là 'red', 'black', null hoặc không truyền</t>
         </is>
       </c>
     </row>
     <row r="138" ht="17" customHeight="1">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>join-room.messages.success</t>
+          <t>join-room.messages.invalid-room-id</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Successfully joined the room</t>
+          <t>Field 'id' is required and must be a positive integer</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Tham gia phòng thành công</t>
+          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
         </is>
       </c>
     </row>
     <row r="139" ht="17" customHeight="1">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.cannot-kick-self</t>
+          <t>join-room.messages.room-not-found</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>You cannot kick yourself</t>
+          <t>Room not found</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>Bạn không thể kick chính mình</t>
+          <t>Không tìm thấy phòng</t>
         </is>
       </c>
     </row>
     <row r="140" ht="17" customHeight="1">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.forbidden</t>
+          <t>join-room.messages.success</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Only the host can kick users</t>
+          <t>Successfully joined the room</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Chỉ chủ phòng mới có thể kick người dùng</t>
+          <t>Tham gia phòng thành công</t>
         </is>
       </c>
     </row>
     <row r="141" ht="17" customHeight="1">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.internal-server-error</t>
+          <t>join-room.messages.team-seat-occupied</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Selected team seat is already occupied</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Vị trí đội đã chọn đã có người chơi</t>
         </is>
       </c>
     </row>
     <row r="142" ht="17" customHeight="1">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.invalid-room-id</t>
+          <t>kick-user.messages.cannot-kick-self</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Field 'id' is required and must be a positive integer</t>
+          <t>You cannot kick yourself</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
+          <t>Bạn không thể kick chính mình</t>
         </is>
       </c>
     </row>
     <row r="143" ht="17" customHeight="1">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.invalid-user-id</t>
+          <t>kick-user.messages.forbidden</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>Field 'userId' is required and must be a positive integer</t>
+          <t>Only the host can kick users</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>Trường 'userId' là bắt buộc và phải là số nguyên dương</t>
+          <t>Chỉ chủ phòng mới có thể kick người dùng</t>
         </is>
       </c>
     </row>
     <row r="144" ht="17" customHeight="1">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.room-not-found</t>
+          <t>kick-user.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Room not found</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy phòng</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="145" ht="17" customHeight="1">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.room-not-waiting</t>
+          <t>kick-user.messages.invalid-room-id</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>You can only kick users while the room is waiting</t>
+          <t>Field 'id' is required and must be a positive integer</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>Chỉ có thể kick người dùng khi phòng đang ở trạng thái chờ</t>
+          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
         </is>
       </c>
     </row>
     <row r="146" ht="17" customHeight="1">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.success</t>
+          <t>kick-user.messages.invalid-user-id</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>User has been kicked</t>
+          <t>Field 'userId' is required and must be a positive integer</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Người dùng đã bị kick</t>
+          <t>Trường 'userId' là bắt buộc và phải là số nguyên dương</t>
         </is>
       </c>
     </row>
     <row r="147" ht="17" customHeight="1">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.user-not-in-room</t>
+          <t>kick-user.messages.room-not-found</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>User is not in this room</t>
+          <t>Room not found</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Người dùng không trong phòng này</t>
+          <t>Không tìm thấy phòng</t>
         </is>
       </c>
     </row>
     <row r="148" ht="17" customHeight="1">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.you-were-kicked</t>
+          <t>kick-user.messages.room-not-waiting</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>You have been removed from the room by the host</t>
+          <t>You can only kick users while the room is waiting</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Bạn đã bị chủ phòng đưa ra khỏi phòng</t>
+          <t>Chỉ có thể kick người dùng khi phòng đang ở trạng thái chờ</t>
         </is>
       </c>
     </row>
     <row r="149" ht="17" customHeight="1">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>leave-room.messages.internal-server-error</t>
+          <t>kick-user.messages.success</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>User has been kicked</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Người dùng đã bị kick</t>
         </is>
       </c>
     </row>
     <row r="150" ht="17" customHeight="1">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>leave-room.messages.invalid-room-id</t>
+          <t>kick-user.messages.user-not-in-room</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Field 'id' is required and must be a positive integer</t>
+          <t>User is not in this room</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
+          <t>Người dùng không trong phòng này</t>
         </is>
       </c>
     </row>
     <row r="151" ht="17" customHeight="1">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>leave-room.messages.player-not-in-room</t>
+          <t>kick-user.messages.you-were-kicked</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>Player is not in this room</t>
+          <t>You have been removed from the room by the host</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>Người chơi không trong phòng này</t>
+          <t>Bạn đã bị chủ phòng đưa ra khỏi phòng</t>
         </is>
       </c>
     </row>
     <row r="152" ht="17" customHeight="1">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>leave-room.messages.success</t>
+          <t>leave-room.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Leave room successfully</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>Rời phòng thành công</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="153" ht="17" customHeight="1">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>load-room.messages.internal-server-error</t>
+          <t>leave-room.messages.invalid-room-id</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Field 'id' is required and must be a positive integer</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
         </is>
       </c>
     </row>
     <row r="154" ht="17" customHeight="1">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>load-room.messages.invalid-room-id</t>
+          <t>leave-room.messages.player-not-in-room</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>Room ID must be a positive integer</t>
+          <t>Player is not in this room</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>ID phòng phải là số nguyên dương</t>
+          <t>Người chơi không trong phòng này</t>
         </is>
       </c>
     </row>
     <row r="155" ht="17" customHeight="1">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>load-room.messages.room-not-found</t>
+          <t>leave-room.messages.success</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>Room not found</t>
+          <t>Leave room successfully</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy phòng</t>
+          <t>Rời phòng thành công</t>
         </is>
       </c>
     </row>
     <row r="156" ht="17" customHeight="1">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>load-room.messages.success</t>
+          <t>load-room.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>Load room successfully</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Tải phòng thành công</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="157" ht="17" customHeight="1">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t>login.messages.incorrect-login</t>
+          <t>load-room.messages.invalid-room-id</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>Invalid username or password</t>
+          <t>Room ID must be a positive integer</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>Tên người dùng hoặc mật khẩu không hợp lệ</t>
+          <t>ID phòng phải là số nguyên dương</t>
         </is>
       </c>
     </row>
     <row r="158" ht="17" customHeight="1">
       <c r="A158" s="1" t="inlineStr">
         <is>
-          <t>login.messages.internal-server-error</t>
+          <t>load-room.messages.room-not-found</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Room not found</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Không tìm thấy phòng</t>
         </is>
       </c>
     </row>
     <row r="159" ht="17" customHeight="1">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t>login.messages.missing-credentials</t>
+          <t>load-room.messages.success</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>Username and password are required</t>
+          <t>Load room successfully</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>Tên người dùng và mật khẩu là bắt buộc</t>
+          <t>Tải phòng thành công</t>
         </is>
       </c>
     </row>
     <row r="160" ht="17" customHeight="1">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>login.messages.success</t>
+          <t>login.messages.incorrect-login</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>Login successful</t>
+          <t>Invalid username or password</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập thành công</t>
+          <t>Tên người dùng hoặc mật khẩu không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="161" ht="17" customHeight="1">
       <c r="A161" s="1" t="inlineStr">
         <is>
-          <t>logout.messages.already-inactive</t>
+          <t>login.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>Session already inactive</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>Phiên đã ngưng hoạt động</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="162" ht="17" customHeight="1">
       <c r="A162" s="1" t="inlineStr">
         <is>
-          <t>logout.messages.internal-server-error</t>
+          <t>login.messages.missing-credentials</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Username and password are required</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Tên người dùng và mật khẩu là bắt buộc</t>
         </is>
       </c>
     </row>
     <row r="163" ht="17" customHeight="1">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t>logout.messages.success</t>
+          <t>login.messages.success</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>Logout successful</t>
+          <t>Login successful</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>Đăng xuất thành công</t>
-        </is>
-      </c>
-    </row>
-    <row r="164" ht="36" customHeight="1">
+          <t>Đăng nhập thành công</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="17" customHeight="1">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t>refresh-token.messages.missing-refresh-token</t>
+          <t>logout.messages.already-inactive</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>Missing refresh token cookie</t>
+          <t>Session already inactive</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Thiếu cookie token làm mới</t>
-        </is>
-      </c>
-    </row>
-    <row r="165" ht="17" customHeight="1">
+          <t>Phiên đã ngưng hoạt động</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="36" customHeight="1">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t>refresh-token.messages.mismatch-or-expired</t>
+          <t>logout.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>Refresh token mismatch or expired</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>Thiếu refresh token hoặc đã hết hạn</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="166" ht="17" customHeight="1">
       <c r="A166" s="1" t="inlineStr">
         <is>
-          <t>refresh-token.messages.success</t>
+          <t>logout.messages.success</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>Token refreshed</t>
+          <t>Logout successful</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>Token đã làm mới</t>
+          <t>Đăng xuất thành công</t>
         </is>
       </c>
     </row>
     <row r="167" ht="17" customHeight="1">
       <c r="A167" s="1" t="inlineStr">
         <is>
-          <t>register.messages.email-exists</t>
+          <t>refresh-token.messages.missing-refresh-token</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>Email already exists</t>
+          <t>Missing refresh token cookie</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>Email đã tồn tại</t>
+          <t>Thiếu cookie token làm mới</t>
         </is>
       </c>
     </row>
     <row r="168" ht="17" customHeight="1">
       <c r="A168" s="1" t="inlineStr">
         <is>
-          <t>register.messages.internal-server-error</t>
+          <t>refresh-token.messages.mismatch-or-expired</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Refresh token mismatch or expired</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Thiếu refresh token hoặc đã hết hạn</t>
         </is>
       </c>
     </row>
     <row r="169" ht="17" customHeight="1">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t>register.messages.missing-fields</t>
+          <t>refresh-token.messages.success</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>Username, password, gender, displayName and email are required</t>
+          <t>Token refreshed</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>Tên người dùng, mật khẩu, giới tính, tên hiển thị và email là bắt buộc</t>
+          <t>Token đã làm mới</t>
         </is>
       </c>
     </row>
     <row r="170" ht="17" customHeight="1">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t>register.messages.success</t>
+          <t>register.messages.email-exists</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>User created successfully</t>
+          <t>Email already exists</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>Người dùng được tạo thành công</t>
+          <t>Email đã tồn tại</t>
         </is>
       </c>
     </row>
     <row r="171" ht="17" customHeight="1">
       <c r="A171" s="1" t="inlineStr">
         <is>
-          <t>register.messages.username-exists</t>
+          <t>register.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>Username already exists</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>Tên người dùng đã tồn tại</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="172" ht="17" customHeight="1">
       <c r="A172" s="1" t="inlineStr">
         <is>
-          <t>reset-password.messages.internal-server-error</t>
+          <t>register.messages.missing-fields</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Username, password, gender, displayName and email are required</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Tên người dùng, mật khẩu, giới tính, tên hiển thị và email là bắt buộc</t>
         </is>
       </c>
     </row>
     <row r="173" ht="17" customHeight="1">
       <c r="A173" s="1" t="inlineStr">
         <is>
-          <t>reset-password.messages.invalid-or-expired-token</t>
+          <t>register.messages.success</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>Invalid or expired reset password token</t>
+          <t>User created successfully</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>Token đặt lại mật khẩu không hợp lệ hoặc đã hết hạn</t>
+          <t>Người dùng được tạo thành công</t>
         </is>
       </c>
     </row>
     <row r="174" ht="17" customHeight="1">
       <c r="A174" s="1" t="inlineStr">
         <is>
-          <t>reset-password.messages.invalid-user-id</t>
+          <t>register.messages.username-exists</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>Invalid user id</t>
+          <t>Username already exists</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>ID người dùng không hợp lệ</t>
+          <t>Tên người dùng đã tồn tại</t>
         </is>
       </c>
     </row>
     <row r="175" ht="17" customHeight="1">
       <c r="A175" s="1" t="inlineStr">
         <is>
-          <t>reset-password.messages.missing-id-or-token</t>
+          <t>reset-password.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>ID and token are required</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>ID và token là bắt buộc</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="176" ht="17" customHeight="1">
       <c r="A176" s="1" t="inlineStr">
         <is>
-          <t>reset-password.messages.missing-userId-or-password</t>
+          <t>reset-password.messages.invalid-or-expired-token</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>UserId and password are required</t>
+          <t>Invalid or expired reset password token</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>UserId và mật khẩu là bắt buộc</t>
+          <t>Token đặt lại mật khẩu không hợp lệ hoặc đã hết hạn</t>
         </is>
       </c>
     </row>
     <row r="177" ht="17" customHeight="1">
       <c r="A177" s="1" t="inlineStr">
         <is>
-          <t>reset-password.messages.token-valid</t>
+          <t>reset-password.messages.invalid-user-id</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>Reset password token is valid</t>
+          <t>Invalid user id</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>Token đặt lại mật khẩu hợp lệ</t>
+          <t>ID người dùng không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="178" ht="17" customHeight="1">
       <c r="A178" s="1" t="inlineStr">
         <is>
-          <t>reset-password.messages.user-not-found</t>
+          <t>reset-password.messages.missing-id-or-token</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>User not found</t>
+          <t>ID and token are required</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy người dùng</t>
+          <t>ID và token là bắt buộc</t>
         </is>
       </c>
     </row>
     <row r="179" ht="17" customHeight="1">
       <c r="A179" s="1" t="inlineStr">
         <is>
-          <t>set-room-status.messages.internal-server-error</t>
+          <t>reset-password.messages.missing-userId-or-password</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>UserId and password are required</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>UserId và mật khẩu là bắt buộc</t>
         </is>
       </c>
     </row>
     <row r="180" ht="17" customHeight="1">
       <c r="A180" s="1" t="inlineStr">
         <is>
-          <t>set-room-status.messages.invalid-room-id</t>
+          <t>reset-password.messages.token-valid</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>Field 'id' is required and must be a positive integer</t>
+          <t>Reset password token is valid</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
+          <t>Token đặt lại mật khẩu hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="181" ht="17" customHeight="1">
       <c r="A181" s="1" t="inlineStr">
         <is>
-          <t>set-room-status.messages.invalid-status</t>
+          <t>reset-password.messages.user-not-found</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>Field 'status' must be either 1 or 2</t>
+          <t>User not found</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>Trường 'status' phải là 1 hoặc 2</t>
+          <t>Không tìm thấy người dùng</t>
         </is>
       </c>
     </row>
     <row r="182" ht="17" customHeight="1">
       <c r="A182" s="1" t="inlineStr">
         <is>
-          <t>set-room-status.messages.room-not-found</t>
+          <t>set-room-status.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>Room not found</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy phòng</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="183" ht="17" customHeight="1">
       <c r="A183" s="1" t="inlineStr">
         <is>
-          <t>set-room-status.messages.success</t>
+          <t>set-room-status.messages.invalid-room-id</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>Set room status successfully</t>
+          <t>Field 'id' is required and must be a positive integer</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>Đặt trạng thái phòng thành công</t>
+          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
         </is>
       </c>
     </row>
     <row r="184" ht="17" customHeight="1">
       <c r="A184" s="1" t="inlineStr">
         <is>
-          <t>room.actions.start-room</t>
+          <t>set-room-status.messages.invalid-status</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>Start room</t>
+          <t>Field 'status' must be either 1 or 2</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>Bắt đầu chơi</t>
+          <t>Trường 'status' phải là 1 hoặc 2</t>
         </is>
       </c>
     </row>
     <row r="185" ht="17" customHeight="1">
       <c r="A185" s="1" t="inlineStr">
         <is>
-          <t>room.actions.undo</t>
+          <t>set-room-status.messages.room-not-found</t>
         </is>
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>Undo</t>
+          <t>Room not found</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>Hoán tác</t>
+          <t>Không tìm thấy phòng</t>
         </is>
       </c>
     </row>
     <row r="186" ht="17" customHeight="1">
       <c r="A186" s="1" t="inlineStr">
         <is>
-          <t>room.actions.surrender</t>
+          <t>set-room-status.messages.success</t>
         </is>
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>Surrender</t>
+          <t>Set room status successfully</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>Đầu hàng</t>
+          <t>Đặt trạng thái phòng thành công</t>
         </is>
       </c>
     </row>
     <row r="187" ht="17" customHeight="1">
       <c r="A187" s="1" t="inlineStr">
         <is>
-          <t>room.actions.draw</t>
+          <t>room.actions.start-room</t>
         </is>
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>Draw</t>
+          <t>Start room</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>Hòa</t>
+          <t>Bắt đầu chơi</t>
         </is>
       </c>
     </row>
     <row r="188" ht="17" customHeight="1">
       <c r="A188" s="1" t="inlineStr">
         <is>
-          <t>room.actions.back-home</t>
+          <t>room.actions.undo</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>Back to home</t>
+          <t>Undo</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>Thoát phòng</t>
+          <t>Hoán tác</t>
         </is>
       </c>
     </row>
     <row r="189" ht="17" customHeight="1">
       <c r="A189" s="1" t="inlineStr">
         <is>
-          <t>room.actions.confirm-leave</t>
+          <t>room.actions.surrender</t>
         </is>
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>Are you sure you want to leave room?</t>
+          <t>Surrender</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>Bạn có chắc muốn rời bàn chơi?</t>
+          <t>Đầu hàng</t>
         </is>
       </c>
     </row>
     <row r="190" ht="17" customHeight="1">
       <c r="A190" s="1" t="inlineStr">
         <is>
-          <t>room.actions.confirm-surrender</t>
+          <t>room.actions.draw</t>
         </is>
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>Are you sure you want to surrender?</t>
+          <t>Draw</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>Bạn có chắc chắn muốn đầu hàng không?</t>
+          <t>Hòa</t>
         </is>
       </c>
     </row>
     <row r="191" ht="17" customHeight="1">
       <c r="A191" s="1" t="inlineStr">
         <is>
-          <t>room.actions.confirm-draw</t>
+          <t>room.actions.back-home</t>
         </is>
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>Are you sure you want to draw?</t>
+          <t>Back to home</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>Bạn có chắc chắn muốn hòa không?</t>
+          <t>Thoát phòng</t>
         </is>
       </c>
     </row>
     <row r="192" ht="17" customHeight="1">
       <c r="A192" s="1" t="inlineStr">
         <is>
-          <t>room.actions.confirm-accept-draw</t>
+          <t>room.actions.confirm-leave</t>
         </is>
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>Opponent has proposed a draw. Do you accept?</t>
+          <t>Are you sure you want to leave room?</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>Đối phương đã chủ hòa, bạn có đồng ý không?</t>
+          <t>Bạn có chắc muốn rời bàn chơi?</t>
         </is>
       </c>
     </row>
     <row r="193" ht="17" customHeight="1">
       <c r="A193" s="1" t="inlineStr">
         <is>
-          <t>room.actions.accept-draw</t>
+          <t>room.actions.confirm-surrender</t>
         </is>
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>Accept</t>
+          <t>Are you sure you want to surrender?</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>Chấp nhận</t>
+          <t>Bạn có chắc chắn muốn đầu hàng không?</t>
         </is>
       </c>
     </row>
     <row r="194" ht="17" customHeight="1">
       <c r="A194" s="1" t="inlineStr">
         <is>
-          <t>room.actions.reject-draw</t>
+          <t>room.actions.confirm-draw</t>
         </is>
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>Reject</t>
+          <t>Are you sure you want to draw?</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>Từ chối</t>
+          <t>Bạn có chắc chắn muốn hòa không?</t>
         </is>
       </c>
     </row>
     <row r="195" ht="17" customHeight="1">
       <c r="A195" s="1" t="inlineStr">
         <is>
-          <t>room.actions.draw-accepted</t>
+          <t>room.actions.confirm-accept-draw</t>
         </is>
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>Opponent accepted the draw</t>
+          <t>Opponent has proposed a draw. Do you accept?</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>Đối phương đã đồng ý hòa</t>
-        </is>
-      </c>
-    </row>
-    <row r="196" ht="18" customHeight="1">
+          <t>Đối phương đã chủ hòa, bạn có đồng ý không?</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="17" customHeight="1">
       <c r="A196" s="1" t="inlineStr">
         <is>
-          <t>room.actions.draw-rejected</t>
+          <t>room.actions.accept-draw</t>
         </is>
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>Opponent rejected the draw</t>
+          <t>Accept</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>Đối phương từ chối hòa</t>
+          <t>Chấp nhận</t>
         </is>
       </c>
     </row>
     <row r="197" ht="18" customHeight="1">
       <c r="A197" s="1" t="inlineStr">
         <is>
-          <t>room.actions.draw-completed</t>
+          <t>room.actions.reject-draw</t>
         </is>
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>Draw completed</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>Hòa cờ thành công</t>
+          <t>Từ chối</t>
         </is>
       </c>
     </row>
     <row r="198" ht="18" customHeight="1">
       <c r="A198" s="1" t="inlineStr">
         <is>
-          <t>room.actions.opponent-surrendered</t>
+          <t>room.actions.draw-accepted</t>
         </is>
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>Opponent surrendered! You won!</t>
+          <t>Opponent accepted the draw</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>Đối phương đã đầu hàng! Bạn thắng!</t>
+          <t>Đối phương đã đồng ý hòa</t>
         </is>
       </c>
     </row>
     <row r="199" ht="18" customHeight="1">
       <c r="A199" s="1" t="inlineStr">
         <is>
-          <t>room.actions.kick</t>
+          <t>room.actions.draw-rejected</t>
         </is>
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>Kick</t>
+          <t>Opponent rejected the draw</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>Kick</t>
+          <t>Đối phương từ chối hòa</t>
         </is>
       </c>
     </row>
     <row r="200" ht="18" customHeight="1">
       <c r="A200" s="1" t="inlineStr">
         <is>
-          <t>room.actions.settings</t>
+          <t>room.actions.draw-completed</t>
         </is>
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>Room settings</t>
+          <t>Draw completed</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>Cài đặt phòng</t>
+          <t>Hòa cờ thành công</t>
         </is>
       </c>
     </row>
     <row r="201" ht="18" customHeight="1">
       <c r="A201" s="1" t="inlineStr">
         <is>
-          <t>room.settings.title</t>
+          <t>room.actions.opponent-surrendered</t>
         </is>
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>Room Settings</t>
+          <t>Opponent surrendered! You won!</t>
         </is>
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>Cài đặt phòng</t>
+          <t>Đối phương đã đầu hàng! Bạn thắng!</t>
         </is>
       </c>
     </row>
     <row r="202" ht="18" customHeight="1">
       <c r="A202" s="1" t="inlineStr">
         <is>
-          <t>room.settings.room-name</t>
+          <t>room.actions.send-pm</t>
         </is>
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>Room name</t>
+          <t>Send PM</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>Tên phòng</t>
+          <t>Chat</t>
         </is>
       </c>
     </row>
     <row r="203" ht="18" customHeight="1">
       <c r="A203" s="1" t="inlineStr">
         <is>
-          <t>room.settings.players</t>
+          <t>room.actions.view-history</t>
         </is>
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>Spectators</t>
+          <t>History</t>
         </is>
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>Người xem</t>
+          <t>Lịch sử</t>
         </is>
       </c>
     </row>
     <row r="204" ht="18" customHeight="1">
       <c r="A204" s="1" t="inlineStr">
         <is>
-          <t>room.settings.save</t>
+          <t>room.actions.kick</t>
         </is>
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>Save</t>
+          <t>Kick</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>Lưu</t>
+          <t>Kick</t>
         </is>
       </c>
     </row>
     <row r="205" ht="18" customHeight="1">
       <c r="A205" s="1" t="inlineStr">
         <is>
-          <t>update-room.messages.success</t>
+          <t>room.actions.settings</t>
         </is>
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>Room updated successfully</t>
+          <t>Room settings</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>Cập nhật phòng thành công</t>
+          <t>Cài đặt phòng</t>
         </is>
       </c>
     </row>
     <row r="206" ht="18" customHeight="1">
       <c r="A206" s="1" t="inlineStr">
         <is>
-          <t>update-room.messages.internal-server-error</t>
+          <t>room.settings.title</t>
         </is>
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Room Settings</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Cài đặt phòng</t>
         </is>
       </c>
     </row>
     <row r="207" ht="18" customHeight="1">
       <c r="A207" s="1" t="inlineStr">
         <is>
-          <t>update-room.messages.invalid-room-id</t>
+          <t>room.settings.room-name</t>
         </is>
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>Invalid room ID</t>
+          <t>Room name</t>
         </is>
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>ID phòng không hợp lệ</t>
+          <t>Tên phòng</t>
         </is>
       </c>
     </row>
     <row r="208" ht="18" customHeight="1">
       <c r="A208" s="1" t="inlineStr">
         <is>
-          <t>update-room.messages.name-required</t>
+          <t>room.settings.players</t>
         </is>
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>Room name is required</t>
+          <t>Spectators</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>Tên phòng không được để trống</t>
+          <t>Người xem</t>
         </is>
       </c>
     </row>
     <row r="209" ht="18" customHeight="1">
       <c r="A209" s="1" t="inlineStr">
         <is>
-          <t>update-room.messages.room-not-found</t>
+          <t>room.settings.save</t>
         </is>
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>Room not found</t>
+          <t>Save</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy phòng</t>
+          <t>Lưu</t>
         </is>
       </c>
     </row>
     <row r="210" ht="18" customHeight="1">
       <c r="A210" s="1" t="inlineStr">
         <is>
-          <t>update-room.messages.forbidden</t>
+          <t>update-room.messages.success</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>You are not the host of this room</t>
+          <t>Room updated successfully</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>Bạn không phải chủ phòng</t>
+          <t>Cập nhật phòng thành công</t>
         </is>
       </c>
     </row>
     <row r="211" ht="18" customHeight="1">
       <c r="A211" s="1" t="inlineStr">
         <is>
-          <t>draw-game.messages.invalid-game-id</t>
+          <t>update-room.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>Invalid game ID</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>ID trò chơi không hợp lệ</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="212" ht="18" customHeight="1">
       <c r="A212" s="1" t="inlineStr">
         <is>
-          <t>draw-game.messages.game-not-found</t>
+          <t>update-room.messages.invalid-room-id</t>
         </is>
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>Game not found</t>
+          <t>Invalid room ID</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy trò chơi</t>
+          <t>ID phòng không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="213" ht="18" customHeight="1">
       <c r="A213" s="1" t="inlineStr">
         <is>
-          <t>draw-game.messages.forbidden</t>
+          <t>update-room.messages.name-required</t>
         </is>
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>You are not in this room</t>
+          <t>Room name is required</t>
         </is>
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>Bạn không có trong phòng này</t>
+          <t>Tên phòng không được để trống</t>
         </is>
       </c>
     </row>
     <row r="214" ht="18" customHeight="1">
       <c r="A214" s="1" t="inlineStr">
         <is>
-          <t>draw-game.messages.game-history-not-found</t>
+          <t>update-room.messages.room-not-found</t>
         </is>
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>Game history not found</t>
+          <t>Room not found</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy lịch sử trò chơi</t>
+          <t>Không tìm thấy phòng</t>
         </is>
       </c>
     </row>
     <row r="215" ht="18" customHeight="1">
       <c r="A215" s="1" t="inlineStr">
         <is>
-          <t>draw-game.messages.game-already-finished</t>
+          <t>update-room.messages.forbidden</t>
         </is>
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>Game is already finished</t>
+          <t>You are not the host of this room</t>
         </is>
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>Trò chơi đã kết thúc</t>
+          <t>Bạn không phải chủ phòng</t>
         </is>
       </c>
     </row>
     <row r="216" ht="18" customHeight="1">
       <c r="A216" s="1" t="inlineStr">
         <is>
-          <t>draw-game.messages.success</t>
+          <t>draw-game.messages.invalid-game-id</t>
         </is>
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>Draw game successfully</t>
+          <t>Invalid game ID</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>Hòa cờ thành công</t>
+          <t>ID trò chơi không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="217" ht="18" customHeight="1">
       <c r="A217" s="1" t="inlineStr">
         <is>
-          <t>draw-game.messages.internal-server-error</t>
+          <t>draw-game.messages.game-not-found</t>
         </is>
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Game not found</t>
         </is>
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Không tìm thấy trò chơi</t>
         </is>
       </c>
     </row>
     <row r="218" ht="18" customHeight="1">
       <c r="A218" s="1" t="inlineStr">
         <is>
-          <t>surrender.messages.game-already-finished</t>
+          <t>draw-game.messages.forbidden</t>
         </is>
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>Game is already finished</t>
+          <t>You are not in this room</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>Trò chơi đã kết thúc</t>
+          <t>Bạn không có trong phòng này</t>
         </is>
       </c>
     </row>
     <row r="219" ht="18" customHeight="1">
       <c r="A219" s="1" t="inlineStr">
         <is>
-          <t>surrender.messages.game-history-not-found</t>
+          <t>draw-game.messages.game-history-not-found</t>
         </is>
       </c>
       <c r="B219" s="2" t="inlineStr">
@@ -4059,1151 +4059,1241 @@
     <row r="220" ht="18" customHeight="1">
       <c r="A220" s="1" t="inlineStr">
         <is>
-          <t>surrender.messages.game-not-found</t>
+          <t>draw-game.messages.game-already-finished</t>
         </is>
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>Game not found</t>
+          <t>Game is already finished</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy trò chơi</t>
-        </is>
-      </c>
-    </row>
-    <row r="221" ht="17" customHeight="1">
+          <t>Trò chơi đã kết thúc</t>
+        </is>
+      </c>
+    </row>
+    <row r="221" ht="18" customHeight="1">
       <c r="A221" s="1" t="inlineStr">
         <is>
-          <t>surrender.messages.internal-server-error</t>
+          <t>draw-game.messages.success</t>
         </is>
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
+          <t>Draw game successfully</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>Hòa cờ thành công</t>
+        </is>
+      </c>
+    </row>
+    <row r="222" ht="18" customHeight="1">
+      <c r="A222" s="1" t="inlineStr">
+        <is>
+          <t>draw-game.messages.internal-server-error</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
           <t>Internal server error</t>
         </is>
       </c>
-      <c r="C221" s="2" t="inlineStr">
+      <c r="C222" s="2" t="inlineStr">
         <is>
           <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
-    <row r="222" ht="17" customHeight="1">
-      <c r="A222" s="1" t="inlineStr">
-        <is>
-          <t>surrender.messages.invalid-game-id</t>
-        </is>
-      </c>
-      <c r="B222" s="2" t="inlineStr">
-        <is>
-          <t>Invalid game ID</t>
-        </is>
-      </c>
-      <c r="C222" s="2" t="inlineStr">
-        <is>
-          <t>ID trò chơi không hợp lệ</t>
-        </is>
-      </c>
-    </row>
-    <row r="223" ht="17" customHeight="1">
+    <row r="223" ht="18" customHeight="1">
       <c r="A223" s="1" t="inlineStr">
         <is>
-          <t>surrender.messages.invalid-surrender-player</t>
+          <t>surrender.messages.game-already-finished</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>You are not a player in this game</t>
+          <t>Game is already finished</t>
         </is>
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>Bạn không phải là người chơi trong trò chơi này</t>
+          <t>Trò chơi đã kết thúc</t>
         </is>
       </c>
     </row>
     <row r="224" ht="17" customHeight="1">
       <c r="A224" s="1" t="inlineStr">
         <is>
-          <t>surrender.messages.opponent-not-found</t>
+          <t>surrender.messages.game-history-not-found</t>
         </is>
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>Opponent not found</t>
+          <t>Game history not found</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy đối thủ</t>
+          <t>Không tìm thấy lịch sử trò chơi</t>
         </is>
       </c>
     </row>
     <row r="225" ht="17" customHeight="1">
       <c r="A225" s="1" t="inlineStr">
         <is>
-          <t>surrender.messages.success</t>
+          <t>surrender.messages.game-not-found</t>
         </is>
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>Surrendered</t>
+          <t>Game not found</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>Đã đầu hàng</t>
+          <t>Không tìm thấy trò chơi</t>
         </is>
       </c>
     </row>
     <row r="226" ht="17" customHeight="1">
       <c r="A226" s="1" t="inlineStr">
         <is>
-          <t>undo.messages.invalid-game-id</t>
+          <t>surrender.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>Invalid game ID</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>ID trò chơi không hợp lệ</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="227" ht="17" customHeight="1">
       <c r="A227" s="1" t="inlineStr">
         <is>
-          <t>undo.messages.unauthorized</t>
+          <t>surrender.messages.invalid-game-id</t>
         </is>
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>Unauthorized</t>
+          <t>Invalid game ID</t>
         </is>
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>Không được phép truy cập</t>
+          <t>ID trò chơi không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="228" ht="17" customHeight="1">
       <c r="A228" s="1" t="inlineStr">
         <is>
-          <t>undo.messages.game-not-found</t>
+          <t>surrender.messages.invalid-surrender-player</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>Game not found</t>
+          <t>You are not a player in this game</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy trò chơi</t>
+          <t>Bạn không phải là người chơi trong trò chơi này</t>
         </is>
       </c>
     </row>
     <row r="229" ht="17" customHeight="1">
       <c r="A229" s="1" t="inlineStr">
         <is>
-          <t>undo.messages.not-in-game</t>
+          <t>surrender.messages.opponent-not-found</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>You are not part of this game</t>
+          <t>Opponent not found</t>
         </is>
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>Bạn không phải là người chơi trong trò chơi này</t>
+          <t>Không tìm thấy đối thủ</t>
         </is>
       </c>
     </row>
     <row r="230" ht="17" customHeight="1">
       <c r="A230" s="1" t="inlineStr">
         <is>
-          <t>undo.messages.not-in-room</t>
+          <t>surrender.messages.success</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>You are not in this room</t>
+          <t>Surrendered</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>Bạn không trong phòng này</t>
+          <t>Đã đầu hàng</t>
         </is>
       </c>
     </row>
     <row r="231" ht="17" customHeight="1">
       <c r="A231" s="1" t="inlineStr">
         <is>
-          <t>undo.messages.spectator-cannot-undo</t>
+          <t>undo.messages.invalid-game-id</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>Spectators cannot undo moves</t>
+          <t>Invalid game ID</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>Người xem không thể hoàn tác nước đi</t>
+          <t>ID trò chơi không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="232" ht="17" customHeight="1">
       <c r="A232" s="1" t="inlineStr">
         <is>
-          <t>undo.messages.no-moves</t>
+          <t>undo.messages.unauthorized</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>No moves to undo</t>
+          <t>Unauthorized</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>Không có nước đi để hoàn tác</t>
+          <t>Không được phép truy cập</t>
         </is>
       </c>
     </row>
     <row r="233" ht="17" customHeight="1">
       <c r="A233" s="1" t="inlineStr">
         <is>
-          <t>undo.messages.delete-failed</t>
+          <t>undo.messages.game-not-found</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>Failed to undo move</t>
+          <t>Game not found</t>
         </is>
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>Không thể hoàn tác nước đi</t>
+          <t>Không tìm thấy trò chơi</t>
         </is>
       </c>
     </row>
     <row r="234" ht="17" customHeight="1">
       <c r="A234" s="1" t="inlineStr">
         <is>
-          <t>undo.messages.undo-limit-exceeded</t>
+          <t>undo.messages.not-in-game</t>
         </is>
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>Maximum 3 undo per game exceeded</t>
+          <t>You are not part of this game</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>Đã đạt tối đa 3 lần hoàn tác trong trò chơi</t>
+          <t>Bạn không phải là người chơi trong trò chơi này</t>
         </is>
       </c>
     </row>
     <row r="235" ht="17" customHeight="1">
       <c r="A235" s="1" t="inlineStr">
         <is>
-          <t>undo.messages.success</t>
-        </is>
-      </c>
-      <c r="B235" s="1" t="inlineStr">
-        <is>
-          <t>Move undone successfully</t>
-        </is>
-      </c>
-      <c r="C235" s="1" t="inlineStr">
-        <is>
-          <t>Hoàn tác nước đi thành công</t>
+          <t>undo.messages.not-in-room</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>You are not in this room</t>
+        </is>
+      </c>
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>Bạn không trong phòng này</t>
         </is>
       </c>
     </row>
     <row r="236" ht="17" customHeight="1">
-      <c r="A236" s="2" t="inlineStr">
-        <is>
-          <t>undo.messages.internal-server-error</t>
+      <c r="A236" s="1" t="inlineStr">
+        <is>
+          <t>undo.messages.spectator-cannot-undo</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Spectators cannot undo moves</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
-        </is>
-      </c>
-    </row>
-    <row r="237" ht="18" customHeight="1">
-      <c r="A237" s="2" t="inlineStr">
-        <is>
-          <t>player-history.messages.invalid-user-id</t>
+          <t>Người xem không thể hoàn tác nước đi</t>
+        </is>
+      </c>
+    </row>
+    <row r="237" ht="17" customHeight="1">
+      <c r="A237" s="1" t="inlineStr">
+        <is>
+          <t>undo.messages.no-moves</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>Invalid user ID</t>
+          <t>No moves to undo</t>
         </is>
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>ID người dùng không hợp lệ</t>
-        </is>
-      </c>
-    </row>
-    <row r="238" ht="18" customHeight="1">
-      <c r="A238" s="2" t="inlineStr">
-        <is>
-          <t>player-history.messages.success</t>
-        </is>
-      </c>
-      <c r="B238" s="2" t="inlineStr">
-        <is>
-          <t>Fetch game history successfully</t>
-        </is>
-      </c>
-      <c r="C238" s="2" t="inlineStr">
-        <is>
-          <t>Lấy lịch sử trò chơi thành công</t>
-        </is>
-      </c>
-    </row>
-    <row r="239" ht="18" customHeight="1">
+          <t>Không có nước đi để hoàn tác</t>
+        </is>
+      </c>
+    </row>
+    <row r="238" ht="17" customHeight="1">
+      <c r="A238" s="1" t="inlineStr">
+        <is>
+          <t>undo.messages.delete-failed</t>
+        </is>
+      </c>
+      <c r="B238" s="1" t="inlineStr">
+        <is>
+          <t>Failed to undo move</t>
+        </is>
+      </c>
+      <c r="C238" s="1" t="inlineStr">
+        <is>
+          <t>Không thể hoàn tác nước đi</t>
+        </is>
+      </c>
+    </row>
+    <row r="239" ht="17" customHeight="1">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>validate-token.messages.success</t>
+          <t>undo.messages.undo-limit-exceeded</t>
         </is>
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>Token is valid</t>
+          <t>Maximum 3 undo per game exceeded</t>
         </is>
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>Token hợp lệ</t>
+          <t>Đã đạt tối đa 3 lần hoàn tác trong trò chơi</t>
         </is>
       </c>
     </row>
     <row r="240" ht="18" customHeight="1">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>guide.section.objective</t>
+          <t>undo.messages.success</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>Objective of the game</t>
+          <t>Move undone successfully</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>Mục tiêu của trò chơi</t>
+          <t>Hoàn tác nước đi thành công</t>
         </is>
       </c>
     </row>
     <row r="241" ht="18" customHeight="1">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>guide.section.pieces</t>
+          <t>undo.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>Pieces</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>Quân cờ</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="242" ht="18" customHeight="1">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>guide.section.moving-pieces</t>
+          <t>player-history.messages.invalid-user-id</t>
         </is>
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>Moving pieces</t>
+          <t>Invalid user ID</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>Đi quân</t>
+          <t>ID người dùng không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="243" ht="18" customHeight="1">
       <c r="A243" s="2" t="inlineStr">
         <is>
+          <t>player-history.messages.success</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>Fetch game history successfully</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>Lấy lịch sử trò chơi thành công</t>
+        </is>
+      </c>
+    </row>
+    <row r="244" ht="18" customHeight="1">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>validate-token.messages.success</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>Token is valid</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>Token hợp lệ</t>
+        </is>
+      </c>
+    </row>
+    <row r="245" ht="18" customHeight="1">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>guide.section.objective</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>Objective of the game</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>Mục tiêu của trò chơi</t>
+        </is>
+      </c>
+    </row>
+    <row r="246" ht="18" customHeight="1">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>guide.section.pieces</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>Pieces</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>Quân cờ</t>
+        </is>
+      </c>
+    </row>
+    <row r="247" ht="90" customHeight="1">
+      <c r="A247" s="1" t="inlineStr">
+        <is>
+          <t>guide.section.moving-pieces</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>Moving pieces</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>Đi quân</t>
+        </is>
+      </c>
+    </row>
+    <row r="248" ht="90" customHeight="1">
+      <c r="A248" s="1" t="inlineStr">
+        <is>
           <t>guide.section.capturing</t>
         </is>
       </c>
-      <c r="B243" s="2" t="inlineStr">
+      <c r="B248" s="2" t="inlineStr">
         <is>
           <t>Capturing</t>
         </is>
       </c>
-      <c r="C243" s="2" t="inlineStr">
+      <c r="C248" s="2" t="inlineStr">
         <is>
           <t>Bắt quân</t>
-        </is>
-      </c>
-    </row>
-    <row r="244" ht="90" customHeight="1">
-      <c r="A244" s="1" t="inlineStr">
-        <is>
-          <t>guide.section.check</t>
-        </is>
-      </c>
-      <c r="B244" s="2" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
-      <c r="C244" s="2" t="inlineStr">
-        <is>
-          <t>Chiếu tướng</t>
-        </is>
-      </c>
-    </row>
-    <row r="245" ht="90" customHeight="1">
-      <c r="A245" s="1" t="inlineStr">
-        <is>
-          <t>guide.section.result</t>
-        </is>
-      </c>
-      <c r="B245" s="2" t="inlineStr">
-        <is>
-          <t>Result</t>
-        </is>
-      </c>
-      <c r="C245" s="2" t="inlineStr">
-        <is>
-          <t>Kết quả</t>
-        </is>
-      </c>
-    </row>
-    <row r="246" ht="18" customHeight="1">
-      <c r="A246" s="1" t="inlineStr">
-        <is>
-          <t>guide.table.piece</t>
-        </is>
-      </c>
-      <c r="B246" s="2" t="inlineStr">
-        <is>
-          <t>Piece</t>
-        </is>
-      </c>
-      <c r="C246" s="2" t="inlineStr">
-        <is>
-          <t>Quân</t>
-        </is>
-      </c>
-    </row>
-    <row r="247" ht="18" customHeight="1">
-      <c r="A247" s="1" t="inlineStr">
-        <is>
-          <t>guide.table.symbol</t>
-        </is>
-      </c>
-      <c r="B247" s="2" t="inlineStr">
-        <is>
-          <t>Symbol</t>
-        </is>
-      </c>
-      <c r="C247" s="2" t="inlineStr">
-        <is>
-          <t>Ký hiệu</t>
-        </is>
-      </c>
-    </row>
-    <row r="248" ht="18" customHeight="1">
-      <c r="A248" s="1" t="inlineStr">
-        <is>
-          <t>guide.table.quantity</t>
-        </is>
-      </c>
-      <c r="B248" s="2" t="inlineStr">
-        <is>
-          <t>Quantity</t>
-        </is>
-      </c>
-      <c r="C248" s="2" t="inlineStr">
-        <is>
-          <t>Số lượng</t>
         </is>
       </c>
     </row>
     <row r="249" ht="18" customHeight="1">
       <c r="A249" s="1" t="inlineStr">
         <is>
-          <t>guide.objective.paragraph1</t>
+          <t>guide.section.check</t>
         </is>
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>A match is played between two players: one controls the Red pieces, and the other controls the Black pieces. The objective of each player is to use their pieces on the board to &lt;b&gt;checkmate&lt;/b&gt; the opponent's General, and win the game.</t>
+          <t>Check</t>
         </is>
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>Ván cờ được tiến hành giữa 2 đấu thủ, một người cầm Quân Đỏ, một người cầm Quân Đen. Mục đích của mỗi đấu thủ là tìm mọi cách sử dụng các quân trên bàn cờ để &lt;b&gt;chiếu bí Tướng&lt;/b&gt; của đối phương, giành thắng lợi.</t>
+          <t>Chiếu tướng</t>
         </is>
       </c>
     </row>
     <row r="250" ht="18" customHeight="1">
       <c r="A250" s="1" t="inlineStr">
         <is>
-          <t>guide.pieces.paragraph1</t>
+          <t>guide.section.result</t>
         </is>
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>At the start of each game, there must be 32 pieces in total, consisting of &lt;b&gt;7 piece types&lt;/b&gt; split evenly between both sides: 16 Red pieces and 16 Black pieces. The 7 piece types with their symbols and quantities are as follows:</t>
+          <t>Result</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>Mỗi ván cờ lúc bắt đầu phải có đủ 32 quân, gồm 7 loại chia đều cho mỗi bên gồm 16 quân Đỏ và 16 quân Đen. &lt;b&gt;7 loại quân&lt;/b&gt; có ký hiệu và số lượng như sau:</t>
+          <t>Kết quả</t>
         </is>
       </c>
     </row>
     <row r="251" ht="18" customHeight="1">
       <c r="A251" s="1" t="inlineStr">
         <is>
-          <t>guide.piece.general</t>
+          <t>guide.table.piece</t>
         </is>
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Piece</t>
         </is>
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>Tướng</t>
+          <t>Quân</t>
         </is>
       </c>
     </row>
     <row r="252" ht="18" customHeight="1">
       <c r="A252" s="1" t="inlineStr">
         <is>
-          <t>guide.piece.advisor</t>
+          <t>guide.table.symbol</t>
         </is>
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>Advisor</t>
+          <t>Symbol</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>Sĩ</t>
-        </is>
-      </c>
-    </row>
-    <row r="253" ht="54" customHeight="1">
+          <t>Ký hiệu</t>
+        </is>
+      </c>
+    </row>
+    <row r="253" ht="18" customHeight="1">
       <c r="A253" s="1" t="inlineStr">
         <is>
-          <t>guide.piece.elephant</t>
+          <t>guide.table.quantity</t>
         </is>
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Quantity</t>
         </is>
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>Tượng</t>
+          <t>Số lượng</t>
         </is>
       </c>
     </row>
     <row r="254" ht="18" customHeight="1">
       <c r="A254" s="1" t="inlineStr">
         <is>
+          <t>guide.objective.paragraph1</t>
+        </is>
+      </c>
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t>A match is played between two players: one controls the Red pieces, and the other controls the Black pieces. The objective of each player is to use their pieces on the board to &lt;b&gt;checkmate&lt;/b&gt; the opponent's General, and win the game.</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>Ván cờ được tiến hành giữa 2 đấu thủ, một người cầm Quân Đỏ, một người cầm Quân Đen. Mục đích của mỗi đấu thủ là tìm mọi cách sử dụng các quân trên bàn cờ để &lt;b&gt;chiếu bí Tướng&lt;/b&gt; của đối phương, giành thắng lợi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="255" ht="18" customHeight="1">
+      <c r="A255" s="1" t="inlineStr">
+        <is>
+          <t>guide.pieces.paragraph1</t>
+        </is>
+      </c>
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>At the start of each game, there must be 32 pieces in total, consisting of &lt;b&gt;7 piece types&lt;/b&gt; split evenly between both sides: 16 Red pieces and 16 Black pieces. The 7 piece types with their symbols and quantities are as follows:</t>
+        </is>
+      </c>
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t>Mỗi ván cờ lúc bắt đầu phải có đủ 32 quân, gồm 7 loại chia đều cho mỗi bên gồm 16 quân Đỏ và 16 quân Đen. &lt;b&gt;7 loại quân&lt;/b&gt; có ký hiệu và số lượng như sau:</t>
+        </is>
+      </c>
+    </row>
+    <row r="256" ht="54" customHeight="1">
+      <c r="A256" s="1" t="inlineStr">
+        <is>
+          <t>guide.piece.general</t>
+        </is>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>Tướng</t>
+        </is>
+      </c>
+    </row>
+    <row r="257" ht="18" customHeight="1">
+      <c r="A257" s="1" t="inlineStr">
+        <is>
+          <t>guide.piece.advisor</t>
+        </is>
+      </c>
+      <c r="B257" s="2" t="inlineStr">
+        <is>
+          <t>Advisor</t>
+        </is>
+      </c>
+      <c r="C257" s="2" t="inlineStr">
+        <is>
+          <t>Sĩ</t>
+        </is>
+      </c>
+    </row>
+    <row r="258" ht="90" customHeight="1">
+      <c r="A258" s="1" t="inlineStr">
+        <is>
+          <t>guide.piece.elephant</t>
+        </is>
+      </c>
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>Elephant</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>Tượng</t>
+        </is>
+      </c>
+    </row>
+    <row r="259" ht="18" customHeight="1">
+      <c r="A259" s="1" t="inlineStr">
+        <is>
           <t>guide.piece.chariot</t>
         </is>
       </c>
-      <c r="B254" s="2" t="inlineStr">
+      <c r="B259" s="2" t="inlineStr">
         <is>
           <t>Chariot</t>
         </is>
       </c>
-      <c r="C254" s="2" t="inlineStr">
+      <c r="C259" s="2" t="inlineStr">
         <is>
           <t>Xe</t>
         </is>
       </c>
     </row>
-    <row r="255" ht="90" customHeight="1">
-      <c r="A255" s="1" t="inlineStr">
+    <row r="260" ht="36" customHeight="1">
+      <c r="A260" s="1" t="inlineStr">
         <is>
           <t>guide.piece.horse</t>
         </is>
       </c>
-      <c r="B255" s="2" t="inlineStr">
+      <c r="B260" s="2" t="inlineStr">
         <is>
           <t>Horse</t>
         </is>
       </c>
-      <c r="C255" s="2" t="inlineStr">
+      <c r="C260" s="2" t="inlineStr">
         <is>
           <t>Mã</t>
         </is>
       </c>
     </row>
-    <row r="256" ht="18" customHeight="1">
-      <c r="A256" s="1" t="inlineStr">
+    <row r="261" ht="18" customHeight="1">
+      <c r="A261" s="1" t="inlineStr">
         <is>
           <t>guide.piece.cannon</t>
         </is>
       </c>
-      <c r="B256" s="2" t="inlineStr">
+      <c r="B261" s="2" t="inlineStr">
         <is>
           <t>Cannon</t>
         </is>
       </c>
-      <c r="C256" s="2" t="inlineStr">
+      <c r="C261" s="2" t="inlineStr">
         <is>
           <t>Pháo</t>
         </is>
       </c>
     </row>
-    <row r="257" ht="36" customHeight="1">
-      <c r="A257" s="1" t="inlineStr">
+    <row r="262" ht="72" customHeight="1">
+      <c r="A262" s="1" t="inlineStr">
         <is>
           <t>guide.piece.soldier</t>
         </is>
       </c>
-      <c r="B257" s="2" t="inlineStr">
+      <c r="B262" s="2" t="inlineStr">
         <is>
           <t>Soldier</t>
         </is>
       </c>
-      <c r="C257" s="2" t="inlineStr">
+      <c r="C262" s="2" t="inlineStr">
         <is>
           <t>Tốt</t>
         </is>
       </c>
     </row>
-    <row r="258" ht="18" customHeight="1">
-      <c r="A258" s="1" t="inlineStr">
+    <row r="263" ht="18" customHeight="1">
+      <c r="A263" s="1" t="inlineStr">
         <is>
           <t>guide.moving-pieces.paragraph1</t>
         </is>
       </c>
-      <c r="B258" s="2" t="inlineStr">
+      <c r="B263" s="2" t="inlineStr">
         <is>
           <t>On each turn, each side may move only one of its own pieces according to the rules. The movement rules are as follows:</t>
         </is>
       </c>
-      <c r="C258" s="2" t="inlineStr">
+      <c r="C263" s="2" t="inlineStr">
         <is>
           <t>Mỗi nước đi, mỗi bên chỉ được di chuyển quân của mình theo đúng quy định. Quy định di chuyển của các quân như sau:</t>
         </is>
       </c>
     </row>
-    <row r="259" ht="72" customHeight="1">
-      <c r="A259" s="1" t="inlineStr">
+    <row r="264" ht="54" customHeight="1">
+      <c r="A264" s="1" t="inlineStr">
         <is>
           <t>guide.general.paragraph1</t>
         </is>
       </c>
-      <c r="B259" s="2" t="inlineStr">
+      <c r="B264" s="2" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="C259" s="2" t="inlineStr">
+      <c r="C264" s="2" t="inlineStr">
         <is>
           <t>Tướng</t>
         </is>
       </c>
     </row>
-    <row r="260" ht="18" customHeight="1">
-      <c r="A260" s="1" t="inlineStr">
+    <row r="265" ht="18" customHeight="1">
+      <c r="A265" s="1" t="inlineStr">
         <is>
           <t>guide.general.paragraph2</t>
         </is>
       </c>
-      <c r="B260" s="2" t="inlineStr">
+      <c r="B265" s="2" t="inlineStr">
         <is>
           <t>Moves one step &lt;b&gt;horizontally or vertically&lt;/b&gt; within the palace. The two Generals may not face each other directly on the same file. If they are facing each other, there must be at least one piece of either side placed between them.</t>
         </is>
       </c>
-      <c r="C260" s="2" t="inlineStr">
+      <c r="C265" s="2" t="inlineStr">
         <is>
           <t>Mỗi nước được đi một bước &lt;b&gt;ngang hoặc dọc&lt;/b&gt; tùy ý trong cung Tướng. Hai tướng của 2 bên không được đối mặt nhau trực tiếp trên cùng một đường thẳng. Nếu đối mặt, bắt buộc phải có quân của bất kỳ bên nào đứng che mặt.</t>
         </is>
       </c>
     </row>
-    <row r="261" ht="54" customHeight="1">
-      <c r="A261" s="1" t="inlineStr">
+    <row r="266" ht="72" customHeight="1">
+      <c r="A266" s="1" t="inlineStr">
         <is>
           <t>guide.advisor.paragraph1</t>
         </is>
       </c>
-      <c r="B261" s="2" t="inlineStr">
+      <c r="B266" s="2" t="inlineStr">
         <is>
           <t>Advisor</t>
         </is>
       </c>
-      <c r="C261" s="2" t="inlineStr">
+      <c r="C266" s="2" t="inlineStr">
         <is>
           <t>Sĩ</t>
         </is>
       </c>
     </row>
-    <row r="262" ht="18" customHeight="1">
-      <c r="A262" s="1" t="inlineStr">
+    <row r="267" ht="18" customHeight="1">
+      <c r="A267" s="1" t="inlineStr">
         <is>
           <t>guide.advisor.paragraph2</t>
         </is>
       </c>
-      <c r="B262" s="2" t="inlineStr">
+      <c r="B267" s="2" t="inlineStr">
         <is>
           <t>Moves one step &lt;b&gt;diagonally&lt;/b&gt; within the palace.</t>
         </is>
       </c>
-      <c r="C262" s="2" t="inlineStr">
+      <c r="C267" s="2" t="inlineStr">
         <is>
           <t>Mỗi nước &lt;b&gt;đi chéo một bước&lt;/b&gt; trong cung Tướng.</t>
         </is>
       </c>
     </row>
-    <row r="263" ht="72" customHeight="1">
-      <c r="A263" s="1" t="inlineStr">
+    <row r="268" ht="90" customHeight="1">
+      <c r="A268" s="1" t="inlineStr">
         <is>
           <t>guide.elephant.paragraph1</t>
         </is>
       </c>
-      <c r="B263" s="2" t="inlineStr">
+      <c r="B268" s="2" t="inlineStr">
         <is>
           <t>Elephant</t>
         </is>
       </c>
-      <c r="C263" s="2" t="inlineStr">
+      <c r="C268" s="2" t="inlineStr">
         <is>
           <t>Tượng</t>
         </is>
       </c>
     </row>
-    <row r="264" ht="18" customHeight="1">
-      <c r="A264" s="1" t="inlineStr">
+    <row r="269" ht="18" customHeight="1">
+      <c r="A269" s="1" t="inlineStr">
         <is>
           <t>guide.elephant.paragraph2</t>
         </is>
       </c>
-      <c r="B264" s="2" t="inlineStr">
+      <c r="B269" s="2" t="inlineStr">
         <is>
           <t>Moves &lt;b&gt;two steps diagonally&lt;/b&gt; on its own side of the board and may not cross the river. If there is another piece on the midpoint of that diagonal path, the Elephant is blocked and cannot move.</t>
         </is>
       </c>
-      <c r="C264" s="2" t="inlineStr">
+      <c r="C269" s="2" t="inlineStr">
         <is>
           <t>Mỗi nước &lt;b&gt;đi chéo hai bước&lt;/b&gt; tại trận địa bên mình, không được qua sông. Nếu ở giữa đường chéo đó có quân khác đứng thì quân Tượng bị cản, không đi được.</t>
         </is>
       </c>
     </row>
-    <row r="265" ht="90" customHeight="1">
-      <c r="A265" s="1" t="inlineStr">
+    <row r="270" ht="72" customHeight="1">
+      <c r="A270" s="1" t="inlineStr">
         <is>
           <t>guide.chariot.paragraph1</t>
         </is>
       </c>
-      <c r="B265" s="2" t="inlineStr">
+      <c r="B270" s="2" t="inlineStr">
         <is>
           <t>Chariot</t>
         </is>
       </c>
-      <c r="C265" s="2" t="inlineStr">
+      <c r="C270" s="2" t="inlineStr">
         <is>
           <t>Xe</t>
         </is>
       </c>
     </row>
-    <row r="266" ht="18" customHeight="1">
-      <c r="A266" s="1" t="inlineStr">
+    <row r="271" ht="54" customHeight="1">
+      <c r="A271" s="1" t="inlineStr">
         <is>
           <t>guide.chariot.paragraph2</t>
         </is>
       </c>
-      <c r="B266" s="2" t="inlineStr">
+      <c r="B271" s="2" t="inlineStr">
         <is>
           <t>Moves &lt;b&gt;horizontally or vertically&lt;/b&gt; with no limit on distance, as long as no piece blocks the path.</t>
         </is>
       </c>
-      <c r="C266" s="2" t="inlineStr">
+      <c r="C271" s="2" t="inlineStr">
         <is>
           <t>Mỗi nước được &lt;b&gt;đi dọc hoặc đi ngang&lt;/b&gt;, không hạn chế số bước đi nếu không có quân khác cản đường.</t>
-        </is>
-      </c>
-    </row>
-    <row r="267" ht="72" customHeight="1">
-      <c r="A267" s="1" t="inlineStr">
-        <is>
-          <t>guide.horse.paragraph1</t>
-        </is>
-      </c>
-      <c r="B267" s="2" t="inlineStr">
-        <is>
-          <t>Horse</t>
-        </is>
-      </c>
-      <c r="C267" s="2" t="inlineStr">
-        <is>
-          <t>Mã</t>
-        </is>
-      </c>
-    </row>
-    <row r="268" ht="54" customHeight="1">
-      <c r="A268" s="1" t="inlineStr">
-        <is>
-          <t>guide.horse.paragraph2</t>
-        </is>
-      </c>
-      <c r="B268" s="2" t="inlineStr">
-        <is>
-          <t>Moves in an &lt;b&gt;L-shape&lt;/b&gt; (one step orthogonally then one step diagonally outward). If the adjacent orthogonal point is occupied by any piece, the Horse is blocked and cannot move.</t>
-        </is>
-      </c>
-      <c r="C268" s="2" t="inlineStr">
-        <is>
-          <t>Đi theo &lt;b&gt;đường chéo hình chữ nhật&lt;/b&gt; của hai ô vuông liền nhau. Nếu giao điểm liền kề bước thẳng dọc ngang có một quân khác đứng thì Mã bị cản, không đi được.</t>
-        </is>
-      </c>
-    </row>
-    <row r="269" ht="54" customHeight="1">
-      <c r="A269" s="1" t="inlineStr">
-        <is>
-          <t>guide.cannon.paragraph1</t>
-        </is>
-      </c>
-      <c r="B269" s="2" t="inlineStr">
-        <is>
-          <t>Cannon</t>
-        </is>
-      </c>
-      <c r="C269" s="2" t="inlineStr">
-        <is>
-          <t>Pháo</t>
-        </is>
-      </c>
-    </row>
-    <row r="270" ht="54" customHeight="1">
-      <c r="A270" s="1" t="inlineStr">
-        <is>
-          <t>guide.cannon.paragraph2</t>
-        </is>
-      </c>
-      <c r="B270" s="2" t="inlineStr">
-        <is>
-          <t>Moves &lt;b&gt;horizontally or vertically&lt;/b&gt; like a Chariot when not capturing. To capture, it must &lt;b&gt;jump over exactly one piece&lt;/b&gt; to reach its target. If there are zero or more than one pieces between the Cannon and the target, it cannot capture.</t>
-        </is>
-      </c>
-      <c r="C270" s="2" t="inlineStr">
-        <is>
-          <t>Đi ngang hoặc dọc giống Xe khi không bắt quân. Để bắt quân, nó phải &lt;b&gt;nhảy qua đúng một quân khác&lt;/b&gt; để đến mục tiêu. Nếu không có hoặc có nhiều hơn một quân giữa Pháo và mục tiêu, nó không thể bắt quân.</t>
-        </is>
-      </c>
-    </row>
-    <row r="271" ht="72" customHeight="1">
-      <c r="A271" s="1" t="inlineStr">
-        <is>
-          <t>guide.soldier.paragraph1</t>
-        </is>
-      </c>
-      <c r="B271" s="2" t="inlineStr">
-        <is>
-          <t>Soldier</t>
-        </is>
-      </c>
-      <c r="C271" s="2" t="inlineStr">
-        <is>
-          <t>Tốt</t>
         </is>
       </c>
     </row>
     <row r="272" ht="54" customHeight="1">
       <c r="A272" s="1" t="inlineStr">
         <is>
-          <t>guide.soldier.paragraph2</t>
+          <t>guide.horse.paragraph1</t>
         </is>
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>Moves &lt;b&gt;one step&lt;/b&gt; each turn. Before crossing the river, it can only move forward. After crossing the river, it may move &lt;b&gt;forward or sideways&lt;/b&gt;, but never backward.</t>
+          <t>Horse</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>Mỗi nước đi &lt;b&gt;một bước&lt;/b&gt;. Khi chưa qua sông, Tốt chỉ được tiến. Khi Tốt đã qua sông được quyền &lt;b&gt;đi tiến và đi ngang&lt;/b&gt;, không được phép lùi.</t>
-        </is>
-      </c>
-    </row>
-    <row r="273" ht="36" customHeight="1">
+          <t>Mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="273" ht="54" customHeight="1">
       <c r="A273" s="1" t="inlineStr">
         <is>
-          <t>guide.capturing.paragraph1</t>
+          <t>guide.horse.paragraph2</t>
         </is>
       </c>
       <c r="B273" s="2" t="inlineStr">
         <is>
-          <t>When a piece moves to an intersection occupied by an opponent's piece, it may &lt;b&gt;capture that piece&lt;/b&gt; and occupy its position.</t>
+          <t>Moves in an &lt;b&gt;L-shape&lt;/b&gt; (one step orthogonally then one step diagonally outward). If the adjacent orthogonal point is occupied by any piece, the Horse is blocked and cannot move.</t>
         </is>
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>Khi một quân đi tới một giao điểm khác đã có quân đối phương đứng thì được quyền &lt;b&gt;bắt quân đó&lt;/b&gt;, đồng thời chiếm giữ vị trí quân bị bắt.</t>
-        </is>
-      </c>
-    </row>
-    <row r="274" ht="18" customHeight="1">
+          <t>Đi theo &lt;b&gt;đường chéo hình chữ nhật&lt;/b&gt; của hai ô vuông liền nhau. Nếu giao điểm liền kề bước thẳng dọc ngang có một quân khác đứng thì Mã bị cản, không đi được.</t>
+        </is>
+      </c>
+    </row>
+    <row r="274" ht="72" customHeight="1">
       <c r="A274" s="1" t="inlineStr">
         <is>
-          <t>guide.capturing.paragraph2</t>
+          <t>guide.cannon.paragraph1</t>
         </is>
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>You may not capture your own pieces. You may sacrifice your own pieces to be captured by the opponent, &lt;b&gt;except for the General&lt;/b&gt;.</t>
+          <t>Cannon</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>Không được bắt quân bên mình. Được phép cho đối phương bắt đầu quân mình chủ động hiến mình cho đối phương, &lt;b&gt;trừ Tướng&lt;/b&gt;.</t>
-        </is>
-      </c>
-    </row>
-    <row r="275" ht="36" customHeight="1">
+          <t>Pháo</t>
+        </is>
+      </c>
+    </row>
+    <row r="275" ht="54" customHeight="1">
       <c r="A275" s="1" t="inlineStr">
         <is>
-          <t>guide.capturing.paragraph3</t>
+          <t>guide.cannon.paragraph2</t>
         </is>
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>A captured piece is removed from the board. &lt;b&gt;Chasing one piece for more than 6 consecutive moves is not allowed&lt;/b&gt;.</t>
+          <t>Moves &lt;b&gt;horizontally or vertically&lt;/b&gt; like a Chariot when not capturing. To capture, it must &lt;b&gt;jump over exactly one piece&lt;/b&gt; to reach its target. If there are zero or more than one pieces between the Cannon and the target, it cannot capture.</t>
         </is>
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>Quân bị bắt phải bị loại và bị nhấc ra khỏi bàn cờ. &lt;b&gt;Không được đuổi 1 quân quá 6 nước cờ liên tiếp&lt;/b&gt;.</t>
+          <t>Đi ngang hoặc dọc giống Xe khi không bắt quân. Để bắt quân, nó phải &lt;b&gt;nhảy qua đúng một quân khác&lt;/b&gt; để đến mục tiêu. Nếu không có hoặc có nhiều hơn một quân giữa Pháo và mục tiêu, nó không thể bắt quân.</t>
         </is>
       </c>
     </row>
     <row r="276" ht="36" customHeight="1">
       <c r="A276" s="1" t="inlineStr">
         <is>
-          <t>guide.check.paragraph1</t>
+          <t>guide.soldier.paragraph1</t>
         </is>
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>If a player makes a move that threatens to capture the opponent's General on the next move (by the same piece or another piece), it is called a &lt;b&gt;Check&lt;/b&gt;. The checked side must respond to avoid check</t>
+          <t>Soldier</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> otherwise, that side loses.</t>
-        </is>
-      </c>
-    </row>
-    <row r="277" ht="72" customHeight="1">
+          <t>Tốt</t>
+        </is>
+      </c>
+    </row>
+    <row r="277" ht="18" customHeight="1">
       <c r="A277" s="1" t="inlineStr">
         <is>
-          <t>guide.check.paragraph2</t>
+          <t>guide.soldier.paragraph2</t>
         </is>
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>When the General is checked from any direction (including from behind), the checked side may respond in one of the following ways:</t>
+          <t>Moves &lt;b&gt;one step&lt;/b&gt; each turn. Before crossing the river, it can only move forward. After crossing the river, it may move &lt;b&gt;forward or sideways&lt;/b&gt;, but never backward.</t>
         </is>
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t>Tướng bị chiếu từ cả bốn hướng (bị chiếu cả từ phía sau) có thể ứng phó với nước chiếu tướng bằng một trong các cách sau:</t>
-        </is>
-      </c>
-    </row>
-    <row r="278" ht="54" customHeight="1">
+          <t>Mỗi nước đi &lt;b&gt;một bước&lt;/b&gt;. Khi chưa qua sông, Tốt chỉ được tiến. Khi Tốt đã qua sông được quyền &lt;b&gt;đi tiến và đi ngang&lt;/b&gt;, không được phép lùi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="278" ht="36" customHeight="1">
       <c r="A278" s="1" t="inlineStr">
         <is>
-          <t>guide.check.paragraph3</t>
+          <t>guide.capturing.paragraph1</t>
         </is>
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>Move the General to another position to escape check</t>
+          <t>When a piece moves to an intersection occupied by an opponent's piece, it may &lt;b&gt;capture that piece&lt;/b&gt; and occupy its position.</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>Di chuyển tướng sang vị trí khác để tránh nước chiếu</t>
-        </is>
-      </c>
-    </row>
-    <row r="279" ht="54" customHeight="1">
+          <t>Khi một quân đi tới một giao điểm khác đã có quân đối phương đứng thì được quyền &lt;b&gt;bắt quân đó&lt;/b&gt;, đồng thời chiếm giữ vị trí quân bị bắt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="279" ht="90" customHeight="1">
       <c r="A279" s="1" t="inlineStr">
         <is>
-          <t>guide.check.paragraph4</t>
+          <t>guide.capturing.paragraph2</t>
         </is>
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>Capture the checking piece</t>
+          <t>You may not capture your own pieces. You may sacrifice your own pieces to be captured by the opponent, &lt;b&gt;except for the General&lt;/b&gt;.</t>
         </is>
       </c>
       <c r="C279" s="2" t="inlineStr">
         <is>
-          <t>Bắt quân đang chiếu</t>
-        </is>
-      </c>
-    </row>
-    <row r="280" ht="90" customHeight="1">
+          <t>Không được bắt quân bên mình. Được phép cho đối phương bắt đầu quân mình chủ động hiến mình cho đối phương, &lt;b&gt;trừ Tướng&lt;/b&gt;.</t>
+        </is>
+      </c>
+    </row>
+    <row r="280" ht="72" customHeight="1">
       <c r="A280" s="1" t="inlineStr">
         <is>
-          <t>guide.check.paragraph5</t>
+          <t>guide.capturing.paragraph3</t>
         </is>
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>Block the checking line with another piece to protect the General</t>
+          <t>A captured piece is removed from the board. &lt;b&gt;Chasing one piece for more than 6 consecutive moves is not allowed&lt;/b&gt;.</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>Dùng quân khác cản quân chiếu, đi quân che đỡ cho tướng</t>
+          <t>Quân bị bắt phải bị loại và bị nhấc ra khỏi bàn cờ. &lt;b&gt;Không được đuổi 1 quân quá 6 nước cờ liên tiếp&lt;/b&gt;.</t>
         </is>
       </c>
     </row>
     <row r="281" ht="54" customHeight="1">
       <c r="A281" s="1" t="inlineStr">
         <is>
+          <t>guide.check.paragraph1</t>
+        </is>
+      </c>
+      <c r="B281" s="2" t="inlineStr">
+        <is>
+          <t>If a player makes a move that threatens to capture the opponent's General on the next move (by the same piece or another piece), it is called a &lt;b&gt;Check&lt;/b&gt;. The checked side must respond to avoid check. Otherwise, that side loses</t>
+        </is>
+      </c>
+      <c r="C281" s="2" t="inlineStr">
+        <is>
+          <t>Nếu người chơi thực hiện một nước đi đe dọa bắt Tướng của đối phương ở nước đi tiếp theo (bằng chính quân cờ đó hoặc một quân cờ khác), thì đó được gọi là &lt;b&gt;Chiếu&lt;/b&gt;. Bên bị chiếu phải đáp trả để tránh bị chiếu. Nếu không sẽ bị xử thua</t>
+        </is>
+      </c>
+    </row>
+    <row r="282" ht="54" customHeight="1">
+      <c r="A282" s="1" t="inlineStr">
+        <is>
+          <t>guide.check.paragraph2</t>
+        </is>
+      </c>
+      <c r="B282" s="2" t="inlineStr">
+        <is>
+          <t>When the General is checked from any direction (including from behind), the checked side may respond in one of the following ways:</t>
+        </is>
+      </c>
+      <c r="C282" s="2" t="inlineStr">
+        <is>
+          <t>Tướng bị chiếu từ cả bốn hướng (bị chiếu cả từ phía sau) có thể ứng phó với nước chiếu tướng bằng một trong các cách sau:</t>
+        </is>
+      </c>
+    </row>
+    <row r="283" ht="90" customHeight="1">
+      <c r="A283" s="1" t="inlineStr">
+        <is>
+          <t>guide.check.paragraph3</t>
+        </is>
+      </c>
+      <c r="B283" s="2" t="inlineStr">
+        <is>
+          <t>Move the General to another position to escape check</t>
+        </is>
+      </c>
+      <c r="C283" s="2" t="inlineStr">
+        <is>
+          <t>Di chuyển tướng sang vị trí khác để tránh nước chiếu</t>
+        </is>
+      </c>
+    </row>
+    <row r="284" ht="54" customHeight="1">
+      <c r="A284" s="1" t="inlineStr">
+        <is>
+          <t>guide.check.paragraph4</t>
+        </is>
+      </c>
+      <c r="B284" s="2" t="inlineStr">
+        <is>
+          <t>Capture the checking piece</t>
+        </is>
+      </c>
+      <c r="C284" s="2" t="inlineStr">
+        <is>
+          <t>Bắt quân đang chiếu</t>
+        </is>
+      </c>
+    </row>
+    <row r="285" ht="17" customHeight="1">
+      <c r="A285" s="2" t="inlineStr">
+        <is>
+          <t>guide.check.paragraph5</t>
+        </is>
+      </c>
+      <c r="B285" s="2" t="inlineStr">
+        <is>
+          <t>Block the checking line with another piece to protect the General</t>
+        </is>
+      </c>
+      <c r="C285" s="2" t="inlineStr">
+        <is>
+          <t>Dùng quân khác cản quân chiếu, đi quân che đỡ cho tướng</t>
+        </is>
+      </c>
+    </row>
+    <row r="286" ht="17" customHeight="1">
+      <c r="A286" s="2" t="inlineStr">
+        <is>
           <t>guide.check.paragraph6</t>
         </is>
       </c>
-      <c r="B281" s="2" t="inlineStr">
+      <c r="B286" s="2" t="inlineStr">
         <is>
           <t>Repeatedly checking for more than 6 consecutive moves is not allowed</t>
         </is>
       </c>
-      <c r="C281" s="2" t="inlineStr">
+      <c r="C286" s="2" t="inlineStr">
         <is>
           <t>Không được chiếu tướng quá 6 nước cờ liên tiếp</t>
         </is>
       </c>
     </row>
-    <row r="282" ht="17" customHeight="1">
-      <c r="A282" s="2" t="inlineStr">
+    <row r="287" ht="54" customHeight="1">
+      <c r="A287" t="inlineStr">
         <is>
           <t>guide.result.paragraph1</t>
         </is>
       </c>
-      <c r="B282" s="2" t="inlineStr">
+      <c r="B287" s="2" t="inlineStr">
         <is>
           <t>When one side gives Check and the other side has no legal way to protect the General, it is called a &lt;b&gt;Checkmate&lt;/b&gt;. The side that delivers Checkmate wins.</t>
         </is>
       </c>
-      <c r="C282" s="2" t="inlineStr">
+      <c r="C287" s="2" t="inlineStr">
         <is>
           <t>Khi một bên chiếu Tướng mà bên còn lại không thể làm gì để bảo vệ Tướng thì được gọi là &lt;b&gt;Chiếu Hết&lt;/b&gt;, bên thực hiện được Chiếu Hết sẽ giành chiến thắng.</t>
         </is>
       </c>
     </row>
-    <row r="283" ht="17" customHeight="1">
-      <c r="A283" s="2" t="inlineStr">
+    <row r="288" ht="90" customHeight="1">
+      <c r="A288" t="inlineStr">
         <is>
           <t>guide.result.paragraph2</t>
         </is>
       </c>
-      <c r="B283" s="2" t="inlineStr">
+      <c r="B288" s="2" t="inlineStr">
         <is>
           <t>If a player runs out of time for a single move (for example: 90s) without moving, the other side is awarded a &lt;b&gt;win&lt;/b&gt;.</t>
         </is>
       </c>
-      <c r="C283" s="2" t="inlineStr">
+      <c r="C288" s="2" t="inlineStr">
         <is>
           <t>Khi hết thời gian một nước đi (ví dụ: 90s) mà vẫn chưa di chuyển quân thì bên còn lại sẽ được &lt;b&gt;xử Thắng&lt;/b&gt;.</t>
         </is>
       </c>
     </row>
-    <row r="284">
-      <c r="A284" t="inlineStr">
+    <row r="289" ht="54" customHeight="1">
+      <c r="A289" t="inlineStr">
         <is>
           <t>guide.result.paragraph3</t>
         </is>
       </c>
-      <c r="B284" t="inlineStr">
+      <c r="B289" s="2" t="inlineStr">
         <is>
           <t>If a player runs out of total game time (for example: 5 minutes or 10 minutes), the other side is awarded a &lt;b&gt;win&lt;/b&gt;.</t>
         </is>
       </c>
-      <c r="C284" t="inlineStr">
+      <c r="C289" s="2" t="inlineStr">
         <is>
           <t>Khi một bên hết thời gian ván đấu (ví dụ: 5 phút, 10 phút) thì bên còn lại sẽ được &lt;b&gt;xử Thắng&lt;/b&gt;.</t>
         </is>
       </c>
     </row>
-    <row r="285">
-      <c r="A285" t="inlineStr">
+    <row r="290" ht="17" customHeight="1">
+      <c r="A290" t="inlineStr">
         <is>
           <t>guide.result.paragraph4</t>
         </is>
       </c>
-      <c r="B285" t="inlineStr">
+      <c r="B290" s="2" t="inlineStr">
         <is>
           <t>If both sides have no pieces that have crossed the river, the game is declared a &lt;b&gt;draw&lt;/b&gt;. If one side still has pieces across the river but runs out of time, while the other side still has time but has no pieces across the river, the game is declared a &lt;b&gt;draw&lt;/b&gt;.</t>
         </is>
       </c>
-      <c r="C285" t="inlineStr">
+      <c r="C290" s="2" t="inlineStr">
         <is>
           <t>Khi cả 2 bên đều không còn quân qua sông, ván đấu sẽ được &lt;b&gt;xử Hòa&lt;/b&gt;. Khi một bên còn quân qua sông nhưng cạn thời gian, một bên còn thời gian nhưng hết quân qua sông, ván đấu sẽ được &lt;b&gt;xử Hòa&lt;/b&gt;.</t>
         </is>
       </c>
     </row>
-    <row r="286">
-      <c r="A286" t="inlineStr">
+    <row r="291" ht="17" customHeight="1">
+      <c r="A291" t="inlineStr">
         <is>
           <t>guide.result.paragraph5</t>
         </is>
       </c>
-      <c r="B286" t="inlineStr">
+      <c r="B291" s="2" t="inlineStr">
         <is>
           <t>Within 40 moves, if there is no capture and no Soldier advances by one square, the game is declared a &lt;b&gt;draw&lt;/b&gt;.</t>
         </is>
       </c>
-      <c r="C286" t="inlineStr">
+      <c r="C291" s="2" t="inlineStr">
         <is>
           <t>Trong vòng 40 nước nếu không phát sinh nước bắt quân, Tốt không tiến 1 ô thì ván đấu sẽ được &lt;b&gt;xử Hòa&lt;/b&gt;.</t>
         </is>
       </c>
     </row>
-    <row r="287">
-      <c r="A287" t="inlineStr"/>
-      <c r="B287" t="inlineStr"/>
-      <c r="C287" t="inlineStr"/>
-    </row>
-    <row r="288">
-      <c r="A288" t="inlineStr"/>
-      <c r="B288" t="inlineStr"/>
-      <c r="C288" t="inlineStr"/>
+    <row r="292" ht="17" customHeight="1">
+      <c r="A292" t="inlineStr"/>
+      <c r="B292" s="2" t="inlineStr"/>
+      <c r="C292" s="2" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr"/>
+      <c r="B293" t="inlineStr"/>
+      <c r="C293" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr"/>
+      <c r="B294" t="inlineStr"/>
+      <c r="C294" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tools/languages.xlsx
+++ b/tools/languages.xlsx
@@ -325,7 +325,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C351"/>
+  <dimension ref="A1:C378"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -350,7 +350,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="17" customHeight="1">
+    <row r="2" ht="18" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>common.input.is-required</t>
@@ -367,7 +367,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="17" customHeight="1">
+    <row r="3" ht="18" customHeight="1">
       <c r="A3" s="1" t="inlineStr">
         <is>
           <t>common.loading</t>
@@ -384,7 +384,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="17" customHeight="1">
+    <row r="4" ht="18" customHeight="1">
       <c r="A4" s="1" t="inlineStr">
         <is>
           <t>common.password.policy-1</t>
@@ -401,7 +401,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="17" customHeight="1">
+    <row r="5" ht="18" customHeight="1">
       <c r="A5" s="1" t="inlineStr">
         <is>
           <t>common.password.policy-2</t>
@@ -418,7 +418,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="17" customHeight="1">
+    <row r="6" ht="18" customHeight="1">
       <c r="A6" s="1" t="inlineStr">
         <is>
           <t>common.password.policy-3</t>
@@ -639,7 +639,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="17" customHeight="1">
+    <row r="19" ht="18" customHeight="1">
       <c r="A19" s="1" t="inlineStr">
         <is>
           <t>page.history.no-games</t>
@@ -656,7 +656,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="17" customHeight="1">
+    <row r="20" ht="18" customHeight="1">
       <c r="A20" s="1" t="inlineStr">
         <is>
           <t>page.history.point-label</t>
@@ -673,7 +673,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="17" customHeight="1">
+    <row r="21" ht="18" customHeight="1">
       <c r="A21" s="1" t="inlineStr">
         <is>
           <t>page.about.title</t>
@@ -690,7 +690,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="17" customHeight="1">
+    <row r="22" ht="18" customHeight="1">
       <c r="A22" s="1" t="inlineStr">
         <is>
           <t>menu.app-name</t>
@@ -707,7 +707,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="17" customHeight="1">
+    <row r="23" ht="18" customHeight="1">
       <c r="A23" s="1" t="inlineStr">
         <is>
           <t>menu.profile</t>
@@ -724,7 +724,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="17" customHeight="1">
+    <row r="24" ht="18" customHeight="1">
       <c r="A24" s="1" t="inlineStr">
         <is>
           <t>menu.messages</t>
@@ -741,7 +741,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="17" customHeight="1">
+    <row r="25" ht="18" customHeight="1">
       <c r="A25" s="1" t="inlineStr">
         <is>
           <t>menu.guide</t>
@@ -758,7 +758,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="17" customHeight="1">
+    <row r="26" ht="18" customHeight="1">
       <c r="A26" s="1" t="inlineStr">
         <is>
           <t>menu.announce</t>
@@ -775,75 +775,75 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="17" customHeight="1">
+    <row r="27" ht="18" customHeight="1">
       <c r="A27" s="1" t="inlineStr">
         <is>
+          <t>menu.extra</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Daily tasks</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Tác vụ thường nhật</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
           <t>menu.setting.button</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>Settings</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>Cài đặt</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="17" customHeight="1">
-      <c r="A28" s="1" t="inlineStr">
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="1" t="inlineStr">
         <is>
           <t>menu.app-name</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>Xiangqi</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>Cờ tướng</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="17" customHeight="1">
-      <c r="A29" s="1" t="inlineStr">
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="1" t="inlineStr">
         <is>
           <t>menu.home</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>Trang chủ</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="17" customHeight="1">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>menu.profile</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>Profile</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Trang cá nhân</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="17" customHeight="1">
+    <row r="31" ht="18" customHeight="1">
       <c r="A31" s="1" t="inlineStr">
         <is>
           <t>menu.expired</t>
@@ -860,7 +860,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="17" customHeight="1">
+    <row r="32" ht="18" customHeight="1">
       <c r="A32" s="1" t="inlineStr">
         <is>
           <t>menu.logout</t>
@@ -877,7 +877,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="17" customHeight="1">
+    <row r="33" ht="18" customHeight="1">
       <c r="A33" s="1" t="inlineStr">
         <is>
           <t>menu.rooms</t>
@@ -894,7 +894,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="17" customHeight="1">
+    <row r="34" ht="18" customHeight="1">
       <c r="A34" s="1" t="inlineStr">
         <is>
           <t>announce.title</t>
@@ -911,7 +911,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="17" customHeight="1">
+    <row r="35" ht="18" customHeight="1">
       <c r="A35" s="1" t="inlineStr">
         <is>
           <t>announce.placeholder</t>
@@ -928,7 +928,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="17" customHeight="1">
+    <row r="36" ht="18" customHeight="1">
       <c r="A36" s="1" t="inlineStr">
         <is>
           <t>announce.empty</t>
@@ -945,7 +945,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="17" customHeight="1">
+    <row r="37" ht="18" customHeight="1">
       <c r="A37" s="1" t="inlineStr">
         <is>
           <t>announce.loading-older</t>
@@ -962,7 +962,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="17" customHeight="1">
+    <row r="38" ht="36" customHeight="1">
       <c r="A38" s="1" t="inlineStr">
         <is>
           <t>archivement.title-01</t>
@@ -979,7 +979,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="17" customHeight="1">
+    <row r="39" ht="18" customHeight="1">
       <c r="A39" s="1" t="inlineStr">
         <is>
           <t>archivement.title-02</t>
@@ -996,7 +996,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="17" customHeight="1">
+    <row r="40" ht="18" customHeight="1">
       <c r="A40" s="1" t="inlineStr">
         <is>
           <t>archivement.title-03</t>
@@ -1013,7 +1013,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="17" customHeight="1">
+    <row r="41" ht="18" customHeight="1">
       <c r="A41" s="1" t="inlineStr">
         <is>
           <t>archivement.title-04</t>
@@ -1030,7 +1030,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="17" customHeight="1">
+    <row r="42" ht="18" customHeight="1">
       <c r="A42" s="1" t="inlineStr">
         <is>
           <t>archivement.title-05</t>
@@ -1047,7 +1047,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="17" customHeight="1">
+    <row r="43" ht="18" customHeight="1">
       <c r="A43" s="1" t="inlineStr">
         <is>
           <t>archivement.title-06</t>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="17" customHeight="1">
+    <row r="44" ht="18" customHeight="1">
       <c r="A44" s="1" t="inlineStr">
         <is>
           <t>archivement.title-07</t>
@@ -1081,7 +1081,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="17" customHeight="1">
+    <row r="45" ht="36" customHeight="1">
       <c r="A45" s="1" t="inlineStr">
         <is>
           <t>archivement.title-08</t>
@@ -1098,7 +1098,7 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="17" customHeight="1">
+    <row r="46" ht="36" customHeight="1">
       <c r="A46" s="1" t="inlineStr">
         <is>
           <t>archivement.title-09</t>
@@ -1115,7 +1115,7 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="17" customHeight="1">
+    <row r="47" ht="18" customHeight="1">
       <c r="A47" s="1" t="inlineStr">
         <is>
           <t>archivement.title-10</t>
@@ -1132,7 +1132,7 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="17" customHeight="1">
+    <row r="48" ht="36" customHeight="1">
       <c r="A48" s="1" t="inlineStr">
         <is>
           <t>archivement.title-11</t>
@@ -1149,7 +1149,7 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="17" customHeight="1">
+    <row r="49" ht="18" customHeight="1">
       <c r="A49" s="1" t="inlineStr">
         <is>
           <t>archivement.title-12</t>
@@ -1166,7 +1166,7 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="17" customHeight="1">
+    <row r="50" ht="18" customHeight="1">
       <c r="A50" s="1" t="inlineStr">
         <is>
           <t>chat.conversation.you</t>
@@ -1183,7 +1183,7 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="17" customHeight="1">
+    <row r="51" ht="18" customHeight="1">
       <c r="A51" s="1" t="inlineStr">
         <is>
           <t>chat.conversation.new</t>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="17" customHeight="1">
+    <row r="52" ht="18" customHeight="1">
       <c r="A52" s="1" t="inlineStr">
         <is>
           <t>chat.messages.unread</t>
@@ -1217,7 +1217,7 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="17" customHeight="1">
+    <row r="53" ht="18" customHeight="1">
       <c r="A53" s="1" t="inlineStr">
         <is>
           <t>search.user.title</t>
@@ -1234,7 +1234,7 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="17" customHeight="1">
+    <row r="54" ht="18" customHeight="1">
       <c r="A54" s="1" t="inlineStr">
         <is>
           <t>search.user.placeholder</t>
@@ -1251,7 +1251,7 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="17" customHeight="1">
+    <row r="55" ht="18" customHeight="1">
       <c r="A55" s="1" t="inlineStr">
         <is>
           <t>search.user.no-results</t>
@@ -1268,7 +1268,7 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="17" customHeight="1">
+    <row r="56" ht="18" customHeight="1">
       <c r="A56" s="1" t="inlineStr">
         <is>
           <t>search.button.search</t>
@@ -1285,7 +1285,7 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="17" customHeight="1">
+    <row r="57" ht="18" customHeight="1">
       <c r="A57" s="1" t="inlineStr">
         <is>
           <t>dashboard.page.title</t>
@@ -1302,7 +1302,7 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="17" customHeight="1">
+    <row r="58" ht="18" customHeight="1">
       <c r="A58" s="1" t="inlineStr">
         <is>
           <t>dashboard.filters.all</t>
@@ -1319,7 +1319,7 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="17" customHeight="1">
+    <row r="59" ht="18" customHeight="1">
       <c r="A59" s="1" t="inlineStr">
         <is>
           <t>dashboard.filters.available</t>
@@ -1336,7 +1336,7 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="17" customHeight="1">
+    <row r="60" ht="18" customHeight="1">
       <c r="A60" s="1" t="inlineStr">
         <is>
           <t>dashboard.filters.playing</t>
@@ -1353,7 +1353,7 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="17" customHeight="1">
+    <row r="61" ht="18" customHeight="1">
       <c r="A61" s="1" t="inlineStr">
         <is>
           <t>dashboard.feedback.empty</t>
@@ -1370,7 +1370,7 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="17" customHeight="1">
+    <row r="62" ht="18" customHeight="1">
       <c r="A62" s="1" t="inlineStr">
         <is>
           <t>dashboard.feedback.error</t>
@@ -1387,7 +1387,7 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="17" customHeight="1">
+    <row r="63" ht="18" customHeight="1">
       <c r="A63" s="1" t="inlineStr">
         <is>
           <t>dashboard.status.unknown</t>
@@ -1404,7 +1404,7 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="17" customHeight="1">
+    <row r="64" ht="18" customHeight="1">
       <c r="A64" s="1" t="inlineStr">
         <is>
           <t>dashboard.feedback.result-count</t>
@@ -1421,7 +1421,7 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="17" customHeight="1">
+    <row r="65" ht="18" customHeight="1">
       <c r="A65" s="1" t="inlineStr">
         <is>
           <t>dashboard.room.create</t>
@@ -1438,7 +1438,7 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="17" customHeight="1">
+    <row r="66" ht="18" customHeight="1">
       <c r="A66" s="1" t="inlineStr">
         <is>
           <t>dashboard.popup.piece-selection</t>
@@ -1455,7 +1455,7 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="17" customHeight="1">
+    <row r="67" ht="18" customHeight="1">
       <c r="A67" s="1" t="inlineStr">
         <is>
           <t>dashboard.popup.red-first</t>
@@ -1472,7 +1472,7 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="17" customHeight="1">
+    <row r="68" ht="18" customHeight="1">
       <c r="A68" s="1" t="inlineStr">
         <is>
           <t>dashboard.popup.pve-mode</t>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="17" customHeight="1">
+    <row r="69" ht="18" customHeight="1">
       <c r="A69" s="1" t="inlineStr">
         <is>
           <t>dashboard.popup.bet-amount</t>
@@ -1506,7 +1506,7 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="17" customHeight="1">
+    <row r="70" ht="18" customHeight="1">
       <c r="A70" s="1" t="inlineStr">
         <is>
           <t>dashboard.popup.room-name-label</t>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="17" customHeight="1">
+    <row r="71" ht="18" customHeight="1">
       <c r="A71" s="1" t="inlineStr">
         <is>
           <t>dashboard.popup.room-name-helptext</t>
@@ -1540,7 +1540,7 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="17" customHeight="1">
+    <row r="72" ht="18" customHeight="1">
       <c r="A72" s="1" t="inlineStr">
         <is>
           <t>dashboard.popup.play</t>
@@ -1557,7 +1557,7 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="17" customHeight="1">
+    <row r="73" ht="18" customHeight="1">
       <c r="A73" s="1" t="inlineStr">
         <is>
           <t>dashboard.popup.view</t>
@@ -1574,7 +1574,7 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="17" customHeight="1">
+    <row r="74" ht="18" customHeight="1">
       <c r="A74" s="1" t="inlineStr">
         <is>
           <t>settings.header</t>
@@ -1591,7 +1591,7 @@
         </is>
       </c>
     </row>
-    <row r="75" ht="17" customHeight="1">
+    <row r="75" ht="18" customHeight="1">
       <c r="A75" s="1" t="inlineStr">
         <is>
           <t>settings.language</t>
@@ -1608,7 +1608,7 @@
         </is>
       </c>
     </row>
-    <row r="76" ht="17" customHeight="1">
+    <row r="76" ht="18" customHeight="1">
       <c r="A76" s="1" t="inlineStr">
         <is>
           <t>settings.dark-mode</t>
@@ -1625,7 +1625,7 @@
         </is>
       </c>
     </row>
-    <row r="77" ht="17" customHeight="1">
+    <row r="77" ht="18" customHeight="1">
       <c r="A77" s="1" t="inlineStr">
         <is>
           <t>settings.debug-mode</t>
@@ -1642,7 +1642,7 @@
         </is>
       </c>
     </row>
-    <row r="78" ht="17" customHeight="1">
+    <row r="78" ht="18" customHeight="1">
       <c r="A78" s="1" t="inlineStr">
         <is>
           <t>settings.close</t>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
     </row>
-    <row r="79" ht="17" customHeight="1">
+    <row r="79" ht="18" customHeight="1">
       <c r="A79" s="1" t="inlineStr">
         <is>
           <t>settings.change-password</t>
@@ -1676,7 +1676,7 @@
         </is>
       </c>
     </row>
-    <row r="80" ht="17" customHeight="1">
+    <row r="80" ht="18" customHeight="1">
       <c r="A80" s="1" t="inlineStr">
         <is>
           <t>popup.alert.title</t>
@@ -1693,7 +1693,7 @@
         </is>
       </c>
     </row>
-    <row r="81" ht="17" customHeight="1">
+    <row r="81" ht="18" customHeight="1">
       <c r="A81" s="1" t="inlineStr">
         <is>
           <t>popup.confirm.title</t>
@@ -1710,7 +1710,7 @@
         </is>
       </c>
     </row>
-    <row r="82" ht="17" customHeight="1">
+    <row r="82" ht="18" customHeight="1">
       <c r="A82" s="1" t="inlineStr">
         <is>
           <t>popup.confirm.ok</t>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
     </row>
-    <row r="83" ht="17" customHeight="1">
+    <row r="83" ht="18" customHeight="1">
       <c r="A83" s="1" t="inlineStr">
         <is>
           <t>popup.confirm.cancel</t>
@@ -1744,7 +1744,7 @@
         </is>
       </c>
     </row>
-    <row r="84" ht="17" customHeight="1">
+    <row r="84" ht="18" customHeight="1">
       <c r="A84" s="1" t="inlineStr">
         <is>
           <t>home.turn.title</t>
@@ -1761,7 +1761,7 @@
         </is>
       </c>
     </row>
-    <row r="85" ht="17" customHeight="1">
+    <row r="85" ht="18" customHeight="1">
       <c r="A85" s="1" t="inlineStr">
         <is>
           <t>game.general.captured</t>
@@ -1778,7 +1778,7 @@
         </is>
       </c>
     </row>
-    <row r="86" ht="17" customHeight="1">
+    <row r="86" ht="18" customHeight="1">
       <c r="A86" s="1" t="inlineStr">
         <is>
           <t>game.general.in-check</t>
@@ -1795,7 +1795,7 @@
         </is>
       </c>
     </row>
-    <row r="87" ht="17" customHeight="1">
+    <row r="87" ht="18" customHeight="1">
       <c r="A87" s="1" t="inlineStr">
         <is>
           <t>room.bot-difficulty.title</t>
@@ -1812,7 +1812,7 @@
         </is>
       </c>
     </row>
-    <row r="88" ht="17" customHeight="1">
+    <row r="88" ht="18" customHeight="1">
       <c r="A88" s="1" t="inlineStr">
         <is>
           <t>room.bot-difficulty.beginner</t>
@@ -1829,7 +1829,7 @@
         </is>
       </c>
     </row>
-    <row r="89" ht="17" customHeight="1">
+    <row r="89" ht="18" customHeight="1">
       <c r="A89" s="1" t="inlineStr">
         <is>
           <t>room.bot-difficulty.amateur</t>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
     </row>
-    <row r="90" ht="17" customHeight="1">
+    <row r="90" ht="18" customHeight="1">
       <c r="A90" s="1" t="inlineStr">
         <is>
           <t>room.bot-difficulty.intermediate</t>
@@ -1863,7 +1863,7 @@
         </is>
       </c>
     </row>
-    <row r="91" ht="17" customHeight="1">
+    <row r="91" ht="18" customHeight="1">
       <c r="A91" s="1" t="inlineStr">
         <is>
           <t>room.bot-difficulty.advanced</t>
@@ -1880,7 +1880,7 @@
         </is>
       </c>
     </row>
-    <row r="92" ht="17" customHeight="1">
+    <row r="92" ht="18" customHeight="1">
       <c r="A92" s="1" t="inlineStr">
         <is>
           <t>room.bot-difficulty.master</t>
@@ -1897,7 +1897,7 @@
         </is>
       </c>
     </row>
-    <row r="93" ht="17" customHeight="1">
+    <row r="93" ht="18" customHeight="1">
       <c r="A93" s="1" t="inlineStr">
         <is>
           <t>login.page.title</t>
@@ -1914,7 +1914,7 @@
         </is>
       </c>
     </row>
-    <row r="94" ht="17" customHeight="1">
+    <row r="94" ht="18" customHeight="1">
       <c r="A94" s="1" t="inlineStr">
         <is>
           <t>login.form.title</t>
@@ -1931,7 +1931,7 @@
         </is>
       </c>
     </row>
-    <row r="95" ht="17" customHeight="1">
+    <row r="95" ht="18" customHeight="1">
       <c r="A95" s="1" t="inlineStr">
         <is>
           <t>login.username.label</t>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
     </row>
-    <row r="96" ht="17" customHeight="1">
+    <row r="96" ht="18" customHeight="1">
       <c r="A96" s="1" t="inlineStr">
         <is>
           <t>login.username.placeholder</t>
@@ -1965,7 +1965,7 @@
         </is>
       </c>
     </row>
-    <row r="97" ht="17" customHeight="1">
+    <row r="97" ht="18" customHeight="1">
       <c r="A97" s="1" t="inlineStr">
         <is>
           <t>login.password.label</t>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
     </row>
-    <row r="98" ht="17" customHeight="1">
+    <row r="98" ht="18" customHeight="1">
       <c r="A98" s="1" t="inlineStr">
         <is>
           <t>login.password.placeholder</t>
@@ -1999,7 +1999,7 @@
         </is>
       </c>
     </row>
-    <row r="99" ht="17" customHeight="1">
+    <row r="99" ht="18" customHeight="1">
       <c r="A99" s="1" t="inlineStr">
         <is>
           <t>login.password.error1</t>
@@ -2016,7 +2016,7 @@
         </is>
       </c>
     </row>
-    <row r="100" ht="17" customHeight="1">
+    <row r="100" ht="18" customHeight="1">
       <c r="A100" s="1" t="inlineStr">
         <is>
           <t>login.password.show</t>
@@ -2033,7 +2033,7 @@
         </is>
       </c>
     </row>
-    <row r="101" ht="17" customHeight="1">
+    <row r="101" ht="18" customHeight="1">
       <c r="A101" s="1" t="inlineStr">
         <is>
           <t>login.password.hide</t>
@@ -2050,7 +2050,7 @@
         </is>
       </c>
     </row>
-    <row r="102" ht="17" customHeight="1">
+    <row r="102" ht="18" customHeight="1">
       <c r="A102" s="1" t="inlineStr">
         <is>
           <t>login.form.error1</t>
@@ -2067,7 +2067,7 @@
         </is>
       </c>
     </row>
-    <row r="103" ht="17" customHeight="1">
+    <row r="103" ht="18" customHeight="1">
       <c r="A103" s="1" t="inlineStr">
         <is>
           <t>login.form.forgot-password</t>
@@ -2084,7 +2084,7 @@
         </is>
       </c>
     </row>
-    <row r="104" ht="17" customHeight="1">
+    <row r="104" ht="18" customHeight="1">
       <c r="A104" s="1" t="inlineStr">
         <is>
           <t>login.form.register</t>
@@ -2101,7 +2101,7 @@
         </is>
       </c>
     </row>
-    <row r="105" ht="17" customHeight="1">
+    <row r="105" ht="18" customHeight="1">
       <c r="A105" s="1" t="inlineStr">
         <is>
           <t>login.form.submit</t>
@@ -2118,7 +2118,7 @@
         </is>
       </c>
     </row>
-    <row r="106" ht="17" customHeight="1">
+    <row r="106" ht="18" customHeight="1">
       <c r="A106" s="1" t="inlineStr">
         <is>
           <t>notfound.title</t>
@@ -2135,7 +2135,7 @@
         </is>
       </c>
     </row>
-    <row r="107" ht="17" customHeight="1">
+    <row r="107" ht="36" customHeight="1">
       <c r="A107" s="1" t="inlineStr">
         <is>
           <t>notfound.description</t>
@@ -2152,7 +2152,7 @@
         </is>
       </c>
     </row>
-    <row r="108" ht="17" customHeight="1">
+    <row r="108" ht="18" customHeight="1">
       <c r="A108" s="1" t="inlineStr">
         <is>
           <t>notfound.home</t>
@@ -2169,7 +2169,7 @@
         </is>
       </c>
     </row>
-    <row r="109" ht="17" customHeight="1">
+    <row r="109" ht="18" customHeight="1">
       <c r="A109" s="1" t="inlineStr">
         <is>
           <t>notfound.back</t>
@@ -2186,7 +2186,7 @@
         </is>
       </c>
     </row>
-    <row r="110" ht="17" customHeight="1">
+    <row r="110" ht="18" customHeight="1">
       <c r="A110" s="1" t="inlineStr">
         <is>
           <t>register.confirm-password.error1</t>
@@ -2203,7 +2203,7 @@
         </is>
       </c>
     </row>
-    <row r="111" ht="17" customHeight="1">
+    <row r="111" ht="18" customHeight="1">
       <c r="A111" s="1" t="inlineStr">
         <is>
           <t>register.confirm-password.label</t>
@@ -2220,7 +2220,7 @@
         </is>
       </c>
     </row>
-    <row r="112" ht="17" customHeight="1">
+    <row r="112" ht="18" customHeight="1">
       <c r="A112" s="1" t="inlineStr">
         <is>
           <t>register.confirm-password.placeholder</t>
@@ -2237,7 +2237,7 @@
         </is>
       </c>
     </row>
-    <row r="113" ht="17" customHeight="1">
+    <row r="113" ht="18" customHeight="1">
       <c r="A113" s="1" t="inlineStr">
         <is>
           <t>register.display-name.label</t>
@@ -2254,7 +2254,7 @@
         </is>
       </c>
     </row>
-    <row r="114" ht="17" customHeight="1">
+    <row r="114" ht="18" customHeight="1">
       <c r="A114" s="1" t="inlineStr">
         <is>
           <t>register.display-name.placeholder</t>
@@ -2271,7 +2271,7 @@
         </is>
       </c>
     </row>
-    <row r="115" ht="17" customHeight="1">
+    <row r="115" ht="18" customHeight="1">
       <c r="A115" s="1" t="inlineStr">
         <is>
           <t>register.email.error1</t>
@@ -2288,7 +2288,7 @@
         </is>
       </c>
     </row>
-    <row r="116" ht="17" customHeight="1">
+    <row r="116" ht="18" customHeight="1">
       <c r="A116" s="1" t="inlineStr">
         <is>
           <t>register.email.label</t>
@@ -2305,7 +2305,7 @@
         </is>
       </c>
     </row>
-    <row r="117" ht="17" customHeight="1">
+    <row r="117" ht="18" customHeight="1">
       <c r="A117" s="1" t="inlineStr">
         <is>
           <t>register.email.placeholder</t>
@@ -2322,7 +2322,7 @@
         </is>
       </c>
     </row>
-    <row r="118" ht="17" customHeight="1">
+    <row r="118" ht="18" customHeight="1">
       <c r="A118" s="1" t="inlineStr">
         <is>
           <t>register.form.login</t>
@@ -2339,7 +2339,7 @@
         </is>
       </c>
     </row>
-    <row r="119" ht="17" customHeight="1">
+    <row r="119" ht="18" customHeight="1">
       <c r="A119" s="1" t="inlineStr">
         <is>
           <t>register.form.submit</t>
@@ -2356,7 +2356,7 @@
         </is>
       </c>
     </row>
-    <row r="120" ht="17" customHeight="1">
+    <row r="120" ht="18" customHeight="1">
       <c r="A120" s="1" t="inlineStr">
         <is>
           <t>register.form.success</t>
@@ -2373,7 +2373,7 @@
         </is>
       </c>
     </row>
-    <row r="121" ht="17" customHeight="1">
+    <row r="121" ht="18" customHeight="1">
       <c r="A121" s="1" t="inlineStr">
         <is>
           <t>register.form.title</t>
@@ -2390,7 +2390,7 @@
         </is>
       </c>
     </row>
-    <row r="122" ht="17" customHeight="1">
+    <row r="122" ht="18" customHeight="1">
       <c r="A122" s="1" t="inlineStr">
         <is>
           <t>register.gender.female</t>
@@ -2407,7 +2407,7 @@
         </is>
       </c>
     </row>
-    <row r="123" ht="17" customHeight="1">
+    <row r="123" ht="18" customHeight="1">
       <c r="A123" s="1" t="inlineStr">
         <is>
           <t>register.gender.label</t>
@@ -2424,7 +2424,7 @@
         </is>
       </c>
     </row>
-    <row r="124" ht="17" customHeight="1">
+    <row r="124" ht="18" customHeight="1">
       <c r="A124" s="1" t="inlineStr">
         <is>
           <t>register.gender.male</t>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
     </row>
-    <row r="125" ht="17" customHeight="1">
+    <row r="125" ht="18" customHeight="1">
       <c r="A125" s="1" t="inlineStr">
         <is>
           <t>register.gender.select</t>
@@ -2458,7 +2458,7 @@
         </is>
       </c>
     </row>
-    <row r="126" ht="17" customHeight="1">
+    <row r="126" ht="18" customHeight="1">
       <c r="A126" s="1" t="inlineStr">
         <is>
           <t>register.page.title</t>
@@ -2475,7 +2475,7 @@
         </is>
       </c>
     </row>
-    <row r="127" ht="17" customHeight="1">
+    <row r="127" ht="36" customHeight="1">
       <c r="A127" s="1" t="inlineStr">
         <is>
           <t>register.password.error1</t>
@@ -2492,7 +2492,7 @@
         </is>
       </c>
     </row>
-    <row r="128" ht="17" customHeight="1">
+    <row r="128" ht="18" customHeight="1">
       <c r="A128" s="1" t="inlineStr">
         <is>
           <t>register.password.hide</t>
@@ -2509,7 +2509,7 @@
         </is>
       </c>
     </row>
-    <row r="129" ht="17" customHeight="1">
+    <row r="129" ht="18" customHeight="1">
       <c r="A129" s="1" t="inlineStr">
         <is>
           <t>register.password.label</t>
@@ -2526,7 +2526,7 @@
         </is>
       </c>
     </row>
-    <row r="130" ht="17" customHeight="1">
+    <row r="130" ht="18" customHeight="1">
       <c r="A130" s="1" t="inlineStr">
         <is>
           <t>register.password.placeholder</t>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
     </row>
-    <row r="131" ht="17" customHeight="1">
+    <row r="131" ht="18" customHeight="1">
       <c r="A131" s="1" t="inlineStr">
         <is>
           <t>register.password.show</t>
@@ -2560,7 +2560,7 @@
         </is>
       </c>
     </row>
-    <row r="132" ht="17" customHeight="1">
+    <row r="132" ht="36" customHeight="1">
       <c r="A132" s="1" t="inlineStr">
         <is>
           <t>register.username.error1</t>
@@ -2577,7 +2577,7 @@
         </is>
       </c>
     </row>
-    <row r="133" ht="17" customHeight="1">
+    <row r="133" ht="18" customHeight="1">
       <c r="A133" s="1" t="inlineStr">
         <is>
           <t>register.username.label</t>
@@ -2594,7 +2594,7 @@
         </is>
       </c>
     </row>
-    <row r="134" ht="17" customHeight="1">
+    <row r="134" ht="18" customHeight="1">
       <c r="A134" s="1" t="inlineStr">
         <is>
           <t>register.username.placeholder</t>
@@ -2611,7 +2611,7 @@
         </is>
       </c>
     </row>
-    <row r="135" ht="17" customHeight="1">
+    <row r="135" ht="18" customHeight="1">
       <c r="A135" s="1" t="inlineStr">
         <is>
           <t>forgot-password.page.title</t>
@@ -2628,7 +2628,7 @@
         </is>
       </c>
     </row>
-    <row r="136" ht="17" customHeight="1">
+    <row r="136" ht="18" customHeight="1">
       <c r="A136" s="1" t="inlineStr">
         <is>
           <t>forgot-password.form.title</t>
@@ -2645,7 +2645,7 @@
         </is>
       </c>
     </row>
-    <row r="137" ht="17" customHeight="1">
+    <row r="137" ht="18" customHeight="1">
       <c r="A137" s="1" t="inlineStr">
         <is>
           <t>forgot-password.form.login</t>
@@ -2662,7 +2662,7 @@
         </is>
       </c>
     </row>
-    <row r="138" ht="17" customHeight="1">
+    <row r="138" ht="18" customHeight="1">
       <c r="A138" s="1" t="inlineStr">
         <is>
           <t>forgot-password.form.submit</t>
@@ -2679,7 +2679,7 @@
         </is>
       </c>
     </row>
-    <row r="139" ht="17" customHeight="1">
+    <row r="139" ht="36" customHeight="1">
       <c r="A139" s="1" t="inlineStr">
         <is>
           <t>forgot-password.form.success</t>
@@ -2696,7 +2696,7 @@
         </is>
       </c>
     </row>
-    <row r="140" ht="17" customHeight="1">
+    <row r="140" ht="18" customHeight="1">
       <c r="A140" s="1" t="inlineStr">
         <is>
           <t>forgot-password.form.error1</t>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
     </row>
-    <row r="141" ht="17" customHeight="1">
+    <row r="141" ht="18" customHeight="1">
       <c r="A141" s="1" t="inlineStr">
         <is>
           <t>reset-password.page.title</t>
@@ -2730,7 +2730,7 @@
         </is>
       </c>
     </row>
-    <row r="142" ht="17" customHeight="1">
+    <row r="142" ht="18" customHeight="1">
       <c r="A142" s="1" t="inlineStr">
         <is>
           <t>reset-password.form.title</t>
@@ -2747,7 +2747,7 @@
         </is>
       </c>
     </row>
-    <row r="143" ht="17" customHeight="1">
+    <row r="143" ht="18" customHeight="1">
       <c r="A143" s="1" t="inlineStr">
         <is>
           <t>reset-password.form.submit</t>
@@ -2764,7 +2764,7 @@
         </is>
       </c>
     </row>
-    <row r="144" ht="17" customHeight="1">
+    <row r="144" ht="36" customHeight="1">
       <c r="A144" s="1" t="inlineStr">
         <is>
           <t>reset-password.form.error1</t>
@@ -2781,7 +2781,7 @@
         </is>
       </c>
     </row>
-    <row r="145" ht="17" customHeight="1">
+    <row r="145" ht="18" customHeight="1">
       <c r="A145" s="1" t="inlineStr">
         <is>
           <t>reset-password.form.invalid-token</t>
@@ -2798,7 +2798,7 @@
         </is>
       </c>
     </row>
-    <row r="146" ht="17" customHeight="1">
+    <row r="146" ht="36" customHeight="1">
       <c r="A146" s="1" t="inlineStr">
         <is>
           <t>reset-password.form.success</t>
@@ -2815,7 +2815,7 @@
         </is>
       </c>
     </row>
-    <row r="147" ht="17" customHeight="1">
+    <row r="147" ht="18" customHeight="1">
       <c r="A147" s="1" t="inlineStr">
         <is>
           <t>reset-password.action.back-to-login</t>
@@ -2832,7 +2832,7 @@
         </is>
       </c>
     </row>
-    <row r="148" ht="17" customHeight="1">
+    <row r="148" ht="18" customHeight="1">
       <c r="A148" s="1" t="inlineStr">
         <is>
           <t>reset-password.action.submit</t>
@@ -2849,7 +2849,7 @@
         </is>
       </c>
     </row>
-    <row r="149" ht="17" customHeight="1">
+    <row r="149" ht="18" customHeight="1">
       <c r="A149" s="1" t="inlineStr">
         <is>
           <t>auth-middleware.messages.invalid-token-payload</t>
@@ -2866,7 +2866,7 @@
         </is>
       </c>
     </row>
-    <row r="150" ht="17" customHeight="1">
+    <row r="150" ht="18" customHeight="1">
       <c r="A150" s="1" t="inlineStr">
         <is>
           <t>auth-middleware.messages.session-not-found</t>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
     </row>
-    <row r="151" ht="17" customHeight="1">
+    <row r="151" ht="18" customHeight="1">
       <c r="A151" s="1" t="inlineStr">
         <is>
           <t>auth-middleware.messages.token-expired</t>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
     </row>
-    <row r="152" ht="17" customHeight="1">
+    <row r="152" ht="18" customHeight="1">
       <c r="A152" s="1" t="inlineStr">
         <is>
           <t>auth-middleware.messages.token-invalid</t>
@@ -2917,7 +2917,7 @@
         </is>
       </c>
     </row>
-    <row r="153" ht="17" customHeight="1">
+    <row r="153" ht="18" customHeight="1">
       <c r="A153" s="1" t="inlineStr">
         <is>
           <t>auth-middleware.messages.token-required</t>
@@ -2934,7 +2934,7 @@
         </is>
       </c>
     </row>
-    <row r="154" ht="17" customHeight="1">
+    <row r="154" ht="18" customHeight="1">
       <c r="A154" s="1" t="inlineStr">
         <is>
           <t>auth-middleware.messages.token-subject-mismatch</t>
@@ -2951,7 +2951,7 @@
         </is>
       </c>
     </row>
-    <row r="155" ht="17" customHeight="1">
+    <row r="155" ht="18" customHeight="1">
       <c r="A155" s="1" t="inlineStr">
         <is>
           <t>auth-middleware.messages.token-validation-failed</t>
@@ -2968,7 +2968,7 @@
         </is>
       </c>
     </row>
-    <row r="156" ht="17" customHeight="1">
+    <row r="156" ht="36" customHeight="1">
       <c r="A156" s="1" t="inlineStr">
         <is>
           <t>create-room.messages.insufficient-amount</t>
@@ -2985,7 +2985,7 @@
         </is>
       </c>
     </row>
-    <row r="157" ht="17" customHeight="1">
+    <row r="157" ht="18" customHeight="1">
       <c r="A157" s="1" t="inlineStr">
         <is>
           <t>create-room.messages.internal-server-error</t>
@@ -3002,7 +3002,7 @@
         </is>
       </c>
     </row>
-    <row r="158" ht="17" customHeight="1">
+    <row r="158" ht="36" customHeight="1">
       <c r="A158" s="1" t="inlineStr">
         <is>
           <t>create-room.messages.invalid-bet-amount</t>
@@ -3019,7 +3019,7 @@
         </is>
       </c>
     </row>
-    <row r="159" ht="17" customHeight="1">
+    <row r="159" ht="18" customHeight="1">
       <c r="A159" s="1" t="inlineStr">
         <is>
           <t>create-room.messages.invalid-redFirst</t>
@@ -3036,7 +3036,7 @@
         </is>
       </c>
     </row>
-    <row r="160" ht="17" customHeight="1">
+    <row r="160" ht="18" customHeight="1">
       <c r="A160" s="1" t="inlineStr">
         <is>
           <t>create-room.messages.invalid-team-name</t>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
     </row>
-    <row r="161" ht="17" customHeight="1">
+    <row r="161" ht="36" customHeight="1">
       <c r="A161" s="1" t="inlineStr">
         <is>
           <t>create-room.messages.name-required</t>
@@ -3070,7 +3070,7 @@
         </is>
       </c>
     </row>
-    <row r="162" ht="17" customHeight="1">
+    <row r="162" ht="18" customHeight="1">
       <c r="A162" s="1" t="inlineStr">
         <is>
           <t>create-room.messages.room-created</t>
@@ -3087,7 +3087,7 @@
         </is>
       </c>
     </row>
-    <row r="163" ht="17" customHeight="1">
+    <row r="163" ht="18" customHeight="1">
       <c r="A163" s="1" t="inlineStr">
         <is>
           <t>fetch-rooms.messages.internal-server-error</t>
@@ -3104,7 +3104,7 @@
         </is>
       </c>
     </row>
-    <row r="164" ht="17" customHeight="1">
+    <row r="164" ht="18" customHeight="1">
       <c r="A164" s="1" t="inlineStr">
         <is>
           <t>fetch-rooms.messages.invalid-status</t>
@@ -3121,7 +3121,7 @@
         </is>
       </c>
     </row>
-    <row r="165" ht="17" customHeight="1">
+    <row r="165" ht="18" customHeight="1">
       <c r="A165" s="1" t="inlineStr">
         <is>
           <t>fetch-rooms.messages.success</t>
@@ -3138,7 +3138,7 @@
         </is>
       </c>
     </row>
-    <row r="166" ht="17" customHeight="1">
+    <row r="166" ht="18" customHeight="1">
       <c r="A166" s="1" t="inlineStr">
         <is>
           <t>forgot-password.messages.email-not-found</t>
@@ -3155,7 +3155,7 @@
         </is>
       </c>
     </row>
-    <row r="167" ht="17" customHeight="1">
+    <row r="167" ht="18" customHeight="1">
       <c r="A167" s="1" t="inlineStr">
         <is>
           <t>forgot-password.messages.email-service-not-configured</t>
@@ -3172,7 +3172,7 @@
         </is>
       </c>
     </row>
-    <row r="168" ht="17" customHeight="1">
+    <row r="168" ht="18" customHeight="1">
       <c r="A168" s="1" t="inlineStr">
         <is>
           <t>forgot-password.messages.internal-server-error</t>
@@ -3189,7 +3189,7 @@
         </is>
       </c>
     </row>
-    <row r="169" ht="17" customHeight="1">
+    <row r="169" ht="18" customHeight="1">
       <c r="A169" s="1" t="inlineStr">
         <is>
           <t>forgot-password.messages.invalid-email-format</t>
@@ -3206,7 +3206,7 @@
         </is>
       </c>
     </row>
-    <row r="170" ht="17" customHeight="1">
+    <row r="170" ht="18" customHeight="1">
       <c r="A170" s="1" t="inlineStr">
         <is>
           <t>forgot-password.messages.missing-email</t>
@@ -3223,7 +3223,7 @@
         </is>
       </c>
     </row>
-    <row r="171" ht="17" customHeight="1">
+    <row r="171" ht="18" customHeight="1">
       <c r="A171" s="1" t="inlineStr">
         <is>
           <t>forgot-password.messages.success</t>
@@ -3240,7 +3240,7 @@
         </is>
       </c>
     </row>
-    <row r="172" ht="17" customHeight="1">
+    <row r="172" ht="18" customHeight="1">
       <c r="A172" s="1" t="inlineStr">
         <is>
           <t>join-room.messages.internal-server-error</t>
@@ -3257,7 +3257,7 @@
         </is>
       </c>
     </row>
-    <row r="173" ht="17" customHeight="1">
+    <row r="173" ht="36" customHeight="1">
       <c r="A173" s="1" t="inlineStr">
         <is>
           <t>join-room.messages.invalid-team</t>
@@ -3274,7 +3274,7 @@
         </is>
       </c>
     </row>
-    <row r="174" ht="17" customHeight="1">
+    <row r="174" ht="18" customHeight="1">
       <c r="A174" s="1" t="inlineStr">
         <is>
           <t>join-room.messages.invalid-room-id</t>
@@ -3291,7 +3291,7 @@
         </is>
       </c>
     </row>
-    <row r="175" ht="17" customHeight="1">
+    <row r="175" ht="18" customHeight="1">
       <c r="A175" s="1" t="inlineStr">
         <is>
           <t>join-room.messages.room-not-found</t>
@@ -3308,7 +3308,7 @@
         </is>
       </c>
     </row>
-    <row r="176" ht="17" customHeight="1">
+    <row r="176" ht="18" customHeight="1">
       <c r="A176" s="1" t="inlineStr">
         <is>
           <t>join-room.messages.success</t>
@@ -3325,7 +3325,7 @@
         </is>
       </c>
     </row>
-    <row r="177" ht="17" customHeight="1">
+    <row r="177" ht="18" customHeight="1">
       <c r="A177" s="1" t="inlineStr">
         <is>
           <t>join-room.messages.team-seat-occupied</t>
@@ -3342,7 +3342,7 @@
         </is>
       </c>
     </row>
-    <row r="178" ht="17" customHeight="1">
+    <row r="178" ht="18" customHeight="1">
       <c r="A178" s="1" t="inlineStr">
         <is>
           <t>kick-user.messages.cannot-kick-self</t>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
     </row>
-    <row r="179" ht="17" customHeight="1">
+    <row r="179" ht="18" customHeight="1">
       <c r="A179" s="1" t="inlineStr">
         <is>
           <t>kick-user.messages.forbidden</t>
@@ -3376,7 +3376,7 @@
         </is>
       </c>
     </row>
-    <row r="180" ht="17" customHeight="1">
+    <row r="180" ht="18" customHeight="1">
       <c r="A180" s="1" t="inlineStr">
         <is>
           <t>kick-user.messages.internal-server-error</t>
@@ -3393,7 +3393,7 @@
         </is>
       </c>
     </row>
-    <row r="181" ht="17" customHeight="1">
+    <row r="181" ht="18" customHeight="1">
       <c r="A181" s="1" t="inlineStr">
         <is>
           <t>kick-user.messages.invalid-room-id</t>
@@ -3410,7 +3410,7 @@
         </is>
       </c>
     </row>
-    <row r="182" ht="17" customHeight="1">
+    <row r="182" ht="36" customHeight="1">
       <c r="A182" s="1" t="inlineStr">
         <is>
           <t>kick-user.messages.invalid-user-id</t>
@@ -3427,7 +3427,7 @@
         </is>
       </c>
     </row>
-    <row r="183" ht="17" customHeight="1">
+    <row r="183" ht="18" customHeight="1">
       <c r="A183" s="1" t="inlineStr">
         <is>
           <t>kick-user.messages.room-not-found</t>
@@ -3444,7 +3444,7 @@
         </is>
       </c>
     </row>
-    <row r="184" ht="17" customHeight="1">
+    <row r="184" ht="36" customHeight="1">
       <c r="A184" s="1" t="inlineStr">
         <is>
           <t>kick-user.messages.room-not-waiting</t>
@@ -3461,7 +3461,7 @@
         </is>
       </c>
     </row>
-    <row r="185" ht="17" customHeight="1">
+    <row r="185" ht="18" customHeight="1">
       <c r="A185" s="1" t="inlineStr">
         <is>
           <t>kick-user.messages.success</t>
@@ -3478,7 +3478,7 @@
         </is>
       </c>
     </row>
-    <row r="186" ht="17" customHeight="1">
+    <row r="186" ht="18" customHeight="1">
       <c r="A186" s="1" t="inlineStr">
         <is>
           <t>kick-user.messages.user-not-in-room</t>
@@ -3495,7 +3495,7 @@
         </is>
       </c>
     </row>
-    <row r="187" ht="17" customHeight="1">
+    <row r="187" ht="18" customHeight="1">
       <c r="A187" s="1" t="inlineStr">
         <is>
           <t>kick-user.messages.you-were-kicked</t>
@@ -3512,7 +3512,7 @@
         </is>
       </c>
     </row>
-    <row r="188" ht="36" customHeight="1">
+    <row r="188" ht="18" customHeight="1">
       <c r="A188" s="1" t="inlineStr">
         <is>
           <t>leave-room.messages.internal-server-error</t>
@@ -3529,7 +3529,7 @@
         </is>
       </c>
     </row>
-    <row r="189" ht="17" customHeight="1">
+    <row r="189" ht="18" customHeight="1">
       <c r="A189" s="1" t="inlineStr">
         <is>
           <t>leave-room.messages.invalid-room-id</t>
@@ -3546,7 +3546,7 @@
         </is>
       </c>
     </row>
-    <row r="190" ht="17" customHeight="1">
+    <row r="190" ht="18" customHeight="1">
       <c r="A190" s="1" t="inlineStr">
         <is>
           <t>leave-room.messages.player-not-in-room</t>
@@ -3563,7 +3563,7 @@
         </is>
       </c>
     </row>
-    <row r="191" ht="17" customHeight="1">
+    <row r="191" ht="18" customHeight="1">
       <c r="A191" s="1" t="inlineStr">
         <is>
           <t>leave-room.messages.success</t>
@@ -3580,7 +3580,7 @@
         </is>
       </c>
     </row>
-    <row r="192" ht="17" customHeight="1">
+    <row r="192" ht="18" customHeight="1">
       <c r="A192" s="1" t="inlineStr">
         <is>
           <t>load-room.messages.internal-server-error</t>
@@ -3597,7 +3597,7 @@
         </is>
       </c>
     </row>
-    <row r="193" ht="17" customHeight="1">
+    <row r="193" ht="18" customHeight="1">
       <c r="A193" s="1" t="inlineStr">
         <is>
           <t>load-room.messages.invalid-room-id</t>
@@ -3614,7 +3614,7 @@
         </is>
       </c>
     </row>
-    <row r="194" ht="17" customHeight="1">
+    <row r="194" ht="18" customHeight="1">
       <c r="A194" s="1" t="inlineStr">
         <is>
           <t>load-room.messages.room-not-found</t>
@@ -3631,7 +3631,7 @@
         </is>
       </c>
     </row>
-    <row r="195" ht="17" customHeight="1">
+    <row r="195" ht="18" customHeight="1">
       <c r="A195" s="1" t="inlineStr">
         <is>
           <t>load-room.messages.success</t>
@@ -3648,7 +3648,7 @@
         </is>
       </c>
     </row>
-    <row r="196" ht="17" customHeight="1">
+    <row r="196" ht="18" customHeight="1">
       <c r="A196" s="1" t="inlineStr">
         <is>
           <t>login.messages.incorrect-login</t>
@@ -3665,7 +3665,7 @@
         </is>
       </c>
     </row>
-    <row r="197" ht="17" customHeight="1">
+    <row r="197" ht="18" customHeight="1">
       <c r="A197" s="1" t="inlineStr">
         <is>
           <t>login.messages.internal-server-error</t>
@@ -3682,7 +3682,7 @@
         </is>
       </c>
     </row>
-    <row r="198" ht="17" customHeight="1">
+    <row r="198" ht="18" customHeight="1">
       <c r="A198" s="1" t="inlineStr">
         <is>
           <t>login.messages.missing-credentials</t>
@@ -3699,7 +3699,7 @@
         </is>
       </c>
     </row>
-    <row r="199" ht="17" customHeight="1">
+    <row r="199" ht="18" customHeight="1">
       <c r="A199" s="1" t="inlineStr">
         <is>
           <t>login.messages.success</t>
@@ -3716,7 +3716,7 @@
         </is>
       </c>
     </row>
-    <row r="200" ht="17" customHeight="1">
+    <row r="200" ht="18" customHeight="1">
       <c r="A200" s="1" t="inlineStr">
         <is>
           <t>logout.messages.already-inactive</t>
@@ -3733,7 +3733,7 @@
         </is>
       </c>
     </row>
-    <row r="201" ht="17" customHeight="1">
+    <row r="201" ht="18" customHeight="1">
       <c r="A201" s="1" t="inlineStr">
         <is>
           <t>logout.messages.internal-server-error</t>
@@ -3750,7 +3750,7 @@
         </is>
       </c>
     </row>
-    <row r="202" ht="17" customHeight="1">
+    <row r="202" ht="18" customHeight="1">
       <c r="A202" s="1" t="inlineStr">
         <is>
           <t>logout.messages.success</t>
@@ -3767,7 +3767,7 @@
         </is>
       </c>
     </row>
-    <row r="203" ht="17" customHeight="1">
+    <row r="203" ht="18" customHeight="1">
       <c r="A203" s="1" t="inlineStr">
         <is>
           <t>refresh-token.messages.missing-refresh-token</t>
@@ -3784,7 +3784,7 @@
         </is>
       </c>
     </row>
-    <row r="204" ht="17" customHeight="1">
+    <row r="204" ht="18" customHeight="1">
       <c r="A204" s="1" t="inlineStr">
         <is>
           <t>refresh-token.messages.mismatch-or-expired</t>
@@ -3801,7 +3801,7 @@
         </is>
       </c>
     </row>
-    <row r="205" ht="17" customHeight="1">
+    <row r="205" ht="18" customHeight="1">
       <c r="A205" s="1" t="inlineStr">
         <is>
           <t>refresh-token.messages.success</t>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
     </row>
-    <row r="206" ht="17" customHeight="1">
+    <row r="206" ht="18" customHeight="1">
       <c r="A206" s="1" t="inlineStr">
         <is>
           <t>register.messages.email-exists</t>
@@ -3835,7 +3835,7 @@
         </is>
       </c>
     </row>
-    <row r="207" ht="17" customHeight="1">
+    <row r="207" ht="18" customHeight="1">
       <c r="A207" s="1" t="inlineStr">
         <is>
           <t>register.messages.internal-server-error</t>
@@ -3852,7 +3852,7 @@
         </is>
       </c>
     </row>
-    <row r="208" ht="17" customHeight="1">
+    <row r="208" ht="36" customHeight="1">
       <c r="A208" s="1" t="inlineStr">
         <is>
           <t>register.messages.missing-fields</t>
@@ -3869,7 +3869,7 @@
         </is>
       </c>
     </row>
-    <row r="209" ht="17" customHeight="1">
+    <row r="209" ht="18" customHeight="1">
       <c r="A209" s="1" t="inlineStr">
         <is>
           <t>register.messages.success</t>
@@ -3886,7 +3886,7 @@
         </is>
       </c>
     </row>
-    <row r="210" ht="17" customHeight="1">
+    <row r="210" ht="18" customHeight="1">
       <c r="A210" s="1" t="inlineStr">
         <is>
           <t>register.messages.username-exists</t>
@@ -3903,7 +3903,7 @@
         </is>
       </c>
     </row>
-    <row r="211" ht="17" customHeight="1">
+    <row r="211" ht="18" customHeight="1">
       <c r="A211" s="1" t="inlineStr">
         <is>
           <t>reset-password.messages.internal-server-error</t>
@@ -3920,7 +3920,7 @@
         </is>
       </c>
     </row>
-    <row r="212" ht="17" customHeight="1">
+    <row r="212" ht="18" customHeight="1">
       <c r="A212" s="1" t="inlineStr">
         <is>
           <t>reset-password.messages.invalid-or-expired-token</t>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
     </row>
-    <row r="213" ht="17" customHeight="1">
+    <row r="213" ht="18" customHeight="1">
       <c r="A213" s="1" t="inlineStr">
         <is>
           <t>reset-password.messages.invalid-user-id</t>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
     </row>
-    <row r="214" ht="17" customHeight="1">
+    <row r="214" ht="18" customHeight="1">
       <c r="A214" s="1" t="inlineStr">
         <is>
           <t>reset-password.messages.missing-id-or-token</t>
@@ -3971,7 +3971,7 @@
         </is>
       </c>
     </row>
-    <row r="215" ht="17" customHeight="1">
+    <row r="215" ht="18" customHeight="1">
       <c r="A215" s="1" t="inlineStr">
         <is>
           <t>reset-password.messages.missing-userId-or-password</t>
@@ -3988,7 +3988,7 @@
         </is>
       </c>
     </row>
-    <row r="216" ht="17" customHeight="1">
+    <row r="216" ht="18" customHeight="1">
       <c r="A216" s="1" t="inlineStr">
         <is>
           <t>reset-password.messages.token-valid</t>
@@ -4005,7 +4005,7 @@
         </is>
       </c>
     </row>
-    <row r="217" ht="17" customHeight="1">
+    <row r="217" ht="18" customHeight="1">
       <c r="A217" s="1" t="inlineStr">
         <is>
           <t>reset-password.messages.user-not-found</t>
@@ -4022,7 +4022,7 @@
         </is>
       </c>
     </row>
-    <row r="218" ht="17" customHeight="1">
+    <row r="218" ht="18" customHeight="1">
       <c r="A218" s="1" t="inlineStr">
         <is>
           <t>set-room-status.messages.internal-server-error</t>
@@ -4039,7 +4039,7 @@
         </is>
       </c>
     </row>
-    <row r="219" ht="17" customHeight="1">
+    <row r="219" ht="18" customHeight="1">
       <c r="A219" s="1" t="inlineStr">
         <is>
           <t>set-room-status.messages.invalid-room-id</t>
@@ -4229,721 +4229,721 @@
     <row r="230" ht="18" customHeight="1">
       <c r="A230" s="1" t="inlineStr">
         <is>
-          <t>room.actions.accept-draw</t>
+          <t>room.actions.flip-board</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>Accept</t>
+          <t>Flip board</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>Chấp nhận</t>
+          <t>Đảo chiều bàn cờ</t>
         </is>
       </c>
     </row>
     <row r="231" ht="18" customHeight="1">
       <c r="A231" s="1" t="inlineStr">
         <is>
-          <t>room.actions.reject-draw</t>
+          <t>room.actions.accept-draw</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>Reject</t>
+          <t>Accept</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>Từ chối</t>
+          <t>Chấp nhận</t>
         </is>
       </c>
     </row>
     <row r="232" ht="18" customHeight="1">
       <c r="A232" s="1" t="inlineStr">
         <is>
-          <t>room.actions.send-pm</t>
+          <t>room.actions.reject-draw</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>Send PM</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>Chat</t>
+          <t>Từ chối</t>
         </is>
       </c>
     </row>
     <row r="233" ht="18" customHeight="1">
       <c r="A233" s="1" t="inlineStr">
         <is>
-          <t>room.actions.view-history</t>
+          <t>room.actions.send-pm</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>History</t>
+          <t>Send PM</t>
         </is>
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>Lịch sử</t>
+          <t>Chat</t>
         </is>
       </c>
     </row>
     <row r="234" ht="18" customHeight="1">
       <c r="A234" s="1" t="inlineStr">
         <is>
-          <t>room.actions.kick</t>
+          <t>room.actions.view-history</t>
         </is>
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>Kick</t>
+          <t>History</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>Kick</t>
+          <t>Lịch sử</t>
         </is>
       </c>
     </row>
     <row r="235" ht="18" customHeight="1">
       <c r="A235" s="1" t="inlineStr">
         <is>
-          <t>room.actions.settings</t>
+          <t>room.actions.kick</t>
         </is>
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>Room settings</t>
+          <t>Kick</t>
         </is>
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>Cài đặt phòng</t>
+          <t>Kick</t>
         </is>
       </c>
     </row>
     <row r="236" ht="18" customHeight="1">
       <c r="A236" s="1" t="inlineStr">
         <is>
-          <t>room.messages.draw-accepted</t>
+          <t>room.actions.settings</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>Opponent accepted the draw</t>
+          <t>Room settings</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>Đối phương đã đồng ý hòa</t>
+          <t>Cài đặt phòng</t>
         </is>
       </c>
     </row>
     <row r="237" ht="18" customHeight="1">
       <c r="A237" s="1" t="inlineStr">
         <is>
-          <t>room.messages.draw-rejected</t>
+          <t>room.messages.draw-accepted</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>Opponent rejected the draw</t>
+          <t>Opponent accepted the draw</t>
         </is>
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>Đối phương từ chối hòa</t>
+          <t>Đối phương đã đồng ý hòa</t>
         </is>
       </c>
     </row>
     <row r="238" ht="18" customHeight="1">
       <c r="A238" s="1" t="inlineStr">
         <is>
-          <t>room.messages.draw-completed</t>
+          <t>room.messages.draw-rejected</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>Draw completed</t>
+          <t>Opponent rejected the draw</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>Hòa cờ thành công</t>
+          <t>Đối phương từ chối hòa</t>
         </is>
       </c>
     </row>
     <row r="239" ht="18" customHeight="1">
       <c r="A239" s="1" t="inlineStr">
         <is>
-          <t>room.messages.opponent-surrendered</t>
+          <t>room.messages.draw-completed</t>
         </is>
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>Opponent surrendered! You won!</t>
+          <t>Draw completed</t>
         </is>
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>Đối phương đã đầu hàng! Bạn thắng!</t>
+          <t>Hòa cờ thành công</t>
         </is>
       </c>
     </row>
     <row r="240" ht="18" customHeight="1">
       <c r="A240" s="1" t="inlineStr">
         <is>
-          <t>room.messages.confirm-leave</t>
+          <t>room.messages.opponent-surrendered</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>Are you sure you want to leave room?</t>
+          <t>Opponent surrendered! You won!</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>Bạn có chắc muốn rời bàn chơi?</t>
+          <t>Đối phương đã đầu hàng! Bạn thắng!</t>
         </is>
       </c>
     </row>
     <row r="241" ht="18" customHeight="1">
       <c r="A241" s="1" t="inlineStr">
         <is>
-          <t>room.messages.confirm-surrender</t>
+          <t>room.messages.confirm-leave</t>
         </is>
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>Are you sure you want to surrender?</t>
+          <t>Are you sure you want to leave room?</t>
         </is>
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>Bạn có chắc chắn muốn đầu hàng không?</t>
+          <t>Bạn có chắc muốn rời bàn chơi?</t>
         </is>
       </c>
     </row>
     <row r="242" ht="18" customHeight="1">
       <c r="A242" s="1" t="inlineStr">
         <is>
-          <t>room.messages.confirm-draw</t>
+          <t>room.messages.confirm-surrender</t>
         </is>
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>Are you sure you want to draw?</t>
+          <t>Are you sure you want to surrender?</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>Bạn có chắc chắn muốn hòa không?</t>
+          <t>Bạn có chắc chắn muốn đầu hàng không?</t>
         </is>
       </c>
     </row>
     <row r="243" ht="18" customHeight="1">
       <c r="A243" s="1" t="inlineStr">
         <is>
-          <t>room.messages.confirm-accept-draw</t>
+          <t>room.messages.confirm-draw</t>
         </is>
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>Opponent has proposed a draw. Do you accept?</t>
+          <t>Are you sure you want to draw?</t>
         </is>
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>Đối phương đã chủ hòa, bạn có đồng ý không?</t>
+          <t>Bạn có chắc chắn muốn hòa không?</t>
         </is>
       </c>
     </row>
     <row r="244" ht="18" customHeight="1">
       <c r="A244" s="1" t="inlineStr">
         <is>
-          <t>room.messages.insufficient-amount</t>
+          <t>room.messages.confirm-accept-draw</t>
         </is>
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>You do not have enough balance to join this room</t>
+          <t>Opponent has proposed a draw. Do you accept?</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>Bạn không đủ tiền để tham gia bàn chơi này</t>
+          <t>Đối phương đã chủ hòa, bạn có đồng ý không?</t>
         </is>
       </c>
     </row>
     <row r="245" ht="18" customHeight="1">
       <c r="A245" s="1" t="inlineStr">
         <is>
-          <t>room.messages.all-seats-occupied</t>
+          <t>room.messages.insufficient-amount</t>
         </is>
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>All player seats are occupied</t>
+          <t>You do not have enough balance to join this room</t>
         </is>
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>Tất cả ghế chơi đã được chiếm</t>
+          <t>Bạn không đủ tiền để tham gia bàn chơi này</t>
         </is>
       </c>
     </row>
     <row r="246" ht="18" customHeight="1">
       <c r="A246" s="1" t="inlineStr">
         <is>
-          <t>room.settings.title</t>
+          <t>room.messages.all-seats-occupied</t>
         </is>
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>Room Settings</t>
+          <t>All player seats are occupied</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>Cài đặt phòng</t>
+          <t>Tất cả ghế chơi đã được chiếm</t>
         </is>
       </c>
     </row>
     <row r="247" ht="18" customHeight="1">
       <c r="A247" s="1" t="inlineStr">
         <is>
+          <t>room.notifications.joined</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>{0} joined the room</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>{0} đã vào phòng</t>
+        </is>
+      </c>
+    </row>
+    <row r="248" ht="18" customHeight="1">
+      <c r="A248" s="1" t="inlineStr">
+        <is>
+          <t>room.notifications.left</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>{0} left the room</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>{0} đã rời phòng</t>
+        </is>
+      </c>
+    </row>
+    <row r="249" ht="18" customHeight="1">
+      <c r="A249" s="1" t="inlineStr">
+        <is>
+          <t>room.settings.title</t>
+        </is>
+      </c>
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>Room Settings</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>Cài đặt phòng</t>
+        </is>
+      </c>
+    </row>
+    <row r="250" ht="18" customHeight="1">
+      <c r="A250" s="1" t="inlineStr">
+        <is>
           <t>room.settings.room-name</t>
         </is>
       </c>
-      <c r="B247" s="2" t="inlineStr">
+      <c r="B250" s="2" t="inlineStr">
         <is>
           <t>Room name</t>
         </is>
       </c>
-      <c r="C247" s="2" t="inlineStr">
+      <c r="C250" s="2" t="inlineStr">
         <is>
           <t>Tên phòng</t>
         </is>
       </c>
     </row>
-    <row r="248" ht="17" customHeight="1">
-      <c r="A248" s="1" t="inlineStr">
+    <row r="251" ht="18" customHeight="1">
+      <c r="A251" s="1" t="inlineStr">
         <is>
           <t>room.settings.players</t>
         </is>
       </c>
-      <c r="B248" s="2" t="inlineStr">
+      <c r="B251" s="2" t="inlineStr">
         <is>
           <t>Spectators</t>
         </is>
       </c>
-      <c r="C248" s="2" t="inlineStr">
+      <c r="C251" s="2" t="inlineStr">
         <is>
           <t>Người xem</t>
         </is>
       </c>
     </row>
-    <row r="249" ht="17" customHeight="1">
-      <c r="A249" s="1" t="inlineStr">
+    <row r="252" ht="18" customHeight="1">
+      <c r="A252" s="1" t="inlineStr">
         <is>
           <t>room.settings.save</t>
         </is>
       </c>
-      <c r="B249" s="2" t="inlineStr">
+      <c r="B252" s="2" t="inlineStr">
         <is>
           <t>Save</t>
         </is>
       </c>
-      <c r="C249" s="2" t="inlineStr">
+      <c r="C252" s="2" t="inlineStr">
         <is>
           <t>Lưu</t>
         </is>
       </c>
     </row>
-    <row r="250" ht="17" customHeight="1">
-      <c r="A250" s="1" t="inlineStr">
+    <row r="253" ht="18" customHeight="1">
+      <c r="A253" s="1" t="inlineStr">
         <is>
           <t>room-invite.messages.title</t>
         </is>
       </c>
-      <c r="B250" s="2" t="inlineStr">
+      <c r="B253" s="2" t="inlineStr">
         <is>
           <t>Room Invitation</t>
         </is>
       </c>
-      <c r="C250" s="2" t="inlineStr">
+      <c r="C253" s="2" t="inlineStr">
         <is>
           <t>Lời mời vào phòng</t>
         </is>
       </c>
     </row>
-    <row r="251" ht="17" customHeight="1">
-      <c r="A251" s="1" t="inlineStr">
+    <row r="254" ht="18" customHeight="1">
+      <c r="A254" s="1" t="inlineStr">
         <is>
           <t>start-game.messages.success</t>
         </is>
       </c>
-      <c r="B251" s="2" t="inlineStr">
+      <c r="B254" s="2" t="inlineStr">
         <is>
           <t>Game started successfully</t>
         </is>
       </c>
-      <c r="C251" s="2" t="inlineStr">
+      <c r="C254" s="2" t="inlineStr">
         <is>
           <t>Bắt đầu trò chơi thành công</t>
         </is>
       </c>
     </row>
-    <row r="252" ht="17" customHeight="1">
-      <c r="A252" s="1" t="inlineStr">
+    <row r="255" ht="18" customHeight="1">
+      <c r="A255" s="1" t="inlineStr">
         <is>
           <t>start-game.messages.internal-server-error</t>
         </is>
       </c>
-      <c r="B252" s="2" t="inlineStr">
+      <c r="B255" s="2" t="inlineStr">
         <is>
           <t>Internal server error while starting game</t>
         </is>
       </c>
-      <c r="C252" s="2" t="inlineStr">
+      <c r="C255" s="2" t="inlineStr">
         <is>
           <t>Lỗi máy chủ nội bộ khi bắt đầu trò chơi</t>
         </is>
       </c>
     </row>
-    <row r="253" ht="17" customHeight="1">
-      <c r="A253" s="1" t="inlineStr">
+    <row r="256" ht="18" customHeight="1">
+      <c r="A256" s="1" t="inlineStr">
         <is>
           <t>start-game.messages.invalid-room-id</t>
         </is>
       </c>
-      <c r="B253" s="2" t="inlineStr">
+      <c r="B256" s="2" t="inlineStr">
         <is>
           <t>Field 'id' is required and must be a positive integer</t>
         </is>
       </c>
-      <c r="C253" s="2" t="inlineStr">
+      <c r="C256" s="2" t="inlineStr">
         <is>
           <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
         </is>
       </c>
     </row>
-    <row r="254" ht="17" customHeight="1">
-      <c r="A254" s="1" t="inlineStr">
+    <row r="257" ht="36" customHeight="1">
+      <c r="A257" s="1" t="inlineStr">
         <is>
           <t>start-game.messages.invalid-difficulty</t>
         </is>
       </c>
-      <c r="B254" s="2" t="inlineStr">
+      <c r="B257" s="2" t="inlineStr">
         <is>
           <t>Bot difficulty must be between 1 and 5</t>
         </is>
       </c>
-      <c r="C254" s="2" t="inlineStr">
+      <c r="C257" s="2" t="inlineStr">
         <is>
           <t>Độ khó của bot phải từ 1 đến 5</t>
         </is>
       </c>
     </row>
-    <row r="255" ht="17" customHeight="1">
-      <c r="A255" s="1" t="inlineStr">
+    <row r="258" ht="36" customHeight="1">
+      <c r="A258" s="1" t="inlineStr">
         <is>
           <t>start-game.messages.room-not-found</t>
         </is>
       </c>
-      <c r="B255" s="2" t="inlineStr">
+      <c r="B258" s="2" t="inlineStr">
         <is>
           <t>Room not found</t>
         </is>
       </c>
-      <c r="C255" s="2" t="inlineStr">
+      <c r="C258" s="2" t="inlineStr">
         <is>
           <t>Không tìm thấy phòng</t>
         </is>
       </c>
     </row>
-    <row r="256" ht="17" customHeight="1">
-      <c r="A256" s="1" t="inlineStr">
+    <row r="259" ht="18" customHeight="1">
+      <c r="A259" s="1" t="inlineStr">
         <is>
           <t>start-game.messages.forbidden</t>
         </is>
       </c>
-      <c r="B256" s="2" t="inlineStr">
+      <c r="B259" s="2" t="inlineStr">
         <is>
           <t>Only the room host can start the game</t>
         </is>
       </c>
-      <c r="C256" s="2" t="inlineStr">
+      <c r="C259" s="2" t="inlineStr">
         <is>
           <t>Chỉ chủ phòng mới có thể bắt đầu trò chơi</t>
         </is>
       </c>
     </row>
-    <row r="257" ht="17" customHeight="1">
-      <c r="A257" s="1" t="inlineStr">
+    <row r="260" ht="18" customHeight="1">
+      <c r="A260" s="1" t="inlineStr">
         <is>
           <t>start-game.messages.insufficient-amount</t>
         </is>
       </c>
-      <c r="B257" s="2" t="inlineStr">
+      <c r="B260" s="2" t="inlineStr">
         <is>
           <t>You do not have enough balance to start a game with this bet</t>
         </is>
       </c>
-      <c r="C257" s="2" t="inlineStr">
+      <c r="C260" s="2" t="inlineStr">
         <is>
           <t>Bạn không còn đủ amount để start room</t>
         </is>
       </c>
     </row>
-    <row r="258" ht="17" customHeight="1">
-      <c r="A258" s="1" t="inlineStr">
+    <row r="261" ht="18" customHeight="1">
+      <c r="A261" s="1" t="inlineStr">
         <is>
           <t>start-game.messages.requester-must-pick-team</t>
         </is>
       </c>
-      <c r="B258" s="2" t="inlineStr">
+      <c r="B261" s="2" t="inlineStr">
         <is>
           <t>You must select a team before starting a game with bot</t>
         </is>
       </c>
-      <c r="C258" s="2" t="inlineStr">
+      <c r="C261" s="2" t="inlineStr">
         <is>
           <t>Bạn phải chọn team trước khi bắt đầu trò chơi với bot</t>
-        </is>
-      </c>
-    </row>
-    <row r="259" ht="17" customHeight="1">
-      <c r="A259" s="1" t="inlineStr">
-        <is>
-          <t>update-room.messages.success</t>
-        </is>
-      </c>
-      <c r="B259" s="2" t="inlineStr">
-        <is>
-          <t>Room updated successfully</t>
-        </is>
-      </c>
-      <c r="C259" s="2" t="inlineStr">
-        <is>
-          <t>Cập nhật phòng thành công</t>
-        </is>
-      </c>
-    </row>
-    <row r="260" ht="17" customHeight="1">
-      <c r="A260" s="1" t="inlineStr">
-        <is>
-          <t>update-room.messages.internal-server-error</t>
-        </is>
-      </c>
-      <c r="B260" s="2" t="inlineStr">
-        <is>
-          <t>Internal server error</t>
-        </is>
-      </c>
-      <c r="C260" s="2" t="inlineStr">
-        <is>
-          <t>Lỗi máy chủ nội bộ</t>
-        </is>
-      </c>
-    </row>
-    <row r="261" ht="17" customHeight="1">
-      <c r="A261" s="1" t="inlineStr">
-        <is>
-          <t>update-room.messages.invalid-room-id</t>
-        </is>
-      </c>
-      <c r="B261" s="2" t="inlineStr">
-        <is>
-          <t>Invalid room ID</t>
-        </is>
-      </c>
-      <c r="C261" s="2" t="inlineStr">
-        <is>
-          <t>ID phòng không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="262" ht="17" customHeight="1">
       <c r="A262" s="1" t="inlineStr">
         <is>
-          <t>update-room.messages.name-required</t>
+          <t>update-room.messages.success</t>
         </is>
       </c>
       <c r="B262" s="1" t="inlineStr">
         <is>
-          <t>Room name is required</t>
+          <t>Room updated successfully</t>
         </is>
       </c>
       <c r="C262" s="1" t="inlineStr">
         <is>
-          <t>Tên phòng không được để trống</t>
-        </is>
-      </c>
-    </row>
-    <row r="263" ht="17" customHeight="1">
+          <t>Cập nhật phòng thành công</t>
+        </is>
+      </c>
+    </row>
+    <row r="263" ht="18" customHeight="1">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>update-room.messages.room-not-found</t>
+          <t>update-room.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t>Room not found</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy phòng</t>
-        </is>
-      </c>
-    </row>
-    <row r="264" ht="36" customHeight="1">
+          <t>Lỗi máy chủ nội bộ</t>
+        </is>
+      </c>
+    </row>
+    <row r="264" ht="18" customHeight="1">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>update-room.messages.forbidden</t>
+          <t>update-room.messages.invalid-room-id</t>
         </is>
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>You are not the host of this room</t>
+          <t>Invalid room ID</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>Bạn không phải chủ phòng</t>
+          <t>ID phòng không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="265" ht="18" customHeight="1">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>draw-game.messages.invalid-game-id</t>
+          <t>update-room.messages.name-required</t>
         </is>
       </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
-          <t>Invalid game ID</t>
+          <t>Room name is required</t>
         </is>
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t>ID trò chơi không hợp lệ</t>
+          <t>Tên phòng không được để trống</t>
         </is>
       </c>
     </row>
     <row r="266" ht="18" customHeight="1">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>draw-game.messages.game-not-found</t>
+          <t>update-room.messages.room-not-found</t>
         </is>
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>Game not found</t>
+          <t>Room not found</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy trò chơi</t>
+          <t>Không tìm thấy phòng</t>
         </is>
       </c>
     </row>
     <row r="267" ht="18" customHeight="1">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>draw-game.messages.forbidden</t>
+          <t>update-room.messages.forbidden</t>
         </is>
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>You are not in this room</t>
+          <t>You are not the host of this room</t>
         </is>
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>Bạn không có trong phòng này</t>
-        </is>
-      </c>
-    </row>
-    <row r="268" ht="18" customHeight="1">
+          <t>Bạn không phải chủ phòng</t>
+        </is>
+      </c>
+    </row>
+    <row r="268" ht="36" customHeight="1">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>draw-game.messages.game-history-not-found</t>
+          <t>draw-game.messages.invalid-game-id</t>
         </is>
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>Game history not found</t>
+          <t>Invalid game ID</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy lịch sử trò chơi</t>
+          <t>ID trò chơi không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="269" ht="36" customHeight="1">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>draw-game.messages.game-already-finished</t>
+          <t>draw-game.messages.game-not-found</t>
         </is>
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>Game is already finished</t>
+          <t>Game not found</t>
         </is>
       </c>
       <c r="C269" s="2" t="inlineStr">
         <is>
-          <t>Trò chơi đã kết thúc</t>
+          <t>Không tìm thấy trò chơi</t>
         </is>
       </c>
     </row>
     <row r="270" ht="18" customHeight="1">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>draw-game.messages.success</t>
+          <t>draw-game.messages.forbidden</t>
         </is>
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>Draw game successfully</t>
+          <t>You are not in this room</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>Hòa cờ thành công</t>
+          <t>Bạn không có trong phòng này</t>
         </is>
       </c>
     </row>
     <row r="271" ht="18" customHeight="1">
       <c r="A271" s="1" t="inlineStr">
         <is>
-          <t>draw-game.messages.internal-server-error</t>
+          <t>draw-game.messages.game-history-not-found</t>
         </is>
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Game history not found</t>
         </is>
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Không tìm thấy lịch sử trò chơi</t>
         </is>
       </c>
     </row>
     <row r="272" ht="18" customHeight="1">
       <c r="A272" s="1" t="inlineStr">
         <is>
-          <t>surrender.messages.game-already-finished</t>
+          <t>draw-game.messages.game-already-finished</t>
         </is>
       </c>
       <c r="B272" s="2" t="inlineStr">
@@ -4960,1213 +4960,1576 @@
     <row r="273" ht="18" customHeight="1">
       <c r="A273" s="1" t="inlineStr">
         <is>
-          <t>surrender.messages.game-history-not-found</t>
+          <t>draw-game.messages.success</t>
         </is>
       </c>
       <c r="B273" s="2" t="inlineStr">
         <is>
-          <t>Game history not found</t>
+          <t>Draw game successfully</t>
         </is>
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy lịch sử trò chơi</t>
+          <t>Hòa cờ thành công</t>
         </is>
       </c>
     </row>
     <row r="274" ht="18" customHeight="1">
       <c r="A274" s="1" t="inlineStr">
         <is>
-          <t>surrender.messages.game-not-found</t>
+          <t>draw-game.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>Game not found</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy trò chơi</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="275" ht="18" customHeight="1">
       <c r="A275" s="1" t="inlineStr">
         <is>
-          <t>surrender.messages.internal-server-error</t>
+          <t>surrender.messages.game-already-finished</t>
         </is>
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Game is already finished</t>
         </is>
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Trò chơi đã kết thúc</t>
         </is>
       </c>
     </row>
     <row r="276" ht="18" customHeight="1">
       <c r="A276" s="1" t="inlineStr">
         <is>
-          <t>surrender.messages.invalid-game-id</t>
+          <t>surrender.messages.game-history-not-found</t>
         </is>
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>Invalid game ID</t>
+          <t>Game history not found</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>ID trò chơi không hợp lệ</t>
+          <t>Không tìm thấy lịch sử trò chơi</t>
         </is>
       </c>
     </row>
     <row r="277" ht="18" customHeight="1">
       <c r="A277" s="1" t="inlineStr">
         <is>
-          <t>surrender.messages.invalid-surrender-player</t>
+          <t>surrender.messages.game-not-found</t>
         </is>
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>You are not a player in this game</t>
+          <t>Game not found</t>
         </is>
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t>Bạn không phải là người chơi trong trò chơi này</t>
+          <t>Không tìm thấy trò chơi</t>
         </is>
       </c>
     </row>
     <row r="278" ht="18" customHeight="1">
       <c r="A278" s="1" t="inlineStr">
         <is>
-          <t>surrender.messages.opponent-not-found</t>
+          <t>surrender.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>Opponent not found</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy đối thủ</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="279" ht="18" customHeight="1">
       <c r="A279" s="1" t="inlineStr">
         <is>
-          <t>surrender.messages.success</t>
+          <t>surrender.messages.invalid-game-id</t>
         </is>
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>Surrendered</t>
+          <t>Invalid game ID</t>
         </is>
       </c>
       <c r="C279" s="2" t="inlineStr">
         <is>
-          <t>Đã đầu hàng</t>
+          <t>ID trò chơi không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="280" ht="18" customHeight="1">
       <c r="A280" s="1" t="inlineStr">
         <is>
-          <t>undo.messages.invalid-game-id</t>
+          <t>surrender.messages.invalid-surrender-player</t>
         </is>
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>Invalid game ID</t>
+          <t>You are not a player in this game</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>ID trò chơi không hợp lệ</t>
+          <t>Bạn không phải là người chơi trong trò chơi này</t>
         </is>
       </c>
     </row>
     <row r="281" ht="18" customHeight="1">
       <c r="A281" s="1" t="inlineStr">
         <is>
-          <t>undo.messages.unauthorized</t>
+          <t>surrender.messages.opponent-not-found</t>
         </is>
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>Unauthorized</t>
+          <t>Opponent not found</t>
         </is>
       </c>
       <c r="C281" s="2" t="inlineStr">
         <is>
-          <t>Không được phép truy cập</t>
+          <t>Không tìm thấy đối thủ</t>
         </is>
       </c>
     </row>
     <row r="282" ht="18" customHeight="1">
       <c r="A282" s="1" t="inlineStr">
         <is>
-          <t>undo.messages.game-not-found</t>
+          <t>surrender.messages.success</t>
         </is>
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>Game not found</t>
+          <t>Surrendered</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy trò chơi</t>
+          <t>Đã đầu hàng</t>
         </is>
       </c>
     </row>
     <row r="283" ht="18" customHeight="1">
       <c r="A283" s="1" t="inlineStr">
         <is>
-          <t>undo.messages.not-in-game</t>
+          <t>undo.messages.invalid-game-id</t>
         </is>
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>You are not part of this game</t>
+          <t>Invalid game ID</t>
         </is>
       </c>
       <c r="C283" s="2" t="inlineStr">
         <is>
-          <t>Bạn không phải là người chơi trong trò chơi này</t>
+          <t>ID trò chơi không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="284" ht="18" customHeight="1">
       <c r="A284" s="1" t="inlineStr">
         <is>
-          <t>undo.messages.not-in-room</t>
+          <t>undo.messages.unauthorized</t>
         </is>
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>You are not in this room</t>
+          <t>Unauthorized</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>Bạn không trong phòng này</t>
+          <t>Không được phép truy cập</t>
         </is>
       </c>
     </row>
     <row r="285" ht="18" customHeight="1">
       <c r="A285" s="1" t="inlineStr">
         <is>
-          <t>undo.messages.spectator-cannot-undo</t>
+          <t>undo.messages.game-not-found</t>
         </is>
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>Spectators cannot undo moves</t>
+          <t>Game not found</t>
         </is>
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>Người xem không thể hoàn tác nước đi</t>
+          <t>Không tìm thấy trò chơi</t>
         </is>
       </c>
     </row>
     <row r="286" ht="18" customHeight="1">
       <c r="A286" s="1" t="inlineStr">
         <is>
-          <t>undo.messages.no-moves</t>
+          <t>undo.messages.not-in-game</t>
         </is>
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>No moves to undo</t>
+          <t>You are not part of this game</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>Không có nước đi để hoàn tác</t>
+          <t>Bạn không phải là người chơi trong trò chơi này</t>
         </is>
       </c>
     </row>
     <row r="287" ht="18" customHeight="1">
       <c r="A287" s="1" t="inlineStr">
         <is>
-          <t>undo.messages.delete-failed</t>
+          <t>undo.messages.not-in-room</t>
         </is>
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>Failed to undo move</t>
+          <t>You are not in this room</t>
         </is>
       </c>
       <c r="C287" s="2" t="inlineStr">
         <is>
-          <t>Không thể hoàn tác nước đi</t>
+          <t>Bạn không trong phòng này</t>
         </is>
       </c>
     </row>
     <row r="288" ht="18" customHeight="1">
       <c r="A288" s="1" t="inlineStr">
         <is>
-          <t>undo.messages.undo-limit-exceeded</t>
+          <t>undo.messages.spectator-cannot-undo</t>
         </is>
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>Maximum 3 undo per game exceeded</t>
+          <t>Spectators cannot undo moves</t>
         </is>
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>Đã đạt tối đa 3 lần hoàn tác trong trò chơi</t>
+          <t>Người xem không thể hoàn tác nước đi</t>
         </is>
       </c>
     </row>
     <row r="289" ht="18" customHeight="1">
       <c r="A289" s="1" t="inlineStr">
         <is>
-          <t>undo.messages.success</t>
+          <t>undo.messages.no-moves</t>
         </is>
       </c>
       <c r="B289" s="2" t="inlineStr">
         <is>
-          <t>Move undone successfully</t>
+          <t>No moves to undo</t>
         </is>
       </c>
       <c r="C289" s="2" t="inlineStr">
         <is>
-          <t>Hoàn tác nước đi thành công</t>
+          <t>Không có nước đi để hoàn tác</t>
         </is>
       </c>
     </row>
     <row r="290" ht="18" customHeight="1">
       <c r="A290" s="1" t="inlineStr">
         <is>
-          <t>undo.messages.internal-server-error</t>
+          <t>undo.messages.delete-failed</t>
         </is>
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Failed to undo move</t>
         </is>
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Không thể hoàn tác nước đi</t>
         </is>
       </c>
     </row>
     <row r="291" ht="18" customHeight="1">
       <c r="A291" s="1" t="inlineStr">
         <is>
-          <t>player-history.messages.invalid-user-id</t>
+          <t>undo.messages.undo-limit-exceeded</t>
         </is>
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>Invalid user ID</t>
+          <t>Maximum 3 undo per game exceeded</t>
         </is>
       </c>
       <c r="C291" s="2" t="inlineStr">
         <is>
-          <t>ID người dùng không hợp lệ</t>
+          <t>Đã đạt tối đa 3 lần hoàn tác trong trò chơi</t>
         </is>
       </c>
     </row>
     <row r="292" ht="18" customHeight="1">
       <c r="A292" s="1" t="inlineStr">
         <is>
-          <t>player-history.messages.success</t>
+          <t>undo.messages.success</t>
         </is>
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>Fetch game history successfully</t>
+          <t>Move undone successfully</t>
         </is>
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>Lấy lịch sử trò chơi thành công</t>
+          <t>Hoàn tác nước đi thành công</t>
         </is>
       </c>
     </row>
     <row r="293" ht="18" customHeight="1">
       <c r="A293" s="1" t="inlineStr">
         <is>
-          <t>validate-token.messages.success</t>
+          <t>undo.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t>Token is valid</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C293" s="2" t="inlineStr">
         <is>
-          <t>Token hợp lệ</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="294" ht="18" customHeight="1">
       <c r="A294" s="1" t="inlineStr">
         <is>
-          <t>guide.section.objective</t>
+          <t>player-history.messages.invalid-user-id</t>
         </is>
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>Objective of the game</t>
+          <t>Invalid user ID</t>
         </is>
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>Mục tiêu của trò chơi</t>
+          <t>ID người dùng không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="295" ht="18" customHeight="1">
       <c r="A295" s="1" t="inlineStr">
         <is>
-          <t>guide.section.pieces</t>
+          <t>player-history.messages.success</t>
         </is>
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>Pieces</t>
+          <t>Fetch game history successfully</t>
         </is>
       </c>
       <c r="C295" s="2" t="inlineStr">
         <is>
-          <t>Quân cờ</t>
+          <t>Lấy lịch sử trò chơi thành công</t>
         </is>
       </c>
     </row>
     <row r="296" ht="18" customHeight="1">
       <c r="A296" s="1" t="inlineStr">
         <is>
-          <t>guide.section.moving-pieces</t>
+          <t>validate-token.messages.success</t>
         </is>
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>Moving pieces</t>
+          <t>Token is valid</t>
         </is>
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>Đi quân</t>
+          <t>Token hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="297" ht="18" customHeight="1">
       <c r="A297" s="1" t="inlineStr">
         <is>
-          <t>guide.section.capturing</t>
+          <t>guide.section.objective</t>
         </is>
       </c>
       <c r="B297" s="2" t="inlineStr">
         <is>
-          <t>Capturing</t>
+          <t>Objective of the game</t>
         </is>
       </c>
       <c r="C297" s="2" t="inlineStr">
         <is>
-          <t>Bắt quân</t>
+          <t>Mục tiêu của trò chơi</t>
         </is>
       </c>
     </row>
     <row r="298" ht="18" customHeight="1">
       <c r="A298" s="1" t="inlineStr">
         <is>
-          <t>guide.section.check</t>
+          <t>guide.section.pieces</t>
         </is>
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>Check</t>
+          <t>Pieces</t>
         </is>
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>Chiếu tướng</t>
-        </is>
-      </c>
-    </row>
-    <row r="299" ht="90" customHeight="1">
+          <t>Quân cờ</t>
+        </is>
+      </c>
+    </row>
+    <row r="299" ht="18" customHeight="1">
       <c r="A299" s="1" t="inlineStr">
         <is>
-          <t>guide.section.result</t>
+          <t>guide.section.moving-pieces</t>
         </is>
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
-          <t>Result</t>
+          <t>Moving pieces</t>
         </is>
       </c>
       <c r="C299" s="2" t="inlineStr">
         <is>
-          <t>Kết quả</t>
-        </is>
-      </c>
-    </row>
-    <row r="300" ht="90" customHeight="1">
+          <t>Đi quân</t>
+        </is>
+      </c>
+    </row>
+    <row r="300" ht="18" customHeight="1">
       <c r="A300" s="1" t="inlineStr">
         <is>
-          <t>guide.table.piece</t>
+          <t>guide.section.capturing</t>
         </is>
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>Piece</t>
+          <t>Capturing</t>
         </is>
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>Quân</t>
+          <t>Bắt quân</t>
         </is>
       </c>
     </row>
     <row r="301" ht="18" customHeight="1">
       <c r="A301" s="1" t="inlineStr">
         <is>
-          <t>guide.table.symbol</t>
+          <t>guide.section.check</t>
         </is>
       </c>
       <c r="B301" s="2" t="inlineStr">
         <is>
-          <t>Symbol</t>
+          <t>Check</t>
         </is>
       </c>
       <c r="C301" s="2" t="inlineStr">
         <is>
-          <t>Ký hiệu</t>
+          <t>Chiếu tướng</t>
         </is>
       </c>
     </row>
     <row r="302" ht="18" customHeight="1">
       <c r="A302" s="1" t="inlineStr">
         <is>
-          <t>guide.table.quantity</t>
+          <t>guide.section.result</t>
         </is>
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>Quantity</t>
+          <t>Result</t>
         </is>
       </c>
       <c r="C302" s="2" t="inlineStr">
         <is>
-          <t>Số lượng</t>
-        </is>
-      </c>
-    </row>
-    <row r="303" ht="18" customHeight="1">
+          <t>Kết quả</t>
+        </is>
+      </c>
+    </row>
+    <row r="303" ht="90" customHeight="1">
       <c r="A303" s="1" t="inlineStr">
         <is>
-          <t>guide.objective.paragraph1</t>
+          <t>guide.table.piece</t>
         </is>
       </c>
       <c r="B303" s="2" t="inlineStr">
         <is>
-          <t>A match is played between two players: one controls the Red pieces, and the other controls the Black pieces. The objective of each player is to use their pieces on the board to &lt;b&gt;checkmate&lt;/b&gt; the opponent's General, and win the game.</t>
+          <t>Piece</t>
         </is>
       </c>
       <c r="C303" s="2" t="inlineStr">
         <is>
-          <t>Ván cờ được tiến hành giữa 2 đấu thủ, một người cầm Quân Đỏ, một người cầm Quân Đen. Mục đích của mỗi đấu thủ là tìm mọi cách sử dụng các quân trên bàn cờ để &lt;b&gt;chiếu bí Tướng&lt;/b&gt; của đối phương, giành thắng lợi.</t>
-        </is>
-      </c>
-    </row>
-    <row r="304" ht="18" customHeight="1">
+          <t>Quân</t>
+        </is>
+      </c>
+    </row>
+    <row r="304" ht="90" customHeight="1">
       <c r="A304" s="1" t="inlineStr">
         <is>
-          <t>guide.pieces.paragraph1</t>
+          <t>guide.table.symbol</t>
         </is>
       </c>
       <c r="B304" s="2" t="inlineStr">
         <is>
-          <t>At the start of each game, there must be 32 pieces in total, consisting of &lt;b&gt;7 piece types&lt;/b&gt; split evenly between both sides: 16 Red pieces and 16 Black pieces. The 7 piece types with their symbols and quantities are as follows:</t>
+          <t>Symbol</t>
         </is>
       </c>
       <c r="C304" s="2" t="inlineStr">
         <is>
-          <t>Mỗi ván cờ lúc bắt đầu phải có đủ 32 quân, gồm 7 loại chia đều cho mỗi bên gồm 16 quân Đỏ và 16 quân Đen. &lt;b&gt;7 loại quân&lt;/b&gt; có ký hiệu và số lượng như sau:</t>
+          <t>Ký hiệu</t>
         </is>
       </c>
     </row>
     <row r="305" ht="18" customHeight="1">
       <c r="A305" s="1" t="inlineStr">
         <is>
-          <t>guide.piece.general</t>
+          <t>guide.table.quantity</t>
         </is>
       </c>
       <c r="B305" s="2" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Quantity</t>
         </is>
       </c>
       <c r="C305" s="2" t="inlineStr">
         <is>
-          <t>Tướng</t>
+          <t>Số lượng</t>
         </is>
       </c>
     </row>
     <row r="306" ht="18" customHeight="1">
       <c r="A306" s="1" t="inlineStr">
         <is>
-          <t>guide.piece.advisor</t>
+          <t>guide.objective.paragraph1</t>
         </is>
       </c>
       <c r="B306" s="2" t="inlineStr">
         <is>
-          <t>Advisor</t>
+          <t>A match is played between two players: one controls the Red pieces, and the other controls the Black pieces. The objective of each player is to use their pieces on the board to &lt;b&gt;checkmate&lt;/b&gt; the opponent's General, and win the game.</t>
         </is>
       </c>
       <c r="C306" s="2" t="inlineStr">
         <is>
-          <t>Sĩ</t>
+          <t>Ván cờ được tiến hành giữa 2 đấu thủ, một người cầm Quân Đỏ, một người cầm Quân Đen. Mục đích của mỗi đấu thủ là tìm mọi cách sử dụng các quân trên bàn cờ để &lt;b&gt;chiếu bí Tướng&lt;/b&gt; của đối phương, giành thắng lợi.</t>
         </is>
       </c>
     </row>
     <row r="307" ht="18" customHeight="1">
       <c r="A307" s="1" t="inlineStr">
         <is>
-          <t>guide.piece.elephant</t>
+          <t>guide.pieces.paragraph1</t>
         </is>
       </c>
       <c r="B307" s="2" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>At the start of each game, there must be 32 pieces in total, consisting of &lt;b&gt;7 piece types&lt;/b&gt; split evenly between both sides: 16 Red pieces and 16 Black pieces. The 7 piece types with their symbols and quantities are as follows:</t>
         </is>
       </c>
       <c r="C307" s="2" t="inlineStr">
         <is>
-          <t>Tượng</t>
-        </is>
-      </c>
-    </row>
-    <row r="308" ht="54" customHeight="1">
+          <t>Mỗi ván cờ lúc bắt đầu phải có đủ 32 quân, gồm 7 loại chia đều cho mỗi bên gồm 16 quân Đỏ và 16 quân Đen. &lt;b&gt;7 loại quân&lt;/b&gt; có ký hiệu và số lượng như sau:</t>
+        </is>
+      </c>
+    </row>
+    <row r="308" ht="18" customHeight="1">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>guide.piece.chariot</t>
+          <t>guide.piece.general</t>
         </is>
       </c>
       <c r="B308" s="2" t="inlineStr">
         <is>
-          <t>Chariot</t>
+          <t>General</t>
         </is>
       </c>
       <c r="C308" s="2" t="inlineStr">
         <is>
-          <t>Xe</t>
+          <t>Tướng</t>
         </is>
       </c>
     </row>
     <row r="309" ht="18" customHeight="1">
       <c r="A309" s="2" t="inlineStr">
         <is>
-          <t>guide.piece.horse</t>
+          <t>guide.piece.advisor</t>
         </is>
       </c>
       <c r="B309" s="2" t="inlineStr">
         <is>
-          <t>Horse</t>
+          <t>Advisor</t>
         </is>
       </c>
       <c r="C309" s="2" t="inlineStr">
         <is>
-          <t>Mã</t>
-        </is>
-      </c>
-    </row>
-    <row r="310" ht="90" customHeight="1">
+          <t>Sĩ</t>
+        </is>
+      </c>
+    </row>
+    <row r="310" ht="18" customHeight="1">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>guide.piece.cannon</t>
+          <t>guide.piece.elephant</t>
         </is>
       </c>
       <c r="B310" s="2" t="inlineStr">
         <is>
-          <t>Cannon</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="C310" s="2" t="inlineStr">
         <is>
-          <t>Pháo</t>
+          <t>Tượng</t>
         </is>
       </c>
     </row>
     <row r="311" ht="18" customHeight="1">
       <c r="A311" s="2" t="inlineStr">
         <is>
-          <t>guide.piece.soldier</t>
+          <t>guide.piece.chariot</t>
         </is>
       </c>
       <c r="B311" s="2" t="inlineStr">
         <is>
-          <t>Soldier</t>
+          <t>Chariot</t>
         </is>
       </c>
       <c r="C311" s="2" t="inlineStr">
         <is>
-          <t>Tốt</t>
-        </is>
-      </c>
-    </row>
-    <row r="312" ht="36" customHeight="1">
+          <t>Xe</t>
+        </is>
+      </c>
+    </row>
+    <row r="312" ht="54" customHeight="1">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>guide.moving-pieces.paragraph1</t>
+          <t>guide.piece.horse</t>
         </is>
       </c>
       <c r="B312" s="2" t="inlineStr">
         <is>
-          <t>On each turn, each side may move only one of its own pieces according to the rules. The movement rules are as follows:</t>
+          <t>Horse</t>
         </is>
       </c>
       <c r="C312" s="2" t="inlineStr">
         <is>
-          <t>Mỗi nước đi, mỗi bên chỉ được di chuyển quân của mình theo đúng quy định. Quy định di chuyển của các quân như sau:</t>
+          <t>Mã</t>
         </is>
       </c>
     </row>
     <row r="313" ht="18" customHeight="1">
       <c r="A313" s="2" t="inlineStr">
         <is>
-          <t>guide.general.paragraph1</t>
+          <t>guide.piece.cannon</t>
         </is>
       </c>
       <c r="B313" s="2" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Cannon</t>
         </is>
       </c>
       <c r="C313" s="2" t="inlineStr">
         <is>
-          <t>Tướng</t>
-        </is>
-      </c>
-    </row>
-    <row r="314" ht="72" customHeight="1">
+          <t>Pháo</t>
+        </is>
+      </c>
+    </row>
+    <row r="314" ht="90" customHeight="1">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>guide.general.paragraph2</t>
+          <t>guide.piece.soldier</t>
         </is>
       </c>
       <c r="B314" s="2" t="inlineStr">
         <is>
-          <t>Moves one step &lt;b&gt;horizontally or vertically&lt;/b&gt; within the palace. The two Generals may not face each other directly on the same file. If they are facing each other, there must be at least one piece of either side placed between them.</t>
+          <t>Soldier</t>
         </is>
       </c>
       <c r="C314" s="2" t="inlineStr">
         <is>
-          <t>Mỗi nước được đi một bước &lt;b&gt;ngang hoặc dọc&lt;/b&gt; tùy ý trong cung Tướng. Hai tướng của 2 bên không được đối mặt nhau trực tiếp trên cùng một đường thẳng. Nếu đối mặt, bắt buộc phải có quân của bất kỳ bên nào đứng che mặt.</t>
+          <t>Tốt</t>
         </is>
       </c>
     </row>
     <row r="315" ht="18" customHeight="1">
       <c r="A315" s="2" t="inlineStr">
         <is>
-          <t>guide.advisor.paragraph1</t>
+          <t>guide.moving-pieces.paragraph1</t>
         </is>
       </c>
       <c r="B315" s="2" t="inlineStr">
         <is>
-          <t>Advisor</t>
+          <t>On each turn, each side may move only one of its own pieces according to the rules. The movement rules are as follows:</t>
         </is>
       </c>
       <c r="C315" s="2" t="inlineStr">
         <is>
-          <t>Sĩ</t>
-        </is>
-      </c>
-    </row>
-    <row r="316" ht="54" customHeight="1">
+          <t>Mỗi nước đi, mỗi bên chỉ được di chuyển quân của mình theo đúng quy định. Quy định di chuyển của các quân như sau:</t>
+        </is>
+      </c>
+    </row>
+    <row r="316" ht="36" customHeight="1">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>guide.advisor.paragraph2</t>
+          <t>guide.general.paragraph1</t>
         </is>
       </c>
       <c r="B316" s="2" t="inlineStr">
         <is>
-          <t>Moves one step &lt;b&gt;diagonally&lt;/b&gt; within the palace.</t>
+          <t>General</t>
         </is>
       </c>
       <c r="C316" s="2" t="inlineStr">
         <is>
-          <t>Mỗi nước &lt;b&gt;đi chéo một bước&lt;/b&gt; trong cung Tướng.</t>
+          <t>Tướng</t>
         </is>
       </c>
     </row>
     <row r="317" ht="18" customHeight="1">
       <c r="A317" s="2" t="inlineStr">
         <is>
-          <t>guide.elephant.paragraph1</t>
+          <t>guide.general.paragraph2</t>
         </is>
       </c>
       <c r="B317" s="2" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Moves one step &lt;b&gt;horizontally or vertically&lt;/b&gt; within the palace. The two Generals may not face each other directly on the same file. If they are facing each other, there must be at least one piece of either side placed between them.</t>
         </is>
       </c>
       <c r="C317" s="2" t="inlineStr">
         <is>
-          <t>Tượng</t>
+          <t>Mỗi nước được đi một bước &lt;b&gt;ngang hoặc dọc&lt;/b&gt; tùy ý trong cung Tướng. Hai tướng của 2 bên không được đối mặt nhau trực tiếp trên cùng một đường thẳng. Nếu đối mặt, bắt buộc phải có quân của bất kỳ bên nào đứng che mặt.</t>
         </is>
       </c>
     </row>
     <row r="318" ht="72" customHeight="1">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>guide.elephant.paragraph2</t>
+          <t>guide.advisor.paragraph1</t>
         </is>
       </c>
       <c r="B318" s="2" t="inlineStr">
         <is>
-          <t>Moves &lt;b&gt;two steps diagonally&lt;/b&gt; on its own side of the board and may not cross the river. If there is another piece on the midpoint of that diagonal path, the Elephant is blocked and cannot move.</t>
+          <t>Advisor</t>
         </is>
       </c>
       <c r="C318" s="2" t="inlineStr">
         <is>
-          <t>Mỗi nước &lt;b&gt;đi chéo hai bước&lt;/b&gt; tại trận địa bên mình, không được qua sông. Nếu ở giữa đường chéo đó có quân khác đứng thì quân Tượng bị cản, không đi được.</t>
+          <t>Sĩ</t>
         </is>
       </c>
     </row>
     <row r="319" ht="18" customHeight="1">
       <c r="A319" s="2" t="inlineStr">
         <is>
-          <t>guide.chariot.paragraph1</t>
+          <t>guide.advisor.paragraph2</t>
         </is>
       </c>
       <c r="B319" s="2" t="inlineStr">
         <is>
-          <t>Chariot</t>
+          <t>Moves one step &lt;b&gt;diagonally&lt;/b&gt; within the palace.</t>
         </is>
       </c>
       <c r="C319" s="2" t="inlineStr">
         <is>
-          <t>Xe</t>
-        </is>
-      </c>
-    </row>
-    <row r="320" ht="90" customHeight="1">
+          <t>Mỗi nước &lt;b&gt;đi chéo một bước&lt;/b&gt; trong cung Tướng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="320" ht="54" customHeight="1">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>guide.chariot.paragraph2</t>
+          <t>guide.elephant.paragraph1</t>
         </is>
       </c>
       <c r="B320" s="2" t="inlineStr">
         <is>
-          <t>Moves &lt;b&gt;horizontally or vertically&lt;/b&gt; with no limit on distance, as long as no piece blocks the path.</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="C320" s="2" t="inlineStr">
         <is>
-          <t>Mỗi nước được &lt;b&gt;đi dọc hoặc đi ngang&lt;/b&gt;, không hạn chế số bước đi nếu không có quân khác cản đường.</t>
+          <t>Tượng</t>
         </is>
       </c>
     </row>
     <row r="321" ht="18" customHeight="1">
       <c r="A321" s="2" t="inlineStr">
         <is>
-          <t>guide.horse.paragraph1</t>
+          <t>guide.elephant.paragraph2</t>
         </is>
       </c>
       <c r="B321" s="2" t="inlineStr">
         <is>
-          <t>Horse</t>
+          <t>Moves &lt;b&gt;two steps diagonally&lt;/b&gt; on its own side of the board and may not cross the river. If there is another piece on the midpoint of that diagonal path, the Elephant is blocked and cannot move.</t>
         </is>
       </c>
       <c r="C321" s="2" t="inlineStr">
         <is>
-          <t>Mã</t>
+          <t>Mỗi nước &lt;b&gt;đi chéo hai bước&lt;/b&gt; tại trận địa bên mình, không được qua sông. Nếu ở giữa đường chéo đó có quân khác đứng thì quân Tượng bị cản, không đi được.</t>
         </is>
       </c>
     </row>
     <row r="322" ht="72" customHeight="1">
       <c r="A322" s="2" t="inlineStr">
         <is>
+          <t>guide.chariot.paragraph1</t>
+        </is>
+      </c>
+      <c r="B322" s="2" t="inlineStr">
+        <is>
+          <t>Chariot</t>
+        </is>
+      </c>
+      <c r="C322" s="2" t="inlineStr">
+        <is>
+          <t>Xe</t>
+        </is>
+      </c>
+    </row>
+    <row r="323" ht="18" customHeight="1">
+      <c r="A323" s="2" t="inlineStr">
+        <is>
+          <t>guide.chariot.paragraph2</t>
+        </is>
+      </c>
+      <c r="B323" s="2" t="inlineStr">
+        <is>
+          <t>Moves &lt;b&gt;horizontally or vertically&lt;/b&gt; with no limit on distance, as long as no piece blocks the path.</t>
+        </is>
+      </c>
+      <c r="C323" s="2" t="inlineStr">
+        <is>
+          <t>Mỗi nước được &lt;b&gt;đi dọc hoặc đi ngang&lt;/b&gt;, không hạn chế số bước đi nếu không có quân khác cản đường.</t>
+        </is>
+      </c>
+    </row>
+    <row r="324" ht="90" customHeight="1">
+      <c r="A324" s="2" t="inlineStr">
+        <is>
+          <t>guide.horse.paragraph1</t>
+        </is>
+      </c>
+      <c r="B324" s="2" t="inlineStr">
+        <is>
+          <t>Horse</t>
+        </is>
+      </c>
+      <c r="C324" s="2" t="inlineStr">
+        <is>
+          <t>Mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="325" ht="18" customHeight="1">
+      <c r="A325" s="2" t="inlineStr">
+        <is>
           <t>guide.horse.paragraph2</t>
         </is>
       </c>
-      <c r="B322" s="2" t="inlineStr">
+      <c r="B325" s="2" t="inlineStr">
         <is>
           <t>Moves in an &lt;b&gt;L-shape&lt;/b&gt; (one step orthogonally then one step diagonally outward). If the adjacent orthogonal point is occupied by any piece, the Horse is blocked and cannot move.</t>
         </is>
       </c>
-      <c r="C322" s="2" t="inlineStr">
+      <c r="C325" s="2" t="inlineStr">
         <is>
           <t>Đi theo &lt;b&gt;đường chéo hình chữ nhật&lt;/b&gt; của hai ô vuông liền nhau. Nếu giao điểm liền kề bước thẳng dọc ngang có một quân khác đứng thì Mã bị cản, không đi được.</t>
         </is>
       </c>
     </row>
-    <row r="323" ht="54" customHeight="1">
-      <c r="A323" s="2" t="inlineStr">
+    <row r="326" ht="72" customHeight="1">
+      <c r="A326" s="2" t="inlineStr">
         <is>
           <t>guide.cannon.paragraph1</t>
         </is>
       </c>
-      <c r="B323" s="2" t="inlineStr">
+      <c r="B326" s="2" t="inlineStr">
         <is>
           <t>Cannon</t>
         </is>
       </c>
-      <c r="C323" s="2" t="inlineStr">
+      <c r="C326" s="2" t="inlineStr">
         <is>
           <t>Pháo</t>
-        </is>
-      </c>
-    </row>
-    <row r="324" ht="54" customHeight="1">
-      <c r="A324" s="2" t="inlineStr">
-        <is>
-          <t>guide.cannon.paragraph2</t>
-        </is>
-      </c>
-      <c r="B324" s="2" t="inlineStr">
-        <is>
-          <t>Moves &lt;b&gt;horizontally or vertically&lt;/b&gt; like a Chariot when not capturing. To capture, it must &lt;b&gt;jump over exactly one piece&lt;/b&gt; to reach its target. If there are zero or more than one pieces between the Cannon and the target, it cannot capture.</t>
-        </is>
-      </c>
-      <c r="C324" s="2" t="inlineStr">
-        <is>
-          <t>Đi ngang hoặc dọc giống Xe khi không bắt quân. Để bắt quân, nó phải &lt;b&gt;nhảy qua đúng một quân khác&lt;/b&gt; để đến mục tiêu. Nếu không có hoặc có nhiều hơn một quân giữa Pháo và mục tiêu, nó không thể bắt quân.</t>
-        </is>
-      </c>
-    </row>
-    <row r="325" ht="54" customHeight="1">
-      <c r="A325" s="2" t="inlineStr">
-        <is>
-          <t>guide.soldier.paragraph1</t>
-        </is>
-      </c>
-      <c r="B325" s="2" t="inlineStr">
-        <is>
-          <t>Soldier</t>
-        </is>
-      </c>
-      <c r="C325" s="2" t="inlineStr">
-        <is>
-          <t>Tốt</t>
-        </is>
-      </c>
-    </row>
-    <row r="326" ht="90" customHeight="1">
-      <c r="A326" s="2" t="inlineStr">
-        <is>
-          <t>guide.soldier.paragraph2</t>
-        </is>
-      </c>
-      <c r="B326" s="2" t="inlineStr">
-        <is>
-          <t>Moves &lt;b&gt;one step&lt;/b&gt; each turn. Before crossing the river, it can only move forward. After crossing the river, it may move &lt;b&gt;forward or sideways&lt;/b&gt;, but never backward.</t>
-        </is>
-      </c>
-      <c r="C326" s="2" t="inlineStr">
-        <is>
-          <t>Mỗi nước đi &lt;b&gt;một bước&lt;/b&gt;. Khi chưa qua sông, Tốt chỉ được tiến. Khi Tốt đã qua sông được quyền &lt;b&gt;đi tiến và đi ngang&lt;/b&gt;, không được phép lùi.</t>
         </is>
       </c>
     </row>
     <row r="327" ht="54" customHeight="1">
       <c r="A327" s="2" t="inlineStr">
         <is>
+          <t>guide.cannon.paragraph2</t>
+        </is>
+      </c>
+      <c r="B327" s="2" t="inlineStr">
+        <is>
+          <t>Moves &lt;b&gt;horizontally or vertically&lt;/b&gt; like a Chariot when not capturing. To capture, it must &lt;b&gt;jump over exactly one piece&lt;/b&gt; to reach its target. If there are zero or more than one pieces between the Cannon and the target, it cannot capture.</t>
+        </is>
+      </c>
+      <c r="C327" s="2" t="inlineStr">
+        <is>
+          <t>Đi ngang hoặc dọc giống Xe khi không bắt quân. Để bắt quân, nó phải &lt;b&gt;nhảy qua đúng một quân khác&lt;/b&gt; để đến mục tiêu. Nếu không có hoặc có nhiều hơn một quân giữa Pháo và mục tiêu, nó không thể bắt quân.</t>
+        </is>
+      </c>
+    </row>
+    <row r="328" ht="54" customHeight="1">
+      <c r="A328" s="2" t="inlineStr">
+        <is>
+          <t>guide.soldier.paragraph1</t>
+        </is>
+      </c>
+      <c r="B328" s="2" t="inlineStr">
+        <is>
+          <t>Soldier</t>
+        </is>
+      </c>
+      <c r="C328" s="2" t="inlineStr">
+        <is>
+          <t>Tốt</t>
+        </is>
+      </c>
+    </row>
+    <row r="329" ht="54" customHeight="1">
+      <c r="A329" s="2" t="inlineStr">
+        <is>
+          <t>guide.soldier.paragraph2</t>
+        </is>
+      </c>
+      <c r="B329" s="2" t="inlineStr">
+        <is>
+          <t>Moves &lt;b&gt;one step&lt;/b&gt; each turn. Before crossing the river, it can only move forward. After crossing the river, it may move &lt;b&gt;forward or sideways&lt;/b&gt;, but never backward.</t>
+        </is>
+      </c>
+      <c r="C329" s="2" t="inlineStr">
+        <is>
+          <t>Mỗi nước đi &lt;b&gt;một bước&lt;/b&gt;. Khi chưa qua sông, Tốt chỉ được tiến. Khi Tốt đã qua sông được quyền &lt;b&gt;đi tiến và đi ngang&lt;/b&gt;, không được phép lùi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="330" ht="90" customHeight="1">
+      <c r="A330" s="2" t="inlineStr">
+        <is>
           <t>guide.capturing.paragraph1</t>
         </is>
       </c>
-      <c r="B327" s="2" t="inlineStr">
+      <c r="B330" s="2" t="inlineStr">
         <is>
           <t>When a piece moves to an intersection occupied by an opponent's piece, it may &lt;b&gt;capture that piece&lt;/b&gt; and occupy its position.</t>
         </is>
       </c>
-      <c r="C327" s="2" t="inlineStr">
+      <c r="C330" s="2" t="inlineStr">
         <is>
           <t>Khi một quân đi tới một giao điểm khác đã có quân đối phương đứng thì được quyền &lt;b&gt;bắt quân đó&lt;/b&gt;, đồng thời chiếm giữ vị trí quân bị bắt.</t>
         </is>
       </c>
     </row>
-    <row r="328" ht="36" customHeight="1">
-      <c r="A328" s="2" t="inlineStr">
+    <row r="331" ht="54" customHeight="1">
+      <c r="A331" s="2" t="inlineStr">
         <is>
           <t>guide.capturing.paragraph2</t>
         </is>
       </c>
-      <c r="B328" s="2" t="inlineStr">
+      <c r="B331" s="2" t="inlineStr">
         <is>
           <t>You may not capture your own pieces. You may sacrifice your own pieces to be captured by the opponent, &lt;b&gt;except for the General&lt;/b&gt;.</t>
         </is>
       </c>
-      <c r="C328" s="2" t="inlineStr">
+      <c r="C331" s="2" t="inlineStr">
         <is>
           <t>Không được bắt quân bên mình. Được phép cho đối phương bắt đầu quân mình chủ động hiến mình cho đối phương, &lt;b&gt;trừ Tướng&lt;/b&gt;.</t>
         </is>
       </c>
     </row>
-    <row r="329" ht="18" customHeight="1">
-      <c r="A329" s="2" t="inlineStr">
+    <row r="332" ht="36" customHeight="1">
+      <c r="A332" s="2" t="inlineStr">
         <is>
           <t>guide.capturing.paragraph3</t>
         </is>
       </c>
-      <c r="B329" s="2" t="inlineStr">
+      <c r="B332" s="2" t="inlineStr">
         <is>
           <t>A captured piece is removed from the board. &lt;b&gt;Chasing one piece for more than 6 consecutive moves is not allowed&lt;/b&gt;.</t>
         </is>
       </c>
-      <c r="C329" s="2" t="inlineStr">
+      <c r="C332" s="2" t="inlineStr">
         <is>
           <t>Quân bị bắt phải bị loại và bị nhấc ra khỏi bàn cờ. &lt;b&gt;Không được đuổi 1 quân quá 6 nước cờ liên tiếp&lt;/b&gt;.</t>
         </is>
       </c>
     </row>
-    <row r="330" ht="36" customHeight="1">
-      <c r="A330" s="2" t="inlineStr">
+    <row r="333" ht="18" customHeight="1">
+      <c r="A333" s="2" t="inlineStr">
         <is>
           <t>guide.check.paragraph1</t>
         </is>
       </c>
-      <c r="B330" s="2" t="inlineStr">
+      <c r="B333" s="2" t="inlineStr">
         <is>
           <t>If a player makes a move that threatens to capture the opponent's General on the next move (by the same piece or another piece), it is called a &lt;b&gt;Check&lt;/b&gt;. The checked side must respond to avoid check. Otherwise, that side loses</t>
         </is>
       </c>
-      <c r="C330" s="2" t="inlineStr">
+      <c r="C333" s="2" t="inlineStr">
         <is>
           <t>Nếu người chơi thực hiện một nước đi đe dọa bắt Tướng của đối phương ở nước đi tiếp theo (bằng chính quân cờ đó hoặc một quân cờ khác), thì đó được gọi là &lt;b&gt;Chiếu&lt;/b&gt;. Bên bị chiếu phải đáp trả để tránh bị chiếu. Nếu không sẽ bị xử thua</t>
         </is>
       </c>
     </row>
-    <row r="331" ht="36" customHeight="1">
-      <c r="A331" s="2" t="inlineStr">
+    <row r="334" ht="36" customHeight="1">
+      <c r="A334" s="2" t="inlineStr">
         <is>
           <t>guide.check.paragraph2</t>
         </is>
       </c>
-      <c r="B331" s="2" t="inlineStr">
+      <c r="B334" s="2" t="inlineStr">
         <is>
           <t>When the General is checked from any direction (including from behind), the checked side may respond in one of the following ways:</t>
         </is>
       </c>
-      <c r="C331" s="2" t="inlineStr">
+      <c r="C334" s="2" t="inlineStr">
         <is>
           <t>Tướng bị chiếu từ cả bốn hướng (bị chiếu cả từ phía sau) có thể ứng phó với nước chiếu tướng bằng một trong các cách sau:</t>
         </is>
       </c>
     </row>
-    <row r="332" ht="72" customHeight="1">
-      <c r="A332" s="2" t="inlineStr">
+    <row r="335" ht="36" customHeight="1">
+      <c r="A335" s="2" t="inlineStr">
         <is>
           <t>guide.check.paragraph3</t>
         </is>
       </c>
-      <c r="B332" s="2" t="inlineStr">
+      <c r="B335" s="2" t="inlineStr">
         <is>
           <t>Move the General to another position to escape check</t>
         </is>
       </c>
-      <c r="C332" s="2" t="inlineStr">
+      <c r="C335" s="2" t="inlineStr">
         <is>
           <t>Di chuyển tướng sang vị trí khác để tránh nước chiếu</t>
         </is>
       </c>
     </row>
-    <row r="333" ht="54" customHeight="1">
-      <c r="A333" s="2" t="inlineStr">
+    <row r="336" ht="72" customHeight="1">
+      <c r="A336" s="2" t="inlineStr">
         <is>
           <t>guide.check.paragraph4</t>
         </is>
       </c>
-      <c r="B333" s="2" t="inlineStr">
+      <c r="B336" s="2" t="inlineStr">
         <is>
           <t>Capture the checking piece</t>
         </is>
       </c>
-      <c r="C333" s="2" t="inlineStr">
+      <c r="C336" s="2" t="inlineStr">
         <is>
           <t>Bắt quân đang chiếu</t>
         </is>
       </c>
     </row>
-    <row r="334" ht="54" customHeight="1">
-      <c r="A334" s="2" t="inlineStr">
+    <row r="337" ht="54" customHeight="1">
+      <c r="A337" s="2" t="inlineStr">
         <is>
           <t>guide.check.paragraph5</t>
         </is>
       </c>
-      <c r="B334" s="2" t="inlineStr">
+      <c r="B337" s="2" t="inlineStr">
         <is>
           <t>Block the checking line with another piece to protect the General</t>
         </is>
       </c>
-      <c r="C334" s="2" t="inlineStr">
+      <c r="C337" s="2" t="inlineStr">
         <is>
           <t>Dùng quân khác cản quân chiếu, đi quân che đỡ cho tướng</t>
         </is>
       </c>
     </row>
-    <row r="335" ht="90" customHeight="1">
-      <c r="A335" s="2" t="inlineStr">
+    <row r="338" ht="54" customHeight="1">
+      <c r="A338" s="2" t="inlineStr">
         <is>
           <t>guide.check.paragraph6</t>
         </is>
       </c>
-      <c r="B335" s="2" t="inlineStr">
+      <c r="B338" s="2" t="inlineStr">
         <is>
           <t>Repeatedly checking for more than 6 consecutive moves is not allowed</t>
         </is>
       </c>
-      <c r="C335" s="2" t="inlineStr">
+      <c r="C338" s="2" t="inlineStr">
         <is>
           <t>Không được chiếu tướng quá 6 nước cờ liên tiếp</t>
         </is>
       </c>
     </row>
-    <row r="336" ht="54" customHeight="1">
-      <c r="A336" s="2" t="inlineStr">
+    <row r="339" ht="90" customHeight="1">
+      <c r="A339" s="2" t="inlineStr">
         <is>
           <t>guide.result.paragraph1</t>
         </is>
       </c>
-      <c r="B336" s="2" t="inlineStr">
+      <c r="B339" s="2" t="inlineStr">
         <is>
           <t>When one side gives Check and the other side has no legal way to protect the General, it is called a &lt;b&gt;Checkmate&lt;/b&gt;. The side that delivers Checkmate wins.</t>
         </is>
       </c>
-      <c r="C336" s="2" t="inlineStr">
+      <c r="C339" s="2" t="inlineStr">
         <is>
           <t>Khi một bên chiếu Tướng mà bên còn lại không thể làm gì để bảo vệ Tướng thì được gọi là &lt;b&gt;Chiếu Hết&lt;/b&gt;, bên thực hiện được Chiếu Hết sẽ giành chiến thắng.</t>
         </is>
       </c>
     </row>
-    <row r="337" ht="17" customHeight="1">
-      <c r="A337" s="2" t="inlineStr">
+    <row r="340" ht="54" customHeight="1">
+      <c r="A340" s="2" t="inlineStr">
         <is>
           <t>guide.result.paragraph2</t>
         </is>
       </c>
-      <c r="B337" s="2" t="inlineStr">
+      <c r="B340" s="2" t="inlineStr">
         <is>
           <t>If a player runs out of time for a single move (for example: 90s) without moving, the other side is awarded a &lt;b&gt;win&lt;/b&gt;.</t>
         </is>
       </c>
-      <c r="C337" s="2" t="inlineStr">
+      <c r="C340" s="2" t="inlineStr">
         <is>
           <t>Khi hết thời gian một nước đi (ví dụ: 90s) mà vẫn chưa di chuyển quân thì bên còn lại sẽ được &lt;b&gt;xử Thắng&lt;/b&gt;.</t>
         </is>
       </c>
     </row>
-    <row r="338" ht="17" customHeight="1">
-      <c r="A338" s="2" t="inlineStr">
+    <row r="341" ht="18" customHeight="1">
+      <c r="A341" s="2" t="inlineStr">
         <is>
           <t>guide.result.paragraph3</t>
         </is>
       </c>
-      <c r="B338" s="2" t="inlineStr">
+      <c r="B341" s="2" t="inlineStr">
         <is>
           <t>If a player runs out of total game time (for example: 5 minutes or 10 minutes), the other side is awarded a &lt;b&gt;win&lt;/b&gt;.</t>
         </is>
       </c>
-      <c r="C338" s="2" t="inlineStr">
+      <c r="C341" s="2" t="inlineStr">
         <is>
           <t>Khi một bên hết thời gian ván đấu (ví dụ: 5 phút, 10 phút) thì bên còn lại sẽ được &lt;b&gt;xử Thắng&lt;/b&gt;.</t>
         </is>
       </c>
     </row>
-    <row r="339" ht="17" customHeight="1">
-      <c r="A339" s="2" t="inlineStr">
+    <row r="342" ht="18" customHeight="1">
+      <c r="A342" s="2" t="inlineStr">
         <is>
           <t>guide.result.paragraph4</t>
         </is>
       </c>
-      <c r="B339" s="2" t="inlineStr">
+      <c r="B342" s="2" t="inlineStr">
         <is>
           <t>If both sides have no pieces that have crossed the river, the game is declared a &lt;b&gt;draw&lt;/b&gt;. If one side still has pieces across the river but runs out of time, while the other side still has time but has no pieces across the river, the game is declared a &lt;b&gt;draw&lt;/b&gt;.</t>
         </is>
       </c>
-      <c r="C339" s="2" t="inlineStr">
+      <c r="C342" s="2" t="inlineStr">
         <is>
           <t>Khi cả 2 bên đều không còn quân qua sông, ván đấu sẽ được &lt;b&gt;xử Hòa&lt;/b&gt;. Khi một bên còn quân qua sông nhưng cạn thời gian, một bên còn thời gian nhưng hết quân qua sông, ván đấu sẽ được &lt;b&gt;xử Hòa&lt;/b&gt;.</t>
         </is>
       </c>
     </row>
-    <row r="340" ht="17" customHeight="1">
-      <c r="A340" s="2" t="inlineStr">
+    <row r="343" ht="36" customHeight="1">
+      <c r="A343" s="2" t="inlineStr">
         <is>
           <t>guide.result.paragraph5</t>
         </is>
       </c>
-      <c r="B340" s="2" t="inlineStr">
+      <c r="B343" s="2" t="inlineStr">
         <is>
           <t>Within 40 moves, if there is no capture and no Soldier advances by one square, the game is declared a &lt;b&gt;draw&lt;/b&gt;.</t>
         </is>
       </c>
-      <c r="C340" s="2" t="inlineStr">
+      <c r="C343" s="2" t="inlineStr">
         <is>
           <t>Trong vòng 40 nước nếu không phát sinh nước bắt quân, Tốt không tiến 1 ô thì ván đấu sẽ được &lt;b&gt;xử Hòa&lt;/b&gt;.</t>
         </is>
       </c>
     </row>
-    <row r="341" ht="17" customHeight="1">
-      <c r="A341" s="2" t="inlineStr"/>
-      <c r="B341" s="2" t="inlineStr"/>
-      <c r="C341" s="2" t="inlineStr"/>
-    </row>
-    <row r="342" ht="17" customHeight="1">
-      <c r="A342" s="2" t="inlineStr"/>
-      <c r="B342" s="2" t="inlineStr"/>
-      <c r="C342" s="2" t="inlineStr"/>
-    </row>
-    <row r="343" ht="17" customHeight="1">
-      <c r="A343" s="2" t="inlineStr"/>
-      <c r="B343" s="2" t="inlineStr"/>
-      <c r="C343" s="2" t="inlineStr"/>
-    </row>
-    <row r="344" ht="17" customHeight="1">
-      <c r="A344" s="2" t="inlineStr"/>
-      <c r="B344" s="2" t="inlineStr"/>
-      <c r="C344" s="2" t="inlineStr"/>
-    </row>
-    <row r="345">
-      <c r="A345" t="inlineStr"/>
-      <c r="B345" t="inlineStr"/>
-      <c r="C345" t="inlineStr"/>
-    </row>
-    <row r="346">
-      <c r="A346" t="inlineStr"/>
-      <c r="B346" t="inlineStr"/>
-      <c r="C346" t="inlineStr"/>
-    </row>
-    <row r="347">
-      <c r="A347" t="inlineStr"/>
-      <c r="B347" t="inlineStr"/>
-      <c r="C347" t="inlineStr"/>
-    </row>
-    <row r="348">
-      <c r="A348" t="inlineStr"/>
-      <c r="B348" t="inlineStr"/>
-      <c r="C348" t="inlineStr"/>
-    </row>
-    <row r="349">
-      <c r="A349" t="inlineStr"/>
-      <c r="B349" t="inlineStr"/>
-      <c r="C349" t="inlineStr"/>
-    </row>
-    <row r="350">
-      <c r="A350" t="inlineStr"/>
-      <c r="B350" t="inlineStr"/>
-      <c r="C350" t="inlineStr"/>
-    </row>
-    <row r="351">
-      <c r="A351" t="inlineStr"/>
-      <c r="B351" t="inlineStr"/>
-      <c r="C351" t="inlineStr"/>
+    <row r="344" ht="18" customHeight="1">
+      <c r="A344" s="2" t="inlineStr">
+        <is>
+          <t>extra-money.lucky-wheel.title</t>
+        </is>
+      </c>
+      <c r="B344" s="2" t="inlineStr">
+        <is>
+          <t>Lucky Wheel</t>
+        </is>
+      </c>
+      <c r="C344" s="2" t="inlineStr">
+        <is>
+          <t>Vòng quay may mắn</t>
+        </is>
+      </c>
+    </row>
+    <row r="345" ht="18" customHeight="1">
+      <c r="A345" s="2" t="inlineStr">
+        <is>
+          <t>extra-money.lucky-wheel.description</t>
+        </is>
+      </c>
+      <c r="B345" s="2" t="inlineStr">
+        <is>
+          <t>Spin the wheel to earn money! Click the spin button in the middle of the wheel to try your luck.</t>
+        </is>
+      </c>
+      <c r="C345" s="2" t="inlineStr">
+        <is>
+          <t>Quay vòng để kiếm tiền! Bấm nút Quay ở giữa vòng quay để thử vận may của bạn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="346" ht="36" customHeight="1">
+      <c r="A346" s="2" t="inlineStr">
+        <is>
+          <t>extra-money.lucky-wheel.spin-button</t>
+        </is>
+      </c>
+      <c r="B346" s="2" t="inlineStr">
+        <is>
+          <t>Spin</t>
+        </is>
+      </c>
+      <c r="C346" s="2" t="inlineStr">
+        <is>
+          <t>Quay</t>
+        </is>
+      </c>
+    </row>
+    <row r="347" ht="18" customHeight="1">
+      <c r="A347" s="2" t="inlineStr">
+        <is>
+          <t>extra-money.lucky-wheel.reward-placeholder</t>
+        </is>
+      </c>
+      <c r="B347" s="2" t="inlineStr">
+        <is>
+          <t>Click Spin to get started</t>
+        </is>
+      </c>
+      <c r="C347" s="2" t="inlineStr">
+        <is>
+          <t>Nhấp Quay để bắt đầu</t>
+        </is>
+      </c>
+    </row>
+    <row r="348" ht="36" customHeight="1">
+      <c r="A348" s="2" t="inlineStr">
+        <is>
+          <t>extra-money.title</t>
+        </is>
+      </c>
+      <c r="B348" s="2" t="inlineStr">
+        <is>
+          <t>Daily tasks</t>
+        </is>
+      </c>
+      <c r="C348" s="2" t="inlineStr">
+        <is>
+          <t>Tác vụ thường nhật</t>
+        </is>
+      </c>
+    </row>
+    <row r="349" ht="18" customHeight="1">
+      <c r="A349" s="2" t="inlineStr">
+        <is>
+          <t>extra-money.tab.lucky-wheel</t>
+        </is>
+      </c>
+      <c r="B349" s="2" t="inlineStr">
+        <is>
+          <t>Lucky Wheel</t>
+        </is>
+      </c>
+      <c r="C349" s="2" t="inlineStr">
+        <is>
+          <t>Vòng Quay May Mắn</t>
+        </is>
+      </c>
+    </row>
+    <row r="350" ht="18" customHeight="1">
+      <c r="A350" s="2" t="inlineStr">
+        <is>
+          <t>extra-money.tab.bonus-coin</t>
+        </is>
+      </c>
+      <c r="B350" s="2" t="inlineStr">
+        <is>
+          <t>Bonus Coin</t>
+        </is>
+      </c>
+      <c r="C350" s="2" t="inlineStr">
+        <is>
+          <t>Xu Thưởng</t>
+        </is>
+      </c>
+    </row>
+    <row r="351" ht="18" customHeight="1">
+      <c r="A351" s="2" t="inlineStr">
+        <is>
+          <t>extra-money.tab.daily-bonus</t>
+        </is>
+      </c>
+      <c r="B351" s="2" t="inlineStr">
+        <is>
+          <t>Daily Bonus</t>
+        </is>
+      </c>
+      <c r="C351" s="2" t="inlineStr">
+        <is>
+          <t>Thưởng hàng ngày</t>
+        </is>
+      </c>
+    </row>
+    <row r="352" ht="18" customHeight="1">
+      <c r="A352" s="2" t="inlineStr">
+        <is>
+          <t>extra-money.bonus-coin.subtitle</t>
+        </is>
+      </c>
+      <c r="B352" s="2" t="inlineStr">
+        <is>
+          <t>Watch a short video to earn free coin</t>
+        </is>
+      </c>
+      <c r="C352" s="2" t="inlineStr">
+        <is>
+          <t>Xem video ngắn để nhận xu miễn phí</t>
+        </is>
+      </c>
+    </row>
+    <row r="353" ht="18" customHeight="1">
+      <c r="A353" s="2" t="inlineStr">
+        <is>
+          <t>extra-money.bonus-coin.next-in</t>
+        </is>
+      </c>
+      <c r="B353" s="2" t="inlineStr">
+        <is>
+          <t>Next in:</t>
+        </is>
+      </c>
+      <c r="C353" s="2" t="inlineStr">
+        <is>
+          <t>Lượt kế tiếp:</t>
+        </is>
+      </c>
+    </row>
+    <row r="354" ht="17" customHeight="1">
+      <c r="A354" s="2" t="inlineStr">
+        <is>
+          <t>extra-money.bonus-coin.coin-unit</t>
+        </is>
+      </c>
+      <c r="B354" s="2" t="inlineStr">
+        <is>
+          <t>coin</t>
+        </is>
+      </c>
+      <c r="C354" s="2" t="inlineStr">
+        <is>
+          <t>xu</t>
+        </is>
+      </c>
+    </row>
+    <row r="355" ht="18" customHeight="1">
+      <c r="A355" s="2" t="inlineStr">
+        <is>
+          <t>extra-money.bonus-coin.watch-video</t>
+        </is>
+      </c>
+      <c r="B355" s="2" t="inlineStr">
+        <is>
+          <t>Watch video</t>
+        </is>
+      </c>
+      <c r="C355" s="2" t="inlineStr">
+        <is>
+          <t>Xem video</t>
+        </is>
+      </c>
+    </row>
+    <row r="356" ht="18" customHeight="1">
+      <c r="A356" s="2" t="inlineStr">
+        <is>
+          <t>extra-money.daily-bonus.subtitle</t>
+        </is>
+      </c>
+      <c r="B356" s="2" t="inlineStr">
+        <is>
+          <t>Login 7 days in a row to earn 4000 coin</t>
+        </is>
+      </c>
+      <c r="C356" s="2" t="inlineStr">
+        <is>
+          <t>Đăng nhập 7 ngày liên tiếp để nhận 4000 xu</t>
+        </is>
+      </c>
+    </row>
+    <row r="357" ht="18" customHeight="1">
+      <c r="A357" s="2" t="inlineStr">
+        <is>
+          <t>extra-money.daily-bonus.day</t>
+        </is>
+      </c>
+      <c r="B357" s="2" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="C357" s="2" t="inlineStr">
+        <is>
+          <t>Ngày</t>
+        </is>
+      </c>
+    </row>
+    <row r="358" ht="18" customHeight="1">
+      <c r="A358" s="2" t="inlineStr">
+        <is>
+          <t>profile.button.save</t>
+        </is>
+      </c>
+      <c r="B358" s="2" t="inlineStr">
+        <is>
+          <t>Save</t>
+        </is>
+      </c>
+      <c r="C358" s="2" t="inlineStr">
+        <is>
+          <t>Lưu</t>
+        </is>
+      </c>
+    </row>
+    <row r="359" ht="18" customHeight="1">
+      <c r="A359" s="2" t="inlineStr">
+        <is>
+          <t>profile.button.cancel</t>
+        </is>
+      </c>
+      <c r="B359" s="2" t="inlineStr">
+        <is>
+          <t>Cancel</t>
+        </is>
+      </c>
+      <c r="C359" s="2" t="inlineStr">
+        <is>
+          <t>Huỷ</t>
+        </is>
+      </c>
+    </row>
+    <row r="360" ht="18" customHeight="1">
+      <c r="A360" s="2" t="inlineStr"/>
+      <c r="B360" s="2" t="inlineStr"/>
+      <c r="C360" s="2" t="inlineStr"/>
+    </row>
+    <row r="361" ht="17" customHeight="1">
+      <c r="A361" s="2" t="inlineStr"/>
+      <c r="B361" s="2" t="inlineStr"/>
+      <c r="C361" s="2" t="inlineStr"/>
+    </row>
+    <row r="362" ht="17" customHeight="1">
+      <c r="A362" s="2" t="inlineStr"/>
+      <c r="B362" s="2" t="inlineStr"/>
+      <c r="C362" s="2" t="inlineStr"/>
+    </row>
+    <row r="363" ht="17" customHeight="1">
+      <c r="A363" s="2" t="inlineStr"/>
+      <c r="B363" s="2" t="inlineStr"/>
+      <c r="C363" s="2" t="inlineStr"/>
+    </row>
+    <row r="364" ht="17" customHeight="1">
+      <c r="A364" s="2" t="inlineStr"/>
+      <c r="B364" s="2" t="inlineStr"/>
+      <c r="C364" s="2" t="inlineStr"/>
+    </row>
+    <row r="365" ht="17" customHeight="1">
+      <c r="A365" s="2" t="inlineStr"/>
+      <c r="B365" s="2" t="inlineStr"/>
+      <c r="C365" s="2" t="inlineStr"/>
+    </row>
+    <row r="366" ht="17" customHeight="1">
+      <c r="A366" s="2" t="inlineStr"/>
+      <c r="B366" s="2" t="inlineStr"/>
+      <c r="C366" s="2" t="inlineStr"/>
+    </row>
+    <row r="367" ht="17" customHeight="1">
+      <c r="A367" s="2" t="inlineStr"/>
+      <c r="B367" s="2" t="inlineStr"/>
+      <c r="C367" s="2" t="inlineStr"/>
+    </row>
+    <row r="368" ht="17" customHeight="1">
+      <c r="A368" s="2" t="inlineStr"/>
+      <c r="B368" s="2" t="inlineStr"/>
+      <c r="C368" s="2" t="inlineStr"/>
+    </row>
+    <row r="369" ht="17" customHeight="1">
+      <c r="A369" s="2" t="inlineStr"/>
+      <c r="B369" s="2" t="inlineStr"/>
+      <c r="C369" s="2" t="inlineStr"/>
+    </row>
+    <row r="370" ht="17" customHeight="1">
+      <c r="A370" s="2" t="inlineStr"/>
+      <c r="B370" s="2" t="inlineStr"/>
+      <c r="C370" s="2" t="inlineStr"/>
+    </row>
+    <row r="371" ht="17" customHeight="1">
+      <c r="A371" s="2" t="inlineStr"/>
+      <c r="B371" s="2" t="inlineStr"/>
+      <c r="C371" s="2" t="inlineStr"/>
+    </row>
+    <row r="372" ht="17" customHeight="1">
+      <c r="A372" s="2" t="inlineStr"/>
+      <c r="B372" s="2" t="inlineStr"/>
+      <c r="C372" s="2" t="inlineStr"/>
+    </row>
+    <row r="373" ht="17" customHeight="1">
+      <c r="A373" s="2" t="inlineStr"/>
+      <c r="B373" s="2" t="inlineStr"/>
+      <c r="C373" s="2" t="inlineStr"/>
+    </row>
+    <row r="374" ht="17" customHeight="1">
+      <c r="A374" s="2" t="inlineStr"/>
+      <c r="B374" s="2" t="inlineStr"/>
+      <c r="C374" s="2" t="inlineStr"/>
+    </row>
+    <row r="375" ht="17" customHeight="1">
+      <c r="A375" s="2" t="inlineStr"/>
+      <c r="B375" s="2" t="inlineStr"/>
+      <c r="C375" s="2" t="inlineStr"/>
+    </row>
+    <row r="376" ht="17" customHeight="1">
+      <c r="A376" s="2" t="inlineStr"/>
+      <c r="B376" s="2" t="inlineStr"/>
+      <c r="C376" s="2" t="inlineStr"/>
+    </row>
+    <row r="377" ht="17" customHeight="1">
+      <c r="A377" s="2" t="inlineStr"/>
+      <c r="B377" s="2" t="inlineStr"/>
+      <c r="C377" s="2" t="inlineStr"/>
+    </row>
+    <row r="378" ht="17" customHeight="1">
+      <c r="A378" s="2" t="n"/>
+      <c r="B378" s="2" t="n"/>
+      <c r="C378" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tools/languages.xlsx
+++ b/tools/languages.xlsx
@@ -325,7 +325,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C378"/>
+  <dimension ref="A1:C430"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -744,3288 +744,3288 @@
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>menu.guide</t>
+          <t>menu.change-password</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Guide</t>
+          <t>Change password</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Luật chơi</t>
+          <t>Đổi mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>menu.announce</t>
+          <t>menu.guide</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Announcement</t>
+          <t>Guide</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Thông báo</t>
+          <t>Luật chơi</t>
         </is>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>menu.extra</t>
+          <t>menu.announce</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Daily tasks</t>
+          <t>Announcement</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Tác vụ thường nhật</t>
+          <t>Thông báo</t>
         </is>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>menu.setting.button</t>
+          <t>menu.extra</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Daily tasks</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Cài đặt</t>
+          <t>Kiếm tiền</t>
         </is>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>menu.app-name</t>
+          <t>menu.setting.button</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Xiangqi</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Cờ tướng</t>
+          <t>Cài đặt</t>
         </is>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>menu.home</t>
+          <t>menu.app-name</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Xiangqi</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Trang chủ</t>
+          <t>Cờ tướng</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>menu.expired</t>
+          <t>menu.home</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Set expired</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Hết hạn token</t>
+          <t>Trang chủ</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>menu.logout</t>
+          <t>menu.expired</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Logout</t>
+          <t>Set expired</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Đăng xuất</t>
+          <t>Hết hạn token</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>menu.rooms</t>
+          <t>menu.logout</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Rooms</t>
+          <t>Logout</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Trò chơi</t>
+          <t>Đăng xuất</t>
         </is>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>announce.title</t>
+          <t>menu.rooms</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Announcement</t>
+          <t>Rooms</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Thông báo</t>
+          <t>Trò chơi</t>
         </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>announce.placeholder</t>
+          <t>announce.title</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Type an announcement...</t>
+          <t>Announcement</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Nhập thông báo...</t>
+          <t>Thông báo</t>
         </is>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>announce.empty</t>
+          <t>announce.placeholder</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>No announcements yet</t>
+          <t>Type an announcement...</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Chưa có thông báo nào</t>
+          <t>Nhập thông báo...</t>
         </is>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>announce.loading-older</t>
+          <t>announce.empty</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Loading older announcements...</t>
+          <t>No announcements yet</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Đang tải thông báo cũ hơn...</t>
+          <t>Chưa có thông báo nào</t>
         </is>
       </c>
     </row>
     <row r="38" ht="36" customHeight="1">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>archivement.title-01</t>
+          <t>announce.loading-older</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Checkmate an opponent who still has 13 or more pieces</t>
+          <t>Loading older announcements...</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Chiếu bí khi đối thủ vẫn còn &gt;= 13 quân</t>
+          <t>Đang tải thông báo cũ hơn...</t>
         </is>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>archivement.title-02</t>
+          <t>archivement.title-01</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Win your first game</t>
+          <t>Checkmate an opponent who still has 13 or more pieces</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Thắng trận đầu khi chơi game</t>
+          <t>Chiếu bí khi đối thủ vẫn còn &gt;= 13 quân</t>
         </is>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>archivement.title-03</t>
+          <t>archivement.title-02</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Leave your opponent with no legal moves</t>
+          <t>Win your first game</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Đánh cho đối thủ không còn nước đi</t>
+          <t>Thắng trận đầu khi chơi game</t>
         </is>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>archivement.title-04</t>
+          <t>archivement.title-03</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Defeat opponents of equal or higher rank in 10 games</t>
+          <t>Leave your opponent with no legal moves</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Thắng đối thủ cùng hoặc hơn đẳng cấp 10 ván</t>
+          <t>Đánh cho đối thủ không còn nước đi</t>
         </is>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>archivement.title-05</t>
+          <t>archivement.title-04</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Hold a draw with only your king remaining</t>
+          <t>Defeat opponents of equal or higher rank in 10 games</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Cầm hoà đối thủ khi chỉ còn tướng</t>
+          <t>Thắng đối thủ cùng hoặc hơn đẳng cấp 10 ván</t>
         </is>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>archivement.title-06</t>
+          <t>archivement.title-05</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Win 100 games</t>
+          <t>Hold a draw with only your king remaining</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Thắng 100 trận</t>
+          <t>Cầm hoà đối thủ khi chỉ còn tướng</t>
         </is>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>archivement.title-07</t>
+          <t>archivement.title-06</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Draw 50 games</t>
+          <t>Win 100 games</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Hoà 50 trận</t>
+          <t>Thắng 100 trận</t>
         </is>
       </c>
     </row>
     <row r="45" ht="36" customHeight="1">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>archivement.title-08</t>
+          <t>archivement.title-07</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Checkmate an opponent with only 1 attacking piece remaining</t>
+          <t>Draw 50 games</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Chiếu bí khi đối thủ khi chỉ còn 1 quân tấn công</t>
+          <t>Hoà 50 trận</t>
         </is>
       </c>
     </row>
     <row r="46" ht="36" customHeight="1">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>archivement.title-09</t>
+          <t>archivement.title-08</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Checkmate an opponent with only a knight remaining</t>
+          <t>Checkmate an opponent with only 1 attacking piece remaining</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Chiếu bí khi đối thủ khi chỉ còn mã</t>
+          <t>Chiếu bí khi đối thủ khi chỉ còn 1 quân tấn công</t>
         </is>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>archivement.title-10</t>
+          <t>archivement.title-09</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Checkmate an opponent with only a pawn remaining</t>
+          <t>Checkmate an opponent with only a knight remaining</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Chiếu bí khi đối thủ khi chỉ còn tốt</t>
+          <t>Chiếu bí khi đối thủ khi chỉ còn mã</t>
         </is>
       </c>
     </row>
     <row r="48" ht="36" customHeight="1">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>archivement.title-11</t>
+          <t>archivement.title-10</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Checkmate an opponent with only a cannon remaining</t>
+          <t>Checkmate an opponent with only a pawn remaining</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Chiếu bí khi đối thủ khi chỉ còn pháo</t>
+          <t>Chiếu bí khi đối thủ khi chỉ còn tốt</t>
         </is>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>archivement.title-12</t>
+          <t>archivement.title-11</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Defeat opponents with master rank in 50 games</t>
+          <t>Checkmate an opponent with only a cannon remaining</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Thắng đối thủ có đẳng cấp kỳ thủ 50 ván</t>
+          <t>Chiếu bí khi đối thủ khi chỉ còn pháo</t>
         </is>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>chat.conversation.you</t>
+          <t>archivement.title-12</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>You</t>
+          <t>Defeat opponents with master rank in 50 games</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Bạn</t>
+          <t>Thắng đối thủ có đẳng cấp kỳ thủ 50 ván</t>
         </is>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>chat.conversation.new</t>
+          <t>chat.conversation.you</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>New conversation</t>
+          <t>You</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Cuộc trò chuyện mới</t>
+          <t>Bạn</t>
         </is>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>chat.messages.unread</t>
+          <t>chat.conversation.new</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Unread messages</t>
+          <t>New conversation</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Tin nhắn chưa đọc</t>
+          <t>Cuộc trò chuyện mới</t>
         </is>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>search.user.title</t>
+          <t>chat.messages.unread</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Search user</t>
+          <t>Unread messages</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Tìm kiếm</t>
+          <t>Tin nhắn chưa đọc</t>
         </is>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>search.user.placeholder</t>
+          <t>search.user.title</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Search user...</t>
+          <t>Search user</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Tìm kiếm người dùng...</t>
+          <t>Tìm kiếm</t>
         </is>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>search.user.no-results</t>
+          <t>search.user.placeholder</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>No users found</t>
+          <t>Search user...</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy người dùng</t>
+          <t>Tìm kiếm người dùng...</t>
         </is>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>search.button.search</t>
+          <t>search.user.no-results</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>No users found</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Tìm kiếm</t>
+          <t>Không tìm thấy người dùng</t>
         </is>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>dashboard.page.title</t>
+          <t>search.button.search</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Room list</t>
+          <t>Search</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Danh sách phòng</t>
+          <t>Tìm kiếm</t>
         </is>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>dashboard.filters.all</t>
+          <t>dashboard.page.title</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Room list</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Tất cả</t>
+          <t>Danh sách phòng</t>
         </is>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>dashboard.filters.available</t>
+          <t>dashboard.filters.all</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Available</t>
+          <t>All</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Chờ</t>
+          <t>Tất cả</t>
         </is>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>dashboard.filters.playing</t>
+          <t>dashboard.filters.available</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Playing</t>
+          <t>Available</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Đang chơi</t>
+          <t>Chờ</t>
         </is>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>dashboard.feedback.empty</t>
+          <t>dashboard.filters.playing</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>No room tables match the selected filter.</t>
+          <t>Playing</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Không có bàn chơi phù hợp với bộ lọc đã chọn.</t>
+          <t>Đang chơi</t>
         </is>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>dashboard.feedback.error</t>
+          <t>dashboard.feedback.empty</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Unable to load room tables.</t>
+          <t>No room tables match the selected filter.</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Không tải được danh sách phòng chơi.</t>
+          <t>Không có bàn chơi phù hợp với bộ lọc đã chọn.</t>
         </is>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>dashboard.status.unknown</t>
+          <t>dashboard.feedback.error</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Unable to load room tables.</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Không xác định</t>
+          <t>Không tải được danh sách phòng chơi.</t>
         </is>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>dashboard.feedback.result-count</t>
+          <t>dashboard.status.unknown</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Found {{count}} tables</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Tìm thấy {{count}} bàn chơi</t>
+          <t>Không xác định</t>
         </is>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>dashboard.room.create</t>
+          <t>dashboard.feedback.result-count</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Create room</t>
+          <t>Found {{count}} tables</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Tạo phòng chơi</t>
+          <t>Tìm thấy {{count}} bàn chơi</t>
         </is>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>dashboard.popup.piece-selection</t>
+          <t>dashboard.room.create</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Select team</t>
+          <t>Create room</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Chọn quân</t>
+          <t>Tạo phòng chơi</t>
         </is>
       </c>
     </row>
     <row r="67" ht="18" customHeight="1">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>dashboard.popup.red-first</t>
+          <t>dashboard.popup.piece-selection</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Red first</t>
+          <t>Select team</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Đỏ tiên</t>
+          <t>Chọn quân</t>
         </is>
       </c>
     </row>
     <row r="68" ht="18" customHeight="1">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>dashboard.popup.pve-mode</t>
+          <t>dashboard.popup.red-first</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>PVE mode</t>
+          <t>Red first</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Chơi với máy</t>
+          <t>Đỏ tiên</t>
         </is>
       </c>
     </row>
     <row r="69" ht="18" customHeight="1">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>dashboard.popup.bet-amount</t>
+          <t>dashboard.popup.pve-mode</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Bet amount</t>
+          <t>PVE mode</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Giá trị cược</t>
+          <t>Chơi với máy</t>
         </is>
       </c>
     </row>
     <row r="70" ht="18" customHeight="1">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>dashboard.popup.room-name-label</t>
+          <t>dashboard.popup.bet-amount</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Room table name</t>
+          <t>Bet amount</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Tên phòng chơi</t>
+          <t>Giá trị cược</t>
         </is>
       </c>
     </row>
     <row r="71" ht="18" customHeight="1">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>dashboard.popup.room-name-helptext</t>
+          <t>dashboard.popup.room-name-label</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>is required</t>
+          <t>Room table name</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>không được để trống</t>
+          <t>Tên phòng chơi</t>
         </is>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>dashboard.popup.play</t>
+          <t>dashboard.popup.room-name-helptext</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Play</t>
+          <t>is required</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Chơi</t>
+          <t>không được để trống</t>
         </is>
       </c>
     </row>
     <row r="73" ht="18" customHeight="1">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>dashboard.popup.view</t>
+          <t>dashboard.popup.play</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>View</t>
+          <t>Play</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>Xem</t>
+          <t>Chơi</t>
         </is>
       </c>
     </row>
     <row r="74" ht="18" customHeight="1">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>settings.header</t>
+          <t>dashboard.popup.view</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>View</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>Cài đặt</t>
+          <t>Xem</t>
         </is>
       </c>
     </row>
     <row r="75" ht="18" customHeight="1">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>settings.language</t>
+          <t>settings.header</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>Ngôn ngữ</t>
+          <t>Cài đặt</t>
         </is>
       </c>
     </row>
     <row r="76" ht="18" customHeight="1">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>settings.dark-mode</t>
+          <t>settings.language</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Dark mode</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>Chế độ tối</t>
+          <t>Ngôn ngữ</t>
         </is>
       </c>
     </row>
     <row r="77" ht="18" customHeight="1">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>settings.debug-mode</t>
+          <t>settings.dark-mode</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Debug mode</t>
+          <t>Dark mode</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Chế độ test</t>
+          <t>Chế độ tối</t>
         </is>
       </c>
     </row>
     <row r="78" ht="18" customHeight="1">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>settings.close</t>
+          <t>settings.debug-mode</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Close</t>
+          <t>Debug mode</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Đóng</t>
+          <t>Chế độ test</t>
         </is>
       </c>
     </row>
     <row r="79" ht="18" customHeight="1">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>settings.change-password</t>
+          <t>settings.connected-accounts.label</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Change password</t>
+          <t>Connected accounts</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Đổi mật khẩu</t>
+          <t>Tài khoản liên kết</t>
         </is>
       </c>
     </row>
     <row r="80" ht="18" customHeight="1">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>popup.alert.title</t>
+          <t>settings.connected-accounts.link-facebook</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Link Facebook</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Cảnh báo</t>
+          <t>Liên kết Facebook</t>
         </is>
       </c>
     </row>
     <row r="81" ht="18" customHeight="1">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>popup.confirm.title</t>
+          <t>settings.connected-accounts.unlink-facebook</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Confirm</t>
+          <t>Unlink Facebook</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Xác nhận</t>
+          <t>Huỷ liên kết Facebook</t>
         </is>
       </c>
     </row>
     <row r="82" ht="18" customHeight="1">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>popup.confirm.ok</t>
+          <t>settings.connected-accounts.link-success</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Ok</t>
+          <t>Facebook linked successfully</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Ok</t>
+          <t>Đã liên kết Facebook</t>
         </is>
       </c>
     </row>
     <row r="83" ht="18" customHeight="1">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>popup.confirm.cancel</t>
+          <t>settings.connected-accounts.unlink-success</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Facebook unlinked</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Huỷ</t>
+          <t>Đã huỷ liên kết Facebook</t>
         </is>
       </c>
     </row>
     <row r="84" ht="18" customHeight="1">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>home.turn.title</t>
+          <t>settings.connected-accounts.link-error</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Turn</t>
+          <t>Could not update Facebook link</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Lượt đánh</t>
+          <t>Không cập nhật được liên kết Facebook</t>
         </is>
       </c>
     </row>
     <row r="85" ht="18" customHeight="1">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>game.general.captured</t>
+          <t>settings.close</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>General has been captured. Room over</t>
+          <t>Close</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Tướng đã bị bắt. Game kết thúc</t>
+          <t>Đóng</t>
         </is>
       </c>
     </row>
     <row r="86" ht="18" customHeight="1">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>game.general.in-check</t>
+          <t>settings.change-password</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Your general is under attack</t>
+          <t>Change password</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Tướng của bạn đang bị chiếu</t>
+          <t>Đổi mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="87" ht="18" customHeight="1">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>room.bot-difficulty.title</t>
+          <t>popup.alert.title</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Select Bot Difficulty</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Chọn độ khó của Bot</t>
+          <t>Cảnh báo</t>
         </is>
       </c>
     </row>
     <row r="88" ht="18" customHeight="1">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>room.bot-difficulty.beginner</t>
+          <t>popup.confirm.title</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Beginner</t>
+          <t>Confirm</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Mới bắt đầu</t>
+          <t>Xác nhận</t>
         </is>
       </c>
     </row>
     <row r="89" ht="18" customHeight="1">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>room.bot-difficulty.amateur</t>
+          <t>popup.confirm.ok</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Amateur</t>
+          <t>Ok</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Nghiệp dư</t>
+          <t>Ok</t>
         </is>
       </c>
     </row>
     <row r="90" ht="18" customHeight="1">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>room.bot-difficulty.intermediate</t>
+          <t>popup.confirm.cancel</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Intermediate</t>
+          <t>Cancel</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Trung bình</t>
+          <t>Huỷ</t>
         </is>
       </c>
     </row>
     <row r="91" ht="18" customHeight="1">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>room.bot-difficulty.advanced</t>
+          <t>home.turn.title</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Advanced</t>
+          <t>Turn</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Nâng cao</t>
+          <t>Lượt đánh</t>
         </is>
       </c>
     </row>
     <row r="92" ht="18" customHeight="1">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>room.bot-difficulty.master</t>
+          <t>game.general.captured</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Master</t>
+          <t>General has been captured. Room over</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Lão luyện</t>
+          <t>Tướng đã bị bắt. Game kết thúc</t>
         </is>
       </c>
     </row>
     <row r="93" ht="18" customHeight="1">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>login.page.title</t>
+          <t>game.general.in-check</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Login</t>
+          <t>Your general is under attack</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập</t>
+          <t>Tướng của bạn đang bị chiếu</t>
         </is>
       </c>
     </row>
     <row r="94" ht="18" customHeight="1">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>login.form.title</t>
+          <t>room.bot-difficulty.title</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Login</t>
+          <t>Select Bot Difficulty</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập</t>
+          <t>Chọn độ khó của Bot</t>
         </is>
       </c>
     </row>
     <row r="95" ht="18" customHeight="1">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>login.username.label</t>
+          <t>room.bot-difficulty.beginner</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>User name</t>
+          <t>Beginner</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Tên người dùng</t>
+          <t>Mới bắt đầu</t>
         </is>
       </c>
     </row>
     <row r="96" ht="18" customHeight="1">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>login.username.placeholder</t>
+          <t>room.bot-difficulty.amateur</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>User name</t>
+          <t>Amateur</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Tên người dùng</t>
+          <t>Nghiệp dư</t>
         </is>
       </c>
     </row>
     <row r="97" ht="18" customHeight="1">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>login.password.label</t>
+          <t>room.bot-difficulty.intermediate</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Password</t>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Mật khẩu</t>
+          <t>Trung bình</t>
         </is>
       </c>
     </row>
     <row r="98" ht="18" customHeight="1">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>login.password.placeholder</t>
+          <t>room.bot-difficulty.advanced</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Password</t>
+          <t>Advanced</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Mật khẩu</t>
+          <t>Nâng cao</t>
         </is>
       </c>
     </row>
     <row r="99" ht="18" customHeight="1">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>login.password.error1</t>
+          <t>room.bot-difficulty.master</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Password is required</t>
+          <t>Master</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Mật khẩu bắt buộc nhập</t>
+          <t>Lão luyện</t>
         </is>
       </c>
     </row>
     <row r="100" ht="18" customHeight="1">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>login.password.show</t>
+          <t>login.page.title</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Show password</t>
+          <t>Login</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Hiện mật khẩu</t>
+          <t>Đăng nhập</t>
         </is>
       </c>
     </row>
     <row r="101" ht="18" customHeight="1">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>login.password.hide</t>
+          <t>login.form.title</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Hide password</t>
+          <t>Login</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Ẩn mật khẩu</t>
+          <t>Đăng nhập</t>
         </is>
       </c>
     </row>
     <row r="102" ht="18" customHeight="1">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>login.form.error1</t>
+          <t>login.username.label</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Login failed. Please check your credentials </t>
+          <t>User name</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập không thành công. Hãy kiểm tra lại</t>
+          <t>Tên người dùng</t>
         </is>
       </c>
     </row>
     <row r="103" ht="18" customHeight="1">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>login.form.forgot-password</t>
+          <t>login.username.placeholder</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Forgot password</t>
+          <t>User name</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Quên mật khẩu</t>
+          <t>Tên người dùng</t>
         </is>
       </c>
     </row>
     <row r="104" ht="18" customHeight="1">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>login.form.register</t>
+          <t>login.password.label</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Register</t>
+          <t>Password</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Đăng ký</t>
+          <t>Mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="105" ht="18" customHeight="1">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>login.form.submit</t>
+          <t>login.password.placeholder</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Login</t>
+          <t>Password</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập</t>
+          <t>Mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="106" ht="18" customHeight="1">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>notfound.title</t>
+          <t>login.password.error1</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Page Not Found</t>
+          <t>Password is required</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Trang không tìm thấy</t>
+          <t>Mật khẩu bắt buộc nhập</t>
         </is>
       </c>
     </row>
     <row r="107" ht="36" customHeight="1">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>notfound.description</t>
+          <t>login.password.show</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>The page you are looking for does not exist or has been moved.</t>
+          <t>Show password</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Trang bạn tìm kiếm không tồn tại hoặc đã được di chuyển.</t>
+          <t>Hiện mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="108" ht="18" customHeight="1">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>notfound.home</t>
+          <t>login.password.hide</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Go to Home</t>
+          <t>Hide password</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Về trang chủ</t>
+          <t>Ẩn mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="109" ht="18" customHeight="1">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>notfound.back</t>
+          <t>login.form.error1</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Go Back</t>
+          <t xml:space="preserve">Login failed. Please check your credentials </t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Quay lại</t>
+          <t>Đăng nhập không thành công. Hãy kiểm tra lại</t>
         </is>
       </c>
     </row>
     <row r="110" ht="18" customHeight="1">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>register.confirm-password.error1</t>
+          <t>login.form.forgot-password</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Confirm password does not match password</t>
+          <t>Forgot password</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Mật khẩu xác nhận không khớp với mật khẩu</t>
+          <t>Quên mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="111" ht="18" customHeight="1">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>register.confirm-password.label</t>
+          <t>login.form.register</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Confirm Password</t>
+          <t>Register</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Xác nhận mật khẩu</t>
+          <t>Đăng ký</t>
         </is>
       </c>
     </row>
     <row r="112" ht="18" customHeight="1">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>register.confirm-password.placeholder</t>
+          <t>login.form.submit</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Confirm Password</t>
+          <t>Login</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Xác nhận mật khẩu</t>
+          <t>Đăng nhập</t>
         </is>
       </c>
     </row>
     <row r="113" ht="18" customHeight="1">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>register.display-name.label</t>
+          <t>login.form.or</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Display name</t>
+          <t>or</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Tên hiển thị</t>
+          <t>hoặc</t>
         </is>
       </c>
     </row>
     <row r="114" ht="18" customHeight="1">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>register.display-name.placeholder</t>
+          <t>login.google.load-error</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Display name</t>
+          <t>Could not load Google Sign-In</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Tên hiển thị</t>
+          <t>Không tải được đăng nhập Google</t>
         </is>
       </c>
     </row>
     <row r="115" ht="18" customHeight="1">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>register.email.error1</t>
+          <t>login.facebook.button</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Invalid email format</t>
+          <t>Sign-in with Facebook</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Định dạng email không hợp lệ</t>
+          <t>Đăng nhập với Facebook</t>
         </is>
       </c>
     </row>
     <row r="116" ht="18" customHeight="1">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>register.email.label</t>
+          <t>login.messages.incorrect-login</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Invalid username or password</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Tên người dùng hoặc mật khẩu không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="117" ht="18" customHeight="1">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>register.email.placeholder</t>
+          <t>login.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="118" ht="18" customHeight="1">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>register.form.login</t>
+          <t>login.messages.missing-credentials</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Back to login</t>
+          <t>Username and password are required</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Về trang đăng nhập</t>
+          <t>Tên người dùng và mật khẩu là bắt buộc</t>
         </is>
       </c>
     </row>
     <row r="119" ht="18" customHeight="1">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>register.form.submit</t>
+          <t>login.messages.success</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Register</t>
+          <t>Login successful</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Đăng ký</t>
+          <t>Đăng nhập thành công</t>
         </is>
       </c>
     </row>
     <row r="120" ht="18" customHeight="1">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>register.form.success</t>
+          <t>notfound.title</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Registration successful. Redirecting to login...</t>
+          <t>Page Not Found</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Đăng ký thành công. Đang chuyển hướng...</t>
+          <t>Trang không tìm thấy</t>
         </is>
       </c>
     </row>
     <row r="121" ht="18" customHeight="1">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>register.form.title</t>
+          <t>notfound.description</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Register</t>
+          <t>The page you are looking for does not exist or has been moved.</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Đăng ký</t>
+          <t>Trang bạn tìm kiếm không tồn tại hoặc đã được di chuyển.</t>
         </is>
       </c>
     </row>
     <row r="122" ht="18" customHeight="1">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>register.gender.female</t>
+          <t>notfound.home</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Go to Home</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Nữ</t>
+          <t>Về trang chủ</t>
         </is>
       </c>
     </row>
     <row r="123" ht="18" customHeight="1">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>register.gender.label</t>
+          <t>notfound.back</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>Gender</t>
+          <t>Go Back</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>Giới tính</t>
+          <t>Quay lại</t>
         </is>
       </c>
     </row>
     <row r="124" ht="18" customHeight="1">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>register.gender.male</t>
+          <t>register.confirm-password.error1</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Confirm password does not match password</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Nam</t>
+          <t>Mật khẩu xác nhận không khớp với mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="125" ht="18" customHeight="1">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>register.gender.select</t>
+          <t>register.confirm-password.label</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>Select gender</t>
+          <t>Confirm Password</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Chọn giới tính</t>
+          <t>Xác nhận mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="126" ht="18" customHeight="1">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>register.page.title</t>
+          <t>register.confirm-password.placeholder</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Register</t>
+          <t>Confirm Password</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Đăng ký</t>
+          <t>Xác nhận mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="127" ht="36" customHeight="1">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>register.password.error1</t>
+          <t>register.display-name.label</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>Password must be at least 8 characters and contain uppercase, lowercase, number, and special character</t>
+          <t>Display name</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Mật khẩu phải có ít nhất 8 ký tự và chứa chữ hoa, chữ thường, số và ký tự đặc biệt</t>
+          <t>Tên hiển thị</t>
         </is>
       </c>
     </row>
     <row r="128" ht="18" customHeight="1">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>register.password.hide</t>
+          <t>register.display-name.placeholder</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Hide password</t>
+          <t>Display name</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Ẩn mật khẩu</t>
+          <t>Tên hiển thị</t>
         </is>
       </c>
     </row>
     <row r="129" ht="18" customHeight="1">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>register.password.label</t>
+          <t>register.email.error1</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>Password</t>
+          <t>Invalid email format</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Mật khẩu</t>
+          <t>Định dạng email không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="130" ht="18" customHeight="1">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>register.password.placeholder</t>
+          <t>register.email.label</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Password</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Mật khẩu</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="131" ht="18" customHeight="1">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>register.password.show</t>
+          <t>register.email.placeholder</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>Show password</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>Hiện mật khẩu</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="132" ht="36" customHeight="1">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>register.username.error1</t>
+          <t>register.form.login</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>User name must contain only alphanumeric characters, underscore, and dot</t>
+          <t>Back to login</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Tên người dùng chỉ chứa ký tự chữ số, dấu gạch dưới và dấu chấm</t>
+          <t>Về trang đăng nhập</t>
         </is>
       </c>
     </row>
     <row r="133" ht="18" customHeight="1">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>register.username.label</t>
+          <t>register.form.submit</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>User name</t>
+          <t>Register</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>Tên người dùng</t>
+          <t>Đăng ký</t>
         </is>
       </c>
     </row>
     <row r="134" ht="18" customHeight="1">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>register.username.placeholder</t>
+          <t>register.form.success</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>User name</t>
+          <t>Registration successful. Redirecting to login...</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Tên người dùng</t>
+          <t>Đăng ký thành công. Đang chuyển hướng...</t>
         </is>
       </c>
     </row>
     <row r="135" ht="18" customHeight="1">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.page.title</t>
+          <t>register.form.title</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>Forgot Password</t>
+          <t>Register</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>Quên mật khẩu</t>
+          <t>Đăng ký</t>
         </is>
       </c>
     </row>
     <row r="136" ht="18" customHeight="1">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.form.title</t>
+          <t>register.gender.female</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Forgot Password</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Quên mật khẩu</t>
+          <t>Nữ</t>
         </is>
       </c>
     </row>
     <row r="137" ht="18" customHeight="1">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.form.login</t>
+          <t>register.gender.label</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>Back to login</t>
+          <t>Gender</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>Về trang đăng nhập</t>
+          <t>Giới tính</t>
         </is>
       </c>
     </row>
     <row r="138" ht="18" customHeight="1">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.form.submit</t>
+          <t>register.gender.male</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Forgot password</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Quên mật khẩu</t>
+          <t>Nam</t>
         </is>
       </c>
     </row>
     <row r="139" ht="36" customHeight="1">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.form.success</t>
+          <t>register.gender.select</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>Check your email for reset password details.</t>
+          <t>Select gender</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>Hãy kiểm tra email để xem thông tin đặt lại mật khẩu.</t>
+          <t>Chọn giới tính</t>
         </is>
       </c>
     </row>
     <row r="140" ht="18" customHeight="1">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.form.error1</t>
+          <t>register.page.title</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Forgot password failed.</t>
+          <t>Register</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Quên mật khẩu không thành công.</t>
+          <t>Đăng ký</t>
         </is>
       </c>
     </row>
     <row r="141" ht="18" customHeight="1">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>reset-password.page.title</t>
+          <t>register.password.error1</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>Reset Password</t>
+          <t>Password must be at least 8 characters and contain uppercase, lowercase, number, and special character</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>Đặt lại mật khẩu</t>
+          <t>Mật khẩu phải có ít nhất 8 ký tự và chứa chữ hoa, chữ thường, số và ký tự đặc biệt</t>
         </is>
       </c>
     </row>
     <row r="142" ht="18" customHeight="1">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>reset-password.form.title</t>
+          <t>register.password.hide</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Reset your password</t>
+          <t>Hide password</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Đặt lại mật khẩu của bạn</t>
+          <t>Ẩn mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="143" ht="18" customHeight="1">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>reset-password.form.submit</t>
+          <t>register.password.label</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>Reset Password</t>
+          <t>Password</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>Đặt lại mật khẩu</t>
+          <t>Mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="144" ht="36" customHeight="1">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>reset-password.form.error1</t>
+          <t>register.password.placeholder</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>An error occurred while resetting your password. Please try again.</t>
+          <t>Password</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Có lỗi xảy ra khi đặt lại mật khẩu. Vui lòng thử lại.</t>
+          <t>Mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="145" ht="18" customHeight="1">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>reset-password.form.invalid-token</t>
+          <t>register.password.show</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>Invalid or expired reset password token</t>
+          <t>Show password</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>Token đặt lại mật khẩu không hợp lệ hoặc đã hết hạn</t>
+          <t>Hiện mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="146" ht="36" customHeight="1">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>reset-password.form.success</t>
+          <t>register.username.error1</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Password reset successfully. Redirecting to login...</t>
+          <t>User name must contain only alphanumeric characters, underscore, and dot</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Đặt lại mật khẩu thành công. Đang chuyển hướng đến đăng nhập...</t>
+          <t>Tên người dùng chỉ chứa ký tự chữ số, dấu gạch dưới và dấu chấm</t>
         </is>
       </c>
     </row>
     <row r="147" ht="18" customHeight="1">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>reset-password.action.back-to-login</t>
+          <t>register.username.label</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>Back to login</t>
+          <t>User name</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Quay lại trang chủ</t>
+          <t>Tên người dùng</t>
         </is>
       </c>
     </row>
     <row r="148" ht="18" customHeight="1">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>reset-password.action.submit</t>
+          <t>register.username.placeholder</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Reset password</t>
+          <t>User name</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Đặt lại mật khẩu</t>
+          <t>Tên người dùng</t>
         </is>
       </c>
     </row>
     <row r="149" ht="18" customHeight="1">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>auth-middleware.messages.invalid-token-payload</t>
+          <t>forgot-password.page.title</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>Invalid token payload</t>
+          <t>Forgot Password</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>Payload của token không hợp lệ</t>
+          <t>Quên mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="150" ht="18" customHeight="1">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>auth-middleware.messages.session-not-found</t>
+          <t>forgot-password.form.title</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Session not found</t>
+          <t>Forgot Password</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy phiên</t>
+          <t>Quên mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="151" ht="18" customHeight="1">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>auth-middleware.messages.token-expired</t>
+          <t>forgot-password.form.login</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>Token is expired</t>
+          <t>Back to login</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>Token đã hết hạn</t>
+          <t>Về trang đăng nhập</t>
         </is>
       </c>
     </row>
     <row r="152" ht="18" customHeight="1">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>auth-middleware.messages.token-invalid</t>
+          <t>forgot-password.form.submit</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Token is invalid</t>
+          <t>Forgot password</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>Token không hợp lệ</t>
+          <t>Quên mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="153" ht="18" customHeight="1">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>auth-middleware.messages.token-required</t>
+          <t>forgot-password.form.success</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>Token not provided</t>
+          <t>Check your email for reset password details.</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>Token không được cung cấp</t>
+          <t>Hãy kiểm tra email để xem thông tin đặt lại mật khẩu.</t>
         </is>
       </c>
     </row>
     <row r="154" ht="18" customHeight="1">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>auth-middleware.messages.token-subject-mismatch</t>
+          <t>forgot-password.form.error1</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>Token subject mismatch</t>
+          <t>Forgot password failed.</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>Token chủ đề không khớp</t>
+          <t>Quên mật khẩu không thành công.</t>
         </is>
       </c>
     </row>
     <row r="155" ht="18" customHeight="1">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>auth-middleware.messages.token-validation-failed</t>
+          <t>reset-password.page.title</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>Token validation failed</t>
+          <t>Reset Password</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>Xác thực token không thành công</t>
+          <t>Đặt lại mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="156" ht="36" customHeight="1">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.insufficient-amount</t>
+          <t>reset-password.form.title</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>You do not have enough balance to create a room with this bet</t>
+          <t>Reset your password</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Bạn không còn đủ amount để tạo phòng với mức cược này</t>
+          <t>Đặt lại mật khẩu của bạn</t>
         </is>
       </c>
     </row>
     <row r="157" ht="18" customHeight="1">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.internal-server-error</t>
+          <t>reset-password.form.submit</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>Internal server error while creating room</t>
+          <t>Reset Password</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ khi tạo phòng</t>
+          <t>Đặt lại mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="158" ht="36" customHeight="1">
       <c r="A158" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.invalid-bet-amount</t>
+          <t>reset-password.form.error1</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>Bet amount is required and must be one of the acceptable values</t>
+          <t>An error occurred while resetting your password. Please try again.</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>Số tiền cược là bắt buộc và phải là một trong các giá trị được chấp nhận</t>
+          <t>Có lỗi xảy ra khi đặt lại mật khẩu. Vui lòng thử lại.</t>
         </is>
       </c>
     </row>
     <row r="159" ht="18" customHeight="1">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.invalid-redFirst</t>
+          <t>reset-password.form.invalid-token</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>'redFirst' must be a boolean</t>
+          <t>Invalid or expired reset password token</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>'redFirst' phải là giá trị boolean</t>
+          <t>Token đặt lại mật khẩu không hợp lệ hoặc đã hết hạn</t>
         </is>
       </c>
     </row>
     <row r="160" ht="18" customHeight="1">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.invalid-team-name</t>
+          <t>reset-password.form.success</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>Team name must be either 'red', 'black', or null</t>
+          <t>Password reset successfully. Redirecting to login...</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Tên đội phải là 'red', 'black' hoặc null</t>
+          <t>Đặt lại mật khẩu thành công. Đang chuyển hướng đến đăng nhập...</t>
         </is>
       </c>
     </row>
     <row r="161" ht="36" customHeight="1">
       <c r="A161" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.name-required</t>
+          <t>reset-password.action.back-to-login</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>Room name (tableName) is required and must not be empty</t>
+          <t>Back to login</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>Tên phòng (tableName) là bắt buộc và không được để trống</t>
+          <t>Quay lại trang chủ</t>
         </is>
       </c>
     </row>
     <row r="162" ht="18" customHeight="1">
       <c r="A162" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.room-created</t>
+          <t>reset-password.action.submit</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>Room created successfully</t>
+          <t>Reset password</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Phòng được tạo thành công</t>
+          <t>Đặt lại mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="163" ht="18" customHeight="1">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t>fetch-rooms.messages.internal-server-error</t>
+          <t>auth-middleware.messages.invalid-token-payload</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Invalid token payload</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Payload của token không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="164" ht="18" customHeight="1">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t>fetch-rooms.messages.invalid-status</t>
+          <t>auth-middleware.messages.session-not-found</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>Query parameter 'status' must be an integer</t>
+          <t>Session not found</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Tham số truy vấn 'status' phải là số nguyên</t>
+          <t>Không tìm thấy phiên</t>
         </is>
       </c>
     </row>
     <row r="165" ht="18" customHeight="1">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t>fetch-rooms.messages.success</t>
+          <t>auth-middleware.messages.token-expired</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>Fetch rooms successfully</t>
+          <t>Token is expired</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>Lấy phòng thành công</t>
+          <t>Token đã hết hạn</t>
         </is>
       </c>
     </row>
     <row r="166" ht="18" customHeight="1">
       <c r="A166" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.messages.email-not-found</t>
+          <t>auth-middleware.messages.token-invalid</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>Email does not exist</t>
+          <t>Token is invalid</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>Email không tồn tại</t>
+          <t>Token không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="167" ht="18" customHeight="1">
       <c r="A167" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.messages.email-service-not-configured</t>
+          <t>auth-middleware.messages.token-required</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>Email service is not configured</t>
+          <t>Token not provided</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>Dịch vụ email chưa được cấu hình</t>
+          <t>Token không được cung cấp</t>
         </is>
       </c>
     </row>
     <row r="168" ht="18" customHeight="1">
       <c r="A168" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.messages.internal-server-error</t>
+          <t>auth-middleware.messages.token-subject-mismatch</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Token subject mismatch</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Token chủ đề không khớp</t>
         </is>
       </c>
     </row>
     <row r="169" ht="18" customHeight="1">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.messages.invalid-email-format</t>
+          <t>auth-middleware.messages.token-validation-failed</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>Invalid email format</t>
+          <t>Token validation failed</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>Định dạng email không hợp lệ</t>
+          <t>Xác thực token không thành công</t>
         </is>
       </c>
     </row>
     <row r="170" ht="18" customHeight="1">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.messages.missing-email</t>
+          <t>create-room.messages.insufficient-amount</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>Email is required</t>
+          <t>You do not have enough balance to create a room with this bet</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>Email là bắt buộc</t>
+          <t>Bạn không còn đủ amount để tạo phòng với mức cược này</t>
         </is>
       </c>
     </row>
     <row r="171" ht="18" customHeight="1">
       <c r="A171" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.messages.success</t>
+          <t>create-room.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>Forgot password email sent</t>
+          <t>Internal server error while creating room</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>Email đặt lại mật khẩu đã được gửi</t>
+          <t>Lỗi máy chủ nội bộ khi tạo phòng</t>
         </is>
       </c>
     </row>
     <row r="172" ht="18" customHeight="1">
       <c r="A172" s="1" t="inlineStr">
         <is>
-          <t>join-room.messages.internal-server-error</t>
+          <t>create-room.messages.invalid-bet-amount</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Bet amount is required and must be one of the acceptable values</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Số tiền cược là bắt buộc và phải là một trong các giá trị được chấp nhận</t>
         </is>
       </c>
     </row>
     <row r="173" ht="36" customHeight="1">
       <c r="A173" s="1" t="inlineStr">
         <is>
-          <t>join-room.messages.invalid-team</t>
+          <t>create-room.messages.invalid-redFirst</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>Field 'team' must be 'red', 'black', null, or undefined</t>
+          <t>'redFirst' must be a boolean</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>Trường 'team' phải là 'red', 'black', null hoặc không truyền</t>
+          <t>'redFirst' phải là giá trị boolean</t>
         </is>
       </c>
     </row>
     <row r="174" ht="18" customHeight="1">
       <c r="A174" s="1" t="inlineStr">
         <is>
-          <t>join-room.messages.invalid-room-id</t>
+          <t>create-room.messages.invalid-team-name</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>Field 'id' is required and must be a positive integer</t>
+          <t>Team name must be either 'red', 'black', or null</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
+          <t>Tên đội phải là 'red', 'black' hoặc null</t>
         </is>
       </c>
     </row>
     <row r="175" ht="18" customHeight="1">
       <c r="A175" s="1" t="inlineStr">
         <is>
-          <t>join-room.messages.room-not-found</t>
+          <t>create-room.messages.name-required</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>Room not found</t>
+          <t>Room name (tableName) is required and must not be empty</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy phòng</t>
+          <t>Tên phòng (tableName) là bắt buộc và không được để trống</t>
         </is>
       </c>
     </row>
     <row r="176" ht="18" customHeight="1">
       <c r="A176" s="1" t="inlineStr">
         <is>
-          <t>join-room.messages.success</t>
+          <t>create-room.messages.room-created</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>Successfully joined the room</t>
+          <t>Room created successfully</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>Tham gia phòng thành công</t>
+          <t>Phòng được tạo thành công</t>
         </is>
       </c>
     </row>
     <row r="177" ht="18" customHeight="1">
       <c r="A177" s="1" t="inlineStr">
         <is>
-          <t>join-room.messages.team-seat-occupied</t>
+          <t>fetch-rooms.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>Selected team seat is already occupied</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>Vị trí đội đã chọn đã có người chơi</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="178" ht="18" customHeight="1">
       <c r="A178" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.cannot-kick-self</t>
+          <t>fetch-rooms.messages.invalid-status</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>You cannot kick yourself</t>
+          <t>Query parameter 'status' must be an integer</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>Bạn không thể kick chính mình</t>
+          <t>Tham số truy vấn 'status' phải là số nguyên</t>
         </is>
       </c>
     </row>
     <row r="179" ht="18" customHeight="1">
       <c r="A179" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.forbidden</t>
+          <t>fetch-rooms.messages.success</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>Only the host can kick users</t>
+          <t>Fetch rooms successfully</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>Chỉ chủ phòng mới có thể kick người dùng</t>
+          <t>Lấy phòng thành công</t>
         </is>
       </c>
     </row>
     <row r="180" ht="18" customHeight="1">
       <c r="A180" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.internal-server-error</t>
+          <t>forgot-password.messages.email-not-found</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Email does not exist</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Email không tồn tại</t>
         </is>
       </c>
     </row>
     <row r="181" ht="18" customHeight="1">
       <c r="A181" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.invalid-room-id</t>
+          <t>forgot-password.messages.email-service-not-configured</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>Field 'id' is required and must be a positive integer</t>
+          <t>Email service is not configured</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
+          <t>Dịch vụ email chưa được cấu hình</t>
         </is>
       </c>
     </row>
     <row r="182" ht="36" customHeight="1">
       <c r="A182" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.invalid-user-id</t>
+          <t>forgot-password.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>Field 'userId' is required and must be a positive integer</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>Trường 'userId' là bắt buộc và phải là số nguyên dương</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="183" ht="18" customHeight="1">
       <c r="A183" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.room-not-found</t>
+          <t>forgot-password.messages.invalid-email-format</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>Room not found</t>
+          <t>Invalid email format</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy phòng</t>
+          <t>Định dạng email không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="184" ht="36" customHeight="1">
       <c r="A184" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.room-not-waiting</t>
+          <t>forgot-password.messages.missing-email</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>You can only kick users while the room is waiting</t>
+          <t>Email is required</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>Chỉ có thể kick người dùng khi phòng đang ở trạng thái chờ</t>
+          <t>Email là bắt buộc</t>
         </is>
       </c>
     </row>
     <row r="185" ht="18" customHeight="1">
       <c r="A185" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.success</t>
+          <t>forgot-password.messages.success</t>
         </is>
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>User has been kicked</t>
+          <t>Forgot password email sent</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>Người dùng đã bị kick</t>
+          <t>Email đặt lại mật khẩu đã được gửi</t>
         </is>
       </c>
     </row>
     <row r="186" ht="18" customHeight="1">
       <c r="A186" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.user-not-in-room</t>
+          <t>join-room.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>User is not in this room</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>Người dùng không trong phòng này</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="187" ht="18" customHeight="1">
       <c r="A187" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.you-were-kicked</t>
+          <t>join-room.messages.invalid-team</t>
         </is>
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>You have been removed from the room by the host</t>
+          <t>Field 'team' must be 'red', 'black', null, or undefined</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>Bạn đã bị chủ phòng đưa ra khỏi phòng</t>
+          <t>Trường 'team' phải là 'red', 'black', null hoặc không truyền</t>
         </is>
       </c>
     </row>
     <row r="188" ht="18" customHeight="1">
       <c r="A188" s="1" t="inlineStr">
         <is>
-          <t>leave-room.messages.internal-server-error</t>
+          <t>join-room.messages.invalid-room-id</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Field 'id' is required and must be a positive integer</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
         </is>
       </c>
     </row>
     <row r="189" ht="18" customHeight="1">
       <c r="A189" s="1" t="inlineStr">
         <is>
-          <t>leave-room.messages.invalid-room-id</t>
+          <t>join-room.messages.room-not-found</t>
         </is>
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>Field 'id' is required and must be a positive integer</t>
+          <t>Room not found</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
+          <t>Không tìm thấy phòng</t>
         </is>
       </c>
     </row>
     <row r="190" ht="18" customHeight="1">
       <c r="A190" s="1" t="inlineStr">
         <is>
-          <t>leave-room.messages.player-not-in-room</t>
+          <t>join-room.messages.success</t>
         </is>
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>Player is not in this room</t>
+          <t>Successfully joined the room</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>Người chơi không trong phòng này</t>
+          <t>Tham gia phòng thành công</t>
         </is>
       </c>
     </row>
     <row r="191" ht="18" customHeight="1">
       <c r="A191" s="1" t="inlineStr">
         <is>
-          <t>leave-room.messages.success</t>
+          <t>join-room.messages.team-seat-occupied</t>
         </is>
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>Leave room successfully</t>
+          <t>Selected team seat is already occupied</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>Rời phòng thành công</t>
+          <t>Vị trí đội đã chọn đã có người chơi</t>
         </is>
       </c>
     </row>
     <row r="192" ht="18" customHeight="1">
       <c r="A192" s="1" t="inlineStr">
         <is>
-          <t>load-room.messages.internal-server-error</t>
+          <t>kick-user.messages.cannot-kick-self</t>
         </is>
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>You cannot kick yourself</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Bạn không thể kick chính mình</t>
         </is>
       </c>
     </row>
     <row r="193" ht="18" customHeight="1">
       <c r="A193" s="1" t="inlineStr">
         <is>
-          <t>load-room.messages.invalid-room-id</t>
+          <t>kick-user.messages.forbidden</t>
         </is>
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>Room ID must be a positive integer</t>
+          <t>Only the host can kick users</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>ID phòng phải là số nguyên dương</t>
+          <t>Chỉ chủ phòng mới có thể kick người dùng</t>
         </is>
       </c>
     </row>
     <row r="194" ht="18" customHeight="1">
       <c r="A194" s="1" t="inlineStr">
         <is>
-          <t>load-room.messages.room-not-found</t>
+          <t>kick-user.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>Room not found</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy phòng</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="195" ht="18" customHeight="1">
       <c r="A195" s="1" t="inlineStr">
         <is>
-          <t>load-room.messages.success</t>
+          <t>kick-user.messages.invalid-room-id</t>
         </is>
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>Load room successfully</t>
+          <t>Field 'id' is required and must be a positive integer</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>Tải phòng thành công</t>
+          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
         </is>
       </c>
     </row>
     <row r="196" ht="18" customHeight="1">
       <c r="A196" s="1" t="inlineStr">
         <is>
-          <t>login.messages.incorrect-login</t>
+          <t>kick-user.messages.invalid-user-id</t>
         </is>
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>Invalid username or password</t>
+          <t>Field 'userId' is required and must be a positive integer</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>Tên người dùng hoặc mật khẩu không hợp lệ</t>
+          <t>Trường 'userId' là bắt buộc và phải là số nguyên dương</t>
         </is>
       </c>
     </row>
     <row r="197" ht="18" customHeight="1">
       <c r="A197" s="1" t="inlineStr">
         <is>
-          <t>login.messages.internal-server-error</t>
+          <t>kick-user.messages.room-not-found</t>
         </is>
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Room not found</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Không tìm thấy phòng</t>
         </is>
       </c>
     </row>
     <row r="198" ht="18" customHeight="1">
       <c r="A198" s="1" t="inlineStr">
         <is>
-          <t>login.messages.missing-credentials</t>
+          <t>kick-user.messages.room-not-waiting</t>
         </is>
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>Username and password are required</t>
+          <t>You can only kick users while the room is waiting</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>Tên người dùng và mật khẩu là bắt buộc</t>
+          <t>Chỉ có thể kick người dùng khi phòng đang ở trạng thái chờ</t>
         </is>
       </c>
     </row>
     <row r="199" ht="18" customHeight="1">
       <c r="A199" s="1" t="inlineStr">
         <is>
-          <t>login.messages.success</t>
+          <t>kick-user.messages.success</t>
         </is>
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>Login successful</t>
+          <t>User has been kicked</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập thành công</t>
+          <t>Người dùng đã bị kick</t>
         </is>
       </c>
     </row>
     <row r="200" ht="18" customHeight="1">
       <c r="A200" s="1" t="inlineStr">
         <is>
-          <t>logout.messages.already-inactive</t>
+          <t>kick-user.messages.user-not-in-room</t>
         </is>
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>Session already inactive</t>
+          <t>User is not in this room</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>Phiên đã ngưng hoạt động</t>
+          <t>Người dùng không trong phòng này</t>
         </is>
       </c>
     </row>
     <row r="201" ht="18" customHeight="1">
       <c r="A201" s="1" t="inlineStr">
         <is>
-          <t>logout.messages.internal-server-error</t>
+          <t>kick-user.messages.you-were-kicked</t>
         </is>
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>You have been removed from the room by the host</t>
         </is>
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Bạn đã bị chủ phòng đưa ra khỏi phòng</t>
         </is>
       </c>
     </row>
     <row r="202" ht="18" customHeight="1">
       <c r="A202" s="1" t="inlineStr">
         <is>
-          <t>logout.messages.success</t>
+          <t>leave-room.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>Logout successful</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>Đăng xuất thành công</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="203" ht="18" customHeight="1">
       <c r="A203" s="1" t="inlineStr">
         <is>
-          <t>refresh-token.messages.missing-refresh-token</t>
+          <t>leave-room.messages.invalid-room-id</t>
         </is>
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>Missing refresh token cookie</t>
+          <t>Field 'id' is required and must be a positive integer</t>
         </is>
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>Thiếu cookie token làm mới</t>
+          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
         </is>
       </c>
     </row>
     <row r="204" ht="18" customHeight="1">
       <c r="A204" s="1" t="inlineStr">
         <is>
-          <t>refresh-token.messages.mismatch-or-expired</t>
+          <t>leave-room.messages.player-not-in-room</t>
         </is>
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>Refresh token mismatch or expired</t>
+          <t>Player is not in this room</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>Thiếu refresh token hoặc đã hết hạn</t>
+          <t>Người chơi không trong phòng này</t>
         </is>
       </c>
     </row>
     <row r="205" ht="18" customHeight="1">
       <c r="A205" s="1" t="inlineStr">
         <is>
-          <t>refresh-token.messages.success</t>
+          <t>leave-room.messages.success</t>
         </is>
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>Token refreshed</t>
+          <t>Leave room successfully</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>Token đã làm mới</t>
+          <t>Rời phòng thành công</t>
         </is>
       </c>
     </row>
     <row r="206" ht="18" customHeight="1">
       <c r="A206" s="1" t="inlineStr">
         <is>
-          <t>register.messages.email-exists</t>
+          <t>load-room.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>Email already exists</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>Email đã tồn tại</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="207" ht="18" customHeight="1">
       <c r="A207" s="1" t="inlineStr">
         <is>
-          <t>register.messages.internal-server-error</t>
+          <t>load-room.messages.invalid-room-id</t>
         </is>
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Room ID must be a positive integer</t>
         </is>
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>ID phòng phải là số nguyên dương</t>
         </is>
       </c>
     </row>
     <row r="208" ht="36" customHeight="1">
       <c r="A208" s="1" t="inlineStr">
         <is>
-          <t>register.messages.missing-fields</t>
+          <t>load-room.messages.room-not-found</t>
         </is>
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>Username, password, gender, displayName and email are required</t>
+          <t>Room not found</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>Tên người dùng, mật khẩu, giới tính, tên hiển thị và email là bắt buộc</t>
+          <t>Không tìm thấy phòng</t>
         </is>
       </c>
     </row>
     <row r="209" ht="18" customHeight="1">
       <c r="A209" s="1" t="inlineStr">
         <is>
-          <t>register.messages.success</t>
+          <t>load-room.messages.success</t>
         </is>
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>User created successfully</t>
+          <t>Load room successfully</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>Người dùng được tạo thành công</t>
+          <t>Tải phòng thành công</t>
         </is>
       </c>
     </row>
     <row r="210" ht="18" customHeight="1">
       <c r="A210" s="1" t="inlineStr">
         <is>
-          <t>register.messages.username-exists</t>
+          <t>google-login.messages.email-not-verified</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>Username already exists</t>
+          <t>Your Google email is not verified</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>Tên người dùng đã tồn tại</t>
+          <t>Email Google của bạn chưa được xác minh</t>
         </is>
       </c>
     </row>
     <row r="211" ht="18" customHeight="1">
       <c r="A211" s="1" t="inlineStr">
         <is>
-          <t>reset-password.messages.internal-server-error</t>
+          <t>google-login.messages.failed</t>
         </is>
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Login failed</t>
         </is>
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Đăng nhập không thành công</t>
         </is>
       </c>
     </row>
     <row r="212" ht="18" customHeight="1">
       <c r="A212" s="1" t="inlineStr">
         <is>
-          <t>reset-password.messages.invalid-or-expired-token</t>
+          <t>google-login.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>Invalid or expired reset password token</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>Token đặt lại mật khẩu không hợp lệ hoặc đã hết hạn</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="213" ht="18" customHeight="1">
       <c r="A213" s="1" t="inlineStr">
         <is>
-          <t>reset-password.messages.invalid-user-id</t>
+          <t>google-login.messages.invalid-token</t>
         </is>
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>Invalid user id</t>
+          <t>Invalid Google credential</t>
         </is>
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>ID người dùng không hợp lệ</t>
+          <t>Thông tin đăng nhập Google không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="214" ht="18" customHeight="1">
       <c r="A214" s="1" t="inlineStr">
         <is>
-          <t>reset-password.messages.missing-id-or-token</t>
+          <t>google-login.messages.missing-credential</t>
         </is>
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>ID and token are required</t>
+          <t>Google credential is required</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>ID và token là bắt buộc</t>
+          <t>Thiếu thông tin đăng nhập Google</t>
         </is>
       </c>
     </row>
     <row r="215" ht="18" customHeight="1">
       <c r="A215" s="1" t="inlineStr">
         <is>
-          <t>reset-password.messages.missing-userId-or-password</t>
+          <t>facebook-login.messages.missing-token</t>
         </is>
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>UserId and password are required</t>
+          <t>Facebook token is required</t>
         </is>
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>UserId và mật khẩu là bắt buộc</t>
+          <t>Thiếu thông tin đăng nhập Facebook</t>
         </is>
       </c>
     </row>
     <row r="216" ht="18" customHeight="1">
       <c r="A216" s="1" t="inlineStr">
         <is>
-          <t>reset-password.messages.token-valid</t>
+          <t>facebook-login.messages.invalid-token</t>
         </is>
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>Reset password token is valid</t>
+          <t>Invalid Facebook token</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>Token đặt lại mật khẩu hợp lệ</t>
+          <t>Thông tin đăng nhập Facebook không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="217" ht="18" customHeight="1">
       <c r="A217" s="1" t="inlineStr">
         <is>
-          <t>reset-password.messages.user-not-found</t>
+          <t>facebook-login.messages.not-linked</t>
         </is>
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>User not found</t>
+          <t>This Facebook account is not linked. Log in another way and link it in Settings</t>
         </is>
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy người dùng</t>
+          <t>Tài khoản Facebook này chưa được liên kết. Hãy đăng nhập cách khác rồi liên kết trong Cài đặt</t>
         </is>
       </c>
     </row>
     <row r="218" ht="18" customHeight="1">
       <c r="A218" s="1" t="inlineStr">
         <is>
-          <t>set-room-status.messages.internal-server-error</t>
+          <t>facebook-login.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B218" s="2" t="inlineStr">
@@ -4042,2494 +4042,3378 @@
     <row r="219" ht="18" customHeight="1">
       <c r="A219" s="1" t="inlineStr">
         <is>
-          <t>set-room-status.messages.invalid-room-id</t>
+          <t>facebook-link.messages.missing-token</t>
         </is>
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>Field 'id' is required and must be a positive integer</t>
+          <t>Facebook token is required</t>
         </is>
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
+          <t>Thiếu thông tin đăng nhập Facebook</t>
         </is>
       </c>
     </row>
     <row r="220" ht="18" customHeight="1">
       <c r="A220" s="1" t="inlineStr">
         <is>
-          <t>set-room-status.messages.invalid-status</t>
+          <t>facebook-link.messages.invalid-token</t>
         </is>
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>Field 'status' must be either 1 or 2</t>
+          <t>Invalid Facebook token</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>Trường 'status' phải là 1 hoặc 2</t>
+          <t>Thông tin đăng nhập Facebook không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="221" ht="18" customHeight="1">
       <c r="A221" s="1" t="inlineStr">
         <is>
-          <t>set-room-status.messages.room-not-found</t>
+          <t>facebook-link.messages.linked</t>
         </is>
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>Room not found</t>
+          <t>Facebook linked successfully</t>
         </is>
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy phòng</t>
+          <t>Đã liên kết Facebook</t>
         </is>
       </c>
     </row>
     <row r="222" ht="18" customHeight="1">
       <c r="A222" s="1" t="inlineStr">
         <is>
-          <t>set-room-status.messages.success</t>
+          <t>facebook-link.messages.already-linked</t>
         </is>
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>Set room status successfully</t>
+          <t>This Facebook account is already linked to your account</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>Đặt trạng thái phòng thành công</t>
+          <t>Tài khoản Facebook này đã được liên kết với bạn</t>
         </is>
       </c>
     </row>
     <row r="223" ht="18" customHeight="1">
       <c r="A223" s="1" t="inlineStr">
         <is>
-          <t>room.actions.start-room</t>
+          <t>facebook-link.messages.linked-to-other</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>Start room</t>
+          <t>This Facebook account is already linked to another account</t>
         </is>
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>Bắt đầu chơi</t>
+          <t>Tài khoản Facebook này đã được liên kết với tài khoản khác</t>
         </is>
       </c>
     </row>
     <row r="224" ht="18" customHeight="1">
       <c r="A224" s="1" t="inlineStr">
         <is>
-          <t>room.actions.challenge</t>
+          <t>facebook-link.messages.already-has-facebook</t>
         </is>
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>Challenge</t>
+          <t>You already linked a different Facebook account</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>Thách đấu</t>
+          <t>Bạn đã liên kết một tài khoản Facebook khác</t>
         </is>
       </c>
     </row>
     <row r="225" ht="18" customHeight="1">
       <c r="A225" s="1" t="inlineStr">
         <is>
-          <t>room.actions.leave-seat</t>
+          <t>facebook-link.messages.unlinked</t>
         </is>
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>Leave seat</t>
+          <t>Facebook unlinked</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>Dự khán</t>
+          <t>Đã huỷ liên kết Facebook</t>
         </is>
       </c>
     </row>
     <row r="226" ht="18" customHeight="1">
       <c r="A226" s="1" t="inlineStr">
         <is>
-          <t>room.actions.undo</t>
+          <t>facebook-link.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>Undo</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>Hoán tác</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="227" ht="18" customHeight="1">
       <c r="A227" s="1" t="inlineStr">
         <is>
-          <t>room.actions.surrender</t>
+          <t>logout.messages.already-inactive</t>
         </is>
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>Surrender</t>
+          <t>Session already inactive</t>
         </is>
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>Đầu hàng</t>
+          <t>Phiên đã ngưng hoạt động</t>
         </is>
       </c>
     </row>
     <row r="228" ht="18" customHeight="1">
       <c r="A228" s="1" t="inlineStr">
         <is>
-          <t>room.actions.draw</t>
+          <t>logout.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>Draw</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>Hòa</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="229" ht="18" customHeight="1">
       <c r="A229" s="1" t="inlineStr">
         <is>
-          <t>room.actions.back-home</t>
+          <t>logout.messages.success</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>Back to home</t>
+          <t>Logout successful</t>
         </is>
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>Thoát phòng</t>
+          <t>Đăng xuất thành công</t>
         </is>
       </c>
     </row>
     <row r="230" ht="18" customHeight="1">
       <c r="A230" s="1" t="inlineStr">
         <is>
-          <t>room.actions.flip-board</t>
+          <t>refresh-token.messages.missing-refresh-token</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>Flip board</t>
+          <t>Missing refresh token cookie</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>Đảo chiều bàn cờ</t>
+          <t>Thiếu cookie token làm mới</t>
         </is>
       </c>
     </row>
     <row r="231" ht="18" customHeight="1">
       <c r="A231" s="1" t="inlineStr">
         <is>
-          <t>room.actions.accept-draw</t>
+          <t>refresh-token.messages.mismatch-or-expired</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>Accept</t>
+          <t>Refresh token mismatch or expired</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>Chấp nhận</t>
+          <t>Thiếu refresh token hoặc đã hết hạn</t>
         </is>
       </c>
     </row>
     <row r="232" ht="18" customHeight="1">
       <c r="A232" s="1" t="inlineStr">
         <is>
-          <t>room.actions.reject-draw</t>
+          <t>refresh-token.messages.success</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>Reject</t>
+          <t>Token refreshed</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>Từ chối</t>
+          <t>Token đã làm mới</t>
         </is>
       </c>
     </row>
     <row r="233" ht="18" customHeight="1">
       <c r="A233" s="1" t="inlineStr">
         <is>
-          <t>room.actions.send-pm</t>
+          <t>register.messages.email-exists</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>Send PM</t>
+          <t>Email already exists</t>
         </is>
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>Chat</t>
+          <t>Email đã tồn tại</t>
         </is>
       </c>
     </row>
     <row r="234" ht="18" customHeight="1">
       <c r="A234" s="1" t="inlineStr">
         <is>
-          <t>room.actions.view-history</t>
+          <t>register.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>History</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>Lịch sử</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="235" ht="18" customHeight="1">
       <c r="A235" s="1" t="inlineStr">
         <is>
-          <t>room.actions.kick</t>
+          <t>register.messages.missing-fields</t>
         </is>
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>Kick</t>
+          <t>Username, password, gender, displayName and email are required</t>
         </is>
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>Kick</t>
+          <t>Tên người dùng, mật khẩu, giới tính, tên hiển thị và email là bắt buộc</t>
         </is>
       </c>
     </row>
     <row r="236" ht="18" customHeight="1">
       <c r="A236" s="1" t="inlineStr">
         <is>
-          <t>room.actions.settings</t>
+          <t>register.messages.success</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>Room settings</t>
+          <t>User created successfully</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>Cài đặt phòng</t>
+          <t>Người dùng được tạo thành công</t>
         </is>
       </c>
     </row>
     <row r="237" ht="18" customHeight="1">
       <c r="A237" s="1" t="inlineStr">
         <is>
-          <t>room.messages.draw-accepted</t>
+          <t>register.messages.username-exists</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>Opponent accepted the draw</t>
+          <t>Username already exists</t>
         </is>
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>Đối phương đã đồng ý hòa</t>
+          <t>Tên người dùng đã tồn tại</t>
         </is>
       </c>
     </row>
     <row r="238" ht="18" customHeight="1">
       <c r="A238" s="1" t="inlineStr">
         <is>
-          <t>room.messages.draw-rejected</t>
+          <t>reset-password.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>Opponent rejected the draw</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>Đối phương từ chối hòa</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="239" ht="18" customHeight="1">
       <c r="A239" s="1" t="inlineStr">
         <is>
-          <t>room.messages.draw-completed</t>
+          <t>reset-password.messages.invalid-or-expired-token</t>
         </is>
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>Draw completed</t>
+          <t>Invalid or expired reset password token</t>
         </is>
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>Hòa cờ thành công</t>
+          <t>Token đặt lại mật khẩu không hợp lệ hoặc đã hết hạn</t>
         </is>
       </c>
     </row>
     <row r="240" ht="18" customHeight="1">
       <c r="A240" s="1" t="inlineStr">
         <is>
-          <t>room.messages.opponent-surrendered</t>
+          <t>reset-password.messages.invalid-user-id</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>Opponent surrendered! You won!</t>
+          <t>Invalid user id</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>Đối phương đã đầu hàng! Bạn thắng!</t>
+          <t>ID người dùng không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="241" ht="18" customHeight="1">
       <c r="A241" s="1" t="inlineStr">
         <is>
-          <t>room.messages.confirm-leave</t>
+          <t>reset-password.messages.missing-id-or-token</t>
         </is>
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>Are you sure you want to leave room?</t>
+          <t>ID and token are required</t>
         </is>
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>Bạn có chắc muốn rời bàn chơi?</t>
+          <t>ID và token là bắt buộc</t>
         </is>
       </c>
     </row>
     <row r="242" ht="18" customHeight="1">
       <c r="A242" s="1" t="inlineStr">
         <is>
-          <t>room.messages.confirm-surrender</t>
+          <t>reset-password.messages.missing-userId-or-password</t>
         </is>
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>Are you sure you want to surrender?</t>
+          <t>UserId and password are required</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>Bạn có chắc chắn muốn đầu hàng không?</t>
+          <t>UserId và mật khẩu là bắt buộc</t>
         </is>
       </c>
     </row>
     <row r="243" ht="18" customHeight="1">
       <c r="A243" s="1" t="inlineStr">
         <is>
-          <t>room.messages.confirm-draw</t>
+          <t>reset-password.messages.token-valid</t>
         </is>
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>Are you sure you want to draw?</t>
+          <t>Reset password token is valid</t>
         </is>
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>Bạn có chắc chắn muốn hòa không?</t>
+          <t>Token đặt lại mật khẩu hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="244" ht="18" customHeight="1">
       <c r="A244" s="1" t="inlineStr">
         <is>
-          <t>room.messages.confirm-accept-draw</t>
+          <t>reset-password.messages.user-not-found</t>
         </is>
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>Opponent has proposed a draw. Do you accept?</t>
+          <t>User not found</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>Đối phương đã chủ hòa, bạn có đồng ý không?</t>
+          <t>Không tìm thấy người dùng</t>
         </is>
       </c>
     </row>
     <row r="245" ht="18" customHeight="1">
       <c r="A245" s="1" t="inlineStr">
         <is>
-          <t>room.messages.insufficient-amount</t>
+          <t>set-room-status.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>You do not have enough balance to join this room</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>Bạn không đủ tiền để tham gia bàn chơi này</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="246" ht="18" customHeight="1">
       <c r="A246" s="1" t="inlineStr">
         <is>
-          <t>room.messages.all-seats-occupied</t>
+          <t>set-room-status.messages.invalid-room-id</t>
         </is>
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>All player seats are occupied</t>
+          <t>Field 'id' is required and must be a positive integer</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>Tất cả ghế chơi đã được chiếm</t>
+          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
         </is>
       </c>
     </row>
     <row r="247" ht="18" customHeight="1">
       <c r="A247" s="1" t="inlineStr">
         <is>
-          <t>room.notifications.joined</t>
+          <t>set-room-status.messages.invalid-status</t>
         </is>
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>{0} joined the room</t>
+          <t>Field 'status' must be either 1 or 2</t>
         </is>
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>{0} đã vào phòng</t>
+          <t>Trường 'status' phải là 1 hoặc 2</t>
         </is>
       </c>
     </row>
     <row r="248" ht="18" customHeight="1">
       <c r="A248" s="1" t="inlineStr">
         <is>
-          <t>room.notifications.left</t>
+          <t>set-room-status.messages.room-not-found</t>
         </is>
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>{0} left the room</t>
+          <t>Room not found</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>{0} đã rời phòng</t>
+          <t>Không tìm thấy phòng</t>
         </is>
       </c>
     </row>
     <row r="249" ht="18" customHeight="1">
       <c r="A249" s="1" t="inlineStr">
         <is>
-          <t>room.settings.title</t>
+          <t>set-room-status.messages.success</t>
         </is>
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>Room Settings</t>
+          <t>Set room status successfully</t>
         </is>
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>Cài đặt phòng</t>
+          <t>Đặt trạng thái phòng thành công</t>
         </is>
       </c>
     </row>
     <row r="250" ht="18" customHeight="1">
       <c r="A250" s="1" t="inlineStr">
         <is>
-          <t>room.settings.room-name</t>
+          <t>room.actions.start-room</t>
         </is>
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>Room name</t>
+          <t>Start room</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>Tên phòng</t>
+          <t>Bắt đầu chơi</t>
         </is>
       </c>
     </row>
     <row r="251" ht="18" customHeight="1">
       <c r="A251" s="1" t="inlineStr">
         <is>
-          <t>room.settings.players</t>
+          <t>room.actions.challenge</t>
         </is>
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t>Spectators</t>
+          <t>Challenge</t>
         </is>
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>Người xem</t>
+          <t>Thách đấu</t>
         </is>
       </c>
     </row>
     <row r="252" ht="18" customHeight="1">
       <c r="A252" s="1" t="inlineStr">
         <is>
-          <t>room.settings.save</t>
+          <t>room.actions.leave-seat</t>
         </is>
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>Save</t>
+          <t>Leave seat</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>Lưu</t>
+          <t>Dự khán</t>
         </is>
       </c>
     </row>
     <row r="253" ht="18" customHeight="1">
       <c r="A253" s="1" t="inlineStr">
         <is>
-          <t>room-invite.messages.title</t>
+          <t>room.actions.undo</t>
         </is>
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>Room Invitation</t>
+          <t>Undo</t>
         </is>
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>Lời mời vào phòng</t>
+          <t>Hoán tác</t>
         </is>
       </c>
     </row>
     <row r="254" ht="18" customHeight="1">
       <c r="A254" s="1" t="inlineStr">
         <is>
-          <t>start-game.messages.success</t>
+          <t>room.actions.surrender</t>
         </is>
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>Game started successfully</t>
+          <t>Surrender</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>Bắt đầu trò chơi thành công</t>
+          <t>Đầu hàng</t>
         </is>
       </c>
     </row>
     <row r="255" ht="18" customHeight="1">
       <c r="A255" s="1" t="inlineStr">
         <is>
-          <t>start-game.messages.internal-server-error</t>
+          <t>room.actions.draw</t>
         </is>
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>Internal server error while starting game</t>
+          <t>Draw</t>
         </is>
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ khi bắt đầu trò chơi</t>
+          <t>Hòa</t>
         </is>
       </c>
     </row>
     <row r="256" ht="18" customHeight="1">
       <c r="A256" s="1" t="inlineStr">
         <is>
-          <t>start-game.messages.invalid-room-id</t>
+          <t>room.actions.back-home</t>
         </is>
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>Field 'id' is required and must be a positive integer</t>
+          <t>Back to home</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
+          <t>Thoát phòng</t>
         </is>
       </c>
     </row>
     <row r="257" ht="36" customHeight="1">
       <c r="A257" s="1" t="inlineStr">
         <is>
-          <t>start-game.messages.invalid-difficulty</t>
+          <t>room.actions.flip-board</t>
         </is>
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>Bot difficulty must be between 1 and 5</t>
+          <t>Flip board</t>
         </is>
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>Độ khó của bot phải từ 1 đến 5</t>
+          <t>Đảo chiều bàn cờ</t>
         </is>
       </c>
     </row>
     <row r="258" ht="36" customHeight="1">
       <c r="A258" s="1" t="inlineStr">
         <is>
-          <t>start-game.messages.room-not-found</t>
+          <t>room.actions.accept-draw</t>
         </is>
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>Room not found</t>
+          <t>Accept</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy phòng</t>
+          <t>Chấp nhận</t>
         </is>
       </c>
     </row>
     <row r="259" ht="18" customHeight="1">
       <c r="A259" s="1" t="inlineStr">
         <is>
-          <t>start-game.messages.forbidden</t>
+          <t>room.actions.reject-draw</t>
         </is>
       </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
-          <t>Only the room host can start the game</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>Chỉ chủ phòng mới có thể bắt đầu trò chơi</t>
+          <t>Từ chối</t>
         </is>
       </c>
     </row>
     <row r="260" ht="18" customHeight="1">
       <c r="A260" s="1" t="inlineStr">
         <is>
-          <t>start-game.messages.insufficient-amount</t>
+          <t>room.actions.send-pm</t>
         </is>
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>You do not have enough balance to start a game with this bet</t>
+          <t>Send PM</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>Bạn không còn đủ amount để start room</t>
+          <t>Chat</t>
         </is>
       </c>
     </row>
     <row r="261" ht="18" customHeight="1">
       <c r="A261" s="1" t="inlineStr">
         <is>
-          <t>start-game.messages.requester-must-pick-team</t>
+          <t>room.actions.view-history</t>
         </is>
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>You must select a team before starting a game with bot</t>
+          <t>History</t>
         </is>
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>Bạn phải chọn team trước khi bắt đầu trò chơi với bot</t>
+          <t>Lịch sử</t>
         </is>
       </c>
     </row>
     <row r="262" ht="17" customHeight="1">
       <c r="A262" s="1" t="inlineStr">
         <is>
-          <t>update-room.messages.success</t>
+          <t>room.actions.kick</t>
         </is>
       </c>
       <c r="B262" s="1" t="inlineStr">
         <is>
-          <t>Room updated successfully</t>
+          <t>Kick</t>
         </is>
       </c>
       <c r="C262" s="1" t="inlineStr">
         <is>
-          <t>Cập nhật phòng thành công</t>
+          <t>Kick</t>
         </is>
       </c>
     </row>
     <row r="263" ht="18" customHeight="1">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>update-room.messages.internal-server-error</t>
+          <t>room.actions.settings</t>
         </is>
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Room settings</t>
         </is>
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Cài đặt phòng</t>
         </is>
       </c>
     </row>
     <row r="264" ht="18" customHeight="1">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>update-room.messages.invalid-room-id</t>
+          <t>room.messages.draw-accepted</t>
         </is>
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>Invalid room ID</t>
+          <t>Opponent accepted the draw</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>ID phòng không hợp lệ</t>
+          <t>Đối phương đã đồng ý hòa</t>
         </is>
       </c>
     </row>
     <row r="265" ht="18" customHeight="1">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>update-room.messages.name-required</t>
+          <t>room.messages.draw-rejected</t>
         </is>
       </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
-          <t>Room name is required</t>
+          <t>Opponent rejected the draw</t>
         </is>
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t>Tên phòng không được để trống</t>
+          <t>Đối phương từ chối hòa</t>
         </is>
       </c>
     </row>
     <row r="266" ht="18" customHeight="1">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>update-room.messages.room-not-found</t>
+          <t>room.messages.draw-completed</t>
         </is>
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>Room not found</t>
+          <t>Draw completed</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy phòng</t>
+          <t>Hòa cờ thành công</t>
         </is>
       </c>
     </row>
     <row r="267" ht="18" customHeight="1">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>update-room.messages.forbidden</t>
+          <t>room.messages.opponent-surrendered</t>
         </is>
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>You are not the host of this room</t>
+          <t>Opponent surrendered! You won!</t>
         </is>
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>Bạn không phải chủ phòng</t>
+          <t>Đối phương đã đầu hàng! Bạn thắng!</t>
         </is>
       </c>
     </row>
     <row r="268" ht="36" customHeight="1">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>draw-game.messages.invalid-game-id</t>
+          <t>room.messages.confirm-leave</t>
         </is>
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>Invalid game ID</t>
+          <t>Are you sure you want to leave room?</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>ID trò chơi không hợp lệ</t>
+          <t>Bạn có chắc muốn rời bàn chơi?</t>
         </is>
       </c>
     </row>
     <row r="269" ht="36" customHeight="1">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>draw-game.messages.game-not-found</t>
+          <t>room.messages.confirm-surrender</t>
         </is>
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>Game not found</t>
+          <t>Are you sure you want to surrender?</t>
         </is>
       </c>
       <c r="C269" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy trò chơi</t>
+          <t>Bạn có chắc chắn muốn đầu hàng không?</t>
         </is>
       </c>
     </row>
     <row r="270" ht="18" customHeight="1">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>draw-game.messages.forbidden</t>
+          <t>room.messages.confirm-draw</t>
         </is>
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>You are not in this room</t>
+          <t>Are you sure you want to draw?</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>Bạn không có trong phòng này</t>
+          <t>Bạn có chắc chắn muốn hòa không?</t>
         </is>
       </c>
     </row>
     <row r="271" ht="18" customHeight="1">
       <c r="A271" s="1" t="inlineStr">
         <is>
-          <t>draw-game.messages.game-history-not-found</t>
+          <t>room.messages.confirm-accept-draw</t>
         </is>
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>Game history not found</t>
+          <t>Opponent has proposed a draw. Do you accept?</t>
         </is>
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy lịch sử trò chơi</t>
+          <t>Đối phương đã chủ hòa, bạn có đồng ý không?</t>
         </is>
       </c>
     </row>
     <row r="272" ht="18" customHeight="1">
       <c r="A272" s="1" t="inlineStr">
         <is>
-          <t>draw-game.messages.game-already-finished</t>
+          <t>room.messages.insufficient-amount</t>
         </is>
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>Game is already finished</t>
+          <t>You do not have enough balance to join this room</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>Trò chơi đã kết thúc</t>
+          <t>Bạn không đủ tiền để tham gia bàn chơi này</t>
         </is>
       </c>
     </row>
     <row r="273" ht="18" customHeight="1">
       <c r="A273" s="1" t="inlineStr">
         <is>
-          <t>draw-game.messages.success</t>
+          <t>room.messages.will-leave-current-room</t>
         </is>
       </c>
       <c r="B273" s="2" t="inlineStr">
         <is>
-          <t>Draw game successfully</t>
+          <t>You are currently in another room. Joining this room will remove you from the current room</t>
         </is>
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>Hòa cờ thành công</t>
+          <t>Bạn đang ở trong một phòng khác. Tham gia phòng này sẽ loại bạn ra khỏi phòng hiện tại</t>
         </is>
       </c>
     </row>
     <row r="274" ht="18" customHeight="1">
       <c r="A274" s="1" t="inlineStr">
         <is>
-          <t>draw-game.messages.internal-server-error</t>
+          <t>room.messages.all-seats-occupied</t>
         </is>
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>All player seats are occupied</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Tất cả ghế chơi đã được chiếm</t>
         </is>
       </c>
     </row>
     <row r="275" ht="18" customHeight="1">
       <c r="A275" s="1" t="inlineStr">
         <is>
-          <t>surrender.messages.game-already-finished</t>
+          <t>room.notifications.joined</t>
         </is>
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>Game is already finished</t>
+          <t>{0} joined the room</t>
         </is>
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>Trò chơi đã kết thúc</t>
+          <t>{0} đã vào phòng</t>
         </is>
       </c>
     </row>
     <row r="276" ht="18" customHeight="1">
       <c r="A276" s="1" t="inlineStr">
         <is>
-          <t>surrender.messages.game-history-not-found</t>
+          <t>room.notifications.left</t>
         </is>
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>Game history not found</t>
+          <t>{0} left the room</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy lịch sử trò chơi</t>
+          <t>{0} đã rời phòng</t>
         </is>
       </c>
     </row>
     <row r="277" ht="18" customHeight="1">
       <c r="A277" s="1" t="inlineStr">
         <is>
-          <t>surrender.messages.game-not-found</t>
+          <t>room.settings.title</t>
         </is>
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>Game not found</t>
+          <t>Room Settings</t>
         </is>
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy trò chơi</t>
+          <t>Cài đặt phòng</t>
         </is>
       </c>
     </row>
     <row r="278" ht="18" customHeight="1">
       <c r="A278" s="1" t="inlineStr">
         <is>
-          <t>surrender.messages.internal-server-error</t>
+          <t>room.settings.room-name</t>
         </is>
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Room name</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Tên phòng</t>
         </is>
       </c>
     </row>
     <row r="279" ht="18" customHeight="1">
       <c r="A279" s="1" t="inlineStr">
         <is>
-          <t>surrender.messages.invalid-game-id</t>
+          <t>room.settings.players</t>
         </is>
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>Invalid game ID</t>
+          <t>Spectators</t>
         </is>
       </c>
       <c r="C279" s="2" t="inlineStr">
         <is>
-          <t>ID trò chơi không hợp lệ</t>
+          <t>Người xem</t>
         </is>
       </c>
     </row>
     <row r="280" ht="18" customHeight="1">
       <c r="A280" s="1" t="inlineStr">
         <is>
-          <t>surrender.messages.invalid-surrender-player</t>
+          <t>room.settings.save</t>
         </is>
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>You are not a player in this game</t>
+          <t>Save</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>Bạn không phải là người chơi trong trò chơi này</t>
+          <t>Lưu</t>
         </is>
       </c>
     </row>
     <row r="281" ht="18" customHeight="1">
       <c r="A281" s="1" t="inlineStr">
         <is>
-          <t>surrender.messages.opponent-not-found</t>
+          <t>room-invite.messages.title</t>
         </is>
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>Opponent not found</t>
+          <t>Room Invitation</t>
         </is>
       </c>
       <c r="C281" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy đối thủ</t>
+          <t>Lời mời vào phòng</t>
         </is>
       </c>
     </row>
     <row r="282" ht="18" customHeight="1">
       <c r="A282" s="1" t="inlineStr">
         <is>
-          <t>surrender.messages.success</t>
+          <t>start-game.messages.success</t>
         </is>
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>Surrendered</t>
+          <t>Game started successfully</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>Đã đầu hàng</t>
+          <t>Bắt đầu trò chơi thành công</t>
         </is>
       </c>
     </row>
     <row r="283" ht="18" customHeight="1">
       <c r="A283" s="1" t="inlineStr">
         <is>
-          <t>undo.messages.invalid-game-id</t>
+          <t>start-game.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>Invalid game ID</t>
+          <t>Internal server error while starting game</t>
         </is>
       </c>
       <c r="C283" s="2" t="inlineStr">
         <is>
-          <t>ID trò chơi không hợp lệ</t>
+          <t>Lỗi máy chủ nội bộ khi bắt đầu trò chơi</t>
         </is>
       </c>
     </row>
     <row r="284" ht="18" customHeight="1">
       <c r="A284" s="1" t="inlineStr">
         <is>
-          <t>undo.messages.unauthorized</t>
+          <t>start-game.messages.invalid-room-id</t>
         </is>
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>Unauthorized</t>
+          <t>Field 'id' is required and must be a positive integer</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>Không được phép truy cập</t>
+          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
         </is>
       </c>
     </row>
     <row r="285" ht="18" customHeight="1">
       <c r="A285" s="1" t="inlineStr">
         <is>
-          <t>undo.messages.game-not-found</t>
+          <t>start-game.messages.invalid-difficulty</t>
         </is>
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>Game not found</t>
+          <t>Bot difficulty must be between 1 and 5</t>
         </is>
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy trò chơi</t>
+          <t>Độ khó của bot phải từ 1 đến 5</t>
         </is>
       </c>
     </row>
     <row r="286" ht="18" customHeight="1">
       <c r="A286" s="1" t="inlineStr">
         <is>
-          <t>undo.messages.not-in-game</t>
+          <t>start-game.messages.room-not-found</t>
         </is>
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>You are not part of this game</t>
+          <t>Room not found</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>Bạn không phải là người chơi trong trò chơi này</t>
+          <t>Không tìm thấy phòng</t>
         </is>
       </c>
     </row>
     <row r="287" ht="18" customHeight="1">
       <c r="A287" s="1" t="inlineStr">
         <is>
-          <t>undo.messages.not-in-room</t>
+          <t>start-game.messages.forbidden</t>
         </is>
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>You are not in this room</t>
+          <t>Only the room host can start the game</t>
         </is>
       </c>
       <c r="C287" s="2" t="inlineStr">
         <is>
-          <t>Bạn không trong phòng này</t>
+          <t>Chỉ chủ phòng mới có thể bắt đầu trò chơi</t>
         </is>
       </c>
     </row>
     <row r="288" ht="18" customHeight="1">
       <c r="A288" s="1" t="inlineStr">
         <is>
-          <t>undo.messages.spectator-cannot-undo</t>
+          <t>start-game.messages.insufficient-amount</t>
         </is>
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>Spectators cannot undo moves</t>
+          <t>You do not have enough balance to start a game with this bet</t>
         </is>
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>Người xem không thể hoàn tác nước đi</t>
+          <t>Bạn không còn đủ amount để start room</t>
         </is>
       </c>
     </row>
     <row r="289" ht="18" customHeight="1">
       <c r="A289" s="1" t="inlineStr">
         <is>
-          <t>undo.messages.no-moves</t>
+          <t>start-game.messages.requester-must-pick-team</t>
         </is>
       </c>
       <c r="B289" s="2" t="inlineStr">
         <is>
-          <t>No moves to undo</t>
+          <t>You must select a team before starting a game with bot</t>
         </is>
       </c>
       <c r="C289" s="2" t="inlineStr">
         <is>
-          <t>Không có nước đi để hoàn tác</t>
+          <t>Bạn phải chọn team trước khi bắt đầu trò chơi với bot</t>
         </is>
       </c>
     </row>
     <row r="290" ht="18" customHeight="1">
       <c r="A290" s="1" t="inlineStr">
         <is>
-          <t>undo.messages.delete-failed</t>
+          <t>update-room.messages.success</t>
         </is>
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>Failed to undo move</t>
+          <t>Room updated successfully</t>
         </is>
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>Không thể hoàn tác nước đi</t>
+          <t>Cập nhật phòng thành công</t>
         </is>
       </c>
     </row>
     <row r="291" ht="18" customHeight="1">
       <c r="A291" s="1" t="inlineStr">
         <is>
-          <t>undo.messages.undo-limit-exceeded</t>
+          <t>update-room.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>Maximum 3 undo per game exceeded</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C291" s="2" t="inlineStr">
         <is>
-          <t>Đã đạt tối đa 3 lần hoàn tác trong trò chơi</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="292" ht="18" customHeight="1">
       <c r="A292" s="1" t="inlineStr">
         <is>
-          <t>undo.messages.success</t>
+          <t>update-room.messages.invalid-room-id</t>
         </is>
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>Move undone successfully</t>
+          <t>Invalid room ID</t>
         </is>
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>Hoàn tác nước đi thành công</t>
+          <t>ID phòng không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="293" ht="18" customHeight="1">
       <c r="A293" s="1" t="inlineStr">
         <is>
-          <t>undo.messages.internal-server-error</t>
+          <t>update-room.messages.name-required</t>
         </is>
       </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Room name is required</t>
         </is>
       </c>
       <c r="C293" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Tên phòng không được để trống</t>
         </is>
       </c>
     </row>
     <row r="294" ht="18" customHeight="1">
       <c r="A294" s="1" t="inlineStr">
         <is>
-          <t>player-history.messages.invalid-user-id</t>
+          <t>update-room.messages.room-not-found</t>
         </is>
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>Invalid user ID</t>
+          <t>Room not found</t>
         </is>
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>ID người dùng không hợp lệ</t>
+          <t>Không tìm thấy phòng</t>
         </is>
       </c>
     </row>
     <row r="295" ht="18" customHeight="1">
       <c r="A295" s="1" t="inlineStr">
         <is>
-          <t>player-history.messages.success</t>
+          <t>update-room.messages.forbidden</t>
         </is>
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>Fetch game history successfully</t>
+          <t>You are not the host of this room</t>
         </is>
       </c>
       <c r="C295" s="2" t="inlineStr">
         <is>
-          <t>Lấy lịch sử trò chơi thành công</t>
+          <t>Bạn không phải chủ phòng</t>
         </is>
       </c>
     </row>
     <row r="296" ht="18" customHeight="1">
       <c r="A296" s="1" t="inlineStr">
         <is>
-          <t>validate-token.messages.success</t>
+          <t>draw-game.messages.invalid-game-id</t>
         </is>
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>Token is valid</t>
+          <t>Invalid game ID</t>
         </is>
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>Token hợp lệ</t>
+          <t>ID trò chơi không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="297" ht="18" customHeight="1">
       <c r="A297" s="1" t="inlineStr">
         <is>
-          <t>guide.section.objective</t>
+          <t>draw-game.messages.game-not-found</t>
         </is>
       </c>
       <c r="B297" s="2" t="inlineStr">
         <is>
-          <t>Objective of the game</t>
+          <t>Game not found</t>
         </is>
       </c>
       <c r="C297" s="2" t="inlineStr">
         <is>
-          <t>Mục tiêu của trò chơi</t>
+          <t>Không tìm thấy trò chơi</t>
         </is>
       </c>
     </row>
     <row r="298" ht="18" customHeight="1">
       <c r="A298" s="1" t="inlineStr">
         <is>
-          <t>guide.section.pieces</t>
+          <t>draw-game.messages.forbidden</t>
         </is>
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>Pieces</t>
+          <t>You are not in this room</t>
         </is>
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>Quân cờ</t>
+          <t>Bạn không có trong phòng này</t>
         </is>
       </c>
     </row>
     <row r="299" ht="18" customHeight="1">
       <c r="A299" s="1" t="inlineStr">
         <is>
-          <t>guide.section.moving-pieces</t>
+          <t>draw-game.messages.game-history-not-found</t>
         </is>
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
-          <t>Moving pieces</t>
+          <t>Game history not found</t>
         </is>
       </c>
       <c r="C299" s="2" t="inlineStr">
         <is>
-          <t>Đi quân</t>
+          <t>Không tìm thấy lịch sử trò chơi</t>
         </is>
       </c>
     </row>
     <row r="300" ht="18" customHeight="1">
       <c r="A300" s="1" t="inlineStr">
         <is>
-          <t>guide.section.capturing</t>
+          <t>draw-game.messages.game-already-finished</t>
         </is>
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>Capturing</t>
+          <t>Game is already finished</t>
         </is>
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>Bắt quân</t>
+          <t>Trò chơi đã kết thúc</t>
         </is>
       </c>
     </row>
     <row r="301" ht="18" customHeight="1">
       <c r="A301" s="1" t="inlineStr">
         <is>
-          <t>guide.section.check</t>
+          <t>draw-game.messages.success</t>
         </is>
       </c>
       <c r="B301" s="2" t="inlineStr">
         <is>
-          <t>Check</t>
+          <t>Draw game successfully</t>
         </is>
       </c>
       <c r="C301" s="2" t="inlineStr">
         <is>
-          <t>Chiếu tướng</t>
+          <t>Hòa cờ thành công</t>
         </is>
       </c>
     </row>
     <row r="302" ht="18" customHeight="1">
       <c r="A302" s="1" t="inlineStr">
         <is>
-          <t>guide.section.result</t>
+          <t>draw-game.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>Result</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C302" s="2" t="inlineStr">
         <is>
-          <t>Kết quả</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="303" ht="90" customHeight="1">
       <c r="A303" s="1" t="inlineStr">
         <is>
-          <t>guide.table.piece</t>
+          <t>surrender.messages.game-already-finished</t>
         </is>
       </c>
       <c r="B303" s="2" t="inlineStr">
         <is>
-          <t>Piece</t>
+          <t>Game is already finished</t>
         </is>
       </c>
       <c r="C303" s="2" t="inlineStr">
         <is>
-          <t>Quân</t>
+          <t>Trò chơi đã kết thúc</t>
         </is>
       </c>
     </row>
     <row r="304" ht="90" customHeight="1">
       <c r="A304" s="1" t="inlineStr">
         <is>
-          <t>guide.table.symbol</t>
+          <t>surrender.messages.game-history-not-found</t>
         </is>
       </c>
       <c r="B304" s="2" t="inlineStr">
         <is>
-          <t>Symbol</t>
+          <t>Game history not found</t>
         </is>
       </c>
       <c r="C304" s="2" t="inlineStr">
         <is>
-          <t>Ký hiệu</t>
+          <t>Không tìm thấy lịch sử trò chơi</t>
         </is>
       </c>
     </row>
     <row r="305" ht="18" customHeight="1">
       <c r="A305" s="1" t="inlineStr">
         <is>
-          <t>guide.table.quantity</t>
+          <t>surrender.messages.game-not-found</t>
         </is>
       </c>
       <c r="B305" s="2" t="inlineStr">
         <is>
-          <t>Quantity</t>
+          <t>Game not found</t>
         </is>
       </c>
       <c r="C305" s="2" t="inlineStr">
         <is>
-          <t>Số lượng</t>
+          <t>Không tìm thấy trò chơi</t>
         </is>
       </c>
     </row>
     <row r="306" ht="18" customHeight="1">
       <c r="A306" s="1" t="inlineStr">
         <is>
-          <t>guide.objective.paragraph1</t>
+          <t>surrender.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B306" s="2" t="inlineStr">
         <is>
-          <t>A match is played between two players: one controls the Red pieces, and the other controls the Black pieces. The objective of each player is to use their pieces on the board to &lt;b&gt;checkmate&lt;/b&gt; the opponent's General, and win the game.</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C306" s="2" t="inlineStr">
         <is>
-          <t>Ván cờ được tiến hành giữa 2 đấu thủ, một người cầm Quân Đỏ, một người cầm Quân Đen. Mục đích của mỗi đấu thủ là tìm mọi cách sử dụng các quân trên bàn cờ để &lt;b&gt;chiếu bí Tướng&lt;/b&gt; của đối phương, giành thắng lợi.</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="307" ht="18" customHeight="1">
       <c r="A307" s="1" t="inlineStr">
         <is>
-          <t>guide.pieces.paragraph1</t>
+          <t>surrender.messages.invalid-game-id</t>
         </is>
       </c>
       <c r="B307" s="2" t="inlineStr">
         <is>
-          <t>At the start of each game, there must be 32 pieces in total, consisting of &lt;b&gt;7 piece types&lt;/b&gt; split evenly between both sides: 16 Red pieces and 16 Black pieces. The 7 piece types with their symbols and quantities are as follows:</t>
+          <t>Invalid game ID</t>
         </is>
       </c>
       <c r="C307" s="2" t="inlineStr">
         <is>
-          <t>Mỗi ván cờ lúc bắt đầu phải có đủ 32 quân, gồm 7 loại chia đều cho mỗi bên gồm 16 quân Đỏ và 16 quân Đen. &lt;b&gt;7 loại quân&lt;/b&gt; có ký hiệu và số lượng như sau:</t>
+          <t>ID trò chơi không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="308" ht="18" customHeight="1">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>guide.piece.general</t>
+          <t>surrender.messages.invalid-surrender-player</t>
         </is>
       </c>
       <c r="B308" s="2" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>You are not a player in this game</t>
         </is>
       </c>
       <c r="C308" s="2" t="inlineStr">
         <is>
-          <t>Tướng</t>
+          <t>Bạn không phải là người chơi trong trò chơi này</t>
         </is>
       </c>
     </row>
     <row r="309" ht="18" customHeight="1">
       <c r="A309" s="2" t="inlineStr">
         <is>
-          <t>guide.piece.advisor</t>
+          <t>surrender.messages.opponent-not-found</t>
         </is>
       </c>
       <c r="B309" s="2" t="inlineStr">
         <is>
-          <t>Advisor</t>
+          <t>Opponent not found</t>
         </is>
       </c>
       <c r="C309" s="2" t="inlineStr">
         <is>
-          <t>Sĩ</t>
+          <t>Không tìm thấy đối thủ</t>
         </is>
       </c>
     </row>
     <row r="310" ht="18" customHeight="1">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>guide.piece.elephant</t>
+          <t>surrender.messages.success</t>
         </is>
       </c>
       <c r="B310" s="2" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Surrendered</t>
         </is>
       </c>
       <c r="C310" s="2" t="inlineStr">
         <is>
-          <t>Tượng</t>
+          <t>Đã đầu hàng</t>
         </is>
       </c>
     </row>
     <row r="311" ht="18" customHeight="1">
       <c r="A311" s="2" t="inlineStr">
         <is>
-          <t>guide.piece.chariot</t>
+          <t>undo.messages.invalid-game-id</t>
         </is>
       </c>
       <c r="B311" s="2" t="inlineStr">
         <is>
-          <t>Chariot</t>
+          <t>Invalid game ID</t>
         </is>
       </c>
       <c r="C311" s="2" t="inlineStr">
         <is>
-          <t>Xe</t>
+          <t>ID trò chơi không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="312" ht="54" customHeight="1">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>guide.piece.horse</t>
+          <t>undo.messages.unauthorized</t>
         </is>
       </c>
       <c r="B312" s="2" t="inlineStr">
         <is>
-          <t>Horse</t>
+          <t>Unauthorized</t>
         </is>
       </c>
       <c r="C312" s="2" t="inlineStr">
         <is>
-          <t>Mã</t>
+          <t>Không được phép truy cập</t>
         </is>
       </c>
     </row>
     <row r="313" ht="18" customHeight="1">
       <c r="A313" s="2" t="inlineStr">
         <is>
-          <t>guide.piece.cannon</t>
+          <t>undo.messages.game-not-found</t>
         </is>
       </c>
       <c r="B313" s="2" t="inlineStr">
         <is>
-          <t>Cannon</t>
+          <t>Game not found</t>
         </is>
       </c>
       <c r="C313" s="2" t="inlineStr">
         <is>
-          <t>Pháo</t>
+          <t>Không tìm thấy trò chơi</t>
         </is>
       </c>
     </row>
     <row r="314" ht="90" customHeight="1">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>guide.piece.soldier</t>
+          <t>undo.messages.not-in-game</t>
         </is>
       </c>
       <c r="B314" s="2" t="inlineStr">
         <is>
-          <t>Soldier</t>
+          <t>You are not part of this game</t>
         </is>
       </c>
       <c r="C314" s="2" t="inlineStr">
         <is>
-          <t>Tốt</t>
+          <t>Bạn không phải là người chơi trong trò chơi này</t>
         </is>
       </c>
     </row>
     <row r="315" ht="18" customHeight="1">
       <c r="A315" s="2" t="inlineStr">
         <is>
-          <t>guide.moving-pieces.paragraph1</t>
+          <t>undo.messages.not-in-room</t>
         </is>
       </c>
       <c r="B315" s="2" t="inlineStr">
         <is>
-          <t>On each turn, each side may move only one of its own pieces according to the rules. The movement rules are as follows:</t>
+          <t>You are not in this room</t>
         </is>
       </c>
       <c r="C315" s="2" t="inlineStr">
         <is>
-          <t>Mỗi nước đi, mỗi bên chỉ được di chuyển quân của mình theo đúng quy định. Quy định di chuyển của các quân như sau:</t>
+          <t>Bạn không trong phòng này</t>
         </is>
       </c>
     </row>
     <row r="316" ht="36" customHeight="1">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>guide.general.paragraph1</t>
+          <t>undo.messages.spectator-cannot-undo</t>
         </is>
       </c>
       <c r="B316" s="2" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Spectators cannot undo moves</t>
         </is>
       </c>
       <c r="C316" s="2" t="inlineStr">
         <is>
-          <t>Tướng</t>
+          <t>Người xem không thể hoàn tác nước đi</t>
         </is>
       </c>
     </row>
     <row r="317" ht="18" customHeight="1">
       <c r="A317" s="2" t="inlineStr">
         <is>
-          <t>guide.general.paragraph2</t>
+          <t>undo.messages.no-moves</t>
         </is>
       </c>
       <c r="B317" s="2" t="inlineStr">
         <is>
-          <t>Moves one step &lt;b&gt;horizontally or vertically&lt;/b&gt; within the palace. The two Generals may not face each other directly on the same file. If they are facing each other, there must be at least one piece of either side placed between them.</t>
+          <t>No moves to undo</t>
         </is>
       </c>
       <c r="C317" s="2" t="inlineStr">
         <is>
-          <t>Mỗi nước được đi một bước &lt;b&gt;ngang hoặc dọc&lt;/b&gt; tùy ý trong cung Tướng. Hai tướng của 2 bên không được đối mặt nhau trực tiếp trên cùng một đường thẳng. Nếu đối mặt, bắt buộc phải có quân của bất kỳ bên nào đứng che mặt.</t>
+          <t>Không có nước đi để hoàn tác</t>
         </is>
       </c>
     </row>
     <row r="318" ht="72" customHeight="1">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>guide.advisor.paragraph1</t>
+          <t>undo.messages.delete-failed</t>
         </is>
       </c>
       <c r="B318" s="2" t="inlineStr">
         <is>
-          <t>Advisor</t>
+          <t>Failed to undo move</t>
         </is>
       </c>
       <c r="C318" s="2" t="inlineStr">
         <is>
-          <t>Sĩ</t>
+          <t>Không thể hoàn tác nước đi</t>
         </is>
       </c>
     </row>
     <row r="319" ht="18" customHeight="1">
       <c r="A319" s="2" t="inlineStr">
         <is>
-          <t>guide.advisor.paragraph2</t>
+          <t>undo.messages.undo-limit-exceeded</t>
         </is>
       </c>
       <c r="B319" s="2" t="inlineStr">
         <is>
-          <t>Moves one step &lt;b&gt;diagonally&lt;/b&gt; within the palace.</t>
+          <t>Maximum 3 undo per game exceeded</t>
         </is>
       </c>
       <c r="C319" s="2" t="inlineStr">
         <is>
-          <t>Mỗi nước &lt;b&gt;đi chéo một bước&lt;/b&gt; trong cung Tướng.</t>
+          <t>Đã đạt tối đa 3 lần hoàn tác trong trò chơi</t>
         </is>
       </c>
     </row>
     <row r="320" ht="54" customHeight="1">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>guide.elephant.paragraph1</t>
+          <t>undo.messages.success</t>
         </is>
       </c>
       <c r="B320" s="2" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Move undone successfully</t>
         </is>
       </c>
       <c r="C320" s="2" t="inlineStr">
         <is>
-          <t>Tượng</t>
+          <t>Hoàn tác nước đi thành công</t>
         </is>
       </c>
     </row>
     <row r="321" ht="18" customHeight="1">
       <c r="A321" s="2" t="inlineStr">
         <is>
-          <t>guide.elephant.paragraph2</t>
+          <t>undo.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B321" s="2" t="inlineStr">
         <is>
-          <t>Moves &lt;b&gt;two steps diagonally&lt;/b&gt; on its own side of the board and may not cross the river. If there is another piece on the midpoint of that diagonal path, the Elephant is blocked and cannot move.</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C321" s="2" t="inlineStr">
         <is>
-          <t>Mỗi nước &lt;b&gt;đi chéo hai bước&lt;/b&gt; tại trận địa bên mình, không được qua sông. Nếu ở giữa đường chéo đó có quân khác đứng thì quân Tượng bị cản, không đi được.</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="322" ht="72" customHeight="1">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>guide.chariot.paragraph1</t>
+          <t>player-history.messages.invalid-user-id</t>
         </is>
       </c>
       <c r="B322" s="2" t="inlineStr">
         <is>
-          <t>Chariot</t>
+          <t>Invalid user ID</t>
         </is>
       </c>
       <c r="C322" s="2" t="inlineStr">
         <is>
-          <t>Xe</t>
+          <t>ID người dùng không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="323" ht="18" customHeight="1">
       <c r="A323" s="2" t="inlineStr">
         <is>
-          <t>guide.chariot.paragraph2</t>
+          <t>player-history.messages.success</t>
         </is>
       </c>
       <c r="B323" s="2" t="inlineStr">
         <is>
-          <t>Moves &lt;b&gt;horizontally or vertically&lt;/b&gt; with no limit on distance, as long as no piece blocks the path.</t>
+          <t>Fetch game history successfully</t>
         </is>
       </c>
       <c r="C323" s="2" t="inlineStr">
         <is>
-          <t>Mỗi nước được &lt;b&gt;đi dọc hoặc đi ngang&lt;/b&gt;, không hạn chế số bước đi nếu không có quân khác cản đường.</t>
+          <t>Lấy lịch sử trò chơi thành công</t>
         </is>
       </c>
     </row>
     <row r="324" ht="90" customHeight="1">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>guide.horse.paragraph1</t>
+          <t>validate-token.messages.success</t>
         </is>
       </c>
       <c r="B324" s="2" t="inlineStr">
         <is>
-          <t>Horse</t>
+          <t>Token is valid</t>
         </is>
       </c>
       <c r="C324" s="2" t="inlineStr">
         <is>
-          <t>Mã</t>
+          <t>Token hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="325" ht="18" customHeight="1">
       <c r="A325" s="2" t="inlineStr">
         <is>
-          <t>guide.horse.paragraph2</t>
+          <t>guide.section.objective</t>
         </is>
       </c>
       <c r="B325" s="2" t="inlineStr">
         <is>
-          <t>Moves in an &lt;b&gt;L-shape&lt;/b&gt; (one step orthogonally then one step diagonally outward). If the adjacent orthogonal point is occupied by any piece, the Horse is blocked and cannot move.</t>
+          <t>Objective of the game</t>
         </is>
       </c>
       <c r="C325" s="2" t="inlineStr">
         <is>
-          <t>Đi theo &lt;b&gt;đường chéo hình chữ nhật&lt;/b&gt; của hai ô vuông liền nhau. Nếu giao điểm liền kề bước thẳng dọc ngang có một quân khác đứng thì Mã bị cản, không đi được.</t>
+          <t>Mục tiêu của trò chơi</t>
         </is>
       </c>
     </row>
     <row r="326" ht="72" customHeight="1">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>guide.cannon.paragraph1</t>
+          <t>guide.section.pieces</t>
         </is>
       </c>
       <c r="B326" s="2" t="inlineStr">
         <is>
-          <t>Cannon</t>
+          <t>Pieces</t>
         </is>
       </c>
       <c r="C326" s="2" t="inlineStr">
         <is>
-          <t>Pháo</t>
+          <t>Quân cờ</t>
         </is>
       </c>
     </row>
     <row r="327" ht="54" customHeight="1">
       <c r="A327" s="2" t="inlineStr">
         <is>
-          <t>guide.cannon.paragraph2</t>
+          <t>guide.section.moving-pieces</t>
         </is>
       </c>
       <c r="B327" s="2" t="inlineStr">
         <is>
-          <t>Moves &lt;b&gt;horizontally or vertically&lt;/b&gt; like a Chariot when not capturing. To capture, it must &lt;b&gt;jump over exactly one piece&lt;/b&gt; to reach its target. If there are zero or more than one pieces between the Cannon and the target, it cannot capture.</t>
+          <t>Moving pieces</t>
         </is>
       </c>
       <c r="C327" s="2" t="inlineStr">
         <is>
-          <t>Đi ngang hoặc dọc giống Xe khi không bắt quân. Để bắt quân, nó phải &lt;b&gt;nhảy qua đúng một quân khác&lt;/b&gt; để đến mục tiêu. Nếu không có hoặc có nhiều hơn một quân giữa Pháo và mục tiêu, nó không thể bắt quân.</t>
+          <t>Đi quân</t>
         </is>
       </c>
     </row>
     <row r="328" ht="54" customHeight="1">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>guide.soldier.paragraph1</t>
+          <t>guide.section.capturing</t>
         </is>
       </c>
       <c r="B328" s="2" t="inlineStr">
         <is>
-          <t>Soldier</t>
+          <t>Capturing</t>
         </is>
       </c>
       <c r="C328" s="2" t="inlineStr">
         <is>
-          <t>Tốt</t>
+          <t>Bắt quân</t>
         </is>
       </c>
     </row>
     <row r="329" ht="54" customHeight="1">
       <c r="A329" s="2" t="inlineStr">
         <is>
-          <t>guide.soldier.paragraph2</t>
+          <t>guide.section.check</t>
         </is>
       </c>
       <c r="B329" s="2" t="inlineStr">
         <is>
-          <t>Moves &lt;b&gt;one step&lt;/b&gt; each turn. Before crossing the river, it can only move forward. After crossing the river, it may move &lt;b&gt;forward or sideways&lt;/b&gt;, but never backward.</t>
+          <t>Check</t>
         </is>
       </c>
       <c r="C329" s="2" t="inlineStr">
         <is>
-          <t>Mỗi nước đi &lt;b&gt;một bước&lt;/b&gt;. Khi chưa qua sông, Tốt chỉ được tiến. Khi Tốt đã qua sông được quyền &lt;b&gt;đi tiến và đi ngang&lt;/b&gt;, không được phép lùi.</t>
+          <t>Chiếu tướng</t>
         </is>
       </c>
     </row>
     <row r="330" ht="90" customHeight="1">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>guide.capturing.paragraph1</t>
+          <t>guide.section.result</t>
         </is>
       </c>
       <c r="B330" s="2" t="inlineStr">
         <is>
-          <t>When a piece moves to an intersection occupied by an opponent's piece, it may &lt;b&gt;capture that piece&lt;/b&gt; and occupy its position.</t>
+          <t>Result</t>
         </is>
       </c>
       <c r="C330" s="2" t="inlineStr">
         <is>
-          <t>Khi một quân đi tới một giao điểm khác đã có quân đối phương đứng thì được quyền &lt;b&gt;bắt quân đó&lt;/b&gt;, đồng thời chiếm giữ vị trí quân bị bắt.</t>
+          <t>Kết quả</t>
         </is>
       </c>
     </row>
     <row r="331" ht="54" customHeight="1">
       <c r="A331" s="2" t="inlineStr">
         <is>
-          <t>guide.capturing.paragraph2</t>
+          <t>guide.table.piece</t>
         </is>
       </c>
       <c r="B331" s="2" t="inlineStr">
         <is>
-          <t>You may not capture your own pieces. You may sacrifice your own pieces to be captured by the opponent, &lt;b&gt;except for the General&lt;/b&gt;.</t>
+          <t>Piece</t>
         </is>
       </c>
       <c r="C331" s="2" t="inlineStr">
         <is>
-          <t>Không được bắt quân bên mình. Được phép cho đối phương bắt đầu quân mình chủ động hiến mình cho đối phương, &lt;b&gt;trừ Tướng&lt;/b&gt;.</t>
+          <t>Quân</t>
         </is>
       </c>
     </row>
     <row r="332" ht="36" customHeight="1">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>guide.capturing.paragraph3</t>
+          <t>guide.table.symbol</t>
         </is>
       </c>
       <c r="B332" s="2" t="inlineStr">
         <is>
-          <t>A captured piece is removed from the board. &lt;b&gt;Chasing one piece for more than 6 consecutive moves is not allowed&lt;/b&gt;.</t>
+          <t>Symbol</t>
         </is>
       </c>
       <c r="C332" s="2" t="inlineStr">
         <is>
-          <t>Quân bị bắt phải bị loại và bị nhấc ra khỏi bàn cờ. &lt;b&gt;Không được đuổi 1 quân quá 6 nước cờ liên tiếp&lt;/b&gt;.</t>
+          <t>Ký hiệu</t>
         </is>
       </c>
     </row>
     <row r="333" ht="18" customHeight="1">
       <c r="A333" s="2" t="inlineStr">
         <is>
-          <t>guide.check.paragraph1</t>
+          <t>guide.table.quantity</t>
         </is>
       </c>
       <c r="B333" s="2" t="inlineStr">
         <is>
-          <t>If a player makes a move that threatens to capture the opponent's General on the next move (by the same piece or another piece), it is called a &lt;b&gt;Check&lt;/b&gt;. The checked side must respond to avoid check. Otherwise, that side loses</t>
+          <t>Quantity</t>
         </is>
       </c>
       <c r="C333" s="2" t="inlineStr">
         <is>
-          <t>Nếu người chơi thực hiện một nước đi đe dọa bắt Tướng của đối phương ở nước đi tiếp theo (bằng chính quân cờ đó hoặc một quân cờ khác), thì đó được gọi là &lt;b&gt;Chiếu&lt;/b&gt;. Bên bị chiếu phải đáp trả để tránh bị chiếu. Nếu không sẽ bị xử thua</t>
+          <t>Số lượng</t>
         </is>
       </c>
     </row>
     <row r="334" ht="36" customHeight="1">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>guide.check.paragraph2</t>
+          <t>guide.objective.paragraph1</t>
         </is>
       </c>
       <c r="B334" s="2" t="inlineStr">
         <is>
-          <t>When the General is checked from any direction (including from behind), the checked side may respond in one of the following ways:</t>
+          <t>A match is played between two players: one controls the Red pieces, and the other controls the Black pieces. The objective of each player is to use their pieces on the board to &lt;b&gt;checkmate&lt;/b&gt; the opponent's General, and win the game.</t>
         </is>
       </c>
       <c r="C334" s="2" t="inlineStr">
         <is>
-          <t>Tướng bị chiếu từ cả bốn hướng (bị chiếu cả từ phía sau) có thể ứng phó với nước chiếu tướng bằng một trong các cách sau:</t>
+          <t>Ván cờ được tiến hành giữa 2 đấu thủ, một người cầm Quân Đỏ, một người cầm Quân Đen. Mục đích của mỗi đấu thủ là tìm mọi cách sử dụng các quân trên bàn cờ để &lt;b&gt;chiếu bí Tướng&lt;/b&gt; của đối phương, giành thắng lợi.</t>
         </is>
       </c>
     </row>
     <row r="335" ht="36" customHeight="1">
       <c r="A335" s="2" t="inlineStr">
         <is>
-          <t>guide.check.paragraph3</t>
+          <t>guide.pieces.paragraph1</t>
         </is>
       </c>
       <c r="B335" s="2" t="inlineStr">
         <is>
-          <t>Move the General to another position to escape check</t>
+          <t>At the start of each game, there must be 32 pieces in total, consisting of &lt;b&gt;7 piece types&lt;/b&gt; split evenly between both sides: 16 Red pieces and 16 Black pieces. The 7 piece types with their symbols and quantities are as follows:</t>
         </is>
       </c>
       <c r="C335" s="2" t="inlineStr">
         <is>
-          <t>Di chuyển tướng sang vị trí khác để tránh nước chiếu</t>
+          <t>Mỗi ván cờ lúc bắt đầu phải có đủ 32 quân, gồm 7 loại chia đều cho mỗi bên gồm 16 quân Đỏ và 16 quân Đen. &lt;b&gt;7 loại quân&lt;/b&gt; có ký hiệu và số lượng như sau:</t>
         </is>
       </c>
     </row>
     <row r="336" ht="72" customHeight="1">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>guide.check.paragraph4</t>
+          <t>guide.piece.general</t>
         </is>
       </c>
       <c r="B336" s="2" t="inlineStr">
         <is>
-          <t>Capture the checking piece</t>
+          <t>General</t>
         </is>
       </c>
       <c r="C336" s="2" t="inlineStr">
         <is>
-          <t>Bắt quân đang chiếu</t>
+          <t>Tướng</t>
         </is>
       </c>
     </row>
     <row r="337" ht="54" customHeight="1">
       <c r="A337" s="2" t="inlineStr">
         <is>
-          <t>guide.check.paragraph5</t>
+          <t>guide.piece.advisor</t>
         </is>
       </c>
       <c r="B337" s="2" t="inlineStr">
         <is>
-          <t>Block the checking line with another piece to protect the General</t>
+          <t>Advisor</t>
         </is>
       </c>
       <c r="C337" s="2" t="inlineStr">
         <is>
-          <t>Dùng quân khác cản quân chiếu, đi quân che đỡ cho tướng</t>
+          <t>Sĩ</t>
         </is>
       </c>
     </row>
     <row r="338" ht="54" customHeight="1">
       <c r="A338" s="2" t="inlineStr">
         <is>
-          <t>guide.check.paragraph6</t>
+          <t>guide.piece.elephant</t>
         </is>
       </c>
       <c r="B338" s="2" t="inlineStr">
         <is>
-          <t>Repeatedly checking for more than 6 consecutive moves is not allowed</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="C338" s="2" t="inlineStr">
         <is>
-          <t>Không được chiếu tướng quá 6 nước cờ liên tiếp</t>
+          <t>Tượng</t>
         </is>
       </c>
     </row>
     <row r="339" ht="90" customHeight="1">
       <c r="A339" s="2" t="inlineStr">
         <is>
-          <t>guide.result.paragraph1</t>
+          <t>guide.piece.chariot</t>
         </is>
       </c>
       <c r="B339" s="2" t="inlineStr">
         <is>
-          <t>When one side gives Check and the other side has no legal way to protect the General, it is called a &lt;b&gt;Checkmate&lt;/b&gt;. The side that delivers Checkmate wins.</t>
+          <t>Chariot</t>
         </is>
       </c>
       <c r="C339" s="2" t="inlineStr">
         <is>
-          <t>Khi một bên chiếu Tướng mà bên còn lại không thể làm gì để bảo vệ Tướng thì được gọi là &lt;b&gt;Chiếu Hết&lt;/b&gt;, bên thực hiện được Chiếu Hết sẽ giành chiến thắng.</t>
+          <t>Xe</t>
         </is>
       </c>
     </row>
     <row r="340" ht="54" customHeight="1">
       <c r="A340" s="2" t="inlineStr">
         <is>
-          <t>guide.result.paragraph2</t>
+          <t>guide.piece.horse</t>
         </is>
       </c>
       <c r="B340" s="2" t="inlineStr">
         <is>
-          <t>If a player runs out of time for a single move (for example: 90s) without moving, the other side is awarded a &lt;b&gt;win&lt;/b&gt;.</t>
+          <t>Horse</t>
         </is>
       </c>
       <c r="C340" s="2" t="inlineStr">
         <is>
-          <t>Khi hết thời gian một nước đi (ví dụ: 90s) mà vẫn chưa di chuyển quân thì bên còn lại sẽ được &lt;b&gt;xử Thắng&lt;/b&gt;.</t>
+          <t>Mã</t>
         </is>
       </c>
     </row>
     <row r="341" ht="18" customHeight="1">
       <c r="A341" s="2" t="inlineStr">
         <is>
-          <t>guide.result.paragraph3</t>
+          <t>guide.piece.cannon</t>
         </is>
       </c>
       <c r="B341" s="2" t="inlineStr">
         <is>
-          <t>If a player runs out of total game time (for example: 5 minutes or 10 minutes), the other side is awarded a &lt;b&gt;win&lt;/b&gt;.</t>
+          <t>Cannon</t>
         </is>
       </c>
       <c r="C341" s="2" t="inlineStr">
         <is>
-          <t>Khi một bên hết thời gian ván đấu (ví dụ: 5 phút, 10 phút) thì bên còn lại sẽ được &lt;b&gt;xử Thắng&lt;/b&gt;.</t>
+          <t>Pháo</t>
         </is>
       </c>
     </row>
     <row r="342" ht="18" customHeight="1">
       <c r="A342" s="2" t="inlineStr">
         <is>
-          <t>guide.result.paragraph4</t>
+          <t>guide.piece.soldier</t>
         </is>
       </c>
       <c r="B342" s="2" t="inlineStr">
         <is>
-          <t>If both sides have no pieces that have crossed the river, the game is declared a &lt;b&gt;draw&lt;/b&gt;. If one side still has pieces across the river but runs out of time, while the other side still has time but has no pieces across the river, the game is declared a &lt;b&gt;draw&lt;/b&gt;.</t>
+          <t>Soldier</t>
         </is>
       </c>
       <c r="C342" s="2" t="inlineStr">
         <is>
-          <t>Khi cả 2 bên đều không còn quân qua sông, ván đấu sẽ được &lt;b&gt;xử Hòa&lt;/b&gt;. Khi một bên còn quân qua sông nhưng cạn thời gian, một bên còn thời gian nhưng hết quân qua sông, ván đấu sẽ được &lt;b&gt;xử Hòa&lt;/b&gt;.</t>
+          <t>Tốt</t>
         </is>
       </c>
     </row>
     <row r="343" ht="36" customHeight="1">
       <c r="A343" s="2" t="inlineStr">
         <is>
-          <t>guide.result.paragraph5</t>
+          <t>guide.moving-pieces.paragraph1</t>
         </is>
       </c>
       <c r="B343" s="2" t="inlineStr">
         <is>
-          <t>Within 40 moves, if there is no capture and no Soldier advances by one square, the game is declared a &lt;b&gt;draw&lt;/b&gt;.</t>
+          <t>On each turn, each side may move only one of its own pieces according to the rules. The movement rules are as follows:</t>
         </is>
       </c>
       <c r="C343" s="2" t="inlineStr">
         <is>
-          <t>Trong vòng 40 nước nếu không phát sinh nước bắt quân, Tốt không tiến 1 ô thì ván đấu sẽ được &lt;b&gt;xử Hòa&lt;/b&gt;.</t>
+          <t>Mỗi nước đi, mỗi bên chỉ được di chuyển quân của mình theo đúng quy định. Quy định di chuyển của các quân như sau:</t>
         </is>
       </c>
     </row>
     <row r="344" ht="18" customHeight="1">
       <c r="A344" s="2" t="inlineStr">
         <is>
-          <t>extra-money.lucky-wheel.title</t>
+          <t>guide.general.paragraph1</t>
         </is>
       </c>
       <c r="B344" s="2" t="inlineStr">
         <is>
-          <t>Lucky Wheel</t>
+          <t>General</t>
         </is>
       </c>
       <c r="C344" s="2" t="inlineStr">
         <is>
-          <t>Vòng quay may mắn</t>
+          <t>Tướng</t>
         </is>
       </c>
     </row>
     <row r="345" ht="18" customHeight="1">
       <c r="A345" s="2" t="inlineStr">
         <is>
-          <t>extra-money.lucky-wheel.description</t>
+          <t>guide.general.paragraph2</t>
         </is>
       </c>
       <c r="B345" s="2" t="inlineStr">
         <is>
-          <t>Spin the wheel to earn money! Click the spin button in the middle of the wheel to try your luck.</t>
+          <t>Moves one step &lt;b&gt;horizontally or vertically&lt;/b&gt; within the palace. The two Generals may not face each other directly on the same file. If they are facing each other, there must be at least one piece of either side placed between them.</t>
         </is>
       </c>
       <c r="C345" s="2" t="inlineStr">
         <is>
-          <t>Quay vòng để kiếm tiền! Bấm nút Quay ở giữa vòng quay để thử vận may của bạn.</t>
+          <t>Mỗi nước được đi một bước &lt;b&gt;ngang hoặc dọc&lt;/b&gt; tùy ý trong cung Tướng. Hai tướng của 2 bên không được đối mặt nhau trực tiếp trên cùng một đường thẳng. Nếu đối mặt, bắt buộc phải có quân của bất kỳ bên nào đứng che mặt.</t>
         </is>
       </c>
     </row>
     <row r="346" ht="36" customHeight="1">
       <c r="A346" s="2" t="inlineStr">
         <is>
-          <t>extra-money.lucky-wheel.spin-button</t>
+          <t>guide.advisor.paragraph1</t>
         </is>
       </c>
       <c r="B346" s="2" t="inlineStr">
         <is>
-          <t>Spin</t>
+          <t>Advisor</t>
         </is>
       </c>
       <c r="C346" s="2" t="inlineStr">
         <is>
-          <t>Quay</t>
+          <t>Sĩ</t>
         </is>
       </c>
     </row>
     <row r="347" ht="18" customHeight="1">
       <c r="A347" s="2" t="inlineStr">
         <is>
-          <t>extra-money.lucky-wheel.reward-placeholder</t>
+          <t>guide.advisor.paragraph2</t>
         </is>
       </c>
       <c r="B347" s="2" t="inlineStr">
         <is>
-          <t>Click Spin to get started</t>
+          <t>Moves one step &lt;b&gt;diagonally&lt;/b&gt; within the palace.</t>
         </is>
       </c>
       <c r="C347" s="2" t="inlineStr">
         <is>
-          <t>Nhấp Quay để bắt đầu</t>
+          <t>Mỗi nước &lt;b&gt;đi chéo một bước&lt;/b&gt; trong cung Tướng.</t>
         </is>
       </c>
     </row>
     <row r="348" ht="36" customHeight="1">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>extra-money.title</t>
+          <t>guide.elephant.paragraph1</t>
         </is>
       </c>
       <c r="B348" s="2" t="inlineStr">
         <is>
-          <t>Daily tasks</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="C348" s="2" t="inlineStr">
         <is>
-          <t>Tác vụ thường nhật</t>
+          <t>Tượng</t>
         </is>
       </c>
     </row>
     <row r="349" ht="18" customHeight="1">
       <c r="A349" s="2" t="inlineStr">
         <is>
-          <t>extra-money.tab.lucky-wheel</t>
+          <t>guide.elephant.paragraph2</t>
         </is>
       </c>
       <c r="B349" s="2" t="inlineStr">
         <is>
-          <t>Lucky Wheel</t>
+          <t>Moves &lt;b&gt;two steps diagonally&lt;/b&gt; on its own side of the board and may not cross the river. If there is another piece on the midpoint of that diagonal path, the Elephant is blocked and cannot move.</t>
         </is>
       </c>
       <c r="C349" s="2" t="inlineStr">
         <is>
-          <t>Vòng Quay May Mắn</t>
+          <t>Mỗi nước &lt;b&gt;đi chéo hai bước&lt;/b&gt; tại trận địa bên mình, không được qua sông. Nếu ở giữa đường chéo đó có quân khác đứng thì quân Tượng bị cản, không đi được.</t>
         </is>
       </c>
     </row>
     <row r="350" ht="18" customHeight="1">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>extra-money.tab.bonus-coin</t>
+          <t>guide.chariot.paragraph1</t>
         </is>
       </c>
       <c r="B350" s="2" t="inlineStr">
         <is>
-          <t>Bonus Coin</t>
+          <t>Chariot</t>
         </is>
       </c>
       <c r="C350" s="2" t="inlineStr">
         <is>
-          <t>Xu Thưởng</t>
+          <t>Xe</t>
         </is>
       </c>
     </row>
     <row r="351" ht="18" customHeight="1">
       <c r="A351" s="2" t="inlineStr">
         <is>
-          <t>extra-money.tab.daily-bonus</t>
+          <t>guide.chariot.paragraph2</t>
         </is>
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>Daily Bonus</t>
+          <t>Moves &lt;b&gt;horizontally or vertically&lt;/b&gt; with no limit on distance, as long as no piece blocks the path.</t>
         </is>
       </c>
       <c r="C351" s="2" t="inlineStr">
         <is>
-          <t>Thưởng hàng ngày</t>
+          <t>Mỗi nước được &lt;b&gt;đi dọc hoặc đi ngang&lt;/b&gt;, không hạn chế số bước đi nếu không có quân khác cản đường.</t>
         </is>
       </c>
     </row>
     <row r="352" ht="18" customHeight="1">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>extra-money.bonus-coin.subtitle</t>
+          <t>guide.horse.paragraph1</t>
         </is>
       </c>
       <c r="B352" s="2" t="inlineStr">
         <is>
-          <t>Watch a short video to earn free coin</t>
+          <t>Horse</t>
         </is>
       </c>
       <c r="C352" s="2" t="inlineStr">
         <is>
-          <t>Xem video ngắn để nhận xu miễn phí</t>
+          <t>Mã</t>
         </is>
       </c>
     </row>
     <row r="353" ht="18" customHeight="1">
       <c r="A353" s="2" t="inlineStr">
         <is>
-          <t>extra-money.bonus-coin.next-in</t>
+          <t>guide.horse.paragraph2</t>
         </is>
       </c>
       <c r="B353" s="2" t="inlineStr">
         <is>
-          <t>Next in:</t>
+          <t>Moves in an &lt;b&gt;L-shape&lt;/b&gt; (one step orthogonally then one step diagonally outward). If the adjacent orthogonal point is occupied by any piece, the Horse is blocked and cannot move.</t>
         </is>
       </c>
       <c r="C353" s="2" t="inlineStr">
         <is>
-          <t>Lượt kế tiếp:</t>
+          <t>Đi theo &lt;b&gt;đường chéo hình chữ nhật&lt;/b&gt; của hai ô vuông liền nhau. Nếu giao điểm liền kề bước thẳng dọc ngang có một quân khác đứng thì Mã bị cản, không đi được.</t>
         </is>
       </c>
     </row>
     <row r="354" ht="17" customHeight="1">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>extra-money.bonus-coin.coin-unit</t>
+          <t>guide.cannon.paragraph1</t>
         </is>
       </c>
       <c r="B354" s="2" t="inlineStr">
         <is>
-          <t>coin</t>
+          <t>Cannon</t>
         </is>
       </c>
       <c r="C354" s="2" t="inlineStr">
         <is>
-          <t>xu</t>
+          <t>Pháo</t>
         </is>
       </c>
     </row>
     <row r="355" ht="18" customHeight="1">
       <c r="A355" s="2" t="inlineStr">
         <is>
-          <t>extra-money.bonus-coin.watch-video</t>
+          <t>guide.cannon.paragraph2</t>
         </is>
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>Watch video</t>
+          <t>Moves &lt;b&gt;horizontally or vertically&lt;/b&gt; like a Chariot when not capturing. To capture, it must &lt;b&gt;jump over exactly one piece&lt;/b&gt; to reach its target. If there are zero or more than one pieces between the Cannon and the target, it cannot capture.</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
         <is>
-          <t>Xem video</t>
+          <t>Đi ngang hoặc dọc giống Xe khi không bắt quân. Để bắt quân, nó phải &lt;b&gt;nhảy qua đúng một quân khác&lt;/b&gt; để đến mục tiêu. Nếu không có hoặc có nhiều hơn một quân giữa Pháo và mục tiêu, nó không thể bắt quân.</t>
         </is>
       </c>
     </row>
     <row r="356" ht="18" customHeight="1">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>extra-money.daily-bonus.subtitle</t>
+          <t>guide.soldier.paragraph1</t>
         </is>
       </c>
       <c r="B356" s="2" t="inlineStr">
         <is>
-          <t>Login 7 days in a row to earn 4000 coin</t>
+          <t>Soldier</t>
         </is>
       </c>
       <c r="C356" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập 7 ngày liên tiếp để nhận 4000 xu</t>
+          <t>Tốt</t>
         </is>
       </c>
     </row>
     <row r="357" ht="18" customHeight="1">
       <c r="A357" s="2" t="inlineStr">
         <is>
-          <t>extra-money.daily-bonus.day</t>
+          <t>guide.soldier.paragraph2</t>
         </is>
       </c>
       <c r="B357" s="2" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Moves &lt;b&gt;one step&lt;/b&gt; each turn. Before crossing the river, it can only move forward. After crossing the river, it may move &lt;b&gt;forward or sideways&lt;/b&gt;, but never backward.</t>
         </is>
       </c>
       <c r="C357" s="2" t="inlineStr">
         <is>
-          <t>Ngày</t>
+          <t>Mỗi nước đi &lt;b&gt;một bước&lt;/b&gt;. Khi chưa qua sông, Tốt chỉ được tiến. Khi Tốt đã qua sông được quyền &lt;b&gt;đi tiến và đi ngang&lt;/b&gt;, không được phép lùi.</t>
         </is>
       </c>
     </row>
     <row r="358" ht="18" customHeight="1">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>profile.button.save</t>
+          <t>guide.capturing.paragraph1</t>
         </is>
       </c>
       <c r="B358" s="2" t="inlineStr">
         <is>
-          <t>Save</t>
+          <t>When a piece moves to an intersection occupied by an opponent's piece, it may &lt;b&gt;capture that piece&lt;/b&gt; and occupy its position.</t>
         </is>
       </c>
       <c r="C358" s="2" t="inlineStr">
         <is>
-          <t>Lưu</t>
+          <t>Khi một quân đi tới một giao điểm khác đã có quân đối phương đứng thì được quyền &lt;b&gt;bắt quân đó&lt;/b&gt;, đồng thời chiếm giữ vị trí quân bị bắt.</t>
         </is>
       </c>
     </row>
     <row r="359" ht="18" customHeight="1">
       <c r="A359" s="2" t="inlineStr">
         <is>
+          <t>guide.capturing.paragraph2</t>
+        </is>
+      </c>
+      <c r="B359" s="2" t="inlineStr">
+        <is>
+          <t>You may not capture your own pieces. You may sacrifice your own pieces to be captured by the opponent, &lt;b&gt;except for the General&lt;/b&gt;.</t>
+        </is>
+      </c>
+      <c r="C359" s="2" t="inlineStr">
+        <is>
+          <t>Không được bắt quân bên mình. Được phép cho đối phương bắt đầu quân mình chủ động hiến mình cho đối phương, &lt;b&gt;trừ Tướng&lt;/b&gt;.</t>
+        </is>
+      </c>
+    </row>
+    <row r="360" ht="18" customHeight="1">
+      <c r="A360" s="2" t="inlineStr">
+        <is>
+          <t>guide.capturing.paragraph3</t>
+        </is>
+      </c>
+      <c r="B360" s="2" t="inlineStr">
+        <is>
+          <t>A captured piece is removed from the board. &lt;b&gt;Chasing one piece for more than 6 consecutive moves is not allowed&lt;/b&gt;.</t>
+        </is>
+      </c>
+      <c r="C360" s="2" t="inlineStr">
+        <is>
+          <t>Quân bị bắt phải bị loại và bị nhấc ra khỏi bàn cờ. &lt;b&gt;Không được đuổi 1 quân quá 6 nước cờ liên tiếp&lt;/b&gt;.</t>
+        </is>
+      </c>
+    </row>
+    <row r="361" ht="17" customHeight="1">
+      <c r="A361" s="2" t="inlineStr">
+        <is>
+          <t>guide.check.paragraph1</t>
+        </is>
+      </c>
+      <c r="B361" s="2" t="inlineStr">
+        <is>
+          <t>If a player makes a move that threatens to capture the opponent's General on the next move (by the same piece or another piece), it is called a &lt;b&gt;Check&lt;/b&gt;. The checked side must respond to avoid check. Otherwise, that side loses</t>
+        </is>
+      </c>
+      <c r="C361" s="2" t="inlineStr">
+        <is>
+          <t>Nếu người chơi thực hiện một nước đi đe dọa bắt Tướng của đối phương ở nước đi tiếp theo (bằng chính quân cờ đó hoặc một quân cờ khác), thì đó được gọi là &lt;b&gt;Chiếu&lt;/b&gt;. Bên bị chiếu phải đáp trả để tránh bị chiếu. Nếu không sẽ bị xử thua</t>
+        </is>
+      </c>
+    </row>
+    <row r="362" ht="17" customHeight="1">
+      <c r="A362" s="2" t="inlineStr">
+        <is>
+          <t>guide.check.paragraph2</t>
+        </is>
+      </c>
+      <c r="B362" s="2" t="inlineStr">
+        <is>
+          <t>When the General is checked from any direction (including from behind), the checked side may respond in one of the following ways:</t>
+        </is>
+      </c>
+      <c r="C362" s="2" t="inlineStr">
+        <is>
+          <t>Tướng bị chiếu từ cả bốn hướng (bị chiếu cả từ phía sau) có thể ứng phó với nước chiếu tướng bằng một trong các cách sau:</t>
+        </is>
+      </c>
+    </row>
+    <row r="363" ht="17" customHeight="1">
+      <c r="A363" s="2" t="inlineStr">
+        <is>
+          <t>guide.check.paragraph3</t>
+        </is>
+      </c>
+      <c r="B363" s="2" t="inlineStr">
+        <is>
+          <t>Move the General to another position to escape check</t>
+        </is>
+      </c>
+      <c r="C363" s="2" t="inlineStr">
+        <is>
+          <t>Di chuyển tướng sang vị trí khác để tránh nước chiếu</t>
+        </is>
+      </c>
+    </row>
+    <row r="364" ht="17" customHeight="1">
+      <c r="A364" s="2" t="inlineStr">
+        <is>
+          <t>guide.check.paragraph4</t>
+        </is>
+      </c>
+      <c r="B364" s="2" t="inlineStr">
+        <is>
+          <t>Capture the checking piece</t>
+        </is>
+      </c>
+      <c r="C364" s="2" t="inlineStr">
+        <is>
+          <t>Bắt quân đang chiếu</t>
+        </is>
+      </c>
+    </row>
+    <row r="365" ht="17" customHeight="1">
+      <c r="A365" s="2" t="inlineStr">
+        <is>
+          <t>guide.check.paragraph5</t>
+        </is>
+      </c>
+      <c r="B365" s="2" t="inlineStr">
+        <is>
+          <t>Block the checking line with another piece to protect the General</t>
+        </is>
+      </c>
+      <c r="C365" s="2" t="inlineStr">
+        <is>
+          <t>Dùng quân khác cản quân chiếu, đi quân che đỡ cho tướng</t>
+        </is>
+      </c>
+    </row>
+    <row r="366" ht="17" customHeight="1">
+      <c r="A366" s="2" t="inlineStr">
+        <is>
+          <t>guide.check.paragraph6</t>
+        </is>
+      </c>
+      <c r="B366" s="2" t="inlineStr">
+        <is>
+          <t>Repeatedly checking for more than 6 consecutive moves is not allowed</t>
+        </is>
+      </c>
+      <c r="C366" s="2" t="inlineStr">
+        <is>
+          <t>Không được chiếu tướng quá 6 nước cờ liên tiếp</t>
+        </is>
+      </c>
+    </row>
+    <row r="367" ht="17" customHeight="1">
+      <c r="A367" s="2" t="inlineStr">
+        <is>
+          <t>guide.result.paragraph1</t>
+        </is>
+      </c>
+      <c r="B367" s="2" t="inlineStr">
+        <is>
+          <t>When one side gives Check and the other side has no legal way to protect the General, it is called a &lt;b&gt;Checkmate&lt;/b&gt;. The side that delivers Checkmate wins.</t>
+        </is>
+      </c>
+      <c r="C367" s="2" t="inlineStr">
+        <is>
+          <t>Khi một bên chiếu Tướng mà bên còn lại không thể làm gì để bảo vệ Tướng thì được gọi là &lt;b&gt;Chiếu Hết&lt;/b&gt;, bên thực hiện được Chiếu Hết sẽ giành chiến thắng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="368" ht="17" customHeight="1">
+      <c r="A368" s="2" t="inlineStr">
+        <is>
+          <t>guide.result.paragraph2</t>
+        </is>
+      </c>
+      <c r="B368" s="2" t="inlineStr">
+        <is>
+          <t>If a player runs out of time for a single move (for example: 90s) without moving, the other side is awarded a &lt;b&gt;win&lt;/b&gt;.</t>
+        </is>
+      </c>
+      <c r="C368" s="2" t="inlineStr">
+        <is>
+          <t>Khi hết thời gian một nước đi (ví dụ: 90s) mà vẫn chưa di chuyển quân thì bên còn lại sẽ được &lt;b&gt;xử Thắng&lt;/b&gt;.</t>
+        </is>
+      </c>
+    </row>
+    <row r="369" ht="17" customHeight="1">
+      <c r="A369" s="2" t="inlineStr">
+        <is>
+          <t>guide.result.paragraph3</t>
+        </is>
+      </c>
+      <c r="B369" s="2" t="inlineStr">
+        <is>
+          <t>If a player runs out of total game time (for example: 5 minutes or 10 minutes), the other side is awarded a &lt;b&gt;win&lt;/b&gt;.</t>
+        </is>
+      </c>
+      <c r="C369" s="2" t="inlineStr">
+        <is>
+          <t>Khi một bên hết thời gian ván đấu (ví dụ: 5 phút, 10 phút) thì bên còn lại sẽ được &lt;b&gt;xử Thắng&lt;/b&gt;.</t>
+        </is>
+      </c>
+    </row>
+    <row r="370" ht="17" customHeight="1">
+      <c r="A370" s="2" t="inlineStr">
+        <is>
+          <t>guide.result.paragraph4</t>
+        </is>
+      </c>
+      <c r="B370" s="2" t="inlineStr">
+        <is>
+          <t>If both sides have no pieces that have crossed the river, the game is declared a &lt;b&gt;draw&lt;/b&gt;. If one side still has pieces across the river but runs out of time, while the other side still has time but has no pieces across the river, the game is declared a &lt;b&gt;draw&lt;/b&gt;.</t>
+        </is>
+      </c>
+      <c r="C370" s="2" t="inlineStr">
+        <is>
+          <t>Khi cả 2 bên đều không còn quân qua sông, ván đấu sẽ được &lt;b&gt;xử Hòa&lt;/b&gt;. Khi một bên còn quân qua sông nhưng cạn thời gian, một bên còn thời gian nhưng hết quân qua sông, ván đấu sẽ được &lt;b&gt;xử Hòa&lt;/b&gt;.</t>
+        </is>
+      </c>
+    </row>
+    <row r="371" ht="17" customHeight="1">
+      <c r="A371" s="2" t="inlineStr">
+        <is>
+          <t>guide.result.paragraph5</t>
+        </is>
+      </c>
+      <c r="B371" s="2" t="inlineStr">
+        <is>
+          <t>Within 40 moves, if there is no capture and no Soldier advances by one square, the game is declared a &lt;b&gt;draw&lt;/b&gt;.</t>
+        </is>
+      </c>
+      <c r="C371" s="2" t="inlineStr">
+        <is>
+          <t>Trong vòng 40 nước nếu không phát sinh nước bắt quân, Tốt không tiến 1 ô thì ván đấu sẽ được &lt;b&gt;xử Hòa&lt;/b&gt;.</t>
+        </is>
+      </c>
+    </row>
+    <row r="372" ht="17" customHeight="1">
+      <c r="A372" s="2" t="inlineStr">
+        <is>
+          <t>extra-money.lucky-wheel.title</t>
+        </is>
+      </c>
+      <c r="B372" s="2" t="inlineStr">
+        <is>
+          <t>Lucky Wheel</t>
+        </is>
+      </c>
+      <c r="C372" s="2" t="inlineStr">
+        <is>
+          <t>Vòng quay may mắn</t>
+        </is>
+      </c>
+    </row>
+    <row r="373" ht="17" customHeight="1">
+      <c r="A373" s="2" t="inlineStr">
+        <is>
+          <t>extra-money.lucky-wheel.description</t>
+        </is>
+      </c>
+      <c r="B373" s="2" t="inlineStr">
+        <is>
+          <t>Spin the wheel to earn money! Click the spin button in the middle of the wheel to try your luck.</t>
+        </is>
+      </c>
+      <c r="C373" s="2" t="inlineStr">
+        <is>
+          <t>Quay vòng để kiếm tiền! Bấm nút Quay ở giữa vòng quay để thử vận may của bạn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="374" ht="17" customHeight="1">
+      <c r="A374" s="2" t="inlineStr">
+        <is>
+          <t>extra-money.lucky-wheel.spin-button</t>
+        </is>
+      </c>
+      <c r="B374" s="2" t="inlineStr">
+        <is>
+          <t>Spin</t>
+        </is>
+      </c>
+      <c r="C374" s="2" t="inlineStr">
+        <is>
+          <t>Quay</t>
+        </is>
+      </c>
+    </row>
+    <row r="375" ht="17" customHeight="1">
+      <c r="A375" s="2" t="inlineStr">
+        <is>
+          <t>extra-money.lucky-wheel.reward-placeholder</t>
+        </is>
+      </c>
+      <c r="B375" s="2" t="inlineStr">
+        <is>
+          <t>Click Spin to get started</t>
+        </is>
+      </c>
+      <c r="C375" s="2" t="inlineStr">
+        <is>
+          <t>Nhấp Quay để bắt đầu</t>
+        </is>
+      </c>
+    </row>
+    <row r="376" ht="17" customHeight="1">
+      <c r="A376" s="2" t="inlineStr">
+        <is>
+          <t>extra-money.title</t>
+        </is>
+      </c>
+      <c r="B376" s="2" t="inlineStr">
+        <is>
+          <t>Daily tasks</t>
+        </is>
+      </c>
+      <c r="C376" s="2" t="inlineStr">
+        <is>
+          <t>Kiếm tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="377" ht="17" customHeight="1">
+      <c r="A377" s="2" t="inlineStr">
+        <is>
+          <t>extra-money.tab.lucky-wheel</t>
+        </is>
+      </c>
+      <c r="B377" s="2" t="inlineStr">
+        <is>
+          <t>Lucky Wheel</t>
+        </is>
+      </c>
+      <c r="C377" s="2" t="inlineStr">
+        <is>
+          <t>Vòng Quay May Mắn</t>
+        </is>
+      </c>
+    </row>
+    <row r="378" ht="17" customHeight="1">
+      <c r="A378" s="2" t="inlineStr">
+        <is>
+          <t>extra-money.tab.bonus-coin</t>
+        </is>
+      </c>
+      <c r="B378" s="2" t="inlineStr">
+        <is>
+          <t>Bonus Coin</t>
+        </is>
+      </c>
+      <c r="C378" s="2" t="inlineStr">
+        <is>
+          <t>Xu Thưởng</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>extra-money.tab.daily-bonus</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Daily Bonus</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>Thưởng hàng ngày</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>extra-money.bonus-coin.subtitle</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Watch a short video to earn free coin</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>Xem video ngắn để nhận xu miễn phí</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>extra-money.bonus-coin.next-in</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>Next in:</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>Lượt kế tiếp:</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>extra-money.bonus-coin.coin-unit</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>coin</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>xu</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>extra-money.bonus-coin.watch-video</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Watch video</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>Xem video</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>extra-money.daily-bonus.subtitle</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Login 7 days in a row to earn 4000 coin</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>Đăng nhập 7 ngày liên tiếp để nhận 4000 xu</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>extra-money.daily-bonus.day</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>Ngày</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>extra-money.reward-ad.loading</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>Loading ad...</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>Đang tải quảng cáo...</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>extra-money.reward-ad.error</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Could not load the ad. Please try again.</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>Không tải được quảng cáo. Vui lòng thử lại.</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>extra-money.reward-ad.retry</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Try again</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>Thử lại</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>extra-money.reward-ad.close</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>Đóng</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>profile.button.save</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>Save</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>Lưu</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
           <t>profile.button.cancel</t>
         </is>
       </c>
-      <c r="B359" s="2" t="inlineStr">
+      <c r="B391" t="inlineStr">
         <is>
           <t>Cancel</t>
         </is>
       </c>
-      <c r="C359" s="2" t="inlineStr">
+      <c r="C391" t="inlineStr">
         <is>
           <t>Huỷ</t>
         </is>
       </c>
     </row>
-    <row r="360" ht="18" customHeight="1">
-      <c r="A360" s="2" t="inlineStr"/>
-      <c r="B360" s="2" t="inlineStr"/>
-      <c r="C360" s="2" t="inlineStr"/>
-    </row>
-    <row r="361" ht="17" customHeight="1">
-      <c r="A361" s="2" t="inlineStr"/>
-      <c r="B361" s="2" t="inlineStr"/>
-      <c r="C361" s="2" t="inlineStr"/>
-    </row>
-    <row r="362" ht="17" customHeight="1">
-      <c r="A362" s="2" t="inlineStr"/>
-      <c r="B362" s="2" t="inlineStr"/>
-      <c r="C362" s="2" t="inlineStr"/>
-    </row>
-    <row r="363" ht="17" customHeight="1">
-      <c r="A363" s="2" t="inlineStr"/>
-      <c r="B363" s="2" t="inlineStr"/>
-      <c r="C363" s="2" t="inlineStr"/>
-    </row>
-    <row r="364" ht="17" customHeight="1">
-      <c r="A364" s="2" t="inlineStr"/>
-      <c r="B364" s="2" t="inlineStr"/>
-      <c r="C364" s="2" t="inlineStr"/>
-    </row>
-    <row r="365" ht="17" customHeight="1">
-      <c r="A365" s="2" t="inlineStr"/>
-      <c r="B365" s="2" t="inlineStr"/>
-      <c r="C365" s="2" t="inlineStr"/>
-    </row>
-    <row r="366" ht="17" customHeight="1">
-      <c r="A366" s="2" t="inlineStr"/>
-      <c r="B366" s="2" t="inlineStr"/>
-      <c r="C366" s="2" t="inlineStr"/>
-    </row>
-    <row r="367" ht="17" customHeight="1">
-      <c r="A367" s="2" t="inlineStr"/>
-      <c r="B367" s="2" t="inlineStr"/>
-      <c r="C367" s="2" t="inlineStr"/>
-    </row>
-    <row r="368" ht="17" customHeight="1">
-      <c r="A368" s="2" t="inlineStr"/>
-      <c r="B368" s="2" t="inlineStr"/>
-      <c r="C368" s="2" t="inlineStr"/>
-    </row>
-    <row r="369" ht="17" customHeight="1">
-      <c r="A369" s="2" t="inlineStr"/>
-      <c r="B369" s="2" t="inlineStr"/>
-      <c r="C369" s="2" t="inlineStr"/>
-    </row>
-    <row r="370" ht="17" customHeight="1">
-      <c r="A370" s="2" t="inlineStr"/>
-      <c r="B370" s="2" t="inlineStr"/>
-      <c r="C370" s="2" t="inlineStr"/>
-    </row>
-    <row r="371" ht="17" customHeight="1">
-      <c r="A371" s="2" t="inlineStr"/>
-      <c r="B371" s="2" t="inlineStr"/>
-      <c r="C371" s="2" t="inlineStr"/>
-    </row>
-    <row r="372" ht="17" customHeight="1">
-      <c r="A372" s="2" t="inlineStr"/>
-      <c r="B372" s="2" t="inlineStr"/>
-      <c r="C372" s="2" t="inlineStr"/>
-    </row>
-    <row r="373" ht="17" customHeight="1">
-      <c r="A373" s="2" t="inlineStr"/>
-      <c r="B373" s="2" t="inlineStr"/>
-      <c r="C373" s="2" t="inlineStr"/>
-    </row>
-    <row r="374" ht="17" customHeight="1">
-      <c r="A374" s="2" t="inlineStr"/>
-      <c r="B374" s="2" t="inlineStr"/>
-      <c r="C374" s="2" t="inlineStr"/>
-    </row>
-    <row r="375" ht="17" customHeight="1">
-      <c r="A375" s="2" t="inlineStr"/>
-      <c r="B375" s="2" t="inlineStr"/>
-      <c r="C375" s="2" t="inlineStr"/>
-    </row>
-    <row r="376" ht="17" customHeight="1">
-      <c r="A376" s="2" t="inlineStr"/>
-      <c r="B376" s="2" t="inlineStr"/>
-      <c r="C376" s="2" t="inlineStr"/>
-    </row>
-    <row r="377" ht="17" customHeight="1">
-      <c r="A377" s="2" t="inlineStr"/>
-      <c r="B377" s="2" t="inlineStr"/>
-      <c r="C377" s="2" t="inlineStr"/>
-    </row>
-    <row r="378" ht="17" customHeight="1">
-      <c r="A378" s="2" t="n"/>
-      <c r="B378" s="2" t="n"/>
-      <c r="C378" s="2" t="n"/>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>change-password.title</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Change password</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>Đổi mật khẩu</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>change-password.current.label</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>Current password</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>Mật khẩu hiện tại</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>change-password.current.placeholder</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Enter current password</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>Nhập mật khẩu hiện tại</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>change-password.new.label</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>New password</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>Mật khẩu mới</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>change-password.new.placeholder</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Enter new password</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>Nhập mật khẩu mới</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>change-password.confirm.label</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>Confirm new password</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>Xác nhận mật khẩu mới</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>change-password.confirm.placeholder</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Re-enter new password</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>Nhập lại mật khẩu mới</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>change-password.confirm.mismatch</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Passwords do not match</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>Mật khẩu xác nhận không khớp</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>change-password.show</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Show password</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>Hiện mật khẩu</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>change-password.hide</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Hide password</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>Ẩn mật khẩu</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>change-password.submit</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Change password</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>Đổi mật khẩu</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>change-password.submitting</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Changing...</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>Đang đổi...</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>change-password.messages.success</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>Password changed successfully</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>Đổi mật khẩu thành công</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>change-password.messages.missing-fields</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>Please fill in all fields</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>Vui lòng nhập đầy đủ thông tin</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>change-password.messages.weak-password</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>New password does not meet the requirements</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>Mật khẩu mới không đạt yêu cầu</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>change-password.messages.same-as-current</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>New password must be different from the current one</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>Mật khẩu mới phải khác mật khẩu hiện tại</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>change-password.messages.incorrect-current-password</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>Current password is incorrect</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>Mật khẩu hiện tại không đúng</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>change-password.messages.user-not-found</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>User not found</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>Không tìm thấy người dùng</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>change-password.messages.unauthorized</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>Session expired. Please sign in again.</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>Phiên đăng nhập đã hết hạn. Vui lòng đăng nhập lại.</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>change-password.messages.internal-server-error</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Something went wrong. Please try again.</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>Đã có lỗi xảy ra. Vui lòng thử lại.</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr"/>
+      <c r="B412" t="inlineStr"/>
+      <c r="C412" t="inlineStr"/>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr"/>
+      <c r="B413" t="inlineStr"/>
+      <c r="C413" t="inlineStr"/>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr"/>
+      <c r="B414" t="inlineStr"/>
+      <c r="C414" t="inlineStr"/>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr"/>
+      <c r="B415" t="inlineStr"/>
+      <c r="C415" t="inlineStr"/>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr"/>
+      <c r="B416" t="inlineStr"/>
+      <c r="C416" t="inlineStr"/>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr"/>
+      <c r="B417" t="inlineStr"/>
+      <c r="C417" t="inlineStr"/>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr"/>
+      <c r="B418" t="inlineStr"/>
+      <c r="C418" t="inlineStr"/>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr"/>
+      <c r="B419" t="inlineStr"/>
+      <c r="C419" t="inlineStr"/>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr"/>
+      <c r="B420" t="inlineStr"/>
+      <c r="C420" t="inlineStr"/>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr"/>
+      <c r="B421" t="inlineStr"/>
+      <c r="C421" t="inlineStr"/>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr"/>
+      <c r="B422" t="inlineStr"/>
+      <c r="C422" t="inlineStr"/>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr"/>
+      <c r="B423" t="inlineStr"/>
+      <c r="C423" t="inlineStr"/>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr"/>
+      <c r="B424" t="inlineStr"/>
+      <c r="C424" t="inlineStr"/>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr"/>
+      <c r="B425" t="inlineStr"/>
+      <c r="C425" t="inlineStr"/>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr"/>
+      <c r="B426" t="inlineStr"/>
+      <c r="C426" t="inlineStr"/>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr"/>
+      <c r="B427" t="inlineStr"/>
+      <c r="C427" t="inlineStr"/>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr"/>
+      <c r="B428" t="inlineStr"/>
+      <c r="C428" t="inlineStr"/>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr"/>
+      <c r="B429" t="inlineStr"/>
+      <c r="C429" t="inlineStr"/>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr"/>
+      <c r="B430" t="inlineStr"/>
+      <c r="C430" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tools/languages.xlsx
+++ b/tools/languages.xlsx
@@ -325,7 +325,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C430"/>
+  <dimension ref="A1:C427"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -472,170 +472,170 @@
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>common.date.yesterday</t>
+          <t>common.date.today</t>
         </is>
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>Yesterday</t>
+          <t>Today</t>
         </is>
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>Hôm qua</t>
+          <t>Hôm nay</t>
         </is>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>common.date.mon</t>
+          <t>common.date.yesterday</t>
         </is>
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Yesterday</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>Thứ 2</t>
+          <t>Hôm qua</t>
         </is>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>common.date.tue</t>
+          <t>common.date.mon</t>
         </is>
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>Thứ 3</t>
+          <t>Thứ 2</t>
         </is>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>common.date.wed</t>
+          <t>common.date.tue</t>
         </is>
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>Thứ 4</t>
+          <t>Thứ 3</t>
         </is>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>common.date.thu</t>
+          <t>common.date.wed</t>
         </is>
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>Thứ 5</t>
+          <t>Thứ 4</t>
         </is>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>common.date.fri</t>
+          <t>common.date.thu</t>
         </is>
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>Thứ 6</t>
+          <t>Thứ 5</t>
         </is>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>common.date.sat</t>
+          <t>common.date.fri</t>
         </is>
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>Thứ 7</t>
+          <t>Thứ 6</t>
         </is>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>common.date.sun</t>
+          <t>common.date.sat</t>
         </is>
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C16" s="1" t="inlineStr">
         <is>
-          <t>Chủ nhật</t>
+          <t>Thứ 7</t>
         </is>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>page.home.title</t>
+          <t>common.date.sun</t>
         </is>
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C17" s="1" t="inlineStr">
         <is>
-          <t>Trang chủ</t>
+          <t>Chủ nhật</t>
         </is>
       </c>
     </row>
     <row r="18" ht="17" customHeight="1">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>page.history.title</t>
+          <t>page.home.title</t>
         </is>
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>History</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="C18" s="1" t="inlineStr">
         <is>
-          <t>Lịch sử</t>
+          <t>Trang chủ</t>
         </is>
       </c>
     </row>
@@ -659,2256 +659,2256 @@
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>page.history.point-label</t>
+          <t>page.replay.title</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Points:</t>
+          <t>Game Replay</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Điểm:</t>
+          <t>Xem lại ván đấu</t>
         </is>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>page.about.title</t>
+          <t>page.replay.no-moves</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>About</t>
+          <t>No moves to replay</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Thông tin</t>
+          <t>Không có nước đi để xem lại</t>
         </is>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>menu.app-name</t>
+          <t>page.replay.play</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Xiangqi</t>
+          <t>Play</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Cờ tướng</t>
+          <t>Phát</t>
         </is>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>menu.profile</t>
+          <t>page.replay.pause</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>Pause</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Trang cá nhân</t>
+          <t>Tạm dừng</t>
         </is>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>menu.messages</t>
+          <t>menu.app-name</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Message</t>
+          <t>Xiangqi</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Tin nhắn</t>
+          <t>Cờ tướng</t>
         </is>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>menu.change-password</t>
+          <t>menu.profile</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Change password</t>
+          <t>Profile</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Đổi mật khẩu</t>
+          <t>Trang cá nhân</t>
         </is>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>menu.guide</t>
+          <t>menu.messages</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Guide</t>
+          <t>Message</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Luật chơi</t>
+          <t>Tin nhắn</t>
         </is>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>menu.announce</t>
+          <t>menu.change-password</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Announcement</t>
+          <t>Change password</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Thông báo</t>
+          <t>Đổi mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>menu.extra</t>
+          <t>menu.guide</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Daily tasks</t>
+          <t>Guide</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Kiếm tiền</t>
+          <t>Luật chơi</t>
         </is>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>menu.setting.button</t>
+          <t>menu.announce</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Announcement</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Cài đặt</t>
+          <t>Thông báo</t>
         </is>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>menu.app-name</t>
+          <t>menu.extra</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Xiangqi</t>
+          <t>Daily tasks</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Cờ tướng</t>
+          <t>Kiếm tiền</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>menu.home</t>
+          <t>menu.setting.button</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Trang chủ</t>
+          <t>Cài đặt</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>menu.expired</t>
+          <t>menu.app-name</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Set expired</t>
+          <t>Xiangqi</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Hết hạn token</t>
+          <t>Cờ tướng</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>menu.logout</t>
+          <t>menu.home</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Logout</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Đăng xuất</t>
+          <t>Trang chủ</t>
         </is>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>menu.rooms</t>
+          <t>menu.expired</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Rooms</t>
+          <t>Set expired</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Trò chơi</t>
+          <t>Hết hạn token</t>
         </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>announce.title</t>
+          <t>menu.logout</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Announcement</t>
+          <t>Logout</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Thông báo</t>
+          <t>Đăng xuất</t>
         </is>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>announce.placeholder</t>
+          <t>announce.title</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Type an announcement...</t>
+          <t>Announcement</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Nhập thông báo...</t>
+          <t>Thông báo</t>
         </is>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>announce.empty</t>
+          <t>announce.placeholder</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>No announcements yet</t>
+          <t>Type an announcement...</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Chưa có thông báo nào</t>
+          <t>Nhập thông báo...</t>
         </is>
       </c>
     </row>
     <row r="38" ht="36" customHeight="1">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>announce.loading-older</t>
+          <t>announce.empty</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Loading older announcements...</t>
+          <t>No announcements yet</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Đang tải thông báo cũ hơn...</t>
+          <t>Chưa có thông báo nào</t>
         </is>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>archivement.title-01</t>
+          <t>announce.loading-older</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Checkmate an opponent who still has 13 or more pieces</t>
+          <t>Loading older announcements...</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Chiếu bí khi đối thủ vẫn còn &gt;= 13 quân</t>
+          <t>Đang tải thông báo cũ hơn...</t>
         </is>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>archivement.title-02</t>
+          <t>achievement.title-01</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Win your first game</t>
+          <t>Checkmate an opponent who still has 13 or more pieces</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Thắng trận đầu khi chơi game</t>
+          <t>Chiếu bí khi đối thủ vẫn còn &gt;= 13 quân</t>
         </is>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>archivement.title-03</t>
+          <t>achievement.title-02</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Leave your opponent with no legal moves</t>
+          <t>Win your first game</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Đánh cho đối thủ không còn nước đi</t>
+          <t>Thắng trận đầu khi chơi game</t>
         </is>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>archivement.title-04</t>
+          <t>achievement.title-03</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Defeat opponents of equal or higher rank in 10 games</t>
+          <t>Leave your opponent with no legal moves</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Thắng đối thủ cùng hoặc hơn đẳng cấp 10 ván</t>
+          <t>Đánh cho đối thủ không còn nước đi</t>
         </is>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>archivement.title-05</t>
+          <t>achievement.title-04</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Hold a draw with only your king remaining</t>
+          <t>Defeat opponents of equal or higher rank in 10 games</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Cầm hoà đối thủ khi chỉ còn tướng</t>
+          <t>Thắng đối thủ cùng hoặc hơn đẳng cấp 10 ván</t>
         </is>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>archivement.title-06</t>
+          <t>achievement.title-05</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Win 100 games</t>
+          <t>Hold a draw with only your king remaining</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Thắng 100 trận</t>
+          <t>Cầm hoà đối thủ khi chỉ còn tướng</t>
         </is>
       </c>
     </row>
     <row r="45" ht="36" customHeight="1">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>archivement.title-07</t>
+          <t>achievement.title-06</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Draw 50 games</t>
+          <t>Win 100 games</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Hoà 50 trận</t>
+          <t>Thắng 100 trận</t>
         </is>
       </c>
     </row>
     <row r="46" ht="36" customHeight="1">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>archivement.title-08</t>
+          <t>achievement.title-07</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Checkmate an opponent with only 1 attacking piece remaining</t>
+          <t>Draw 50 games</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Chiếu bí khi đối thủ khi chỉ còn 1 quân tấn công</t>
+          <t>Hoà 50 trận</t>
         </is>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>archivement.title-09</t>
+          <t>achievement.title-08</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Checkmate an opponent with only a knight remaining</t>
+          <t>Checkmate an opponent with only 1 attacking piece remaining</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Chiếu bí khi đối thủ khi chỉ còn mã</t>
+          <t>Chiếu bí khi đối thủ khi chỉ còn 1 quân tấn công</t>
         </is>
       </c>
     </row>
     <row r="48" ht="36" customHeight="1">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>archivement.title-10</t>
+          <t>achievement.title-09</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Checkmate an opponent with only a pawn remaining</t>
+          <t>Checkmate an opponent with only a knight remaining</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Chiếu bí khi đối thủ khi chỉ còn tốt</t>
+          <t>Chiếu bí khi đối thủ khi chỉ còn mã</t>
         </is>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>archivement.title-11</t>
+          <t>achievement.title-10</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Checkmate an opponent with only a cannon remaining</t>
+          <t>Checkmate an opponent with only a pawn remaining</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Chiếu bí khi đối thủ khi chỉ còn pháo</t>
+          <t>Chiếu bí khi đối thủ khi chỉ còn tốt</t>
         </is>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>archivement.title-12</t>
+          <t>achievement.title-11</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Defeat opponents with master rank in 50 games</t>
+          <t>Checkmate an opponent with only a cannon remaining</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Thắng đối thủ có đẳng cấp kỳ thủ 50 ván</t>
+          <t>Chiếu bí khi đối thủ khi chỉ còn pháo</t>
         </is>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>chat.conversation.you</t>
+          <t>achievement.title-12</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>You</t>
+          <t>Defeat opponents with master rank in 50 games</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Bạn</t>
+          <t>Thắng đối thủ có đẳng cấp kỳ thủ 50 ván</t>
         </is>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>chat.conversation.new</t>
+          <t>achievement.tab-title</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>New conversation</t>
+          <t>Achievements</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Cuộc trò chuyện mới</t>
+          <t>Thành tựu</t>
         </is>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>chat.messages.unread</t>
+          <t>achievement.messages.success</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Unread messages</t>
+          <t>Success</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Tin nhắn chưa đọc</t>
+          <t>Thành công</t>
         </is>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>search.user.title</t>
+          <t>achievement.messages.invalid-user-id</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Search user</t>
+          <t>Invalid user ID</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Tìm kiếm</t>
+          <t>ID người dùng không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>search.user.placeholder</t>
+          <t>achievement.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Search user...</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Tìm kiếm người dùng...</t>
+          <t>Lỗi máy chủ</t>
         </is>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>search.user.no-results</t>
+          <t>chat.conversation.you</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>No users found</t>
+          <t>You</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy người dùng</t>
+          <t>Bạn</t>
         </is>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>search.button.search</t>
+          <t>chat.messages.unread</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>Unread messages</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Tìm kiếm</t>
+          <t>Tin nhắn chưa đọc</t>
         </is>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>dashboard.page.title</t>
+          <t>search.user.title</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Room list</t>
+          <t>Search user</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Danh sách phòng</t>
+          <t>Tìm kiếm</t>
         </is>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>dashboard.filters.all</t>
+          <t>search.user.placeholder</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Search user...</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Tất cả</t>
+          <t>Tìm kiếm người dùng...</t>
         </is>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>dashboard.filters.available</t>
+          <t>search.user.no-results</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Available</t>
+          <t>No users found</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Chờ</t>
+          <t>Không tìm thấy người dùng</t>
         </is>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>dashboard.filters.playing</t>
+          <t>search.button.search</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Playing</t>
+          <t>Search</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Đang chơi</t>
+          <t>Tìm kiếm</t>
         </is>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>dashboard.feedback.empty</t>
+          <t>dashboard.page.title</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>No room tables match the selected filter.</t>
+          <t>Room list</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Không có bàn chơi phù hợp với bộ lọc đã chọn.</t>
+          <t>Danh sách phòng</t>
         </is>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>dashboard.feedback.error</t>
+          <t>dashboard.filters.all</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Unable to load room tables.</t>
+          <t>All</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Không tải được danh sách phòng chơi.</t>
+          <t>Tất cả</t>
         </is>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>dashboard.status.unknown</t>
+          <t>dashboard.filters.available</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Available</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Không xác định</t>
+          <t>Chờ</t>
         </is>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>dashboard.feedback.result-count</t>
+          <t>dashboard.filters.playing</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Found {{count}} tables</t>
+          <t>Playing</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Tìm thấy {{count}} bàn chơi</t>
+          <t>Đang chơi</t>
         </is>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>dashboard.room.create</t>
+          <t>dashboard.feedback.empty</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Create room</t>
+          <t>No room tables match the selected filter.</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Tạo phòng chơi</t>
+          <t>Không có bàn chơi phù hợp với bộ lọc đã chọn.</t>
         </is>
       </c>
     </row>
     <row r="67" ht="18" customHeight="1">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>dashboard.popup.piece-selection</t>
+          <t>dashboard.feedback.error</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Select team</t>
+          <t>Unable to load room tables.</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Chọn quân</t>
+          <t>Không tải được danh sách phòng chơi.</t>
         </is>
       </c>
     </row>
     <row r="68" ht="18" customHeight="1">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>dashboard.popup.red-first</t>
+          <t>dashboard.status.unknown</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Red first</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Đỏ tiên</t>
+          <t>Không xác định</t>
         </is>
       </c>
     </row>
     <row r="69" ht="18" customHeight="1">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>dashboard.popup.pve-mode</t>
+          <t>dashboard.room.create</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>PVE mode</t>
+          <t>Create room</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Chơi với máy</t>
+          <t>Tạo phòng chơi</t>
         </is>
       </c>
     </row>
     <row r="70" ht="18" customHeight="1">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>dashboard.popup.bet-amount</t>
+          <t>dashboard.popup.piece-selection</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Bet amount</t>
+          <t>Select team</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Giá trị cược</t>
+          <t>Chọn quân</t>
         </is>
       </c>
     </row>
     <row r="71" ht="18" customHeight="1">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>dashboard.popup.room-name-label</t>
+          <t>dashboard.popup.red-first</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Room table name</t>
+          <t>Red first</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Tên phòng chơi</t>
+          <t>Đỏ tiên</t>
         </is>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>dashboard.popup.room-name-helptext</t>
+          <t>dashboard.popup.pve-mode</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>is required</t>
+          <t>PVE mode</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>không được để trống</t>
+          <t>Chơi với máy</t>
         </is>
       </c>
     </row>
     <row r="73" ht="18" customHeight="1">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>dashboard.popup.play</t>
+          <t>dashboard.popup.bet-amount</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Play</t>
+          <t>Bet amount</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>Chơi</t>
+          <t>Giá trị cược</t>
         </is>
       </c>
     </row>
     <row r="74" ht="18" customHeight="1">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>dashboard.popup.view</t>
+          <t>dashboard.popup.room-name-label</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>View</t>
+          <t>Room table name</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>Xem</t>
+          <t>Tên phòng chơi</t>
         </is>
       </c>
     </row>
     <row r="75" ht="18" customHeight="1">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>settings.header</t>
+          <t>dashboard.popup.room-name-helptext</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>is required</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>Cài đặt</t>
+          <t>không được để trống</t>
         </is>
       </c>
     </row>
     <row r="76" ht="18" customHeight="1">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>settings.language</t>
+          <t>dashboard.popup.play</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>Play</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>Ngôn ngữ</t>
+          <t>Chơi</t>
         </is>
       </c>
     </row>
     <row r="77" ht="18" customHeight="1">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>settings.dark-mode</t>
+          <t>dashboard.popup.view</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Dark mode</t>
+          <t>View</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Chế độ tối</t>
+          <t>Xem</t>
         </is>
       </c>
     </row>
     <row r="78" ht="18" customHeight="1">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>settings.debug-mode</t>
+          <t>settings.header</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Debug mode</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Chế độ test</t>
+          <t>Cài đặt</t>
         </is>
       </c>
     </row>
     <row r="79" ht="18" customHeight="1">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>settings.connected-accounts.label</t>
+          <t>settings.language</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Connected accounts</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản liên kết</t>
+          <t>Ngôn ngữ</t>
         </is>
       </c>
     </row>
     <row r="80" ht="18" customHeight="1">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>settings.connected-accounts.link-facebook</t>
+          <t>settings.dark-mode</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Link Facebook</t>
+          <t>Dark mode</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Liên kết Facebook</t>
+          <t>Chế độ tối</t>
         </is>
       </c>
     </row>
     <row r="81" ht="18" customHeight="1">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>settings.connected-accounts.unlink-facebook</t>
+          <t>settings.debug-mode</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Unlink Facebook</t>
+          <t>Debug mode</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Huỷ liên kết Facebook</t>
+          <t>Chế độ test</t>
         </is>
       </c>
     </row>
     <row r="82" ht="18" customHeight="1">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>settings.connected-accounts.link-success</t>
+          <t>settings.connected-accounts.label</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Facebook linked successfully</t>
+          <t>Connected accounts</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Đã liên kết Facebook</t>
+          <t>Tài khoản liên kết</t>
         </is>
       </c>
     </row>
     <row r="83" ht="18" customHeight="1">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>settings.connected-accounts.unlink-success</t>
+          <t>settings.connected-accounts.link-facebook</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Facebook unlinked</t>
+          <t>Link Facebook</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Đã huỷ liên kết Facebook</t>
+          <t>Liên kết Facebook</t>
         </is>
       </c>
     </row>
     <row r="84" ht="18" customHeight="1">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>settings.connected-accounts.link-error</t>
+          <t>settings.connected-accounts.unlink-facebook</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Could not update Facebook link</t>
+          <t>Unlink Facebook</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Không cập nhật được liên kết Facebook</t>
+          <t>Huỷ liên kết Facebook</t>
         </is>
       </c>
     </row>
     <row r="85" ht="18" customHeight="1">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>settings.close</t>
+          <t>settings.connected-accounts.link-success</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Close</t>
+          <t>Facebook linked successfully</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Đóng</t>
+          <t>Đã liên kết Facebook</t>
         </is>
       </c>
     </row>
     <row r="86" ht="18" customHeight="1">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>settings.change-password</t>
+          <t>settings.connected-accounts.unlink-success</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Change password</t>
+          <t>Facebook unlinked</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Đổi mật khẩu</t>
+          <t>Đã huỷ liên kết Facebook</t>
         </is>
       </c>
     </row>
     <row r="87" ht="18" customHeight="1">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>popup.alert.title</t>
+          <t>settings.connected-accounts.link-error</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Could not update Facebook link</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Cảnh báo</t>
+          <t>Không cập nhật được liên kết Facebook</t>
         </is>
       </c>
     </row>
     <row r="88" ht="18" customHeight="1">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>popup.confirm.title</t>
+          <t>settings.close</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Confirm</t>
+          <t>Close</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Xác nhận</t>
+          <t>Đóng</t>
         </is>
       </c>
     </row>
     <row r="89" ht="18" customHeight="1">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>popup.confirm.ok</t>
+          <t>popup.alert.title</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Ok</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Ok</t>
+          <t>Cảnh báo</t>
         </is>
       </c>
     </row>
     <row r="90" ht="18" customHeight="1">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>popup.confirm.cancel</t>
+          <t>popup.confirm.title</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Confirm</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Huỷ</t>
+          <t>Xác nhận</t>
         </is>
       </c>
     </row>
     <row r="91" ht="18" customHeight="1">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>home.turn.title</t>
+          <t>popup.confirm.ok</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Turn</t>
+          <t>Ok</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Lượt đánh</t>
+          <t>Ok</t>
         </is>
       </c>
     </row>
     <row r="92" ht="18" customHeight="1">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>game.general.captured</t>
+          <t>popup.confirm.cancel</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>General has been captured. Room over</t>
+          <t>Cancel</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Tướng đã bị bắt. Game kết thúc</t>
+          <t>Huỷ</t>
         </is>
       </c>
     </row>
     <row r="93" ht="18" customHeight="1">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>game.general.in-check</t>
+          <t>game.general.captured</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Your general is under attack</t>
+          <t>General has been captured. Room over</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Tướng của bạn đang bị chiếu</t>
+          <t>Tướng đã bị bắt. Game kết thúc</t>
         </is>
       </c>
     </row>
     <row r="94" ht="18" customHeight="1">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>room.bot-difficulty.title</t>
+          <t>game.general.in-check</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Select Bot Difficulty</t>
+          <t>Your general is under attack</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Chọn độ khó của Bot</t>
+          <t>Tướng của bạn đang bị chiếu</t>
         </is>
       </c>
     </row>
     <row r="95" ht="18" customHeight="1">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>room.bot-difficulty.beginner</t>
+          <t>game.label.win</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Beginner</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Mới bắt đầu</t>
+          <t>Thắng</t>
         </is>
       </c>
     </row>
     <row r="96" ht="18" customHeight="1">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>room.bot-difficulty.amateur</t>
+          <t>game.label.draw</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Amateur</t>
+          <t>Draw</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Nghiệp dư</t>
+          <t>Hoà</t>
         </is>
       </c>
     </row>
     <row r="97" ht="18" customHeight="1">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>room.bot-difficulty.intermediate</t>
+          <t>game.label.lose</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Intermediate</t>
+          <t>Lose</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Trung bình</t>
+          <t>Thua</t>
         </is>
       </c>
     </row>
     <row r="98" ht="18" customHeight="1">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>room.bot-difficulty.advanced</t>
+          <t>room.bot-difficulty.title</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Advanced</t>
+          <t>Select Bot Difficulty</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Nâng cao</t>
+          <t>Chọn độ khó của Bot</t>
         </is>
       </c>
     </row>
     <row r="99" ht="18" customHeight="1">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>room.bot-difficulty.master</t>
+          <t>room.bot-difficulty.beginner</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Master</t>
+          <t>Beginner</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Lão luyện</t>
+          <t>Mới bắt đầu</t>
         </is>
       </c>
     </row>
     <row r="100" ht="18" customHeight="1">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>login.page.title</t>
+          <t>room.bot-difficulty.amateur</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Login</t>
+          <t>Amateur</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập</t>
+          <t>Nghiệp dư</t>
         </is>
       </c>
     </row>
     <row r="101" ht="18" customHeight="1">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>login.form.title</t>
+          <t>room.bot-difficulty.intermediate</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Login</t>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập</t>
+          <t>Trung bình</t>
         </is>
       </c>
     </row>
     <row r="102" ht="18" customHeight="1">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>login.username.label</t>
+          <t>room.bot-difficulty.advanced</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>User name</t>
+          <t>Advanced</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Tên người dùng</t>
+          <t>Nâng cao</t>
         </is>
       </c>
     </row>
     <row r="103" ht="18" customHeight="1">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>login.username.placeholder</t>
+          <t>room.bot-difficulty.master</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>User name</t>
+          <t>Master</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Tên người dùng</t>
+          <t>Lão luyện</t>
         </is>
       </c>
     </row>
     <row r="104" ht="18" customHeight="1">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>login.password.label</t>
+          <t>login.page.title</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Password</t>
+          <t>Login</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Mật khẩu</t>
+          <t>Đăng nhập</t>
         </is>
       </c>
     </row>
     <row r="105" ht="18" customHeight="1">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>login.password.placeholder</t>
+          <t>login.form.title</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Password</t>
+          <t>Login</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Mật khẩu</t>
+          <t>Đăng nhập</t>
         </is>
       </c>
     </row>
     <row r="106" ht="18" customHeight="1">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>login.password.error1</t>
+          <t>login.username.label</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Password is required</t>
+          <t>User name</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Mật khẩu bắt buộc nhập</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="36" customHeight="1">
+          <t>Tên người dùng</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="18" customHeight="1">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>login.password.show</t>
+          <t>login.username.placeholder</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Show password</t>
+          <t>User name</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Hiện mật khẩu</t>
+          <t>Tên người dùng</t>
         </is>
       </c>
     </row>
     <row r="108" ht="18" customHeight="1">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>login.password.hide</t>
+          <t>login.password.label</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Hide password</t>
+          <t>Password</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Ẩn mật khẩu</t>
+          <t>Mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="109" ht="18" customHeight="1">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>login.form.error1</t>
+          <t>login.password.placeholder</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Login failed. Please check your credentials </t>
+          <t>Password</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập không thành công. Hãy kiểm tra lại</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="18" customHeight="1">
+          <t>Mật khẩu</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="36" customHeight="1">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>login.form.forgot-password</t>
+          <t>login.password.show</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Forgot password</t>
+          <t>Show password</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Quên mật khẩu</t>
+          <t>Hiện mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="111" ht="18" customHeight="1">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>login.form.register</t>
+          <t>login.password.hide</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Register</t>
+          <t>Hide password</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Đăng ký</t>
+          <t>Ẩn mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="112" ht="18" customHeight="1">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>login.form.submit</t>
+          <t>login.form.error1</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Login</t>
+          <t xml:space="preserve">Login failed. Please check your credentials </t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập</t>
+          <t>Đăng nhập không thành công. Hãy kiểm tra lại</t>
         </is>
       </c>
     </row>
     <row r="113" ht="18" customHeight="1">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>login.form.or</t>
+          <t>login.form.forgot-password</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>or</t>
+          <t>Forgot password</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>hoặc</t>
+          <t>Quên mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="114" ht="18" customHeight="1">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>login.google.load-error</t>
+          <t>login.form.register</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Could not load Google Sign-In</t>
+          <t>Register</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Không tải được đăng nhập Google</t>
+          <t>Đăng ký</t>
         </is>
       </c>
     </row>
     <row r="115" ht="18" customHeight="1">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>login.facebook.button</t>
+          <t>login.form.submit</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Sign-in with Facebook</t>
+          <t>Login</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập với Facebook</t>
+          <t>Đăng nhập</t>
         </is>
       </c>
     </row>
     <row r="116" ht="18" customHeight="1">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>login.messages.incorrect-login</t>
+          <t>login.form.or</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Invalid username or password</t>
+          <t>or</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Tên người dùng hoặc mật khẩu không hợp lệ</t>
+          <t>hoặc</t>
         </is>
       </c>
     </row>
     <row r="117" ht="18" customHeight="1">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>login.messages.internal-server-error</t>
+          <t>login.google.load-error</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Could not load Google Sign-In</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Không tải được đăng nhập Google</t>
         </is>
       </c>
     </row>
     <row r="118" ht="18" customHeight="1">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>login.messages.missing-credentials</t>
+          <t>login.facebook.button</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Username and password are required</t>
+          <t>Sign-in with Facebook</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Tên người dùng và mật khẩu là bắt buộc</t>
+          <t>Đăng nhập với Facebook</t>
         </is>
       </c>
     </row>
     <row r="119" ht="18" customHeight="1">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>login.messages.success</t>
+          <t>login.messages.incorrect-login</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Login successful</t>
+          <t>Invalid username or password</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập thành công</t>
+          <t>Tên người dùng hoặc mật khẩu không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="120" ht="18" customHeight="1">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>notfound.title</t>
+          <t>login.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Page Not Found</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Trang không tìm thấy</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="121" ht="18" customHeight="1">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>notfound.description</t>
+          <t>login.messages.missing-credentials</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>The page you are looking for does not exist or has been moved.</t>
+          <t>Username and password are required</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Trang bạn tìm kiếm không tồn tại hoặc đã được di chuyển.</t>
+          <t>Tên người dùng và mật khẩu là bắt buộc</t>
         </is>
       </c>
     </row>
     <row r="122" ht="18" customHeight="1">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>notfound.home</t>
+          <t>login.messages.success</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Go to Home</t>
+          <t>Login successful</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Về trang chủ</t>
+          <t>Đăng nhập thành công</t>
         </is>
       </c>
     </row>
     <row r="123" ht="18" customHeight="1">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>notfound.back</t>
+          <t>notfound.title</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>Go Back</t>
+          <t>Page Not Found</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>Quay lại</t>
+          <t>Trang không tìm thấy</t>
         </is>
       </c>
     </row>
     <row r="124" ht="18" customHeight="1">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>register.confirm-password.error1</t>
+          <t>notfound.description</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Confirm password does not match password</t>
+          <t>The page you are looking for does not exist or has been moved.</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Mật khẩu xác nhận không khớp với mật khẩu</t>
+          <t>Trang bạn tìm kiếm không tồn tại hoặc đã được di chuyển.</t>
         </is>
       </c>
     </row>
     <row r="125" ht="18" customHeight="1">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>register.confirm-password.label</t>
+          <t>notfound.home</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>Confirm Password</t>
+          <t>Go to Home</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Xác nhận mật khẩu</t>
+          <t>Về trang chủ</t>
         </is>
       </c>
     </row>
     <row r="126" ht="18" customHeight="1">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>register.confirm-password.placeholder</t>
+          <t>notfound.back</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Confirm Password</t>
+          <t>Go Back</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Xác nhận mật khẩu</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="36" customHeight="1">
+          <t>Quay lại</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="18" customHeight="1">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>register.display-name.label</t>
+          <t>register.confirm-password.error1</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>Display name</t>
+          <t>Confirm password does not match password</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Tên hiển thị</t>
+          <t>Mật khẩu xác nhận không khớp với mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="128" ht="18" customHeight="1">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>register.display-name.placeholder</t>
+          <t>register.confirm-password.label</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Display name</t>
+          <t>Confirm Password</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Tên hiển thị</t>
+          <t>Xác nhận mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="129" ht="18" customHeight="1">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>register.email.error1</t>
+          <t>register.confirm-password.placeholder</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>Invalid email format</t>
+          <t>Confirm Password</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Định dạng email không hợp lệ</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="18" customHeight="1">
+          <t>Xác nhận mật khẩu</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="36" customHeight="1">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>register.email.label</t>
+          <t>register.display-name.label</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Display name</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Tên hiển thị</t>
         </is>
       </c>
     </row>
     <row r="131" ht="18" customHeight="1">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>register.email.placeholder</t>
+          <t>register.display-name.placeholder</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Display name</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="36" customHeight="1">
+          <t>Tên hiển thị</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="18" customHeight="1">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>register.form.login</t>
+          <t>register.email.error1</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Back to login</t>
+          <t>Invalid email format</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Về trang đăng nhập</t>
+          <t>Định dạng email không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="133" ht="18" customHeight="1">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>register.form.submit</t>
+          <t>register.email.label</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>Register</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>Đăng ký</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="134" ht="18" customHeight="1">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>register.form.success</t>
+          <t>register.email.placeholder</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Registration successful. Redirecting to login...</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Đăng ký thành công. Đang chuyển hướng...</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="18" customHeight="1">
+          <t>Email</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="36" customHeight="1">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>register.form.title</t>
+          <t>register.form.login</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>Register</t>
+          <t>Back to login</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>Đăng ký</t>
+          <t>Về trang đăng nhập</t>
         </is>
       </c>
     </row>
     <row r="136" ht="18" customHeight="1">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>register.gender.female</t>
+          <t>register.form.submit</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Register</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Nữ</t>
+          <t>Đăng ký</t>
         </is>
       </c>
     </row>
     <row r="137" ht="18" customHeight="1">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>register.gender.label</t>
+          <t>register.form.success</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>Gender</t>
+          <t>Registration successful. Redirecting to login...</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>Giới tính</t>
+          <t>Đăng ký thành công. Đang chuyển hướng...</t>
         </is>
       </c>
     </row>
     <row r="138" ht="18" customHeight="1">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>register.gender.male</t>
+          <t>register.form.title</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Register</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Nam</t>
-        </is>
-      </c>
-    </row>
-    <row r="139" ht="36" customHeight="1">
+          <t>Đăng ký</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="18" customHeight="1">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>register.gender.select</t>
+          <t>register.gender.female</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>Select gender</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>Chọn giới tính</t>
+          <t>Nữ</t>
         </is>
       </c>
     </row>
     <row r="140" ht="18" customHeight="1">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>register.page.title</t>
+          <t>register.gender.label</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Register</t>
+          <t>Gender</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Đăng ký</t>
+          <t>Giới tính</t>
         </is>
       </c>
     </row>
     <row r="141" ht="18" customHeight="1">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>register.password.error1</t>
+          <t>register.gender.male</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>Password must be at least 8 characters and contain uppercase, lowercase, number, and special character</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>Mật khẩu phải có ít nhất 8 ký tự và chứa chữ hoa, chữ thường, số và ký tự đặc biệt</t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="18" customHeight="1">
+          <t>Nam</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="36" customHeight="1">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>register.password.hide</t>
+          <t>register.gender.select</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Hide password</t>
+          <t>Select gender</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Ẩn mật khẩu</t>
+          <t>Chọn giới tính</t>
         </is>
       </c>
     </row>
     <row r="143" ht="18" customHeight="1">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>register.password.label</t>
+          <t>register.page.title</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>Password</t>
+          <t>Register</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>Mật khẩu</t>
-        </is>
-      </c>
-    </row>
-    <row r="144" ht="36" customHeight="1">
+          <t>Đăng ký</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="18" customHeight="1">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>register.password.placeholder</t>
+          <t>register.password.error1</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Password</t>
+          <t>Password must be at least 8 characters and contain uppercase, lowercase, number, and special character</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Mật khẩu</t>
+          <t>Mật khẩu phải có ít nhất 8 ký tự và chứa chữ hoa, chữ thường, số và ký tự đặc biệt</t>
         </is>
       </c>
     </row>
     <row r="145" ht="18" customHeight="1">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>register.password.show</t>
+          <t>register.password.hide</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>Show password</t>
+          <t>Hide password</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>Hiện mật khẩu</t>
-        </is>
-      </c>
-    </row>
-    <row r="146" ht="36" customHeight="1">
+          <t>Ẩn mật khẩu</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="18" customHeight="1">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>register.username.error1</t>
+          <t>register.password.label</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>User name must contain only alphanumeric characters, underscore, and dot</t>
+          <t>Password</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Tên người dùng chỉ chứa ký tự chữ số, dấu gạch dưới và dấu chấm</t>
-        </is>
-      </c>
-    </row>
-    <row r="147" ht="18" customHeight="1">
+          <t>Mật khẩu</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="36" customHeight="1">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>register.username.label</t>
+          <t>register.password.placeholder</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>User name</t>
+          <t>Password</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Tên người dùng</t>
+          <t>Mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="148" ht="18" customHeight="1">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>register.username.placeholder</t>
+          <t>register.password.show</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>User name</t>
+          <t>Show password</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Tên người dùng</t>
-        </is>
-      </c>
-    </row>
-    <row r="149" ht="18" customHeight="1">
+          <t>Hiện mật khẩu</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="36" customHeight="1">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.page.title</t>
+          <t>register.username.error1</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>Forgot Password</t>
+          <t>User name must contain only alphanumeric characters, underscore, and dot</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>Quên mật khẩu</t>
+          <t>Tên người dùng chỉ chứa ký tự chữ số, dấu gạch dưới và dấu chấm</t>
         </is>
       </c>
     </row>
     <row r="150" ht="18" customHeight="1">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.form.title</t>
+          <t>register.username.label</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Forgot Password</t>
+          <t>User name</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Quên mật khẩu</t>
+          <t>Tên người dùng</t>
         </is>
       </c>
     </row>
     <row r="151" ht="18" customHeight="1">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.form.login</t>
+          <t>register.username.placeholder</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>Back to login</t>
+          <t>User name</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>Về trang đăng nhập</t>
+          <t>Tên người dùng</t>
         </is>
       </c>
     </row>
     <row r="152" ht="18" customHeight="1">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.form.submit</t>
+          <t>forgot-password.page.title</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Forgot password</t>
+          <t>Forgot Password</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -2920,1282 +2920,1282 @@
     <row r="153" ht="18" customHeight="1">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.form.success</t>
+          <t>forgot-password.form.title</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>Check your email for reset password details.</t>
+          <t>Forgot Password</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>Hãy kiểm tra email để xem thông tin đặt lại mật khẩu.</t>
+          <t>Quên mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="154" ht="18" customHeight="1">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.form.error1</t>
+          <t>forgot-password.form.login</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>Forgot password failed.</t>
+          <t>Back to login</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>Quên mật khẩu không thành công.</t>
+          <t>Về trang đăng nhập</t>
         </is>
       </c>
     </row>
     <row r="155" ht="18" customHeight="1">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>reset-password.page.title</t>
+          <t>forgot-password.form.submit</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>Reset Password</t>
+          <t>Forgot password</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>Đặt lại mật khẩu</t>
-        </is>
-      </c>
-    </row>
-    <row r="156" ht="36" customHeight="1">
+          <t>Quên mật khẩu</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="18" customHeight="1">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>reset-password.form.title</t>
+          <t>forgot-password.form.success</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>Reset your password</t>
+          <t>Check your email for reset password details.</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Đặt lại mật khẩu của bạn</t>
+          <t>Hãy kiểm tra email để xem thông tin đặt lại mật khẩu.</t>
         </is>
       </c>
     </row>
     <row r="157" ht="18" customHeight="1">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t>reset-password.form.submit</t>
+          <t>forgot-password.form.error1</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
+          <t>Forgot password failed.</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>Quên mật khẩu không thành công.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="18" customHeight="1">
+      <c r="A158" s="1" t="inlineStr">
+        <is>
+          <t>reset-password.page.title</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>Reset Password</t>
         </is>
       </c>
-      <c r="C157" s="2" t="inlineStr">
+      <c r="C158" s="2" t="inlineStr">
         <is>
           <t>Đặt lại mật khẩu</t>
         </is>
       </c>
     </row>
-    <row r="158" ht="36" customHeight="1">
-      <c r="A158" s="1" t="inlineStr">
-        <is>
-          <t>reset-password.form.error1</t>
-        </is>
-      </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>An error occurred while resetting your password. Please try again.</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>Có lỗi xảy ra khi đặt lại mật khẩu. Vui lòng thử lại.</t>
-        </is>
-      </c>
-    </row>
-    <row r="159" ht="18" customHeight="1">
+    <row r="159" ht="36" customHeight="1">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t>reset-password.form.invalid-token</t>
+          <t>reset-password.form.title</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>Invalid or expired reset password token</t>
+          <t>Reset your password</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>Token đặt lại mật khẩu không hợp lệ hoặc đã hết hạn</t>
+          <t>Đặt lại mật khẩu của bạn</t>
         </is>
       </c>
     </row>
     <row r="160" ht="18" customHeight="1">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>reset-password.form.success</t>
+          <t>reset-password.form.submit</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>Password reset successfully. Redirecting to login...</t>
+          <t>Reset Password</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Đặt lại mật khẩu thành công. Đang chuyển hướng đến đăng nhập...</t>
+          <t>Đặt lại mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="161" ht="36" customHeight="1">
       <c r="A161" s="1" t="inlineStr">
         <is>
-          <t>reset-password.action.back-to-login</t>
+          <t>reset-password.form.error1</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>Back to login</t>
+          <t>An error occurred while resetting your password. Please try again.</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>Quay lại trang chủ</t>
+          <t>Có lỗi xảy ra khi đặt lại mật khẩu. Vui lòng thử lại.</t>
         </is>
       </c>
     </row>
     <row r="162" ht="18" customHeight="1">
       <c r="A162" s="1" t="inlineStr">
         <is>
-          <t>reset-password.action.submit</t>
+          <t>reset-password.form.invalid-token</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>Reset password</t>
+          <t>Invalid or expired reset password token</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Đặt lại mật khẩu</t>
+          <t>Token đặt lại mật khẩu không hợp lệ hoặc đã hết hạn</t>
         </is>
       </c>
     </row>
     <row r="163" ht="18" customHeight="1">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t>auth-middleware.messages.invalid-token-payload</t>
+          <t>reset-password.form.success</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>Invalid token payload</t>
+          <t>Password reset successfully. Redirecting to login...</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>Payload của token không hợp lệ</t>
-        </is>
-      </c>
-    </row>
-    <row r="164" ht="18" customHeight="1">
+          <t>Đặt lại mật khẩu thành công. Đang chuyển hướng đến đăng nhập...</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="36" customHeight="1">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t>auth-middleware.messages.session-not-found</t>
+          <t>reset-password.action.back-to-login</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>Session not found</t>
+          <t>Back to login</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy phiên</t>
+          <t>Quay lại trang chủ</t>
         </is>
       </c>
     </row>
     <row r="165" ht="18" customHeight="1">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t>auth-middleware.messages.token-expired</t>
+          <t>auth-middleware.messages.invalid-token-payload</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>Token is expired</t>
+          <t>Invalid token payload</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>Token đã hết hạn</t>
+          <t>Payload của token không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="166" ht="18" customHeight="1">
       <c r="A166" s="1" t="inlineStr">
         <is>
-          <t>auth-middleware.messages.token-invalid</t>
+          <t>auth-middleware.messages.session-not-found</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>Token is invalid</t>
+          <t>Session not found</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>Token không hợp lệ</t>
+          <t>Không tìm thấy phiên</t>
         </is>
       </c>
     </row>
     <row r="167" ht="18" customHeight="1">
       <c r="A167" s="1" t="inlineStr">
         <is>
-          <t>auth-middleware.messages.token-required</t>
+          <t>auth-middleware.messages.token-expired</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>Token not provided</t>
+          <t>Token is expired</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>Token không được cung cấp</t>
+          <t>Token đã hết hạn</t>
         </is>
       </c>
     </row>
     <row r="168" ht="18" customHeight="1">
       <c r="A168" s="1" t="inlineStr">
         <is>
-          <t>auth-middleware.messages.token-subject-mismatch</t>
+          <t>auth-middleware.messages.token-invalid</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>Token subject mismatch</t>
+          <t>Token is invalid</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>Token chủ đề không khớp</t>
+          <t>Token không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="169" ht="18" customHeight="1">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t>auth-middleware.messages.token-validation-failed</t>
+          <t>auth-middleware.messages.token-required</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>Token validation failed</t>
+          <t>Token not provided</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>Xác thực token không thành công</t>
+          <t>Token không được cung cấp</t>
         </is>
       </c>
     </row>
     <row r="170" ht="18" customHeight="1">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.insufficient-amount</t>
+          <t>auth-middleware.messages.token-subject-mismatch</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>You do not have enough balance to create a room with this bet</t>
+          <t>Token subject mismatch</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>Bạn không còn đủ amount để tạo phòng với mức cược này</t>
+          <t>Token chủ đề không khớp</t>
         </is>
       </c>
     </row>
     <row r="171" ht="18" customHeight="1">
       <c r="A171" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.internal-server-error</t>
+          <t>auth-middleware.messages.token-validation-failed</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>Internal server error while creating room</t>
+          <t>Token validation failed</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ khi tạo phòng</t>
+          <t>Xác thực token không thành công</t>
         </is>
       </c>
     </row>
     <row r="172" ht="18" customHeight="1">
       <c r="A172" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.invalid-bet-amount</t>
+          <t>create-room.messages.insufficient-amount</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>Bet amount is required and must be one of the acceptable values</t>
+          <t>You do not have enough balance to create a room with this bet</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>Số tiền cược là bắt buộc và phải là một trong các giá trị được chấp nhận</t>
-        </is>
-      </c>
-    </row>
-    <row r="173" ht="36" customHeight="1">
+          <t>Bạn không còn đủ amount để tạo phòng với mức cược này</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="18" customHeight="1">
       <c r="A173" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.invalid-redFirst</t>
+          <t>create-room.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>'redFirst' must be a boolean</t>
+          <t>Internal server error while creating room</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>'redFirst' phải là giá trị boolean</t>
+          <t>Lỗi máy chủ nội bộ khi tạo phòng</t>
         </is>
       </c>
     </row>
     <row r="174" ht="18" customHeight="1">
       <c r="A174" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.invalid-team-name</t>
+          <t>create-room.messages.invalid-bet-amount</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>Team name must be either 'red', 'black', or null</t>
+          <t>Bet amount is required and must be one of the acceptable values</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>Tên đội phải là 'red', 'black' hoặc null</t>
+          <t>Số tiền cược là bắt buộc và phải là một trong các giá trị được chấp nhận</t>
         </is>
       </c>
     </row>
     <row r="175" ht="18" customHeight="1">
       <c r="A175" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.name-required</t>
+          <t>create-room.messages.invalid-redFirst</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>Room name (tableName) is required and must not be empty</t>
+          <t>'redFirst' must be a boolean</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>Tên phòng (tableName) là bắt buộc và không được để trống</t>
-        </is>
-      </c>
-    </row>
-    <row r="176" ht="18" customHeight="1">
+          <t>'redFirst' phải là giá trị boolean</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="36" customHeight="1">
       <c r="A176" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.room-created</t>
+          <t>create-room.messages.invalid-team-name</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>Room created successfully</t>
+          <t>Team name must be either 'red', 'black', or null</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>Phòng được tạo thành công</t>
+          <t>Tên đội phải là 'red', 'black' hoặc null</t>
         </is>
       </c>
     </row>
     <row r="177" ht="18" customHeight="1">
       <c r="A177" s="1" t="inlineStr">
         <is>
-          <t>fetch-rooms.messages.internal-server-error</t>
+          <t>create-room.messages.name-required</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Room name (tableName) is required and must not be empty</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Tên phòng (tableName) là bắt buộc và không được để trống</t>
         </is>
       </c>
     </row>
     <row r="178" ht="18" customHeight="1">
       <c r="A178" s="1" t="inlineStr">
         <is>
-          <t>fetch-rooms.messages.invalid-status</t>
+          <t>create-room.messages.room-created</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>Query parameter 'status' must be an integer</t>
+          <t>Room created successfully</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>Tham số truy vấn 'status' phải là số nguyên</t>
+          <t>Phòng được tạo thành công</t>
         </is>
       </c>
     </row>
     <row r="179" ht="18" customHeight="1">
       <c r="A179" s="1" t="inlineStr">
         <is>
-          <t>fetch-rooms.messages.success</t>
+          <t>fetch-rooms.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>Fetch rooms successfully</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>Lấy phòng thành công</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="180" ht="18" customHeight="1">
       <c r="A180" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.messages.email-not-found</t>
+          <t>fetch-rooms.messages.invalid-status</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>Email does not exist</t>
+          <t>Query parameter 'status' must be an integer</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>Email không tồn tại</t>
+          <t>Tham số truy vấn 'status' phải là số nguyên</t>
         </is>
       </c>
     </row>
     <row r="181" ht="18" customHeight="1">
       <c r="A181" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.messages.email-service-not-configured</t>
+          <t>fetch-rooms.messages.success</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>Email service is not configured</t>
+          <t>Fetch rooms successfully</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>Dịch vụ email chưa được cấu hình</t>
-        </is>
-      </c>
-    </row>
-    <row r="182" ht="36" customHeight="1">
+          <t>Lấy phòng thành công</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="18" customHeight="1">
       <c r="A182" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.messages.internal-server-error</t>
+          <t>forgot-password.messages.email-not-found</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Email does not exist</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Email không tồn tại</t>
         </is>
       </c>
     </row>
     <row r="183" ht="18" customHeight="1">
       <c r="A183" s="1" t="inlineStr">
         <is>
+          <t>forgot-password.messages.email-service-not-configured</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>Email service is not configured</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>Dịch vụ email chưa được cấu hình</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="18" customHeight="1">
+      <c r="A184" s="1" t="inlineStr">
+        <is>
+          <t>forgot-password.messages.internal-server-error</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>Internal server error</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>Lỗi máy chủ nội bộ</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="36" customHeight="1">
+      <c r="A185" s="1" t="inlineStr">
+        <is>
           <t>forgot-password.messages.invalid-email-format</t>
         </is>
       </c>
-      <c r="B183" s="2" t="inlineStr">
+      <c r="B185" s="2" t="inlineStr">
         <is>
           <t>Invalid email format</t>
         </is>
       </c>
-      <c r="C183" s="2" t="inlineStr">
+      <c r="C185" s="2" t="inlineStr">
         <is>
           <t>Định dạng email không hợp lệ</t>
-        </is>
-      </c>
-    </row>
-    <row r="184" ht="36" customHeight="1">
-      <c r="A184" s="1" t="inlineStr">
-        <is>
-          <t>forgot-password.messages.missing-email</t>
-        </is>
-      </c>
-      <c r="B184" s="2" t="inlineStr">
-        <is>
-          <t>Email is required</t>
-        </is>
-      </c>
-      <c r="C184" s="2" t="inlineStr">
-        <is>
-          <t>Email là bắt buộc</t>
-        </is>
-      </c>
-    </row>
-    <row r="185" ht="18" customHeight="1">
-      <c r="A185" s="1" t="inlineStr">
-        <is>
-          <t>forgot-password.messages.success</t>
-        </is>
-      </c>
-      <c r="B185" s="2" t="inlineStr">
-        <is>
-          <t>Forgot password email sent</t>
-        </is>
-      </c>
-      <c r="C185" s="2" t="inlineStr">
-        <is>
-          <t>Email đặt lại mật khẩu đã được gửi</t>
         </is>
       </c>
     </row>
     <row r="186" ht="18" customHeight="1">
       <c r="A186" s="1" t="inlineStr">
         <is>
-          <t>join-room.messages.internal-server-error</t>
+          <t>forgot-password.messages.missing-email</t>
         </is>
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Email is required</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
-        </is>
-      </c>
-    </row>
-    <row r="187" ht="18" customHeight="1">
+          <t>Email là bắt buộc</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="36" customHeight="1">
       <c r="A187" s="1" t="inlineStr">
         <is>
-          <t>join-room.messages.invalid-team</t>
+          <t>forgot-password.messages.success</t>
         </is>
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>Field 'team' must be 'red', 'black', null, or undefined</t>
+          <t>Forgot password email sent</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>Trường 'team' phải là 'red', 'black', null hoặc không truyền</t>
+          <t>Email đặt lại mật khẩu đã được gửi</t>
         </is>
       </c>
     </row>
     <row r="188" ht="18" customHeight="1">
       <c r="A188" s="1" t="inlineStr">
         <is>
-          <t>join-room.messages.invalid-room-id</t>
+          <t>join-room.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>Field 'id' is required and must be a positive integer</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="189" ht="18" customHeight="1">
       <c r="A189" s="1" t="inlineStr">
         <is>
-          <t>join-room.messages.room-not-found</t>
+          <t>join-room.messages.invalid-team</t>
         </is>
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>Room not found</t>
+          <t>Field 'team' must be 'red', 'black', null, or undefined</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy phòng</t>
+          <t>Trường 'team' phải là 'red', 'black', null hoặc không truyền</t>
         </is>
       </c>
     </row>
     <row r="190" ht="18" customHeight="1">
       <c r="A190" s="1" t="inlineStr">
         <is>
-          <t>join-room.messages.success</t>
+          <t>join-room.messages.invalid-room-id</t>
         </is>
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>Successfully joined the room</t>
+          <t>Field 'id' is required and must be a positive integer</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>Tham gia phòng thành công</t>
+          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
         </is>
       </c>
     </row>
     <row r="191" ht="18" customHeight="1">
       <c r="A191" s="1" t="inlineStr">
         <is>
-          <t>join-room.messages.team-seat-occupied</t>
+          <t>join-room.messages.room-not-found</t>
         </is>
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>Selected team seat is already occupied</t>
+          <t>Room not found</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>Vị trí đội đã chọn đã có người chơi</t>
+          <t>Không tìm thấy phòng</t>
         </is>
       </c>
     </row>
     <row r="192" ht="18" customHeight="1">
       <c r="A192" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.cannot-kick-self</t>
+          <t>join-room.messages.success</t>
         </is>
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>You cannot kick yourself</t>
+          <t>Successfully joined the room</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>Bạn không thể kick chính mình</t>
+          <t>Tham gia phòng thành công</t>
         </is>
       </c>
     </row>
     <row r="193" ht="18" customHeight="1">
       <c r="A193" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.forbidden</t>
+          <t>join-room.messages.team-seat-occupied</t>
         </is>
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>Only the host can kick users</t>
+          <t>Selected team seat is already occupied</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>Chỉ chủ phòng mới có thể kick người dùng</t>
+          <t>Vị trí đội đã chọn đã có người chơi</t>
         </is>
       </c>
     </row>
     <row r="194" ht="18" customHeight="1">
       <c r="A194" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.internal-server-error</t>
+          <t>kick-user.messages.cannot-kick-self</t>
         </is>
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>You cannot kick yourself</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Bạn không thể kick chính mình</t>
         </is>
       </c>
     </row>
     <row r="195" ht="18" customHeight="1">
       <c r="A195" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.invalid-room-id</t>
+          <t>kick-user.messages.forbidden</t>
         </is>
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>Field 'id' is required and must be a positive integer</t>
+          <t>Only the host can kick users</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
+          <t>Chỉ chủ phòng mới có thể kick người dùng</t>
         </is>
       </c>
     </row>
     <row r="196" ht="18" customHeight="1">
       <c r="A196" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.invalid-user-id</t>
+          <t>kick-user.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>Field 'userId' is required and must be a positive integer</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>Trường 'userId' là bắt buộc và phải là số nguyên dương</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="197" ht="18" customHeight="1">
       <c r="A197" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.room-not-found</t>
+          <t>kick-user.messages.invalid-room-id</t>
         </is>
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>Room not found</t>
+          <t>Field 'id' is required and must be a positive integer</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy phòng</t>
+          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
         </is>
       </c>
     </row>
     <row r="198" ht="18" customHeight="1">
       <c r="A198" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.room-not-waiting</t>
+          <t>kick-user.messages.invalid-user-id</t>
         </is>
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>You can only kick users while the room is waiting</t>
+          <t>Field 'userId' is required and must be a positive integer</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>Chỉ có thể kick người dùng khi phòng đang ở trạng thái chờ</t>
+          <t>Trường 'userId' là bắt buộc và phải là số nguyên dương</t>
         </is>
       </c>
     </row>
     <row r="199" ht="18" customHeight="1">
       <c r="A199" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.success</t>
+          <t>kick-user.messages.room-not-found</t>
         </is>
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>User has been kicked</t>
+          <t>Room not found</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>Người dùng đã bị kick</t>
+          <t>Không tìm thấy phòng</t>
         </is>
       </c>
     </row>
     <row r="200" ht="18" customHeight="1">
       <c r="A200" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.user-not-in-room</t>
+          <t>kick-user.messages.room-not-waiting</t>
         </is>
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>User is not in this room</t>
+          <t>You can only kick users while the room is waiting</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>Người dùng không trong phòng này</t>
+          <t>Chỉ có thể kick người dùng khi phòng đang ở trạng thái chờ</t>
         </is>
       </c>
     </row>
     <row r="201" ht="18" customHeight="1">
       <c r="A201" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.you-were-kicked</t>
+          <t>kick-user.messages.success</t>
         </is>
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>You have been removed from the room by the host</t>
+          <t>User has been kicked</t>
         </is>
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>Bạn đã bị chủ phòng đưa ra khỏi phòng</t>
+          <t>Người dùng đã bị kick</t>
         </is>
       </c>
     </row>
     <row r="202" ht="18" customHeight="1">
       <c r="A202" s="1" t="inlineStr">
         <is>
-          <t>leave-room.messages.internal-server-error</t>
+          <t>kick-user.messages.user-not-in-room</t>
         </is>
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>User is not in this room</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Người dùng không trong phòng này</t>
         </is>
       </c>
     </row>
     <row r="203" ht="18" customHeight="1">
       <c r="A203" s="1" t="inlineStr">
         <is>
-          <t>leave-room.messages.invalid-room-id</t>
+          <t>kick-user.messages.you-were-kicked</t>
         </is>
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>Field 'id' is required and must be a positive integer</t>
+          <t>You have been removed from the room by the host</t>
         </is>
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
+          <t>Bạn đã bị chủ phòng đưa ra khỏi phòng</t>
         </is>
       </c>
     </row>
     <row r="204" ht="18" customHeight="1">
       <c r="A204" s="1" t="inlineStr">
         <is>
-          <t>leave-room.messages.player-not-in-room</t>
+          <t>leave-room.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>Player is not in this room</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>Người chơi không trong phòng này</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="205" ht="18" customHeight="1">
       <c r="A205" s="1" t="inlineStr">
         <is>
-          <t>leave-room.messages.success</t>
+          <t>leave-room.messages.invalid-room-id</t>
         </is>
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>Leave room successfully</t>
+          <t>Field 'id' is required and must be a positive integer</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>Rời phòng thành công</t>
+          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
         </is>
       </c>
     </row>
     <row r="206" ht="18" customHeight="1">
       <c r="A206" s="1" t="inlineStr">
         <is>
-          <t>load-room.messages.internal-server-error</t>
+          <t>leave-room.messages.player-not-in-room</t>
         </is>
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Player is not in this room</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Người chơi không trong phòng này</t>
         </is>
       </c>
     </row>
     <row r="207" ht="18" customHeight="1">
       <c r="A207" s="1" t="inlineStr">
         <is>
-          <t>load-room.messages.invalid-room-id</t>
+          <t>leave-room.messages.success</t>
         </is>
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>Room ID must be a positive integer</t>
+          <t>Leave room successfully</t>
         </is>
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>ID phòng phải là số nguyên dương</t>
-        </is>
-      </c>
-    </row>
-    <row r="208" ht="36" customHeight="1">
+          <t>Rời phòng thành công</t>
+        </is>
+      </c>
+    </row>
+    <row r="208" ht="18" customHeight="1">
       <c r="A208" s="1" t="inlineStr">
         <is>
-          <t>load-room.messages.room-not-found</t>
+          <t>load-room.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>Room not found</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy phòng</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="209" ht="18" customHeight="1">
       <c r="A209" s="1" t="inlineStr">
         <is>
-          <t>load-room.messages.success</t>
+          <t>load-room.messages.invalid-room-id</t>
         </is>
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>Load room successfully</t>
+          <t>Room ID must be a positive integer</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>Tải phòng thành công</t>
+          <t>ID phòng phải là số nguyên dương</t>
         </is>
       </c>
     </row>
     <row r="210" ht="18" customHeight="1">
       <c r="A210" s="1" t="inlineStr">
         <is>
-          <t>google-login.messages.email-not-verified</t>
+          <t>load-room.messages.room-not-found</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>Your Google email is not verified</t>
+          <t>Room not found</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>Email Google của bạn chưa được xác minh</t>
-        </is>
-      </c>
-    </row>
-    <row r="211" ht="18" customHeight="1">
+          <t>Không tìm thấy phòng</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" ht="36" customHeight="1">
       <c r="A211" s="1" t="inlineStr">
         <is>
-          <t>google-login.messages.failed</t>
+          <t>load-room.messages.success</t>
         </is>
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>Login failed</t>
+          <t>Load room successfully</t>
         </is>
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập không thành công</t>
+          <t>Tải phòng thành công</t>
         </is>
       </c>
     </row>
     <row r="212" ht="18" customHeight="1">
       <c r="A212" s="1" t="inlineStr">
         <is>
-          <t>google-login.messages.internal-server-error</t>
+          <t>google-login.messages.email-not-verified</t>
         </is>
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Your Google email is not verified</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Email Google của bạn chưa được xác minh</t>
         </is>
       </c>
     </row>
     <row r="213" ht="18" customHeight="1">
       <c r="A213" s="1" t="inlineStr">
         <is>
-          <t>google-login.messages.invalid-token</t>
+          <t>google-login.messages.failed</t>
         </is>
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>Invalid Google credential</t>
+          <t>Login failed</t>
         </is>
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>Thông tin đăng nhập Google không hợp lệ</t>
+          <t>Đăng nhập không thành công</t>
         </is>
       </c>
     </row>
     <row r="214" ht="18" customHeight="1">
       <c r="A214" s="1" t="inlineStr">
         <is>
-          <t>google-login.messages.missing-credential</t>
+          <t>google-login.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>Google credential is required</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>Thiếu thông tin đăng nhập Google</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="215" ht="18" customHeight="1">
       <c r="A215" s="1" t="inlineStr">
         <is>
-          <t>facebook-login.messages.missing-token</t>
+          <t>google-login.messages.invalid-token</t>
         </is>
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>Facebook token is required</t>
+          <t>Invalid Google credential</t>
         </is>
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>Thiếu thông tin đăng nhập Facebook</t>
+          <t>Thông tin đăng nhập Google không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="216" ht="18" customHeight="1">
       <c r="A216" s="1" t="inlineStr">
         <is>
-          <t>facebook-login.messages.invalid-token</t>
+          <t>google-login.messages.missing-credential</t>
         </is>
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>Invalid Facebook token</t>
+          <t>Google credential is required</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>Thông tin đăng nhập Facebook không hợp lệ</t>
+          <t>Thiếu thông tin đăng nhập Google</t>
         </is>
       </c>
     </row>
     <row r="217" ht="18" customHeight="1">
       <c r="A217" s="1" t="inlineStr">
         <is>
-          <t>facebook-login.messages.not-linked</t>
+          <t>facebook-login.messages.missing-token</t>
         </is>
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>This Facebook account is not linked. Log in another way and link it in Settings</t>
+          <t>Facebook token is required</t>
         </is>
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản Facebook này chưa được liên kết. Hãy đăng nhập cách khác rồi liên kết trong Cài đặt</t>
+          <t>Thiếu thông tin đăng nhập Facebook</t>
         </is>
       </c>
     </row>
     <row r="218" ht="18" customHeight="1">
       <c r="A218" s="1" t="inlineStr">
         <is>
-          <t>facebook-login.messages.internal-server-error</t>
+          <t>facebook-login.messages.invalid-token</t>
         </is>
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Invalid Facebook token</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Thông tin đăng nhập Facebook không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="219" ht="18" customHeight="1">
       <c r="A219" s="1" t="inlineStr">
         <is>
-          <t>facebook-link.messages.missing-token</t>
+          <t>facebook-login.messages.not-linked</t>
         </is>
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>Facebook token is required</t>
+          <t>This Facebook account is not linked. Log in another way and link it in Settings</t>
         </is>
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>Thiếu thông tin đăng nhập Facebook</t>
+          <t>Tài khoản Facebook này chưa được liên kết. Hãy đăng nhập cách khác rồi liên kết trong Cài đặt</t>
         </is>
       </c>
     </row>
     <row r="220" ht="18" customHeight="1">
       <c r="A220" s="1" t="inlineStr">
         <is>
-          <t>facebook-link.messages.invalid-token</t>
+          <t>facebook-login.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>Invalid Facebook token</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>Thông tin đăng nhập Facebook không hợp lệ</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="221" ht="18" customHeight="1">
       <c r="A221" s="1" t="inlineStr">
         <is>
-          <t>facebook-link.messages.linked</t>
+          <t>facebook-link.messages.missing-token</t>
         </is>
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>Facebook linked successfully</t>
+          <t>Facebook token is required</t>
         </is>
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>Đã liên kết Facebook</t>
+          <t>Thiếu thông tin đăng nhập Facebook</t>
         </is>
       </c>
     </row>
     <row r="222" ht="18" customHeight="1">
       <c r="A222" s="1" t="inlineStr">
         <is>
-          <t>facebook-link.messages.already-linked</t>
+          <t>facebook-link.messages.invalid-token</t>
         </is>
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>This Facebook account is already linked to your account</t>
+          <t>Invalid Facebook token</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản Facebook này đã được liên kết với bạn</t>
+          <t>Thông tin đăng nhập Facebook không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="223" ht="18" customHeight="1">
       <c r="A223" s="1" t="inlineStr">
         <is>
-          <t>facebook-link.messages.linked-to-other</t>
+          <t>facebook-link.messages.linked</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>This Facebook account is already linked to another account</t>
+          <t>Facebook linked successfully</t>
         </is>
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản Facebook này đã được liên kết với tài khoản khác</t>
+          <t>Đã liên kết Facebook</t>
         </is>
       </c>
     </row>
     <row r="224" ht="18" customHeight="1">
       <c r="A224" s="1" t="inlineStr">
         <is>
-          <t>facebook-link.messages.already-has-facebook</t>
+          <t>facebook-link.messages.already-linked</t>
         </is>
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>You already linked a different Facebook account</t>
+          <t>This Facebook account is already linked to your account</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>Bạn đã liên kết một tài khoản Facebook khác</t>
+          <t>Tài khoản Facebook này đã được liên kết với bạn</t>
         </is>
       </c>
     </row>
     <row r="225" ht="18" customHeight="1">
       <c r="A225" s="1" t="inlineStr">
         <is>
-          <t>facebook-link.messages.unlinked</t>
+          <t>facebook-link.messages.linked-to-other</t>
         </is>
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>Facebook unlinked</t>
+          <t>This Facebook account is already linked to another account</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>Đã huỷ liên kết Facebook</t>
+          <t>Tài khoản Facebook này đã được liên kết với tài khoản khác</t>
         </is>
       </c>
     </row>
     <row r="226" ht="18" customHeight="1">
       <c r="A226" s="1" t="inlineStr">
         <is>
-          <t>facebook-link.messages.internal-server-error</t>
+          <t>facebook-link.messages.already-has-facebook</t>
         </is>
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>You already linked a different Facebook account</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Bạn đã liên kết một tài khoản Facebook khác</t>
         </is>
       </c>
     </row>
     <row r="227" ht="18" customHeight="1">
       <c r="A227" s="1" t="inlineStr">
         <is>
-          <t>logout.messages.already-inactive</t>
+          <t>facebook-link.messages.unlinked</t>
         </is>
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>Session already inactive</t>
+          <t>Facebook unlinked</t>
         </is>
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>Phiên đã ngưng hoạt động</t>
+          <t>Đã huỷ liên kết Facebook</t>
         </is>
       </c>
     </row>
     <row r="228" ht="18" customHeight="1">
       <c r="A228" s="1" t="inlineStr">
         <is>
-          <t>logout.messages.internal-server-error</t>
+          <t>facebook-link.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
@@ -4212,3113 +4212,3077 @@
     <row r="229" ht="18" customHeight="1">
       <c r="A229" s="1" t="inlineStr">
         <is>
-          <t>logout.messages.success</t>
+          <t>logout.messages.already-inactive</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>Logout successful</t>
+          <t>Session already inactive</t>
         </is>
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>Đăng xuất thành công</t>
+          <t>Phiên đã ngưng hoạt động</t>
         </is>
       </c>
     </row>
     <row r="230" ht="18" customHeight="1">
       <c r="A230" s="1" t="inlineStr">
         <is>
-          <t>refresh-token.messages.missing-refresh-token</t>
+          <t>logout.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>Missing refresh token cookie</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>Thiếu cookie token làm mới</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="231" ht="18" customHeight="1">
       <c r="A231" s="1" t="inlineStr">
         <is>
-          <t>refresh-token.messages.mismatch-or-expired</t>
+          <t>logout.messages.success</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>Refresh token mismatch or expired</t>
+          <t>Logout successful</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>Thiếu refresh token hoặc đã hết hạn</t>
+          <t>Đăng xuất thành công</t>
         </is>
       </c>
     </row>
     <row r="232" ht="18" customHeight="1">
       <c r="A232" s="1" t="inlineStr">
         <is>
-          <t>refresh-token.messages.success</t>
+          <t>refresh-token.messages.missing-refresh-token</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>Token refreshed</t>
+          <t>Missing refresh token cookie</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>Token đã làm mới</t>
+          <t>Thiếu cookie token làm mới</t>
         </is>
       </c>
     </row>
     <row r="233" ht="18" customHeight="1">
       <c r="A233" s="1" t="inlineStr">
         <is>
-          <t>register.messages.email-exists</t>
+          <t>refresh-token.messages.mismatch-or-expired</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>Email already exists</t>
+          <t>Refresh token mismatch or expired</t>
         </is>
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>Email đã tồn tại</t>
+          <t>Thiếu refresh token hoặc đã hết hạn</t>
         </is>
       </c>
     </row>
     <row r="234" ht="18" customHeight="1">
       <c r="A234" s="1" t="inlineStr">
         <is>
-          <t>register.messages.internal-server-error</t>
+          <t>refresh-token.messages.success</t>
         </is>
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Token refreshed</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Token đã làm mới</t>
         </is>
       </c>
     </row>
     <row r="235" ht="18" customHeight="1">
       <c r="A235" s="1" t="inlineStr">
         <is>
-          <t>register.messages.missing-fields</t>
+          <t>register.messages.email-exists</t>
         </is>
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>Username, password, gender, displayName and email are required</t>
+          <t>Email already exists</t>
         </is>
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>Tên người dùng, mật khẩu, giới tính, tên hiển thị và email là bắt buộc</t>
+          <t>Email đã tồn tại</t>
         </is>
       </c>
     </row>
     <row r="236" ht="18" customHeight="1">
       <c r="A236" s="1" t="inlineStr">
         <is>
-          <t>register.messages.success</t>
+          <t>register.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>User created successfully</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>Người dùng được tạo thành công</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="237" ht="18" customHeight="1">
       <c r="A237" s="1" t="inlineStr">
         <is>
-          <t>register.messages.username-exists</t>
+          <t>register.messages.missing-fields</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>Username already exists</t>
+          <t>Username, password, gender, displayName and email are required</t>
         </is>
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>Tên người dùng đã tồn tại</t>
+          <t>Tên người dùng, mật khẩu, giới tính, tên hiển thị và email là bắt buộc</t>
         </is>
       </c>
     </row>
     <row r="238" ht="18" customHeight="1">
       <c r="A238" s="1" t="inlineStr">
         <is>
-          <t>reset-password.messages.internal-server-error</t>
+          <t>register.messages.success</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>User created successfully</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Người dùng được tạo thành công</t>
         </is>
       </c>
     </row>
     <row r="239" ht="18" customHeight="1">
       <c r="A239" s="1" t="inlineStr">
         <is>
-          <t>reset-password.messages.invalid-or-expired-token</t>
+          <t>register.messages.username-exists</t>
         </is>
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>Invalid or expired reset password token</t>
+          <t>Username already exists</t>
         </is>
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>Token đặt lại mật khẩu không hợp lệ hoặc đã hết hạn</t>
+          <t>Tên người dùng đã tồn tại</t>
         </is>
       </c>
     </row>
     <row r="240" ht="18" customHeight="1">
       <c r="A240" s="1" t="inlineStr">
         <is>
-          <t>reset-password.messages.invalid-user-id</t>
+          <t>reset-password.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>Invalid user id</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>ID người dùng không hợp lệ</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="241" ht="18" customHeight="1">
       <c r="A241" s="1" t="inlineStr">
         <is>
-          <t>reset-password.messages.missing-id-or-token</t>
+          <t>reset-password.messages.invalid-or-expired-token</t>
         </is>
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>ID and token are required</t>
+          <t>Invalid or expired reset password token</t>
         </is>
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>ID và token là bắt buộc</t>
+          <t>Token đặt lại mật khẩu không hợp lệ hoặc đã hết hạn</t>
         </is>
       </c>
     </row>
     <row r="242" ht="18" customHeight="1">
       <c r="A242" s="1" t="inlineStr">
         <is>
-          <t>reset-password.messages.missing-userId-or-password</t>
+          <t>reset-password.messages.invalid-user-id</t>
         </is>
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>UserId and password are required</t>
+          <t>Invalid user id</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>UserId và mật khẩu là bắt buộc</t>
+          <t>ID người dùng không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="243" ht="18" customHeight="1">
       <c r="A243" s="1" t="inlineStr">
         <is>
-          <t>reset-password.messages.token-valid</t>
+          <t>reset-password.messages.missing-id-or-token</t>
         </is>
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>Reset password token is valid</t>
+          <t>ID and token are required</t>
         </is>
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>Token đặt lại mật khẩu hợp lệ</t>
+          <t>ID và token là bắt buộc</t>
         </is>
       </c>
     </row>
     <row r="244" ht="18" customHeight="1">
       <c r="A244" s="1" t="inlineStr">
         <is>
-          <t>reset-password.messages.user-not-found</t>
+          <t>reset-password.messages.missing-userId-or-password</t>
         </is>
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>User not found</t>
+          <t>UserId and password are required</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy người dùng</t>
+          <t>UserId và mật khẩu là bắt buộc</t>
         </is>
       </c>
     </row>
     <row r="245" ht="18" customHeight="1">
       <c r="A245" s="1" t="inlineStr">
         <is>
-          <t>set-room-status.messages.internal-server-error</t>
+          <t>reset-password.messages.token-valid</t>
         </is>
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Reset password token is valid</t>
         </is>
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Token đặt lại mật khẩu hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="246" ht="18" customHeight="1">
       <c r="A246" s="1" t="inlineStr">
         <is>
-          <t>set-room-status.messages.invalid-room-id</t>
+          <t>reset-password.messages.user-not-found</t>
         </is>
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>Field 'id' is required and must be a positive integer</t>
+          <t>User not found</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
+          <t>Không tìm thấy người dùng</t>
         </is>
       </c>
     </row>
     <row r="247" ht="18" customHeight="1">
       <c r="A247" s="1" t="inlineStr">
         <is>
-          <t>set-room-status.messages.invalid-status</t>
+          <t>room.actions.start-room</t>
         </is>
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>Field 'status' must be either 1 or 2</t>
+          <t>Start room</t>
         </is>
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>Trường 'status' phải là 1 hoặc 2</t>
+          <t>Bắt đầu chơi</t>
         </is>
       </c>
     </row>
     <row r="248" ht="18" customHeight="1">
       <c r="A248" s="1" t="inlineStr">
         <is>
-          <t>set-room-status.messages.room-not-found</t>
+          <t>room.actions.challenge</t>
         </is>
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>Room not found</t>
+          <t>Challenge</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy phòng</t>
+          <t>Thách đấu</t>
         </is>
       </c>
     </row>
     <row r="249" ht="18" customHeight="1">
       <c r="A249" s="1" t="inlineStr">
         <is>
-          <t>set-room-status.messages.success</t>
+          <t>room.actions.leave-seat</t>
         </is>
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>Set room status successfully</t>
+          <t>Leave seat</t>
         </is>
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>Đặt trạng thái phòng thành công</t>
+          <t>Dự khán</t>
         </is>
       </c>
     </row>
     <row r="250" ht="18" customHeight="1">
       <c r="A250" s="1" t="inlineStr">
         <is>
-          <t>room.actions.start-room</t>
+          <t>room.actions.undo</t>
         </is>
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>Start room</t>
+          <t>Undo</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>Bắt đầu chơi</t>
+          <t>Hoán tác</t>
         </is>
       </c>
     </row>
     <row r="251" ht="18" customHeight="1">
       <c r="A251" s="1" t="inlineStr">
         <is>
-          <t>room.actions.challenge</t>
+          <t>room.actions.surrender</t>
         </is>
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t>Challenge</t>
+          <t>Surrender</t>
         </is>
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>Thách đấu</t>
+          <t>Đầu hàng</t>
         </is>
       </c>
     </row>
     <row r="252" ht="18" customHeight="1">
       <c r="A252" s="1" t="inlineStr">
         <is>
-          <t>room.actions.leave-seat</t>
+          <t>room.actions.draw</t>
         </is>
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>Leave seat</t>
+          <t>Draw</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>Dự khán</t>
+          <t>Hòa</t>
         </is>
       </c>
     </row>
     <row r="253" ht="18" customHeight="1">
       <c r="A253" s="1" t="inlineStr">
         <is>
-          <t>room.actions.undo</t>
+          <t>room.actions.back-home</t>
         </is>
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>Undo</t>
+          <t>Back to home</t>
         </is>
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>Hoán tác</t>
+          <t>Thoát phòng</t>
         </is>
       </c>
     </row>
     <row r="254" ht="18" customHeight="1">
       <c r="A254" s="1" t="inlineStr">
         <is>
-          <t>room.actions.surrender</t>
+          <t>room.actions.flip-board</t>
         </is>
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>Surrender</t>
+          <t>Flip board</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>Đầu hàng</t>
+          <t>Đảo chiều bàn cờ</t>
         </is>
       </c>
     </row>
     <row r="255" ht="18" customHeight="1">
       <c r="A255" s="1" t="inlineStr">
         <is>
-          <t>room.actions.draw</t>
+          <t>room.actions.accept-draw</t>
         </is>
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>Draw</t>
+          <t>Accept</t>
         </is>
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>Hòa</t>
+          <t>Chấp nhận</t>
         </is>
       </c>
     </row>
     <row r="256" ht="18" customHeight="1">
       <c r="A256" s="1" t="inlineStr">
         <is>
-          <t>room.actions.back-home</t>
+          <t>room.actions.reject-draw</t>
         </is>
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>Back to home</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>Thoát phòng</t>
-        </is>
-      </c>
-    </row>
-    <row r="257" ht="36" customHeight="1">
+          <t>Từ chối</t>
+        </is>
+      </c>
+    </row>
+    <row r="257" ht="18" customHeight="1">
       <c r="A257" s="1" t="inlineStr">
         <is>
-          <t>room.actions.flip-board</t>
+          <t>room.actions.send-pm</t>
         </is>
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>Flip board</t>
+          <t>Send PM</t>
         </is>
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>Đảo chiều bàn cờ</t>
-        </is>
-      </c>
-    </row>
-    <row r="258" ht="36" customHeight="1">
+          <t>Chat</t>
+        </is>
+      </c>
+    </row>
+    <row r="258" ht="18" customHeight="1">
       <c r="A258" s="1" t="inlineStr">
         <is>
-          <t>room.actions.accept-draw</t>
+          <t>room.actions.view-history</t>
         </is>
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>Accept</t>
+          <t>History</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>Chấp nhận</t>
+          <t>Lịch sử</t>
         </is>
       </c>
     </row>
     <row r="259" ht="18" customHeight="1">
       <c r="A259" s="1" t="inlineStr">
         <is>
-          <t>room.actions.reject-draw</t>
+          <t>room.actions.kick</t>
         </is>
       </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
-          <t>Reject</t>
+          <t>Kick</t>
         </is>
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>Từ chối</t>
-        </is>
-      </c>
-    </row>
-    <row r="260" ht="18" customHeight="1">
+          <t>Kick</t>
+        </is>
+      </c>
+    </row>
+    <row r="260" ht="36" customHeight="1">
       <c r="A260" s="1" t="inlineStr">
         <is>
-          <t>room.actions.send-pm</t>
+          <t>room.actions.back-to-room</t>
         </is>
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>Send PM</t>
+          <t>Back to room</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>Chat</t>
-        </is>
-      </c>
-    </row>
-    <row r="261" ht="18" customHeight="1">
+          <t>Quay lại phòng chơi</t>
+        </is>
+      </c>
+    </row>
+    <row r="261" ht="36" customHeight="1">
       <c r="A261" s="1" t="inlineStr">
         <is>
-          <t>room.actions.view-history</t>
+          <t>room.messages.draw-accepted</t>
         </is>
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>History</t>
+          <t>Opponent accepted the draw</t>
         </is>
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>Lịch sử</t>
-        </is>
-      </c>
-    </row>
-    <row r="262" ht="17" customHeight="1">
+          <t>Đối phương đã đồng ý hòa</t>
+        </is>
+      </c>
+    </row>
+    <row r="262" ht="18" customHeight="1">
       <c r="A262" s="1" t="inlineStr">
         <is>
-          <t>room.actions.kick</t>
-        </is>
-      </c>
-      <c r="B262" s="1" t="inlineStr">
-        <is>
-          <t>Kick</t>
-        </is>
-      </c>
-      <c r="C262" s="1" t="inlineStr">
-        <is>
-          <t>Kick</t>
+          <t>room.messages.draw-rejected</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t>Opponent rejected the draw</t>
+        </is>
+      </c>
+      <c r="C262" s="2" t="inlineStr">
+        <is>
+          <t>Đối phương từ chối hòa</t>
         </is>
       </c>
     </row>
     <row r="263" ht="18" customHeight="1">
-      <c r="A263" s="2" t="inlineStr">
-        <is>
-          <t>room.actions.settings</t>
+      <c r="A263" s="1" t="inlineStr">
+        <is>
+          <t>room.messages.opponent-surrendered</t>
         </is>
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t>Room settings</t>
+          <t>Opponent surrendered! You won!</t>
         </is>
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>Cài đặt phòng</t>
+          <t>Đối phương đã đầu hàng! Bạn thắng!</t>
         </is>
       </c>
     </row>
     <row r="264" ht="18" customHeight="1">
-      <c r="A264" s="2" t="inlineStr">
-        <is>
-          <t>room.messages.draw-accepted</t>
+      <c r="A264" s="1" t="inlineStr">
+        <is>
+          <t>room.messages.confirm-leave</t>
         </is>
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>Opponent accepted the draw</t>
+          <t>Are you sure you want to leave room?</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>Đối phương đã đồng ý hòa</t>
-        </is>
-      </c>
-    </row>
-    <row r="265" ht="18" customHeight="1">
-      <c r="A265" s="2" t="inlineStr">
-        <is>
-          <t>room.messages.draw-rejected</t>
-        </is>
-      </c>
-      <c r="B265" s="2" t="inlineStr">
-        <is>
-          <t>Opponent rejected the draw</t>
-        </is>
-      </c>
-      <c r="C265" s="2" t="inlineStr">
-        <is>
-          <t>Đối phương từ chối hòa</t>
+          <t>Bạn có chắc muốn rời bàn chơi?</t>
+        </is>
+      </c>
+    </row>
+    <row r="265" ht="17" customHeight="1">
+      <c r="A265" s="1" t="inlineStr">
+        <is>
+          <t>room.messages.confirm-surrender</t>
+        </is>
+      </c>
+      <c r="B265" s="1" t="inlineStr">
+        <is>
+          <t>Are you sure you want to surrender?</t>
+        </is>
+      </c>
+      <c r="C265" s="1" t="inlineStr">
+        <is>
+          <t>Bạn có chắc chắn muốn đầu hàng không?</t>
         </is>
       </c>
     </row>
     <row r="266" ht="18" customHeight="1">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>room.messages.draw-completed</t>
+          <t>room.messages.confirm-draw</t>
         </is>
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>Draw completed</t>
+          <t>Are you sure you want to draw?</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>Hòa cờ thành công</t>
+          <t>Bạn có chắc chắn muốn hòa không?</t>
         </is>
       </c>
     </row>
     <row r="267" ht="18" customHeight="1">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>room.messages.opponent-surrendered</t>
+          <t>room.messages.confirm-accept-draw</t>
         </is>
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>Opponent surrendered! You won!</t>
+          <t>Opponent has proposed a draw. Do you accept?</t>
         </is>
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>Đối phương đã đầu hàng! Bạn thắng!</t>
-        </is>
-      </c>
-    </row>
-    <row r="268" ht="36" customHeight="1">
+          <t>Đối phương đã chủ hòa, bạn có đồng ý không?</t>
+        </is>
+      </c>
+    </row>
+    <row r="268" ht="18" customHeight="1">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>room.messages.confirm-leave</t>
+          <t>room.messages.insufficient-amount</t>
         </is>
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>Are you sure you want to leave room?</t>
+          <t>You do not have enough balance to join this room</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>Bạn có chắc muốn rời bàn chơi?</t>
-        </is>
-      </c>
-    </row>
-    <row r="269" ht="36" customHeight="1">
+          <t>Bạn không đủ tiền để tham gia bàn chơi này</t>
+        </is>
+      </c>
+    </row>
+    <row r="269" ht="18" customHeight="1">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>room.messages.confirm-surrender</t>
+          <t>room.messages.will-leave-current-room</t>
         </is>
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>Are you sure you want to surrender?</t>
+          <t>You are currently in another room. Joining this room will remove you from the current room</t>
         </is>
       </c>
       <c r="C269" s="2" t="inlineStr">
         <is>
-          <t>Bạn có chắc chắn muốn đầu hàng không?</t>
+          <t>Bạn đang ở trong một phòng khác. Tham gia phòng này sẽ loại bạn ra khỏi phòng hiện tại</t>
         </is>
       </c>
     </row>
     <row r="270" ht="18" customHeight="1">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>room.messages.confirm-draw</t>
+          <t>room.messages.all-seats-occupied</t>
         </is>
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>Are you sure you want to draw?</t>
+          <t>All player seats are occupied</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>Bạn có chắc chắn muốn hòa không?</t>
-        </is>
-      </c>
-    </row>
-    <row r="271" ht="18" customHeight="1">
-      <c r="A271" s="1" t="inlineStr">
-        <is>
-          <t>room.messages.confirm-accept-draw</t>
+          <t>Tất cả ghế chơi đã được chiếm</t>
+        </is>
+      </c>
+    </row>
+    <row r="271" ht="36" customHeight="1">
+      <c r="A271" s="2" t="inlineStr">
+        <is>
+          <t>room.messages.game-ended</t>
         </is>
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>Opponent has proposed a draw. Do you accept?</t>
+          <t>Game ended</t>
         </is>
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>Đối phương đã chủ hòa, bạn có đồng ý không?</t>
-        </is>
-      </c>
-    </row>
-    <row r="272" ht="18" customHeight="1">
-      <c r="A272" s="1" t="inlineStr">
-        <is>
-          <t>room.messages.insufficient-amount</t>
+          <t>Ván đấu đã kết thúc</t>
+        </is>
+      </c>
+    </row>
+    <row r="272" ht="36" customHeight="1">
+      <c r="A272" s="2" t="inlineStr">
+        <is>
+          <t>room.messages.you-win</t>
         </is>
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>You do not have enough balance to join this room</t>
+          <t>You win</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>Bạn không đủ tiền để tham gia bàn chơi này</t>
+          <t>Bạn đã chiến thắng</t>
         </is>
       </c>
     </row>
     <row r="273" ht="18" customHeight="1">
-      <c r="A273" s="1" t="inlineStr">
-        <is>
-          <t>room.messages.will-leave-current-room</t>
+      <c r="A273" s="2" t="inlineStr">
+        <is>
+          <t>room.messages.you-lose</t>
         </is>
       </c>
       <c r="B273" s="2" t="inlineStr">
         <is>
-          <t>You are currently in another room. Joining this room will remove you from the current room</t>
+          <t>You lose</t>
         </is>
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>Bạn đang ở trong một phòng khác. Tham gia phòng này sẽ loại bạn ra khỏi phòng hiện tại</t>
+          <t>Bạn đã thua</t>
         </is>
       </c>
     </row>
     <row r="274" ht="18" customHeight="1">
       <c r="A274" s="1" t="inlineStr">
         <is>
-          <t>room.messages.all-seats-occupied</t>
+          <t>room.messages.back-to-room</t>
         </is>
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>All player seats are occupied</t>
+          <t>Back to room</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>Tất cả ghế chơi đã được chiếm</t>
+          <t>Quay lại phòng</t>
         </is>
       </c>
     </row>
     <row r="275" ht="18" customHeight="1">
       <c r="A275" s="1" t="inlineStr">
         <is>
-          <t>room.notifications.joined</t>
+          <t>room.messages.auto-back-countdown</t>
         </is>
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>{0} joined the room</t>
+          <t>{0}. Press the back button to return to the room. You will be automatically returned in {1}s</t>
         </is>
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>{0} đã vào phòng</t>
+          <t>{0}. Bấm nút quay lại để quay lại room. Bạn sẽ tự động quay lại trong {1}s</t>
         </is>
       </c>
     </row>
     <row r="276" ht="18" customHeight="1">
       <c r="A276" s="1" t="inlineStr">
         <is>
-          <t>room.notifications.left</t>
+          <t>room.notifications.joined</t>
         </is>
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>{0} left the room</t>
+          <t>{0} joined the room</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>{0} đã rời phòng</t>
+          <t>{0} đã vào phòng</t>
         </is>
       </c>
     </row>
     <row r="277" ht="18" customHeight="1">
       <c r="A277" s="1" t="inlineStr">
         <is>
-          <t>room.settings.title</t>
+          <t>room.notifications.left</t>
         </is>
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>Room Settings</t>
+          <t>{0} left the room</t>
         </is>
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t>Cài đặt phòng</t>
+          <t>{0} đã rời phòng</t>
         </is>
       </c>
     </row>
     <row r="278" ht="18" customHeight="1">
       <c r="A278" s="1" t="inlineStr">
         <is>
-          <t>room.settings.room-name</t>
+          <t>room.settings.title</t>
         </is>
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>Room name</t>
+          <t>Room Settings</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>Tên phòng</t>
+          <t>Cài đặt phòng</t>
         </is>
       </c>
     </row>
     <row r="279" ht="18" customHeight="1">
       <c r="A279" s="1" t="inlineStr">
         <is>
-          <t>room.settings.players</t>
+          <t>room.settings.room-name</t>
         </is>
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>Spectators</t>
+          <t>Room name</t>
         </is>
       </c>
       <c r="C279" s="2" t="inlineStr">
         <is>
-          <t>Người xem</t>
+          <t>Tên phòng</t>
         </is>
       </c>
     </row>
     <row r="280" ht="18" customHeight="1">
       <c r="A280" s="1" t="inlineStr">
         <is>
-          <t>room.settings.save</t>
+          <t>room.settings.players</t>
         </is>
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>Save</t>
+          <t>Spectators</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>Lưu</t>
+          <t>Người xem</t>
         </is>
       </c>
     </row>
     <row r="281" ht="18" customHeight="1">
       <c r="A281" s="1" t="inlineStr">
         <is>
-          <t>room-invite.messages.title</t>
+          <t>room.settings.save</t>
         </is>
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>Room Invitation</t>
+          <t>Save</t>
         </is>
       </c>
       <c r="C281" s="2" t="inlineStr">
         <is>
-          <t>Lời mời vào phòng</t>
+          <t>Lưu</t>
         </is>
       </c>
     </row>
     <row r="282" ht="18" customHeight="1">
       <c r="A282" s="1" t="inlineStr">
         <is>
-          <t>start-game.messages.success</t>
+          <t>room-invite.messages.title</t>
         </is>
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>Game started successfully</t>
+          <t>Room Invitation</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>Bắt đầu trò chơi thành công</t>
+          <t>Lời mời vào phòng</t>
         </is>
       </c>
     </row>
     <row r="283" ht="18" customHeight="1">
       <c r="A283" s="1" t="inlineStr">
         <is>
-          <t>start-game.messages.internal-server-error</t>
+          <t>start-game.messages.success</t>
         </is>
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>Internal server error while starting game</t>
+          <t>Game started successfully</t>
         </is>
       </c>
       <c r="C283" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ khi bắt đầu trò chơi</t>
+          <t>Bắt đầu trò chơi thành công</t>
         </is>
       </c>
     </row>
     <row r="284" ht="18" customHeight="1">
       <c r="A284" s="1" t="inlineStr">
         <is>
-          <t>start-game.messages.invalid-room-id</t>
+          <t>start-game.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>Field 'id' is required and must be a positive integer</t>
+          <t>Internal server error while starting game</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
+          <t>Lỗi máy chủ nội bộ khi bắt đầu trò chơi</t>
         </is>
       </c>
     </row>
     <row r="285" ht="18" customHeight="1">
       <c r="A285" s="1" t="inlineStr">
         <is>
-          <t>start-game.messages.invalid-difficulty</t>
+          <t>start-game.messages.invalid-room-id</t>
         </is>
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>Bot difficulty must be between 1 and 5</t>
+          <t>Field 'id' is required and must be a positive integer</t>
         </is>
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>Độ khó của bot phải từ 1 đến 5</t>
+          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
         </is>
       </c>
     </row>
     <row r="286" ht="18" customHeight="1">
       <c r="A286" s="1" t="inlineStr">
         <is>
-          <t>start-game.messages.room-not-found</t>
+          <t>start-game.messages.invalid-difficulty</t>
         </is>
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>Room not found</t>
+          <t>Bot difficulty must be between 1 and 5</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy phòng</t>
+          <t>Độ khó của bot phải từ 1 đến 5</t>
         </is>
       </c>
     </row>
     <row r="287" ht="18" customHeight="1">
       <c r="A287" s="1" t="inlineStr">
         <is>
-          <t>start-game.messages.forbidden</t>
+          <t>start-game.messages.room-not-found</t>
         </is>
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>Only the room host can start the game</t>
+          <t>Room not found</t>
         </is>
       </c>
       <c r="C287" s="2" t="inlineStr">
         <is>
-          <t>Chỉ chủ phòng mới có thể bắt đầu trò chơi</t>
+          <t>Không tìm thấy phòng</t>
         </is>
       </c>
     </row>
     <row r="288" ht="18" customHeight="1">
       <c r="A288" s="1" t="inlineStr">
         <is>
-          <t>start-game.messages.insufficient-amount</t>
+          <t>start-game.messages.forbidden</t>
         </is>
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>You do not have enough balance to start a game with this bet</t>
+          <t>Only the room host can start the game</t>
         </is>
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>Bạn không còn đủ amount để start room</t>
+          <t>Chỉ chủ phòng mới có thể bắt đầu trò chơi</t>
         </is>
       </c>
     </row>
     <row r="289" ht="18" customHeight="1">
       <c r="A289" s="1" t="inlineStr">
         <is>
-          <t>start-game.messages.requester-must-pick-team</t>
+          <t>start-game.messages.insufficient-amount</t>
         </is>
       </c>
       <c r="B289" s="2" t="inlineStr">
         <is>
-          <t>You must select a team before starting a game with bot</t>
+          <t>You do not have enough balance to start a game with this bet</t>
         </is>
       </c>
       <c r="C289" s="2" t="inlineStr">
         <is>
-          <t>Bạn phải chọn team trước khi bắt đầu trò chơi với bot</t>
+          <t>Bạn không còn đủ amount để start room</t>
         </is>
       </c>
     </row>
     <row r="290" ht="18" customHeight="1">
       <c r="A290" s="1" t="inlineStr">
         <is>
-          <t>update-room.messages.success</t>
+          <t>start-game.messages.requester-must-pick-team</t>
         </is>
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>Room updated successfully</t>
+          <t>You must select a team before starting a game with bot</t>
         </is>
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>Cập nhật phòng thành công</t>
+          <t>Bạn phải chọn team trước khi bắt đầu trò chơi với bot</t>
         </is>
       </c>
     </row>
     <row r="291" ht="18" customHeight="1">
       <c r="A291" s="1" t="inlineStr">
         <is>
-          <t>update-room.messages.internal-server-error</t>
+          <t>update-room.messages.success</t>
         </is>
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Room updated successfully</t>
         </is>
       </c>
       <c r="C291" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Cập nhật phòng thành công</t>
         </is>
       </c>
     </row>
     <row r="292" ht="18" customHeight="1">
       <c r="A292" s="1" t="inlineStr">
         <is>
-          <t>update-room.messages.invalid-room-id</t>
+          <t>update-room.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>Invalid room ID</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>ID phòng không hợp lệ</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="293" ht="18" customHeight="1">
       <c r="A293" s="1" t="inlineStr">
         <is>
-          <t>update-room.messages.name-required</t>
+          <t>update-room.messages.invalid-room-id</t>
         </is>
       </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t>Room name is required</t>
+          <t>Invalid room ID</t>
         </is>
       </c>
       <c r="C293" s="2" t="inlineStr">
         <is>
-          <t>Tên phòng không được để trống</t>
+          <t>ID phòng không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="294" ht="18" customHeight="1">
       <c r="A294" s="1" t="inlineStr">
         <is>
-          <t>update-room.messages.room-not-found</t>
+          <t>update-room.messages.name-required</t>
         </is>
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>Room not found</t>
+          <t>Room name is required</t>
         </is>
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy phòng</t>
+          <t>Tên phòng không được để trống</t>
         </is>
       </c>
     </row>
     <row r="295" ht="18" customHeight="1">
       <c r="A295" s="1" t="inlineStr">
         <is>
-          <t>update-room.messages.forbidden</t>
+          <t>update-room.messages.room-not-found</t>
         </is>
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>You are not the host of this room</t>
+          <t>Room not found</t>
         </is>
       </c>
       <c r="C295" s="2" t="inlineStr">
         <is>
-          <t>Bạn không phải chủ phòng</t>
+          <t>Không tìm thấy phòng</t>
         </is>
       </c>
     </row>
     <row r="296" ht="18" customHeight="1">
       <c r="A296" s="1" t="inlineStr">
         <is>
-          <t>draw-game.messages.invalid-game-id</t>
+          <t>update-room.messages.forbidden</t>
         </is>
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>Invalid game ID</t>
+          <t>You are not the host of this room</t>
         </is>
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>ID trò chơi không hợp lệ</t>
+          <t>Bạn không phải chủ phòng</t>
         </is>
       </c>
     </row>
     <row r="297" ht="18" customHeight="1">
       <c r="A297" s="1" t="inlineStr">
         <is>
-          <t>draw-game.messages.game-not-found</t>
+          <t>draw-game.messages.invalid-game-id</t>
         </is>
       </c>
       <c r="B297" s="2" t="inlineStr">
         <is>
-          <t>Game not found</t>
+          <t>Invalid game ID</t>
         </is>
       </c>
       <c r="C297" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy trò chơi</t>
+          <t>ID trò chơi không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="298" ht="18" customHeight="1">
       <c r="A298" s="1" t="inlineStr">
         <is>
-          <t>draw-game.messages.forbidden</t>
+          <t>draw-game.messages.game-not-found</t>
         </is>
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>You are not in this room</t>
+          <t>Game not found</t>
         </is>
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>Bạn không có trong phòng này</t>
+          <t>Không tìm thấy trò chơi</t>
         </is>
       </c>
     </row>
     <row r="299" ht="18" customHeight="1">
       <c r="A299" s="1" t="inlineStr">
         <is>
-          <t>draw-game.messages.game-history-not-found</t>
+          <t>draw-game.messages.forbidden</t>
         </is>
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
-          <t>Game history not found</t>
+          <t>You are not in this room</t>
         </is>
       </c>
       <c r="C299" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy lịch sử trò chơi</t>
+          <t>Bạn không có trong phòng này</t>
         </is>
       </c>
     </row>
     <row r="300" ht="18" customHeight="1">
       <c r="A300" s="1" t="inlineStr">
         <is>
-          <t>draw-game.messages.game-already-finished</t>
+          <t>draw-game.messages.game-history-not-found</t>
         </is>
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>Game is already finished</t>
+          <t>Game history not found</t>
         </is>
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>Trò chơi đã kết thúc</t>
+          <t>Không tìm thấy lịch sử trò chơi</t>
         </is>
       </c>
     </row>
     <row r="301" ht="18" customHeight="1">
       <c r="A301" s="1" t="inlineStr">
         <is>
-          <t>draw-game.messages.success</t>
+          <t>draw-game.messages.game-already-finished</t>
         </is>
       </c>
       <c r="B301" s="2" t="inlineStr">
         <is>
-          <t>Draw game successfully</t>
+          <t>Game is already finished</t>
         </is>
       </c>
       <c r="C301" s="2" t="inlineStr">
         <is>
-          <t>Hòa cờ thành công</t>
+          <t>Trò chơi đã kết thúc</t>
         </is>
       </c>
     </row>
     <row r="302" ht="18" customHeight="1">
       <c r="A302" s="1" t="inlineStr">
         <is>
+          <t>draw-game.messages.success</t>
+        </is>
+      </c>
+      <c r="B302" s="2" t="inlineStr">
+        <is>
+          <t>Draw game successfully</t>
+        </is>
+      </c>
+      <c r="C302" s="2" t="inlineStr">
+        <is>
+          <t>Hòa cờ thành công</t>
+        </is>
+      </c>
+    </row>
+    <row r="303" ht="18" customHeight="1">
+      <c r="A303" s="1" t="inlineStr">
+        <is>
           <t>draw-game.messages.internal-server-error</t>
         </is>
       </c>
-      <c r="B302" s="2" t="inlineStr">
+      <c r="B303" s="2" t="inlineStr">
         <is>
           <t>Internal server error</t>
         </is>
       </c>
-      <c r="C302" s="2" t="inlineStr">
+      <c r="C303" s="2" t="inlineStr">
         <is>
           <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
-    <row r="303" ht="90" customHeight="1">
-      <c r="A303" s="1" t="inlineStr">
+    <row r="304" ht="18" customHeight="1">
+      <c r="A304" s="1" t="inlineStr">
         <is>
           <t>surrender.messages.game-already-finished</t>
         </is>
       </c>
-      <c r="B303" s="2" t="inlineStr">
+      <c r="B304" s="2" t="inlineStr">
         <is>
           <t>Game is already finished</t>
         </is>
       </c>
-      <c r="C303" s="2" t="inlineStr">
+      <c r="C304" s="2" t="inlineStr">
         <is>
           <t>Trò chơi đã kết thúc</t>
-        </is>
-      </c>
-    </row>
-    <row r="304" ht="90" customHeight="1">
-      <c r="A304" s="1" t="inlineStr">
-        <is>
-          <t>surrender.messages.game-history-not-found</t>
-        </is>
-      </c>
-      <c r="B304" s="2" t="inlineStr">
-        <is>
-          <t>Game history not found</t>
-        </is>
-      </c>
-      <c r="C304" s="2" t="inlineStr">
-        <is>
-          <t>Không tìm thấy lịch sử trò chơi</t>
         </is>
       </c>
     </row>
     <row r="305" ht="18" customHeight="1">
       <c r="A305" s="1" t="inlineStr">
         <is>
+          <t>surrender.messages.game-history-not-found</t>
+        </is>
+      </c>
+      <c r="B305" s="2" t="inlineStr">
+        <is>
+          <t>Game history not found</t>
+        </is>
+      </c>
+      <c r="C305" s="2" t="inlineStr">
+        <is>
+          <t>Không tìm thấy lịch sử trò chơi</t>
+        </is>
+      </c>
+    </row>
+    <row r="306" ht="90" customHeight="1">
+      <c r="A306" s="1" t="inlineStr">
+        <is>
           <t>surrender.messages.game-not-found</t>
         </is>
       </c>
-      <c r="B305" s="2" t="inlineStr">
+      <c r="B306" s="2" t="inlineStr">
         <is>
           <t>Game not found</t>
         </is>
       </c>
-      <c r="C305" s="2" t="inlineStr">
+      <c r="C306" s="2" t="inlineStr">
         <is>
           <t>Không tìm thấy trò chơi</t>
         </is>
       </c>
     </row>
-    <row r="306" ht="18" customHeight="1">
-      <c r="A306" s="1" t="inlineStr">
+    <row r="307" ht="90" customHeight="1">
+      <c r="A307" s="1" t="inlineStr">
         <is>
           <t>surrender.messages.internal-server-error</t>
         </is>
       </c>
-      <c r="B306" s="2" t="inlineStr">
+      <c r="B307" s="2" t="inlineStr">
         <is>
           <t>Internal server error</t>
         </is>
       </c>
-      <c r="C306" s="2" t="inlineStr">
+      <c r="C307" s="2" t="inlineStr">
         <is>
           <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
-    <row r="307" ht="18" customHeight="1">
-      <c r="A307" s="1" t="inlineStr">
+    <row r="308" ht="18" customHeight="1">
+      <c r="A308" s="1" t="inlineStr">
         <is>
           <t>surrender.messages.invalid-game-id</t>
         </is>
       </c>
-      <c r="B307" s="2" t="inlineStr">
+      <c r="B308" s="2" t="inlineStr">
         <is>
           <t>Invalid game ID</t>
         </is>
       </c>
-      <c r="C307" s="2" t="inlineStr">
+      <c r="C308" s="2" t="inlineStr">
         <is>
           <t>ID trò chơi không hợp lệ</t>
         </is>
       </c>
     </row>
-    <row r="308" ht="18" customHeight="1">
-      <c r="A308" s="2" t="inlineStr">
+    <row r="309" ht="18" customHeight="1">
+      <c r="A309" s="1" t="inlineStr">
         <is>
           <t>surrender.messages.invalid-surrender-player</t>
         </is>
       </c>
-      <c r="B308" s="2" t="inlineStr">
+      <c r="B309" s="2" t="inlineStr">
         <is>
           <t>You are not a player in this game</t>
         </is>
       </c>
-      <c r="C308" s="2" t="inlineStr">
+      <c r="C309" s="2" t="inlineStr">
         <is>
           <t>Bạn không phải là người chơi trong trò chơi này</t>
         </is>
       </c>
     </row>
-    <row r="309" ht="18" customHeight="1">
-      <c r="A309" s="2" t="inlineStr">
+    <row r="310" ht="18" customHeight="1">
+      <c r="A310" s="1" t="inlineStr">
         <is>
           <t>surrender.messages.opponent-not-found</t>
         </is>
       </c>
-      <c r="B309" s="2" t="inlineStr">
+      <c r="B310" s="2" t="inlineStr">
         <is>
           <t>Opponent not found</t>
         </is>
       </c>
-      <c r="C309" s="2" t="inlineStr">
+      <c r="C310" s="2" t="inlineStr">
         <is>
           <t>Không tìm thấy đối thủ</t>
-        </is>
-      </c>
-    </row>
-    <row r="310" ht="18" customHeight="1">
-      <c r="A310" s="2" t="inlineStr">
-        <is>
-          <t>surrender.messages.success</t>
-        </is>
-      </c>
-      <c r="B310" s="2" t="inlineStr">
-        <is>
-          <t>Surrendered</t>
-        </is>
-      </c>
-      <c r="C310" s="2" t="inlineStr">
-        <is>
-          <t>Đã đầu hàng</t>
         </is>
       </c>
     </row>
     <row r="311" ht="18" customHeight="1">
       <c r="A311" s="2" t="inlineStr">
         <is>
+          <t>surrender.messages.success</t>
+        </is>
+      </c>
+      <c r="B311" s="2" t="inlineStr">
+        <is>
+          <t>Surrendered</t>
+        </is>
+      </c>
+      <c r="C311" s="2" t="inlineStr">
+        <is>
+          <t>Đã đầu hàng</t>
+        </is>
+      </c>
+    </row>
+    <row r="312" ht="18" customHeight="1">
+      <c r="A312" s="2" t="inlineStr">
+        <is>
           <t>undo.messages.invalid-game-id</t>
         </is>
       </c>
-      <c r="B311" s="2" t="inlineStr">
+      <c r="B312" s="2" t="inlineStr">
         <is>
           <t>Invalid game ID</t>
         </is>
       </c>
-      <c r="C311" s="2" t="inlineStr">
+      <c r="C312" s="2" t="inlineStr">
         <is>
           <t>ID trò chơi không hợp lệ</t>
-        </is>
-      </c>
-    </row>
-    <row r="312" ht="54" customHeight="1">
-      <c r="A312" s="2" t="inlineStr">
-        <is>
-          <t>undo.messages.unauthorized</t>
-        </is>
-      </c>
-      <c r="B312" s="2" t="inlineStr">
-        <is>
-          <t>Unauthorized</t>
-        </is>
-      </c>
-      <c r="C312" s="2" t="inlineStr">
-        <is>
-          <t>Không được phép truy cập</t>
         </is>
       </c>
     </row>
     <row r="313" ht="18" customHeight="1">
       <c r="A313" s="2" t="inlineStr">
         <is>
+          <t>undo.messages.unauthorized</t>
+        </is>
+      </c>
+      <c r="B313" s="2" t="inlineStr">
+        <is>
+          <t>Unauthorized</t>
+        </is>
+      </c>
+      <c r="C313" s="2" t="inlineStr">
+        <is>
+          <t>Không được phép truy cập</t>
+        </is>
+      </c>
+    </row>
+    <row r="314" ht="18" customHeight="1">
+      <c r="A314" s="2" t="inlineStr">
+        <is>
           <t>undo.messages.game-not-found</t>
         </is>
       </c>
-      <c r="B313" s="2" t="inlineStr">
+      <c r="B314" s="2" t="inlineStr">
         <is>
           <t>Game not found</t>
         </is>
       </c>
-      <c r="C313" s="2" t="inlineStr">
+      <c r="C314" s="2" t="inlineStr">
         <is>
           <t>Không tìm thấy trò chơi</t>
         </is>
       </c>
     </row>
-    <row r="314" ht="90" customHeight="1">
-      <c r="A314" s="2" t="inlineStr">
+    <row r="315" ht="54" customHeight="1">
+      <c r="A315" s="2" t="inlineStr">
         <is>
           <t>undo.messages.not-in-game</t>
         </is>
       </c>
-      <c r="B314" s="2" t="inlineStr">
+      <c r="B315" s="2" t="inlineStr">
         <is>
           <t>You are not part of this game</t>
         </is>
       </c>
-      <c r="C314" s="2" t="inlineStr">
+      <c r="C315" s="2" t="inlineStr">
         <is>
           <t>Bạn không phải là người chơi trong trò chơi này</t>
         </is>
       </c>
     </row>
-    <row r="315" ht="18" customHeight="1">
-      <c r="A315" s="2" t="inlineStr">
+    <row r="316" ht="18" customHeight="1">
+      <c r="A316" s="2" t="inlineStr">
         <is>
           <t>undo.messages.not-in-room</t>
         </is>
       </c>
-      <c r="B315" s="2" t="inlineStr">
+      <c r="B316" s="2" t="inlineStr">
         <is>
           <t>You are not in this room</t>
         </is>
       </c>
-      <c r="C315" s="2" t="inlineStr">
+      <c r="C316" s="2" t="inlineStr">
         <is>
           <t>Bạn không trong phòng này</t>
         </is>
       </c>
     </row>
-    <row r="316" ht="36" customHeight="1">
-      <c r="A316" s="2" t="inlineStr">
+    <row r="317" ht="90" customHeight="1">
+      <c r="A317" s="2" t="inlineStr">
         <is>
           <t>undo.messages.spectator-cannot-undo</t>
         </is>
       </c>
-      <c r="B316" s="2" t="inlineStr">
+      <c r="B317" s="2" t="inlineStr">
         <is>
           <t>Spectators cannot undo moves</t>
         </is>
       </c>
-      <c r="C316" s="2" t="inlineStr">
+      <c r="C317" s="2" t="inlineStr">
         <is>
           <t>Người xem không thể hoàn tác nước đi</t>
         </is>
       </c>
     </row>
-    <row r="317" ht="18" customHeight="1">
-      <c r="A317" s="2" t="inlineStr">
+    <row r="318" ht="18" customHeight="1">
+      <c r="A318" s="2" t="inlineStr">
         <is>
           <t>undo.messages.no-moves</t>
         </is>
       </c>
-      <c r="B317" s="2" t="inlineStr">
+      <c r="B318" s="2" t="inlineStr">
         <is>
           <t>No moves to undo</t>
         </is>
       </c>
-      <c r="C317" s="2" t="inlineStr">
+      <c r="C318" s="2" t="inlineStr">
         <is>
           <t>Không có nước đi để hoàn tác</t>
         </is>
       </c>
     </row>
-    <row r="318" ht="72" customHeight="1">
-      <c r="A318" s="2" t="inlineStr">
+    <row r="319" ht="36" customHeight="1">
+      <c r="A319" s="2" t="inlineStr">
         <is>
           <t>undo.messages.delete-failed</t>
         </is>
       </c>
-      <c r="B318" s="2" t="inlineStr">
+      <c r="B319" s="2" t="inlineStr">
         <is>
           <t>Failed to undo move</t>
         </is>
       </c>
-      <c r="C318" s="2" t="inlineStr">
+      <c r="C319" s="2" t="inlineStr">
         <is>
           <t>Không thể hoàn tác nước đi</t>
         </is>
       </c>
     </row>
-    <row r="319" ht="18" customHeight="1">
-      <c r="A319" s="2" t="inlineStr">
+    <row r="320" ht="18" customHeight="1">
+      <c r="A320" s="2" t="inlineStr">
         <is>
           <t>undo.messages.undo-limit-exceeded</t>
         </is>
       </c>
-      <c r="B319" s="2" t="inlineStr">
+      <c r="B320" s="2" t="inlineStr">
         <is>
           <t>Maximum 3 undo per game exceeded</t>
         </is>
       </c>
-      <c r="C319" s="2" t="inlineStr">
+      <c r="C320" s="2" t="inlineStr">
         <is>
           <t>Đã đạt tối đa 3 lần hoàn tác trong trò chơi</t>
         </is>
       </c>
     </row>
-    <row r="320" ht="54" customHeight="1">
-      <c r="A320" s="2" t="inlineStr">
+    <row r="321" ht="72" customHeight="1">
+      <c r="A321" s="2" t="inlineStr">
         <is>
           <t>undo.messages.success</t>
         </is>
       </c>
-      <c r="B320" s="2" t="inlineStr">
+      <c r="B321" s="2" t="inlineStr">
         <is>
           <t>Move undone successfully</t>
         </is>
       </c>
-      <c r="C320" s="2" t="inlineStr">
+      <c r="C321" s="2" t="inlineStr">
         <is>
           <t>Hoàn tác nước đi thành công</t>
         </is>
       </c>
     </row>
-    <row r="321" ht="18" customHeight="1">
-      <c r="A321" s="2" t="inlineStr">
+    <row r="322" ht="18" customHeight="1">
+      <c r="A322" s="2" t="inlineStr">
         <is>
           <t>undo.messages.internal-server-error</t>
         </is>
       </c>
-      <c r="B321" s="2" t="inlineStr">
+      <c r="B322" s="2" t="inlineStr">
         <is>
           <t>Internal server error</t>
         </is>
       </c>
-      <c r="C321" s="2" t="inlineStr">
+      <c r="C322" s="2" t="inlineStr">
         <is>
           <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
-    <row r="322" ht="72" customHeight="1">
-      <c r="A322" s="2" t="inlineStr">
+    <row r="323" ht="54" customHeight="1">
+      <c r="A323" s="2" t="inlineStr">
         <is>
           <t>player-history.messages.invalid-user-id</t>
         </is>
       </c>
-      <c r="B322" s="2" t="inlineStr">
+      <c r="B323" s="2" t="inlineStr">
         <is>
           <t>Invalid user ID</t>
         </is>
       </c>
-      <c r="C322" s="2" t="inlineStr">
+      <c r="C323" s="2" t="inlineStr">
         <is>
           <t>ID người dùng không hợp lệ</t>
         </is>
       </c>
     </row>
-    <row r="323" ht="18" customHeight="1">
-      <c r="A323" s="2" t="inlineStr">
+    <row r="324" ht="18" customHeight="1">
+      <c r="A324" s="2" t="inlineStr">
         <is>
           <t>player-history.messages.success</t>
         </is>
       </c>
-      <c r="B323" s="2" t="inlineStr">
+      <c r="B324" s="2" t="inlineStr">
         <is>
           <t>Fetch game history successfully</t>
         </is>
       </c>
-      <c r="C323" s="2" t="inlineStr">
+      <c r="C324" s="2" t="inlineStr">
         <is>
           <t>Lấy lịch sử trò chơi thành công</t>
         </is>
       </c>
     </row>
-    <row r="324" ht="90" customHeight="1">
-      <c r="A324" s="2" t="inlineStr">
+    <row r="325" ht="72" customHeight="1">
+      <c r="A325" s="2" t="inlineStr">
         <is>
           <t>validate-token.messages.success</t>
         </is>
       </c>
-      <c r="B324" s="2" t="inlineStr">
+      <c r="B325" s="2" t="inlineStr">
         <is>
           <t>Token is valid</t>
         </is>
       </c>
-      <c r="C324" s="2" t="inlineStr">
+      <c r="C325" s="2" t="inlineStr">
         <is>
           <t>Token hợp lệ</t>
         </is>
       </c>
     </row>
-    <row r="325" ht="18" customHeight="1">
-      <c r="A325" s="2" t="inlineStr">
+    <row r="326" ht="18" customHeight="1">
+      <c r="A326" s="2" t="inlineStr">
         <is>
           <t>guide.section.objective</t>
         </is>
       </c>
-      <c r="B325" s="2" t="inlineStr">
+      <c r="B326" s="2" t="inlineStr">
         <is>
           <t>Objective of the game</t>
         </is>
       </c>
-      <c r="C325" s="2" t="inlineStr">
+      <c r="C326" s="2" t="inlineStr">
         <is>
           <t>Mục tiêu của trò chơi</t>
         </is>
       </c>
     </row>
-    <row r="326" ht="72" customHeight="1">
-      <c r="A326" s="2" t="inlineStr">
+    <row r="327" ht="90" customHeight="1">
+      <c r="A327" s="2" t="inlineStr">
         <is>
           <t>guide.section.pieces</t>
         </is>
       </c>
-      <c r="B326" s="2" t="inlineStr">
+      <c r="B327" s="2" t="inlineStr">
         <is>
           <t>Pieces</t>
         </is>
       </c>
-      <c r="C326" s="2" t="inlineStr">
+      <c r="C327" s="2" t="inlineStr">
         <is>
           <t>Quân cờ</t>
         </is>
       </c>
     </row>
-    <row r="327" ht="54" customHeight="1">
-      <c r="A327" s="2" t="inlineStr">
+    <row r="328" ht="18" customHeight="1">
+      <c r="A328" s="2" t="inlineStr">
         <is>
           <t>guide.section.moving-pieces</t>
         </is>
       </c>
-      <c r="B327" s="2" t="inlineStr">
+      <c r="B328" s="2" t="inlineStr">
         <is>
           <t>Moving pieces</t>
         </is>
       </c>
-      <c r="C327" s="2" t="inlineStr">
+      <c r="C328" s="2" t="inlineStr">
         <is>
           <t>Đi quân</t>
         </is>
       </c>
     </row>
-    <row r="328" ht="54" customHeight="1">
-      <c r="A328" s="2" t="inlineStr">
+    <row r="329" ht="72" customHeight="1">
+      <c r="A329" s="2" t="inlineStr">
         <is>
           <t>guide.section.capturing</t>
         </is>
       </c>
-      <c r="B328" s="2" t="inlineStr">
+      <c r="B329" s="2" t="inlineStr">
         <is>
           <t>Capturing</t>
         </is>
       </c>
-      <c r="C328" s="2" t="inlineStr">
+      <c r="C329" s="2" t="inlineStr">
         <is>
           <t>Bắt quân</t>
         </is>
       </c>
     </row>
-    <row r="329" ht="54" customHeight="1">
-      <c r="A329" s="2" t="inlineStr">
+    <row r="330" ht="54" customHeight="1">
+      <c r="A330" s="2" t="inlineStr">
         <is>
           <t>guide.section.check</t>
         </is>
       </c>
-      <c r="B329" s="2" t="inlineStr">
+      <c r="B330" s="2" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
       </c>
-      <c r="C329" s="2" t="inlineStr">
+      <c r="C330" s="2" t="inlineStr">
         <is>
           <t>Chiếu tướng</t>
-        </is>
-      </c>
-    </row>
-    <row r="330" ht="90" customHeight="1">
-      <c r="A330" s="2" t="inlineStr">
-        <is>
-          <t>guide.section.result</t>
-        </is>
-      </c>
-      <c r="B330" s="2" t="inlineStr">
-        <is>
-          <t>Result</t>
-        </is>
-      </c>
-      <c r="C330" s="2" t="inlineStr">
-        <is>
-          <t>Kết quả</t>
         </is>
       </c>
     </row>
     <row r="331" ht="54" customHeight="1">
       <c r="A331" s="2" t="inlineStr">
         <is>
+          <t>guide.section.result</t>
+        </is>
+      </c>
+      <c r="B331" s="2" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="C331" s="2" t="inlineStr">
+        <is>
+          <t>Kết quả</t>
+        </is>
+      </c>
+    </row>
+    <row r="332" ht="54" customHeight="1">
+      <c r="A332" s="2" t="inlineStr">
+        <is>
           <t>guide.table.piece</t>
         </is>
       </c>
-      <c r="B331" s="2" t="inlineStr">
+      <c r="B332" s="2" t="inlineStr">
         <is>
           <t>Piece</t>
         </is>
       </c>
-      <c r="C331" s="2" t="inlineStr">
+      <c r="C332" s="2" t="inlineStr">
         <is>
           <t>Quân</t>
         </is>
       </c>
     </row>
-    <row r="332" ht="36" customHeight="1">
-      <c r="A332" s="2" t="inlineStr">
+    <row r="333" ht="90" customHeight="1">
+      <c r="A333" s="2" t="inlineStr">
         <is>
           <t>guide.table.symbol</t>
         </is>
       </c>
-      <c r="B332" s="2" t="inlineStr">
+      <c r="B333" s="2" t="inlineStr">
         <is>
           <t>Symbol</t>
         </is>
       </c>
-      <c r="C332" s="2" t="inlineStr">
+      <c r="C333" s="2" t="inlineStr">
         <is>
           <t>Ký hiệu</t>
         </is>
       </c>
     </row>
-    <row r="333" ht="18" customHeight="1">
-      <c r="A333" s="2" t="inlineStr">
+    <row r="334" ht="54" customHeight="1">
+      <c r="A334" s="2" t="inlineStr">
         <is>
           <t>guide.table.quantity</t>
         </is>
       </c>
-      <c r="B333" s="2" t="inlineStr">
+      <c r="B334" s="2" t="inlineStr">
         <is>
           <t>Quantity</t>
         </is>
       </c>
-      <c r="C333" s="2" t="inlineStr">
+      <c r="C334" s="2" t="inlineStr">
         <is>
           <t>Số lượng</t>
-        </is>
-      </c>
-    </row>
-    <row r="334" ht="36" customHeight="1">
-      <c r="A334" s="2" t="inlineStr">
-        <is>
-          <t>guide.objective.paragraph1</t>
-        </is>
-      </c>
-      <c r="B334" s="2" t="inlineStr">
-        <is>
-          <t>A match is played between two players: one controls the Red pieces, and the other controls the Black pieces. The objective of each player is to use their pieces on the board to &lt;b&gt;checkmate&lt;/b&gt; the opponent's General, and win the game.</t>
-        </is>
-      </c>
-      <c r="C334" s="2" t="inlineStr">
-        <is>
-          <t>Ván cờ được tiến hành giữa 2 đấu thủ, một người cầm Quân Đỏ, một người cầm Quân Đen. Mục đích của mỗi đấu thủ là tìm mọi cách sử dụng các quân trên bàn cờ để &lt;b&gt;chiếu bí Tướng&lt;/b&gt; của đối phương, giành thắng lợi.</t>
         </is>
       </c>
     </row>
     <row r="335" ht="36" customHeight="1">
       <c r="A335" s="2" t="inlineStr">
         <is>
+          <t>guide.objective.paragraph1</t>
+        </is>
+      </c>
+      <c r="B335" s="2" t="inlineStr">
+        <is>
+          <t>A match is played between two players: one controls the Red pieces, and the other controls the Black pieces. The objective of each player is to use their pieces on the board to &lt;b&gt;checkmate&lt;/b&gt; the opponent's General, and win the game.</t>
+        </is>
+      </c>
+      <c r="C335" s="2" t="inlineStr">
+        <is>
+          <t>Ván cờ được tiến hành giữa 2 đấu thủ, một người cầm Quân Đỏ, một người cầm Quân Đen. Mục đích của mỗi đấu thủ là tìm mọi cách sử dụng các quân trên bàn cờ để &lt;b&gt;chiếu bí Tướng&lt;/b&gt; của đối phương, giành thắng lợi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="336" ht="18" customHeight="1">
+      <c r="A336" s="2" t="inlineStr">
+        <is>
           <t>guide.pieces.paragraph1</t>
         </is>
       </c>
-      <c r="B335" s="2" t="inlineStr">
+      <c r="B336" s="2" t="inlineStr">
         <is>
           <t>At the start of each game, there must be 32 pieces in total, consisting of &lt;b&gt;7 piece types&lt;/b&gt; split evenly between both sides: 16 Red pieces and 16 Black pieces. The 7 piece types with their symbols and quantities are as follows:</t>
         </is>
       </c>
-      <c r="C335" s="2" t="inlineStr">
+      <c r="C336" s="2" t="inlineStr">
         <is>
           <t>Mỗi ván cờ lúc bắt đầu phải có đủ 32 quân, gồm 7 loại chia đều cho mỗi bên gồm 16 quân Đỏ và 16 quân Đen. &lt;b&gt;7 loại quân&lt;/b&gt; có ký hiệu và số lượng như sau:</t>
         </is>
       </c>
     </row>
-    <row r="336" ht="72" customHeight="1">
-      <c r="A336" s="2" t="inlineStr">
+    <row r="337" ht="36" customHeight="1">
+      <c r="A337" s="2" t="inlineStr">
         <is>
           <t>guide.piece.general</t>
         </is>
       </c>
-      <c r="B336" s="2" t="inlineStr">
+      <c r="B337" s="2" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="C336" s="2" t="inlineStr">
+      <c r="C337" s="2" t="inlineStr">
         <is>
           <t>Tướng</t>
         </is>
       </c>
     </row>
-    <row r="337" ht="54" customHeight="1">
-      <c r="A337" s="2" t="inlineStr">
+    <row r="338" ht="36" customHeight="1">
+      <c r="A338" s="2" t="inlineStr">
         <is>
           <t>guide.piece.advisor</t>
         </is>
       </c>
-      <c r="B337" s="2" t="inlineStr">
+      <c r="B338" s="2" t="inlineStr">
         <is>
           <t>Advisor</t>
         </is>
       </c>
-      <c r="C337" s="2" t="inlineStr">
+      <c r="C338" s="2" t="inlineStr">
         <is>
           <t>Sĩ</t>
         </is>
       </c>
     </row>
-    <row r="338" ht="54" customHeight="1">
-      <c r="A338" s="2" t="inlineStr">
+    <row r="339" ht="72" customHeight="1">
+      <c r="A339" s="2" t="inlineStr">
         <is>
           <t>guide.piece.elephant</t>
         </is>
       </c>
-      <c r="B338" s="2" t="inlineStr">
+      <c r="B339" s="2" t="inlineStr">
         <is>
           <t>Elephant</t>
         </is>
       </c>
-      <c r="C338" s="2" t="inlineStr">
+      <c r="C339" s="2" t="inlineStr">
         <is>
           <t>Tượng</t>
-        </is>
-      </c>
-    </row>
-    <row r="339" ht="90" customHeight="1">
-      <c r="A339" s="2" t="inlineStr">
-        <is>
-          <t>guide.piece.chariot</t>
-        </is>
-      </c>
-      <c r="B339" s="2" t="inlineStr">
-        <is>
-          <t>Chariot</t>
-        </is>
-      </c>
-      <c r="C339" s="2" t="inlineStr">
-        <is>
-          <t>Xe</t>
         </is>
       </c>
     </row>
     <row r="340" ht="54" customHeight="1">
       <c r="A340" s="2" t="inlineStr">
         <is>
+          <t>guide.piece.chariot</t>
+        </is>
+      </c>
+      <c r="B340" s="2" t="inlineStr">
+        <is>
+          <t>Chariot</t>
+        </is>
+      </c>
+      <c r="C340" s="2" t="inlineStr">
+        <is>
+          <t>Xe</t>
+        </is>
+      </c>
+    </row>
+    <row r="341" ht="54" customHeight="1">
+      <c r="A341" s="2" t="inlineStr">
+        <is>
           <t>guide.piece.horse</t>
         </is>
       </c>
-      <c r="B340" s="2" t="inlineStr">
+      <c r="B341" s="2" t="inlineStr">
         <is>
           <t>Horse</t>
         </is>
       </c>
-      <c r="C340" s="2" t="inlineStr">
+      <c r="C341" s="2" t="inlineStr">
         <is>
           <t>Mã</t>
         </is>
       </c>
     </row>
-    <row r="341" ht="18" customHeight="1">
-      <c r="A341" s="2" t="inlineStr">
+    <row r="342" ht="90" customHeight="1">
+      <c r="A342" s="2" t="inlineStr">
         <is>
           <t>guide.piece.cannon</t>
         </is>
       </c>
-      <c r="B341" s="2" t="inlineStr">
+      <c r="B342" s="2" t="inlineStr">
         <is>
           <t>Cannon</t>
         </is>
       </c>
-      <c r="C341" s="2" t="inlineStr">
+      <c r="C342" s="2" t="inlineStr">
         <is>
           <t>Pháo</t>
         </is>
       </c>
     </row>
-    <row r="342" ht="18" customHeight="1">
-      <c r="A342" s="2" t="inlineStr">
+    <row r="343" ht="54" customHeight="1">
+      <c r="A343" s="2" t="inlineStr">
         <is>
           <t>guide.piece.soldier</t>
         </is>
       </c>
-      <c r="B342" s="2" t="inlineStr">
+      <c r="B343" s="2" t="inlineStr">
         <is>
           <t>Soldier</t>
         </is>
       </c>
-      <c r="C342" s="2" t="inlineStr">
+      <c r="C343" s="2" t="inlineStr">
         <is>
           <t>Tốt</t>
-        </is>
-      </c>
-    </row>
-    <row r="343" ht="36" customHeight="1">
-      <c r="A343" s="2" t="inlineStr">
-        <is>
-          <t>guide.moving-pieces.paragraph1</t>
-        </is>
-      </c>
-      <c r="B343" s="2" t="inlineStr">
-        <is>
-          <t>On each turn, each side may move only one of its own pieces according to the rules. The movement rules are as follows:</t>
-        </is>
-      </c>
-      <c r="C343" s="2" t="inlineStr">
-        <is>
-          <t>Mỗi nước đi, mỗi bên chỉ được di chuyển quân của mình theo đúng quy định. Quy định di chuyển của các quân như sau:</t>
         </is>
       </c>
     </row>
     <row r="344" ht="18" customHeight="1">
       <c r="A344" s="2" t="inlineStr">
         <is>
-          <t>guide.general.paragraph1</t>
+          <t>guide.moving-pieces.paragraph1</t>
         </is>
       </c>
       <c r="B344" s="2" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>On each turn, each side may move only one of its own pieces according to the rules. The movement rules are as follows:</t>
         </is>
       </c>
       <c r="C344" s="2" t="inlineStr">
         <is>
-          <t>Tướng</t>
+          <t>Mỗi nước đi, mỗi bên chỉ được di chuyển quân của mình theo đúng quy định. Quy định di chuyển của các quân như sau:</t>
         </is>
       </c>
     </row>
     <row r="345" ht="18" customHeight="1">
       <c r="A345" s="2" t="inlineStr">
         <is>
-          <t>guide.general.paragraph2</t>
+          <t>guide.general.paragraph1</t>
         </is>
       </c>
       <c r="B345" s="2" t="inlineStr">
         <is>
-          <t>Moves one step &lt;b&gt;horizontally or vertically&lt;/b&gt; within the palace. The two Generals may not face each other directly on the same file. If they are facing each other, there must be at least one piece of either side placed between them.</t>
+          <t>General</t>
         </is>
       </c>
       <c r="C345" s="2" t="inlineStr">
         <is>
-          <t>Mỗi nước được đi một bước &lt;b&gt;ngang hoặc dọc&lt;/b&gt; tùy ý trong cung Tướng. Hai tướng của 2 bên không được đối mặt nhau trực tiếp trên cùng một đường thẳng. Nếu đối mặt, bắt buộc phải có quân của bất kỳ bên nào đứng che mặt.</t>
+          <t>Tướng</t>
         </is>
       </c>
     </row>
     <row r="346" ht="36" customHeight="1">
       <c r="A346" s="2" t="inlineStr">
         <is>
-          <t>guide.advisor.paragraph1</t>
+          <t>guide.general.paragraph2</t>
         </is>
       </c>
       <c r="B346" s="2" t="inlineStr">
         <is>
-          <t>Advisor</t>
+          <t>Moves one step &lt;b&gt;horizontally or vertically&lt;/b&gt; within the palace. The two Generals may not face each other directly on the same file. If they are facing each other, there must be at least one piece of either side placed between them.</t>
         </is>
       </c>
       <c r="C346" s="2" t="inlineStr">
         <is>
-          <t>Sĩ</t>
+          <t>Mỗi nước được đi một bước &lt;b&gt;ngang hoặc dọc&lt;/b&gt; tùy ý trong cung Tướng. Hai tướng của 2 bên không được đối mặt nhau trực tiếp trên cùng một đường thẳng. Nếu đối mặt, bắt buộc phải có quân của bất kỳ bên nào đứng che mặt.</t>
         </is>
       </c>
     </row>
     <row r="347" ht="18" customHeight="1">
       <c r="A347" s="2" t="inlineStr">
         <is>
+          <t>guide.advisor.paragraph1</t>
+        </is>
+      </c>
+      <c r="B347" s="2" t="inlineStr">
+        <is>
+          <t>Advisor</t>
+        </is>
+      </c>
+      <c r="C347" s="2" t="inlineStr">
+        <is>
+          <t>Sĩ</t>
+        </is>
+      </c>
+    </row>
+    <row r="348" ht="18" customHeight="1">
+      <c r="A348" s="2" t="inlineStr">
+        <is>
           <t>guide.advisor.paragraph2</t>
         </is>
       </c>
-      <c r="B347" s="2" t="inlineStr">
+      <c r="B348" s="2" t="inlineStr">
         <is>
           <t>Moves one step &lt;b&gt;diagonally&lt;/b&gt; within the palace.</t>
         </is>
       </c>
-      <c r="C347" s="2" t="inlineStr">
+      <c r="C348" s="2" t="inlineStr">
         <is>
           <t>Mỗi nước &lt;b&gt;đi chéo một bước&lt;/b&gt; trong cung Tướng.</t>
         </is>
       </c>
     </row>
-    <row r="348" ht="36" customHeight="1">
-      <c r="A348" s="2" t="inlineStr">
+    <row r="349" ht="36" customHeight="1">
+      <c r="A349" s="2" t="inlineStr">
         <is>
           <t>guide.elephant.paragraph1</t>
         </is>
       </c>
-      <c r="B348" s="2" t="inlineStr">
+      <c r="B349" s="2" t="inlineStr">
         <is>
           <t>Elephant</t>
         </is>
       </c>
-      <c r="C348" s="2" t="inlineStr">
+      <c r="C349" s="2" t="inlineStr">
         <is>
           <t>Tượng</t>
-        </is>
-      </c>
-    </row>
-    <row r="349" ht="18" customHeight="1">
-      <c r="A349" s="2" t="inlineStr">
-        <is>
-          <t>guide.elephant.paragraph2</t>
-        </is>
-      </c>
-      <c r="B349" s="2" t="inlineStr">
-        <is>
-          <t>Moves &lt;b&gt;two steps diagonally&lt;/b&gt; on its own side of the board and may not cross the river. If there is another piece on the midpoint of that diagonal path, the Elephant is blocked and cannot move.</t>
-        </is>
-      </c>
-      <c r="C349" s="2" t="inlineStr">
-        <is>
-          <t>Mỗi nước &lt;b&gt;đi chéo hai bước&lt;/b&gt; tại trận địa bên mình, không được qua sông. Nếu ở giữa đường chéo đó có quân khác đứng thì quân Tượng bị cản, không đi được.</t>
         </is>
       </c>
     </row>
     <row r="350" ht="18" customHeight="1">
       <c r="A350" s="2" t="inlineStr">
         <is>
+          <t>guide.elephant.paragraph2</t>
+        </is>
+      </c>
+      <c r="B350" s="2" t="inlineStr">
+        <is>
+          <t>Moves &lt;b&gt;two steps diagonally&lt;/b&gt; on its own side of the board and may not cross the river. If there is another piece on the midpoint of that diagonal path, the Elephant is blocked and cannot move.</t>
+        </is>
+      </c>
+      <c r="C350" s="2" t="inlineStr">
+        <is>
+          <t>Mỗi nước &lt;b&gt;đi chéo hai bước&lt;/b&gt; tại trận địa bên mình, không được qua sông. Nếu ở giữa đường chéo đó có quân khác đứng thì quân Tượng bị cản, không đi được.</t>
+        </is>
+      </c>
+    </row>
+    <row r="351" ht="36" customHeight="1">
+      <c r="A351" s="2" t="inlineStr">
+        <is>
           <t>guide.chariot.paragraph1</t>
         </is>
       </c>
-      <c r="B350" s="2" t="inlineStr">
+      <c r="B351" s="2" t="inlineStr">
         <is>
           <t>Chariot</t>
         </is>
       </c>
-      <c r="C350" s="2" t="inlineStr">
+      <c r="C351" s="2" t="inlineStr">
         <is>
           <t>Xe</t>
-        </is>
-      </c>
-    </row>
-    <row r="351" ht="18" customHeight="1">
-      <c r="A351" s="2" t="inlineStr">
-        <is>
-          <t>guide.chariot.paragraph2</t>
-        </is>
-      </c>
-      <c r="B351" s="2" t="inlineStr">
-        <is>
-          <t>Moves &lt;b&gt;horizontally or vertically&lt;/b&gt; with no limit on distance, as long as no piece blocks the path.</t>
-        </is>
-      </c>
-      <c r="C351" s="2" t="inlineStr">
-        <is>
-          <t>Mỗi nước được &lt;b&gt;đi dọc hoặc đi ngang&lt;/b&gt;, không hạn chế số bước đi nếu không có quân khác cản đường.</t>
         </is>
       </c>
     </row>
     <row r="352" ht="18" customHeight="1">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>guide.horse.paragraph1</t>
+          <t>guide.chariot.paragraph2</t>
         </is>
       </c>
       <c r="B352" s="2" t="inlineStr">
         <is>
-          <t>Horse</t>
+          <t>Moves &lt;b&gt;horizontally or vertically&lt;/b&gt; with no limit on distance, as long as no piece blocks the path.</t>
         </is>
       </c>
       <c r="C352" s="2" t="inlineStr">
         <is>
-          <t>Mã</t>
+          <t>Mỗi nước được &lt;b&gt;đi dọc hoặc đi ngang&lt;/b&gt;, không hạn chế số bước đi nếu không có quân khác cản đường.</t>
         </is>
       </c>
     </row>
     <row r="353" ht="18" customHeight="1">
       <c r="A353" s="2" t="inlineStr">
         <is>
+          <t>guide.horse.paragraph1</t>
+        </is>
+      </c>
+      <c r="B353" s="2" t="inlineStr">
+        <is>
+          <t>Horse</t>
+        </is>
+      </c>
+      <c r="C353" s="2" t="inlineStr">
+        <is>
+          <t>Mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="354" ht="18" customHeight="1">
+      <c r="A354" s="2" t="inlineStr">
+        <is>
           <t>guide.horse.paragraph2</t>
         </is>
       </c>
-      <c r="B353" s="2" t="inlineStr">
+      <c r="B354" s="2" t="inlineStr">
         <is>
           <t>Moves in an &lt;b&gt;L-shape&lt;/b&gt; (one step orthogonally then one step diagonally outward). If the adjacent orthogonal point is occupied by any piece, the Horse is blocked and cannot move.</t>
         </is>
       </c>
-      <c r="C353" s="2" t="inlineStr">
+      <c r="C354" s="2" t="inlineStr">
         <is>
           <t>Đi theo &lt;b&gt;đường chéo hình chữ nhật&lt;/b&gt; của hai ô vuông liền nhau. Nếu giao điểm liền kề bước thẳng dọc ngang có một quân khác đứng thì Mã bị cản, không đi được.</t>
-        </is>
-      </c>
-    </row>
-    <row r="354" ht="17" customHeight="1">
-      <c r="A354" s="2" t="inlineStr">
-        <is>
-          <t>guide.cannon.paragraph1</t>
-        </is>
-      </c>
-      <c r="B354" s="2" t="inlineStr">
-        <is>
-          <t>Cannon</t>
-        </is>
-      </c>
-      <c r="C354" s="2" t="inlineStr">
-        <is>
-          <t>Pháo</t>
         </is>
       </c>
     </row>
     <row r="355" ht="18" customHeight="1">
       <c r="A355" s="2" t="inlineStr">
         <is>
-          <t>guide.cannon.paragraph2</t>
+          <t>guide.cannon.paragraph1</t>
         </is>
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>Moves &lt;b&gt;horizontally or vertically&lt;/b&gt; like a Chariot when not capturing. To capture, it must &lt;b&gt;jump over exactly one piece&lt;/b&gt; to reach its target. If there are zero or more than one pieces between the Cannon and the target, it cannot capture.</t>
+          <t>Cannon</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
         <is>
-          <t>Đi ngang hoặc dọc giống Xe khi không bắt quân. Để bắt quân, nó phải &lt;b&gt;nhảy qua đúng một quân khác&lt;/b&gt; để đến mục tiêu. Nếu không có hoặc có nhiều hơn một quân giữa Pháo và mục tiêu, nó không thể bắt quân.</t>
+          <t>Pháo</t>
         </is>
       </c>
     </row>
     <row r="356" ht="18" customHeight="1">
       <c r="A356" s="2" t="inlineStr">
         <is>
+          <t>guide.cannon.paragraph2</t>
+        </is>
+      </c>
+      <c r="B356" s="2" t="inlineStr">
+        <is>
+          <t>Moves &lt;b&gt;horizontally or vertically&lt;/b&gt; like a Chariot when not capturing. To capture, it must &lt;b&gt;jump over exactly one piece&lt;/b&gt; to reach its target. If there are zero or more than one pieces between the Cannon and the target, it cannot capture.</t>
+        </is>
+      </c>
+      <c r="C356" s="2" t="inlineStr">
+        <is>
+          <t>Đi ngang hoặc dọc giống Xe khi không bắt quân. Để bắt quân, nó phải &lt;b&gt;nhảy qua đúng một quân khác&lt;/b&gt; để đến mục tiêu. Nếu không có hoặc có nhiều hơn một quân giữa Pháo và mục tiêu, nó không thể bắt quân.</t>
+        </is>
+      </c>
+    </row>
+    <row r="357" ht="17" customHeight="1">
+      <c r="A357" s="2" t="inlineStr">
+        <is>
           <t>guide.soldier.paragraph1</t>
         </is>
       </c>
-      <c r="B356" s="2" t="inlineStr">
+      <c r="B357" s="2" t="inlineStr">
         <is>
           <t>Soldier</t>
         </is>
       </c>
-      <c r="C356" s="2" t="inlineStr">
+      <c r="C357" s="2" t="inlineStr">
         <is>
           <t>Tốt</t>
-        </is>
-      </c>
-    </row>
-    <row r="357" ht="18" customHeight="1">
-      <c r="A357" s="2" t="inlineStr">
-        <is>
-          <t>guide.soldier.paragraph2</t>
-        </is>
-      </c>
-      <c r="B357" s="2" t="inlineStr">
-        <is>
-          <t>Moves &lt;b&gt;one step&lt;/b&gt; each turn. Before crossing the river, it can only move forward. After crossing the river, it may move &lt;b&gt;forward or sideways&lt;/b&gt;, but never backward.</t>
-        </is>
-      </c>
-      <c r="C357" s="2" t="inlineStr">
-        <is>
-          <t>Mỗi nước đi &lt;b&gt;một bước&lt;/b&gt;. Khi chưa qua sông, Tốt chỉ được tiến. Khi Tốt đã qua sông được quyền &lt;b&gt;đi tiến và đi ngang&lt;/b&gt;, không được phép lùi.</t>
         </is>
       </c>
     </row>
     <row r="358" ht="18" customHeight="1">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>guide.capturing.paragraph1</t>
+          <t>guide.soldier.paragraph2</t>
         </is>
       </c>
       <c r="B358" s="2" t="inlineStr">
         <is>
-          <t>When a piece moves to an intersection occupied by an opponent's piece, it may &lt;b&gt;capture that piece&lt;/b&gt; and occupy its position.</t>
+          <t>Moves &lt;b&gt;one step&lt;/b&gt; each turn. Before crossing the river, it can only move forward. After crossing the river, it may move &lt;b&gt;forward or sideways&lt;/b&gt;, but never backward.</t>
         </is>
       </c>
       <c r="C358" s="2" t="inlineStr">
         <is>
-          <t>Khi một quân đi tới một giao điểm khác đã có quân đối phương đứng thì được quyền &lt;b&gt;bắt quân đó&lt;/b&gt;, đồng thời chiếm giữ vị trí quân bị bắt.</t>
+          <t>Mỗi nước đi &lt;b&gt;một bước&lt;/b&gt;. Khi chưa qua sông, Tốt chỉ được tiến. Khi Tốt đã qua sông được quyền &lt;b&gt;đi tiến và đi ngang&lt;/b&gt;, không được phép lùi.</t>
         </is>
       </c>
     </row>
     <row r="359" ht="18" customHeight="1">
       <c r="A359" s="2" t="inlineStr">
         <is>
-          <t>guide.capturing.paragraph2</t>
+          <t>guide.capturing.paragraph1</t>
         </is>
       </c>
       <c r="B359" s="2" t="inlineStr">
         <is>
-          <t>You may not capture your own pieces. You may sacrifice your own pieces to be captured by the opponent, &lt;b&gt;except for the General&lt;/b&gt;.</t>
+          <t>When a piece moves to an intersection occupied by an opponent's piece, it may &lt;b&gt;capture that piece&lt;/b&gt; and occupy its position.</t>
         </is>
       </c>
       <c r="C359" s="2" t="inlineStr">
         <is>
-          <t>Không được bắt quân bên mình. Được phép cho đối phương bắt đầu quân mình chủ động hiến mình cho đối phương, &lt;b&gt;trừ Tướng&lt;/b&gt;.</t>
+          <t>Khi một quân đi tới một giao điểm khác đã có quân đối phương đứng thì được quyền &lt;b&gt;bắt quân đó&lt;/b&gt;, đồng thời chiếm giữ vị trí quân bị bắt.</t>
         </is>
       </c>
     </row>
     <row r="360" ht="18" customHeight="1">
       <c r="A360" s="2" t="inlineStr">
         <is>
+          <t>guide.capturing.paragraph2</t>
+        </is>
+      </c>
+      <c r="B360" s="2" t="inlineStr">
+        <is>
+          <t>You may not capture your own pieces. You may sacrifice your own pieces to be captured by the opponent, &lt;b&gt;except for the General&lt;/b&gt;.</t>
+        </is>
+      </c>
+      <c r="C360" s="2" t="inlineStr">
+        <is>
+          <t>Không được bắt quân bên mình. Được phép cho đối phương bắt đầu quân mình chủ động hiến mình cho đối phương, &lt;b&gt;trừ Tướng&lt;/b&gt;.</t>
+        </is>
+      </c>
+    </row>
+    <row r="361" ht="18" customHeight="1">
+      <c r="A361" s="2" t="inlineStr">
+        <is>
           <t>guide.capturing.paragraph3</t>
         </is>
       </c>
-      <c r="B360" s="2" t="inlineStr">
+      <c r="B361" s="2" t="inlineStr">
         <is>
           <t>A captured piece is removed from the board. &lt;b&gt;Chasing one piece for more than 6 consecutive moves is not allowed&lt;/b&gt;.</t>
         </is>
       </c>
-      <c r="C360" s="2" t="inlineStr">
+      <c r="C361" s="2" t="inlineStr">
         <is>
           <t>Quân bị bắt phải bị loại và bị nhấc ra khỏi bàn cờ. &lt;b&gt;Không được đuổi 1 quân quá 6 nước cờ liên tiếp&lt;/b&gt;.</t>
         </is>
       </c>
     </row>
-    <row r="361" ht="17" customHeight="1">
-      <c r="A361" s="2" t="inlineStr">
+    <row r="362" ht="18" customHeight="1">
+      <c r="A362" s="2" t="inlineStr">
         <is>
           <t>guide.check.paragraph1</t>
         </is>
       </c>
-      <c r="B361" s="2" t="inlineStr">
+      <c r="B362" s="2" t="inlineStr">
         <is>
           <t>If a player makes a move that threatens to capture the opponent's General on the next move (by the same piece or another piece), it is called a &lt;b&gt;Check&lt;/b&gt;. The checked side must respond to avoid check. Otherwise, that side loses</t>
         </is>
       </c>
-      <c r="C361" s="2" t="inlineStr">
+      <c r="C362" s="2" t="inlineStr">
         <is>
           <t>Nếu người chơi thực hiện một nước đi đe dọa bắt Tướng của đối phương ở nước đi tiếp theo (bằng chính quân cờ đó hoặc một quân cờ khác), thì đó được gọi là &lt;b&gt;Chiếu&lt;/b&gt;. Bên bị chiếu phải đáp trả để tránh bị chiếu. Nếu không sẽ bị xử thua</t>
         </is>
       </c>
     </row>
-    <row r="362" ht="17" customHeight="1">
-      <c r="A362" s="2" t="inlineStr">
+    <row r="363" ht="18" customHeight="1">
+      <c r="A363" s="2" t="inlineStr">
         <is>
           <t>guide.check.paragraph2</t>
         </is>
       </c>
-      <c r="B362" s="2" t="inlineStr">
+      <c r="B363" s="2" t="inlineStr">
         <is>
           <t>When the General is checked from any direction (including from behind), the checked side may respond in one of the following ways:</t>
         </is>
       </c>
-      <c r="C362" s="2" t="inlineStr">
+      <c r="C363" s="2" t="inlineStr">
         <is>
           <t>Tướng bị chiếu từ cả bốn hướng (bị chiếu cả từ phía sau) có thể ứng phó với nước chiếu tướng bằng một trong các cách sau:</t>
-        </is>
-      </c>
-    </row>
-    <row r="363" ht="17" customHeight="1">
-      <c r="A363" s="2" t="inlineStr">
-        <is>
-          <t>guide.check.paragraph3</t>
-        </is>
-      </c>
-      <c r="B363" s="2" t="inlineStr">
-        <is>
-          <t>Move the General to another position to escape check</t>
-        </is>
-      </c>
-      <c r="C363" s="2" t="inlineStr">
-        <is>
-          <t>Di chuyển tướng sang vị trí khác để tránh nước chiếu</t>
         </is>
       </c>
     </row>
     <row r="364" ht="17" customHeight="1">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>guide.check.paragraph4</t>
+          <t>guide.check.paragraph3</t>
         </is>
       </c>
       <c r="B364" s="2" t="inlineStr">
         <is>
-          <t>Capture the checking piece</t>
+          <t>Move the General to another position to escape check</t>
         </is>
       </c>
       <c r="C364" s="2" t="inlineStr">
         <is>
-          <t>Bắt quân đang chiếu</t>
+          <t>Di chuyển tướng sang vị trí khác để tránh nước chiếu</t>
         </is>
       </c>
     </row>
     <row r="365" ht="17" customHeight="1">
       <c r="A365" s="2" t="inlineStr">
         <is>
-          <t>guide.check.paragraph5</t>
+          <t>guide.check.paragraph4</t>
         </is>
       </c>
       <c r="B365" s="2" t="inlineStr">
         <is>
-          <t>Block the checking line with another piece to protect the General</t>
+          <t>Capture the checking piece</t>
         </is>
       </c>
       <c r="C365" s="2" t="inlineStr">
         <is>
-          <t>Dùng quân khác cản quân chiếu, đi quân che đỡ cho tướng</t>
+          <t>Bắt quân đang chiếu</t>
         </is>
       </c>
     </row>
     <row r="366" ht="17" customHeight="1">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>guide.check.paragraph6</t>
+          <t>guide.check.paragraph5</t>
         </is>
       </c>
       <c r="B366" s="2" t="inlineStr">
         <is>
-          <t>Repeatedly checking for more than 6 consecutive moves is not allowed</t>
+          <t>Block the checking line with another piece to protect the General</t>
         </is>
       </c>
       <c r="C366" s="2" t="inlineStr">
         <is>
-          <t>Không được chiếu tướng quá 6 nước cờ liên tiếp</t>
+          <t>Dùng quân khác cản quân chiếu, đi quân che đỡ cho tướng</t>
         </is>
       </c>
     </row>
     <row r="367" ht="17" customHeight="1">
       <c r="A367" s="2" t="inlineStr">
         <is>
-          <t>guide.result.paragraph1</t>
+          <t>guide.check.paragraph6</t>
         </is>
       </c>
       <c r="B367" s="2" t="inlineStr">
         <is>
-          <t>When one side gives Check and the other side has no legal way to protect the General, it is called a &lt;b&gt;Checkmate&lt;/b&gt;. The side that delivers Checkmate wins.</t>
+          <t>Repeatedly checking for more than 6 consecutive moves is not allowed</t>
         </is>
       </c>
       <c r="C367" s="2" t="inlineStr">
         <is>
-          <t>Khi một bên chiếu Tướng mà bên còn lại không thể làm gì để bảo vệ Tướng thì được gọi là &lt;b&gt;Chiếu Hết&lt;/b&gt;, bên thực hiện được Chiếu Hết sẽ giành chiến thắng.</t>
+          <t>Không được chiếu tướng quá 6 nước cờ liên tiếp</t>
         </is>
       </c>
     </row>
     <row r="368" ht="17" customHeight="1">
       <c r="A368" s="2" t="inlineStr">
         <is>
-          <t>guide.result.paragraph2</t>
+          <t>guide.result.paragraph1</t>
         </is>
       </c>
       <c r="B368" s="2" t="inlineStr">
         <is>
-          <t>If a player runs out of time for a single move (for example: 90s) without moving, the other side is awarded a &lt;b&gt;win&lt;/b&gt;.</t>
+          <t>When one side gives Check and the other side has no legal way to protect the General, it is called a &lt;b&gt;Checkmate&lt;/b&gt;. The side that delivers Checkmate wins.</t>
         </is>
       </c>
       <c r="C368" s="2" t="inlineStr">
         <is>
-          <t>Khi hết thời gian một nước đi (ví dụ: 90s) mà vẫn chưa di chuyển quân thì bên còn lại sẽ được &lt;b&gt;xử Thắng&lt;/b&gt;.</t>
+          <t>Khi một bên chiếu Tướng mà bên còn lại không thể làm gì để bảo vệ Tướng thì được gọi là &lt;b&gt;Chiếu Hết&lt;/b&gt;, bên thực hiện được Chiếu Hết sẽ giành chiến thắng.</t>
         </is>
       </c>
     </row>
     <row r="369" ht="17" customHeight="1">
       <c r="A369" s="2" t="inlineStr">
         <is>
-          <t>guide.result.paragraph3</t>
+          <t>guide.result.paragraph2</t>
         </is>
       </c>
       <c r="B369" s="2" t="inlineStr">
         <is>
-          <t>If a player runs out of total game time (for example: 5 minutes or 10 minutes), the other side is awarded a &lt;b&gt;win&lt;/b&gt;.</t>
+          <t>If a player runs out of time for a single move (for example: 90s) without moving, the other side is awarded a &lt;b&gt;win&lt;/b&gt;.</t>
         </is>
       </c>
       <c r="C369" s="2" t="inlineStr">
         <is>
-          <t>Khi một bên hết thời gian ván đấu (ví dụ: 5 phút, 10 phút) thì bên còn lại sẽ được &lt;b&gt;xử Thắng&lt;/b&gt;.</t>
+          <t>Khi hết thời gian một nước đi (ví dụ: 90s) mà vẫn chưa di chuyển quân thì bên còn lại sẽ được &lt;b&gt;xử Thắng&lt;/b&gt;.</t>
         </is>
       </c>
     </row>
     <row r="370" ht="17" customHeight="1">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>guide.result.paragraph4</t>
+          <t>guide.result.paragraph3</t>
         </is>
       </c>
       <c r="B370" s="2" t="inlineStr">
         <is>
-          <t>If both sides have no pieces that have crossed the river, the game is declared a &lt;b&gt;draw&lt;/b&gt;. If one side still has pieces across the river but runs out of time, while the other side still has time but has no pieces across the river, the game is declared a &lt;b&gt;draw&lt;/b&gt;.</t>
+          <t>If a player runs out of total game time (for example: 5 minutes or 10 minutes), the other side is awarded a &lt;b&gt;win&lt;/b&gt;.</t>
         </is>
       </c>
       <c r="C370" s="2" t="inlineStr">
         <is>
-          <t>Khi cả 2 bên đều không còn quân qua sông, ván đấu sẽ được &lt;b&gt;xử Hòa&lt;/b&gt;. Khi một bên còn quân qua sông nhưng cạn thời gian, một bên còn thời gian nhưng hết quân qua sông, ván đấu sẽ được &lt;b&gt;xử Hòa&lt;/b&gt;.</t>
+          <t>Khi một bên hết thời gian ván đấu (ví dụ: 5 phút, 10 phút) thì bên còn lại sẽ được &lt;b&gt;xử Thắng&lt;/b&gt;.</t>
         </is>
       </c>
     </row>
     <row r="371" ht="17" customHeight="1">
       <c r="A371" s="2" t="inlineStr">
         <is>
-          <t>guide.result.paragraph5</t>
+          <t>guide.result.paragraph4</t>
         </is>
       </c>
       <c r="B371" s="2" t="inlineStr">
         <is>
-          <t>Within 40 moves, if there is no capture and no Soldier advances by one square, the game is declared a &lt;b&gt;draw&lt;/b&gt;.</t>
+          <t>If both sides have no pieces that have crossed the river, the game is declared a &lt;b&gt;draw&lt;/b&gt;. If one side still has pieces across the river but runs out of time, while the other side still has time but has no pieces across the river, the game is declared a &lt;b&gt;draw&lt;/b&gt;.</t>
         </is>
       </c>
       <c r="C371" s="2" t="inlineStr">
         <is>
-          <t>Trong vòng 40 nước nếu không phát sinh nước bắt quân, Tốt không tiến 1 ô thì ván đấu sẽ được &lt;b&gt;xử Hòa&lt;/b&gt;.</t>
+          <t>Khi cả 2 bên đều không còn quân qua sông, ván đấu sẽ được &lt;b&gt;xử Hòa&lt;/b&gt;. Khi một bên còn quân qua sông nhưng cạn thời gian, một bên còn thời gian nhưng hết quân qua sông, ván đấu sẽ được &lt;b&gt;xử Hòa&lt;/b&gt;.</t>
         </is>
       </c>
     </row>
     <row r="372" ht="17" customHeight="1">
       <c r="A372" s="2" t="inlineStr">
         <is>
-          <t>extra-money.lucky-wheel.title</t>
+          <t>guide.result.paragraph5</t>
         </is>
       </c>
       <c r="B372" s="2" t="inlineStr">
         <is>
-          <t>Lucky Wheel</t>
+          <t>Within 40 moves, if there is no capture and no Soldier advances by one square, the game is declared a &lt;b&gt;draw&lt;/b&gt;.</t>
         </is>
       </c>
       <c r="C372" s="2" t="inlineStr">
         <is>
-          <t>Vòng quay may mắn</t>
+          <t>Trong vòng 40 nước nếu không phát sinh nước bắt quân, Tốt không tiến 1 ô thì ván đấu sẽ được &lt;b&gt;xử Hòa&lt;/b&gt;.</t>
         </is>
       </c>
     </row>
     <row r="373" ht="17" customHeight="1">
       <c r="A373" s="2" t="inlineStr">
         <is>
-          <t>extra-money.lucky-wheel.description</t>
+          <t>extra-money.title</t>
         </is>
       </c>
       <c r="B373" s="2" t="inlineStr">
         <is>
-          <t>Spin the wheel to earn money! Click the spin button in the middle of the wheel to try your luck.</t>
+          <t>Daily tasks</t>
         </is>
       </c>
       <c r="C373" s="2" t="inlineStr">
         <is>
-          <t>Quay vòng để kiếm tiền! Bấm nút Quay ở giữa vòng quay để thử vận may của bạn.</t>
+          <t>Kiếm tiền</t>
         </is>
       </c>
     </row>
     <row r="374" ht="17" customHeight="1">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>extra-money.lucky-wheel.spin-button</t>
+          <t>extra-money.tab.lucky-wheel</t>
         </is>
       </c>
       <c r="B374" s="2" t="inlineStr">
         <is>
-          <t>Spin</t>
+          <t>Lucky Wheel</t>
         </is>
       </c>
       <c r="C374" s="2" t="inlineStr">
         <is>
-          <t>Quay</t>
+          <t>Vòng Quay May Mắn</t>
         </is>
       </c>
     </row>
     <row r="375" ht="17" customHeight="1">
       <c r="A375" s="2" t="inlineStr">
         <is>
-          <t>extra-money.lucky-wheel.reward-placeholder</t>
+          <t>extra-money.tab.bonus-coin</t>
         </is>
       </c>
       <c r="B375" s="2" t="inlineStr">
         <is>
-          <t>Click Spin to get started</t>
+          <t>Bonus Coin</t>
         </is>
       </c>
       <c r="C375" s="2" t="inlineStr">
         <is>
-          <t>Nhấp Quay để bắt đầu</t>
+          <t>Xu Thưởng</t>
         </is>
       </c>
     </row>
     <row r="376" ht="17" customHeight="1">
       <c r="A376" s="2" t="inlineStr">
         <is>
-          <t>extra-money.title</t>
+          <t>extra-money.tab.daily-bonus</t>
         </is>
       </c>
       <c r="B376" s="2" t="inlineStr">
         <is>
-          <t>Daily tasks</t>
+          <t>Daily Bonus</t>
         </is>
       </c>
       <c r="C376" s="2" t="inlineStr">
         <is>
-          <t>Kiếm tiền</t>
+          <t>Thưởng hàng ngày</t>
         </is>
       </c>
     </row>
     <row r="377" ht="17" customHeight="1">
       <c r="A377" s="2" t="inlineStr">
         <is>
-          <t>extra-money.tab.lucky-wheel</t>
+          <t>extra-money.bonus-coin.subtitle</t>
         </is>
       </c>
       <c r="B377" s="2" t="inlineStr">
         <is>
-          <t>Lucky Wheel</t>
+          <t>Watch a short video to earn free coin</t>
         </is>
       </c>
       <c r="C377" s="2" t="inlineStr">
         <is>
-          <t>Vòng Quay May Mắn</t>
+          <t>Xem video ngắn để nhận xu miễn phí</t>
         </is>
       </c>
     </row>
     <row r="378" ht="17" customHeight="1">
       <c r="A378" s="2" t="inlineStr">
         <is>
-          <t>extra-money.tab.bonus-coin</t>
+          <t>extra-money.bonus-coin.next-in</t>
         </is>
       </c>
       <c r="B378" s="2" t="inlineStr">
         <is>
-          <t>Bonus Coin</t>
+          <t>Next in:</t>
         </is>
       </c>
       <c r="C378" s="2" t="inlineStr">
         <is>
-          <t>Xu Thưởng</t>
-        </is>
-      </c>
-    </row>
-    <row r="379">
-      <c r="A379" t="inlineStr">
-        <is>
-          <t>extra-money.tab.daily-bonus</t>
-        </is>
-      </c>
-      <c r="B379" t="inlineStr">
-        <is>
-          <t>Daily Bonus</t>
-        </is>
-      </c>
-      <c r="C379" t="inlineStr">
-        <is>
-          <t>Thưởng hàng ngày</t>
-        </is>
-      </c>
-    </row>
-    <row r="380">
-      <c r="A380" t="inlineStr">
-        <is>
-          <t>extra-money.bonus-coin.subtitle</t>
-        </is>
-      </c>
-      <c r="B380" t="inlineStr">
-        <is>
-          <t>Watch a short video to earn free coin</t>
-        </is>
-      </c>
-      <c r="C380" t="inlineStr">
-        <is>
-          <t>Xem video ngắn để nhận xu miễn phí</t>
-        </is>
-      </c>
-    </row>
-    <row r="381">
-      <c r="A381" t="inlineStr">
-        <is>
-          <t>extra-money.bonus-coin.next-in</t>
-        </is>
-      </c>
-      <c r="B381" t="inlineStr">
-        <is>
-          <t>Next in:</t>
-        </is>
-      </c>
-      <c r="C381" t="inlineStr">
-        <is>
           <t>Lượt kế tiếp:</t>
+        </is>
+      </c>
+    </row>
+    <row r="379" ht="17" customHeight="1">
+      <c r="A379" s="2" t="inlineStr">
+        <is>
+          <t>extra-money.bonus-coin.collect</t>
+        </is>
+      </c>
+      <c r="B379" s="2" t="inlineStr">
+        <is>
+          <t>Collect</t>
+        </is>
+      </c>
+      <c r="C379" s="2" t="inlineStr">
+        <is>
+          <t>Thu thập</t>
+        </is>
+      </c>
+    </row>
+    <row r="380" ht="17" customHeight="1">
+      <c r="A380" s="2" t="inlineStr">
+        <is>
+          <t>extra-money.bonus-coin.watch-video</t>
+        </is>
+      </c>
+      <c r="B380" s="2" t="inlineStr">
+        <is>
+          <t>Watch video</t>
+        </is>
+      </c>
+      <c r="C380" s="2" t="inlineStr">
+        <is>
+          <t>Xem video</t>
+        </is>
+      </c>
+    </row>
+    <row r="381" ht="17" customHeight="1">
+      <c r="A381" s="2" t="inlineStr">
+        <is>
+          <t>extra-money.daily-bonus.subtitle</t>
+        </is>
+      </c>
+      <c r="B381" s="2" t="inlineStr">
+        <is>
+          <t>Login 7 days in a row to earn 4000 coin</t>
+        </is>
+      </c>
+      <c r="C381" s="2" t="inlineStr">
+        <is>
+          <t>Đăng nhập 7 ngày liên tiếp để nhận 4000 xu</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>extra-money.bonus-coin.coin-unit</t>
+          <t>extra-money.daily-bonus.day</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>coin</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>xu</t>
+          <t>Ngày</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>extra-money.bonus-coin.watch-video</t>
+          <t>extra-money.reward-ad.loading</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Watch video</t>
+          <t>Loading ad...</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Xem video</t>
+          <t>Đang tải quảng cáo...</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>extra-money.daily-bonus.subtitle</t>
+          <t>extra-money.reward-ad.error</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Login 7 days in a row to earn 4000 coin</t>
+          <t>Could not load the ad. Please try again.</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Đăng nhập 7 ngày liên tiếp để nhận 4000 xu</t>
+          <t>Không tải được quảng cáo. Vui lòng thử lại.</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>extra-money.daily-bonus.day</t>
+          <t>extra-money.reward-ad.retry</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Try again</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Ngày</t>
+          <t>Thử lại</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>extra-money.reward-ad.loading</t>
+          <t>extra-money.reward-ad.close</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Loading ad...</t>
+          <t>Close</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Đang tải quảng cáo...</t>
+          <t>Đóng</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>extra-money.reward-ad.error</t>
+          <t>profile.button.save</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Could not load the ad. Please try again.</t>
+          <t>Save</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Không tải được quảng cáo. Vui lòng thử lại.</t>
+          <t>Lưu</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>extra-money.reward-ad.retry</t>
+          <t>profile.button.cancel</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Try again</t>
+          <t>Cancel</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Thử lại</t>
+          <t>Huỷ</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>extra-money.reward-ad.close</t>
+          <t>change-password.title</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Close</t>
+          <t>Change password</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Đóng</t>
+          <t>Đổi mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>profile.button.save</t>
+          <t>change-password.current.label</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Save</t>
+          <t>Current password</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Lưu</t>
+          <t>Mật khẩu hiện tại</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>profile.button.cancel</t>
+          <t>change-password.current.placeholder</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Enter current password</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Huỷ</t>
+          <t>Nhập mật khẩu hiện tại</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>change-password.title</t>
+          <t>change-password.new.label</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Change password</t>
+          <t>New password</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Đổi mật khẩu</t>
+          <t>Mật khẩu mới</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>change-password.current.label</t>
+          <t>change-password.new.placeholder</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Current password</t>
+          <t>Enter new password</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Mật khẩu hiện tại</t>
+          <t>Nhập mật khẩu mới</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>change-password.current.placeholder</t>
+          <t>change-password.confirm.label</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Enter current password</t>
+          <t>Confirm new password</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Nhập mật khẩu hiện tại</t>
+          <t>Xác nhận mật khẩu mới</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>change-password.new.label</t>
+          <t>change-password.confirm.placeholder</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>New password</t>
+          <t>Re-enter new password</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Mật khẩu mới</t>
+          <t>Nhập lại mật khẩu mới</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>change-password.new.placeholder</t>
+          <t>change-password.confirm.mismatch</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Enter new password</t>
+          <t>Passwords do not match</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Nhập mật khẩu mới</t>
+          <t>Mật khẩu xác nhận không khớp</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>change-password.confirm.label</t>
+          <t>change-password.show</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Confirm new password</t>
+          <t>Show password</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Xác nhận mật khẩu mới</t>
+          <t>Hiện mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>change-password.confirm.placeholder</t>
+          <t>change-password.hide</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Re-enter new password</t>
+          <t>Hide password</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Nhập lại mật khẩu mới</t>
+          <t>Ẩn mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>change-password.confirm.mismatch</t>
+          <t>change-password.submit</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Passwords do not match</t>
+          <t>Change password</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Mật khẩu xác nhận không khớp</t>
+          <t>Đổi mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>change-password.show</t>
+          <t>change-password.submitting</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Show password</t>
+          <t>Changing...</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Hiện mật khẩu</t>
+          <t>Đang đổi...</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>change-password.hide</t>
+          <t>change-password.messages.success</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Hide password</t>
+          <t>Password changed successfully</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Ẩn mật khẩu</t>
+          <t>Đổi mật khẩu thành công</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>change-password.submit</t>
+          <t>change-password.messages.missing-fields</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Change password</t>
+          <t>Please fill in all fields</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Đổi mật khẩu</t>
+          <t>Vui lòng nhập đầy đủ thông tin</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>change-password.submitting</t>
+          <t>change-password.messages.weak-password</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Changing...</t>
+          <t>New password does not meet the requirements</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Đang đổi...</t>
+          <t>Mật khẩu mới không đạt yêu cầu</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>change-password.messages.success</t>
+          <t>change-password.messages.same-as-current</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Password changed successfully</t>
+          <t>New password must be different from the current one</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Đổi mật khẩu thành công</t>
+          <t>Mật khẩu mới phải khác mật khẩu hiện tại</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>change-password.messages.missing-fields</t>
+          <t>change-password.messages.incorrect-current-password</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Please fill in all fields</t>
+          <t>Current password is incorrect</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Vui lòng nhập đầy đủ thông tin</t>
+          <t>Mật khẩu hiện tại không đúng</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>change-password.messages.weak-password</t>
+          <t>change-password.messages.user-not-found</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>New password does not meet the requirements</t>
+          <t>User not found</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Mật khẩu mới không đạt yêu cầu</t>
+          <t>Không tìm thấy người dùng</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>change-password.messages.same-as-current</t>
+          <t>change-password.messages.unauthorized</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>New password must be different from the current one</t>
+          <t>Session expired. Please sign in again.</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Mật khẩu mới phải khác mật khẩu hiện tại</t>
+          <t>Phiên đăng nhập đã hết hạn. Vui lòng đăng nhập lại.</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>change-password.messages.incorrect-current-password</t>
+          <t>change-password.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Current password is incorrect</t>
+          <t>Something went wrong. Please try again.</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Mật khẩu hiện tại không đúng</t>
+          <t>Đã có lỗi xảy ra. Vui lòng thử lại.</t>
         </is>
       </c>
     </row>
     <row r="409">
-      <c r="A409" t="inlineStr">
-        <is>
-          <t>change-password.messages.user-not-found</t>
-        </is>
-      </c>
-      <c r="B409" t="inlineStr">
-        <is>
-          <t>User not found</t>
-        </is>
-      </c>
-      <c r="C409" t="inlineStr">
-        <is>
-          <t>Không tìm thấy người dùng</t>
-        </is>
-      </c>
+      <c r="A409" t="inlineStr"/>
+      <c r="B409" t="inlineStr"/>
+      <c r="C409" t="inlineStr"/>
     </row>
     <row r="410">
-      <c r="A410" t="inlineStr">
-        <is>
-          <t>change-password.messages.unauthorized</t>
-        </is>
-      </c>
-      <c r="B410" t="inlineStr">
-        <is>
-          <t>Session expired. Please sign in again.</t>
-        </is>
-      </c>
-      <c r="C410" t="inlineStr">
-        <is>
-          <t>Phiên đăng nhập đã hết hạn. Vui lòng đăng nhập lại.</t>
-        </is>
-      </c>
+      <c r="A410" t="inlineStr"/>
+      <c r="B410" t="inlineStr"/>
+      <c r="C410" t="inlineStr"/>
     </row>
     <row r="411">
-      <c r="A411" t="inlineStr">
-        <is>
-          <t>change-password.messages.internal-server-error</t>
-        </is>
-      </c>
-      <c r="B411" t="inlineStr">
-        <is>
-          <t>Something went wrong. Please try again.</t>
-        </is>
-      </c>
-      <c r="C411" t="inlineStr">
-        <is>
-          <t>Đã có lỗi xảy ra. Vui lòng thử lại.</t>
-        </is>
-      </c>
+      <c r="A411" t="inlineStr"/>
+      <c r="B411" t="inlineStr"/>
+      <c r="C411" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr"/>
@@ -7399,21 +7363,6 @@
       <c r="A427" t="inlineStr"/>
       <c r="B427" t="inlineStr"/>
       <c r="C427" t="inlineStr"/>
-    </row>
-    <row r="428">
-      <c r="A428" t="inlineStr"/>
-      <c r="B428" t="inlineStr"/>
-      <c r="C428" t="inlineStr"/>
-    </row>
-    <row r="429">
-      <c r="A429" t="inlineStr"/>
-      <c r="B429" t="inlineStr"/>
-      <c r="C429" t="inlineStr"/>
-    </row>
-    <row r="430">
-      <c r="A430" t="inlineStr"/>
-      <c r="B430" t="inlineStr"/>
-      <c r="C430" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tools/languages.xlsx
+++ b/tools/languages.xlsx
@@ -325,7 +325,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C427"/>
+  <dimension ref="A1:C433"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1577,1389 +1577,1389 @@
     <row r="74" ht="18" customHeight="1">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>dashboard.popup.room-name-label</t>
+          <t>dashboard.popup.time-limit</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Room table name</t>
+          <t>Time per player</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>Tên phòng chơi</t>
+          <t>Thời gian mỗi người</t>
         </is>
       </c>
     </row>
     <row r="75" ht="18" customHeight="1">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>dashboard.popup.room-name-helptext</t>
+          <t>dashboard.popup.time-unlimited</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>is required</t>
+          <t>Unlimited</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>không được để trống</t>
+          <t>Không giới hạn</t>
         </is>
       </c>
     </row>
     <row r="76" ht="18" customHeight="1">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>dashboard.popup.play</t>
+          <t>dashboard.popup.time-minutes</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Play</t>
+          <t>{0} min</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>Chơi</t>
+          <t>{0} phút</t>
         </is>
       </c>
     </row>
     <row r="77" ht="18" customHeight="1">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>dashboard.popup.view</t>
+          <t>dashboard.popup.room-name-label</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>View</t>
+          <t>Room table name</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Xem</t>
+          <t>Tên phòng chơi</t>
         </is>
       </c>
     </row>
     <row r="78" ht="18" customHeight="1">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>settings.header</t>
+          <t>dashboard.popup.room-name-helptext</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>is required</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Cài đặt</t>
+          <t>không được để trống</t>
         </is>
       </c>
     </row>
     <row r="79" ht="18" customHeight="1">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>settings.language</t>
+          <t>dashboard.popup.play</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>Play</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Ngôn ngữ</t>
+          <t>Chơi</t>
         </is>
       </c>
     </row>
     <row r="80" ht="18" customHeight="1">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>settings.dark-mode</t>
+          <t>dashboard.popup.view</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Dark mode</t>
+          <t>View</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Chế độ tối</t>
+          <t>Xem</t>
         </is>
       </c>
     </row>
     <row r="81" ht="18" customHeight="1">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>settings.debug-mode</t>
+          <t>settings.header</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Debug mode</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Chế độ test</t>
+          <t>Cài đặt</t>
         </is>
       </c>
     </row>
     <row r="82" ht="18" customHeight="1">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>settings.connected-accounts.label</t>
+          <t>settings.language</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Connected accounts</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản liên kết</t>
+          <t>Ngôn ngữ</t>
         </is>
       </c>
     </row>
     <row r="83" ht="18" customHeight="1">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>settings.connected-accounts.link-facebook</t>
+          <t>settings.dark-mode</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Link Facebook</t>
+          <t>Dark mode</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Liên kết Facebook</t>
+          <t>Chế độ tối</t>
         </is>
       </c>
     </row>
     <row r="84" ht="18" customHeight="1">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>settings.connected-accounts.unlink-facebook</t>
+          <t>settings.debug-mode</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Unlink Facebook</t>
+          <t>Debug mode</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Huỷ liên kết Facebook</t>
+          <t>Chế độ test</t>
         </is>
       </c>
     </row>
     <row r="85" ht="18" customHeight="1">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>settings.connected-accounts.link-success</t>
+          <t>settings.connected-accounts.label</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Facebook linked successfully</t>
+          <t>Connected accounts</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Đã liên kết Facebook</t>
+          <t>Tài khoản liên kết</t>
         </is>
       </c>
     </row>
     <row r="86" ht="18" customHeight="1">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>settings.connected-accounts.unlink-success</t>
+          <t>settings.connected-accounts.link-facebook</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Facebook unlinked</t>
+          <t>Link Facebook</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Đã huỷ liên kết Facebook</t>
+          <t>Liên kết Facebook</t>
         </is>
       </c>
     </row>
     <row r="87" ht="18" customHeight="1">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>settings.connected-accounts.link-error</t>
+          <t>settings.connected-accounts.unlink-facebook</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Could not update Facebook link</t>
+          <t>Unlink Facebook</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Không cập nhật được liên kết Facebook</t>
+          <t>Huỷ liên kết Facebook</t>
         </is>
       </c>
     </row>
     <row r="88" ht="18" customHeight="1">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>settings.close</t>
+          <t>settings.connected-accounts.link-success</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Close</t>
+          <t>Facebook linked successfully</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Đóng</t>
+          <t>Đã liên kết Facebook</t>
         </is>
       </c>
     </row>
     <row r="89" ht="18" customHeight="1">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>popup.alert.title</t>
+          <t>settings.connected-accounts.unlink-success</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Facebook unlinked</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Cảnh báo</t>
+          <t>Đã huỷ liên kết Facebook</t>
         </is>
       </c>
     </row>
     <row r="90" ht="18" customHeight="1">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>popup.confirm.title</t>
+          <t>settings.connected-accounts.link-error</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Confirm</t>
+          <t>Could not update Facebook link</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Xác nhận</t>
+          <t>Không cập nhật được liên kết Facebook</t>
         </is>
       </c>
     </row>
     <row r="91" ht="18" customHeight="1">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>popup.confirm.ok</t>
+          <t>settings.close</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Ok</t>
+          <t>Close</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Ok</t>
+          <t>Đóng</t>
         </is>
       </c>
     </row>
     <row r="92" ht="18" customHeight="1">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>popup.confirm.cancel</t>
+          <t>popup.alert.title</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Huỷ</t>
+          <t>Cảnh báo</t>
         </is>
       </c>
     </row>
     <row r="93" ht="18" customHeight="1">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>game.general.captured</t>
+          <t>popup.confirm.title</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>General has been captured. Room over</t>
+          <t>Confirm</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Tướng đã bị bắt. Game kết thúc</t>
+          <t>Xác nhận</t>
         </is>
       </c>
     </row>
     <row r="94" ht="18" customHeight="1">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>game.general.in-check</t>
+          <t>popup.confirm.ok</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Your general is under attack</t>
+          <t>Ok</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Tướng của bạn đang bị chiếu</t>
+          <t>Ok</t>
         </is>
       </c>
     </row>
     <row r="95" ht="18" customHeight="1">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>game.label.win</t>
+          <t>popup.confirm.cancel</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Win</t>
+          <t>Cancel</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Thắng</t>
+          <t>Huỷ</t>
         </is>
       </c>
     </row>
     <row r="96" ht="18" customHeight="1">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>game.label.draw</t>
+          <t>game.general.captured</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Draw</t>
+          <t>General has been captured. Room over</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Hoà</t>
+          <t>Tướng đã bị bắt. Game kết thúc</t>
         </is>
       </c>
     </row>
     <row r="97" ht="18" customHeight="1">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>game.label.lose</t>
+          <t>game.general.in-check</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Lose</t>
+          <t>Your general is under attack</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Thua</t>
+          <t>Tướng của bạn đang bị chiếu</t>
         </is>
       </c>
     </row>
     <row r="98" ht="18" customHeight="1">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>room.bot-difficulty.title</t>
+          <t>game.label.win</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Select Bot Difficulty</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Chọn độ khó của Bot</t>
+          <t>Thắng</t>
         </is>
       </c>
     </row>
     <row r="99" ht="18" customHeight="1">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>room.bot-difficulty.beginner</t>
+          <t>game.label.draw</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Beginner</t>
+          <t>Draw</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Mới bắt đầu</t>
+          <t>Hoà</t>
         </is>
       </c>
     </row>
     <row r="100" ht="18" customHeight="1">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>room.bot-difficulty.amateur</t>
+          <t>game.label.lose</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Amateur</t>
+          <t>Lose</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Nghiệp dư</t>
+          <t>Thua</t>
         </is>
       </c>
     </row>
     <row r="101" ht="18" customHeight="1">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>room.bot-difficulty.intermediate</t>
+          <t>room.bot-difficulty.title</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Intermediate</t>
+          <t>Select Bot Difficulty</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Trung bình</t>
+          <t>Chọn độ khó của Bot</t>
         </is>
       </c>
     </row>
     <row r="102" ht="18" customHeight="1">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>room.bot-difficulty.advanced</t>
+          <t>room.bot-difficulty.beginner</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Advanced</t>
+          <t>Beginner</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Nâng cao</t>
+          <t>Mới bắt đầu</t>
         </is>
       </c>
     </row>
     <row r="103" ht="18" customHeight="1">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>room.bot-difficulty.master</t>
+          <t>room.bot-difficulty.amateur</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Master</t>
+          <t>Amateur</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Lão luyện</t>
+          <t>Nghiệp dư</t>
         </is>
       </c>
     </row>
     <row r="104" ht="18" customHeight="1">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>login.page.title</t>
+          <t>room.bot-difficulty.intermediate</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Login</t>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập</t>
+          <t>Trung bình</t>
         </is>
       </c>
     </row>
     <row r="105" ht="18" customHeight="1">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>login.form.title</t>
+          <t>room.bot-difficulty.advanced</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Login</t>
+          <t>Advanced</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập</t>
+          <t>Nâng cao</t>
         </is>
       </c>
     </row>
     <row r="106" ht="18" customHeight="1">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>login.username.label</t>
+          <t>room.bot-difficulty.master</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>User name</t>
+          <t>Master</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Tên người dùng</t>
+          <t>Lão luyện</t>
         </is>
       </c>
     </row>
     <row r="107" ht="18" customHeight="1">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>login.username.placeholder</t>
+          <t>login.page.title</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>User name</t>
+          <t>Login</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Tên người dùng</t>
+          <t>Đăng nhập</t>
         </is>
       </c>
     </row>
     <row r="108" ht="18" customHeight="1">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>login.password.label</t>
+          <t>login.form.title</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Password</t>
+          <t>Login</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Mật khẩu</t>
+          <t>Đăng nhập</t>
         </is>
       </c>
     </row>
     <row r="109" ht="18" customHeight="1">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>login.password.placeholder</t>
+          <t>login.username.label</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Password</t>
+          <t>User name</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Mật khẩu</t>
+          <t>Tên người dùng</t>
         </is>
       </c>
     </row>
     <row r="110" ht="36" customHeight="1">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>login.password.show</t>
+          <t>login.username.placeholder</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Show password</t>
+          <t>User name</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Hiện mật khẩu</t>
+          <t>Tên người dùng</t>
         </is>
       </c>
     </row>
     <row r="111" ht="18" customHeight="1">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>login.password.hide</t>
+          <t>login.password.label</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Hide password</t>
+          <t>Password</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Ẩn mật khẩu</t>
+          <t>Mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="112" ht="18" customHeight="1">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>login.form.error1</t>
+          <t>login.password.placeholder</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Login failed. Please check your credentials </t>
+          <t>Password</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập không thành công. Hãy kiểm tra lại</t>
+          <t>Mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="113" ht="18" customHeight="1">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>login.form.forgot-password</t>
+          <t>login.password.show</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Forgot password</t>
+          <t>Show password</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Quên mật khẩu</t>
+          <t>Hiện mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="114" ht="18" customHeight="1">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>login.form.register</t>
+          <t>login.password.hide</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Register</t>
+          <t>Hide password</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Đăng ký</t>
+          <t>Ẩn mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="115" ht="18" customHeight="1">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>login.form.submit</t>
+          <t>login.form.error1</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Login</t>
+          <t xml:space="preserve">Login failed. Please check your credentials </t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập</t>
+          <t>Đăng nhập không thành công. Hãy kiểm tra lại</t>
         </is>
       </c>
     </row>
     <row r="116" ht="18" customHeight="1">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>login.form.or</t>
+          <t>login.form.forgot-password</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>or</t>
+          <t>Forgot password</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>hoặc</t>
+          <t>Quên mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="117" ht="18" customHeight="1">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>login.google.load-error</t>
+          <t>login.form.register</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Could not load Google Sign-In</t>
+          <t>Register</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Không tải được đăng nhập Google</t>
+          <t>Đăng ký</t>
         </is>
       </c>
     </row>
     <row r="118" ht="18" customHeight="1">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>login.facebook.button</t>
+          <t>login.form.submit</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Sign-in with Facebook</t>
+          <t>Login</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập với Facebook</t>
+          <t>Đăng nhập</t>
         </is>
       </c>
     </row>
     <row r="119" ht="18" customHeight="1">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>login.messages.incorrect-login</t>
+          <t>login.form.or</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Invalid username or password</t>
+          <t>or</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Tên người dùng hoặc mật khẩu không hợp lệ</t>
+          <t>hoặc</t>
         </is>
       </c>
     </row>
     <row r="120" ht="18" customHeight="1">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>login.messages.internal-server-error</t>
+          <t>login.google.load-error</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Could not load Google Sign-In</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Không tải được đăng nhập Google</t>
         </is>
       </c>
     </row>
     <row r="121" ht="18" customHeight="1">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>login.messages.missing-credentials</t>
+          <t>login.facebook.button</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Username and password are required</t>
+          <t>Sign-in with Facebook</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Tên người dùng và mật khẩu là bắt buộc</t>
+          <t>Đăng nhập với Facebook</t>
         </is>
       </c>
     </row>
     <row r="122" ht="18" customHeight="1">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>login.messages.success</t>
+          <t>login.messages.incorrect-login</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Login successful</t>
+          <t>Invalid username or password</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập thành công</t>
+          <t>Tên người dùng hoặc mật khẩu không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="123" ht="18" customHeight="1">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>notfound.title</t>
+          <t>login.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>Page Not Found</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>Trang không tìm thấy</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="124" ht="18" customHeight="1">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>notfound.description</t>
+          <t>login.messages.missing-credentials</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>The page you are looking for does not exist or has been moved.</t>
+          <t>Username and password are required</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Trang bạn tìm kiếm không tồn tại hoặc đã được di chuyển.</t>
+          <t>Tên người dùng và mật khẩu là bắt buộc</t>
         </is>
       </c>
     </row>
     <row r="125" ht="18" customHeight="1">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>notfound.home</t>
+          <t>login.messages.success</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>Go to Home</t>
+          <t>Login successful</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Về trang chủ</t>
+          <t>Đăng nhập thành công</t>
         </is>
       </c>
     </row>
     <row r="126" ht="18" customHeight="1">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>notfound.back</t>
+          <t>notfound.title</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Go Back</t>
+          <t>Page Not Found</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Quay lại</t>
+          <t>Trang không tìm thấy</t>
         </is>
       </c>
     </row>
     <row r="127" ht="18" customHeight="1">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>register.confirm-password.error1</t>
+          <t>notfound.description</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>Confirm password does not match password</t>
+          <t>The page you are looking for does not exist or has been moved.</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Mật khẩu xác nhận không khớp với mật khẩu</t>
+          <t>Trang bạn tìm kiếm không tồn tại hoặc đã được di chuyển.</t>
         </is>
       </c>
     </row>
     <row r="128" ht="18" customHeight="1">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>register.confirm-password.label</t>
+          <t>notfound.home</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Confirm Password</t>
+          <t>Go to Home</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Xác nhận mật khẩu</t>
+          <t>Về trang chủ</t>
         </is>
       </c>
     </row>
     <row r="129" ht="18" customHeight="1">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>register.confirm-password.placeholder</t>
+          <t>notfound.back</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>Confirm Password</t>
+          <t>Go Back</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Xác nhận mật khẩu</t>
+          <t>Quay lại</t>
         </is>
       </c>
     </row>
     <row r="130" ht="36" customHeight="1">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>register.display-name.label</t>
+          <t>register.confirm-password.error1</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Display name</t>
+          <t>Confirm password does not match password</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Tên hiển thị</t>
+          <t>Mật khẩu xác nhận không khớp với mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="131" ht="18" customHeight="1">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>register.display-name.placeholder</t>
+          <t>register.confirm-password.label</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>Display name</t>
+          <t>Confirm Password</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>Tên hiển thị</t>
+          <t>Xác nhận mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="132" ht="18" customHeight="1">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>register.email.error1</t>
+          <t>register.confirm-password.placeholder</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Invalid email format</t>
+          <t>Confirm Password</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Định dạng email không hợp lệ</t>
+          <t>Xác nhận mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="133" ht="18" customHeight="1">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>register.email.label</t>
+          <t>register.display-name.label</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Display name</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Tên hiển thị</t>
         </is>
       </c>
     </row>
     <row r="134" ht="18" customHeight="1">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>register.email.placeholder</t>
+          <t>register.display-name.placeholder</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Display name</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Tên hiển thị</t>
         </is>
       </c>
     </row>
     <row r="135" ht="36" customHeight="1">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>register.form.login</t>
+          <t>register.email.error1</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>Back to login</t>
+          <t>Invalid email format</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>Về trang đăng nhập</t>
+          <t>Định dạng email không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="136" ht="18" customHeight="1">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>register.form.submit</t>
+          <t>register.email.label</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Register</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Đăng ký</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="137" ht="18" customHeight="1">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>register.form.success</t>
+          <t>register.email.placeholder</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>Registration successful. Redirecting to login...</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>Đăng ký thành công. Đang chuyển hướng...</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="138" ht="18" customHeight="1">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>register.form.title</t>
+          <t>register.form.login</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Register</t>
+          <t>Back to login</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Đăng ký</t>
+          <t>Về trang đăng nhập</t>
         </is>
       </c>
     </row>
     <row r="139" ht="18" customHeight="1">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>register.gender.female</t>
+          <t>register.form.submit</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Register</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>Nữ</t>
+          <t>Đăng ký</t>
         </is>
       </c>
     </row>
     <row r="140" ht="18" customHeight="1">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>register.gender.label</t>
+          <t>register.form.success</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Gender</t>
+          <t>Registration successful. Redirecting to login...</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Giới tính</t>
+          <t>Đăng ký thành công. Đang chuyển hướng...</t>
         </is>
       </c>
     </row>
     <row r="141" ht="18" customHeight="1">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>register.gender.male</t>
+          <t>register.form.title</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Register</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>Nam</t>
+          <t>Đăng ký</t>
         </is>
       </c>
     </row>
     <row r="142" ht="36" customHeight="1">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>register.gender.select</t>
+          <t>register.gender.female</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Select gender</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Chọn giới tính</t>
+          <t>Nữ</t>
         </is>
       </c>
     </row>
     <row r="143" ht="18" customHeight="1">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>register.page.title</t>
+          <t>register.gender.label</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>Register</t>
+          <t>Gender</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>Đăng ký</t>
+          <t>Giới tính</t>
         </is>
       </c>
     </row>
     <row r="144" ht="18" customHeight="1">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>register.password.error1</t>
+          <t>register.gender.male</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Password must be at least 8 characters and contain uppercase, lowercase, number, and special character</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Mật khẩu phải có ít nhất 8 ký tự và chứa chữ hoa, chữ thường, số và ký tự đặc biệt</t>
+          <t>Nam</t>
         </is>
       </c>
     </row>
     <row r="145" ht="18" customHeight="1">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>register.password.hide</t>
+          <t>register.gender.select</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>Hide password</t>
+          <t>Select gender</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>Ẩn mật khẩu</t>
+          <t>Chọn giới tính</t>
         </is>
       </c>
     </row>
     <row r="146" ht="18" customHeight="1">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>register.password.label</t>
+          <t>register.page.title</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Password</t>
+          <t>Register</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Mật khẩu</t>
+          <t>Đăng ký</t>
         </is>
       </c>
     </row>
     <row r="147" ht="36" customHeight="1">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>register.password.placeholder</t>
+          <t>register.password.error1</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>Password</t>
+          <t>Password must be at least 8 characters and contain uppercase, lowercase, number, and special character</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Mật khẩu</t>
+          <t>Mật khẩu phải có ít nhất 8 ký tự và chứa chữ hoa, chữ thường, số và ký tự đặc biệt</t>
         </is>
       </c>
     </row>
     <row r="148" ht="18" customHeight="1">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>register.password.show</t>
+          <t>register.password.hide</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Show password</t>
+          <t>Hide password</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Hiện mật khẩu</t>
+          <t>Ẩn mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="149" ht="36" customHeight="1">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>register.username.error1</t>
+          <t>register.password.label</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>User name must contain only alphanumeric characters, underscore, and dot</t>
+          <t>Password</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>Tên người dùng chỉ chứa ký tự chữ số, dấu gạch dưới và dấu chấm</t>
+          <t>Mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="150" ht="18" customHeight="1">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>register.username.label</t>
+          <t>register.password.placeholder</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>User name</t>
+          <t>Password</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Tên người dùng</t>
+          <t>Mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="151" ht="18" customHeight="1">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>register.username.placeholder</t>
+          <t>register.password.show</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>User name</t>
+          <t>Show password</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>Tên người dùng</t>
+          <t>Hiện mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="152" ht="18" customHeight="1">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.page.title</t>
+          <t>register.username.error1</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Forgot Password</t>
+          <t>User name must contain only alphanumeric characters, underscore, and dot</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>Quên mật khẩu</t>
+          <t>Tên người dùng chỉ chứa ký tự chữ số, dấu gạch dưới và dấu chấm</t>
         </is>
       </c>
     </row>
     <row r="153" ht="18" customHeight="1">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.form.title</t>
+          <t>register.username.label</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>Forgot Password</t>
+          <t>User name</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>Quên mật khẩu</t>
+          <t>Tên người dùng</t>
         </is>
       </c>
     </row>
     <row r="154" ht="18" customHeight="1">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.form.login</t>
+          <t>register.username.placeholder</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>Back to login</t>
+          <t>User name</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>Về trang đăng nhập</t>
+          <t>Tên người dùng</t>
         </is>
       </c>
     </row>
     <row r="155" ht="18" customHeight="1">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.form.submit</t>
+          <t>forgot-password.page.title</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>Forgot password</t>
+          <t>Forgot Password</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -2971,551 +2971,551 @@
     <row r="156" ht="18" customHeight="1">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.form.success</t>
+          <t>forgot-password.form.title</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>Check your email for reset password details.</t>
+          <t>Forgot Password</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Hãy kiểm tra email để xem thông tin đặt lại mật khẩu.</t>
+          <t>Quên mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="157" ht="18" customHeight="1">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.form.error1</t>
+          <t>forgot-password.form.login</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>Forgot password failed.</t>
+          <t>Back to login</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>Quên mật khẩu không thành công.</t>
+          <t>Về trang đăng nhập</t>
         </is>
       </c>
     </row>
     <row r="158" ht="18" customHeight="1">
       <c r="A158" s="1" t="inlineStr">
         <is>
-          <t>reset-password.page.title</t>
+          <t>forgot-password.form.submit</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>Reset Password</t>
+          <t>Forgot password</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>Đặt lại mật khẩu</t>
+          <t>Quên mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="159" ht="36" customHeight="1">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t>reset-password.form.title</t>
+          <t>forgot-password.form.success</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>Reset your password</t>
+          <t>Check your email for reset password details.</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>Đặt lại mật khẩu của bạn</t>
+          <t>Hãy kiểm tra email để xem thông tin đặt lại mật khẩu.</t>
         </is>
       </c>
     </row>
     <row r="160" ht="18" customHeight="1">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>reset-password.form.submit</t>
+          <t>forgot-password.form.error1</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>Reset Password</t>
+          <t>Forgot password failed.</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Đặt lại mật khẩu</t>
+          <t>Quên mật khẩu không thành công.</t>
         </is>
       </c>
     </row>
     <row r="161" ht="36" customHeight="1">
       <c r="A161" s="1" t="inlineStr">
         <is>
-          <t>reset-password.form.error1</t>
+          <t>reset-password.page.title</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>An error occurred while resetting your password. Please try again.</t>
+          <t>Reset Password</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>Có lỗi xảy ra khi đặt lại mật khẩu. Vui lòng thử lại.</t>
+          <t>Đặt lại mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="162" ht="18" customHeight="1">
       <c r="A162" s="1" t="inlineStr">
         <is>
-          <t>reset-password.form.invalid-token</t>
+          <t>reset-password.form.title</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>Invalid or expired reset password token</t>
+          <t>Reset your password</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Token đặt lại mật khẩu không hợp lệ hoặc đã hết hạn</t>
+          <t>Đặt lại mật khẩu của bạn</t>
         </is>
       </c>
     </row>
     <row r="163" ht="18" customHeight="1">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t>reset-password.form.success</t>
+          <t>reset-password.form.submit</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>Password reset successfully. Redirecting to login...</t>
+          <t>Reset Password</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>Đặt lại mật khẩu thành công. Đang chuyển hướng đến đăng nhập...</t>
+          <t>Đặt lại mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="164" ht="36" customHeight="1">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t>reset-password.action.back-to-login</t>
+          <t>reset-password.form.error1</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>Back to login</t>
+          <t>An error occurred while resetting your password. Please try again.</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Quay lại trang chủ</t>
+          <t>Có lỗi xảy ra khi đặt lại mật khẩu. Vui lòng thử lại.</t>
         </is>
       </c>
     </row>
     <row r="165" ht="18" customHeight="1">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t>auth-middleware.messages.invalid-token-payload</t>
+          <t>reset-password.form.invalid-token</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>Invalid token payload</t>
+          <t>Invalid or expired reset password token</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>Payload của token không hợp lệ</t>
+          <t>Token đặt lại mật khẩu không hợp lệ hoặc đã hết hạn</t>
         </is>
       </c>
     </row>
     <row r="166" ht="18" customHeight="1">
       <c r="A166" s="1" t="inlineStr">
         <is>
-          <t>auth-middleware.messages.session-not-found</t>
+          <t>reset-password.form.success</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>Session not found</t>
+          <t>Password reset successfully. Redirecting to login...</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy phiên</t>
+          <t>Đặt lại mật khẩu thành công. Đang chuyển hướng đến đăng nhập...</t>
         </is>
       </c>
     </row>
     <row r="167" ht="18" customHeight="1">
       <c r="A167" s="1" t="inlineStr">
         <is>
-          <t>auth-middleware.messages.token-expired</t>
+          <t>reset-password.action.back-to-login</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>Token is expired</t>
+          <t>Back to login</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>Token đã hết hạn</t>
+          <t>Quay lại trang chủ</t>
         </is>
       </c>
     </row>
     <row r="168" ht="18" customHeight="1">
       <c r="A168" s="1" t="inlineStr">
         <is>
-          <t>auth-middleware.messages.token-invalid</t>
+          <t>auth-middleware.messages.invalid-token-payload</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>Token is invalid</t>
+          <t>Invalid token payload</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>Token không hợp lệ</t>
+          <t>Payload của token không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="169" ht="18" customHeight="1">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t>auth-middleware.messages.token-required</t>
+          <t>auth-middleware.messages.session-not-found</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>Token not provided</t>
+          <t>Session not found</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>Token không được cung cấp</t>
+          <t>Không tìm thấy phiên</t>
         </is>
       </c>
     </row>
     <row r="170" ht="18" customHeight="1">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t>auth-middleware.messages.token-subject-mismatch</t>
+          <t>auth-middleware.messages.token-expired</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>Token subject mismatch</t>
+          <t>Token is expired</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>Token chủ đề không khớp</t>
+          <t>Token đã hết hạn</t>
         </is>
       </c>
     </row>
     <row r="171" ht="18" customHeight="1">
       <c r="A171" s="1" t="inlineStr">
         <is>
-          <t>auth-middleware.messages.token-validation-failed</t>
+          <t>auth-middleware.messages.token-invalid</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>Token validation failed</t>
+          <t>Token is invalid</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>Xác thực token không thành công</t>
+          <t>Token không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="172" ht="18" customHeight="1">
       <c r="A172" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.insufficient-amount</t>
+          <t>auth-middleware.messages.token-required</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>You do not have enough balance to create a room with this bet</t>
+          <t>Token not provided</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>Bạn không còn đủ amount để tạo phòng với mức cược này</t>
+          <t>Token không được cung cấp</t>
         </is>
       </c>
     </row>
     <row r="173" ht="18" customHeight="1">
       <c r="A173" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.internal-server-error</t>
+          <t>auth-middleware.messages.token-subject-mismatch</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>Internal server error while creating room</t>
+          <t>Token subject mismatch</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ khi tạo phòng</t>
+          <t>Token chủ đề không khớp</t>
         </is>
       </c>
     </row>
     <row r="174" ht="18" customHeight="1">
       <c r="A174" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.invalid-bet-amount</t>
+          <t>auth-middleware.messages.token-validation-failed</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>Bet amount is required and must be one of the acceptable values</t>
+          <t>Token validation failed</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>Số tiền cược là bắt buộc và phải là một trong các giá trị được chấp nhận</t>
+          <t>Xác thực token không thành công</t>
         </is>
       </c>
     </row>
     <row r="175" ht="18" customHeight="1">
       <c r="A175" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.invalid-redFirst</t>
+          <t>create-room.messages.insufficient-amount</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>'redFirst' must be a boolean</t>
+          <t>You do not have enough balance to create a room with this bet</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>'redFirst' phải là giá trị boolean</t>
+          <t>Bạn không còn đủ amount để tạo phòng với mức cược này</t>
         </is>
       </c>
     </row>
     <row r="176" ht="36" customHeight="1">
       <c r="A176" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.invalid-team-name</t>
+          <t>create-room.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>Team name must be either 'red', 'black', or null</t>
+          <t>Internal server error while creating room</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>Tên đội phải là 'red', 'black' hoặc null</t>
+          <t>Lỗi máy chủ nội bộ khi tạo phòng</t>
         </is>
       </c>
     </row>
     <row r="177" ht="18" customHeight="1">
       <c r="A177" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.name-required</t>
+          <t>create-room.messages.invalid-bet-amount</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>Room name (tableName) is required and must not be empty</t>
+          <t>Bet amount is required and must be one of the acceptable values</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>Tên phòng (tableName) là bắt buộc và không được để trống</t>
+          <t>Số tiền cược là bắt buộc và phải là một trong các giá trị được chấp nhận</t>
         </is>
       </c>
     </row>
     <row r="178" ht="18" customHeight="1">
       <c r="A178" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.room-created</t>
+          <t>create-room.messages.invalid-time-limit</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>Room created successfully</t>
+          <t>Invalid time limit</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>Phòng được tạo thành công</t>
+          <t>Thời gian không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="179" ht="18" customHeight="1">
       <c r="A179" s="1" t="inlineStr">
         <is>
-          <t>fetch-rooms.messages.internal-server-error</t>
+          <t>create-room.messages.invalid-redFirst</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>'redFirst' must be a boolean</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>'redFirst' phải là giá trị boolean</t>
         </is>
       </c>
     </row>
     <row r="180" ht="18" customHeight="1">
       <c r="A180" s="1" t="inlineStr">
         <is>
-          <t>fetch-rooms.messages.invalid-status</t>
+          <t>create-room.messages.invalid-team-name</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>Query parameter 'status' must be an integer</t>
+          <t>Team name must be either 'red', 'black', or null</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>Tham số truy vấn 'status' phải là số nguyên</t>
+          <t>Tên đội phải là 'red', 'black' hoặc null</t>
         </is>
       </c>
     </row>
     <row r="181" ht="18" customHeight="1">
       <c r="A181" s="1" t="inlineStr">
         <is>
-          <t>fetch-rooms.messages.success</t>
+          <t>create-room.messages.name-required</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>Fetch rooms successfully</t>
+          <t>Room name (tableName) is required and must not be empty</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>Lấy phòng thành công</t>
+          <t>Tên phòng (tableName) là bắt buộc và không được để trống</t>
         </is>
       </c>
     </row>
     <row r="182" ht="18" customHeight="1">
       <c r="A182" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.messages.email-not-found</t>
+          <t>create-room.messages.room-created</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>Email does not exist</t>
+          <t>Room created successfully</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>Email không tồn tại</t>
+          <t>Phòng được tạo thành công</t>
         </is>
       </c>
     </row>
     <row r="183" ht="18" customHeight="1">
       <c r="A183" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.messages.email-service-not-configured</t>
+          <t>fetch-rooms.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>Email service is not configured</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>Dịch vụ email chưa được cấu hình</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="184" ht="18" customHeight="1">
       <c r="A184" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.messages.internal-server-error</t>
+          <t>fetch-rooms.messages.invalid-status</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Query parameter 'status' must be an integer</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Tham số truy vấn 'status' phải là số nguyên</t>
         </is>
       </c>
     </row>
     <row r="185" ht="36" customHeight="1">
       <c r="A185" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.messages.invalid-email-format</t>
+          <t>fetch-rooms.messages.success</t>
         </is>
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>Invalid email format</t>
+          <t>Fetch rooms successfully</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>Định dạng email không hợp lệ</t>
+          <t>Lấy phòng thành công</t>
         </is>
       </c>
     </row>
     <row r="186" ht="18" customHeight="1">
       <c r="A186" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.messages.missing-email</t>
+          <t>forgot-password.messages.email-not-found</t>
         </is>
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>Email is required</t>
+          <t>Email does not exist</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>Email là bắt buộc</t>
+          <t>Email không tồn tại</t>
         </is>
       </c>
     </row>
     <row r="187" ht="36" customHeight="1">
       <c r="A187" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.messages.success</t>
+          <t>forgot-password.messages.email-service-not-configured</t>
         </is>
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>Forgot password email sent</t>
+          <t>Email service is not configured</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>Email đặt lại mật khẩu đã được gửi</t>
+          <t>Dịch vụ email chưa được cấu hình</t>
         </is>
       </c>
     </row>
     <row r="188" ht="18" customHeight="1">
       <c r="A188" s="1" t="inlineStr">
         <is>
-          <t>join-room.messages.internal-server-error</t>
+          <t>forgot-password.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr">
@@ -3532,330 +3532,330 @@
     <row r="189" ht="18" customHeight="1">
       <c r="A189" s="1" t="inlineStr">
         <is>
-          <t>join-room.messages.invalid-team</t>
+          <t>forgot-password.messages.invalid-email-format</t>
         </is>
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>Field 'team' must be 'red', 'black', null, or undefined</t>
+          <t>Invalid email format</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>Trường 'team' phải là 'red', 'black', null hoặc không truyền</t>
+          <t>Định dạng email không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="190" ht="18" customHeight="1">
       <c r="A190" s="1" t="inlineStr">
         <is>
-          <t>join-room.messages.invalid-room-id</t>
+          <t>forgot-password.messages.missing-email</t>
         </is>
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>Field 'id' is required and must be a positive integer</t>
+          <t>Email is required</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
+          <t>Email là bắt buộc</t>
         </is>
       </c>
     </row>
     <row r="191" ht="18" customHeight="1">
       <c r="A191" s="1" t="inlineStr">
         <is>
-          <t>join-room.messages.room-not-found</t>
+          <t>forgot-password.messages.success</t>
         </is>
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>Room not found</t>
+          <t>Forgot password email sent</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy phòng</t>
+          <t>Email đặt lại mật khẩu đã được gửi</t>
         </is>
       </c>
     </row>
     <row r="192" ht="18" customHeight="1">
       <c r="A192" s="1" t="inlineStr">
         <is>
-          <t>join-room.messages.success</t>
+          <t>join-room.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>Successfully joined the room</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>Tham gia phòng thành công</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="193" ht="18" customHeight="1">
       <c r="A193" s="1" t="inlineStr">
         <is>
-          <t>join-room.messages.team-seat-occupied</t>
+          <t>join-room.messages.invalid-team</t>
         </is>
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>Selected team seat is already occupied</t>
+          <t>Field 'team' must be 'red', 'black', null, or undefined</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>Vị trí đội đã chọn đã có người chơi</t>
+          <t>Trường 'team' phải là 'red', 'black', null hoặc không truyền</t>
         </is>
       </c>
     </row>
     <row r="194" ht="18" customHeight="1">
       <c r="A194" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.cannot-kick-self</t>
+          <t>join-room.messages.invalid-room-id</t>
         </is>
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>You cannot kick yourself</t>
+          <t>Field 'id' is required and must be a positive integer</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>Bạn không thể kick chính mình</t>
+          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
         </is>
       </c>
     </row>
     <row r="195" ht="18" customHeight="1">
       <c r="A195" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.forbidden</t>
+          <t>join-room.messages.room-not-found</t>
         </is>
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>Only the host can kick users</t>
+          <t>Room not found</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>Chỉ chủ phòng mới có thể kick người dùng</t>
+          <t>Không tìm thấy phòng</t>
         </is>
       </c>
     </row>
     <row r="196" ht="18" customHeight="1">
       <c r="A196" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.internal-server-error</t>
+          <t>join-room.messages.success</t>
         </is>
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Successfully joined the room</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Tham gia phòng thành công</t>
         </is>
       </c>
     </row>
     <row r="197" ht="18" customHeight="1">
       <c r="A197" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.invalid-room-id</t>
+          <t>join-room.messages.team-seat-occupied</t>
         </is>
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>Field 'id' is required and must be a positive integer</t>
+          <t>Selected team seat is already occupied</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
+          <t>Vị trí đội đã chọn đã có người chơi</t>
         </is>
       </c>
     </row>
     <row r="198" ht="18" customHeight="1">
       <c r="A198" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.invalid-user-id</t>
+          <t>kick-user.messages.cannot-kick-self</t>
         </is>
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>Field 'userId' is required and must be a positive integer</t>
+          <t>You cannot kick yourself</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>Trường 'userId' là bắt buộc và phải là số nguyên dương</t>
+          <t>Bạn không thể kick chính mình</t>
         </is>
       </c>
     </row>
     <row r="199" ht="18" customHeight="1">
       <c r="A199" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.room-not-found</t>
+          <t>kick-user.messages.forbidden</t>
         </is>
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>Room not found</t>
+          <t>Only the host can kick users</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy phòng</t>
+          <t>Chỉ chủ phòng mới có thể kick người dùng</t>
         </is>
       </c>
     </row>
     <row r="200" ht="18" customHeight="1">
       <c r="A200" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.room-not-waiting</t>
+          <t>kick-user.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>You can only kick users while the room is waiting</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>Chỉ có thể kick người dùng khi phòng đang ở trạng thái chờ</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="201" ht="18" customHeight="1">
       <c r="A201" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.success</t>
+          <t>kick-user.messages.invalid-room-id</t>
         </is>
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>User has been kicked</t>
+          <t>Field 'id' is required and must be a positive integer</t>
         </is>
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>Người dùng đã bị kick</t>
+          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
         </is>
       </c>
     </row>
     <row r="202" ht="18" customHeight="1">
       <c r="A202" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.user-not-in-room</t>
+          <t>kick-user.messages.invalid-user-id</t>
         </is>
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>User is not in this room</t>
+          <t>Field 'userId' is required and must be a positive integer</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>Người dùng không trong phòng này</t>
+          <t>Trường 'userId' là bắt buộc và phải là số nguyên dương</t>
         </is>
       </c>
     </row>
     <row r="203" ht="18" customHeight="1">
       <c r="A203" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.you-were-kicked</t>
+          <t>kick-user.messages.room-not-found</t>
         </is>
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>You have been removed from the room by the host</t>
+          <t>Room not found</t>
         </is>
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>Bạn đã bị chủ phòng đưa ra khỏi phòng</t>
+          <t>Không tìm thấy phòng</t>
         </is>
       </c>
     </row>
     <row r="204" ht="18" customHeight="1">
       <c r="A204" s="1" t="inlineStr">
         <is>
-          <t>leave-room.messages.internal-server-error</t>
+          <t>kick-user.messages.room-not-waiting</t>
         </is>
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>You can only kick users while the room is waiting</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Chỉ có thể kick người dùng khi phòng đang ở trạng thái chờ</t>
         </is>
       </c>
     </row>
     <row r="205" ht="18" customHeight="1">
       <c r="A205" s="1" t="inlineStr">
         <is>
-          <t>leave-room.messages.invalid-room-id</t>
+          <t>kick-user.messages.success</t>
         </is>
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>Field 'id' is required and must be a positive integer</t>
+          <t>User has been kicked</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
+          <t>Người dùng đã bị kick</t>
         </is>
       </c>
     </row>
     <row r="206" ht="18" customHeight="1">
       <c r="A206" s="1" t="inlineStr">
         <is>
-          <t>leave-room.messages.player-not-in-room</t>
+          <t>kick-user.messages.user-not-in-room</t>
         </is>
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>Player is not in this room</t>
+          <t>User is not in this room</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>Người chơi không trong phòng này</t>
+          <t>Người dùng không trong phòng này</t>
         </is>
       </c>
     </row>
     <row r="207" ht="18" customHeight="1">
       <c r="A207" s="1" t="inlineStr">
         <is>
-          <t>leave-room.messages.success</t>
+          <t>kick-user.messages.you-were-kicked</t>
         </is>
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>Leave room successfully</t>
+          <t>You have been removed from the room by the host</t>
         </is>
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>Rời phòng thành công</t>
+          <t>Bạn đã bị chủ phòng đưa ra khỏi phòng</t>
         </is>
       </c>
     </row>
     <row r="208" ht="18" customHeight="1">
       <c r="A208" s="1" t="inlineStr">
         <is>
-          <t>load-room.messages.internal-server-error</t>
+          <t>leave-room.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B208" s="2" t="inlineStr">
@@ -3872,211 +3872,211 @@
     <row r="209" ht="18" customHeight="1">
       <c r="A209" s="1" t="inlineStr">
         <is>
-          <t>load-room.messages.invalid-room-id</t>
+          <t>leave-room.messages.invalid-room-id</t>
         </is>
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>Room ID must be a positive integer</t>
+          <t>Field 'id' is required and must be a positive integer</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>ID phòng phải là số nguyên dương</t>
+          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
         </is>
       </c>
     </row>
     <row r="210" ht="18" customHeight="1">
       <c r="A210" s="1" t="inlineStr">
         <is>
-          <t>load-room.messages.room-not-found</t>
+          <t>leave-room.messages.player-not-in-room</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>Room not found</t>
+          <t>Player is not in this room</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy phòng</t>
+          <t>Người chơi không trong phòng này</t>
         </is>
       </c>
     </row>
     <row r="211" ht="36" customHeight="1">
       <c r="A211" s="1" t="inlineStr">
         <is>
-          <t>load-room.messages.success</t>
+          <t>leave-room.messages.success</t>
         </is>
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>Load room successfully</t>
+          <t>Leave room successfully</t>
         </is>
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>Tải phòng thành công</t>
+          <t>Rời phòng thành công</t>
         </is>
       </c>
     </row>
     <row r="212" ht="18" customHeight="1">
       <c r="A212" s="1" t="inlineStr">
         <is>
-          <t>google-login.messages.email-not-verified</t>
+          <t>load-room.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>Your Google email is not verified</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>Email Google của bạn chưa được xác minh</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="213" ht="18" customHeight="1">
       <c r="A213" s="1" t="inlineStr">
         <is>
-          <t>google-login.messages.failed</t>
+          <t>load-room.messages.invalid-room-id</t>
         </is>
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>Login failed</t>
+          <t>Room ID must be a positive integer</t>
         </is>
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập không thành công</t>
+          <t>ID phòng phải là số nguyên dương</t>
         </is>
       </c>
     </row>
     <row r="214" ht="18" customHeight="1">
       <c r="A214" s="1" t="inlineStr">
         <is>
-          <t>google-login.messages.internal-server-error</t>
+          <t>load-room.messages.room-not-found</t>
         </is>
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Room not found</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Không tìm thấy phòng</t>
         </is>
       </c>
     </row>
     <row r="215" ht="18" customHeight="1">
       <c r="A215" s="1" t="inlineStr">
         <is>
-          <t>google-login.messages.invalid-token</t>
+          <t>load-room.messages.success</t>
         </is>
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>Invalid Google credential</t>
+          <t>Load room successfully</t>
         </is>
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>Thông tin đăng nhập Google không hợp lệ</t>
+          <t>Tải phòng thành công</t>
         </is>
       </c>
     </row>
     <row r="216" ht="18" customHeight="1">
       <c r="A216" s="1" t="inlineStr">
         <is>
-          <t>google-login.messages.missing-credential</t>
+          <t>google-login.messages.email-not-verified</t>
         </is>
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>Google credential is required</t>
+          <t>Your Google email is not verified</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>Thiếu thông tin đăng nhập Google</t>
+          <t>Email Google của bạn chưa được xác minh</t>
         </is>
       </c>
     </row>
     <row r="217" ht="18" customHeight="1">
       <c r="A217" s="1" t="inlineStr">
         <is>
-          <t>facebook-login.messages.missing-token</t>
+          <t>google-login.messages.failed</t>
         </is>
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>Facebook token is required</t>
+          <t>Login failed</t>
         </is>
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>Thiếu thông tin đăng nhập Facebook</t>
+          <t>Đăng nhập không thành công</t>
         </is>
       </c>
     </row>
     <row r="218" ht="18" customHeight="1">
       <c r="A218" s="1" t="inlineStr">
         <is>
-          <t>facebook-login.messages.invalid-token</t>
+          <t>google-login.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>Invalid Facebook token</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>Thông tin đăng nhập Facebook không hợp lệ</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="219" ht="18" customHeight="1">
       <c r="A219" s="1" t="inlineStr">
         <is>
-          <t>facebook-login.messages.not-linked</t>
+          <t>google-login.messages.invalid-token</t>
         </is>
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>This Facebook account is not linked. Log in another way and link it in Settings</t>
+          <t>Invalid Google credential</t>
         </is>
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản Facebook này chưa được liên kết. Hãy đăng nhập cách khác rồi liên kết trong Cài đặt</t>
+          <t>Thông tin đăng nhập Google không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="220" ht="18" customHeight="1">
       <c r="A220" s="1" t="inlineStr">
         <is>
-          <t>facebook-login.messages.internal-server-error</t>
+          <t>google-login.messages.missing-credential</t>
         </is>
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Google credential is required</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Thiếu thông tin đăng nhập Google</t>
         </is>
       </c>
     </row>
     <row r="221" ht="18" customHeight="1">
       <c r="A221" s="1" t="inlineStr">
         <is>
-          <t>facebook-link.messages.missing-token</t>
+          <t>facebook-login.messages.missing-token</t>
         </is>
       </c>
       <c r="B221" s="2" t="inlineStr">
@@ -4093,7 +4093,7 @@
     <row r="222" ht="18" customHeight="1">
       <c r="A222" s="1" t="inlineStr">
         <is>
-          <t>facebook-link.messages.invalid-token</t>
+          <t>facebook-login.messages.invalid-token</t>
         </is>
       </c>
       <c r="B222" s="2" t="inlineStr">
@@ -4110,296 +4110,296 @@
     <row r="223" ht="18" customHeight="1">
       <c r="A223" s="1" t="inlineStr">
         <is>
-          <t>facebook-link.messages.linked</t>
+          <t>facebook-login.messages.not-linked</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>Facebook linked successfully</t>
+          <t>This Facebook account is not linked. Log in another way and link it in Settings</t>
         </is>
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>Đã liên kết Facebook</t>
+          <t>Tài khoản Facebook này chưa được liên kết. Hãy đăng nhập cách khác rồi liên kết trong Cài đặt</t>
         </is>
       </c>
     </row>
     <row r="224" ht="18" customHeight="1">
       <c r="A224" s="1" t="inlineStr">
         <is>
-          <t>facebook-link.messages.already-linked</t>
+          <t>facebook-login.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>This Facebook account is already linked to your account</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản Facebook này đã được liên kết với bạn</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="225" ht="18" customHeight="1">
       <c r="A225" s="1" t="inlineStr">
         <is>
-          <t>facebook-link.messages.linked-to-other</t>
+          <t>facebook-link.messages.missing-token</t>
         </is>
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>This Facebook account is already linked to another account</t>
+          <t>Facebook token is required</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản Facebook này đã được liên kết với tài khoản khác</t>
+          <t>Thiếu thông tin đăng nhập Facebook</t>
         </is>
       </c>
     </row>
     <row r="226" ht="18" customHeight="1">
       <c r="A226" s="1" t="inlineStr">
         <is>
-          <t>facebook-link.messages.already-has-facebook</t>
+          <t>facebook-link.messages.invalid-token</t>
         </is>
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>You already linked a different Facebook account</t>
+          <t>Invalid Facebook token</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>Bạn đã liên kết một tài khoản Facebook khác</t>
+          <t>Thông tin đăng nhập Facebook không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="227" ht="18" customHeight="1">
       <c r="A227" s="1" t="inlineStr">
         <is>
-          <t>facebook-link.messages.unlinked</t>
+          <t>facebook-link.messages.linked</t>
         </is>
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>Facebook unlinked</t>
+          <t>Facebook linked successfully</t>
         </is>
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>Đã huỷ liên kết Facebook</t>
+          <t>Đã liên kết Facebook</t>
         </is>
       </c>
     </row>
     <row r="228" ht="18" customHeight="1">
       <c r="A228" s="1" t="inlineStr">
         <is>
-          <t>facebook-link.messages.internal-server-error</t>
+          <t>facebook-link.messages.already-linked</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>This Facebook account is already linked to your account</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Tài khoản Facebook này đã được liên kết với bạn</t>
         </is>
       </c>
     </row>
     <row r="229" ht="18" customHeight="1">
       <c r="A229" s="1" t="inlineStr">
         <is>
-          <t>logout.messages.already-inactive</t>
+          <t>facebook-link.messages.linked-to-other</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>Session already inactive</t>
+          <t>This Facebook account is already linked to another account</t>
         </is>
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>Phiên đã ngưng hoạt động</t>
+          <t>Tài khoản Facebook này đã được liên kết với tài khoản khác</t>
         </is>
       </c>
     </row>
     <row r="230" ht="18" customHeight="1">
       <c r="A230" s="1" t="inlineStr">
         <is>
-          <t>logout.messages.internal-server-error</t>
+          <t>facebook-link.messages.already-has-facebook</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>You already linked a different Facebook account</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Bạn đã liên kết một tài khoản Facebook khác</t>
         </is>
       </c>
     </row>
     <row r="231" ht="18" customHeight="1">
       <c r="A231" s="1" t="inlineStr">
         <is>
-          <t>logout.messages.success</t>
+          <t>facebook-link.messages.unlinked</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>Logout successful</t>
+          <t>Facebook unlinked</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>Đăng xuất thành công</t>
+          <t>Đã huỷ liên kết Facebook</t>
         </is>
       </c>
     </row>
     <row r="232" ht="18" customHeight="1">
       <c r="A232" s="1" t="inlineStr">
         <is>
-          <t>refresh-token.messages.missing-refresh-token</t>
+          <t>facebook-link.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>Missing refresh token cookie</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>Thiếu cookie token làm mới</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="233" ht="18" customHeight="1">
       <c r="A233" s="1" t="inlineStr">
         <is>
-          <t>refresh-token.messages.mismatch-or-expired</t>
+          <t>logout.messages.already-inactive</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>Refresh token mismatch or expired</t>
+          <t>Session already inactive</t>
         </is>
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>Thiếu refresh token hoặc đã hết hạn</t>
+          <t>Phiên đã ngưng hoạt động</t>
         </is>
       </c>
     </row>
     <row r="234" ht="18" customHeight="1">
       <c r="A234" s="1" t="inlineStr">
         <is>
-          <t>refresh-token.messages.success</t>
+          <t>logout.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>Token refreshed</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>Token đã làm mới</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="235" ht="18" customHeight="1">
       <c r="A235" s="1" t="inlineStr">
         <is>
-          <t>register.messages.email-exists</t>
+          <t>logout.messages.success</t>
         </is>
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>Email already exists</t>
+          <t>Logout successful</t>
         </is>
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>Email đã tồn tại</t>
+          <t>Đăng xuất thành công</t>
         </is>
       </c>
     </row>
     <row r="236" ht="18" customHeight="1">
       <c r="A236" s="1" t="inlineStr">
         <is>
-          <t>register.messages.internal-server-error</t>
+          <t>refresh-token.messages.missing-refresh-token</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Missing refresh token cookie</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Thiếu cookie token làm mới</t>
         </is>
       </c>
     </row>
     <row r="237" ht="18" customHeight="1">
       <c r="A237" s="1" t="inlineStr">
         <is>
-          <t>register.messages.missing-fields</t>
+          <t>refresh-token.messages.mismatch-or-expired</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>Username, password, gender, displayName and email are required</t>
+          <t>Refresh token mismatch or expired</t>
         </is>
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>Tên người dùng, mật khẩu, giới tính, tên hiển thị và email là bắt buộc</t>
+          <t>Thiếu refresh token hoặc đã hết hạn</t>
         </is>
       </c>
     </row>
     <row r="238" ht="18" customHeight="1">
       <c r="A238" s="1" t="inlineStr">
         <is>
-          <t>register.messages.success</t>
+          <t>refresh-token.messages.success</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>User created successfully</t>
+          <t>Token refreshed</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>Người dùng được tạo thành công</t>
+          <t>Token đã làm mới</t>
         </is>
       </c>
     </row>
     <row r="239" ht="18" customHeight="1">
       <c r="A239" s="1" t="inlineStr">
         <is>
-          <t>register.messages.username-exists</t>
+          <t>register.messages.email-exists</t>
         </is>
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>Username already exists</t>
+          <t>Email already exists</t>
         </is>
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>Tên người dùng đã tồn tại</t>
+          <t>Email đã tồn tại</t>
         </is>
       </c>
     </row>
     <row r="240" ht="18" customHeight="1">
       <c r="A240" s="1" t="inlineStr">
         <is>
-          <t>reset-password.messages.internal-server-error</t>
+          <t>register.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr">
@@ -4416,1270 +4416,1270 @@
     <row r="241" ht="18" customHeight="1">
       <c r="A241" s="1" t="inlineStr">
         <is>
-          <t>reset-password.messages.invalid-or-expired-token</t>
+          <t>register.messages.missing-fields</t>
         </is>
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>Invalid or expired reset password token</t>
+          <t>Username, password, gender, displayName and email are required</t>
         </is>
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>Token đặt lại mật khẩu không hợp lệ hoặc đã hết hạn</t>
+          <t>Tên người dùng, mật khẩu, giới tính, tên hiển thị và email là bắt buộc</t>
         </is>
       </c>
     </row>
     <row r="242" ht="18" customHeight="1">
       <c r="A242" s="1" t="inlineStr">
         <is>
-          <t>reset-password.messages.invalid-user-id</t>
+          <t>register.messages.success</t>
         </is>
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>Invalid user id</t>
+          <t>User created successfully</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>ID người dùng không hợp lệ</t>
+          <t>Người dùng được tạo thành công</t>
         </is>
       </c>
     </row>
     <row r="243" ht="18" customHeight="1">
       <c r="A243" s="1" t="inlineStr">
         <is>
-          <t>reset-password.messages.missing-id-or-token</t>
+          <t>register.messages.username-exists</t>
         </is>
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>ID and token are required</t>
+          <t>Username already exists</t>
         </is>
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>ID và token là bắt buộc</t>
+          <t>Tên người dùng đã tồn tại</t>
         </is>
       </c>
     </row>
     <row r="244" ht="18" customHeight="1">
       <c r="A244" s="1" t="inlineStr">
         <is>
-          <t>reset-password.messages.missing-userId-or-password</t>
+          <t>reset-password.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>UserId and password are required</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>UserId và mật khẩu là bắt buộc</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="245" ht="18" customHeight="1">
       <c r="A245" s="1" t="inlineStr">
         <is>
-          <t>reset-password.messages.token-valid</t>
+          <t>reset-password.messages.invalid-or-expired-token</t>
         </is>
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>Reset password token is valid</t>
+          <t>Invalid or expired reset password token</t>
         </is>
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>Token đặt lại mật khẩu hợp lệ</t>
+          <t>Token đặt lại mật khẩu không hợp lệ hoặc đã hết hạn</t>
         </is>
       </c>
     </row>
     <row r="246" ht="18" customHeight="1">
       <c r="A246" s="1" t="inlineStr">
         <is>
-          <t>reset-password.messages.user-not-found</t>
+          <t>reset-password.messages.invalid-user-id</t>
         </is>
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>User not found</t>
+          <t>Invalid user id</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy người dùng</t>
+          <t>ID người dùng không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="247" ht="18" customHeight="1">
       <c r="A247" s="1" t="inlineStr">
         <is>
-          <t>room.actions.start-room</t>
+          <t>reset-password.messages.missing-id-or-token</t>
         </is>
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>Start room</t>
+          <t>ID and token are required</t>
         </is>
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>Bắt đầu chơi</t>
+          <t>ID và token là bắt buộc</t>
         </is>
       </c>
     </row>
     <row r="248" ht="18" customHeight="1">
       <c r="A248" s="1" t="inlineStr">
         <is>
-          <t>room.actions.challenge</t>
+          <t>reset-password.messages.missing-userId-or-password</t>
         </is>
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>Challenge</t>
+          <t>UserId and password are required</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>Thách đấu</t>
+          <t>UserId và mật khẩu là bắt buộc</t>
         </is>
       </c>
     </row>
     <row r="249" ht="18" customHeight="1">
       <c r="A249" s="1" t="inlineStr">
         <is>
-          <t>room.actions.leave-seat</t>
+          <t>reset-password.messages.token-valid</t>
         </is>
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>Leave seat</t>
+          <t>Reset password token is valid</t>
         </is>
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>Dự khán</t>
+          <t>Token đặt lại mật khẩu hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="250" ht="18" customHeight="1">
       <c r="A250" s="1" t="inlineStr">
         <is>
-          <t>room.actions.undo</t>
+          <t>reset-password.messages.user-not-found</t>
         </is>
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>Undo</t>
+          <t>User not found</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>Hoán tác</t>
+          <t>Không tìm thấy người dùng</t>
         </is>
       </c>
     </row>
     <row r="251" ht="18" customHeight="1">
       <c r="A251" s="1" t="inlineStr">
         <is>
-          <t>room.actions.surrender</t>
+          <t>room.actions.start-room</t>
         </is>
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t>Surrender</t>
+          <t>Start room</t>
         </is>
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>Đầu hàng</t>
+          <t>Bắt đầu chơi</t>
         </is>
       </c>
     </row>
     <row r="252" ht="18" customHeight="1">
       <c r="A252" s="1" t="inlineStr">
         <is>
-          <t>room.actions.draw</t>
+          <t>room.actions.challenge</t>
         </is>
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>Draw</t>
+          <t>Challenge</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>Hòa</t>
+          <t>Vào chơi</t>
         </is>
       </c>
     </row>
     <row r="253" ht="18" customHeight="1">
       <c r="A253" s="1" t="inlineStr">
         <is>
-          <t>room.actions.back-home</t>
+          <t>room.actions.leave-seat</t>
         </is>
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>Back to home</t>
+          <t>Leave seat</t>
         </is>
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>Thoát phòng</t>
+          <t>Ra xem</t>
         </is>
       </c>
     </row>
     <row r="254" ht="18" customHeight="1">
       <c r="A254" s="1" t="inlineStr">
         <is>
-          <t>room.actions.flip-board</t>
+          <t>room.actions.undo</t>
         </is>
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>Flip board</t>
+          <t>Undo</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>Đảo chiều bàn cờ</t>
+          <t>Hoán tác</t>
         </is>
       </c>
     </row>
     <row r="255" ht="18" customHeight="1">
       <c r="A255" s="1" t="inlineStr">
         <is>
-          <t>room.actions.accept-draw</t>
+          <t>room.actions.surrender</t>
         </is>
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>Accept</t>
+          <t>Surrender</t>
         </is>
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>Chấp nhận</t>
+          <t>Đầu hàng</t>
         </is>
       </c>
     </row>
     <row r="256" ht="18" customHeight="1">
       <c r="A256" s="1" t="inlineStr">
         <is>
-          <t>room.actions.reject-draw</t>
+          <t>room.actions.draw</t>
         </is>
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>Reject</t>
+          <t>Draw</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>Từ chối</t>
+          <t>Hòa</t>
         </is>
       </c>
     </row>
     <row r="257" ht="18" customHeight="1">
       <c r="A257" s="1" t="inlineStr">
         <is>
-          <t>room.actions.send-pm</t>
+          <t>room.actions.back-home</t>
         </is>
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>Send PM</t>
+          <t>Back to home</t>
         </is>
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>Chat</t>
+          <t>Thoát phòng</t>
         </is>
       </c>
     </row>
     <row r="258" ht="18" customHeight="1">
       <c r="A258" s="1" t="inlineStr">
         <is>
-          <t>room.actions.view-history</t>
+          <t>room.actions.flip-board</t>
         </is>
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>History</t>
+          <t>Flip board</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>Lịch sử</t>
+          <t>Đảo chiều bàn cờ</t>
         </is>
       </c>
     </row>
     <row r="259" ht="18" customHeight="1">
       <c r="A259" s="1" t="inlineStr">
         <is>
-          <t>room.actions.kick</t>
+          <t>room.actions.accept-draw</t>
         </is>
       </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
-          <t>Kick</t>
+          <t>Accept</t>
         </is>
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>Kick</t>
+          <t>Chấp nhận</t>
         </is>
       </c>
     </row>
     <row r="260" ht="36" customHeight="1">
       <c r="A260" s="1" t="inlineStr">
         <is>
-          <t>room.actions.back-to-room</t>
+          <t>room.actions.reject-draw</t>
         </is>
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>Back to room</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>Quay lại phòng chơi</t>
+          <t>Từ chối</t>
         </is>
       </c>
     </row>
     <row r="261" ht="36" customHeight="1">
       <c r="A261" s="1" t="inlineStr">
         <is>
-          <t>room.messages.draw-accepted</t>
+          <t>room.actions.send-pm</t>
         </is>
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>Opponent accepted the draw</t>
+          <t>Send PM</t>
         </is>
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>Đối phương đã đồng ý hòa</t>
+          <t>Chat</t>
         </is>
       </c>
     </row>
     <row r="262" ht="18" customHeight="1">
       <c r="A262" s="1" t="inlineStr">
         <is>
-          <t>room.messages.draw-rejected</t>
+          <t>room.actions.view-history</t>
         </is>
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>Opponent rejected the draw</t>
+          <t>History</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>Đối phương từ chối hòa</t>
+          <t>Lịch sử</t>
         </is>
       </c>
     </row>
     <row r="263" ht="18" customHeight="1">
       <c r="A263" s="1" t="inlineStr">
         <is>
-          <t>room.messages.opponent-surrendered</t>
+          <t>room.actions.kick</t>
         </is>
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t>Opponent surrendered! You won!</t>
+          <t>Kick</t>
         </is>
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>Đối phương đã đầu hàng! Bạn thắng!</t>
+          <t>Kick</t>
         </is>
       </c>
     </row>
     <row r="264" ht="18" customHeight="1">
       <c r="A264" s="1" t="inlineStr">
         <is>
-          <t>room.messages.confirm-leave</t>
+          <t>room.actions.back-to-room</t>
         </is>
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>Are you sure you want to leave room?</t>
+          <t>Back to room</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>Bạn có chắc muốn rời bàn chơi?</t>
+          <t>Quay lại phòng chơi</t>
         </is>
       </c>
     </row>
     <row r="265" ht="17" customHeight="1">
       <c r="A265" s="1" t="inlineStr">
         <is>
-          <t>room.messages.confirm-surrender</t>
+          <t>room.actions.chat</t>
         </is>
       </c>
       <c r="B265" s="1" t="inlineStr">
         <is>
-          <t>Are you sure you want to surrender?</t>
+          <t>Room chat</t>
         </is>
       </c>
       <c r="C265" s="1" t="inlineStr">
         <is>
-          <t>Bạn có chắc chắn muốn đầu hàng không?</t>
+          <t>Phòng chat</t>
         </is>
       </c>
     </row>
     <row r="266" ht="18" customHeight="1">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>room.messages.confirm-draw</t>
+          <t>room.messages.draw-accepted</t>
         </is>
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>Are you sure you want to draw?</t>
+          <t>Opponent accepted the draw</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>Bạn có chắc chắn muốn hòa không?</t>
+          <t>Đối phương đã đồng ý hòa</t>
         </is>
       </c>
     </row>
     <row r="267" ht="18" customHeight="1">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>room.messages.confirm-accept-draw</t>
+          <t>room.messages.draw-rejected</t>
         </is>
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>Opponent has proposed a draw. Do you accept?</t>
+          <t>Opponent rejected the draw</t>
         </is>
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>Đối phương đã chủ hòa, bạn có đồng ý không?</t>
+          <t>Đối phương từ chối hòa</t>
         </is>
       </c>
     </row>
     <row r="268" ht="18" customHeight="1">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>room.messages.insufficient-amount</t>
+          <t>room.messages.opponent-surrendered</t>
         </is>
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>You do not have enough balance to join this room</t>
+          <t>Opponent surrendered! You won!</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>Bạn không đủ tiền để tham gia bàn chơi này</t>
+          <t>Đối phương đã đầu hàng! Bạn thắng!</t>
         </is>
       </c>
     </row>
     <row r="269" ht="18" customHeight="1">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>room.messages.will-leave-current-room</t>
+          <t>room.messages.confirm-leave</t>
         </is>
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>You are currently in another room. Joining this room will remove you from the current room</t>
+          <t>Are you sure you want to leave room?</t>
         </is>
       </c>
       <c r="C269" s="2" t="inlineStr">
         <is>
-          <t>Bạn đang ở trong một phòng khác. Tham gia phòng này sẽ loại bạn ra khỏi phòng hiện tại</t>
+          <t>Bạn có chắc muốn rời bàn chơi?</t>
         </is>
       </c>
     </row>
     <row r="270" ht="18" customHeight="1">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>room.messages.all-seats-occupied</t>
+          <t>room.messages.confirm-surrender</t>
         </is>
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>All player seats are occupied</t>
+          <t>Are you sure you want to surrender?</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>Tất cả ghế chơi đã được chiếm</t>
+          <t>Bạn có chắc chắn muốn đầu hàng không?</t>
         </is>
       </c>
     </row>
     <row r="271" ht="36" customHeight="1">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>room.messages.game-ended</t>
+          <t>room.messages.confirm-draw</t>
         </is>
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>Game ended</t>
+          <t>Are you sure you want to draw?</t>
         </is>
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>Ván đấu đã kết thúc</t>
+          <t>Bạn có chắc chắn muốn hòa không?</t>
         </is>
       </c>
     </row>
     <row r="272" ht="36" customHeight="1">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>room.messages.you-win</t>
+          <t>room.messages.confirm-accept-draw</t>
         </is>
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>You win</t>
+          <t>Opponent has proposed a draw. Do you accept?</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>Bạn đã chiến thắng</t>
+          <t>Đối phương đã chủ hòa, bạn có đồng ý không?</t>
         </is>
       </c>
     </row>
     <row r="273" ht="18" customHeight="1">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>room.messages.you-lose</t>
+          <t>room.messages.insufficient-amount</t>
         </is>
       </c>
       <c r="B273" s="2" t="inlineStr">
         <is>
-          <t>You lose</t>
+          <t>You do not have enough balance to join this room</t>
         </is>
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>Bạn đã thua</t>
+          <t>Bạn không đủ tiền để tham gia bàn chơi này</t>
         </is>
       </c>
     </row>
     <row r="274" ht="18" customHeight="1">
       <c r="A274" s="1" t="inlineStr">
         <is>
-          <t>room.messages.back-to-room</t>
+          <t>room.messages.will-leave-current-room</t>
         </is>
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>Back to room</t>
+          <t>You are currently in another room. Joining this room will remove you from the current room</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>Quay lại phòng</t>
+          <t>Bạn đang ở trong một phòng khác. Tham gia phòng này sẽ loại bạn ra khỏi phòng hiện tại</t>
         </is>
       </c>
     </row>
     <row r="275" ht="18" customHeight="1">
       <c r="A275" s="1" t="inlineStr">
         <is>
-          <t>room.messages.auto-back-countdown</t>
+          <t>room.messages.all-seats-occupied</t>
         </is>
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>{0}. Press the back button to return to the room. You will be automatically returned in {1}s</t>
+          <t>All player seats are occupied</t>
         </is>
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>{0}. Bấm nút quay lại để quay lại room. Bạn sẽ tự động quay lại trong {1}s</t>
+          <t>Tất cả ghế chơi đã được chiếm</t>
         </is>
       </c>
     </row>
     <row r="276" ht="18" customHeight="1">
       <c r="A276" s="1" t="inlineStr">
         <is>
-          <t>room.notifications.joined</t>
+          <t>room.messages.game-ended</t>
         </is>
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>{0} joined the room</t>
+          <t>Game ended</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>{0} đã vào phòng</t>
+          <t>Ván đấu đã kết thúc</t>
         </is>
       </c>
     </row>
     <row r="277" ht="18" customHeight="1">
       <c r="A277" s="1" t="inlineStr">
         <is>
-          <t>room.notifications.left</t>
+          <t>room.messages.you-win</t>
         </is>
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>{0} left the room</t>
+          <t>You win</t>
         </is>
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t>{0} đã rời phòng</t>
+          <t>Bạn đã chiến thắng</t>
         </is>
       </c>
     </row>
     <row r="278" ht="18" customHeight="1">
       <c r="A278" s="1" t="inlineStr">
         <is>
-          <t>room.settings.title</t>
+          <t>room.messages.you-lose</t>
         </is>
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>Room Settings</t>
+          <t>You lose</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>Cài đặt phòng</t>
+          <t>Bạn đã thua</t>
         </is>
       </c>
     </row>
     <row r="279" ht="18" customHeight="1">
       <c r="A279" s="1" t="inlineStr">
         <is>
-          <t>room.settings.room-name</t>
+          <t>room.messages.back-to-room</t>
         </is>
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>Room name</t>
+          <t>Back to room</t>
         </is>
       </c>
       <c r="C279" s="2" t="inlineStr">
         <is>
-          <t>Tên phòng</t>
+          <t>Quay lại phòng</t>
         </is>
       </c>
     </row>
     <row r="280" ht="18" customHeight="1">
       <c r="A280" s="1" t="inlineStr">
         <is>
-          <t>room.settings.players</t>
+          <t>room.messages.auto-back-countdown</t>
         </is>
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>Spectators</t>
+          <t>{0}. Press the back button to return to the room. You will be automatically returned in {1}s</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>Người xem</t>
+          <t>{0}. Bấm nút quay lại để quay lại room. Bạn sẽ tự động quay lại trong {1}s</t>
         </is>
       </c>
     </row>
     <row r="281" ht="18" customHeight="1">
       <c r="A281" s="1" t="inlineStr">
         <is>
-          <t>room.settings.save</t>
+          <t>room.notifications.joined</t>
         </is>
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>Save</t>
+          <t>{0} joined the room</t>
         </is>
       </c>
       <c r="C281" s="2" t="inlineStr">
         <is>
-          <t>Lưu</t>
+          <t>{0} đã vào phòng</t>
         </is>
       </c>
     </row>
     <row r="282" ht="18" customHeight="1">
       <c r="A282" s="1" t="inlineStr">
         <is>
-          <t>room-invite.messages.title</t>
+          <t>room.notifications.left</t>
         </is>
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>Room Invitation</t>
+          <t>{0} left the room</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>Lời mời vào phòng</t>
+          <t>{0} đã rời phòng</t>
         </is>
       </c>
     </row>
     <row r="283" ht="18" customHeight="1">
       <c r="A283" s="1" t="inlineStr">
         <is>
-          <t>start-game.messages.success</t>
+          <t>room.settings.title</t>
         </is>
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>Game started successfully</t>
+          <t>Room Settings</t>
         </is>
       </c>
       <c r="C283" s="2" t="inlineStr">
         <is>
-          <t>Bắt đầu trò chơi thành công</t>
+          <t>Cài đặt phòng</t>
         </is>
       </c>
     </row>
     <row r="284" ht="18" customHeight="1">
       <c r="A284" s="1" t="inlineStr">
         <is>
-          <t>start-game.messages.internal-server-error</t>
+          <t>room.settings.room-name</t>
         </is>
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>Internal server error while starting game</t>
+          <t>Room name</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ khi bắt đầu trò chơi</t>
+          <t>Tên phòng</t>
         </is>
       </c>
     </row>
     <row r="285" ht="18" customHeight="1">
       <c r="A285" s="1" t="inlineStr">
         <is>
-          <t>start-game.messages.invalid-room-id</t>
+          <t>room.settings.players</t>
         </is>
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>Field 'id' is required and must be a positive integer</t>
+          <t>Spectators</t>
         </is>
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
+          <t>Người xem</t>
         </is>
       </c>
     </row>
     <row r="286" ht="18" customHeight="1">
       <c r="A286" s="1" t="inlineStr">
         <is>
-          <t>start-game.messages.invalid-difficulty</t>
+          <t>room.settings.save</t>
         </is>
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>Bot difficulty must be between 1 and 5</t>
+          <t>Save</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>Độ khó của bot phải từ 1 đến 5</t>
+          <t>Lưu</t>
         </is>
       </c>
     </row>
     <row r="287" ht="18" customHeight="1">
       <c r="A287" s="1" t="inlineStr">
         <is>
-          <t>start-game.messages.room-not-found</t>
+          <t>room-invite.messages.title</t>
         </is>
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>Room not found</t>
+          <t>Room Invitation</t>
         </is>
       </c>
       <c r="C287" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy phòng</t>
+          <t>Lời mời vào phòng</t>
         </is>
       </c>
     </row>
     <row r="288" ht="18" customHeight="1">
       <c r="A288" s="1" t="inlineStr">
         <is>
-          <t>start-game.messages.forbidden</t>
+          <t>start-game.messages.success</t>
         </is>
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>Only the room host can start the game</t>
+          <t>Game started successfully</t>
         </is>
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>Chỉ chủ phòng mới có thể bắt đầu trò chơi</t>
+          <t>Bắt đầu trò chơi thành công</t>
         </is>
       </c>
     </row>
     <row r="289" ht="18" customHeight="1">
       <c r="A289" s="1" t="inlineStr">
         <is>
-          <t>start-game.messages.insufficient-amount</t>
+          <t>start-game.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B289" s="2" t="inlineStr">
         <is>
-          <t>You do not have enough balance to start a game with this bet</t>
+          <t>Internal server error while starting game</t>
         </is>
       </c>
       <c r="C289" s="2" t="inlineStr">
         <is>
-          <t>Bạn không còn đủ amount để start room</t>
+          <t>Lỗi máy chủ nội bộ khi bắt đầu trò chơi</t>
         </is>
       </c>
     </row>
     <row r="290" ht="18" customHeight="1">
       <c r="A290" s="1" t="inlineStr">
         <is>
-          <t>start-game.messages.requester-must-pick-team</t>
+          <t>start-game.messages.invalid-room-id</t>
         </is>
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>You must select a team before starting a game with bot</t>
+          <t>Field 'id' is required and must be a positive integer</t>
         </is>
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>Bạn phải chọn team trước khi bắt đầu trò chơi với bot</t>
+          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
         </is>
       </c>
     </row>
     <row r="291" ht="18" customHeight="1">
       <c r="A291" s="1" t="inlineStr">
         <is>
-          <t>update-room.messages.success</t>
+          <t>start-game.messages.invalid-difficulty</t>
         </is>
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>Room updated successfully</t>
+          <t>Bot difficulty must be between 1 and 5</t>
         </is>
       </c>
       <c r="C291" s="2" t="inlineStr">
         <is>
-          <t>Cập nhật phòng thành công</t>
+          <t>Độ khó của bot phải từ 1 đến 5</t>
         </is>
       </c>
     </row>
     <row r="292" ht="18" customHeight="1">
       <c r="A292" s="1" t="inlineStr">
         <is>
-          <t>update-room.messages.internal-server-error</t>
+          <t>start-game.messages.room-not-found</t>
         </is>
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Room not found</t>
         </is>
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Không tìm thấy phòng</t>
         </is>
       </c>
     </row>
     <row r="293" ht="18" customHeight="1">
       <c r="A293" s="1" t="inlineStr">
         <is>
-          <t>update-room.messages.invalid-room-id</t>
+          <t>start-game.messages.forbidden</t>
         </is>
       </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t>Invalid room ID</t>
+          <t>Only the room host can start the game</t>
         </is>
       </c>
       <c r="C293" s="2" t="inlineStr">
         <is>
-          <t>ID phòng không hợp lệ</t>
+          <t>Chỉ chủ phòng mới có thể bắt đầu trò chơi</t>
         </is>
       </c>
     </row>
     <row r="294" ht="18" customHeight="1">
       <c r="A294" s="1" t="inlineStr">
         <is>
-          <t>update-room.messages.name-required</t>
+          <t>start-game.messages.insufficient-amount</t>
         </is>
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>Room name is required</t>
+          <t>You do not have enough balance to start a game with this bet</t>
         </is>
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>Tên phòng không được để trống</t>
+          <t>Bạn không còn đủ amount để start room</t>
         </is>
       </c>
     </row>
     <row r="295" ht="18" customHeight="1">
       <c r="A295" s="1" t="inlineStr">
         <is>
-          <t>update-room.messages.room-not-found</t>
+          <t>start-game.messages.requester-must-pick-team</t>
         </is>
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>Room not found</t>
+          <t>You must select a team before starting a game with bot</t>
         </is>
       </c>
       <c r="C295" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy phòng</t>
+          <t>Bạn phải chọn team trước khi bắt đầu trò chơi với bot</t>
         </is>
       </c>
     </row>
     <row r="296" ht="18" customHeight="1">
       <c r="A296" s="1" t="inlineStr">
         <is>
-          <t>update-room.messages.forbidden</t>
+          <t>update-room.messages.success</t>
         </is>
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>You are not the host of this room</t>
+          <t>Room updated successfully</t>
         </is>
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>Bạn không phải chủ phòng</t>
+          <t>Cập nhật phòng thành công</t>
         </is>
       </c>
     </row>
     <row r="297" ht="18" customHeight="1">
       <c r="A297" s="1" t="inlineStr">
         <is>
-          <t>draw-game.messages.invalid-game-id</t>
+          <t>update-room.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B297" s="2" t="inlineStr">
         <is>
-          <t>Invalid game ID</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C297" s="2" t="inlineStr">
         <is>
-          <t>ID trò chơi không hợp lệ</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="298" ht="18" customHeight="1">
       <c r="A298" s="1" t="inlineStr">
         <is>
-          <t>draw-game.messages.game-not-found</t>
+          <t>update-room.messages.invalid-room-id</t>
         </is>
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>Game not found</t>
+          <t>Invalid room ID</t>
         </is>
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy trò chơi</t>
+          <t>ID phòng không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="299" ht="18" customHeight="1">
       <c r="A299" s="1" t="inlineStr">
         <is>
-          <t>draw-game.messages.forbidden</t>
+          <t>update-room.messages.invalid-time-limit</t>
         </is>
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
-          <t>You are not in this room</t>
+          <t>Invalid time limit</t>
         </is>
       </c>
       <c r="C299" s="2" t="inlineStr">
         <is>
-          <t>Bạn không có trong phòng này</t>
+          <t>Thời gian không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="300" ht="18" customHeight="1">
       <c r="A300" s="1" t="inlineStr">
         <is>
-          <t>draw-game.messages.game-history-not-found</t>
+          <t>update-room.messages.name-required</t>
         </is>
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>Game history not found</t>
+          <t>Room name is required</t>
         </is>
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy lịch sử trò chơi</t>
+          <t>Tên phòng không được để trống</t>
         </is>
       </c>
     </row>
     <row r="301" ht="18" customHeight="1">
       <c r="A301" s="1" t="inlineStr">
         <is>
-          <t>draw-game.messages.game-already-finished</t>
+          <t>update-room.messages.room-not-found</t>
         </is>
       </c>
       <c r="B301" s="2" t="inlineStr">
         <is>
-          <t>Game is already finished</t>
+          <t>Room not found</t>
         </is>
       </c>
       <c r="C301" s="2" t="inlineStr">
         <is>
-          <t>Trò chơi đã kết thúc</t>
+          <t>Không tìm thấy phòng</t>
         </is>
       </c>
     </row>
     <row r="302" ht="18" customHeight="1">
       <c r="A302" s="1" t="inlineStr">
         <is>
-          <t>draw-game.messages.success</t>
+          <t>update-room.messages.forbidden</t>
         </is>
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>Draw game successfully</t>
+          <t>You are not the host of this room</t>
         </is>
       </c>
       <c r="C302" s="2" t="inlineStr">
         <is>
-          <t>Hòa cờ thành công</t>
+          <t>Bạn không phải chủ phòng</t>
         </is>
       </c>
     </row>
     <row r="303" ht="18" customHeight="1">
       <c r="A303" s="1" t="inlineStr">
         <is>
-          <t>draw-game.messages.internal-server-error</t>
+          <t>draw-game.messages.invalid-game-id</t>
         </is>
       </c>
       <c r="B303" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Invalid game ID</t>
         </is>
       </c>
       <c r="C303" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>ID trò chơi không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="304" ht="18" customHeight="1">
       <c r="A304" s="1" t="inlineStr">
         <is>
-          <t>surrender.messages.game-already-finished</t>
+          <t>draw-game.messages.game-not-found</t>
         </is>
       </c>
       <c r="B304" s="2" t="inlineStr">
         <is>
-          <t>Game is already finished</t>
+          <t>Game not found</t>
         </is>
       </c>
       <c r="C304" s="2" t="inlineStr">
         <is>
-          <t>Trò chơi đã kết thúc</t>
+          <t>Không tìm thấy trò chơi</t>
         </is>
       </c>
     </row>
     <row r="305" ht="18" customHeight="1">
       <c r="A305" s="1" t="inlineStr">
         <is>
-          <t>surrender.messages.game-history-not-found</t>
+          <t>draw-game.messages.forbidden</t>
         </is>
       </c>
       <c r="B305" s="2" t="inlineStr">
         <is>
-          <t>Game history not found</t>
+          <t>You are not in this room</t>
         </is>
       </c>
       <c r="C305" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy lịch sử trò chơi</t>
+          <t>Bạn không có trong phòng này</t>
         </is>
       </c>
     </row>
     <row r="306" ht="90" customHeight="1">
       <c r="A306" s="1" t="inlineStr">
         <is>
-          <t>surrender.messages.game-not-found</t>
+          <t>draw-game.messages.game-history-not-found</t>
         </is>
       </c>
       <c r="B306" s="2" t="inlineStr">
         <is>
-          <t>Game not found</t>
+          <t>Game history not found</t>
         </is>
       </c>
       <c r="C306" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy trò chơi</t>
+          <t>Không tìm thấy lịch sử trò chơi</t>
         </is>
       </c>
     </row>
     <row r="307" ht="90" customHeight="1">
       <c r="A307" s="1" t="inlineStr">
         <is>
-          <t>surrender.messages.internal-server-error</t>
+          <t>draw-game.messages.game-already-finished</t>
         </is>
       </c>
       <c r="B307" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Game is already finished</t>
         </is>
       </c>
       <c r="C307" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Trò chơi đã kết thúc</t>
         </is>
       </c>
     </row>
     <row r="308" ht="18" customHeight="1">
       <c r="A308" s="1" t="inlineStr">
         <is>
-          <t>surrender.messages.invalid-game-id</t>
+          <t>draw-game.messages.success</t>
         </is>
       </c>
       <c r="B308" s="2" t="inlineStr">
         <is>
-          <t>Invalid game ID</t>
+          <t>Draw game successfully</t>
         </is>
       </c>
       <c r="C308" s="2" t="inlineStr">
         <is>
-          <t>ID trò chơi không hợp lệ</t>
+          <t>Hòa cờ thành công</t>
         </is>
       </c>
     </row>
     <row r="309" ht="18" customHeight="1">
       <c r="A309" s="1" t="inlineStr">
         <is>
-          <t>surrender.messages.invalid-surrender-player</t>
+          <t>draw-game.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B309" s="2" t="inlineStr">
         <is>
-          <t>You are not a player in this game</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C309" s="2" t="inlineStr">
         <is>
-          <t>Bạn không phải là người chơi trong trò chơi này</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="310" ht="18" customHeight="1">
       <c r="A310" s="1" t="inlineStr">
         <is>
-          <t>surrender.messages.opponent-not-found</t>
+          <t>surrender.messages.game-already-finished</t>
         </is>
       </c>
       <c r="B310" s="2" t="inlineStr">
         <is>
-          <t>Opponent not found</t>
+          <t>Game is already finished</t>
         </is>
       </c>
       <c r="C310" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy đối thủ</t>
+          <t>Trò chơi đã kết thúc</t>
         </is>
       </c>
     </row>
     <row r="311" ht="18" customHeight="1">
       <c r="A311" s="2" t="inlineStr">
         <is>
-          <t>surrender.messages.success</t>
+          <t>surrender.messages.game-history-not-found</t>
         </is>
       </c>
       <c r="B311" s="2" t="inlineStr">
         <is>
-          <t>Surrendered</t>
+          <t>Game history not found</t>
         </is>
       </c>
       <c r="C311" s="2" t="inlineStr">
         <is>
-          <t>Đã đầu hàng</t>
+          <t>Không tìm thấy lịch sử trò chơi</t>
         </is>
       </c>
     </row>
     <row r="312" ht="18" customHeight="1">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>undo.messages.invalid-game-id</t>
+          <t>surrender.messages.game-not-found</t>
         </is>
       </c>
       <c r="B312" s="2" t="inlineStr">
         <is>
-          <t>Invalid game ID</t>
+          <t>Game not found</t>
         </is>
       </c>
       <c r="C312" s="2" t="inlineStr">
         <is>
-          <t>ID trò chơi không hợp lệ</t>
+          <t>Không tìm thấy trò chơi</t>
         </is>
       </c>
     </row>
     <row r="313" ht="18" customHeight="1">
       <c r="A313" s="2" t="inlineStr">
         <is>
-          <t>undo.messages.unauthorized</t>
+          <t>surrender.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B313" s="2" t="inlineStr">
         <is>
-          <t>Unauthorized</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C313" s="2" t="inlineStr">
         <is>
-          <t>Không được phép truy cập</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="314" ht="18" customHeight="1">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>undo.messages.game-not-found</t>
+          <t>surrender.messages.invalid-game-id</t>
         </is>
       </c>
       <c r="B314" s="2" t="inlineStr">
         <is>
-          <t>Game not found</t>
+          <t>Invalid game ID</t>
         </is>
       </c>
       <c r="C314" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy trò chơi</t>
+          <t>ID trò chơi không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="315" ht="54" customHeight="1">
       <c r="A315" s="2" t="inlineStr">
         <is>
-          <t>undo.messages.not-in-game</t>
+          <t>surrender.messages.invalid-surrender-player</t>
         </is>
       </c>
       <c r="B315" s="2" t="inlineStr">
         <is>
-          <t>You are not part of this game</t>
+          <t>You are not a player in this game</t>
         </is>
       </c>
       <c r="C315" s="2" t="inlineStr">
@@ -5691,1613 +5691,1685 @@
     <row r="316" ht="18" customHeight="1">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>undo.messages.not-in-room</t>
+          <t>surrender.messages.opponent-not-found</t>
         </is>
       </c>
       <c r="B316" s="2" t="inlineStr">
         <is>
-          <t>You are not in this room</t>
+          <t>Opponent not found</t>
         </is>
       </c>
       <c r="C316" s="2" t="inlineStr">
         <is>
-          <t>Bạn không trong phòng này</t>
+          <t>Không tìm thấy đối thủ</t>
         </is>
       </c>
     </row>
     <row r="317" ht="90" customHeight="1">
       <c r="A317" s="2" t="inlineStr">
         <is>
-          <t>undo.messages.spectator-cannot-undo</t>
+          <t>surrender.messages.success</t>
         </is>
       </c>
       <c r="B317" s="2" t="inlineStr">
         <is>
-          <t>Spectators cannot undo moves</t>
+          <t>Surrendered</t>
         </is>
       </c>
       <c r="C317" s="2" t="inlineStr">
         <is>
-          <t>Người xem không thể hoàn tác nước đi</t>
+          <t>Đã đầu hàng</t>
         </is>
       </c>
     </row>
     <row r="318" ht="18" customHeight="1">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>undo.messages.no-moves</t>
+          <t>undo.messages.invalid-game-id</t>
         </is>
       </c>
       <c r="B318" s="2" t="inlineStr">
         <is>
-          <t>No moves to undo</t>
+          <t>Invalid game ID</t>
         </is>
       </c>
       <c r="C318" s="2" t="inlineStr">
         <is>
-          <t>Không có nước đi để hoàn tác</t>
+          <t>ID trò chơi không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="319" ht="36" customHeight="1">
       <c r="A319" s="2" t="inlineStr">
         <is>
-          <t>undo.messages.delete-failed</t>
+          <t>undo.messages.unauthorized</t>
         </is>
       </c>
       <c r="B319" s="2" t="inlineStr">
         <is>
-          <t>Failed to undo move</t>
+          <t>Unauthorized</t>
         </is>
       </c>
       <c r="C319" s="2" t="inlineStr">
         <is>
-          <t>Không thể hoàn tác nước đi</t>
+          <t>Không được phép truy cập</t>
         </is>
       </c>
     </row>
     <row r="320" ht="18" customHeight="1">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>undo.messages.undo-limit-exceeded</t>
+          <t>undo.messages.game-not-found</t>
         </is>
       </c>
       <c r="B320" s="2" t="inlineStr">
         <is>
-          <t>Maximum 3 undo per game exceeded</t>
+          <t>Game not found</t>
         </is>
       </c>
       <c r="C320" s="2" t="inlineStr">
         <is>
-          <t>Đã đạt tối đa 3 lần hoàn tác trong trò chơi</t>
+          <t>Không tìm thấy trò chơi</t>
         </is>
       </c>
     </row>
     <row r="321" ht="72" customHeight="1">
       <c r="A321" s="2" t="inlineStr">
         <is>
-          <t>undo.messages.success</t>
+          <t>undo.messages.not-in-game</t>
         </is>
       </c>
       <c r="B321" s="2" t="inlineStr">
         <is>
-          <t>Move undone successfully</t>
+          <t>You are not part of this game</t>
         </is>
       </c>
       <c r="C321" s="2" t="inlineStr">
         <is>
-          <t>Hoàn tác nước đi thành công</t>
+          <t>Bạn không phải là người chơi trong trò chơi này</t>
         </is>
       </c>
     </row>
     <row r="322" ht="18" customHeight="1">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>undo.messages.internal-server-error</t>
+          <t>undo.messages.not-in-room</t>
         </is>
       </c>
       <c r="B322" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>You are not in this room</t>
         </is>
       </c>
       <c r="C322" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Bạn không trong phòng này</t>
         </is>
       </c>
     </row>
     <row r="323" ht="54" customHeight="1">
       <c r="A323" s="2" t="inlineStr">
         <is>
-          <t>player-history.messages.invalid-user-id</t>
+          <t>undo.messages.spectator-cannot-undo</t>
         </is>
       </c>
       <c r="B323" s="2" t="inlineStr">
         <is>
-          <t>Invalid user ID</t>
+          <t>Spectators cannot undo moves</t>
         </is>
       </c>
       <c r="C323" s="2" t="inlineStr">
         <is>
-          <t>ID người dùng không hợp lệ</t>
+          <t>Người xem không thể hoàn tác nước đi</t>
         </is>
       </c>
     </row>
     <row r="324" ht="18" customHeight="1">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>player-history.messages.success</t>
+          <t>undo.messages.no-moves</t>
         </is>
       </c>
       <c r="B324" s="2" t="inlineStr">
         <is>
-          <t>Fetch game history successfully</t>
+          <t>No moves to undo</t>
         </is>
       </c>
       <c r="C324" s="2" t="inlineStr">
         <is>
-          <t>Lấy lịch sử trò chơi thành công</t>
+          <t>Không có nước đi để hoàn tác</t>
         </is>
       </c>
     </row>
     <row r="325" ht="72" customHeight="1">
       <c r="A325" s="2" t="inlineStr">
         <is>
-          <t>validate-token.messages.success</t>
+          <t>undo.messages.delete-failed</t>
         </is>
       </c>
       <c r="B325" s="2" t="inlineStr">
         <is>
-          <t>Token is valid</t>
+          <t>Failed to undo move</t>
         </is>
       </c>
       <c r="C325" s="2" t="inlineStr">
         <is>
-          <t>Token hợp lệ</t>
+          <t>Không thể hoàn tác nước đi</t>
         </is>
       </c>
     </row>
     <row r="326" ht="18" customHeight="1">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>guide.section.objective</t>
+          <t>undo.messages.undo-limit-exceeded</t>
         </is>
       </c>
       <c r="B326" s="2" t="inlineStr">
         <is>
-          <t>Objective of the game</t>
+          <t>Maximum 3 undo per game exceeded</t>
         </is>
       </c>
       <c r="C326" s="2" t="inlineStr">
         <is>
-          <t>Mục tiêu của trò chơi</t>
+          <t>Đã đạt tối đa 3 lần hoàn tác trong trò chơi</t>
         </is>
       </c>
     </row>
     <row r="327" ht="90" customHeight="1">
       <c r="A327" s="2" t="inlineStr">
         <is>
-          <t>guide.section.pieces</t>
+          <t>undo.messages.success</t>
         </is>
       </c>
       <c r="B327" s="2" t="inlineStr">
         <is>
-          <t>Pieces</t>
+          <t>Move undone successfully</t>
         </is>
       </c>
       <c r="C327" s="2" t="inlineStr">
         <is>
-          <t>Quân cờ</t>
+          <t>Hoàn tác nước đi thành công</t>
         </is>
       </c>
     </row>
     <row r="328" ht="18" customHeight="1">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>guide.section.moving-pieces</t>
+          <t>undo.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B328" s="2" t="inlineStr">
         <is>
-          <t>Moving pieces</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C328" s="2" t="inlineStr">
         <is>
-          <t>Đi quân</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="329" ht="72" customHeight="1">
       <c r="A329" s="2" t="inlineStr">
         <is>
-          <t>guide.section.capturing</t>
+          <t>player-history.messages.invalid-user-id</t>
         </is>
       </c>
       <c r="B329" s="2" t="inlineStr">
         <is>
-          <t>Capturing</t>
+          <t>Invalid user ID</t>
         </is>
       </c>
       <c r="C329" s="2" t="inlineStr">
         <is>
-          <t>Bắt quân</t>
+          <t>ID người dùng không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="330" ht="54" customHeight="1">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>guide.section.check</t>
+          <t>player-history.messages.success</t>
         </is>
       </c>
       <c r="B330" s="2" t="inlineStr">
         <is>
-          <t>Check</t>
+          <t>Fetch game history successfully</t>
         </is>
       </c>
       <c r="C330" s="2" t="inlineStr">
         <is>
-          <t>Chiếu tướng</t>
+          <t>Lấy lịch sử trò chơi thành công</t>
         </is>
       </c>
     </row>
     <row r="331" ht="54" customHeight="1">
       <c r="A331" s="2" t="inlineStr">
         <is>
-          <t>guide.section.result</t>
+          <t>validate-token.messages.success</t>
         </is>
       </c>
       <c r="B331" s="2" t="inlineStr">
         <is>
-          <t>Result</t>
+          <t>Token is valid</t>
         </is>
       </c>
       <c r="C331" s="2" t="inlineStr">
         <is>
-          <t>Kết quả</t>
+          <t>Token hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="332" ht="54" customHeight="1">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>guide.table.piece</t>
+          <t>guide.section.objective</t>
         </is>
       </c>
       <c r="B332" s="2" t="inlineStr">
         <is>
-          <t>Piece</t>
+          <t>Objective of the game</t>
         </is>
       </c>
       <c r="C332" s="2" t="inlineStr">
         <is>
-          <t>Quân</t>
+          <t>Mục tiêu của trò chơi</t>
         </is>
       </c>
     </row>
     <row r="333" ht="90" customHeight="1">
       <c r="A333" s="2" t="inlineStr">
         <is>
-          <t>guide.table.symbol</t>
+          <t>guide.section.pieces</t>
         </is>
       </c>
       <c r="B333" s="2" t="inlineStr">
         <is>
-          <t>Symbol</t>
+          <t>Pieces</t>
         </is>
       </c>
       <c r="C333" s="2" t="inlineStr">
         <is>
-          <t>Ký hiệu</t>
+          <t>Quân cờ</t>
         </is>
       </c>
     </row>
     <row r="334" ht="54" customHeight="1">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>guide.table.quantity</t>
+          <t>guide.section.moving-pieces</t>
         </is>
       </c>
       <c r="B334" s="2" t="inlineStr">
         <is>
-          <t>Quantity</t>
+          <t>Moving pieces</t>
         </is>
       </c>
       <c r="C334" s="2" t="inlineStr">
         <is>
-          <t>Số lượng</t>
+          <t>Đi quân</t>
         </is>
       </c>
     </row>
     <row r="335" ht="36" customHeight="1">
       <c r="A335" s="2" t="inlineStr">
         <is>
-          <t>guide.objective.paragraph1</t>
+          <t>guide.section.capturing</t>
         </is>
       </c>
       <c r="B335" s="2" t="inlineStr">
         <is>
-          <t>A match is played between two players: one controls the Red pieces, and the other controls the Black pieces. The objective of each player is to use their pieces on the board to &lt;b&gt;checkmate&lt;/b&gt; the opponent's General, and win the game.</t>
+          <t>Capturing</t>
         </is>
       </c>
       <c r="C335" s="2" t="inlineStr">
         <is>
-          <t>Ván cờ được tiến hành giữa 2 đấu thủ, một người cầm Quân Đỏ, một người cầm Quân Đen. Mục đích của mỗi đấu thủ là tìm mọi cách sử dụng các quân trên bàn cờ để &lt;b&gt;chiếu bí Tướng&lt;/b&gt; của đối phương, giành thắng lợi.</t>
+          <t>Bắt quân</t>
         </is>
       </c>
     </row>
     <row r="336" ht="18" customHeight="1">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>guide.pieces.paragraph1</t>
+          <t>guide.section.check</t>
         </is>
       </c>
       <c r="B336" s="2" t="inlineStr">
         <is>
-          <t>At the start of each game, there must be 32 pieces in total, consisting of &lt;b&gt;7 piece types&lt;/b&gt; split evenly between both sides: 16 Red pieces and 16 Black pieces. The 7 piece types with their symbols and quantities are as follows:</t>
+          <t>Check</t>
         </is>
       </c>
       <c r="C336" s="2" t="inlineStr">
         <is>
-          <t>Mỗi ván cờ lúc bắt đầu phải có đủ 32 quân, gồm 7 loại chia đều cho mỗi bên gồm 16 quân Đỏ và 16 quân Đen. &lt;b&gt;7 loại quân&lt;/b&gt; có ký hiệu và số lượng như sau:</t>
+          <t>Chiếu tướng</t>
         </is>
       </c>
     </row>
     <row r="337" ht="36" customHeight="1">
       <c r="A337" s="2" t="inlineStr">
         <is>
-          <t>guide.piece.general</t>
+          <t>guide.section.result</t>
         </is>
       </c>
       <c r="B337" s="2" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Result</t>
         </is>
       </c>
       <c r="C337" s="2" t="inlineStr">
         <is>
-          <t>Tướng</t>
+          <t>Kết quả</t>
         </is>
       </c>
     </row>
     <row r="338" ht="36" customHeight="1">
       <c r="A338" s="2" t="inlineStr">
         <is>
-          <t>guide.piece.advisor</t>
+          <t>guide.table.piece</t>
         </is>
       </c>
       <c r="B338" s="2" t="inlineStr">
         <is>
-          <t>Advisor</t>
+          <t>Piece</t>
         </is>
       </c>
       <c r="C338" s="2" t="inlineStr">
         <is>
-          <t>Sĩ</t>
+          <t>Quân</t>
         </is>
       </c>
     </row>
     <row r="339" ht="72" customHeight="1">
       <c r="A339" s="2" t="inlineStr">
         <is>
-          <t>guide.piece.elephant</t>
+          <t>guide.table.symbol</t>
         </is>
       </c>
       <c r="B339" s="2" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Symbol</t>
         </is>
       </c>
       <c r="C339" s="2" t="inlineStr">
         <is>
-          <t>Tượng</t>
+          <t>Ký hiệu</t>
         </is>
       </c>
     </row>
     <row r="340" ht="54" customHeight="1">
       <c r="A340" s="2" t="inlineStr">
         <is>
-          <t>guide.piece.chariot</t>
+          <t>guide.table.quantity</t>
         </is>
       </c>
       <c r="B340" s="2" t="inlineStr">
         <is>
-          <t>Chariot</t>
+          <t>Quantity</t>
         </is>
       </c>
       <c r="C340" s="2" t="inlineStr">
         <is>
-          <t>Xe</t>
+          <t>Số lượng</t>
         </is>
       </c>
     </row>
     <row r="341" ht="54" customHeight="1">
       <c r="A341" s="2" t="inlineStr">
         <is>
-          <t>guide.piece.horse</t>
+          <t>guide.objective.paragraph1</t>
         </is>
       </c>
       <c r="B341" s="2" t="inlineStr">
         <is>
-          <t>Horse</t>
+          <t>A match is played between two players: one controls the Red pieces, and the other controls the Black pieces. The objective of each player is to use their pieces on the board to &lt;b&gt;checkmate&lt;/b&gt; the opponent's General, and win the game.</t>
         </is>
       </c>
       <c r="C341" s="2" t="inlineStr">
         <is>
-          <t>Mã</t>
+          <t>Ván cờ được tiến hành giữa 2 đấu thủ, một người cầm Quân Đỏ, một người cầm Quân Đen. Mục đích của mỗi đấu thủ là tìm mọi cách sử dụng các quân trên bàn cờ để &lt;b&gt;chiếu bí Tướng&lt;/b&gt; của đối phương, giành thắng lợi.</t>
         </is>
       </c>
     </row>
     <row r="342" ht="90" customHeight="1">
       <c r="A342" s="2" t="inlineStr">
         <is>
-          <t>guide.piece.cannon</t>
+          <t>guide.pieces.paragraph1</t>
         </is>
       </c>
       <c r="B342" s="2" t="inlineStr">
         <is>
-          <t>Cannon</t>
+          <t>At the start of each game, there must be 32 pieces in total, consisting of &lt;b&gt;7 piece types&lt;/b&gt; split evenly between both sides: 16 Red pieces and 16 Black pieces. The 7 piece types with their symbols and quantities are as follows:</t>
         </is>
       </c>
       <c r="C342" s="2" t="inlineStr">
         <is>
-          <t>Pháo</t>
+          <t>Mỗi ván cờ lúc bắt đầu phải có đủ 32 quân, gồm 7 loại chia đều cho mỗi bên gồm 16 quân Đỏ và 16 quân Đen. &lt;b&gt;7 loại quân&lt;/b&gt; có ký hiệu và số lượng như sau:</t>
         </is>
       </c>
     </row>
     <row r="343" ht="54" customHeight="1">
       <c r="A343" s="2" t="inlineStr">
         <is>
-          <t>guide.piece.soldier</t>
+          <t>guide.piece.general</t>
         </is>
       </c>
       <c r="B343" s="2" t="inlineStr">
         <is>
-          <t>Soldier</t>
+          <t>General</t>
         </is>
       </c>
       <c r="C343" s="2" t="inlineStr">
         <is>
-          <t>Tốt</t>
+          <t>Tướng</t>
         </is>
       </c>
     </row>
     <row r="344" ht="18" customHeight="1">
       <c r="A344" s="2" t="inlineStr">
         <is>
-          <t>guide.moving-pieces.paragraph1</t>
+          <t>guide.piece.advisor</t>
         </is>
       </c>
       <c r="B344" s="2" t="inlineStr">
         <is>
-          <t>On each turn, each side may move only one of its own pieces according to the rules. The movement rules are as follows:</t>
+          <t>Advisor</t>
         </is>
       </c>
       <c r="C344" s="2" t="inlineStr">
         <is>
-          <t>Mỗi nước đi, mỗi bên chỉ được di chuyển quân của mình theo đúng quy định. Quy định di chuyển của các quân như sau:</t>
+          <t>Sĩ</t>
         </is>
       </c>
     </row>
     <row r="345" ht="18" customHeight="1">
       <c r="A345" s="2" t="inlineStr">
         <is>
-          <t>guide.general.paragraph1</t>
+          <t>guide.piece.elephant</t>
         </is>
       </c>
       <c r="B345" s="2" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="C345" s="2" t="inlineStr">
         <is>
-          <t>Tướng</t>
+          <t>Tượng</t>
         </is>
       </c>
     </row>
     <row r="346" ht="36" customHeight="1">
       <c r="A346" s="2" t="inlineStr">
         <is>
-          <t>guide.general.paragraph2</t>
+          <t>guide.piece.chariot</t>
         </is>
       </c>
       <c r="B346" s="2" t="inlineStr">
         <is>
-          <t>Moves one step &lt;b&gt;horizontally or vertically&lt;/b&gt; within the palace. The two Generals may not face each other directly on the same file. If they are facing each other, there must be at least one piece of either side placed between them.</t>
+          <t>Chariot</t>
         </is>
       </c>
       <c r="C346" s="2" t="inlineStr">
         <is>
-          <t>Mỗi nước được đi một bước &lt;b&gt;ngang hoặc dọc&lt;/b&gt; tùy ý trong cung Tướng. Hai tướng của 2 bên không được đối mặt nhau trực tiếp trên cùng một đường thẳng. Nếu đối mặt, bắt buộc phải có quân của bất kỳ bên nào đứng che mặt.</t>
+          <t>Xe</t>
         </is>
       </c>
     </row>
     <row r="347" ht="18" customHeight="1">
       <c r="A347" s="2" t="inlineStr">
         <is>
-          <t>guide.advisor.paragraph1</t>
+          <t>guide.piece.horse</t>
         </is>
       </c>
       <c r="B347" s="2" t="inlineStr">
         <is>
-          <t>Advisor</t>
+          <t>Horse</t>
         </is>
       </c>
       <c r="C347" s="2" t="inlineStr">
         <is>
-          <t>Sĩ</t>
+          <t>Mã</t>
         </is>
       </c>
     </row>
     <row r="348" ht="18" customHeight="1">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>guide.advisor.paragraph2</t>
+          <t>guide.piece.cannon</t>
         </is>
       </c>
       <c r="B348" s="2" t="inlineStr">
         <is>
-          <t>Moves one step &lt;b&gt;diagonally&lt;/b&gt; within the palace.</t>
+          <t>Cannon</t>
         </is>
       </c>
       <c r="C348" s="2" t="inlineStr">
         <is>
-          <t>Mỗi nước &lt;b&gt;đi chéo một bước&lt;/b&gt; trong cung Tướng.</t>
+          <t>Pháo</t>
         </is>
       </c>
     </row>
     <row r="349" ht="36" customHeight="1">
       <c r="A349" s="2" t="inlineStr">
         <is>
-          <t>guide.elephant.paragraph1</t>
+          <t>guide.piece.soldier</t>
         </is>
       </c>
       <c r="B349" s="2" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Soldier</t>
         </is>
       </c>
       <c r="C349" s="2" t="inlineStr">
         <is>
-          <t>Tượng</t>
+          <t>Tốt</t>
         </is>
       </c>
     </row>
     <row r="350" ht="18" customHeight="1">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>guide.elephant.paragraph2</t>
+          <t>guide.moving-pieces.paragraph1</t>
         </is>
       </c>
       <c r="B350" s="2" t="inlineStr">
         <is>
-          <t>Moves &lt;b&gt;two steps diagonally&lt;/b&gt; on its own side of the board and may not cross the river. If there is another piece on the midpoint of that diagonal path, the Elephant is blocked and cannot move.</t>
+          <t>On each turn, each side may move only one of its own pieces according to the rules. The movement rules are as follows:</t>
         </is>
       </c>
       <c r="C350" s="2" t="inlineStr">
         <is>
-          <t>Mỗi nước &lt;b&gt;đi chéo hai bước&lt;/b&gt; tại trận địa bên mình, không được qua sông. Nếu ở giữa đường chéo đó có quân khác đứng thì quân Tượng bị cản, không đi được.</t>
+          <t>Mỗi nước đi, mỗi bên chỉ được di chuyển quân của mình theo đúng quy định. Quy định di chuyển của các quân như sau:</t>
         </is>
       </c>
     </row>
     <row r="351" ht="36" customHeight="1">
       <c r="A351" s="2" t="inlineStr">
         <is>
-          <t>guide.chariot.paragraph1</t>
+          <t>guide.general.paragraph1</t>
         </is>
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>Chariot</t>
+          <t>General</t>
         </is>
       </c>
       <c r="C351" s="2" t="inlineStr">
         <is>
-          <t>Xe</t>
+          <t>Tướng</t>
         </is>
       </c>
     </row>
     <row r="352" ht="18" customHeight="1">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>guide.chariot.paragraph2</t>
+          <t>guide.general.paragraph2</t>
         </is>
       </c>
       <c r="B352" s="2" t="inlineStr">
         <is>
-          <t>Moves &lt;b&gt;horizontally or vertically&lt;/b&gt; with no limit on distance, as long as no piece blocks the path.</t>
+          <t>Moves one step &lt;b&gt;horizontally or vertically&lt;/b&gt; within the palace. The two Generals may not face each other directly on the same file. If they are facing each other, there must be at least one piece of either side placed between them.</t>
         </is>
       </c>
       <c r="C352" s="2" t="inlineStr">
         <is>
-          <t>Mỗi nước được &lt;b&gt;đi dọc hoặc đi ngang&lt;/b&gt;, không hạn chế số bước đi nếu không có quân khác cản đường.</t>
+          <t>Mỗi nước được đi một bước &lt;b&gt;ngang hoặc dọc&lt;/b&gt; tùy ý trong cung Tướng. Hai tướng của 2 bên không được đối mặt nhau trực tiếp trên cùng một đường thẳng. Nếu đối mặt, bắt buộc phải có quân của bất kỳ bên nào đứng che mặt.</t>
         </is>
       </c>
     </row>
     <row r="353" ht="18" customHeight="1">
       <c r="A353" s="2" t="inlineStr">
         <is>
-          <t>guide.horse.paragraph1</t>
+          <t>guide.advisor.paragraph1</t>
         </is>
       </c>
       <c r="B353" s="2" t="inlineStr">
         <is>
-          <t>Horse</t>
+          <t>Advisor</t>
         </is>
       </c>
       <c r="C353" s="2" t="inlineStr">
         <is>
-          <t>Mã</t>
+          <t>Sĩ</t>
         </is>
       </c>
     </row>
     <row r="354" ht="18" customHeight="1">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>guide.horse.paragraph2</t>
+          <t>guide.advisor.paragraph2</t>
         </is>
       </c>
       <c r="B354" s="2" t="inlineStr">
         <is>
-          <t>Moves in an &lt;b&gt;L-shape&lt;/b&gt; (one step orthogonally then one step diagonally outward). If the adjacent orthogonal point is occupied by any piece, the Horse is blocked and cannot move.</t>
+          <t>Moves one step &lt;b&gt;diagonally&lt;/b&gt; within the palace.</t>
         </is>
       </c>
       <c r="C354" s="2" t="inlineStr">
         <is>
-          <t>Đi theo &lt;b&gt;đường chéo hình chữ nhật&lt;/b&gt; của hai ô vuông liền nhau. Nếu giao điểm liền kề bước thẳng dọc ngang có một quân khác đứng thì Mã bị cản, không đi được.</t>
+          <t>Mỗi nước &lt;b&gt;đi chéo một bước&lt;/b&gt; trong cung Tướng.</t>
         </is>
       </c>
     </row>
     <row r="355" ht="18" customHeight="1">
       <c r="A355" s="2" t="inlineStr">
         <is>
-          <t>guide.cannon.paragraph1</t>
+          <t>guide.elephant.paragraph1</t>
         </is>
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>Cannon</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
         <is>
-          <t>Pháo</t>
+          <t>Tượng</t>
         </is>
       </c>
     </row>
     <row r="356" ht="18" customHeight="1">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>guide.cannon.paragraph2</t>
+          <t>guide.elephant.paragraph2</t>
         </is>
       </c>
       <c r="B356" s="2" t="inlineStr">
         <is>
-          <t>Moves &lt;b&gt;horizontally or vertically&lt;/b&gt; like a Chariot when not capturing. To capture, it must &lt;b&gt;jump over exactly one piece&lt;/b&gt; to reach its target. If there are zero or more than one pieces between the Cannon and the target, it cannot capture.</t>
+          <t>Moves &lt;b&gt;two steps diagonally&lt;/b&gt; on its own side of the board and may not cross the river. If there is another piece on the midpoint of that diagonal path, the Elephant is blocked and cannot move.</t>
         </is>
       </c>
       <c r="C356" s="2" t="inlineStr">
         <is>
-          <t>Đi ngang hoặc dọc giống Xe khi không bắt quân. Để bắt quân, nó phải &lt;b&gt;nhảy qua đúng một quân khác&lt;/b&gt; để đến mục tiêu. Nếu không có hoặc có nhiều hơn một quân giữa Pháo và mục tiêu, nó không thể bắt quân.</t>
+          <t>Mỗi nước &lt;b&gt;đi chéo hai bước&lt;/b&gt; tại trận địa bên mình, không được qua sông. Nếu ở giữa đường chéo đó có quân khác đứng thì quân Tượng bị cản, không đi được.</t>
         </is>
       </c>
     </row>
     <row r="357" ht="17" customHeight="1">
       <c r="A357" s="2" t="inlineStr">
         <is>
-          <t>guide.soldier.paragraph1</t>
+          <t>guide.chariot.paragraph1</t>
         </is>
       </c>
       <c r="B357" s="2" t="inlineStr">
         <is>
-          <t>Soldier</t>
+          <t>Chariot</t>
         </is>
       </c>
       <c r="C357" s="2" t="inlineStr">
         <is>
-          <t>Tốt</t>
+          <t>Xe</t>
         </is>
       </c>
     </row>
     <row r="358" ht="18" customHeight="1">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>guide.soldier.paragraph2</t>
+          <t>guide.chariot.paragraph2</t>
         </is>
       </c>
       <c r="B358" s="2" t="inlineStr">
         <is>
-          <t>Moves &lt;b&gt;one step&lt;/b&gt; each turn. Before crossing the river, it can only move forward. After crossing the river, it may move &lt;b&gt;forward or sideways&lt;/b&gt;, but never backward.</t>
+          <t>Moves &lt;b&gt;horizontally or vertically&lt;/b&gt; with no limit on distance, as long as no piece blocks the path.</t>
         </is>
       </c>
       <c r="C358" s="2" t="inlineStr">
         <is>
-          <t>Mỗi nước đi &lt;b&gt;một bước&lt;/b&gt;. Khi chưa qua sông, Tốt chỉ được tiến. Khi Tốt đã qua sông được quyền &lt;b&gt;đi tiến và đi ngang&lt;/b&gt;, không được phép lùi.</t>
+          <t>Mỗi nước được &lt;b&gt;đi dọc hoặc đi ngang&lt;/b&gt;, không hạn chế số bước đi nếu không có quân khác cản đường.</t>
         </is>
       </c>
     </row>
     <row r="359" ht="18" customHeight="1">
       <c r="A359" s="2" t="inlineStr">
         <is>
-          <t>guide.capturing.paragraph1</t>
+          <t>guide.horse.paragraph1</t>
         </is>
       </c>
       <c r="B359" s="2" t="inlineStr">
         <is>
-          <t>When a piece moves to an intersection occupied by an opponent's piece, it may &lt;b&gt;capture that piece&lt;/b&gt; and occupy its position.</t>
+          <t>Horse</t>
         </is>
       </c>
       <c r="C359" s="2" t="inlineStr">
         <is>
-          <t>Khi một quân đi tới một giao điểm khác đã có quân đối phương đứng thì được quyền &lt;b&gt;bắt quân đó&lt;/b&gt;, đồng thời chiếm giữ vị trí quân bị bắt.</t>
+          <t>Mã</t>
         </is>
       </c>
     </row>
     <row r="360" ht="18" customHeight="1">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>guide.capturing.paragraph2</t>
+          <t>guide.horse.paragraph2</t>
         </is>
       </c>
       <c r="B360" s="2" t="inlineStr">
         <is>
-          <t>You may not capture your own pieces. You may sacrifice your own pieces to be captured by the opponent, &lt;b&gt;except for the General&lt;/b&gt;.</t>
+          <t>Moves in an &lt;b&gt;L-shape&lt;/b&gt; (one step orthogonally then one step diagonally outward). If the adjacent orthogonal point is occupied by any piece, the Horse is blocked and cannot move.</t>
         </is>
       </c>
       <c r="C360" s="2" t="inlineStr">
         <is>
-          <t>Không được bắt quân bên mình. Được phép cho đối phương bắt đầu quân mình chủ động hiến mình cho đối phương, &lt;b&gt;trừ Tướng&lt;/b&gt;.</t>
+          <t>Đi theo &lt;b&gt;đường chéo hình chữ nhật&lt;/b&gt; của hai ô vuông liền nhau. Nếu giao điểm liền kề bước thẳng dọc ngang có một quân khác đứng thì Mã bị cản, không đi được.</t>
         </is>
       </c>
     </row>
     <row r="361" ht="18" customHeight="1">
       <c r="A361" s="2" t="inlineStr">
         <is>
-          <t>guide.capturing.paragraph3</t>
+          <t>guide.cannon.paragraph1</t>
         </is>
       </c>
       <c r="B361" s="2" t="inlineStr">
         <is>
-          <t>A captured piece is removed from the board. &lt;b&gt;Chasing one piece for more than 6 consecutive moves is not allowed&lt;/b&gt;.</t>
+          <t>Cannon</t>
         </is>
       </c>
       <c r="C361" s="2" t="inlineStr">
         <is>
-          <t>Quân bị bắt phải bị loại và bị nhấc ra khỏi bàn cờ. &lt;b&gt;Không được đuổi 1 quân quá 6 nước cờ liên tiếp&lt;/b&gt;.</t>
+          <t>Pháo</t>
         </is>
       </c>
     </row>
     <row r="362" ht="18" customHeight="1">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>guide.check.paragraph1</t>
+          <t>guide.cannon.paragraph2</t>
         </is>
       </c>
       <c r="B362" s="2" t="inlineStr">
         <is>
-          <t>If a player makes a move that threatens to capture the opponent's General on the next move (by the same piece or another piece), it is called a &lt;b&gt;Check&lt;/b&gt;. The checked side must respond to avoid check. Otherwise, that side loses</t>
+          <t>Moves &lt;b&gt;horizontally or vertically&lt;/b&gt; like a Chariot when not capturing. To capture, it must &lt;b&gt;jump over exactly one piece&lt;/b&gt; to reach its target. If there are zero or more than one pieces between the Cannon and the target, it cannot capture.</t>
         </is>
       </c>
       <c r="C362" s="2" t="inlineStr">
         <is>
-          <t>Nếu người chơi thực hiện một nước đi đe dọa bắt Tướng của đối phương ở nước đi tiếp theo (bằng chính quân cờ đó hoặc một quân cờ khác), thì đó được gọi là &lt;b&gt;Chiếu&lt;/b&gt;. Bên bị chiếu phải đáp trả để tránh bị chiếu. Nếu không sẽ bị xử thua</t>
+          <t>Đi ngang hoặc dọc giống Xe khi không bắt quân. Để bắt quân, nó phải &lt;b&gt;nhảy qua đúng một quân khác&lt;/b&gt; để đến mục tiêu. Nếu không có hoặc có nhiều hơn một quân giữa Pháo và mục tiêu, nó không thể bắt quân.</t>
         </is>
       </c>
     </row>
     <row r="363" ht="18" customHeight="1">
       <c r="A363" s="2" t="inlineStr">
         <is>
-          <t>guide.check.paragraph2</t>
+          <t>guide.soldier.paragraph1</t>
         </is>
       </c>
       <c r="B363" s="2" t="inlineStr">
         <is>
-          <t>When the General is checked from any direction (including from behind), the checked side may respond in one of the following ways:</t>
+          <t>Soldier</t>
         </is>
       </c>
       <c r="C363" s="2" t="inlineStr">
         <is>
-          <t>Tướng bị chiếu từ cả bốn hướng (bị chiếu cả từ phía sau) có thể ứng phó với nước chiếu tướng bằng một trong các cách sau:</t>
+          <t>Tốt</t>
         </is>
       </c>
     </row>
     <row r="364" ht="17" customHeight="1">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>guide.check.paragraph3</t>
+          <t>guide.soldier.paragraph2</t>
         </is>
       </c>
       <c r="B364" s="2" t="inlineStr">
         <is>
-          <t>Move the General to another position to escape check</t>
+          <t>Moves &lt;b&gt;one step&lt;/b&gt; each turn. Before crossing the river, it can only move forward. After crossing the river, it may move &lt;b&gt;forward or sideways&lt;/b&gt;, but never backward.</t>
         </is>
       </c>
       <c r="C364" s="2" t="inlineStr">
         <is>
-          <t>Di chuyển tướng sang vị trí khác để tránh nước chiếu</t>
+          <t>Mỗi nước đi &lt;b&gt;một bước&lt;/b&gt;. Khi chưa qua sông, Tốt chỉ được tiến. Khi Tốt đã qua sông được quyền &lt;b&gt;đi tiến và đi ngang&lt;/b&gt;, không được phép lùi.</t>
         </is>
       </c>
     </row>
     <row r="365" ht="17" customHeight="1">
       <c r="A365" s="2" t="inlineStr">
         <is>
-          <t>guide.check.paragraph4</t>
+          <t>guide.capturing.paragraph1</t>
         </is>
       </c>
       <c r="B365" s="2" t="inlineStr">
         <is>
-          <t>Capture the checking piece</t>
+          <t>When a piece moves to an intersection occupied by an opponent's piece, it may &lt;b&gt;capture that piece&lt;/b&gt; and occupy its position.</t>
         </is>
       </c>
       <c r="C365" s="2" t="inlineStr">
         <is>
-          <t>Bắt quân đang chiếu</t>
+          <t>Khi một quân đi tới một giao điểm khác đã có quân đối phương đứng thì được quyền &lt;b&gt;bắt quân đó&lt;/b&gt;, đồng thời chiếm giữ vị trí quân bị bắt.</t>
         </is>
       </c>
     </row>
     <row r="366" ht="17" customHeight="1">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>guide.check.paragraph5</t>
+          <t>guide.capturing.paragraph2</t>
         </is>
       </c>
       <c r="B366" s="2" t="inlineStr">
         <is>
-          <t>Block the checking line with another piece to protect the General</t>
+          <t>You may not capture your own pieces. You may sacrifice your own pieces to be captured by the opponent, &lt;b&gt;except for the General&lt;/b&gt;.</t>
         </is>
       </c>
       <c r="C366" s="2" t="inlineStr">
         <is>
-          <t>Dùng quân khác cản quân chiếu, đi quân che đỡ cho tướng</t>
+          <t>Không được bắt quân bên mình. Được phép cho đối phương bắt đầu quân mình chủ động hiến mình cho đối phương, &lt;b&gt;trừ Tướng&lt;/b&gt;.</t>
         </is>
       </c>
     </row>
     <row r="367" ht="17" customHeight="1">
       <c r="A367" s="2" t="inlineStr">
         <is>
-          <t>guide.check.paragraph6</t>
+          <t>guide.capturing.paragraph3</t>
         </is>
       </c>
       <c r="B367" s="2" t="inlineStr">
         <is>
-          <t>Repeatedly checking for more than 6 consecutive moves is not allowed</t>
+          <t>A captured piece is removed from the board. &lt;b&gt;Chasing one piece for more than 6 consecutive moves is not allowed&lt;/b&gt;.</t>
         </is>
       </c>
       <c r="C367" s="2" t="inlineStr">
         <is>
-          <t>Không được chiếu tướng quá 6 nước cờ liên tiếp</t>
+          <t>Quân bị bắt phải bị loại và bị nhấc ra khỏi bàn cờ. &lt;b&gt;Không được đuổi 1 quân quá 6 nước cờ liên tiếp&lt;/b&gt;.</t>
         </is>
       </c>
     </row>
     <row r="368" ht="17" customHeight="1">
       <c r="A368" s="2" t="inlineStr">
         <is>
-          <t>guide.result.paragraph1</t>
+          <t>guide.check.paragraph1</t>
         </is>
       </c>
       <c r="B368" s="2" t="inlineStr">
         <is>
-          <t>When one side gives Check and the other side has no legal way to protect the General, it is called a &lt;b&gt;Checkmate&lt;/b&gt;. The side that delivers Checkmate wins.</t>
+          <t>If a player makes a move that threatens to capture the opponent's General on the next move (by the same piece or another piece), it is called a &lt;b&gt;Check&lt;/b&gt;. The checked side must respond to avoid check. Otherwise, that side loses</t>
         </is>
       </c>
       <c r="C368" s="2" t="inlineStr">
         <is>
-          <t>Khi một bên chiếu Tướng mà bên còn lại không thể làm gì để bảo vệ Tướng thì được gọi là &lt;b&gt;Chiếu Hết&lt;/b&gt;, bên thực hiện được Chiếu Hết sẽ giành chiến thắng.</t>
+          <t>Nếu người chơi thực hiện một nước đi đe dọa bắt Tướng của đối phương ở nước đi tiếp theo (bằng chính quân cờ đó hoặc một quân cờ khác), thì đó được gọi là &lt;b&gt;Chiếu&lt;/b&gt;. Bên bị chiếu phải đáp trả để tránh bị chiếu. Nếu không sẽ bị xử thua</t>
         </is>
       </c>
     </row>
     <row r="369" ht="17" customHeight="1">
       <c r="A369" s="2" t="inlineStr">
         <is>
-          <t>guide.result.paragraph2</t>
+          <t>guide.check.paragraph2</t>
         </is>
       </c>
       <c r="B369" s="2" t="inlineStr">
         <is>
-          <t>If a player runs out of time for a single move (for example: 90s) without moving, the other side is awarded a &lt;b&gt;win&lt;/b&gt;.</t>
+          <t>When the General is checked from any direction (including from behind), the checked side may respond in one of the following ways:</t>
         </is>
       </c>
       <c r="C369" s="2" t="inlineStr">
         <is>
-          <t>Khi hết thời gian một nước đi (ví dụ: 90s) mà vẫn chưa di chuyển quân thì bên còn lại sẽ được &lt;b&gt;xử Thắng&lt;/b&gt;.</t>
+          <t>Tướng bị chiếu từ cả bốn hướng (bị chiếu cả từ phía sau) có thể ứng phó với nước chiếu tướng bằng một trong các cách sau:</t>
         </is>
       </c>
     </row>
     <row r="370" ht="17" customHeight="1">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>guide.result.paragraph3</t>
+          <t>guide.check.paragraph3</t>
         </is>
       </c>
       <c r="B370" s="2" t="inlineStr">
         <is>
-          <t>If a player runs out of total game time (for example: 5 minutes or 10 minutes), the other side is awarded a &lt;b&gt;win&lt;/b&gt;.</t>
+          <t>Move the General to another position to escape check</t>
         </is>
       </c>
       <c r="C370" s="2" t="inlineStr">
         <is>
-          <t>Khi một bên hết thời gian ván đấu (ví dụ: 5 phút, 10 phút) thì bên còn lại sẽ được &lt;b&gt;xử Thắng&lt;/b&gt;.</t>
+          <t>Di chuyển tướng sang vị trí khác để tránh nước chiếu</t>
         </is>
       </c>
     </row>
     <row r="371" ht="17" customHeight="1">
       <c r="A371" s="2" t="inlineStr">
         <is>
-          <t>guide.result.paragraph4</t>
+          <t>guide.check.paragraph4</t>
         </is>
       </c>
       <c r="B371" s="2" t="inlineStr">
         <is>
-          <t>If both sides have no pieces that have crossed the river, the game is declared a &lt;b&gt;draw&lt;/b&gt;. If one side still has pieces across the river but runs out of time, while the other side still has time but has no pieces across the river, the game is declared a &lt;b&gt;draw&lt;/b&gt;.</t>
+          <t>Capture the checking piece</t>
         </is>
       </c>
       <c r="C371" s="2" t="inlineStr">
         <is>
-          <t>Khi cả 2 bên đều không còn quân qua sông, ván đấu sẽ được &lt;b&gt;xử Hòa&lt;/b&gt;. Khi một bên còn quân qua sông nhưng cạn thời gian, một bên còn thời gian nhưng hết quân qua sông, ván đấu sẽ được &lt;b&gt;xử Hòa&lt;/b&gt;.</t>
+          <t>Bắt quân đang chiếu</t>
         </is>
       </c>
     </row>
     <row r="372" ht="17" customHeight="1">
       <c r="A372" s="2" t="inlineStr">
         <is>
-          <t>guide.result.paragraph5</t>
+          <t>guide.check.paragraph5</t>
         </is>
       </c>
       <c r="B372" s="2" t="inlineStr">
         <is>
-          <t>Within 40 moves, if there is no capture and no Soldier advances by one square, the game is declared a &lt;b&gt;draw&lt;/b&gt;.</t>
+          <t>Block the checking line with another piece to protect the General</t>
         </is>
       </c>
       <c r="C372" s="2" t="inlineStr">
         <is>
-          <t>Trong vòng 40 nước nếu không phát sinh nước bắt quân, Tốt không tiến 1 ô thì ván đấu sẽ được &lt;b&gt;xử Hòa&lt;/b&gt;.</t>
+          <t>Dùng quân khác cản quân chiếu, đi quân che đỡ cho tướng</t>
         </is>
       </c>
     </row>
     <row r="373" ht="17" customHeight="1">
       <c r="A373" s="2" t="inlineStr">
         <is>
-          <t>extra-money.title</t>
+          <t>guide.check.paragraph6</t>
         </is>
       </c>
       <c r="B373" s="2" t="inlineStr">
         <is>
-          <t>Daily tasks</t>
+          <t>Repeatedly checking for more than 6 consecutive moves is not allowed</t>
         </is>
       </c>
       <c r="C373" s="2" t="inlineStr">
         <is>
-          <t>Kiếm tiền</t>
+          <t>Không được chiếu tướng quá 6 nước cờ liên tiếp</t>
         </is>
       </c>
     </row>
     <row r="374" ht="17" customHeight="1">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>extra-money.tab.lucky-wheel</t>
+          <t>guide.result.paragraph1</t>
         </is>
       </c>
       <c r="B374" s="2" t="inlineStr">
         <is>
-          <t>Lucky Wheel</t>
+          <t>When one side gives Check and the other side has no legal way to protect the General, it is called a &lt;b&gt;Checkmate&lt;/b&gt;. The side that delivers Checkmate wins.</t>
         </is>
       </c>
       <c r="C374" s="2" t="inlineStr">
         <is>
-          <t>Vòng Quay May Mắn</t>
+          <t>Khi một bên chiếu Tướng mà bên còn lại không thể làm gì để bảo vệ Tướng thì được gọi là &lt;b&gt;Chiếu Hết&lt;/b&gt;, bên thực hiện được Chiếu Hết sẽ giành chiến thắng.</t>
         </is>
       </c>
     </row>
     <row r="375" ht="17" customHeight="1">
       <c r="A375" s="2" t="inlineStr">
         <is>
-          <t>extra-money.tab.bonus-coin</t>
+          <t>guide.result.paragraph2</t>
         </is>
       </c>
       <c r="B375" s="2" t="inlineStr">
         <is>
-          <t>Bonus Coin</t>
+          <t>If a player runs out of time for a single move (for example: 90s) without moving, the other side is awarded a &lt;b&gt;win&lt;/b&gt;.</t>
         </is>
       </c>
       <c r="C375" s="2" t="inlineStr">
         <is>
-          <t>Xu Thưởng</t>
+          <t>Khi hết thời gian một nước đi (ví dụ: 90s) mà vẫn chưa di chuyển quân thì bên còn lại sẽ được &lt;b&gt;xử Thắng&lt;/b&gt;.</t>
         </is>
       </c>
     </row>
     <row r="376" ht="17" customHeight="1">
       <c r="A376" s="2" t="inlineStr">
         <is>
-          <t>extra-money.tab.daily-bonus</t>
+          <t>guide.result.paragraph3</t>
         </is>
       </c>
       <c r="B376" s="2" t="inlineStr">
         <is>
-          <t>Daily Bonus</t>
+          <t>If a player runs out of total game time (for example: 5 minutes or 10 minutes), the other side is awarded a &lt;b&gt;win&lt;/b&gt;.</t>
         </is>
       </c>
       <c r="C376" s="2" t="inlineStr">
         <is>
-          <t>Thưởng hàng ngày</t>
+          <t>Khi một bên hết thời gian ván đấu (ví dụ: 5 phút, 10 phút) thì bên còn lại sẽ được &lt;b&gt;xử Thắng&lt;/b&gt;.</t>
         </is>
       </c>
     </row>
     <row r="377" ht="17" customHeight="1">
       <c r="A377" s="2" t="inlineStr">
         <is>
-          <t>extra-money.bonus-coin.subtitle</t>
+          <t>guide.result.paragraph4</t>
         </is>
       </c>
       <c r="B377" s="2" t="inlineStr">
         <is>
-          <t>Watch a short video to earn free coin</t>
+          <t>If both sides have no pieces that have crossed the river, the game is declared a &lt;b&gt;draw&lt;/b&gt;. If one side still has pieces across the river but runs out of time, while the other side still has time but has no pieces across the river, the game is declared a &lt;b&gt;draw&lt;/b&gt;.</t>
         </is>
       </c>
       <c r="C377" s="2" t="inlineStr">
         <is>
-          <t>Xem video ngắn để nhận xu miễn phí</t>
+          <t>Khi cả 2 bên đều không còn quân qua sông, ván đấu sẽ được &lt;b&gt;xử Hòa&lt;/b&gt;. Khi một bên còn quân qua sông nhưng cạn thời gian, một bên còn thời gian nhưng hết quân qua sông, ván đấu sẽ được &lt;b&gt;xử Hòa&lt;/b&gt;.</t>
         </is>
       </c>
     </row>
     <row r="378" ht="17" customHeight="1">
       <c r="A378" s="2" t="inlineStr">
         <is>
-          <t>extra-money.bonus-coin.next-in</t>
+          <t>guide.result.paragraph5</t>
         </is>
       </c>
       <c r="B378" s="2" t="inlineStr">
         <is>
-          <t>Next in:</t>
+          <t>Within 40 moves, if there is no capture and no Soldier advances by one square, the game is declared a &lt;b&gt;draw&lt;/b&gt;.</t>
         </is>
       </c>
       <c r="C378" s="2" t="inlineStr">
         <is>
-          <t>Lượt kế tiếp:</t>
+          <t>Trong vòng 40 nước nếu không phát sinh nước bắt quân, Tốt không tiến 1 ô thì ván đấu sẽ được &lt;b&gt;xử Hòa&lt;/b&gt;.</t>
         </is>
       </c>
     </row>
     <row r="379" ht="17" customHeight="1">
       <c r="A379" s="2" t="inlineStr">
         <is>
-          <t>extra-money.bonus-coin.collect</t>
+          <t>extra-money.title</t>
         </is>
       </c>
       <c r="B379" s="2" t="inlineStr">
         <is>
-          <t>Collect</t>
+          <t>Daily tasks</t>
         </is>
       </c>
       <c r="C379" s="2" t="inlineStr">
         <is>
-          <t>Thu thập</t>
+          <t>Kiếm tiền</t>
         </is>
       </c>
     </row>
     <row r="380" ht="17" customHeight="1">
       <c r="A380" s="2" t="inlineStr">
         <is>
-          <t>extra-money.bonus-coin.watch-video</t>
+          <t>extra-money.tab.lucky-wheel</t>
         </is>
       </c>
       <c r="B380" s="2" t="inlineStr">
         <is>
-          <t>Watch video</t>
+          <t>Lucky Wheel</t>
         </is>
       </c>
       <c r="C380" s="2" t="inlineStr">
         <is>
-          <t>Xem video</t>
+          <t>Vòng Quay May Mắn</t>
         </is>
       </c>
     </row>
     <row r="381" ht="17" customHeight="1">
       <c r="A381" s="2" t="inlineStr">
         <is>
-          <t>extra-money.daily-bonus.subtitle</t>
+          <t>extra-money.tab.bonus-coin</t>
         </is>
       </c>
       <c r="B381" s="2" t="inlineStr">
         <is>
-          <t>Login 7 days in a row to earn 4000 coin</t>
+          <t>Bonus Coin</t>
         </is>
       </c>
       <c r="C381" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập 7 ngày liên tiếp để nhận 4000 xu</t>
+          <t>Xu Thưởng</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>extra-money.daily-bonus.day</t>
+          <t>extra-money.tab.daily-bonus</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Daily Bonus</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Ngày</t>
+          <t>Thưởng hàng ngày</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>extra-money.reward-ad.loading</t>
+          <t>extra-money.bonus-coin.subtitle</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Loading ad...</t>
+          <t>Watch a short video to earn free coin</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Đang tải quảng cáo...</t>
+          <t>Xem video ngắn để nhận xu miễn phí</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>extra-money.reward-ad.error</t>
+          <t>extra-money.bonus-coin.next-in</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Could not load the ad. Please try again.</t>
+          <t>Next in:</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Không tải được quảng cáo. Vui lòng thử lại.</t>
+          <t>Lượt kế tiếp:</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>extra-money.reward-ad.retry</t>
+          <t>extra-money.bonus-coin.collect</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Try again</t>
+          <t>Collect</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Thử lại</t>
+          <t>Thu thập</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>extra-money.reward-ad.close</t>
+          <t>extra-money.bonus-coin.watch-video</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Close</t>
+          <t>Watch video</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Đóng</t>
+          <t>Xem video</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>profile.button.save</t>
+          <t>extra-money.daily-bonus.subtitle</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Save</t>
+          <t>Login 7 days in a row to earn 4000 coin</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Lưu</t>
+          <t>Đăng nhập 7 ngày liên tiếp để nhận 4000 xu</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>profile.button.cancel</t>
+          <t>extra-money.daily-bonus.day</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Huỷ</t>
+          <t>Ngày</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>change-password.title</t>
+          <t>extra-money.reward-ad.loading</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Change password</t>
+          <t>Loading ad...</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Đổi mật khẩu</t>
+          <t>Đang tải quảng cáo...</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>change-password.current.label</t>
+          <t>extra-money.reward-ad.error</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Current password</t>
+          <t>Could not load the ad. Please try again.</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Mật khẩu hiện tại</t>
+          <t>Không tải được quảng cáo. Vui lòng thử lại.</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>change-password.current.placeholder</t>
+          <t>extra-money.reward-ad.retry</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Enter current password</t>
+          <t>Try again</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Nhập mật khẩu hiện tại</t>
+          <t>Thử lại</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>change-password.new.label</t>
+          <t>extra-money.reward-ad.close</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>New password</t>
+          <t>Close</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Mật khẩu mới</t>
+          <t>Đóng</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>change-password.new.placeholder</t>
+          <t>profile.button.save</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Enter new password</t>
+          <t>Save</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Nhập mật khẩu mới</t>
+          <t>Lưu</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>change-password.confirm.label</t>
+          <t>profile.button.cancel</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Confirm new password</t>
+          <t>Cancel</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Xác nhận mật khẩu mới</t>
+          <t>Huỷ</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>change-password.confirm.placeholder</t>
+          <t>change-password.title</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Re-enter new password</t>
+          <t>Change password</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Nhập lại mật khẩu mới</t>
+          <t>Đổi mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>change-password.confirm.mismatch</t>
+          <t>change-password.current.label</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Passwords do not match</t>
+          <t>Current password</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Mật khẩu xác nhận không khớp</t>
+          <t>Mật khẩu hiện tại</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>change-password.show</t>
+          <t>change-password.current.placeholder</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Show password</t>
+          <t>Enter current password</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Hiện mật khẩu</t>
+          <t>Nhập mật khẩu hiện tại</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>change-password.hide</t>
+          <t>change-password.new.label</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Hide password</t>
+          <t>New password</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Ẩn mật khẩu</t>
+          <t>Mật khẩu mới</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>change-password.submit</t>
+          <t>change-password.new.placeholder</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Change password</t>
+          <t>Enter new password</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Đổi mật khẩu</t>
+          <t>Nhập mật khẩu mới</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>change-password.submitting</t>
+          <t>change-password.confirm.label</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Changing...</t>
+          <t>Confirm new password</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Đang đổi...</t>
+          <t>Xác nhận mật khẩu mới</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>change-password.messages.success</t>
+          <t>change-password.confirm.placeholder</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Password changed successfully</t>
+          <t>Re-enter new password</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Đổi mật khẩu thành công</t>
+          <t>Nhập lại mật khẩu mới</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>change-password.messages.missing-fields</t>
+          <t>change-password.confirm.mismatch</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Please fill in all fields</t>
+          <t>Passwords do not match</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Vui lòng nhập đầy đủ thông tin</t>
+          <t>Mật khẩu xác nhận không khớp</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>change-password.messages.weak-password</t>
+          <t>change-password.show</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>New password does not meet the requirements</t>
+          <t>Show password</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Mật khẩu mới không đạt yêu cầu</t>
+          <t>Hiện mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>change-password.messages.same-as-current</t>
+          <t>change-password.hide</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>New password must be different from the current one</t>
+          <t>Hide password</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Mật khẩu mới phải khác mật khẩu hiện tại</t>
+          <t>Ẩn mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>change-password.messages.incorrect-current-password</t>
+          <t>change-password.submit</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Current password is incorrect</t>
+          <t>Change password</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Mật khẩu hiện tại không đúng</t>
+          <t>Đổi mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>change-password.messages.user-not-found</t>
+          <t>change-password.submitting</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>User not found</t>
+          <t>Changing...</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Không tìm thấy người dùng</t>
+          <t>Đang đổi...</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>change-password.messages.unauthorized</t>
+          <t>change-password.messages.success</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Session expired. Please sign in again.</t>
+          <t>Password changed successfully</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Phiên đăng nhập đã hết hạn. Vui lòng đăng nhập lại.</t>
+          <t>Đổi mật khẩu thành công</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
+          <t>change-password.messages.missing-fields</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>Please fill in all fields</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>Vui lòng nhập đầy đủ thông tin</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>change-password.messages.weak-password</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>New password does not meet the requirements</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>Mật khẩu mới không đạt yêu cầu</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>change-password.messages.same-as-current</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>New password must be different from the current one</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>Mật khẩu mới phải khác mật khẩu hiện tại</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>change-password.messages.incorrect-current-password</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Current password is incorrect</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>Mật khẩu hiện tại không đúng</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>change-password.messages.user-not-found</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>User not found</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>Không tìm thấy người dùng</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>change-password.messages.unauthorized</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>Session expired. Please sign in again.</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>Phiên đăng nhập đã hết hạn. Vui lòng đăng nhập lại.</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
           <t>change-password.messages.internal-server-error</t>
         </is>
       </c>
-      <c r="B408" t="inlineStr">
+      <c r="B414" t="inlineStr">
         <is>
           <t>Something went wrong. Please try again.</t>
         </is>
       </c>
-      <c r="C408" t="inlineStr">
+      <c r="C414" t="inlineStr">
         <is>
           <t>Đã có lỗi xảy ra. Vui lòng thử lại.</t>
         </is>
       </c>
-    </row>
-    <row r="409">
-      <c r="A409" t="inlineStr"/>
-      <c r="B409" t="inlineStr"/>
-      <c r="C409" t="inlineStr"/>
-    </row>
-    <row r="410">
-      <c r="A410" t="inlineStr"/>
-      <c r="B410" t="inlineStr"/>
-      <c r="C410" t="inlineStr"/>
-    </row>
-    <row r="411">
-      <c r="A411" t="inlineStr"/>
-      <c r="B411" t="inlineStr"/>
-      <c r="C411" t="inlineStr"/>
-    </row>
-    <row r="412">
-      <c r="A412" t="inlineStr"/>
-      <c r="B412" t="inlineStr"/>
-      <c r="C412" t="inlineStr"/>
-    </row>
-    <row r="413">
-      <c r="A413" t="inlineStr"/>
-      <c r="B413" t="inlineStr"/>
-      <c r="C413" t="inlineStr"/>
-    </row>
-    <row r="414">
-      <c r="A414" t="inlineStr"/>
-      <c r="B414" t="inlineStr"/>
-      <c r="C414" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr"/>
@@ -7363,6 +7435,36 @@
       <c r="A427" t="inlineStr"/>
       <c r="B427" t="inlineStr"/>
       <c r="C427" t="inlineStr"/>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr"/>
+      <c r="B428" t="inlineStr"/>
+      <c r="C428" t="inlineStr"/>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr"/>
+      <c r="B429" t="inlineStr"/>
+      <c r="C429" t="inlineStr"/>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr"/>
+      <c r="B430" t="inlineStr"/>
+      <c r="C430" t="inlineStr"/>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr"/>
+      <c r="B431" t="inlineStr"/>
+      <c r="C431" t="inlineStr"/>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr"/>
+      <c r="B432" t="inlineStr"/>
+      <c r="C432" t="inlineStr"/>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr"/>
+      <c r="B433" t="inlineStr"/>
+      <c r="C433" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tools/languages.xlsx
+++ b/tools/languages.xlsx
@@ -325,7 +325,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C433"/>
+  <dimension ref="A1:C442"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3345,2098 +3345,2098 @@
     <row r="178" ht="18" customHeight="1">
       <c r="A178" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.invalid-time-limit</t>
+          <t>create-room.messages.invalid-game-type</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>Invalid time limit</t>
+          <t>Invalid game type</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>Thời gian không hợp lệ</t>
+          <t>Loại cờ không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="179" ht="18" customHeight="1">
       <c r="A179" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.invalid-redFirst</t>
+          <t>create-room.messages.pve-not-supported</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>'redFirst' must be a boolean</t>
+          <t>This game does not support playing against the bot yet</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>'redFirst' phải là giá trị boolean</t>
+          <t>Trò chơi này chưa hỗ trợ đấu với máy</t>
         </is>
       </c>
     </row>
     <row r="180" ht="18" customHeight="1">
       <c r="A180" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.invalid-team-name</t>
+          <t>create-room.messages.invalid-time-limit</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>Team name must be either 'red', 'black', or null</t>
+          <t>Invalid time limit</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>Tên đội phải là 'red', 'black' hoặc null</t>
+          <t>Thời gian không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="181" ht="18" customHeight="1">
       <c r="A181" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.name-required</t>
+          <t>create-room.messages.invalid-redFirst</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>Room name (tableName) is required and must not be empty</t>
+          <t>'redFirst' must be a boolean</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>Tên phòng (tableName) là bắt buộc và không được để trống</t>
+          <t>'redFirst' phải là giá trị boolean</t>
         </is>
       </c>
     </row>
     <row r="182" ht="18" customHeight="1">
       <c r="A182" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.room-created</t>
+          <t>create-room.messages.invalid-team-name</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>Room created successfully</t>
+          <t>Team name must be either 'red', 'black', or null</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>Phòng được tạo thành công</t>
+          <t>Tên đội phải là 'red', 'black' hoặc null</t>
         </is>
       </c>
     </row>
     <row r="183" ht="18" customHeight="1">
       <c r="A183" s="1" t="inlineStr">
         <is>
-          <t>fetch-rooms.messages.internal-server-error</t>
+          <t>create-room.messages.name-required</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Room name (tableName) is required and must not be empty</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Tên phòng (tableName) là bắt buộc và không được để trống</t>
         </is>
       </c>
     </row>
     <row r="184" ht="18" customHeight="1">
       <c r="A184" s="1" t="inlineStr">
         <is>
-          <t>fetch-rooms.messages.invalid-status</t>
+          <t>create-room.messages.room-created</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>Query parameter 'status' must be an integer</t>
+          <t>Room created successfully</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>Tham số truy vấn 'status' phải là số nguyên</t>
+          <t>Phòng được tạo thành công</t>
         </is>
       </c>
     </row>
     <row r="185" ht="36" customHeight="1">
       <c r="A185" s="1" t="inlineStr">
         <is>
-          <t>fetch-rooms.messages.success</t>
+          <t>fetch-rooms.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>Fetch rooms successfully</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>Lấy phòng thành công</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="186" ht="18" customHeight="1">
       <c r="A186" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.messages.email-not-found</t>
+          <t>fetch-rooms.messages.invalid-status</t>
         </is>
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>Email does not exist</t>
+          <t>Query parameter 'status' must be an integer</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>Email không tồn tại</t>
+          <t>Tham số truy vấn 'status' phải là số nguyên</t>
         </is>
       </c>
     </row>
     <row r="187" ht="36" customHeight="1">
       <c r="A187" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.messages.email-service-not-configured</t>
+          <t>fetch-rooms.messages.invalid-game-type</t>
         </is>
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>Email service is not configured</t>
+          <t>Query parameter 'gameType' is invalid</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>Dịch vụ email chưa được cấu hình</t>
+          <t>Tham số truy vấn 'gameType' không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="188" ht="18" customHeight="1">
       <c r="A188" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.messages.internal-server-error</t>
+          <t>variant.xiangqi.name</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Chinese Chess</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Cờ Tướng</t>
         </is>
       </c>
     </row>
     <row r="189" ht="18" customHeight="1">
       <c r="A189" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.messages.invalid-email-format</t>
+          <t>variant.chess.name</t>
         </is>
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>Invalid email format</t>
+          <t>Chess</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>Định dạng email không hợp lệ</t>
+          <t>Cờ Vua</t>
         </is>
       </c>
     </row>
     <row r="190" ht="18" customHeight="1">
       <c r="A190" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.messages.missing-email</t>
+          <t>variant.xiangqi.team.red</t>
         </is>
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>Email is required</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>Email là bắt buộc</t>
+          <t>Đỏ</t>
         </is>
       </c>
     </row>
     <row r="191" ht="18" customHeight="1">
       <c r="A191" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.messages.success</t>
+          <t>variant.xiangqi.team.black</t>
         </is>
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>Forgot password email sent</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>Email đặt lại mật khẩu đã được gửi</t>
+          <t>Đen</t>
         </is>
       </c>
     </row>
     <row r="192" ht="18" customHeight="1">
       <c r="A192" s="1" t="inlineStr">
         <is>
-          <t>join-room.messages.internal-server-error</t>
+          <t>variant.chess.team.white</t>
         </is>
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>White</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Trắng</t>
         </is>
       </c>
     </row>
     <row r="193" ht="18" customHeight="1">
       <c r="A193" s="1" t="inlineStr">
         <is>
-          <t>join-room.messages.invalid-team</t>
+          <t>variant.chess.team.black</t>
         </is>
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>Field 'team' must be 'red', 'black', null, or undefined</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>Trường 'team' phải là 'red', 'black', null hoặc không truyền</t>
+          <t>Đen</t>
         </is>
       </c>
     </row>
     <row r="194" ht="18" customHeight="1">
       <c r="A194" s="1" t="inlineStr">
         <is>
-          <t>join-room.messages.invalid-room-id</t>
+          <t>fetch-rooms.messages.success</t>
         </is>
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>Field 'id' is required and must be a positive integer</t>
+          <t>Fetch rooms successfully</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
+          <t>Lấy phòng thành công</t>
         </is>
       </c>
     </row>
     <row r="195" ht="18" customHeight="1">
       <c r="A195" s="1" t="inlineStr">
         <is>
-          <t>join-room.messages.room-not-found</t>
+          <t>forgot-password.messages.email-not-found</t>
         </is>
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>Room not found</t>
+          <t>Email does not exist</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy phòng</t>
+          <t>Email không tồn tại</t>
         </is>
       </c>
     </row>
     <row r="196" ht="18" customHeight="1">
       <c r="A196" s="1" t="inlineStr">
         <is>
-          <t>join-room.messages.success</t>
+          <t>forgot-password.messages.email-service-not-configured</t>
         </is>
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>Successfully joined the room</t>
+          <t>Email service is not configured</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>Tham gia phòng thành công</t>
+          <t>Dịch vụ email chưa được cấu hình</t>
         </is>
       </c>
     </row>
     <row r="197" ht="18" customHeight="1">
       <c r="A197" s="1" t="inlineStr">
         <is>
-          <t>join-room.messages.team-seat-occupied</t>
+          <t>forgot-password.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>Selected team seat is already occupied</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>Vị trí đội đã chọn đã có người chơi</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="198" ht="18" customHeight="1">
       <c r="A198" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.cannot-kick-self</t>
+          <t>forgot-password.messages.invalid-email-format</t>
         </is>
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>You cannot kick yourself</t>
+          <t>Invalid email format</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>Bạn không thể kick chính mình</t>
+          <t>Định dạng email không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="199" ht="18" customHeight="1">
       <c r="A199" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.forbidden</t>
+          <t>forgot-password.messages.missing-email</t>
         </is>
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>Only the host can kick users</t>
+          <t>Email is required</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>Chỉ chủ phòng mới có thể kick người dùng</t>
+          <t>Email là bắt buộc</t>
         </is>
       </c>
     </row>
     <row r="200" ht="18" customHeight="1">
       <c r="A200" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.internal-server-error</t>
+          <t>forgot-password.messages.success</t>
         </is>
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Forgot password email sent</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Email đặt lại mật khẩu đã được gửi</t>
         </is>
       </c>
     </row>
     <row r="201" ht="18" customHeight="1">
       <c r="A201" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.invalid-room-id</t>
+          <t>join-room.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>Field 'id' is required and must be a positive integer</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="202" ht="18" customHeight="1">
       <c r="A202" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.invalid-user-id</t>
+          <t>join-room.messages.invalid-team</t>
         </is>
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>Field 'userId' is required and must be a positive integer</t>
+          <t>Field 'team' must be 'red', 'black', null, or undefined</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>Trường 'userId' là bắt buộc và phải là số nguyên dương</t>
+          <t>Trường 'team' phải là 'red', 'black', null hoặc không truyền</t>
         </is>
       </c>
     </row>
     <row r="203" ht="18" customHeight="1">
       <c r="A203" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.room-not-found</t>
+          <t>join-room.messages.invalid-room-id</t>
         </is>
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>Room not found</t>
+          <t>Field 'id' is required and must be a positive integer</t>
         </is>
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy phòng</t>
+          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
         </is>
       </c>
     </row>
     <row r="204" ht="18" customHeight="1">
       <c r="A204" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.room-not-waiting</t>
+          <t>join-room.messages.room-not-found</t>
         </is>
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>You can only kick users while the room is waiting</t>
+          <t>Room not found</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>Chỉ có thể kick người dùng khi phòng đang ở trạng thái chờ</t>
+          <t>Không tìm thấy phòng</t>
         </is>
       </c>
     </row>
     <row r="205" ht="18" customHeight="1">
       <c r="A205" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.success</t>
+          <t>join-room.messages.success</t>
         </is>
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>User has been kicked</t>
+          <t>Successfully joined the room</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>Người dùng đã bị kick</t>
+          <t>Tham gia phòng thành công</t>
         </is>
       </c>
     </row>
     <row r="206" ht="18" customHeight="1">
       <c r="A206" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.user-not-in-room</t>
+          <t>join-room.messages.team-seat-occupied</t>
         </is>
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>User is not in this room</t>
+          <t>Selected team seat is already occupied</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>Người dùng không trong phòng này</t>
+          <t>Vị trí đội đã chọn đã có người chơi</t>
         </is>
       </c>
     </row>
     <row r="207" ht="18" customHeight="1">
       <c r="A207" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.you-were-kicked</t>
+          <t>kick-user.messages.cannot-kick-self</t>
         </is>
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>You have been removed from the room by the host</t>
+          <t>You cannot kick yourself</t>
         </is>
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>Bạn đã bị chủ phòng đưa ra khỏi phòng</t>
+          <t>Bạn không thể kick chính mình</t>
         </is>
       </c>
     </row>
     <row r="208" ht="18" customHeight="1">
       <c r="A208" s="1" t="inlineStr">
         <is>
-          <t>leave-room.messages.internal-server-error</t>
+          <t>kick-user.messages.forbidden</t>
         </is>
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Only the host can kick users</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Chỉ chủ phòng mới có thể kick người dùng</t>
         </is>
       </c>
     </row>
     <row r="209" ht="18" customHeight="1">
       <c r="A209" s="1" t="inlineStr">
         <is>
-          <t>leave-room.messages.invalid-room-id</t>
+          <t>kick-user.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>Field 'id' is required and must be a positive integer</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="210" ht="18" customHeight="1">
       <c r="A210" s="1" t="inlineStr">
         <is>
-          <t>leave-room.messages.player-not-in-room</t>
+          <t>kick-user.messages.invalid-room-id</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>Player is not in this room</t>
+          <t>Field 'id' is required and must be a positive integer</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>Người chơi không trong phòng này</t>
+          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
         </is>
       </c>
     </row>
     <row r="211" ht="36" customHeight="1">
       <c r="A211" s="1" t="inlineStr">
         <is>
-          <t>leave-room.messages.success</t>
+          <t>kick-user.messages.invalid-user-id</t>
         </is>
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>Leave room successfully</t>
+          <t>Field 'userId' is required and must be a positive integer</t>
         </is>
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>Rời phòng thành công</t>
+          <t>Trường 'userId' là bắt buộc và phải là số nguyên dương</t>
         </is>
       </c>
     </row>
     <row r="212" ht="18" customHeight="1">
       <c r="A212" s="1" t="inlineStr">
         <is>
-          <t>load-room.messages.internal-server-error</t>
+          <t>kick-user.messages.room-not-found</t>
         </is>
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Room not found</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Không tìm thấy phòng</t>
         </is>
       </c>
     </row>
     <row r="213" ht="18" customHeight="1">
       <c r="A213" s="1" t="inlineStr">
         <is>
-          <t>load-room.messages.invalid-room-id</t>
+          <t>kick-user.messages.room-not-waiting</t>
         </is>
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>Room ID must be a positive integer</t>
+          <t>You can only kick users while the room is waiting</t>
         </is>
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>ID phòng phải là số nguyên dương</t>
+          <t>Chỉ có thể kick người dùng khi phòng đang ở trạng thái chờ</t>
         </is>
       </c>
     </row>
     <row r="214" ht="18" customHeight="1">
       <c r="A214" s="1" t="inlineStr">
         <is>
-          <t>load-room.messages.room-not-found</t>
+          <t>kick-user.messages.success</t>
         </is>
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>Room not found</t>
+          <t>User has been kicked</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy phòng</t>
+          <t>Người dùng đã bị kick</t>
         </is>
       </c>
     </row>
     <row r="215" ht="18" customHeight="1">
       <c r="A215" s="1" t="inlineStr">
         <is>
-          <t>load-room.messages.success</t>
+          <t>kick-user.messages.user-not-in-room</t>
         </is>
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>Load room successfully</t>
+          <t>User is not in this room</t>
         </is>
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>Tải phòng thành công</t>
+          <t>Người dùng không trong phòng này</t>
         </is>
       </c>
     </row>
     <row r="216" ht="18" customHeight="1">
       <c r="A216" s="1" t="inlineStr">
         <is>
-          <t>google-login.messages.email-not-verified</t>
+          <t>kick-user.messages.you-were-kicked</t>
         </is>
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>Your Google email is not verified</t>
+          <t>You have been removed from the room by the host</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>Email Google của bạn chưa được xác minh</t>
+          <t>Bạn đã bị chủ phòng đưa ra khỏi phòng</t>
         </is>
       </c>
     </row>
     <row r="217" ht="18" customHeight="1">
       <c r="A217" s="1" t="inlineStr">
         <is>
-          <t>google-login.messages.failed</t>
+          <t>leave-room.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>Login failed</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập không thành công</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="218" ht="18" customHeight="1">
       <c r="A218" s="1" t="inlineStr">
         <is>
-          <t>google-login.messages.internal-server-error</t>
+          <t>leave-room.messages.invalid-room-id</t>
         </is>
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Field 'id' is required and must be a positive integer</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
         </is>
       </c>
     </row>
     <row r="219" ht="18" customHeight="1">
       <c r="A219" s="1" t="inlineStr">
         <is>
-          <t>google-login.messages.invalid-token</t>
+          <t>leave-room.messages.player-not-in-room</t>
         </is>
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>Invalid Google credential</t>
+          <t>Player is not in this room</t>
         </is>
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>Thông tin đăng nhập Google không hợp lệ</t>
+          <t>Người chơi không trong phòng này</t>
         </is>
       </c>
     </row>
     <row r="220" ht="18" customHeight="1">
       <c r="A220" s="1" t="inlineStr">
         <is>
-          <t>google-login.messages.missing-credential</t>
+          <t>leave-room.messages.success</t>
         </is>
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>Google credential is required</t>
+          <t>Leave room successfully</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>Thiếu thông tin đăng nhập Google</t>
+          <t>Rời phòng thành công</t>
         </is>
       </c>
     </row>
     <row r="221" ht="18" customHeight="1">
       <c r="A221" s="1" t="inlineStr">
         <is>
-          <t>facebook-login.messages.missing-token</t>
+          <t>load-room.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>Facebook token is required</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>Thiếu thông tin đăng nhập Facebook</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="222" ht="18" customHeight="1">
       <c r="A222" s="1" t="inlineStr">
         <is>
-          <t>facebook-login.messages.invalid-token</t>
+          <t>load-room.messages.invalid-room-id</t>
         </is>
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>Invalid Facebook token</t>
+          <t>Room ID must be a positive integer</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>Thông tin đăng nhập Facebook không hợp lệ</t>
+          <t>ID phòng phải là số nguyên dương</t>
         </is>
       </c>
     </row>
     <row r="223" ht="18" customHeight="1">
       <c r="A223" s="1" t="inlineStr">
         <is>
-          <t>facebook-login.messages.not-linked</t>
+          <t>load-room.messages.room-not-found</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>This Facebook account is not linked. Log in another way and link it in Settings</t>
+          <t>Room not found</t>
         </is>
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản Facebook này chưa được liên kết. Hãy đăng nhập cách khác rồi liên kết trong Cài đặt</t>
+          <t>Không tìm thấy phòng</t>
         </is>
       </c>
     </row>
     <row r="224" ht="18" customHeight="1">
       <c r="A224" s="1" t="inlineStr">
         <is>
-          <t>facebook-login.messages.internal-server-error</t>
+          <t>load-room.messages.success</t>
         </is>
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Load room successfully</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Tải phòng thành công</t>
         </is>
       </c>
     </row>
     <row r="225" ht="18" customHeight="1">
       <c r="A225" s="1" t="inlineStr">
         <is>
-          <t>facebook-link.messages.missing-token</t>
+          <t>google-login.messages.email-not-verified</t>
         </is>
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>Facebook token is required</t>
+          <t>Your Google email is not verified</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>Thiếu thông tin đăng nhập Facebook</t>
+          <t>Email Google của bạn chưa được xác minh</t>
         </is>
       </c>
     </row>
     <row r="226" ht="18" customHeight="1">
       <c r="A226" s="1" t="inlineStr">
         <is>
-          <t>facebook-link.messages.invalid-token</t>
+          <t>google-login.messages.failed</t>
         </is>
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>Invalid Facebook token</t>
+          <t>Login failed</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>Thông tin đăng nhập Facebook không hợp lệ</t>
+          <t>Đăng nhập không thành công</t>
         </is>
       </c>
     </row>
     <row r="227" ht="18" customHeight="1">
       <c r="A227" s="1" t="inlineStr">
         <is>
-          <t>facebook-link.messages.linked</t>
+          <t>google-login.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>Facebook linked successfully</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>Đã liên kết Facebook</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="228" ht="18" customHeight="1">
       <c r="A228" s="1" t="inlineStr">
         <is>
-          <t>facebook-link.messages.already-linked</t>
+          <t>google-login.messages.invalid-token</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>This Facebook account is already linked to your account</t>
+          <t>Invalid Google credential</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản Facebook này đã được liên kết với bạn</t>
+          <t>Thông tin đăng nhập Google không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="229" ht="18" customHeight="1">
       <c r="A229" s="1" t="inlineStr">
         <is>
-          <t>facebook-link.messages.linked-to-other</t>
+          <t>google-login.messages.missing-credential</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>This Facebook account is already linked to another account</t>
+          <t>Google credential is required</t>
         </is>
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản Facebook này đã được liên kết với tài khoản khác</t>
+          <t>Thiếu thông tin đăng nhập Google</t>
         </is>
       </c>
     </row>
     <row r="230" ht="18" customHeight="1">
       <c r="A230" s="1" t="inlineStr">
         <is>
-          <t>facebook-link.messages.already-has-facebook</t>
+          <t>facebook-login.messages.missing-token</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>You already linked a different Facebook account</t>
+          <t>Facebook token is required</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>Bạn đã liên kết một tài khoản Facebook khác</t>
+          <t>Thiếu thông tin đăng nhập Facebook</t>
         </is>
       </c>
     </row>
     <row r="231" ht="18" customHeight="1">
       <c r="A231" s="1" t="inlineStr">
         <is>
-          <t>facebook-link.messages.unlinked</t>
+          <t>facebook-login.messages.invalid-token</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>Facebook unlinked</t>
+          <t>Invalid Facebook token</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>Đã huỷ liên kết Facebook</t>
+          <t>Thông tin đăng nhập Facebook không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="232" ht="18" customHeight="1">
       <c r="A232" s="1" t="inlineStr">
         <is>
-          <t>facebook-link.messages.internal-server-error</t>
+          <t>facebook-login.messages.not-linked</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>This Facebook account is not linked. Log in another way and link it in Settings</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Tài khoản Facebook này chưa được liên kết. Hãy đăng nhập cách khác rồi liên kết trong Cài đặt</t>
         </is>
       </c>
     </row>
     <row r="233" ht="18" customHeight="1">
       <c r="A233" s="1" t="inlineStr">
         <is>
-          <t>logout.messages.already-inactive</t>
+          <t>facebook-login.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>Session already inactive</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>Phiên đã ngưng hoạt động</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="234" ht="18" customHeight="1">
       <c r="A234" s="1" t="inlineStr">
         <is>
-          <t>logout.messages.internal-server-error</t>
+          <t>facebook-link.messages.missing-token</t>
         </is>
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Facebook token is required</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Thiếu thông tin đăng nhập Facebook</t>
         </is>
       </c>
     </row>
     <row r="235" ht="18" customHeight="1">
       <c r="A235" s="1" t="inlineStr">
         <is>
-          <t>logout.messages.success</t>
+          <t>facebook-link.messages.invalid-token</t>
         </is>
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>Logout successful</t>
+          <t>Invalid Facebook token</t>
         </is>
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>Đăng xuất thành công</t>
+          <t>Thông tin đăng nhập Facebook không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="236" ht="18" customHeight="1">
       <c r="A236" s="1" t="inlineStr">
         <is>
-          <t>refresh-token.messages.missing-refresh-token</t>
+          <t>facebook-link.messages.linked</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>Missing refresh token cookie</t>
+          <t>Facebook linked successfully</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>Thiếu cookie token làm mới</t>
+          <t>Đã liên kết Facebook</t>
         </is>
       </c>
     </row>
     <row r="237" ht="18" customHeight="1">
       <c r="A237" s="1" t="inlineStr">
         <is>
-          <t>refresh-token.messages.mismatch-or-expired</t>
+          <t>facebook-link.messages.already-linked</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>Refresh token mismatch or expired</t>
+          <t>This Facebook account is already linked to your account</t>
         </is>
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>Thiếu refresh token hoặc đã hết hạn</t>
+          <t>Tài khoản Facebook này đã được liên kết với bạn</t>
         </is>
       </c>
     </row>
     <row r="238" ht="18" customHeight="1">
       <c r="A238" s="1" t="inlineStr">
         <is>
-          <t>refresh-token.messages.success</t>
+          <t>facebook-link.messages.linked-to-other</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>Token refreshed</t>
+          <t>This Facebook account is already linked to another account</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>Token đã làm mới</t>
+          <t>Tài khoản Facebook này đã được liên kết với tài khoản khác</t>
         </is>
       </c>
     </row>
     <row r="239" ht="18" customHeight="1">
       <c r="A239" s="1" t="inlineStr">
         <is>
-          <t>register.messages.email-exists</t>
+          <t>facebook-link.messages.already-has-facebook</t>
         </is>
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>Email already exists</t>
+          <t>You already linked a different Facebook account</t>
         </is>
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>Email đã tồn tại</t>
+          <t>Bạn đã liên kết một tài khoản Facebook khác</t>
         </is>
       </c>
     </row>
     <row r="240" ht="18" customHeight="1">
       <c r="A240" s="1" t="inlineStr">
         <is>
-          <t>register.messages.internal-server-error</t>
+          <t>facebook-link.messages.unlinked</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Facebook unlinked</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Đã huỷ liên kết Facebook</t>
         </is>
       </c>
     </row>
     <row r="241" ht="18" customHeight="1">
       <c r="A241" s="1" t="inlineStr">
         <is>
-          <t>register.messages.missing-fields</t>
+          <t>facebook-link.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>Username, password, gender, displayName and email are required</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>Tên người dùng, mật khẩu, giới tính, tên hiển thị và email là bắt buộc</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="242" ht="18" customHeight="1">
       <c r="A242" s="1" t="inlineStr">
         <is>
-          <t>register.messages.success</t>
+          <t>logout.messages.already-inactive</t>
         </is>
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>User created successfully</t>
+          <t>Session already inactive</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>Người dùng được tạo thành công</t>
+          <t>Phiên đã ngưng hoạt động</t>
         </is>
       </c>
     </row>
     <row r="243" ht="18" customHeight="1">
       <c r="A243" s="1" t="inlineStr">
         <is>
-          <t>register.messages.username-exists</t>
+          <t>logout.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>Username already exists</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>Tên người dùng đã tồn tại</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="244" ht="18" customHeight="1">
       <c r="A244" s="1" t="inlineStr">
         <is>
-          <t>reset-password.messages.internal-server-error</t>
+          <t>logout.messages.success</t>
         </is>
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Logout successful</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Đăng xuất thành công</t>
         </is>
       </c>
     </row>
     <row r="245" ht="18" customHeight="1">
       <c r="A245" s="1" t="inlineStr">
         <is>
-          <t>reset-password.messages.invalid-or-expired-token</t>
+          <t>refresh-token.messages.missing-refresh-token</t>
         </is>
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>Invalid or expired reset password token</t>
+          <t>Missing refresh token cookie</t>
         </is>
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>Token đặt lại mật khẩu không hợp lệ hoặc đã hết hạn</t>
+          <t>Thiếu cookie token làm mới</t>
         </is>
       </c>
     </row>
     <row r="246" ht="18" customHeight="1">
       <c r="A246" s="1" t="inlineStr">
         <is>
-          <t>reset-password.messages.invalid-user-id</t>
+          <t>refresh-token.messages.mismatch-or-expired</t>
         </is>
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>Invalid user id</t>
+          <t>Refresh token mismatch or expired</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>ID người dùng không hợp lệ</t>
+          <t>Thiếu refresh token hoặc đã hết hạn</t>
         </is>
       </c>
     </row>
     <row r="247" ht="18" customHeight="1">
       <c r="A247" s="1" t="inlineStr">
         <is>
-          <t>reset-password.messages.missing-id-or-token</t>
+          <t>refresh-token.messages.success</t>
         </is>
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>ID and token are required</t>
+          <t>Token refreshed</t>
         </is>
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>ID và token là bắt buộc</t>
+          <t>Token đã làm mới</t>
         </is>
       </c>
     </row>
     <row r="248" ht="18" customHeight="1">
       <c r="A248" s="1" t="inlineStr">
         <is>
-          <t>reset-password.messages.missing-userId-or-password</t>
+          <t>register.messages.email-exists</t>
         </is>
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>UserId and password are required</t>
+          <t>Email already exists</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>UserId và mật khẩu là bắt buộc</t>
+          <t>Email đã tồn tại</t>
         </is>
       </c>
     </row>
     <row r="249" ht="18" customHeight="1">
       <c r="A249" s="1" t="inlineStr">
         <is>
-          <t>reset-password.messages.token-valid</t>
+          <t>register.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>Reset password token is valid</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>Token đặt lại mật khẩu hợp lệ</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="250" ht="18" customHeight="1">
       <c r="A250" s="1" t="inlineStr">
         <is>
-          <t>reset-password.messages.user-not-found</t>
+          <t>register.messages.missing-fields</t>
         </is>
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>User not found</t>
+          <t>Username, password, gender, displayName and email are required</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy người dùng</t>
+          <t>Tên người dùng, mật khẩu, giới tính, tên hiển thị và email là bắt buộc</t>
         </is>
       </c>
     </row>
     <row r="251" ht="18" customHeight="1">
       <c r="A251" s="1" t="inlineStr">
         <is>
-          <t>room.actions.start-room</t>
+          <t>register.messages.success</t>
         </is>
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t>Start room</t>
+          <t>User created successfully</t>
         </is>
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>Bắt đầu chơi</t>
+          <t>Người dùng được tạo thành công</t>
         </is>
       </c>
     </row>
     <row r="252" ht="18" customHeight="1">
       <c r="A252" s="1" t="inlineStr">
         <is>
-          <t>room.actions.challenge</t>
+          <t>register.messages.username-exists</t>
         </is>
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>Challenge</t>
+          <t>Username already exists</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>Vào chơi</t>
+          <t>Tên người dùng đã tồn tại</t>
         </is>
       </c>
     </row>
     <row r="253" ht="18" customHeight="1">
       <c r="A253" s="1" t="inlineStr">
         <is>
-          <t>room.actions.leave-seat</t>
+          <t>reset-password.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>Leave seat</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>Ra xem</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="254" ht="18" customHeight="1">
       <c r="A254" s="1" t="inlineStr">
         <is>
-          <t>room.actions.undo</t>
+          <t>reset-password.messages.invalid-or-expired-token</t>
         </is>
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>Undo</t>
+          <t>Invalid or expired reset password token</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>Hoán tác</t>
+          <t>Token đặt lại mật khẩu không hợp lệ hoặc đã hết hạn</t>
         </is>
       </c>
     </row>
     <row r="255" ht="18" customHeight="1">
       <c r="A255" s="1" t="inlineStr">
         <is>
-          <t>room.actions.surrender</t>
+          <t>reset-password.messages.invalid-user-id</t>
         </is>
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>Surrender</t>
+          <t>Invalid user id</t>
         </is>
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>Đầu hàng</t>
+          <t>ID người dùng không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="256" ht="18" customHeight="1">
       <c r="A256" s="1" t="inlineStr">
         <is>
-          <t>room.actions.draw</t>
+          <t>reset-password.messages.missing-id-or-token</t>
         </is>
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>Draw</t>
+          <t>ID and token are required</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>Hòa</t>
+          <t>ID và token là bắt buộc</t>
         </is>
       </c>
     </row>
     <row r="257" ht="18" customHeight="1">
       <c r="A257" s="1" t="inlineStr">
         <is>
-          <t>room.actions.back-home</t>
+          <t>reset-password.messages.missing-userId-or-password</t>
         </is>
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>Back to home</t>
+          <t>UserId and password are required</t>
         </is>
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>Thoát phòng</t>
+          <t>UserId và mật khẩu là bắt buộc</t>
         </is>
       </c>
     </row>
     <row r="258" ht="18" customHeight="1">
       <c r="A258" s="1" t="inlineStr">
         <is>
-          <t>room.actions.flip-board</t>
+          <t>reset-password.messages.token-valid</t>
         </is>
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>Flip board</t>
+          <t>Reset password token is valid</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>Đảo chiều bàn cờ</t>
+          <t>Token đặt lại mật khẩu hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="259" ht="18" customHeight="1">
       <c r="A259" s="1" t="inlineStr">
         <is>
-          <t>room.actions.accept-draw</t>
+          <t>reset-password.messages.user-not-found</t>
         </is>
       </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
-          <t>Accept</t>
+          <t>User not found</t>
         </is>
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>Chấp nhận</t>
+          <t>Không tìm thấy người dùng</t>
         </is>
       </c>
     </row>
     <row r="260" ht="36" customHeight="1">
       <c r="A260" s="1" t="inlineStr">
         <is>
-          <t>room.actions.reject-draw</t>
+          <t>room.actions.start-room</t>
         </is>
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>Reject</t>
+          <t>Start room</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>Từ chối</t>
+          <t>Bắt đầu chơi</t>
         </is>
       </c>
     </row>
     <row r="261" ht="36" customHeight="1">
       <c r="A261" s="1" t="inlineStr">
         <is>
-          <t>room.actions.send-pm</t>
+          <t>room.actions.challenge</t>
         </is>
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>Send PM</t>
+          <t>Challenge</t>
         </is>
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>Chat</t>
+          <t>Vào chơi</t>
         </is>
       </c>
     </row>
     <row r="262" ht="18" customHeight="1">
       <c r="A262" s="1" t="inlineStr">
         <is>
-          <t>room.actions.view-history</t>
+          <t>room.actions.leave-seat</t>
         </is>
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>History</t>
+          <t>Leave seat</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>Lịch sử</t>
+          <t>Ra xem</t>
         </is>
       </c>
     </row>
     <row r="263" ht="18" customHeight="1">
       <c r="A263" s="1" t="inlineStr">
         <is>
-          <t>room.actions.kick</t>
+          <t>room.actions.undo</t>
         </is>
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t>Kick</t>
+          <t>Undo</t>
         </is>
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>Kick</t>
+          <t>Hoán tác</t>
         </is>
       </c>
     </row>
     <row r="264" ht="18" customHeight="1">
       <c r="A264" s="1" t="inlineStr">
         <is>
-          <t>room.actions.back-to-room</t>
+          <t>room.actions.surrender</t>
         </is>
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>Back to room</t>
+          <t>Surrender</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>Quay lại phòng chơi</t>
+          <t>Đầu hàng</t>
         </is>
       </c>
     </row>
     <row r="265" ht="17" customHeight="1">
       <c r="A265" s="1" t="inlineStr">
         <is>
-          <t>room.actions.chat</t>
+          <t>room.actions.draw</t>
         </is>
       </c>
       <c r="B265" s="1" t="inlineStr">
         <is>
-          <t>Room chat</t>
+          <t>Draw</t>
         </is>
       </c>
       <c r="C265" s="1" t="inlineStr">
         <is>
-          <t>Phòng chat</t>
+          <t>Hòa</t>
         </is>
       </c>
     </row>
     <row r="266" ht="18" customHeight="1">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>room.messages.draw-accepted</t>
+          <t>room.actions.back-home</t>
         </is>
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>Opponent accepted the draw</t>
+          <t>Back to home</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>Đối phương đã đồng ý hòa</t>
+          <t>Thoát phòng</t>
         </is>
       </c>
     </row>
     <row r="267" ht="18" customHeight="1">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>room.messages.draw-rejected</t>
+          <t>room.actions.flip-board</t>
         </is>
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>Opponent rejected the draw</t>
+          <t>Flip board</t>
         </is>
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>Đối phương từ chối hòa</t>
+          <t>Đảo chiều bàn cờ</t>
         </is>
       </c>
     </row>
     <row r="268" ht="18" customHeight="1">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>room.messages.opponent-surrendered</t>
+          <t>room.actions.accept-draw</t>
         </is>
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>Opponent surrendered! You won!</t>
+          <t>Accept</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>Đối phương đã đầu hàng! Bạn thắng!</t>
+          <t>Chấp nhận</t>
         </is>
       </c>
     </row>
     <row r="269" ht="18" customHeight="1">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>room.messages.confirm-leave</t>
+          <t>room.actions.reject-draw</t>
         </is>
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>Are you sure you want to leave room?</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="C269" s="2" t="inlineStr">
         <is>
-          <t>Bạn có chắc muốn rời bàn chơi?</t>
+          <t>Từ chối</t>
         </is>
       </c>
     </row>
     <row r="270" ht="18" customHeight="1">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>room.messages.confirm-surrender</t>
+          <t>room.actions.send-pm</t>
         </is>
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>Are you sure you want to surrender?</t>
+          <t>Send PM</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>Bạn có chắc chắn muốn đầu hàng không?</t>
+          <t>Chat</t>
         </is>
       </c>
     </row>
     <row r="271" ht="36" customHeight="1">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>room.messages.confirm-draw</t>
+          <t>room.actions.view-history</t>
         </is>
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>Are you sure you want to draw?</t>
+          <t>History</t>
         </is>
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>Bạn có chắc chắn muốn hòa không?</t>
+          <t>Lịch sử</t>
         </is>
       </c>
     </row>
     <row r="272" ht="36" customHeight="1">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>room.messages.confirm-accept-draw</t>
+          <t>room.actions.kick</t>
         </is>
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>Opponent has proposed a draw. Do you accept?</t>
+          <t>Kick</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>Đối phương đã chủ hòa, bạn có đồng ý không?</t>
+          <t>Kick</t>
         </is>
       </c>
     </row>
     <row r="273" ht="18" customHeight="1">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>room.messages.insufficient-amount</t>
+          <t>room.actions.back-to-room</t>
         </is>
       </c>
       <c r="B273" s="2" t="inlineStr">
         <is>
-          <t>You do not have enough balance to join this room</t>
+          <t>Back to room</t>
         </is>
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>Bạn không đủ tiền để tham gia bàn chơi này</t>
+          <t>Quay lại phòng chơi</t>
         </is>
       </c>
     </row>
     <row r="274" ht="18" customHeight="1">
       <c r="A274" s="1" t="inlineStr">
         <is>
-          <t>room.messages.will-leave-current-room</t>
+          <t>room.actions.chat</t>
         </is>
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>You are currently in another room. Joining this room will remove you from the current room</t>
+          <t>Room chat</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>Bạn đang ở trong một phòng khác. Tham gia phòng này sẽ loại bạn ra khỏi phòng hiện tại</t>
+          <t>Phòng chat</t>
         </is>
       </c>
     </row>
     <row r="275" ht="18" customHeight="1">
       <c r="A275" s="1" t="inlineStr">
         <is>
-          <t>room.messages.all-seats-occupied</t>
+          <t>room.messages.draw-accepted</t>
         </is>
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>All player seats are occupied</t>
+          <t>Opponent accepted the draw</t>
         </is>
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>Tất cả ghế chơi đã được chiếm</t>
+          <t>Đối phương đã đồng ý hòa</t>
         </is>
       </c>
     </row>
     <row r="276" ht="18" customHeight="1">
       <c r="A276" s="1" t="inlineStr">
         <is>
-          <t>room.messages.game-ended</t>
+          <t>room.messages.draw-rejected</t>
         </is>
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>Game ended</t>
+          <t>Opponent rejected the draw</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>Ván đấu đã kết thúc</t>
+          <t>Đối phương từ chối hòa</t>
         </is>
       </c>
     </row>
     <row r="277" ht="18" customHeight="1">
       <c r="A277" s="1" t="inlineStr">
         <is>
-          <t>room.messages.you-win</t>
+          <t>room.messages.opponent-surrendered</t>
         </is>
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>You win</t>
+          <t>Opponent surrendered! You won!</t>
         </is>
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t>Bạn đã chiến thắng</t>
+          <t>Đối phương đã đầu hàng! Bạn thắng!</t>
         </is>
       </c>
     </row>
     <row r="278" ht="18" customHeight="1">
       <c r="A278" s="1" t="inlineStr">
         <is>
-          <t>room.messages.you-lose</t>
+          <t>room.messages.confirm-leave</t>
         </is>
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>You lose</t>
+          <t>Are you sure you want to leave room?</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>Bạn đã thua</t>
+          <t>Bạn có chắc muốn rời bàn chơi?</t>
         </is>
       </c>
     </row>
     <row r="279" ht="18" customHeight="1">
       <c r="A279" s="1" t="inlineStr">
         <is>
-          <t>room.messages.back-to-room</t>
+          <t>room.messages.confirm-surrender</t>
         </is>
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>Back to room</t>
+          <t>Are you sure you want to surrender?</t>
         </is>
       </c>
       <c r="C279" s="2" t="inlineStr">
         <is>
-          <t>Quay lại phòng</t>
+          <t>Bạn có chắc chắn muốn đầu hàng không?</t>
         </is>
       </c>
     </row>
     <row r="280" ht="18" customHeight="1">
       <c r="A280" s="1" t="inlineStr">
         <is>
-          <t>room.messages.auto-back-countdown</t>
+          <t>room.messages.confirm-draw</t>
         </is>
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>{0}. Press the back button to return to the room. You will be automatically returned in {1}s</t>
+          <t>Are you sure you want to draw?</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>{0}. Bấm nút quay lại để quay lại room. Bạn sẽ tự động quay lại trong {1}s</t>
+          <t>Bạn có chắc chắn muốn hòa không?</t>
         </is>
       </c>
     </row>
     <row r="281" ht="18" customHeight="1">
       <c r="A281" s="1" t="inlineStr">
         <is>
-          <t>room.notifications.joined</t>
+          <t>room.messages.confirm-accept-draw</t>
         </is>
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>{0} joined the room</t>
+          <t>Opponent has proposed a draw. Do you accept?</t>
         </is>
       </c>
       <c r="C281" s="2" t="inlineStr">
         <is>
-          <t>{0} đã vào phòng</t>
+          <t>Đối phương đã chủ hòa, bạn có đồng ý không?</t>
         </is>
       </c>
     </row>
     <row r="282" ht="18" customHeight="1">
       <c r="A282" s="1" t="inlineStr">
         <is>
-          <t>room.notifications.left</t>
+          <t>room.messages.insufficient-amount</t>
         </is>
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>{0} left the room</t>
+          <t>You do not have enough balance to join this room</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>{0} đã rời phòng</t>
+          <t>Bạn không đủ tiền để tham gia bàn chơi này</t>
         </is>
       </c>
     </row>
     <row r="283" ht="18" customHeight="1">
       <c r="A283" s="1" t="inlineStr">
         <is>
-          <t>room.settings.title</t>
+          <t>room.messages.will-leave-current-room</t>
         </is>
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>Room Settings</t>
+          <t>You are currently in another room. Joining this room will remove you from the current room</t>
         </is>
       </c>
       <c r="C283" s="2" t="inlineStr">
         <is>
-          <t>Cài đặt phòng</t>
+          <t>Bạn đang ở trong một phòng khác. Tham gia phòng này sẽ loại bạn ra khỏi phòng hiện tại</t>
         </is>
       </c>
     </row>
     <row r="284" ht="18" customHeight="1">
       <c r="A284" s="1" t="inlineStr">
         <is>
-          <t>room.settings.room-name</t>
+          <t>room.messages.all-seats-occupied</t>
         </is>
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>Room name</t>
+          <t>All player seats are occupied</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>Tên phòng</t>
+          <t>Tất cả ghế chơi đã được chiếm</t>
         </is>
       </c>
     </row>
     <row r="285" ht="18" customHeight="1">
       <c r="A285" s="1" t="inlineStr">
         <is>
-          <t>room.settings.players</t>
+          <t>room.messages.game-ended</t>
         </is>
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>Spectators</t>
+          <t>Game ended</t>
         </is>
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>Người xem</t>
+          <t>Ván đấu đã kết thúc</t>
         </is>
       </c>
     </row>
     <row r="286" ht="18" customHeight="1">
       <c r="A286" s="1" t="inlineStr">
         <is>
-          <t>room.settings.save</t>
+          <t>room.messages.you-win</t>
         </is>
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>Save</t>
+          <t>You win</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>Lưu</t>
+          <t>Bạn đã chiến thắng</t>
         </is>
       </c>
     </row>
     <row r="287" ht="18" customHeight="1">
       <c r="A287" s="1" t="inlineStr">
         <is>
-          <t>room-invite.messages.title</t>
+          <t>room.messages.you-lose</t>
         </is>
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>Room Invitation</t>
+          <t>You lose</t>
         </is>
       </c>
       <c r="C287" s="2" t="inlineStr">
         <is>
-          <t>Lời mời vào phòng</t>
+          <t>Bạn đã thua</t>
         </is>
       </c>
     </row>
     <row r="288" ht="18" customHeight="1">
       <c r="A288" s="1" t="inlineStr">
         <is>
-          <t>start-game.messages.success</t>
+          <t>room.messages.back-to-room</t>
         </is>
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>Game started successfully</t>
+          <t>Back to room</t>
         </is>
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>Bắt đầu trò chơi thành công</t>
+          <t>Quay lại phòng</t>
         </is>
       </c>
     </row>
     <row r="289" ht="18" customHeight="1">
       <c r="A289" s="1" t="inlineStr">
         <is>
-          <t>start-game.messages.internal-server-error</t>
+          <t>room.messages.auto-back-countdown</t>
         </is>
       </c>
       <c r="B289" s="2" t="inlineStr">
         <is>
-          <t>Internal server error while starting game</t>
+          <t>{0}. Press the back button to return to the room. You will be automatically returned in {1}s</t>
         </is>
       </c>
       <c r="C289" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ khi bắt đầu trò chơi</t>
+          <t>{0}. Bấm nút quay lại để quay lại room. Bạn sẽ tự động quay lại trong {1}s</t>
         </is>
       </c>
     </row>
     <row r="290" ht="18" customHeight="1">
       <c r="A290" s="1" t="inlineStr">
         <is>
-          <t>start-game.messages.invalid-room-id</t>
+          <t>room.notifications.joined</t>
         </is>
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>Field 'id' is required and must be a positive integer</t>
+          <t>{0} joined the room</t>
         </is>
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
+          <t>{0} đã vào phòng</t>
         </is>
       </c>
     </row>
     <row r="291" ht="18" customHeight="1">
       <c r="A291" s="1" t="inlineStr">
         <is>
-          <t>start-game.messages.invalid-difficulty</t>
+          <t>room.notifications.left</t>
         </is>
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>Bot difficulty must be between 1 and 5</t>
+          <t>{0} left the room</t>
         </is>
       </c>
       <c r="C291" s="2" t="inlineStr">
         <is>
-          <t>Độ khó của bot phải từ 1 đến 5</t>
+          <t>{0} đã rời phòng</t>
         </is>
       </c>
     </row>
     <row r="292" ht="18" customHeight="1">
       <c r="A292" s="1" t="inlineStr">
         <is>
-          <t>start-game.messages.room-not-found</t>
+          <t>room.settings.title</t>
         </is>
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>Room not found</t>
+          <t>Room Settings</t>
         </is>
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy phòng</t>
+          <t>Cài đặt phòng</t>
         </is>
       </c>
     </row>
     <row r="293" ht="18" customHeight="1">
       <c r="A293" s="1" t="inlineStr">
         <is>
-          <t>start-game.messages.forbidden</t>
+          <t>room.settings.room-name</t>
         </is>
       </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t>Only the room host can start the game</t>
+          <t>Room name</t>
         </is>
       </c>
       <c r="C293" s="2" t="inlineStr">
         <is>
-          <t>Chỉ chủ phòng mới có thể bắt đầu trò chơi</t>
+          <t>Tên phòng</t>
         </is>
       </c>
     </row>
     <row r="294" ht="18" customHeight="1">
       <c r="A294" s="1" t="inlineStr">
         <is>
-          <t>start-game.messages.insufficient-amount</t>
+          <t>room.settings.players</t>
         </is>
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>You do not have enough balance to start a game with this bet</t>
+          <t>Spectators</t>
         </is>
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>Bạn không còn đủ amount để start room</t>
+          <t>Người xem</t>
         </is>
       </c>
     </row>
     <row r="295" ht="18" customHeight="1">
       <c r="A295" s="1" t="inlineStr">
         <is>
-          <t>start-game.messages.requester-must-pick-team</t>
+          <t>room.settings.save</t>
         </is>
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>You must select a team before starting a game with bot</t>
+          <t>Save</t>
         </is>
       </c>
       <c r="C295" s="2" t="inlineStr">
         <is>
-          <t>Bạn phải chọn team trước khi bắt đầu trò chơi với bot</t>
+          <t>Lưu</t>
         </is>
       </c>
     </row>
     <row r="296" ht="18" customHeight="1">
       <c r="A296" s="1" t="inlineStr">
         <is>
-          <t>update-room.messages.success</t>
+          <t>room-invite.messages.title</t>
         </is>
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>Room updated successfully</t>
+          <t>Room Invitation</t>
         </is>
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>Cập nhật phòng thành công</t>
+          <t>Lời mời vào phòng</t>
         </is>
       </c>
     </row>
     <row r="297" ht="18" customHeight="1">
       <c r="A297" s="1" t="inlineStr">
         <is>
-          <t>update-room.messages.internal-server-error</t>
+          <t>start-game.messages.success</t>
         </is>
       </c>
       <c r="B297" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Game started successfully</t>
         </is>
       </c>
       <c r="C297" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Bắt đầu trò chơi thành công</t>
         </is>
       </c>
     </row>
     <row r="298" ht="18" customHeight="1">
       <c r="A298" s="1" t="inlineStr">
         <is>
-          <t>update-room.messages.invalid-room-id</t>
+          <t>start-game.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>Invalid room ID</t>
+          <t>Internal server error while starting game</t>
         </is>
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>ID phòng không hợp lệ</t>
+          <t>Lỗi máy chủ nội bộ khi bắt đầu trò chơi</t>
         </is>
       </c>
     </row>
     <row r="299" ht="18" customHeight="1">
       <c r="A299" s="1" t="inlineStr">
         <is>
-          <t>update-room.messages.invalid-time-limit</t>
+          <t>start-game.messages.invalid-room-id</t>
         </is>
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
-          <t>Invalid time limit</t>
+          <t>Field 'id' is required and must be a positive integer</t>
         </is>
       </c>
       <c r="C299" s="2" t="inlineStr">
         <is>
-          <t>Thời gian không hợp lệ</t>
+          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
         </is>
       </c>
     </row>
     <row r="300" ht="18" customHeight="1">
       <c r="A300" s="1" t="inlineStr">
         <is>
-          <t>update-room.messages.name-required</t>
+          <t>start-game.messages.invalid-difficulty</t>
         </is>
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>Room name is required</t>
+          <t>Bot difficulty must be between 1 and 5</t>
         </is>
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>Tên phòng không được để trống</t>
+          <t>Độ khó của bot phải từ 1 đến 5</t>
         </is>
       </c>
     </row>
     <row r="301" ht="18" customHeight="1">
       <c r="A301" s="1" t="inlineStr">
         <is>
-          <t>update-room.messages.room-not-found</t>
+          <t>start-game.messages.room-not-found</t>
         </is>
       </c>
       <c r="B301" s="2" t="inlineStr">
@@ -5453,874 +5453,874 @@
     <row r="302" ht="18" customHeight="1">
       <c r="A302" s="1" t="inlineStr">
         <is>
-          <t>update-room.messages.forbidden</t>
+          <t>start-game.messages.forbidden</t>
         </is>
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>You are not the host of this room</t>
+          <t>Only the room host can start the game</t>
         </is>
       </c>
       <c r="C302" s="2" t="inlineStr">
         <is>
-          <t>Bạn không phải chủ phòng</t>
+          <t>Chỉ chủ phòng mới có thể bắt đầu trò chơi</t>
         </is>
       </c>
     </row>
     <row r="303" ht="18" customHeight="1">
       <c r="A303" s="1" t="inlineStr">
         <is>
-          <t>draw-game.messages.invalid-game-id</t>
+          <t>start-game.messages.insufficient-amount</t>
         </is>
       </c>
       <c r="B303" s="2" t="inlineStr">
         <is>
-          <t>Invalid game ID</t>
+          <t>You do not have enough balance to start a game with this bet</t>
         </is>
       </c>
       <c r="C303" s="2" t="inlineStr">
         <is>
-          <t>ID trò chơi không hợp lệ</t>
+          <t>Bạn không còn đủ amount để start room</t>
         </is>
       </c>
     </row>
     <row r="304" ht="18" customHeight="1">
       <c r="A304" s="1" t="inlineStr">
         <is>
-          <t>draw-game.messages.game-not-found</t>
+          <t>start-game.messages.requester-must-pick-team</t>
         </is>
       </c>
       <c r="B304" s="2" t="inlineStr">
         <is>
-          <t>Game not found</t>
+          <t>You must select a team before starting a game with bot</t>
         </is>
       </c>
       <c r="C304" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy trò chơi</t>
+          <t>Bạn phải chọn team trước khi bắt đầu trò chơi với bot</t>
         </is>
       </c>
     </row>
     <row r="305" ht="18" customHeight="1">
       <c r="A305" s="1" t="inlineStr">
         <is>
-          <t>draw-game.messages.forbidden</t>
+          <t>update-room.messages.success</t>
         </is>
       </c>
       <c r="B305" s="2" t="inlineStr">
         <is>
-          <t>You are not in this room</t>
+          <t>Room updated successfully</t>
         </is>
       </c>
       <c r="C305" s="2" t="inlineStr">
         <is>
-          <t>Bạn không có trong phòng này</t>
+          <t>Cập nhật phòng thành công</t>
         </is>
       </c>
     </row>
     <row r="306" ht="90" customHeight="1">
       <c r="A306" s="1" t="inlineStr">
         <is>
-          <t>draw-game.messages.game-history-not-found</t>
+          <t>update-room.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B306" s="2" t="inlineStr">
         <is>
-          <t>Game history not found</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C306" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy lịch sử trò chơi</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="307" ht="90" customHeight="1">
       <c r="A307" s="1" t="inlineStr">
         <is>
-          <t>draw-game.messages.game-already-finished</t>
+          <t>update-room.messages.invalid-room-id</t>
         </is>
       </c>
       <c r="B307" s="2" t="inlineStr">
         <is>
-          <t>Game is already finished</t>
+          <t>Invalid room ID</t>
         </is>
       </c>
       <c r="C307" s="2" t="inlineStr">
         <is>
-          <t>Trò chơi đã kết thúc</t>
+          <t>ID phòng không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="308" ht="18" customHeight="1">
       <c r="A308" s="1" t="inlineStr">
         <is>
-          <t>draw-game.messages.success</t>
+          <t>update-room.messages.invalid-time-limit</t>
         </is>
       </c>
       <c r="B308" s="2" t="inlineStr">
         <is>
-          <t>Draw game successfully</t>
+          <t>Invalid time limit</t>
         </is>
       </c>
       <c r="C308" s="2" t="inlineStr">
         <is>
-          <t>Hòa cờ thành công</t>
+          <t>Thời gian không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="309" ht="18" customHeight="1">
       <c r="A309" s="1" t="inlineStr">
         <is>
-          <t>draw-game.messages.internal-server-error</t>
+          <t>update-room.messages.name-required</t>
         </is>
       </c>
       <c r="B309" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Room name is required</t>
         </is>
       </c>
       <c r="C309" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Tên phòng không được để trống</t>
         </is>
       </c>
     </row>
     <row r="310" ht="18" customHeight="1">
       <c r="A310" s="1" t="inlineStr">
         <is>
-          <t>surrender.messages.game-already-finished</t>
+          <t>update-room.messages.room-not-found</t>
         </is>
       </c>
       <c r="B310" s="2" t="inlineStr">
         <is>
-          <t>Game is already finished</t>
+          <t>Room not found</t>
         </is>
       </c>
       <c r="C310" s="2" t="inlineStr">
         <is>
-          <t>Trò chơi đã kết thúc</t>
+          <t>Không tìm thấy phòng</t>
         </is>
       </c>
     </row>
     <row r="311" ht="18" customHeight="1">
       <c r="A311" s="2" t="inlineStr">
         <is>
-          <t>surrender.messages.game-history-not-found</t>
+          <t>update-room.messages.forbidden</t>
         </is>
       </c>
       <c r="B311" s="2" t="inlineStr">
         <is>
-          <t>Game history not found</t>
+          <t>You are not the host of this room</t>
         </is>
       </c>
       <c r="C311" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy lịch sử trò chơi</t>
+          <t>Bạn không phải chủ phòng</t>
         </is>
       </c>
     </row>
     <row r="312" ht="18" customHeight="1">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>surrender.messages.game-not-found</t>
+          <t>draw-game.messages.invalid-game-id</t>
         </is>
       </c>
       <c r="B312" s="2" t="inlineStr">
         <is>
-          <t>Game not found</t>
+          <t>Invalid game ID</t>
         </is>
       </c>
       <c r="C312" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy trò chơi</t>
+          <t>ID trò chơi không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="313" ht="18" customHeight="1">
       <c r="A313" s="2" t="inlineStr">
         <is>
-          <t>surrender.messages.internal-server-error</t>
+          <t>draw-game.messages.game-not-found</t>
         </is>
       </c>
       <c r="B313" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Game not found</t>
         </is>
       </c>
       <c r="C313" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Không tìm thấy trò chơi</t>
         </is>
       </c>
     </row>
     <row r="314" ht="18" customHeight="1">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>surrender.messages.invalid-game-id</t>
+          <t>draw-game.messages.forbidden</t>
         </is>
       </c>
       <c r="B314" s="2" t="inlineStr">
         <is>
-          <t>Invalid game ID</t>
+          <t>You are not in this room</t>
         </is>
       </c>
       <c r="C314" s="2" t="inlineStr">
         <is>
-          <t>ID trò chơi không hợp lệ</t>
+          <t>Bạn không có trong phòng này</t>
         </is>
       </c>
     </row>
     <row r="315" ht="54" customHeight="1">
       <c r="A315" s="2" t="inlineStr">
         <is>
-          <t>surrender.messages.invalid-surrender-player</t>
+          <t>draw-game.messages.game-history-not-found</t>
         </is>
       </c>
       <c r="B315" s="2" t="inlineStr">
         <is>
-          <t>You are not a player in this game</t>
+          <t>Game history not found</t>
         </is>
       </c>
       <c r="C315" s="2" t="inlineStr">
         <is>
-          <t>Bạn không phải là người chơi trong trò chơi này</t>
+          <t>Không tìm thấy lịch sử trò chơi</t>
         </is>
       </c>
     </row>
     <row r="316" ht="18" customHeight="1">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>surrender.messages.opponent-not-found</t>
+          <t>draw-game.messages.game-already-finished</t>
         </is>
       </c>
       <c r="B316" s="2" t="inlineStr">
         <is>
-          <t>Opponent not found</t>
+          <t>Game is already finished</t>
         </is>
       </c>
       <c r="C316" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy đối thủ</t>
+          <t>Trò chơi đã kết thúc</t>
         </is>
       </c>
     </row>
     <row r="317" ht="90" customHeight="1">
       <c r="A317" s="2" t="inlineStr">
         <is>
-          <t>surrender.messages.success</t>
+          <t>draw-game.messages.success</t>
         </is>
       </c>
       <c r="B317" s="2" t="inlineStr">
         <is>
-          <t>Surrendered</t>
+          <t>Draw game successfully</t>
         </is>
       </c>
       <c r="C317" s="2" t="inlineStr">
         <is>
-          <t>Đã đầu hàng</t>
+          <t>Hòa cờ thành công</t>
         </is>
       </c>
     </row>
     <row r="318" ht="18" customHeight="1">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>undo.messages.invalid-game-id</t>
+          <t>draw-game.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B318" s="2" t="inlineStr">
         <is>
-          <t>Invalid game ID</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C318" s="2" t="inlineStr">
         <is>
-          <t>ID trò chơi không hợp lệ</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="319" ht="36" customHeight="1">
       <c r="A319" s="2" t="inlineStr">
         <is>
-          <t>undo.messages.unauthorized</t>
+          <t>surrender.messages.game-already-finished</t>
         </is>
       </c>
       <c r="B319" s="2" t="inlineStr">
         <is>
-          <t>Unauthorized</t>
+          <t>Game is already finished</t>
         </is>
       </c>
       <c r="C319" s="2" t="inlineStr">
         <is>
-          <t>Không được phép truy cập</t>
+          <t>Trò chơi đã kết thúc</t>
         </is>
       </c>
     </row>
     <row r="320" ht="18" customHeight="1">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>undo.messages.game-not-found</t>
+          <t>surrender.messages.game-history-not-found</t>
         </is>
       </c>
       <c r="B320" s="2" t="inlineStr">
         <is>
-          <t>Game not found</t>
+          <t>Game history not found</t>
         </is>
       </c>
       <c r="C320" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy trò chơi</t>
+          <t>Không tìm thấy lịch sử trò chơi</t>
         </is>
       </c>
     </row>
     <row r="321" ht="72" customHeight="1">
       <c r="A321" s="2" t="inlineStr">
         <is>
-          <t>undo.messages.not-in-game</t>
+          <t>surrender.messages.game-not-found</t>
         </is>
       </c>
       <c r="B321" s="2" t="inlineStr">
         <is>
-          <t>You are not part of this game</t>
+          <t>Game not found</t>
         </is>
       </c>
       <c r="C321" s="2" t="inlineStr">
         <is>
-          <t>Bạn không phải là người chơi trong trò chơi này</t>
+          <t>Không tìm thấy trò chơi</t>
         </is>
       </c>
     </row>
     <row r="322" ht="18" customHeight="1">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>undo.messages.not-in-room</t>
+          <t>surrender.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B322" s="2" t="inlineStr">
         <is>
-          <t>You are not in this room</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C322" s="2" t="inlineStr">
         <is>
-          <t>Bạn không trong phòng này</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="323" ht="54" customHeight="1">
       <c r="A323" s="2" t="inlineStr">
         <is>
-          <t>undo.messages.spectator-cannot-undo</t>
+          <t>surrender.messages.invalid-game-id</t>
         </is>
       </c>
       <c r="B323" s="2" t="inlineStr">
         <is>
-          <t>Spectators cannot undo moves</t>
+          <t>Invalid game ID</t>
         </is>
       </c>
       <c r="C323" s="2" t="inlineStr">
         <is>
-          <t>Người xem không thể hoàn tác nước đi</t>
+          <t>ID trò chơi không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="324" ht="18" customHeight="1">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>undo.messages.no-moves</t>
+          <t>surrender.messages.invalid-surrender-player</t>
         </is>
       </c>
       <c r="B324" s="2" t="inlineStr">
         <is>
-          <t>No moves to undo</t>
+          <t>You are not a player in this game</t>
         </is>
       </c>
       <c r="C324" s="2" t="inlineStr">
         <is>
-          <t>Không có nước đi để hoàn tác</t>
+          <t>Bạn không phải là người chơi trong trò chơi này</t>
         </is>
       </c>
     </row>
     <row r="325" ht="72" customHeight="1">
       <c r="A325" s="2" t="inlineStr">
         <is>
-          <t>undo.messages.delete-failed</t>
+          <t>surrender.messages.opponent-not-found</t>
         </is>
       </c>
       <c r="B325" s="2" t="inlineStr">
         <is>
-          <t>Failed to undo move</t>
+          <t>Opponent not found</t>
         </is>
       </c>
       <c r="C325" s="2" t="inlineStr">
         <is>
-          <t>Không thể hoàn tác nước đi</t>
+          <t>Không tìm thấy đối thủ</t>
         </is>
       </c>
     </row>
     <row r="326" ht="18" customHeight="1">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>undo.messages.undo-limit-exceeded</t>
+          <t>surrender.messages.success</t>
         </is>
       </c>
       <c r="B326" s="2" t="inlineStr">
         <is>
-          <t>Maximum 3 undo per game exceeded</t>
+          <t>Surrendered</t>
         </is>
       </c>
       <c r="C326" s="2" t="inlineStr">
         <is>
-          <t>Đã đạt tối đa 3 lần hoàn tác trong trò chơi</t>
+          <t>Đã đầu hàng</t>
         </is>
       </c>
     </row>
     <row r="327" ht="90" customHeight="1">
       <c r="A327" s="2" t="inlineStr">
         <is>
-          <t>undo.messages.success</t>
+          <t>undo.messages.invalid-game-id</t>
         </is>
       </c>
       <c r="B327" s="2" t="inlineStr">
         <is>
-          <t>Move undone successfully</t>
+          <t>Invalid game ID</t>
         </is>
       </c>
       <c r="C327" s="2" t="inlineStr">
         <is>
-          <t>Hoàn tác nước đi thành công</t>
+          <t>ID trò chơi không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="328" ht="18" customHeight="1">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>undo.messages.internal-server-error</t>
+          <t>undo.messages.unauthorized</t>
         </is>
       </c>
       <c r="B328" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Unauthorized</t>
         </is>
       </c>
       <c r="C328" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Không được phép truy cập</t>
         </is>
       </c>
     </row>
     <row r="329" ht="72" customHeight="1">
       <c r="A329" s="2" t="inlineStr">
         <is>
-          <t>player-history.messages.invalid-user-id</t>
+          <t>undo.messages.game-not-found</t>
         </is>
       </c>
       <c r="B329" s="2" t="inlineStr">
         <is>
-          <t>Invalid user ID</t>
+          <t>Game not found</t>
         </is>
       </c>
       <c r="C329" s="2" t="inlineStr">
         <is>
-          <t>ID người dùng không hợp lệ</t>
+          <t>Không tìm thấy trò chơi</t>
         </is>
       </c>
     </row>
     <row r="330" ht="54" customHeight="1">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>player-history.messages.success</t>
+          <t>undo.messages.not-in-game</t>
         </is>
       </c>
       <c r="B330" s="2" t="inlineStr">
         <is>
-          <t>Fetch game history successfully</t>
+          <t>You are not part of this game</t>
         </is>
       </c>
       <c r="C330" s="2" t="inlineStr">
         <is>
-          <t>Lấy lịch sử trò chơi thành công</t>
+          <t>Bạn không phải là người chơi trong trò chơi này</t>
         </is>
       </c>
     </row>
     <row r="331" ht="54" customHeight="1">
       <c r="A331" s="2" t="inlineStr">
         <is>
-          <t>validate-token.messages.success</t>
+          <t>undo.messages.not-in-room</t>
         </is>
       </c>
       <c r="B331" s="2" t="inlineStr">
         <is>
-          <t>Token is valid</t>
+          <t>You are not in this room</t>
         </is>
       </c>
       <c r="C331" s="2" t="inlineStr">
         <is>
-          <t>Token hợp lệ</t>
+          <t>Bạn không trong phòng này</t>
         </is>
       </c>
     </row>
     <row r="332" ht="54" customHeight="1">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>guide.section.objective</t>
+          <t>undo.messages.spectator-cannot-undo</t>
         </is>
       </c>
       <c r="B332" s="2" t="inlineStr">
         <is>
-          <t>Objective of the game</t>
+          <t>Spectators cannot undo moves</t>
         </is>
       </c>
       <c r="C332" s="2" t="inlineStr">
         <is>
-          <t>Mục tiêu của trò chơi</t>
+          <t>Người xem không thể hoàn tác nước đi</t>
         </is>
       </c>
     </row>
     <row r="333" ht="90" customHeight="1">
       <c r="A333" s="2" t="inlineStr">
         <is>
-          <t>guide.section.pieces</t>
+          <t>undo.messages.no-moves</t>
         </is>
       </c>
       <c r="B333" s="2" t="inlineStr">
         <is>
-          <t>Pieces</t>
+          <t>No moves to undo</t>
         </is>
       </c>
       <c r="C333" s="2" t="inlineStr">
         <is>
-          <t>Quân cờ</t>
+          <t>Không có nước đi để hoàn tác</t>
         </is>
       </c>
     </row>
     <row r="334" ht="54" customHeight="1">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>guide.section.moving-pieces</t>
+          <t>undo.messages.delete-failed</t>
         </is>
       </c>
       <c r="B334" s="2" t="inlineStr">
         <is>
-          <t>Moving pieces</t>
+          <t>Failed to undo move</t>
         </is>
       </c>
       <c r="C334" s="2" t="inlineStr">
         <is>
-          <t>Đi quân</t>
+          <t>Không thể hoàn tác nước đi</t>
         </is>
       </c>
     </row>
     <row r="335" ht="36" customHeight="1">
       <c r="A335" s="2" t="inlineStr">
         <is>
-          <t>guide.section.capturing</t>
+          <t>undo.messages.undo-limit-exceeded</t>
         </is>
       </c>
       <c r="B335" s="2" t="inlineStr">
         <is>
-          <t>Capturing</t>
+          <t>Maximum 3 undo per game exceeded</t>
         </is>
       </c>
       <c r="C335" s="2" t="inlineStr">
         <is>
-          <t>Bắt quân</t>
+          <t>Đã đạt tối đa 3 lần hoàn tác trong trò chơi</t>
         </is>
       </c>
     </row>
     <row r="336" ht="18" customHeight="1">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>guide.section.check</t>
+          <t>undo.messages.success</t>
         </is>
       </c>
       <c r="B336" s="2" t="inlineStr">
         <is>
-          <t>Check</t>
+          <t>Move undone successfully</t>
         </is>
       </c>
       <c r="C336" s="2" t="inlineStr">
         <is>
-          <t>Chiếu tướng</t>
+          <t>Hoàn tác nước đi thành công</t>
         </is>
       </c>
     </row>
     <row r="337" ht="36" customHeight="1">
       <c r="A337" s="2" t="inlineStr">
         <is>
-          <t>guide.section.result</t>
+          <t>undo.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B337" s="2" t="inlineStr">
         <is>
-          <t>Result</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C337" s="2" t="inlineStr">
         <is>
-          <t>Kết quả</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="338" ht="36" customHeight="1">
       <c r="A338" s="2" t="inlineStr">
         <is>
-          <t>guide.table.piece</t>
+          <t>player-history.messages.invalid-user-id</t>
         </is>
       </c>
       <c r="B338" s="2" t="inlineStr">
         <is>
-          <t>Piece</t>
+          <t>Invalid user ID</t>
         </is>
       </c>
       <c r="C338" s="2" t="inlineStr">
         <is>
-          <t>Quân</t>
+          <t>ID người dùng không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="339" ht="72" customHeight="1">
       <c r="A339" s="2" t="inlineStr">
         <is>
-          <t>guide.table.symbol</t>
+          <t>player-history.messages.success</t>
         </is>
       </c>
       <c r="B339" s="2" t="inlineStr">
         <is>
-          <t>Symbol</t>
+          <t>Fetch game history successfully</t>
         </is>
       </c>
       <c r="C339" s="2" t="inlineStr">
         <is>
-          <t>Ký hiệu</t>
+          <t>Lấy lịch sử trò chơi thành công</t>
         </is>
       </c>
     </row>
     <row r="340" ht="54" customHeight="1">
       <c r="A340" s="2" t="inlineStr">
         <is>
-          <t>guide.table.quantity</t>
+          <t>validate-token.messages.success</t>
         </is>
       </c>
       <c r="B340" s="2" t="inlineStr">
         <is>
-          <t>Quantity</t>
+          <t>Token is valid</t>
         </is>
       </c>
       <c r="C340" s="2" t="inlineStr">
         <is>
-          <t>Số lượng</t>
+          <t>Token hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="341" ht="54" customHeight="1">
       <c r="A341" s="2" t="inlineStr">
         <is>
-          <t>guide.objective.paragraph1</t>
+          <t>guide.section.objective</t>
         </is>
       </c>
       <c r="B341" s="2" t="inlineStr">
         <is>
-          <t>A match is played between two players: one controls the Red pieces, and the other controls the Black pieces. The objective of each player is to use their pieces on the board to &lt;b&gt;checkmate&lt;/b&gt; the opponent's General, and win the game.</t>
+          <t>Objective of the game</t>
         </is>
       </c>
       <c r="C341" s="2" t="inlineStr">
         <is>
-          <t>Ván cờ được tiến hành giữa 2 đấu thủ, một người cầm Quân Đỏ, một người cầm Quân Đen. Mục đích của mỗi đấu thủ là tìm mọi cách sử dụng các quân trên bàn cờ để &lt;b&gt;chiếu bí Tướng&lt;/b&gt; của đối phương, giành thắng lợi.</t>
+          <t>Mục tiêu của trò chơi</t>
         </is>
       </c>
     </row>
     <row r="342" ht="90" customHeight="1">
       <c r="A342" s="2" t="inlineStr">
         <is>
-          <t>guide.pieces.paragraph1</t>
+          <t>guide.section.pieces</t>
         </is>
       </c>
       <c r="B342" s="2" t="inlineStr">
         <is>
-          <t>At the start of each game, there must be 32 pieces in total, consisting of &lt;b&gt;7 piece types&lt;/b&gt; split evenly between both sides: 16 Red pieces and 16 Black pieces. The 7 piece types with their symbols and quantities are as follows:</t>
+          <t>Pieces</t>
         </is>
       </c>
       <c r="C342" s="2" t="inlineStr">
         <is>
-          <t>Mỗi ván cờ lúc bắt đầu phải có đủ 32 quân, gồm 7 loại chia đều cho mỗi bên gồm 16 quân Đỏ và 16 quân Đen. &lt;b&gt;7 loại quân&lt;/b&gt; có ký hiệu và số lượng như sau:</t>
+          <t>Quân cờ</t>
         </is>
       </c>
     </row>
     <row r="343" ht="54" customHeight="1">
       <c r="A343" s="2" t="inlineStr">
         <is>
-          <t>guide.piece.general</t>
+          <t>guide.section.moving-pieces</t>
         </is>
       </c>
       <c r="B343" s="2" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Moving pieces</t>
         </is>
       </c>
       <c r="C343" s="2" t="inlineStr">
         <is>
-          <t>Tướng</t>
+          <t>Đi quân</t>
         </is>
       </c>
     </row>
     <row r="344" ht="18" customHeight="1">
       <c r="A344" s="2" t="inlineStr">
         <is>
-          <t>guide.piece.advisor</t>
+          <t>guide.section.capturing</t>
         </is>
       </c>
       <c r="B344" s="2" t="inlineStr">
         <is>
-          <t>Advisor</t>
+          <t>Capturing</t>
         </is>
       </c>
       <c r="C344" s="2" t="inlineStr">
         <is>
-          <t>Sĩ</t>
+          <t>Bắt quân</t>
         </is>
       </c>
     </row>
     <row r="345" ht="18" customHeight="1">
       <c r="A345" s="2" t="inlineStr">
         <is>
-          <t>guide.piece.elephant</t>
+          <t>guide.section.check</t>
         </is>
       </c>
       <c r="B345" s="2" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Check</t>
         </is>
       </c>
       <c r="C345" s="2" t="inlineStr">
         <is>
-          <t>Tượng</t>
+          <t>Chiếu tướng</t>
         </is>
       </c>
     </row>
     <row r="346" ht="36" customHeight="1">
       <c r="A346" s="2" t="inlineStr">
         <is>
-          <t>guide.piece.chariot</t>
+          <t>guide.section.result</t>
         </is>
       </c>
       <c r="B346" s="2" t="inlineStr">
         <is>
-          <t>Chariot</t>
+          <t>Result</t>
         </is>
       </c>
       <c r="C346" s="2" t="inlineStr">
         <is>
-          <t>Xe</t>
+          <t>Kết quả</t>
         </is>
       </c>
     </row>
     <row r="347" ht="18" customHeight="1">
       <c r="A347" s="2" t="inlineStr">
         <is>
-          <t>guide.piece.horse</t>
+          <t>guide.table.piece</t>
         </is>
       </c>
       <c r="B347" s="2" t="inlineStr">
         <is>
-          <t>Horse</t>
+          <t>Piece</t>
         </is>
       </c>
       <c r="C347" s="2" t="inlineStr">
         <is>
-          <t>Mã</t>
+          <t>Quân</t>
         </is>
       </c>
     </row>
     <row r="348" ht="18" customHeight="1">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>guide.piece.cannon</t>
+          <t>guide.table.symbol</t>
         </is>
       </c>
       <c r="B348" s="2" t="inlineStr">
         <is>
-          <t>Cannon</t>
+          <t>Symbol</t>
         </is>
       </c>
       <c r="C348" s="2" t="inlineStr">
         <is>
-          <t>Pháo</t>
+          <t>Ký hiệu</t>
         </is>
       </c>
     </row>
     <row r="349" ht="36" customHeight="1">
       <c r="A349" s="2" t="inlineStr">
         <is>
-          <t>guide.piece.soldier</t>
+          <t>guide.table.quantity</t>
         </is>
       </c>
       <c r="B349" s="2" t="inlineStr">
         <is>
-          <t>Soldier</t>
+          <t>Quantity</t>
         </is>
       </c>
       <c r="C349" s="2" t="inlineStr">
         <is>
-          <t>Tốt</t>
+          <t>Số lượng</t>
         </is>
       </c>
     </row>
     <row r="350" ht="18" customHeight="1">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>guide.moving-pieces.paragraph1</t>
+          <t>guide.objective.paragraph1</t>
         </is>
       </c>
       <c r="B350" s="2" t="inlineStr">
         <is>
-          <t>On each turn, each side may move only one of its own pieces according to the rules. The movement rules are as follows:</t>
+          <t>A match is played between two players: one controls the Red pieces, and the other controls the Black pieces. The objective of each player is to use their pieces on the board to &lt;b&gt;checkmate&lt;/b&gt; the opponent's General, and win the game.</t>
         </is>
       </c>
       <c r="C350" s="2" t="inlineStr">
         <is>
-          <t>Mỗi nước đi, mỗi bên chỉ được di chuyển quân của mình theo đúng quy định. Quy định di chuyển của các quân như sau:</t>
+          <t>Ván cờ được tiến hành giữa 2 đấu thủ, một người cầm Quân Đỏ, một người cầm Quân Đen. Mục đích của mỗi đấu thủ là tìm mọi cách sử dụng các quân trên bàn cờ để &lt;b&gt;chiếu bí Tướng&lt;/b&gt; của đối phương, giành thắng lợi.</t>
         </is>
       </c>
     </row>
     <row r="351" ht="36" customHeight="1">
       <c r="A351" s="2" t="inlineStr">
         <is>
-          <t>guide.general.paragraph1</t>
+          <t>guide.pieces.paragraph1</t>
         </is>
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>At the start of each game, there must be 32 pieces in total, consisting of &lt;b&gt;7 piece types&lt;/b&gt; split evenly between both sides: 16 Red pieces and 16 Black pieces. The 7 piece types with their symbols and quantities are as follows:</t>
         </is>
       </c>
       <c r="C351" s="2" t="inlineStr">
         <is>
-          <t>Tướng</t>
+          <t>Mỗi ván cờ lúc bắt đầu phải có đủ 32 quân, gồm 7 loại chia đều cho mỗi bên gồm 16 quân Đỏ và 16 quân Đen. &lt;b&gt;7 loại quân&lt;/b&gt; có ký hiệu và số lượng như sau:</t>
         </is>
       </c>
     </row>
     <row r="352" ht="18" customHeight="1">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>guide.general.paragraph2</t>
+          <t>guide.piece.general</t>
         </is>
       </c>
       <c r="B352" s="2" t="inlineStr">
         <is>
-          <t>Moves one step &lt;b&gt;horizontally or vertically&lt;/b&gt; within the palace. The two Generals may not face each other directly on the same file. If they are facing each other, there must be at least one piece of either side placed between them.</t>
+          <t>General</t>
         </is>
       </c>
       <c r="C352" s="2" t="inlineStr">
         <is>
-          <t>Mỗi nước được đi một bước &lt;b&gt;ngang hoặc dọc&lt;/b&gt; tùy ý trong cung Tướng. Hai tướng của 2 bên không được đối mặt nhau trực tiếp trên cùng một đường thẳng. Nếu đối mặt, bắt buộc phải có quân của bất kỳ bên nào đứng che mặt.</t>
+          <t>Tướng</t>
         </is>
       </c>
     </row>
     <row r="353" ht="18" customHeight="1">
       <c r="A353" s="2" t="inlineStr">
         <is>
-          <t>guide.advisor.paragraph1</t>
+          <t>guide.piece.advisor</t>
         </is>
       </c>
       <c r="B353" s="2" t="inlineStr">
@@ -6337,1084 +6337,1192 @@
     <row r="354" ht="18" customHeight="1">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>guide.advisor.paragraph2</t>
+          <t>guide.piece.elephant</t>
         </is>
       </c>
       <c r="B354" s="2" t="inlineStr">
         <is>
-          <t>Moves one step &lt;b&gt;diagonally&lt;/b&gt; within the palace.</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="C354" s="2" t="inlineStr">
         <is>
-          <t>Mỗi nước &lt;b&gt;đi chéo một bước&lt;/b&gt; trong cung Tướng.</t>
+          <t>Tượng</t>
         </is>
       </c>
     </row>
     <row r="355" ht="18" customHeight="1">
       <c r="A355" s="2" t="inlineStr">
         <is>
-          <t>guide.elephant.paragraph1</t>
+          <t>guide.piece.chariot</t>
         </is>
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Chariot</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
         <is>
-          <t>Tượng</t>
+          <t>Xe</t>
         </is>
       </c>
     </row>
     <row r="356" ht="18" customHeight="1">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>guide.elephant.paragraph2</t>
+          <t>guide.piece.horse</t>
         </is>
       </c>
       <c r="B356" s="2" t="inlineStr">
         <is>
-          <t>Moves &lt;b&gt;two steps diagonally&lt;/b&gt; on its own side of the board and may not cross the river. If there is another piece on the midpoint of that diagonal path, the Elephant is blocked and cannot move.</t>
+          <t>Horse</t>
         </is>
       </c>
       <c r="C356" s="2" t="inlineStr">
         <is>
-          <t>Mỗi nước &lt;b&gt;đi chéo hai bước&lt;/b&gt; tại trận địa bên mình, không được qua sông. Nếu ở giữa đường chéo đó có quân khác đứng thì quân Tượng bị cản, không đi được.</t>
+          <t>Mã</t>
         </is>
       </c>
     </row>
     <row r="357" ht="17" customHeight="1">
       <c r="A357" s="2" t="inlineStr">
         <is>
-          <t>guide.chariot.paragraph1</t>
+          <t>guide.piece.cannon</t>
         </is>
       </c>
       <c r="B357" s="2" t="inlineStr">
         <is>
-          <t>Chariot</t>
+          <t>Cannon</t>
         </is>
       </c>
       <c r="C357" s="2" t="inlineStr">
         <is>
-          <t>Xe</t>
+          <t>Pháo</t>
         </is>
       </c>
     </row>
     <row r="358" ht="18" customHeight="1">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>guide.chariot.paragraph2</t>
+          <t>guide.piece.soldier</t>
         </is>
       </c>
       <c r="B358" s="2" t="inlineStr">
         <is>
-          <t>Moves &lt;b&gt;horizontally or vertically&lt;/b&gt; with no limit on distance, as long as no piece blocks the path.</t>
+          <t>Soldier</t>
         </is>
       </c>
       <c r="C358" s="2" t="inlineStr">
         <is>
-          <t>Mỗi nước được &lt;b&gt;đi dọc hoặc đi ngang&lt;/b&gt;, không hạn chế số bước đi nếu không có quân khác cản đường.</t>
+          <t>Tốt</t>
         </is>
       </c>
     </row>
     <row r="359" ht="18" customHeight="1">
       <c r="A359" s="2" t="inlineStr">
         <is>
-          <t>guide.horse.paragraph1</t>
+          <t>guide.moving-pieces.paragraph1</t>
         </is>
       </c>
       <c r="B359" s="2" t="inlineStr">
         <is>
-          <t>Horse</t>
+          <t>On each turn, each side may move only one of its own pieces according to the rules. The movement rules are as follows:</t>
         </is>
       </c>
       <c r="C359" s="2" t="inlineStr">
         <is>
-          <t>Mã</t>
+          <t>Mỗi nước đi, mỗi bên chỉ được di chuyển quân của mình theo đúng quy định. Quy định di chuyển của các quân như sau:</t>
         </is>
       </c>
     </row>
     <row r="360" ht="18" customHeight="1">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>guide.horse.paragraph2</t>
+          <t>guide.general.paragraph1</t>
         </is>
       </c>
       <c r="B360" s="2" t="inlineStr">
         <is>
-          <t>Moves in an &lt;b&gt;L-shape&lt;/b&gt; (one step orthogonally then one step diagonally outward). If the adjacent orthogonal point is occupied by any piece, the Horse is blocked and cannot move.</t>
+          <t>General</t>
         </is>
       </c>
       <c r="C360" s="2" t="inlineStr">
         <is>
-          <t>Đi theo &lt;b&gt;đường chéo hình chữ nhật&lt;/b&gt; của hai ô vuông liền nhau. Nếu giao điểm liền kề bước thẳng dọc ngang có một quân khác đứng thì Mã bị cản, không đi được.</t>
+          <t>Tướng</t>
         </is>
       </c>
     </row>
     <row r="361" ht="18" customHeight="1">
       <c r="A361" s="2" t="inlineStr">
         <is>
-          <t>guide.cannon.paragraph1</t>
+          <t>guide.general.paragraph2</t>
         </is>
       </c>
       <c r="B361" s="2" t="inlineStr">
         <is>
-          <t>Cannon</t>
+          <t>Moves one step &lt;b&gt;horizontally or vertically&lt;/b&gt; within the palace. The two Generals may not face each other directly on the same file. If they are facing each other, there must be at least one piece of either side placed between them.</t>
         </is>
       </c>
       <c r="C361" s="2" t="inlineStr">
         <is>
-          <t>Pháo</t>
+          <t>Mỗi nước được đi một bước &lt;b&gt;ngang hoặc dọc&lt;/b&gt; tùy ý trong cung Tướng. Hai tướng của 2 bên không được đối mặt nhau trực tiếp trên cùng một đường thẳng. Nếu đối mặt, bắt buộc phải có quân của bất kỳ bên nào đứng che mặt.</t>
         </is>
       </c>
     </row>
     <row r="362" ht="18" customHeight="1">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>guide.cannon.paragraph2</t>
+          <t>guide.advisor.paragraph1</t>
         </is>
       </c>
       <c r="B362" s="2" t="inlineStr">
         <is>
-          <t>Moves &lt;b&gt;horizontally or vertically&lt;/b&gt; like a Chariot when not capturing. To capture, it must &lt;b&gt;jump over exactly one piece&lt;/b&gt; to reach its target. If there are zero or more than one pieces between the Cannon and the target, it cannot capture.</t>
+          <t>Advisor</t>
         </is>
       </c>
       <c r="C362" s="2" t="inlineStr">
         <is>
-          <t>Đi ngang hoặc dọc giống Xe khi không bắt quân. Để bắt quân, nó phải &lt;b&gt;nhảy qua đúng một quân khác&lt;/b&gt; để đến mục tiêu. Nếu không có hoặc có nhiều hơn một quân giữa Pháo và mục tiêu, nó không thể bắt quân.</t>
+          <t>Sĩ</t>
         </is>
       </c>
     </row>
     <row r="363" ht="18" customHeight="1">
       <c r="A363" s="2" t="inlineStr">
         <is>
-          <t>guide.soldier.paragraph1</t>
+          <t>guide.advisor.paragraph2</t>
         </is>
       </c>
       <c r="B363" s="2" t="inlineStr">
         <is>
-          <t>Soldier</t>
+          <t>Moves one step &lt;b&gt;diagonally&lt;/b&gt; within the palace.</t>
         </is>
       </c>
       <c r="C363" s="2" t="inlineStr">
         <is>
-          <t>Tốt</t>
+          <t>Mỗi nước &lt;b&gt;đi chéo một bước&lt;/b&gt; trong cung Tướng.</t>
         </is>
       </c>
     </row>
     <row r="364" ht="17" customHeight="1">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>guide.soldier.paragraph2</t>
+          <t>guide.elephant.paragraph1</t>
         </is>
       </c>
       <c r="B364" s="2" t="inlineStr">
         <is>
-          <t>Moves &lt;b&gt;one step&lt;/b&gt; each turn. Before crossing the river, it can only move forward. After crossing the river, it may move &lt;b&gt;forward or sideways&lt;/b&gt;, but never backward.</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="C364" s="2" t="inlineStr">
         <is>
-          <t>Mỗi nước đi &lt;b&gt;một bước&lt;/b&gt;. Khi chưa qua sông, Tốt chỉ được tiến. Khi Tốt đã qua sông được quyền &lt;b&gt;đi tiến và đi ngang&lt;/b&gt;, không được phép lùi.</t>
+          <t>Tượng</t>
         </is>
       </c>
     </row>
     <row r="365" ht="17" customHeight="1">
       <c r="A365" s="2" t="inlineStr">
         <is>
-          <t>guide.capturing.paragraph1</t>
+          <t>guide.elephant.paragraph2</t>
         </is>
       </c>
       <c r="B365" s="2" t="inlineStr">
         <is>
-          <t>When a piece moves to an intersection occupied by an opponent's piece, it may &lt;b&gt;capture that piece&lt;/b&gt; and occupy its position.</t>
+          <t>Moves &lt;b&gt;two steps diagonally&lt;/b&gt; on its own side of the board and may not cross the river. If there is another piece on the midpoint of that diagonal path, the Elephant is blocked and cannot move.</t>
         </is>
       </c>
       <c r="C365" s="2" t="inlineStr">
         <is>
-          <t>Khi một quân đi tới một giao điểm khác đã có quân đối phương đứng thì được quyền &lt;b&gt;bắt quân đó&lt;/b&gt;, đồng thời chiếm giữ vị trí quân bị bắt.</t>
+          <t>Mỗi nước &lt;b&gt;đi chéo hai bước&lt;/b&gt; tại trận địa bên mình, không được qua sông. Nếu ở giữa đường chéo đó có quân khác đứng thì quân Tượng bị cản, không đi được.</t>
         </is>
       </c>
     </row>
     <row r="366" ht="17" customHeight="1">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>guide.capturing.paragraph2</t>
+          <t>guide.chariot.paragraph1</t>
         </is>
       </c>
       <c r="B366" s="2" t="inlineStr">
         <is>
-          <t>You may not capture your own pieces. You may sacrifice your own pieces to be captured by the opponent, &lt;b&gt;except for the General&lt;/b&gt;.</t>
+          <t>Chariot</t>
         </is>
       </c>
       <c r="C366" s="2" t="inlineStr">
         <is>
-          <t>Không được bắt quân bên mình. Được phép cho đối phương bắt đầu quân mình chủ động hiến mình cho đối phương, &lt;b&gt;trừ Tướng&lt;/b&gt;.</t>
+          <t>Xe</t>
         </is>
       </c>
     </row>
     <row r="367" ht="17" customHeight="1">
       <c r="A367" s="2" t="inlineStr">
         <is>
-          <t>guide.capturing.paragraph3</t>
+          <t>guide.chariot.paragraph2</t>
         </is>
       </c>
       <c r="B367" s="2" t="inlineStr">
         <is>
-          <t>A captured piece is removed from the board. &lt;b&gt;Chasing one piece for more than 6 consecutive moves is not allowed&lt;/b&gt;.</t>
+          <t>Moves &lt;b&gt;horizontally or vertically&lt;/b&gt; with no limit on distance, as long as no piece blocks the path.</t>
         </is>
       </c>
       <c r="C367" s="2" t="inlineStr">
         <is>
-          <t>Quân bị bắt phải bị loại và bị nhấc ra khỏi bàn cờ. &lt;b&gt;Không được đuổi 1 quân quá 6 nước cờ liên tiếp&lt;/b&gt;.</t>
+          <t>Mỗi nước được &lt;b&gt;đi dọc hoặc đi ngang&lt;/b&gt;, không hạn chế số bước đi nếu không có quân khác cản đường.</t>
         </is>
       </c>
     </row>
     <row r="368" ht="17" customHeight="1">
       <c r="A368" s="2" t="inlineStr">
         <is>
-          <t>guide.check.paragraph1</t>
+          <t>guide.horse.paragraph1</t>
         </is>
       </c>
       <c r="B368" s="2" t="inlineStr">
         <is>
-          <t>If a player makes a move that threatens to capture the opponent's General on the next move (by the same piece or another piece), it is called a &lt;b&gt;Check&lt;/b&gt;. The checked side must respond to avoid check. Otherwise, that side loses</t>
+          <t>Horse</t>
         </is>
       </c>
       <c r="C368" s="2" t="inlineStr">
         <is>
-          <t>Nếu người chơi thực hiện một nước đi đe dọa bắt Tướng của đối phương ở nước đi tiếp theo (bằng chính quân cờ đó hoặc một quân cờ khác), thì đó được gọi là &lt;b&gt;Chiếu&lt;/b&gt;. Bên bị chiếu phải đáp trả để tránh bị chiếu. Nếu không sẽ bị xử thua</t>
+          <t>Mã</t>
         </is>
       </c>
     </row>
     <row r="369" ht="17" customHeight="1">
       <c r="A369" s="2" t="inlineStr">
         <is>
-          <t>guide.check.paragraph2</t>
+          <t>guide.horse.paragraph2</t>
         </is>
       </c>
       <c r="B369" s="2" t="inlineStr">
         <is>
-          <t>When the General is checked from any direction (including from behind), the checked side may respond in one of the following ways:</t>
+          <t>Moves in an &lt;b&gt;L-shape&lt;/b&gt; (one step orthogonally then one step diagonally outward). If the adjacent orthogonal point is occupied by any piece, the Horse is blocked and cannot move.</t>
         </is>
       </c>
       <c r="C369" s="2" t="inlineStr">
         <is>
-          <t>Tướng bị chiếu từ cả bốn hướng (bị chiếu cả từ phía sau) có thể ứng phó với nước chiếu tướng bằng một trong các cách sau:</t>
+          <t>Đi theo &lt;b&gt;đường chéo hình chữ nhật&lt;/b&gt; của hai ô vuông liền nhau. Nếu giao điểm liền kề bước thẳng dọc ngang có một quân khác đứng thì Mã bị cản, không đi được.</t>
         </is>
       </c>
     </row>
     <row r="370" ht="17" customHeight="1">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>guide.check.paragraph3</t>
+          <t>guide.cannon.paragraph1</t>
         </is>
       </c>
       <c r="B370" s="2" t="inlineStr">
         <is>
-          <t>Move the General to another position to escape check</t>
+          <t>Cannon</t>
         </is>
       </c>
       <c r="C370" s="2" t="inlineStr">
         <is>
-          <t>Di chuyển tướng sang vị trí khác để tránh nước chiếu</t>
+          <t>Pháo</t>
         </is>
       </c>
     </row>
     <row r="371" ht="17" customHeight="1">
       <c r="A371" s="2" t="inlineStr">
         <is>
-          <t>guide.check.paragraph4</t>
+          <t>guide.cannon.paragraph2</t>
         </is>
       </c>
       <c r="B371" s="2" t="inlineStr">
         <is>
-          <t>Capture the checking piece</t>
+          <t>Moves &lt;b&gt;horizontally or vertically&lt;/b&gt; like a Chariot when not capturing. To capture, it must &lt;b&gt;jump over exactly one piece&lt;/b&gt; to reach its target. If there are zero or more than one pieces between the Cannon and the target, it cannot capture.</t>
         </is>
       </c>
       <c r="C371" s="2" t="inlineStr">
         <is>
-          <t>Bắt quân đang chiếu</t>
+          <t>Đi ngang hoặc dọc giống Xe khi không bắt quân. Để bắt quân, nó phải &lt;b&gt;nhảy qua đúng một quân khác&lt;/b&gt; để đến mục tiêu. Nếu không có hoặc có nhiều hơn một quân giữa Pháo và mục tiêu, nó không thể bắt quân.</t>
         </is>
       </c>
     </row>
     <row r="372" ht="17" customHeight="1">
       <c r="A372" s="2" t="inlineStr">
         <is>
-          <t>guide.check.paragraph5</t>
+          <t>guide.soldier.paragraph1</t>
         </is>
       </c>
       <c r="B372" s="2" t="inlineStr">
         <is>
-          <t>Block the checking line with another piece to protect the General</t>
+          <t>Soldier</t>
         </is>
       </c>
       <c r="C372" s="2" t="inlineStr">
         <is>
-          <t>Dùng quân khác cản quân chiếu, đi quân che đỡ cho tướng</t>
+          <t>Tốt</t>
         </is>
       </c>
     </row>
     <row r="373" ht="17" customHeight="1">
       <c r="A373" s="2" t="inlineStr">
         <is>
-          <t>guide.check.paragraph6</t>
+          <t>guide.soldier.paragraph2</t>
         </is>
       </c>
       <c r="B373" s="2" t="inlineStr">
         <is>
-          <t>Repeatedly checking for more than 6 consecutive moves is not allowed</t>
+          <t>Moves &lt;b&gt;one step&lt;/b&gt; each turn. Before crossing the river, it can only move forward. After crossing the river, it may move &lt;b&gt;forward or sideways&lt;/b&gt;, but never backward.</t>
         </is>
       </c>
       <c r="C373" s="2" t="inlineStr">
         <is>
-          <t>Không được chiếu tướng quá 6 nước cờ liên tiếp</t>
+          <t>Mỗi nước đi &lt;b&gt;một bước&lt;/b&gt;. Khi chưa qua sông, Tốt chỉ được tiến. Khi Tốt đã qua sông được quyền &lt;b&gt;đi tiến và đi ngang&lt;/b&gt;, không được phép lùi.</t>
         </is>
       </c>
     </row>
     <row r="374" ht="17" customHeight="1">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>guide.result.paragraph1</t>
+          <t>guide.capturing.paragraph1</t>
         </is>
       </c>
       <c r="B374" s="2" t="inlineStr">
         <is>
-          <t>When one side gives Check and the other side has no legal way to protect the General, it is called a &lt;b&gt;Checkmate&lt;/b&gt;. The side that delivers Checkmate wins.</t>
+          <t>When a piece moves to an intersection occupied by an opponent's piece, it may &lt;b&gt;capture that piece&lt;/b&gt; and occupy its position.</t>
         </is>
       </c>
       <c r="C374" s="2" t="inlineStr">
         <is>
-          <t>Khi một bên chiếu Tướng mà bên còn lại không thể làm gì để bảo vệ Tướng thì được gọi là &lt;b&gt;Chiếu Hết&lt;/b&gt;, bên thực hiện được Chiếu Hết sẽ giành chiến thắng.</t>
+          <t>Khi một quân đi tới một giao điểm khác đã có quân đối phương đứng thì được quyền &lt;b&gt;bắt quân đó&lt;/b&gt;, đồng thời chiếm giữ vị trí quân bị bắt.</t>
         </is>
       </c>
     </row>
     <row r="375" ht="17" customHeight="1">
       <c r="A375" s="2" t="inlineStr">
         <is>
-          <t>guide.result.paragraph2</t>
+          <t>guide.capturing.paragraph2</t>
         </is>
       </c>
       <c r="B375" s="2" t="inlineStr">
         <is>
-          <t>If a player runs out of time for a single move (for example: 90s) without moving, the other side is awarded a &lt;b&gt;win&lt;/b&gt;.</t>
+          <t>You may not capture your own pieces. You may sacrifice your own pieces to be captured by the opponent, &lt;b&gt;except for the General&lt;/b&gt;.</t>
         </is>
       </c>
       <c r="C375" s="2" t="inlineStr">
         <is>
-          <t>Khi hết thời gian một nước đi (ví dụ: 90s) mà vẫn chưa di chuyển quân thì bên còn lại sẽ được &lt;b&gt;xử Thắng&lt;/b&gt;.</t>
+          <t>Không được bắt quân bên mình. Được phép cho đối phương bắt đầu quân mình chủ động hiến mình cho đối phương, &lt;b&gt;trừ Tướng&lt;/b&gt;.</t>
         </is>
       </c>
     </row>
     <row r="376" ht="17" customHeight="1">
       <c r="A376" s="2" t="inlineStr">
         <is>
-          <t>guide.result.paragraph3</t>
+          <t>guide.capturing.paragraph3</t>
         </is>
       </c>
       <c r="B376" s="2" t="inlineStr">
         <is>
-          <t>If a player runs out of total game time (for example: 5 minutes or 10 minutes), the other side is awarded a &lt;b&gt;win&lt;/b&gt;.</t>
+          <t>A captured piece is removed from the board. &lt;b&gt;Chasing one piece for more than 6 consecutive moves is not allowed&lt;/b&gt;.</t>
         </is>
       </c>
       <c r="C376" s="2" t="inlineStr">
         <is>
-          <t>Khi một bên hết thời gian ván đấu (ví dụ: 5 phút, 10 phút) thì bên còn lại sẽ được &lt;b&gt;xử Thắng&lt;/b&gt;.</t>
+          <t>Quân bị bắt phải bị loại và bị nhấc ra khỏi bàn cờ. &lt;b&gt;Không được đuổi 1 quân quá 6 nước cờ liên tiếp&lt;/b&gt;.</t>
         </is>
       </c>
     </row>
     <row r="377" ht="17" customHeight="1">
       <c r="A377" s="2" t="inlineStr">
         <is>
-          <t>guide.result.paragraph4</t>
+          <t>guide.check.paragraph1</t>
         </is>
       </c>
       <c r="B377" s="2" t="inlineStr">
         <is>
-          <t>If both sides have no pieces that have crossed the river, the game is declared a &lt;b&gt;draw&lt;/b&gt;. If one side still has pieces across the river but runs out of time, while the other side still has time but has no pieces across the river, the game is declared a &lt;b&gt;draw&lt;/b&gt;.</t>
+          <t>If a player makes a move that threatens to capture the opponent's General on the next move (by the same piece or another piece), it is called a &lt;b&gt;Check&lt;/b&gt;. The checked side must respond to avoid check. Otherwise, that side loses</t>
         </is>
       </c>
       <c r="C377" s="2" t="inlineStr">
         <is>
-          <t>Khi cả 2 bên đều không còn quân qua sông, ván đấu sẽ được &lt;b&gt;xử Hòa&lt;/b&gt;. Khi một bên còn quân qua sông nhưng cạn thời gian, một bên còn thời gian nhưng hết quân qua sông, ván đấu sẽ được &lt;b&gt;xử Hòa&lt;/b&gt;.</t>
+          <t>Nếu người chơi thực hiện một nước đi đe dọa bắt Tướng của đối phương ở nước đi tiếp theo (bằng chính quân cờ đó hoặc một quân cờ khác), thì đó được gọi là &lt;b&gt;Chiếu&lt;/b&gt;. Bên bị chiếu phải đáp trả để tránh bị chiếu. Nếu không sẽ bị xử thua</t>
         </is>
       </c>
     </row>
     <row r="378" ht="17" customHeight="1">
       <c r="A378" s="2" t="inlineStr">
         <is>
-          <t>guide.result.paragraph5</t>
+          <t>guide.check.paragraph2</t>
         </is>
       </c>
       <c r="B378" s="2" t="inlineStr">
         <is>
-          <t>Within 40 moves, if there is no capture and no Soldier advances by one square, the game is declared a &lt;b&gt;draw&lt;/b&gt;.</t>
+          <t>When the General is checked from any direction (including from behind), the checked side may respond in one of the following ways:</t>
         </is>
       </c>
       <c r="C378" s="2" t="inlineStr">
         <is>
-          <t>Trong vòng 40 nước nếu không phát sinh nước bắt quân, Tốt không tiến 1 ô thì ván đấu sẽ được &lt;b&gt;xử Hòa&lt;/b&gt;.</t>
+          <t>Tướng bị chiếu từ cả bốn hướng (bị chiếu cả từ phía sau) có thể ứng phó với nước chiếu tướng bằng một trong các cách sau:</t>
         </is>
       </c>
     </row>
     <row r="379" ht="17" customHeight="1">
       <c r="A379" s="2" t="inlineStr">
         <is>
-          <t>extra-money.title</t>
+          <t>guide.check.paragraph3</t>
         </is>
       </c>
       <c r="B379" s="2" t="inlineStr">
         <is>
-          <t>Daily tasks</t>
+          <t>Move the General to another position to escape check</t>
         </is>
       </c>
       <c r="C379" s="2" t="inlineStr">
         <is>
-          <t>Kiếm tiền</t>
+          <t>Di chuyển tướng sang vị trí khác để tránh nước chiếu</t>
         </is>
       </c>
     </row>
     <row r="380" ht="17" customHeight="1">
       <c r="A380" s="2" t="inlineStr">
         <is>
-          <t>extra-money.tab.lucky-wheel</t>
+          <t>guide.check.paragraph4</t>
         </is>
       </c>
       <c r="B380" s="2" t="inlineStr">
         <is>
-          <t>Lucky Wheel</t>
+          <t>Capture the checking piece</t>
         </is>
       </c>
       <c r="C380" s="2" t="inlineStr">
         <is>
-          <t>Vòng Quay May Mắn</t>
+          <t>Bắt quân đang chiếu</t>
         </is>
       </c>
     </row>
     <row r="381" ht="17" customHeight="1">
       <c r="A381" s="2" t="inlineStr">
         <is>
-          <t>extra-money.tab.bonus-coin</t>
+          <t>guide.check.paragraph5</t>
         </is>
       </c>
       <c r="B381" s="2" t="inlineStr">
         <is>
-          <t>Bonus Coin</t>
+          <t>Block the checking line with another piece to protect the General</t>
         </is>
       </c>
       <c r="C381" s="2" t="inlineStr">
         <is>
-          <t>Xu Thưởng</t>
+          <t>Dùng quân khác cản quân chiếu, đi quân che đỡ cho tướng</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>extra-money.tab.daily-bonus</t>
+          <t>guide.check.paragraph6</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Daily Bonus</t>
+          <t>Repeatedly checking for more than 6 consecutive moves is not allowed</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Thưởng hàng ngày</t>
+          <t>Không được chiếu tướng quá 6 nước cờ liên tiếp</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>extra-money.bonus-coin.subtitle</t>
+          <t>guide.result.paragraph1</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Watch a short video to earn free coin</t>
+          <t>When one side gives Check and the other side has no legal way to protect the General, it is called a &lt;b&gt;Checkmate&lt;/b&gt;. The side that delivers Checkmate wins.</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Xem video ngắn để nhận xu miễn phí</t>
+          <t>Khi một bên chiếu Tướng mà bên còn lại không thể làm gì để bảo vệ Tướng thì được gọi là &lt;b&gt;Chiếu Hết&lt;/b&gt;, bên thực hiện được Chiếu Hết sẽ giành chiến thắng.</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>extra-money.bonus-coin.next-in</t>
+          <t>guide.result.paragraph2</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Next in:</t>
+          <t>If a player runs out of time for a single move (for example: 90s) without moving, the other side is awarded a &lt;b&gt;win&lt;/b&gt;.</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Lượt kế tiếp:</t>
+          <t>Khi hết thời gian một nước đi (ví dụ: 90s) mà vẫn chưa di chuyển quân thì bên còn lại sẽ được &lt;b&gt;xử Thắng&lt;/b&gt;.</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>extra-money.bonus-coin.collect</t>
+          <t>guide.result.paragraph3</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Collect</t>
+          <t>If a player runs out of total game time (for example: 5 minutes or 10 minutes), the other side is awarded a &lt;b&gt;win&lt;/b&gt;.</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Thu thập</t>
+          <t>Khi một bên hết thời gian ván đấu (ví dụ: 5 phút, 10 phút) thì bên còn lại sẽ được &lt;b&gt;xử Thắng&lt;/b&gt;.</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>extra-money.bonus-coin.watch-video</t>
+          <t>guide.result.paragraph4</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Watch video</t>
+          <t>If both sides have no pieces that have crossed the river, the game is declared a &lt;b&gt;draw&lt;/b&gt;. If one side still has pieces across the river but runs out of time, while the other side still has time but has no pieces across the river, the game is declared a &lt;b&gt;draw&lt;/b&gt;.</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Xem video</t>
+          <t>Khi cả 2 bên đều không còn quân qua sông, ván đấu sẽ được &lt;b&gt;xử Hòa&lt;/b&gt;. Khi một bên còn quân qua sông nhưng cạn thời gian, một bên còn thời gian nhưng hết quân qua sông, ván đấu sẽ được &lt;b&gt;xử Hòa&lt;/b&gt;.</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>extra-money.daily-bonus.subtitle</t>
+          <t>guide.result.paragraph5</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Login 7 days in a row to earn 4000 coin</t>
+          <t>Within 40 moves, if there is no capture and no Soldier advances by one square, the game is declared a &lt;b&gt;draw&lt;/b&gt;.</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Đăng nhập 7 ngày liên tiếp để nhận 4000 xu</t>
+          <t>Trong vòng 40 nước nếu không phát sinh nước bắt quân, Tốt không tiến 1 ô thì ván đấu sẽ được &lt;b&gt;xử Hòa&lt;/b&gt;.</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>extra-money.daily-bonus.day</t>
+          <t>extra-money.title</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Daily tasks</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Ngày</t>
+          <t>Kiếm tiền</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>extra-money.reward-ad.loading</t>
+          <t>extra-money.tab.lucky-wheel</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Loading ad...</t>
+          <t>Lucky Wheel</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Đang tải quảng cáo...</t>
+          <t>Vòng Quay May Mắn</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>extra-money.reward-ad.error</t>
+          <t>extra-money.tab.bonus-coin</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Could not load the ad. Please try again.</t>
+          <t>Bonus Coin</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Không tải được quảng cáo. Vui lòng thử lại.</t>
+          <t>Xu Thưởng</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>extra-money.reward-ad.retry</t>
+          <t>extra-money.tab.daily-bonus</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Try again</t>
+          <t>Daily Bonus</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Thử lại</t>
+          <t>Thưởng hàng ngày</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>extra-money.reward-ad.close</t>
+          <t>extra-money.bonus-coin.subtitle</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Close</t>
+          <t>Watch a short video to earn free coin</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Đóng</t>
+          <t>Xem video ngắn để nhận xu miễn phí</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>profile.button.save</t>
+          <t>extra-money.bonus-coin.next-in</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Save</t>
+          <t>Next in:</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Lưu</t>
+          <t>Lượt kế tiếp:</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>profile.button.cancel</t>
+          <t>extra-money.bonus-coin.collect</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Collect</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Huỷ</t>
+          <t>Thu thập</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>change-password.title</t>
+          <t>extra-money.bonus-coin.watch-video</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Change password</t>
+          <t>Watch video</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Đổi mật khẩu</t>
+          <t>Xem video</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>change-password.current.label</t>
+          <t>extra-money.daily-bonus.subtitle</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Current password</t>
+          <t>Login 7 days in a row to earn 4000 coin</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Mật khẩu hiện tại</t>
+          <t>Đăng nhập 7 ngày liên tiếp để nhận 4000 xu</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>change-password.current.placeholder</t>
+          <t>extra-money.daily-bonus.day</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Enter current password</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Nhập mật khẩu hiện tại</t>
+          <t>Ngày</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>change-password.new.label</t>
+          <t>extra-money.reward-ad.loading</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>New password</t>
+          <t>Loading ad...</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Mật khẩu mới</t>
+          <t>Đang tải quảng cáo...</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>change-password.new.placeholder</t>
+          <t>extra-money.reward-ad.error</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Enter new password</t>
+          <t>Could not load the ad. Please try again.</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Nhập mật khẩu mới</t>
+          <t>Không tải được quảng cáo. Vui lòng thử lại.</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>change-password.confirm.label</t>
+          <t>extra-money.reward-ad.retry</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Confirm new password</t>
+          <t>Try again</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Xác nhận mật khẩu mới</t>
+          <t>Thử lại</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>change-password.confirm.placeholder</t>
+          <t>extra-money.reward-ad.close</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Re-enter new password</t>
+          <t>Close</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Nhập lại mật khẩu mới</t>
+          <t>Đóng</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>change-password.confirm.mismatch</t>
+          <t>profile.button.save</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Passwords do not match</t>
+          <t>Save</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Mật khẩu xác nhận không khớp</t>
+          <t>Lưu</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>change-password.show</t>
+          <t>profile.button.cancel</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Show password</t>
+          <t>Cancel</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Hiện mật khẩu</t>
+          <t>Huỷ</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>change-password.hide</t>
+          <t>change-password.title</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Hide password</t>
+          <t>Change password</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Ẩn mật khẩu</t>
+          <t>Đổi mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>change-password.submit</t>
+          <t>change-password.current.label</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Change password</t>
+          <t>Current password</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Đổi mật khẩu</t>
+          <t>Mật khẩu hiện tại</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>change-password.submitting</t>
+          <t>change-password.current.placeholder</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Changing...</t>
+          <t>Enter current password</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Đang đổi...</t>
+          <t>Nhập mật khẩu hiện tại</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>change-password.messages.success</t>
+          <t>change-password.new.label</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Password changed successfully</t>
+          <t>New password</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Đổi mật khẩu thành công</t>
+          <t>Mật khẩu mới</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>change-password.messages.missing-fields</t>
+          <t>change-password.new.placeholder</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Please fill in all fields</t>
+          <t>Enter new password</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Vui lòng nhập đầy đủ thông tin</t>
+          <t>Nhập mật khẩu mới</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>change-password.messages.weak-password</t>
+          <t>change-password.confirm.label</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>New password does not meet the requirements</t>
+          <t>Confirm new password</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Mật khẩu mới không đạt yêu cầu</t>
+          <t>Xác nhận mật khẩu mới</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>change-password.messages.same-as-current</t>
+          <t>change-password.confirm.placeholder</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>New password must be different from the current one</t>
+          <t>Re-enter new password</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Mật khẩu mới phải khác mật khẩu hiện tại</t>
+          <t>Nhập lại mật khẩu mới</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>change-password.messages.incorrect-current-password</t>
+          <t>change-password.confirm.mismatch</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Current password is incorrect</t>
+          <t>Passwords do not match</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Mật khẩu hiện tại không đúng</t>
+          <t>Mật khẩu xác nhận không khớp</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>change-password.messages.user-not-found</t>
+          <t>change-password.show</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>User not found</t>
+          <t>Show password</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Không tìm thấy người dùng</t>
+          <t>Hiện mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>change-password.messages.unauthorized</t>
+          <t>change-password.hide</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Session expired. Please sign in again.</t>
+          <t>Hide password</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Phiên đăng nhập đã hết hạn. Vui lòng đăng nhập lại.</t>
+          <t>Ẩn mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
+          <t>change-password.submit</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Change password</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>Đổi mật khẩu</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>change-password.submitting</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Changing...</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>Đang đổi...</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>change-password.messages.success</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Password changed successfully</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>Đổi mật khẩu thành công</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>change-password.messages.missing-fields</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Please fill in all fields</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>Vui lòng nhập đầy đủ thông tin</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>change-password.messages.weak-password</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>New password does not meet the requirements</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>Mật khẩu mới không đạt yêu cầu</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>change-password.messages.same-as-current</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>New password must be different from the current one</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>Mật khẩu mới phải khác mật khẩu hiện tại</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>change-password.messages.incorrect-current-password</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Current password is incorrect</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>Mật khẩu hiện tại không đúng</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>change-password.messages.user-not-found</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>User not found</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>Không tìm thấy người dùng</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>change-password.messages.unauthorized</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Session expired. Please sign in again.</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>Phiên đăng nhập đã hết hạn. Vui lòng đăng nhập lại.</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
           <t>change-password.messages.internal-server-error</t>
         </is>
       </c>
-      <c r="B414" t="inlineStr">
+      <c r="B423" t="inlineStr">
         <is>
           <t>Something went wrong. Please try again.</t>
         </is>
       </c>
-      <c r="C414" t="inlineStr">
+      <c r="C423" t="inlineStr">
         <is>
           <t>Đã có lỗi xảy ra. Vui lòng thử lại.</t>
         </is>
       </c>
-    </row>
-    <row r="415">
-      <c r="A415" t="inlineStr"/>
-      <c r="B415" t="inlineStr"/>
-      <c r="C415" t="inlineStr"/>
-    </row>
-    <row r="416">
-      <c r="A416" t="inlineStr"/>
-      <c r="B416" t="inlineStr"/>
-      <c r="C416" t="inlineStr"/>
-    </row>
-    <row r="417">
-      <c r="A417" t="inlineStr"/>
-      <c r="B417" t="inlineStr"/>
-      <c r="C417" t="inlineStr"/>
-    </row>
-    <row r="418">
-      <c r="A418" t="inlineStr"/>
-      <c r="B418" t="inlineStr"/>
-      <c r="C418" t="inlineStr"/>
-    </row>
-    <row r="419">
-      <c r="A419" t="inlineStr"/>
-      <c r="B419" t="inlineStr"/>
-      <c r="C419" t="inlineStr"/>
-    </row>
-    <row r="420">
-      <c r="A420" t="inlineStr"/>
-      <c r="B420" t="inlineStr"/>
-      <c r="C420" t="inlineStr"/>
-    </row>
-    <row r="421">
-      <c r="A421" t="inlineStr"/>
-      <c r="B421" t="inlineStr"/>
-      <c r="C421" t="inlineStr"/>
-    </row>
-    <row r="422">
-      <c r="A422" t="inlineStr"/>
-      <c r="B422" t="inlineStr"/>
-      <c r="C422" t="inlineStr"/>
-    </row>
-    <row r="423">
-      <c r="A423" t="inlineStr"/>
-      <c r="B423" t="inlineStr"/>
-      <c r="C423" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr"/>
@@ -7465,6 +7573,51 @@
       <c r="A433" t="inlineStr"/>
       <c r="B433" t="inlineStr"/>
       <c r="C433" t="inlineStr"/>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr"/>
+      <c r="B434" t="inlineStr"/>
+      <c r="C434" t="inlineStr"/>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr"/>
+      <c r="B435" t="inlineStr"/>
+      <c r="C435" t="inlineStr"/>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr"/>
+      <c r="B436" t="inlineStr"/>
+      <c r="C436" t="inlineStr"/>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr"/>
+      <c r="B437" t="inlineStr"/>
+      <c r="C437" t="inlineStr"/>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr"/>
+      <c r="B438" t="inlineStr"/>
+      <c r="C438" t="inlineStr"/>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr"/>
+      <c r="B439" t="inlineStr"/>
+      <c r="C439" t="inlineStr"/>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr"/>
+      <c r="B440" t="inlineStr"/>
+      <c r="C440" t="inlineStr"/>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr"/>
+      <c r="B441" t="inlineStr"/>
+      <c r="C441" t="inlineStr"/>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr"/>
+      <c r="B442" t="inlineStr"/>
+      <c r="C442" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tools/languages.xlsx
+++ b/tools/languages.xlsx
@@ -325,7 +325,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C433"/>
+  <dimension ref="A1:C434"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5810,1571 +5810,1583 @@
     <row r="323" ht="54" customHeight="1">
       <c r="A323" s="2" t="inlineStr">
         <is>
-          <t>undo.messages.spectator-cannot-undo</t>
+          <t>undo.messages.pve-only</t>
         </is>
       </c>
       <c r="B323" s="2" t="inlineStr">
         <is>
-          <t>Spectators cannot undo moves</t>
+          <t>Undo is only available in PvE rooms</t>
         </is>
       </c>
       <c r="C323" s="2" t="inlineStr">
         <is>
-          <t>Người xem không thể hoàn tác nước đi</t>
+          <t>Hoàn tác chỉ khả dụng trong phòng PvE</t>
         </is>
       </c>
     </row>
     <row r="324" ht="18" customHeight="1">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>undo.messages.no-moves</t>
+          <t>undo.messages.spectator-cannot-undo</t>
         </is>
       </c>
       <c r="B324" s="2" t="inlineStr">
         <is>
-          <t>No moves to undo</t>
+          <t>Spectators cannot undo moves</t>
         </is>
       </c>
       <c r="C324" s="2" t="inlineStr">
         <is>
-          <t>Không có nước đi để hoàn tác</t>
+          <t>Người xem không thể hoàn tác nước đi</t>
         </is>
       </c>
     </row>
     <row r="325" ht="72" customHeight="1">
       <c r="A325" s="2" t="inlineStr">
         <is>
-          <t>undo.messages.delete-failed</t>
+          <t>undo.messages.no-moves</t>
         </is>
       </c>
       <c r="B325" s="2" t="inlineStr">
         <is>
-          <t>Failed to undo move</t>
+          <t>No moves to undo</t>
         </is>
       </c>
       <c r="C325" s="2" t="inlineStr">
         <is>
-          <t>Không thể hoàn tác nước đi</t>
+          <t>Không có nước đi để hoàn tác</t>
         </is>
       </c>
     </row>
     <row r="326" ht="18" customHeight="1">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>undo.messages.undo-limit-exceeded</t>
+          <t>undo.messages.delete-failed</t>
         </is>
       </c>
       <c r="B326" s="2" t="inlineStr">
         <is>
-          <t>Maximum 3 undo per game exceeded</t>
+          <t>Failed to undo move</t>
         </is>
       </c>
       <c r="C326" s="2" t="inlineStr">
         <is>
-          <t>Đã đạt tối đa 3 lần hoàn tác trong trò chơi</t>
+          <t>Không thể hoàn tác nước đi</t>
         </is>
       </c>
     </row>
     <row r="327" ht="90" customHeight="1">
       <c r="A327" s="2" t="inlineStr">
         <is>
-          <t>undo.messages.success</t>
+          <t>undo.messages.undo-limit-exceeded</t>
         </is>
       </c>
       <c r="B327" s="2" t="inlineStr">
         <is>
-          <t>Move undone successfully</t>
+          <t>Maximum 3 undo per game exceeded</t>
         </is>
       </c>
       <c r="C327" s="2" t="inlineStr">
         <is>
-          <t>Hoàn tác nước đi thành công</t>
+          <t>Đã đạt tối đa 3 lần hoàn tác trong trò chơi</t>
         </is>
       </c>
     </row>
     <row r="328" ht="18" customHeight="1">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>undo.messages.internal-server-error</t>
+          <t>undo.messages.success</t>
         </is>
       </c>
       <c r="B328" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Move undone successfully</t>
         </is>
       </c>
       <c r="C328" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Hoàn tác nước đi thành công</t>
         </is>
       </c>
     </row>
     <row r="329" ht="72" customHeight="1">
       <c r="A329" s="2" t="inlineStr">
         <is>
-          <t>player-history.messages.invalid-user-id</t>
+          <t>undo.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B329" s="2" t="inlineStr">
         <is>
-          <t>Invalid user ID</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C329" s="2" t="inlineStr">
         <is>
-          <t>ID người dùng không hợp lệ</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="330" ht="54" customHeight="1">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>player-history.messages.success</t>
+          <t>player-history.messages.invalid-user-id</t>
         </is>
       </c>
       <c r="B330" s="2" t="inlineStr">
         <is>
-          <t>Fetch game history successfully</t>
+          <t>Invalid user ID</t>
         </is>
       </c>
       <c r="C330" s="2" t="inlineStr">
         <is>
-          <t>Lấy lịch sử trò chơi thành công</t>
+          <t>ID người dùng không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="331" ht="54" customHeight="1">
       <c r="A331" s="2" t="inlineStr">
         <is>
-          <t>validate-token.messages.success</t>
+          <t>player-history.messages.success</t>
         </is>
       </c>
       <c r="B331" s="2" t="inlineStr">
         <is>
-          <t>Token is valid</t>
+          <t>Fetch game history successfully</t>
         </is>
       </c>
       <c r="C331" s="2" t="inlineStr">
         <is>
-          <t>Token hợp lệ</t>
+          <t>Lấy lịch sử trò chơi thành công</t>
         </is>
       </c>
     </row>
     <row r="332" ht="54" customHeight="1">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>guide.section.objective</t>
+          <t>validate-token.messages.success</t>
         </is>
       </c>
       <c r="B332" s="2" t="inlineStr">
         <is>
-          <t>Objective of the game</t>
+          <t>Token is valid</t>
         </is>
       </c>
       <c r="C332" s="2" t="inlineStr">
         <is>
-          <t>Mục tiêu của trò chơi</t>
+          <t>Token hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="333" ht="90" customHeight="1">
       <c r="A333" s="2" t="inlineStr">
         <is>
-          <t>guide.section.pieces</t>
+          <t>guide.section.objective</t>
         </is>
       </c>
       <c r="B333" s="2" t="inlineStr">
         <is>
-          <t>Pieces</t>
+          <t>Objective of the game</t>
         </is>
       </c>
       <c r="C333" s="2" t="inlineStr">
         <is>
-          <t>Quân cờ</t>
+          <t>Mục tiêu của trò chơi</t>
         </is>
       </c>
     </row>
     <row r="334" ht="54" customHeight="1">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>guide.section.moving-pieces</t>
+          <t>guide.section.pieces</t>
         </is>
       </c>
       <c r="B334" s="2" t="inlineStr">
         <is>
-          <t>Moving pieces</t>
+          <t>Pieces</t>
         </is>
       </c>
       <c r="C334" s="2" t="inlineStr">
         <is>
-          <t>Đi quân</t>
+          <t>Quân cờ</t>
         </is>
       </c>
     </row>
     <row r="335" ht="36" customHeight="1">
       <c r="A335" s="2" t="inlineStr">
         <is>
-          <t>guide.section.capturing</t>
+          <t>guide.section.moving-pieces</t>
         </is>
       </c>
       <c r="B335" s="2" t="inlineStr">
         <is>
-          <t>Capturing</t>
+          <t>Moving pieces</t>
         </is>
       </c>
       <c r="C335" s="2" t="inlineStr">
         <is>
-          <t>Bắt quân</t>
+          <t>Đi quân</t>
         </is>
       </c>
     </row>
     <row r="336" ht="18" customHeight="1">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>guide.section.check</t>
+          <t>guide.section.capturing</t>
         </is>
       </c>
       <c r="B336" s="2" t="inlineStr">
         <is>
-          <t>Check</t>
+          <t>Capturing</t>
         </is>
       </c>
       <c r="C336" s="2" t="inlineStr">
         <is>
-          <t>Chiếu tướng</t>
+          <t>Bắt quân</t>
         </is>
       </c>
     </row>
     <row r="337" ht="36" customHeight="1">
       <c r="A337" s="2" t="inlineStr">
         <is>
-          <t>guide.section.result</t>
+          <t>guide.section.check</t>
         </is>
       </c>
       <c r="B337" s="2" t="inlineStr">
         <is>
-          <t>Result</t>
+          <t>Check</t>
         </is>
       </c>
       <c r="C337" s="2" t="inlineStr">
         <is>
-          <t>Kết quả</t>
+          <t>Chiếu tướng</t>
         </is>
       </c>
     </row>
     <row r="338" ht="36" customHeight="1">
       <c r="A338" s="2" t="inlineStr">
         <is>
-          <t>guide.table.piece</t>
+          <t>guide.section.result</t>
         </is>
       </c>
       <c r="B338" s="2" t="inlineStr">
         <is>
-          <t>Piece</t>
+          <t>Result</t>
         </is>
       </c>
       <c r="C338" s="2" t="inlineStr">
         <is>
-          <t>Quân</t>
+          <t>Kết quả</t>
         </is>
       </c>
     </row>
     <row r="339" ht="72" customHeight="1">
       <c r="A339" s="2" t="inlineStr">
         <is>
-          <t>guide.table.symbol</t>
+          <t>guide.table.piece</t>
         </is>
       </c>
       <c r="B339" s="2" t="inlineStr">
         <is>
-          <t>Symbol</t>
+          <t>Piece</t>
         </is>
       </c>
       <c r="C339" s="2" t="inlineStr">
         <is>
-          <t>Ký hiệu</t>
+          <t>Quân</t>
         </is>
       </c>
     </row>
     <row r="340" ht="54" customHeight="1">
       <c r="A340" s="2" t="inlineStr">
         <is>
-          <t>guide.table.quantity</t>
+          <t>guide.table.symbol</t>
         </is>
       </c>
       <c r="B340" s="2" t="inlineStr">
         <is>
-          <t>Quantity</t>
+          <t>Symbol</t>
         </is>
       </c>
       <c r="C340" s="2" t="inlineStr">
         <is>
-          <t>Số lượng</t>
+          <t>Ký hiệu</t>
         </is>
       </c>
     </row>
     <row r="341" ht="54" customHeight="1">
       <c r="A341" s="2" t="inlineStr">
         <is>
-          <t>guide.objective.paragraph1</t>
+          <t>guide.table.quantity</t>
         </is>
       </c>
       <c r="B341" s="2" t="inlineStr">
         <is>
-          <t>A match is played between two players: one controls the Red pieces, and the other controls the Black pieces. The objective of each player is to use their pieces on the board to &lt;b&gt;checkmate&lt;/b&gt; the opponent's General, and win the game.</t>
+          <t>Quantity</t>
         </is>
       </c>
       <c r="C341" s="2" t="inlineStr">
         <is>
-          <t>Ván cờ được tiến hành giữa 2 đấu thủ, một người cầm Quân Đỏ, một người cầm Quân Đen. Mục đích của mỗi đấu thủ là tìm mọi cách sử dụng các quân trên bàn cờ để &lt;b&gt;chiếu bí Tướng&lt;/b&gt; của đối phương, giành thắng lợi.</t>
+          <t>Số lượng</t>
         </is>
       </c>
     </row>
     <row r="342" ht="90" customHeight="1">
       <c r="A342" s="2" t="inlineStr">
         <is>
-          <t>guide.pieces.paragraph1</t>
+          <t>guide.objective.paragraph1</t>
         </is>
       </c>
       <c r="B342" s="2" t="inlineStr">
         <is>
-          <t>At the start of each game, there must be 32 pieces in total, consisting of &lt;b&gt;7 piece types&lt;/b&gt; split evenly between both sides: 16 Red pieces and 16 Black pieces. The 7 piece types with their symbols and quantities are as follows:</t>
+          <t>A match is played between two players: one controls the Red pieces, and the other controls the Black pieces. The objective of each player is to use their pieces on the board to &lt;b&gt;checkmate&lt;/b&gt; the opponent's General, and win the game.</t>
         </is>
       </c>
       <c r="C342" s="2" t="inlineStr">
         <is>
-          <t>Mỗi ván cờ lúc bắt đầu phải có đủ 32 quân, gồm 7 loại chia đều cho mỗi bên gồm 16 quân Đỏ và 16 quân Đen. &lt;b&gt;7 loại quân&lt;/b&gt; có ký hiệu và số lượng như sau:</t>
+          <t>Ván cờ được tiến hành giữa 2 đấu thủ, một người cầm Quân Đỏ, một người cầm Quân Đen. Mục đích của mỗi đấu thủ là tìm mọi cách sử dụng các quân trên bàn cờ để &lt;b&gt;chiếu bí Tướng&lt;/b&gt; của đối phương, giành thắng lợi.</t>
         </is>
       </c>
     </row>
     <row r="343" ht="54" customHeight="1">
       <c r="A343" s="2" t="inlineStr">
         <is>
-          <t>guide.piece.general</t>
+          <t>guide.pieces.paragraph1</t>
         </is>
       </c>
       <c r="B343" s="2" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>At the start of each game, there must be 32 pieces in total, consisting of &lt;b&gt;7 piece types&lt;/b&gt; split evenly between both sides: 16 Red pieces and 16 Black pieces. The 7 piece types with their symbols and quantities are as follows:</t>
         </is>
       </c>
       <c r="C343" s="2" t="inlineStr">
         <is>
-          <t>Tướng</t>
+          <t>Mỗi ván cờ lúc bắt đầu phải có đủ 32 quân, gồm 7 loại chia đều cho mỗi bên gồm 16 quân Đỏ và 16 quân Đen. &lt;b&gt;7 loại quân&lt;/b&gt; có ký hiệu và số lượng như sau:</t>
         </is>
       </c>
     </row>
     <row r="344" ht="18" customHeight="1">
       <c r="A344" s="2" t="inlineStr">
         <is>
-          <t>guide.piece.advisor</t>
+          <t>guide.piece.general</t>
         </is>
       </c>
       <c r="B344" s="2" t="inlineStr">
         <is>
-          <t>Advisor</t>
+          <t>General</t>
         </is>
       </c>
       <c r="C344" s="2" t="inlineStr">
         <is>
-          <t>Sĩ</t>
+          <t>Tướng</t>
         </is>
       </c>
     </row>
     <row r="345" ht="18" customHeight="1">
       <c r="A345" s="2" t="inlineStr">
         <is>
-          <t>guide.piece.elephant</t>
+          <t>guide.piece.advisor</t>
         </is>
       </c>
       <c r="B345" s="2" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Advisor</t>
         </is>
       </c>
       <c r="C345" s="2" t="inlineStr">
         <is>
-          <t>Tượng</t>
+          <t>Sĩ</t>
         </is>
       </c>
     </row>
     <row r="346" ht="36" customHeight="1">
       <c r="A346" s="2" t="inlineStr">
         <is>
-          <t>guide.piece.chariot</t>
+          <t>guide.piece.elephant</t>
         </is>
       </c>
       <c r="B346" s="2" t="inlineStr">
         <is>
-          <t>Chariot</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="C346" s="2" t="inlineStr">
         <is>
-          <t>Xe</t>
+          <t>Tượng</t>
         </is>
       </c>
     </row>
     <row r="347" ht="18" customHeight="1">
       <c r="A347" s="2" t="inlineStr">
         <is>
-          <t>guide.piece.horse</t>
+          <t>guide.piece.chariot</t>
         </is>
       </c>
       <c r="B347" s="2" t="inlineStr">
         <is>
-          <t>Horse</t>
+          <t>Chariot</t>
         </is>
       </c>
       <c r="C347" s="2" t="inlineStr">
         <is>
-          <t>Mã</t>
+          <t>Xe</t>
         </is>
       </c>
     </row>
     <row r="348" ht="18" customHeight="1">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>guide.piece.cannon</t>
+          <t>guide.piece.horse</t>
         </is>
       </c>
       <c r="B348" s="2" t="inlineStr">
         <is>
-          <t>Cannon</t>
+          <t>Horse</t>
         </is>
       </c>
       <c r="C348" s="2" t="inlineStr">
         <is>
-          <t>Pháo</t>
+          <t>Mã</t>
         </is>
       </c>
     </row>
     <row r="349" ht="36" customHeight="1">
       <c r="A349" s="2" t="inlineStr">
         <is>
-          <t>guide.piece.soldier</t>
+          <t>guide.piece.cannon</t>
         </is>
       </c>
       <c r="B349" s="2" t="inlineStr">
         <is>
-          <t>Soldier</t>
+          <t>Cannon</t>
         </is>
       </c>
       <c r="C349" s="2" t="inlineStr">
         <is>
-          <t>Tốt</t>
+          <t>Pháo</t>
         </is>
       </c>
     </row>
     <row r="350" ht="18" customHeight="1">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>guide.moving-pieces.paragraph1</t>
+          <t>guide.piece.soldier</t>
         </is>
       </c>
       <c r="B350" s="2" t="inlineStr">
         <is>
-          <t>On each turn, each side may move only one of its own pieces according to the rules. The movement rules are as follows:</t>
+          <t>Soldier</t>
         </is>
       </c>
       <c r="C350" s="2" t="inlineStr">
         <is>
-          <t>Mỗi nước đi, mỗi bên chỉ được di chuyển quân của mình theo đúng quy định. Quy định di chuyển của các quân như sau:</t>
+          <t>Tốt</t>
         </is>
       </c>
     </row>
     <row r="351" ht="36" customHeight="1">
       <c r="A351" s="2" t="inlineStr">
         <is>
-          <t>guide.general.paragraph1</t>
+          <t>guide.moving-pieces.paragraph1</t>
         </is>
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>On each turn, each side may move only one of its own pieces according to the rules. The movement rules are as follows:</t>
         </is>
       </c>
       <c r="C351" s="2" t="inlineStr">
         <is>
-          <t>Tướng</t>
+          <t>Mỗi nước đi, mỗi bên chỉ được di chuyển quân của mình theo đúng quy định. Quy định di chuyển của các quân như sau:</t>
         </is>
       </c>
     </row>
     <row r="352" ht="18" customHeight="1">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>guide.general.paragraph2</t>
+          <t>guide.general.paragraph1</t>
         </is>
       </c>
       <c r="B352" s="2" t="inlineStr">
         <is>
-          <t>Moves one step &lt;b&gt;horizontally or vertically&lt;/b&gt; within the palace. The two Generals may not face each other directly on the same file. If they are facing each other, there must be at least one piece of either side placed between them.</t>
+          <t>General</t>
         </is>
       </c>
       <c r="C352" s="2" t="inlineStr">
         <is>
-          <t>Mỗi nước được đi một bước &lt;b&gt;ngang hoặc dọc&lt;/b&gt; tùy ý trong cung Tướng. Hai tướng của 2 bên không được đối mặt nhau trực tiếp trên cùng một đường thẳng. Nếu đối mặt, bắt buộc phải có quân của bất kỳ bên nào đứng che mặt.</t>
+          <t>Tướng</t>
         </is>
       </c>
     </row>
     <row r="353" ht="18" customHeight="1">
       <c r="A353" s="2" t="inlineStr">
         <is>
-          <t>guide.advisor.paragraph1</t>
+          <t>guide.general.paragraph2</t>
         </is>
       </c>
       <c r="B353" s="2" t="inlineStr">
         <is>
-          <t>Advisor</t>
+          <t>Moves one step &lt;b&gt;horizontally or vertically&lt;/b&gt; within the palace. The two Generals may not face each other directly on the same file. If they are facing each other, there must be at least one piece of either side placed between them.</t>
         </is>
       </c>
       <c r="C353" s="2" t="inlineStr">
         <is>
-          <t>Sĩ</t>
+          <t>Mỗi nước được đi một bước &lt;b&gt;ngang hoặc dọc&lt;/b&gt; tùy ý trong cung Tướng. Hai tướng của 2 bên không được đối mặt nhau trực tiếp trên cùng một đường thẳng. Nếu đối mặt, bắt buộc phải có quân của bất kỳ bên nào đứng che mặt.</t>
         </is>
       </c>
     </row>
     <row r="354" ht="18" customHeight="1">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>guide.advisor.paragraph2</t>
+          <t>guide.advisor.paragraph1</t>
         </is>
       </c>
       <c r="B354" s="2" t="inlineStr">
         <is>
-          <t>Moves one step &lt;b&gt;diagonally&lt;/b&gt; within the palace.</t>
+          <t>Advisor</t>
         </is>
       </c>
       <c r="C354" s="2" t="inlineStr">
         <is>
-          <t>Mỗi nước &lt;b&gt;đi chéo một bước&lt;/b&gt; trong cung Tướng.</t>
+          <t>Sĩ</t>
         </is>
       </c>
     </row>
     <row r="355" ht="18" customHeight="1">
       <c r="A355" s="2" t="inlineStr">
         <is>
-          <t>guide.elephant.paragraph1</t>
+          <t>guide.advisor.paragraph2</t>
         </is>
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Moves one step &lt;b&gt;diagonally&lt;/b&gt; within the palace.</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
         <is>
-          <t>Tượng</t>
+          <t>Mỗi nước &lt;b&gt;đi chéo một bước&lt;/b&gt; trong cung Tướng.</t>
         </is>
       </c>
     </row>
     <row r="356" ht="18" customHeight="1">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>guide.elephant.paragraph2</t>
+          <t>guide.elephant.paragraph1</t>
         </is>
       </c>
       <c r="B356" s="2" t="inlineStr">
         <is>
-          <t>Moves &lt;b&gt;two steps diagonally&lt;/b&gt; on its own side of the board and may not cross the river. If there is another piece on the midpoint of that diagonal path, the Elephant is blocked and cannot move.</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="C356" s="2" t="inlineStr">
         <is>
-          <t>Mỗi nước &lt;b&gt;đi chéo hai bước&lt;/b&gt; tại trận địa bên mình, không được qua sông. Nếu ở giữa đường chéo đó có quân khác đứng thì quân Tượng bị cản, không đi được.</t>
+          <t>Tượng</t>
         </is>
       </c>
     </row>
     <row r="357" ht="17" customHeight="1">
       <c r="A357" s="2" t="inlineStr">
         <is>
-          <t>guide.chariot.paragraph1</t>
+          <t>guide.elephant.paragraph2</t>
         </is>
       </c>
       <c r="B357" s="2" t="inlineStr">
         <is>
-          <t>Chariot</t>
+          <t>Moves &lt;b&gt;two steps diagonally&lt;/b&gt; on its own side of the board and may not cross the river. If there is another piece on the midpoint of that diagonal path, the Elephant is blocked and cannot move.</t>
         </is>
       </c>
       <c r="C357" s="2" t="inlineStr">
         <is>
-          <t>Xe</t>
+          <t>Mỗi nước &lt;b&gt;đi chéo hai bước&lt;/b&gt; tại trận địa bên mình, không được qua sông. Nếu ở giữa đường chéo đó có quân khác đứng thì quân Tượng bị cản, không đi được.</t>
         </is>
       </c>
     </row>
     <row r="358" ht="18" customHeight="1">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>guide.chariot.paragraph2</t>
+          <t>guide.chariot.paragraph1</t>
         </is>
       </c>
       <c r="B358" s="2" t="inlineStr">
         <is>
-          <t>Moves &lt;b&gt;horizontally or vertically&lt;/b&gt; with no limit on distance, as long as no piece blocks the path.</t>
+          <t>Chariot</t>
         </is>
       </c>
       <c r="C358" s="2" t="inlineStr">
         <is>
-          <t>Mỗi nước được &lt;b&gt;đi dọc hoặc đi ngang&lt;/b&gt;, không hạn chế số bước đi nếu không có quân khác cản đường.</t>
+          <t>Xe</t>
         </is>
       </c>
     </row>
     <row r="359" ht="18" customHeight="1">
       <c r="A359" s="2" t="inlineStr">
         <is>
-          <t>guide.horse.paragraph1</t>
+          <t>guide.chariot.paragraph2</t>
         </is>
       </c>
       <c r="B359" s="2" t="inlineStr">
         <is>
-          <t>Horse</t>
+          <t>Moves &lt;b&gt;horizontally or vertically&lt;/b&gt; with no limit on distance, as long as no piece blocks the path.</t>
         </is>
       </c>
       <c r="C359" s="2" t="inlineStr">
         <is>
-          <t>Mã</t>
+          <t>Mỗi nước được &lt;b&gt;đi dọc hoặc đi ngang&lt;/b&gt;, không hạn chế số bước đi nếu không có quân khác cản đường.</t>
         </is>
       </c>
     </row>
     <row r="360" ht="18" customHeight="1">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>guide.horse.paragraph2</t>
+          <t>guide.horse.paragraph1</t>
         </is>
       </c>
       <c r="B360" s="2" t="inlineStr">
         <is>
-          <t>Moves in an &lt;b&gt;L-shape&lt;/b&gt; (one step orthogonally then one step diagonally outward). If the adjacent orthogonal point is occupied by any piece, the Horse is blocked and cannot move.</t>
+          <t>Horse</t>
         </is>
       </c>
       <c r="C360" s="2" t="inlineStr">
         <is>
-          <t>Đi theo &lt;b&gt;đường chéo hình chữ nhật&lt;/b&gt; của hai ô vuông liền nhau. Nếu giao điểm liền kề bước thẳng dọc ngang có một quân khác đứng thì Mã bị cản, không đi được.</t>
+          <t>Mã</t>
         </is>
       </c>
     </row>
     <row r="361" ht="18" customHeight="1">
       <c r="A361" s="2" t="inlineStr">
         <is>
-          <t>guide.cannon.paragraph1</t>
+          <t>guide.horse.paragraph2</t>
         </is>
       </c>
       <c r="B361" s="2" t="inlineStr">
         <is>
-          <t>Cannon</t>
+          <t>Moves in an &lt;b&gt;L-shape&lt;/b&gt; (one step orthogonally then one step diagonally outward). If the adjacent orthogonal point is occupied by any piece, the Horse is blocked and cannot move.</t>
         </is>
       </c>
       <c r="C361" s="2" t="inlineStr">
         <is>
-          <t>Pháo</t>
+          <t>Đi theo &lt;b&gt;đường chéo hình chữ nhật&lt;/b&gt; của hai ô vuông liền nhau. Nếu giao điểm liền kề bước thẳng dọc ngang có một quân khác đứng thì Mã bị cản, không đi được.</t>
         </is>
       </c>
     </row>
     <row r="362" ht="18" customHeight="1">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>guide.cannon.paragraph2</t>
+          <t>guide.cannon.paragraph1</t>
         </is>
       </c>
       <c r="B362" s="2" t="inlineStr">
         <is>
-          <t>Moves &lt;b&gt;horizontally or vertically&lt;/b&gt; like a Chariot when not capturing. To capture, it must &lt;b&gt;jump over exactly one piece&lt;/b&gt; to reach its target. If there are zero or more than one pieces between the Cannon and the target, it cannot capture.</t>
+          <t>Cannon</t>
         </is>
       </c>
       <c r="C362" s="2" t="inlineStr">
         <is>
-          <t>Đi ngang hoặc dọc giống Xe khi không bắt quân. Để bắt quân, nó phải &lt;b&gt;nhảy qua đúng một quân khác&lt;/b&gt; để đến mục tiêu. Nếu không có hoặc có nhiều hơn một quân giữa Pháo và mục tiêu, nó không thể bắt quân.</t>
+          <t>Pháo</t>
         </is>
       </c>
     </row>
     <row r="363" ht="18" customHeight="1">
       <c r="A363" s="2" t="inlineStr">
         <is>
-          <t>guide.soldier.paragraph1</t>
+          <t>guide.cannon.paragraph2</t>
         </is>
       </c>
       <c r="B363" s="2" t="inlineStr">
         <is>
-          <t>Soldier</t>
+          <t>Moves &lt;b&gt;horizontally or vertically&lt;/b&gt; like a Chariot when not capturing. To capture, it must &lt;b&gt;jump over exactly one piece&lt;/b&gt; to reach its target. If there are zero or more than one pieces between the Cannon and the target, it cannot capture.</t>
         </is>
       </c>
       <c r="C363" s="2" t="inlineStr">
         <is>
-          <t>Tốt</t>
+          <t>Đi ngang hoặc dọc giống Xe khi không bắt quân. Để bắt quân, nó phải &lt;b&gt;nhảy qua đúng một quân khác&lt;/b&gt; để đến mục tiêu. Nếu không có hoặc có nhiều hơn một quân giữa Pháo và mục tiêu, nó không thể bắt quân.</t>
         </is>
       </c>
     </row>
     <row r="364" ht="17" customHeight="1">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>guide.soldier.paragraph2</t>
+          <t>guide.soldier.paragraph1</t>
         </is>
       </c>
       <c r="B364" s="2" t="inlineStr">
         <is>
-          <t>Moves &lt;b&gt;one step&lt;/b&gt; each turn. Before crossing the river, it can only move forward. After crossing the river, it may move &lt;b&gt;forward or sideways&lt;/b&gt;, but never backward.</t>
+          <t>Soldier</t>
         </is>
       </c>
       <c r="C364" s="2" t="inlineStr">
         <is>
-          <t>Mỗi nước đi &lt;b&gt;một bước&lt;/b&gt;. Khi chưa qua sông, Tốt chỉ được tiến. Khi Tốt đã qua sông được quyền &lt;b&gt;đi tiến và đi ngang&lt;/b&gt;, không được phép lùi.</t>
+          <t>Tốt</t>
         </is>
       </c>
     </row>
     <row r="365" ht="17" customHeight="1">
       <c r="A365" s="2" t="inlineStr">
         <is>
-          <t>guide.capturing.paragraph1</t>
+          <t>guide.soldier.paragraph2</t>
         </is>
       </c>
       <c r="B365" s="2" t="inlineStr">
         <is>
-          <t>When a piece moves to an intersection occupied by an opponent's piece, it may &lt;b&gt;capture that piece&lt;/b&gt; and occupy its position.</t>
+          <t>Moves &lt;b&gt;one step&lt;/b&gt; each turn. Before crossing the river, it can only move forward. After crossing the river, it may move &lt;b&gt;forward or sideways&lt;/b&gt;, but never backward.</t>
         </is>
       </c>
       <c r="C365" s="2" t="inlineStr">
         <is>
-          <t>Khi một quân đi tới một giao điểm khác đã có quân đối phương đứng thì được quyền &lt;b&gt;bắt quân đó&lt;/b&gt;, đồng thời chiếm giữ vị trí quân bị bắt.</t>
+          <t>Mỗi nước đi &lt;b&gt;một bước&lt;/b&gt;. Khi chưa qua sông, Tốt chỉ được tiến. Khi Tốt đã qua sông được quyền &lt;b&gt;đi tiến và đi ngang&lt;/b&gt;, không được phép lùi.</t>
         </is>
       </c>
     </row>
     <row r="366" ht="17" customHeight="1">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>guide.capturing.paragraph2</t>
+          <t>guide.capturing.paragraph1</t>
         </is>
       </c>
       <c r="B366" s="2" t="inlineStr">
         <is>
-          <t>You may not capture your own pieces. You may sacrifice your own pieces to be captured by the opponent, &lt;b&gt;except for the General&lt;/b&gt;.</t>
+          <t>When a piece moves to an intersection occupied by an opponent's piece, it may &lt;b&gt;capture that piece&lt;/b&gt; and occupy its position.</t>
         </is>
       </c>
       <c r="C366" s="2" t="inlineStr">
         <is>
-          <t>Không được bắt quân bên mình. Được phép cho đối phương bắt đầu quân mình chủ động hiến mình cho đối phương, &lt;b&gt;trừ Tướng&lt;/b&gt;.</t>
+          <t>Khi một quân đi tới một giao điểm khác đã có quân đối phương đứng thì được quyền &lt;b&gt;bắt quân đó&lt;/b&gt;, đồng thời chiếm giữ vị trí quân bị bắt.</t>
         </is>
       </c>
     </row>
     <row r="367" ht="17" customHeight="1">
       <c r="A367" s="2" t="inlineStr">
         <is>
-          <t>guide.capturing.paragraph3</t>
+          <t>guide.capturing.paragraph2</t>
         </is>
       </c>
       <c r="B367" s="2" t="inlineStr">
         <is>
-          <t>A captured piece is removed from the board. &lt;b&gt;Chasing one piece for more than 6 consecutive moves is not allowed&lt;/b&gt;.</t>
+          <t>You may not capture your own pieces. You may sacrifice your own pieces to be captured by the opponent, &lt;b&gt;except for the General&lt;/b&gt;.</t>
         </is>
       </c>
       <c r="C367" s="2" t="inlineStr">
         <is>
-          <t>Quân bị bắt phải bị loại và bị nhấc ra khỏi bàn cờ. &lt;b&gt;Không được đuổi 1 quân quá 6 nước cờ liên tiếp&lt;/b&gt;.</t>
+          <t>Không được bắt quân bên mình. Được phép cho đối phương bắt đầu quân mình chủ động hiến mình cho đối phương, &lt;b&gt;trừ Tướng&lt;/b&gt;.</t>
         </is>
       </c>
     </row>
     <row r="368" ht="17" customHeight="1">
       <c r="A368" s="2" t="inlineStr">
         <is>
-          <t>guide.check.paragraph1</t>
+          <t>guide.capturing.paragraph3</t>
         </is>
       </c>
       <c r="B368" s="2" t="inlineStr">
         <is>
-          <t>If a player makes a move that threatens to capture the opponent's General on the next move (by the same piece or another piece), it is called a &lt;b&gt;Check&lt;/b&gt;. The checked side must respond to avoid check. Otherwise, that side loses</t>
+          <t>A captured piece is removed from the board. &lt;b&gt;Chasing one piece for more than 6 consecutive moves is not allowed&lt;/b&gt;.</t>
         </is>
       </c>
       <c r="C368" s="2" t="inlineStr">
         <is>
-          <t>Nếu người chơi thực hiện một nước đi đe dọa bắt Tướng của đối phương ở nước đi tiếp theo (bằng chính quân cờ đó hoặc một quân cờ khác), thì đó được gọi là &lt;b&gt;Chiếu&lt;/b&gt;. Bên bị chiếu phải đáp trả để tránh bị chiếu. Nếu không sẽ bị xử thua</t>
+          <t>Quân bị bắt phải bị loại và bị nhấc ra khỏi bàn cờ. &lt;b&gt;Không được đuổi 1 quân quá 6 nước cờ liên tiếp&lt;/b&gt;.</t>
         </is>
       </c>
     </row>
     <row r="369" ht="17" customHeight="1">
       <c r="A369" s="2" t="inlineStr">
         <is>
-          <t>guide.check.paragraph2</t>
+          <t>guide.check.paragraph1</t>
         </is>
       </c>
       <c r="B369" s="2" t="inlineStr">
         <is>
-          <t>When the General is checked from any direction (including from behind), the checked side may respond in one of the following ways:</t>
+          <t>If a player makes a move that threatens to capture the opponent's General on the next move (by the same piece or another piece), it is called a &lt;b&gt;Check&lt;/b&gt;. The checked side must respond to avoid check. Otherwise, that side loses</t>
         </is>
       </c>
       <c r="C369" s="2" t="inlineStr">
         <is>
-          <t>Tướng bị chiếu từ cả bốn hướng (bị chiếu cả từ phía sau) có thể ứng phó với nước chiếu tướng bằng một trong các cách sau:</t>
+          <t>Nếu người chơi thực hiện một nước đi đe dọa bắt Tướng của đối phương ở nước đi tiếp theo (bằng chính quân cờ đó hoặc một quân cờ khác), thì đó được gọi là &lt;b&gt;Chiếu&lt;/b&gt;. Bên bị chiếu phải đáp trả để tránh bị chiếu. Nếu không sẽ bị xử thua</t>
         </is>
       </c>
     </row>
     <row r="370" ht="17" customHeight="1">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>guide.check.paragraph3</t>
+          <t>guide.check.paragraph2</t>
         </is>
       </c>
       <c r="B370" s="2" t="inlineStr">
         <is>
-          <t>Move the General to another position to escape check</t>
+          <t>When the General is checked from any direction (including from behind), the checked side may respond in one of the following ways:</t>
         </is>
       </c>
       <c r="C370" s="2" t="inlineStr">
         <is>
-          <t>Di chuyển tướng sang vị trí khác để tránh nước chiếu</t>
+          <t>Tướng bị chiếu từ cả bốn hướng (bị chiếu cả từ phía sau) có thể ứng phó với nước chiếu tướng bằng một trong các cách sau:</t>
         </is>
       </c>
     </row>
     <row r="371" ht="17" customHeight="1">
       <c r="A371" s="2" t="inlineStr">
         <is>
-          <t>guide.check.paragraph4</t>
+          <t>guide.check.paragraph3</t>
         </is>
       </c>
       <c r="B371" s="2" t="inlineStr">
         <is>
-          <t>Capture the checking piece</t>
+          <t>Move the General to another position to escape check</t>
         </is>
       </c>
       <c r="C371" s="2" t="inlineStr">
         <is>
-          <t>Bắt quân đang chiếu</t>
+          <t>Di chuyển tướng sang vị trí khác để tránh nước chiếu</t>
         </is>
       </c>
     </row>
     <row r="372" ht="17" customHeight="1">
       <c r="A372" s="2" t="inlineStr">
         <is>
-          <t>guide.check.paragraph5</t>
+          <t>guide.check.paragraph4</t>
         </is>
       </c>
       <c r="B372" s="2" t="inlineStr">
         <is>
-          <t>Block the checking line with another piece to protect the General</t>
+          <t>Capture the checking piece</t>
         </is>
       </c>
       <c r="C372" s="2" t="inlineStr">
         <is>
-          <t>Dùng quân khác cản quân chiếu, đi quân che đỡ cho tướng</t>
+          <t>Bắt quân đang chiếu</t>
         </is>
       </c>
     </row>
     <row r="373" ht="17" customHeight="1">
       <c r="A373" s="2" t="inlineStr">
         <is>
-          <t>guide.check.paragraph6</t>
+          <t>guide.check.paragraph5</t>
         </is>
       </c>
       <c r="B373" s="2" t="inlineStr">
         <is>
-          <t>Repeatedly checking for more than 6 consecutive moves is not allowed</t>
+          <t>Block the checking line with another piece to protect the General</t>
         </is>
       </c>
       <c r="C373" s="2" t="inlineStr">
         <is>
-          <t>Không được chiếu tướng quá 6 nước cờ liên tiếp</t>
+          <t>Dùng quân khác cản quân chiếu, đi quân che đỡ cho tướng</t>
         </is>
       </c>
     </row>
     <row r="374" ht="17" customHeight="1">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>guide.result.paragraph1</t>
+          <t>guide.check.paragraph6</t>
         </is>
       </c>
       <c r="B374" s="2" t="inlineStr">
         <is>
-          <t>When one side gives Check and the other side has no legal way to protect the General, it is called a &lt;b&gt;Checkmate&lt;/b&gt;. The side that delivers Checkmate wins.</t>
+          <t>Repeatedly checking for more than 6 consecutive moves is not allowed</t>
         </is>
       </c>
       <c r="C374" s="2" t="inlineStr">
         <is>
-          <t>Khi một bên chiếu Tướng mà bên còn lại không thể làm gì để bảo vệ Tướng thì được gọi là &lt;b&gt;Chiếu Hết&lt;/b&gt;, bên thực hiện được Chiếu Hết sẽ giành chiến thắng.</t>
+          <t>Không được chiếu tướng quá 6 nước cờ liên tiếp</t>
         </is>
       </c>
     </row>
     <row r="375" ht="17" customHeight="1">
       <c r="A375" s="2" t="inlineStr">
         <is>
-          <t>guide.result.paragraph2</t>
+          <t>guide.result.paragraph1</t>
         </is>
       </c>
       <c r="B375" s="2" t="inlineStr">
         <is>
-          <t>If a player runs out of time for a single move (for example: 90s) without moving, the other side is awarded a &lt;b&gt;win&lt;/b&gt;.</t>
+          <t>When one side gives Check and the other side has no legal way to protect the General, it is called a &lt;b&gt;Checkmate&lt;/b&gt;. The side that delivers Checkmate wins.</t>
         </is>
       </c>
       <c r="C375" s="2" t="inlineStr">
         <is>
-          <t>Khi hết thời gian một nước đi (ví dụ: 90s) mà vẫn chưa di chuyển quân thì bên còn lại sẽ được &lt;b&gt;xử Thắng&lt;/b&gt;.</t>
+          <t>Khi một bên chiếu Tướng mà bên còn lại không thể làm gì để bảo vệ Tướng thì được gọi là &lt;b&gt;Chiếu Hết&lt;/b&gt;, bên thực hiện được Chiếu Hết sẽ giành chiến thắng.</t>
         </is>
       </c>
     </row>
     <row r="376" ht="17" customHeight="1">
       <c r="A376" s="2" t="inlineStr">
         <is>
-          <t>guide.result.paragraph3</t>
+          <t>guide.result.paragraph2</t>
         </is>
       </c>
       <c r="B376" s="2" t="inlineStr">
         <is>
-          <t>If a player runs out of total game time (for example: 5 minutes or 10 minutes), the other side is awarded a &lt;b&gt;win&lt;/b&gt;.</t>
+          <t>If a player runs out of time for a single move (for example: 90s) without moving, the other side is awarded a &lt;b&gt;win&lt;/b&gt;.</t>
         </is>
       </c>
       <c r="C376" s="2" t="inlineStr">
         <is>
-          <t>Khi một bên hết thời gian ván đấu (ví dụ: 5 phút, 10 phút) thì bên còn lại sẽ được &lt;b&gt;xử Thắng&lt;/b&gt;.</t>
+          <t>Khi hết thời gian một nước đi (ví dụ: 90s) mà vẫn chưa di chuyển quân thì bên còn lại sẽ được &lt;b&gt;xử Thắng&lt;/b&gt;.</t>
         </is>
       </c>
     </row>
     <row r="377" ht="17" customHeight="1">
       <c r="A377" s="2" t="inlineStr">
         <is>
-          <t>guide.result.paragraph4</t>
+          <t>guide.result.paragraph3</t>
         </is>
       </c>
       <c r="B377" s="2" t="inlineStr">
         <is>
-          <t>If both sides have no pieces that have crossed the river, the game is declared a &lt;b&gt;draw&lt;/b&gt;. If one side still has pieces across the river but runs out of time, while the other side still has time but has no pieces across the river, the game is declared a &lt;b&gt;draw&lt;/b&gt;.</t>
+          <t>If a player runs out of total game time (for example: 5 minutes or 10 minutes), the other side is awarded a &lt;b&gt;win&lt;/b&gt;.</t>
         </is>
       </c>
       <c r="C377" s="2" t="inlineStr">
         <is>
-          <t>Khi cả 2 bên đều không còn quân qua sông, ván đấu sẽ được &lt;b&gt;xử Hòa&lt;/b&gt;. Khi một bên còn quân qua sông nhưng cạn thời gian, một bên còn thời gian nhưng hết quân qua sông, ván đấu sẽ được &lt;b&gt;xử Hòa&lt;/b&gt;.</t>
+          <t>Khi một bên hết thời gian ván đấu (ví dụ: 5 phút, 10 phút) thì bên còn lại sẽ được &lt;b&gt;xử Thắng&lt;/b&gt;.</t>
         </is>
       </c>
     </row>
     <row r="378" ht="17" customHeight="1">
       <c r="A378" s="2" t="inlineStr">
         <is>
-          <t>guide.result.paragraph5</t>
+          <t>guide.result.paragraph4</t>
         </is>
       </c>
       <c r="B378" s="2" t="inlineStr">
         <is>
-          <t>Within 40 moves, if there is no capture and no Soldier advances by one square, the game is declared a &lt;b&gt;draw&lt;/b&gt;.</t>
+          <t>If both sides have no pieces that have crossed the river, the game is declared a &lt;b&gt;draw&lt;/b&gt;. If one side still has pieces across the river but runs out of time, while the other side still has time but has no pieces across the river, the game is declared a &lt;b&gt;draw&lt;/b&gt;.</t>
         </is>
       </c>
       <c r="C378" s="2" t="inlineStr">
         <is>
-          <t>Trong vòng 40 nước nếu không phát sinh nước bắt quân, Tốt không tiến 1 ô thì ván đấu sẽ được &lt;b&gt;xử Hòa&lt;/b&gt;.</t>
+          <t>Khi cả 2 bên đều không còn quân qua sông, ván đấu sẽ được &lt;b&gt;xử Hòa&lt;/b&gt;. Khi một bên còn quân qua sông nhưng cạn thời gian, một bên còn thời gian nhưng hết quân qua sông, ván đấu sẽ được &lt;b&gt;xử Hòa&lt;/b&gt;.</t>
         </is>
       </c>
     </row>
     <row r="379" ht="17" customHeight="1">
       <c r="A379" s="2" t="inlineStr">
         <is>
-          <t>extra-money.title</t>
+          <t>guide.result.paragraph5</t>
         </is>
       </c>
       <c r="B379" s="2" t="inlineStr">
         <is>
-          <t>Daily tasks</t>
+          <t>Within 40 moves, if there is no capture and no Soldier advances by one square, the game is declared a &lt;b&gt;draw&lt;/b&gt;.</t>
         </is>
       </c>
       <c r="C379" s="2" t="inlineStr">
         <is>
-          <t>Kiếm tiền</t>
+          <t>Trong vòng 40 nước nếu không phát sinh nước bắt quân, Tốt không tiến 1 ô thì ván đấu sẽ được &lt;b&gt;xử Hòa&lt;/b&gt;.</t>
         </is>
       </c>
     </row>
     <row r="380" ht="17" customHeight="1">
       <c r="A380" s="2" t="inlineStr">
         <is>
-          <t>extra-money.tab.lucky-wheel</t>
+          <t>extra-money.title</t>
         </is>
       </c>
       <c r="B380" s="2" t="inlineStr">
         <is>
-          <t>Lucky Wheel</t>
+          <t>Daily tasks</t>
         </is>
       </c>
       <c r="C380" s="2" t="inlineStr">
         <is>
-          <t>Vòng Quay May Mắn</t>
+          <t>Kiếm tiền</t>
         </is>
       </c>
     </row>
     <row r="381" ht="17" customHeight="1">
       <c r="A381" s="2" t="inlineStr">
         <is>
-          <t>extra-money.tab.bonus-coin</t>
+          <t>extra-money.tab.lucky-wheel</t>
         </is>
       </c>
       <c r="B381" s="2" t="inlineStr">
         <is>
-          <t>Bonus Coin</t>
+          <t>Lucky Wheel</t>
         </is>
       </c>
       <c r="C381" s="2" t="inlineStr">
         <is>
-          <t>Xu Thưởng</t>
+          <t>Vòng Quay May Mắn</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>extra-money.tab.daily-bonus</t>
+          <t>extra-money.tab.bonus-coin</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Daily Bonus</t>
+          <t>Bonus Coin</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Thưởng hàng ngày</t>
+          <t>Xu Thưởng</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>extra-money.bonus-coin.subtitle</t>
+          <t>extra-money.tab.daily-bonus</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Watch a short video to earn free coin</t>
+          <t>Daily Bonus</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Xem video ngắn để nhận xu miễn phí</t>
+          <t>Thưởng hàng ngày</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>extra-money.bonus-coin.next-in</t>
+          <t>extra-money.bonus-coin.subtitle</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Next in:</t>
+          <t>Watch a short video to earn free coin</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Lượt kế tiếp:</t>
+          <t>Xem video ngắn để nhận xu miễn phí</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>extra-money.bonus-coin.collect</t>
+          <t>extra-money.bonus-coin.next-in</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Collect</t>
+          <t>Next in:</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Thu thập</t>
+          <t>Lượt kế tiếp:</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>extra-money.bonus-coin.watch-video</t>
+          <t>extra-money.bonus-coin.collect</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Watch video</t>
+          <t>Collect</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Xem video</t>
+          <t>Thu thập</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>extra-money.daily-bonus.subtitle</t>
+          <t>extra-money.bonus-coin.watch-video</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Login 7 days in a row to earn 4000 coin</t>
+          <t>Watch video</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Đăng nhập 7 ngày liên tiếp để nhận 4000 xu</t>
+          <t>Xem video</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>extra-money.daily-bonus.day</t>
+          <t>extra-money.daily-bonus.subtitle</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Login 7 days in a row to earn 4000 coin</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Ngày</t>
+          <t>Đăng nhập 7 ngày liên tiếp để nhận 4000 xu</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>extra-money.reward-ad.loading</t>
+          <t>extra-money.daily-bonus.day</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Loading ad...</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Đang tải quảng cáo...</t>
+          <t>Ngày</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>extra-money.reward-ad.error</t>
+          <t>extra-money.reward-ad.loading</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Could not load the ad. Please try again.</t>
+          <t>Loading ad...</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Không tải được quảng cáo. Vui lòng thử lại.</t>
+          <t>Đang tải quảng cáo...</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>extra-money.reward-ad.retry</t>
+          <t>extra-money.reward-ad.error</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Try again</t>
+          <t>Could not load the ad. Please try again.</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Thử lại</t>
+          <t>Không tải được quảng cáo. Vui lòng thử lại.</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>extra-money.reward-ad.close</t>
+          <t>extra-money.reward-ad.retry</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Close</t>
+          <t>Try again</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Đóng</t>
+          <t>Thử lại</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>profile.button.save</t>
+          <t>extra-money.reward-ad.close</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Save</t>
+          <t>Close</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Lưu</t>
+          <t>Đóng</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>profile.button.cancel</t>
+          <t>profile.button.save</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Save</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Huỷ</t>
+          <t>Lưu</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>change-password.title</t>
+          <t>profile.button.cancel</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Change password</t>
+          <t>Cancel</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Đổi mật khẩu</t>
+          <t>Huỷ</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>change-password.current.label</t>
+          <t>change-password.title</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Current password</t>
+          <t>Change password</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Mật khẩu hiện tại</t>
+          <t>Đổi mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>change-password.current.placeholder</t>
+          <t>change-password.current.label</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Enter current password</t>
+          <t>Current password</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Nhập mật khẩu hiện tại</t>
+          <t>Mật khẩu hiện tại</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>change-password.new.label</t>
+          <t>change-password.current.placeholder</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>New password</t>
+          <t>Enter current password</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Mật khẩu mới</t>
+          <t>Nhập mật khẩu hiện tại</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>change-password.new.placeholder</t>
+          <t>change-password.new.label</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Enter new password</t>
+          <t>New password</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Nhập mật khẩu mới</t>
+          <t>Mật khẩu mới</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>change-password.confirm.label</t>
+          <t>change-password.new.placeholder</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Confirm new password</t>
+          <t>Enter new password</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Xác nhận mật khẩu mới</t>
+          <t>Nhập mật khẩu mới</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>change-password.confirm.placeholder</t>
+          <t>change-password.confirm.label</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Re-enter new password</t>
+          <t>Confirm new password</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Nhập lại mật khẩu mới</t>
+          <t>Xác nhận mật khẩu mới</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>change-password.confirm.mismatch</t>
+          <t>change-password.confirm.placeholder</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Passwords do not match</t>
+          <t>Re-enter new password</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Mật khẩu xác nhận không khớp</t>
+          <t>Nhập lại mật khẩu mới</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>change-password.show</t>
+          <t>change-password.confirm.mismatch</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Show password</t>
+          <t>Passwords do not match</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Hiện mật khẩu</t>
+          <t>Mật khẩu xác nhận không khớp</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>change-password.hide</t>
+          <t>change-password.show</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Hide password</t>
+          <t>Show password</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Ẩn mật khẩu</t>
+          <t>Hiện mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>change-password.submit</t>
+          <t>change-password.hide</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Change password</t>
+          <t>Hide password</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Đổi mật khẩu</t>
+          <t>Ẩn mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>change-password.submitting</t>
+          <t>change-password.submit</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Changing...</t>
+          <t>Change password</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Đang đổi...</t>
+          <t>Đổi mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>change-password.messages.success</t>
+          <t>change-password.submitting</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Password changed successfully</t>
+          <t>Changing...</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Đổi mật khẩu thành công</t>
+          <t>Đang đổi...</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>change-password.messages.missing-fields</t>
+          <t>change-password.messages.success</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Please fill in all fields</t>
+          <t>Password changed successfully</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Vui lòng nhập đầy đủ thông tin</t>
+          <t>Đổi mật khẩu thành công</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>change-password.messages.weak-password</t>
+          <t>change-password.messages.missing-fields</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>New password does not meet the requirements</t>
+          <t>Please fill in all fields</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Mật khẩu mới không đạt yêu cầu</t>
+          <t>Vui lòng nhập đầy đủ thông tin</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>change-password.messages.same-as-current</t>
+          <t>change-password.messages.weak-password</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>New password must be different from the current one</t>
+          <t>New password does not meet the requirements</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Mật khẩu mới phải khác mật khẩu hiện tại</t>
+          <t>Mật khẩu mới không đạt yêu cầu</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>change-password.messages.incorrect-current-password</t>
+          <t>change-password.messages.same-as-current</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Current password is incorrect</t>
+          <t>New password must be different from the current one</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Mật khẩu hiện tại không đúng</t>
+          <t>Mật khẩu mới phải khác mật khẩu hiện tại</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>change-password.messages.user-not-found</t>
+          <t>change-password.messages.incorrect-current-password</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>User not found</t>
+          <t>Current password is incorrect</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Không tìm thấy người dùng</t>
+          <t>Mật khẩu hiện tại không đúng</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>change-password.messages.unauthorized</t>
+          <t>change-password.messages.user-not-found</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Session expired. Please sign in again.</t>
+          <t>User not found</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Phiên đăng nhập đã hết hạn. Vui lòng đăng nhập lại.</t>
+          <t>Không tìm thấy người dùng</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
+          <t>change-password.messages.unauthorized</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Session expired. Please sign in again.</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>Phiên đăng nhập đã hết hạn. Vui lòng đăng nhập lại.</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
           <t>change-password.messages.internal-server-error</t>
         </is>
       </c>
-      <c r="B414" t="inlineStr">
+      <c r="B415" t="inlineStr">
         <is>
           <t>Something went wrong. Please try again.</t>
         </is>
       </c>
-      <c r="C414" t="inlineStr">
+      <c r="C415" t="inlineStr">
         <is>
           <t>Đã có lỗi xảy ra. Vui lòng thử lại.</t>
         </is>
       </c>
-    </row>
-    <row r="415">
-      <c r="A415" t="inlineStr"/>
-      <c r="B415" t="inlineStr"/>
-      <c r="C415" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr"/>
@@ -7465,6 +7477,11 @@
       <c r="A433" t="inlineStr"/>
       <c r="B433" t="inlineStr"/>
       <c r="C433" t="inlineStr"/>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr"/>
+      <c r="B434" t="inlineStr"/>
+      <c r="C434" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tools/languages.xlsx
+++ b/tools/languages.xlsx
@@ -325,7 +325,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C433"/>
+  <dimension ref="A1:C462"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -727,3237 +727,3237 @@
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>menu.app-name</t>
+          <t>page.replay.end-title</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Xiangqi</t>
+          <t>Game over</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Cờ tướng</t>
+          <t>Ván đấu kết thúc</t>
         </is>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>menu.profile</t>
+          <t>page.replay.reason-checkmate</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>{{name}} won by checkmate</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Trang cá nhân</t>
+          <t>{{name}} thắng bằng chiếu bí</t>
         </is>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>menu.messages</t>
+          <t>page.replay.reason-stalemate</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Message</t>
+          <t>Stalemate</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Tin nhắn</t>
+          <t>Hết nước đi</t>
         </is>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>menu.change-password</t>
+          <t>page.replay.reason-perpetual-check</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Change password</t>
+          <t>{{name}} won by opponent's perpetual check</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Đổi mật khẩu</t>
+          <t>{{name}} thắng do đối thủ chiếu tướng liên tục</t>
         </is>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>menu.guide</t>
+          <t>page.replay.reason-surrender</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Guide</t>
+          <t>{{name}} surrendered</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Luật chơi</t>
+          <t>{{name}} đã đầu hàng</t>
         </is>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>menu.announce</t>
+          <t>page.replay.reason-leave</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Announcement</t>
+          <t>{{name}} left the game</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Thông báo</t>
+          <t>{{name}} đã rời trận</t>
         </is>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>menu.extra</t>
+          <t>page.replay.reason-draw</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Daily tasks</t>
+          <t>Draw</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Kiếm tiền</t>
+          <t>Hoà</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>menu.setting.button</t>
+          <t>page.replay.reason-timeout</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>{{name}} ran out of time</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Cài đặt</t>
+          <t>{{name}} đã hết giờ</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>menu.app-name</t>
+          <t>page.replay.reason-ended</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Xiangqi</t>
+          <t>The game has ended</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Cờ tướng</t>
+          <t>Ván đấu đã kết thúc</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>menu.home</t>
+          <t>menu.app-name</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Xiangqi</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Trang chủ</t>
+          <t>Cờ tướng</t>
         </is>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>menu.expired</t>
+          <t>menu.profile</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Set expired</t>
+          <t>Profile</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Hết hạn token</t>
+          <t>Trang cá nhân</t>
         </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>menu.logout</t>
+          <t>menu.messages</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Logout</t>
+          <t>Message</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Đăng xuất</t>
+          <t>Tin nhắn</t>
         </is>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>announce.title</t>
+          <t>menu.change-password</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Announcement</t>
+          <t>Change password</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Thông báo</t>
+          <t>Đổi mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>announce.placeholder</t>
+          <t>menu.guide</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Type an announcement...</t>
+          <t>Guide</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Nhập thông báo...</t>
+          <t>Luật chơi</t>
         </is>
       </c>
     </row>
     <row r="38" ht="36" customHeight="1">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>announce.empty</t>
+          <t>menu.announce</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>No announcements yet</t>
+          <t>Announcement</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Chưa có thông báo nào</t>
+          <t>Thông báo</t>
         </is>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>announce.loading-older</t>
+          <t>menu.extra</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Loading older announcements...</t>
+          <t>Daily tasks</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Đang tải thông báo cũ hơn...</t>
+          <t>Kiếm tiền</t>
         </is>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>achievement.title-01</t>
+          <t>menu.setting.button</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Checkmate an opponent who still has 13 or more pieces</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Chiếu bí khi đối thủ vẫn còn &gt;= 13 quân</t>
+          <t>Cài đặt</t>
         </is>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>achievement.title-02</t>
+          <t>menu.app-name</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Win your first game</t>
+          <t>Xiangqi</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Thắng trận đầu khi chơi game</t>
+          <t>Cờ tướng</t>
         </is>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>achievement.title-03</t>
+          <t>menu.home</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Leave your opponent with no legal moves</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Đánh cho đối thủ không còn nước đi</t>
+          <t>Trang chủ</t>
         </is>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>achievement.title-04</t>
+          <t>menu.expired</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Defeat opponents of equal or higher rank in 10 games</t>
+          <t>Set expired</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Thắng đối thủ cùng hoặc hơn đẳng cấp 10 ván</t>
+          <t>Hết hạn token</t>
         </is>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>achievement.title-05</t>
+          <t>menu.logout</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Hold a draw with only your king remaining</t>
+          <t>Logout</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Cầm hoà đối thủ khi chỉ còn tướng</t>
+          <t>Đăng xuất</t>
         </is>
       </c>
     </row>
     <row r="45" ht="36" customHeight="1">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>achievement.title-06</t>
+          <t>announce.title</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Win 100 games</t>
+          <t>Announcement</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Thắng 100 trận</t>
+          <t>Thông báo</t>
         </is>
       </c>
     </row>
     <row r="46" ht="36" customHeight="1">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>achievement.title-07</t>
+          <t>announce.placeholder</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Draw 50 games</t>
+          <t>Type an announcement...</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Hoà 50 trận</t>
+          <t>Nhập thông báo...</t>
         </is>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>achievement.title-08</t>
+          <t>announce.empty</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Checkmate an opponent with only 1 attacking piece remaining</t>
+          <t>No announcements yet</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Chiếu bí khi đối thủ khi chỉ còn 1 quân tấn công</t>
+          <t>Chưa có thông báo nào</t>
         </is>
       </c>
     </row>
     <row r="48" ht="36" customHeight="1">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>achievement.title-09</t>
+          <t>announce.loading-older</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Checkmate an opponent with only a knight remaining</t>
+          <t>Loading older announcements...</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Chiếu bí khi đối thủ khi chỉ còn mã</t>
+          <t>Đang tải thông báo cũ hơn...</t>
         </is>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>achievement.title-10</t>
+          <t>achievement.title-01</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Checkmate an opponent with only a pawn remaining</t>
+          <t>Checkmate an opponent who still has 13 or more pieces</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Chiếu bí khi đối thủ khi chỉ còn tốt</t>
+          <t>Chiếu bí khi đối thủ vẫn còn &gt;= 13 quân</t>
         </is>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>achievement.title-11</t>
+          <t>achievement.title-02</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Checkmate an opponent with only a cannon remaining</t>
+          <t>Win your first game</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Chiếu bí khi đối thủ khi chỉ còn pháo</t>
+          <t>Thắng trận đầu khi chơi game</t>
         </is>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>achievement.title-12</t>
+          <t>achievement.title-03</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Defeat opponents with master rank in 50 games</t>
+          <t>Leave your opponent with no legal moves</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Thắng đối thủ có đẳng cấp kỳ thủ 50 ván</t>
+          <t>Đánh cho đối thủ không còn nước đi</t>
         </is>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>achievement.tab-title</t>
+          <t>achievement.title-04</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Achievements</t>
+          <t>Defeat opponents of equal or higher rank in 10 games</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Thành tựu</t>
+          <t>Thắng đối thủ cùng hoặc hơn đẳng cấp 10 ván</t>
         </is>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>achievement.messages.success</t>
+          <t>achievement.title-05</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Success</t>
+          <t>Hold a draw with only your king remaining</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Thành công</t>
+          <t>Cầm hoà đối thủ khi chỉ còn tướng</t>
         </is>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>achievement.messages.invalid-user-id</t>
+          <t>achievement.title-06</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Invalid user ID</t>
+          <t>Win 100 games</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>ID người dùng không hợp lệ</t>
+          <t>Thắng 100 trận</t>
         </is>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>achievement.messages.internal-server-error</t>
+          <t>achievement.title-07</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Draw 50 games</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ</t>
+          <t>Hoà 50 trận</t>
         </is>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>chat.conversation.you</t>
+          <t>achievement.title-08</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>You</t>
+          <t>Checkmate an opponent with only 1 attacking piece remaining</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Bạn</t>
+          <t>Chiếu bí khi đối thủ khi chỉ còn 1 quân tấn công</t>
         </is>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>chat.messages.unread</t>
+          <t>achievement.title-09</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Unread messages</t>
+          <t>Checkmate an opponent with only a knight remaining</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Tin nhắn chưa đọc</t>
+          <t>Chiếu bí khi đối thủ khi chỉ còn mã</t>
         </is>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>search.user.title</t>
+          <t>achievement.title-10</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Search user</t>
+          <t>Checkmate an opponent with only a pawn remaining</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Tìm kiếm</t>
+          <t>Chiếu bí khi đối thủ khi chỉ còn tốt</t>
         </is>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>search.user.placeholder</t>
+          <t>achievement.title-11</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Search user...</t>
+          <t>Checkmate an opponent with only a cannon remaining</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Tìm kiếm người dùng...</t>
+          <t>Chiếu bí khi đối thủ khi chỉ còn pháo</t>
         </is>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>search.user.no-results</t>
+          <t>achievement.title-12</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>No users found</t>
+          <t>Defeat opponents with master rank in 50 games</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy người dùng</t>
+          <t>Thắng đối thủ có đẳng cấp kỳ thủ 50 ván</t>
         </is>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>search.button.search</t>
+          <t>achievement.tab-title</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>Achievements</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Tìm kiếm</t>
+          <t>Thành tựu</t>
         </is>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>dashboard.page.title</t>
+          <t>achievement.messages.success</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Room list</t>
+          <t>Success</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Danh sách phòng</t>
+          <t>Thành công</t>
         </is>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>dashboard.filters.all</t>
+          <t>achievement.messages.invalid-user-id</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Invalid user ID</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Tất cả</t>
+          <t>ID người dùng không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>dashboard.filters.available</t>
+          <t>achievement.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Available</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Chờ</t>
+          <t>Lỗi máy chủ</t>
         </is>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>dashboard.filters.playing</t>
+          <t>chat.conversation.you</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Playing</t>
+          <t>You</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Đang chơi</t>
+          <t>Bạn</t>
         </is>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>dashboard.feedback.empty</t>
+          <t>chat.messages.unread</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>No room tables match the selected filter.</t>
+          <t>Unread messages</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Không có bàn chơi phù hợp với bộ lọc đã chọn.</t>
+          <t>Tin nhắn chưa đọc</t>
         </is>
       </c>
     </row>
     <row r="67" ht="18" customHeight="1">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>dashboard.feedback.error</t>
+          <t>search.user.title</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Unable to load room tables.</t>
+          <t>Search user</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Không tải được danh sách phòng chơi.</t>
+          <t>Tìm kiếm</t>
         </is>
       </c>
     </row>
     <row r="68" ht="18" customHeight="1">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>dashboard.status.unknown</t>
+          <t>search.user.placeholder</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Search user...</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Không xác định</t>
+          <t>Tìm kiếm người dùng...</t>
         </is>
       </c>
     </row>
     <row r="69" ht="18" customHeight="1">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>dashboard.room.create</t>
+          <t>search.user.no-results</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Create room</t>
+          <t>No users found</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Tạo phòng chơi</t>
+          <t>Không tìm thấy người dùng</t>
         </is>
       </c>
     </row>
     <row r="70" ht="18" customHeight="1">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>dashboard.popup.piece-selection</t>
+          <t>search.button.search</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Select team</t>
+          <t>Search</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Chọn quân</t>
+          <t>Tìm kiếm</t>
         </is>
       </c>
     </row>
     <row r="71" ht="18" customHeight="1">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>dashboard.popup.red-first</t>
+          <t>dashboard.page.title</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Red first</t>
+          <t>Room list</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Đỏ tiên</t>
+          <t>Danh sách phòng</t>
         </is>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>dashboard.popup.pve-mode</t>
+          <t>dashboard.filters.all</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>PVE mode</t>
+          <t>All</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Chơi với máy</t>
+          <t>Tất cả</t>
         </is>
       </c>
     </row>
     <row r="73" ht="18" customHeight="1">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>dashboard.popup.bet-amount</t>
+          <t>dashboard.filters.available</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Bet amount</t>
+          <t>Available</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>Giá trị cược</t>
+          <t>Chờ</t>
         </is>
       </c>
     </row>
     <row r="74" ht="18" customHeight="1">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>dashboard.popup.time-limit</t>
+          <t>dashboard.filters.playing</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Time per player</t>
+          <t>Playing</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>Thời gian mỗi người</t>
+          <t>Đang chơi</t>
         </is>
       </c>
     </row>
     <row r="75" ht="18" customHeight="1">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>dashboard.popup.time-unlimited</t>
+          <t>dashboard.feedback.empty</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Unlimited</t>
+          <t>No room tables match the selected filter.</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>Không giới hạn</t>
+          <t>Không có bàn chơi phù hợp với bộ lọc đã chọn.</t>
         </is>
       </c>
     </row>
     <row r="76" ht="18" customHeight="1">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>dashboard.popup.time-minutes</t>
+          <t>dashboard.feedback.error</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>{0} min</t>
+          <t>Unable to load room tables.</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>{0} phút</t>
+          <t>Không tải được danh sách phòng chơi.</t>
         </is>
       </c>
     </row>
     <row r="77" ht="18" customHeight="1">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>dashboard.popup.room-name-label</t>
+          <t>dashboard.status.unknown</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Room table name</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Tên phòng chơi</t>
+          <t>Không xác định</t>
         </is>
       </c>
     </row>
     <row r="78" ht="18" customHeight="1">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>dashboard.popup.room-name-helptext</t>
+          <t>dashboard.room.create</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>is required</t>
+          <t>Create room</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>không được để trống</t>
+          <t>Tạo phòng chơi</t>
         </is>
       </c>
     </row>
     <row r="79" ht="18" customHeight="1">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>dashboard.popup.play</t>
+          <t>dashboard.popup.piece-selection</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Play</t>
+          <t>Select team</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Chơi</t>
+          <t>Chọn quân</t>
         </is>
       </c>
     </row>
     <row r="80" ht="18" customHeight="1">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>dashboard.popup.view</t>
+          <t>dashboard.popup.red-first</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>View</t>
+          <t>Red first</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Xem</t>
+          <t>Đỏ tiên</t>
         </is>
       </c>
     </row>
     <row r="81" ht="18" customHeight="1">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>settings.header</t>
+          <t>dashboard.popup.pve-mode</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>PVE mode</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Cài đặt</t>
+          <t>Chơi với máy</t>
         </is>
       </c>
     </row>
     <row r="82" ht="18" customHeight="1">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>settings.language</t>
+          <t>dashboard.popup.bet-amount</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>Bet amount</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Ngôn ngữ</t>
+          <t>Giá trị cược</t>
         </is>
       </c>
     </row>
     <row r="83" ht="18" customHeight="1">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>settings.dark-mode</t>
+          <t>dashboard.popup.time-limit</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Dark mode</t>
+          <t>Time limit</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Chế độ tối</t>
+          <t>Giới hạn thời gian</t>
         </is>
       </c>
     </row>
     <row r="84" ht="18" customHeight="1">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>settings.debug-mode</t>
+          <t>dashboard.popup.time-limit-per-player</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Debug mode</t>
+          <t>Time per player</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Chế độ test</t>
+          <t>Thời gian mỗi người</t>
         </is>
       </c>
     </row>
     <row r="85" ht="18" customHeight="1">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>settings.connected-accounts.label</t>
+          <t>dashboard.popup.time-unlimited</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Connected accounts</t>
+          <t>Unlimited</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản liên kết</t>
+          <t>Không giới hạn</t>
         </is>
       </c>
     </row>
     <row r="86" ht="18" customHeight="1">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>settings.connected-accounts.link-facebook</t>
+          <t>dashboard.popup.time-minutes</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Link Facebook</t>
+          <t>{0} min</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Liên kết Facebook</t>
+          <t>{0} phút</t>
         </is>
       </c>
     </row>
     <row r="87" ht="18" customHeight="1">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>settings.connected-accounts.unlink-facebook</t>
+          <t>dashboard.popup.time-seconds</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Unlink Facebook</t>
+          <t>{0}s</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Huỷ liên kết Facebook</t>
+          <t>{0}s</t>
         </is>
       </c>
     </row>
     <row r="88" ht="18" customHeight="1">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>settings.connected-accounts.link-success</t>
+          <t>dashboard.popup.time-off</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Facebook linked successfully</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Đã liên kết Facebook</t>
+          <t>Tắt</t>
         </is>
       </c>
     </row>
     <row r="89" ht="18" customHeight="1">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>settings.connected-accounts.unlink-success</t>
+          <t>dashboard.popup.time-increment</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Facebook unlinked</t>
+          <t>Bonus per move</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Đã huỷ liên kết Facebook</t>
+          <t>Cộng giờ mỗi nước</t>
         </is>
       </c>
     </row>
     <row r="90" ht="18" customHeight="1">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>settings.connected-accounts.link-error</t>
+          <t>dashboard.popup.time-per-move</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Could not update Facebook link</t>
+          <t>Time per move</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Không cập nhật được liên kết Facebook</t>
+          <t>Thời gian mỗi nước</t>
         </is>
       </c>
     </row>
     <row r="91" ht="18" customHeight="1">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>settings.close</t>
+          <t>dashboard.popup.room-name-label</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Close</t>
+          <t>Room table name</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Đóng</t>
+          <t>Tên phòng chơi</t>
         </is>
       </c>
     </row>
     <row r="92" ht="18" customHeight="1">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>popup.alert.title</t>
+          <t>dashboard.popup.room-name-helptext</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>is required</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Cảnh báo</t>
+          <t>không được để trống</t>
         </is>
       </c>
     </row>
     <row r="93" ht="18" customHeight="1">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>popup.confirm.title</t>
+          <t>dashboard.popup.play</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Confirm</t>
+          <t>Play</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Xác nhận</t>
+          <t>Chơi</t>
         </is>
       </c>
     </row>
     <row r="94" ht="18" customHeight="1">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>popup.confirm.ok</t>
+          <t>dashboard.popup.view</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Ok</t>
+          <t>View</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Ok</t>
+          <t>Xem</t>
         </is>
       </c>
     </row>
     <row r="95" ht="18" customHeight="1">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>popup.confirm.cancel</t>
+          <t>settings.header</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Huỷ</t>
+          <t>Cài đặt</t>
         </is>
       </c>
     </row>
     <row r="96" ht="18" customHeight="1">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>game.general.captured</t>
+          <t>settings.language</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>General has been captured. Room over</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Tướng đã bị bắt. Game kết thúc</t>
+          <t>Ngôn ngữ</t>
         </is>
       </c>
     </row>
     <row r="97" ht="18" customHeight="1">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>game.general.in-check</t>
+          <t>settings.dark-mode</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Your general is under attack</t>
+          <t>Dark mode</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Tướng của bạn đang bị chiếu</t>
+          <t>Chế độ tối</t>
         </is>
       </c>
     </row>
     <row r="98" ht="18" customHeight="1">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>game.label.win</t>
+          <t>settings.sound</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Win</t>
+          <t>Sound</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Thắng</t>
+          <t>Âm thanh</t>
         </is>
       </c>
     </row>
     <row r="99" ht="18" customHeight="1">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>game.label.draw</t>
+          <t>settings.debug-mode</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Draw</t>
+          <t>Debug mode</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Hoà</t>
+          <t>Chế độ test</t>
         </is>
       </c>
     </row>
     <row r="100" ht="18" customHeight="1">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>game.label.lose</t>
+          <t>settings.connected-accounts.label</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Lose</t>
+          <t>Connected accounts</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Thua</t>
+          <t>Tài khoản liên kết</t>
         </is>
       </c>
     </row>
     <row r="101" ht="18" customHeight="1">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>room.bot-difficulty.title</t>
+          <t>settings.connected-accounts.link-facebook</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Select Bot Difficulty</t>
+          <t>Link Facebook</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Chọn độ khó của Bot</t>
+          <t>Liên kết Facebook</t>
         </is>
       </c>
     </row>
     <row r="102" ht="18" customHeight="1">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>room.bot-difficulty.beginner</t>
+          <t>settings.connected-accounts.unlink-facebook</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Beginner</t>
+          <t>Unlink Facebook</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Mới bắt đầu</t>
+          <t>Huỷ liên kết Facebook</t>
         </is>
       </c>
     </row>
     <row r="103" ht="18" customHeight="1">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>room.bot-difficulty.amateur</t>
+          <t>settings.connected-accounts.link-success</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Amateur</t>
+          <t>Facebook linked successfully</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Nghiệp dư</t>
+          <t>Đã liên kết Facebook</t>
         </is>
       </c>
     </row>
     <row r="104" ht="18" customHeight="1">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>room.bot-difficulty.intermediate</t>
+          <t>settings.connected-accounts.unlink-success</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Intermediate</t>
+          <t>Facebook unlinked</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Trung bình</t>
+          <t>Đã huỷ liên kết Facebook</t>
         </is>
       </c>
     </row>
     <row r="105" ht="18" customHeight="1">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>room.bot-difficulty.advanced</t>
+          <t>settings.connected-accounts.link-error</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Advanced</t>
+          <t>Could not update Facebook link</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Nâng cao</t>
+          <t>Không cập nhật được liên kết Facebook</t>
         </is>
       </c>
     </row>
     <row r="106" ht="18" customHeight="1">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>room.bot-difficulty.master</t>
+          <t>settings.close</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Master</t>
+          <t>Close</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Lão luyện</t>
+          <t>Đóng</t>
         </is>
       </c>
     </row>
     <row r="107" ht="18" customHeight="1">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>login.page.title</t>
+          <t>popup.alert.title</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Login</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập</t>
+          <t>Cảnh báo</t>
         </is>
       </c>
     </row>
     <row r="108" ht="18" customHeight="1">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>login.form.title</t>
+          <t>popup.confirm.title</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Login</t>
+          <t>Confirm</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập</t>
+          <t>Xác nhận</t>
         </is>
       </c>
     </row>
     <row r="109" ht="18" customHeight="1">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>login.username.label</t>
+          <t>popup.confirm.ok</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>User name</t>
+          <t>Ok</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Tên người dùng</t>
+          <t>Ok</t>
         </is>
       </c>
     </row>
     <row r="110" ht="36" customHeight="1">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>login.username.placeholder</t>
+          <t>popup.confirm.cancel</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>User name</t>
+          <t>Cancel</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Tên người dùng</t>
+          <t>Huỷ</t>
         </is>
       </c>
     </row>
     <row r="111" ht="18" customHeight="1">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>login.password.label</t>
+          <t>game.general.captured</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Password</t>
+          <t>General has been captured. Room over</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Mật khẩu</t>
+          <t>Tướng đã bị bắt. Game kết thúc</t>
         </is>
       </c>
     </row>
     <row r="112" ht="18" customHeight="1">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>login.password.placeholder</t>
+          <t>game.general.in-check</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Password</t>
+          <t>Your general is under attack</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Mật khẩu</t>
+          <t>Tướng của bạn đang bị chiếu</t>
         </is>
       </c>
     </row>
     <row r="113" ht="18" customHeight="1">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>login.password.show</t>
+          <t>game.perpetual-check.warning-self</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Show password</t>
+          <t>You are perpetual checking. If you make one more repeated check, you will lose</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Hiện mật khẩu</t>
+          <t>Bạn đang chiếu quẩn, nếu thực hiện 1 nước nữa, bạn sẽ bị xử thua</t>
         </is>
       </c>
     </row>
     <row r="114" ht="18" customHeight="1">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>login.password.hide</t>
+          <t>game.perpetual-check.warning-sent</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Hide password</t>
+          <t>A perpetual-check warning has been sent to your opponent</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Ẩn mật khẩu</t>
+          <t>Đã gửi cảnh báo chiếu quẩn cho đối thủ</t>
         </is>
       </c>
     </row>
     <row r="115" ht="18" customHeight="1">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>login.form.error1</t>
+          <t>game.label.win</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Login failed. Please check your credentials </t>
+          <t>Win</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập không thành công. Hãy kiểm tra lại</t>
+          <t>Thắng</t>
         </is>
       </c>
     </row>
     <row r="116" ht="18" customHeight="1">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>login.form.forgot-password</t>
+          <t>game.label.draw</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Forgot password</t>
+          <t>Draw</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Quên mật khẩu</t>
+          <t>Hoà</t>
         </is>
       </c>
     </row>
     <row r="117" ht="18" customHeight="1">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>login.form.register</t>
+          <t>game.label.lose</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Register</t>
+          <t>Lose</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Đăng ký</t>
+          <t>Thua</t>
         </is>
       </c>
     </row>
     <row r="118" ht="18" customHeight="1">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>login.form.submit</t>
+          <t>room.bot-difficulty.title</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Login</t>
+          <t>Select Bot Difficulty</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập</t>
+          <t>Chọn độ khó của Bot</t>
         </is>
       </c>
     </row>
     <row r="119" ht="18" customHeight="1">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>login.form.or</t>
+          <t>room.bot-difficulty.beginner</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>or</t>
+          <t>Beginner</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>hoặc</t>
+          <t>Mới bắt đầu</t>
         </is>
       </c>
     </row>
     <row r="120" ht="18" customHeight="1">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>login.google.load-error</t>
+          <t>room.bot-difficulty.amateur</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Could not load Google Sign-In</t>
+          <t>Amateur</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Không tải được đăng nhập Google</t>
+          <t>Nghiệp dư</t>
         </is>
       </c>
     </row>
     <row r="121" ht="18" customHeight="1">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>login.facebook.button</t>
+          <t>room.bot-difficulty.intermediate</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Sign-in with Facebook</t>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập với Facebook</t>
+          <t>Trung bình</t>
         </is>
       </c>
     </row>
     <row r="122" ht="18" customHeight="1">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>login.messages.incorrect-login</t>
+          <t>room.bot-difficulty.advanced</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Invalid username or password</t>
+          <t>Advanced</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Tên người dùng hoặc mật khẩu không hợp lệ</t>
+          <t>Nâng cao</t>
         </is>
       </c>
     </row>
     <row r="123" ht="18" customHeight="1">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>login.messages.internal-server-error</t>
+          <t>room.bot-difficulty.master</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Master</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Lão luyện</t>
         </is>
       </c>
     </row>
     <row r="124" ht="18" customHeight="1">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>login.messages.missing-credentials</t>
+          <t>login.page.title</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Username and password are required</t>
+          <t>Login</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Tên người dùng và mật khẩu là bắt buộc</t>
+          <t>Đăng nhập</t>
         </is>
       </c>
     </row>
     <row r="125" ht="18" customHeight="1">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>login.messages.success</t>
+          <t>login.form.title</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>Login successful</t>
+          <t>Login</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập thành công</t>
+          <t>Đăng nhập</t>
         </is>
       </c>
     </row>
     <row r="126" ht="18" customHeight="1">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>notfound.title</t>
+          <t>login.username.label</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Page Not Found</t>
+          <t>User name</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Trang không tìm thấy</t>
+          <t>Tên người dùng</t>
         </is>
       </c>
     </row>
     <row r="127" ht="18" customHeight="1">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>notfound.description</t>
+          <t>login.username.placeholder</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>The page you are looking for does not exist or has been moved.</t>
+          <t>User name</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Trang bạn tìm kiếm không tồn tại hoặc đã được di chuyển.</t>
+          <t>Tên người dùng</t>
         </is>
       </c>
     </row>
     <row r="128" ht="18" customHeight="1">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>notfound.home</t>
+          <t>login.password.label</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Go to Home</t>
+          <t>Password</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Về trang chủ</t>
+          <t>Mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="129" ht="18" customHeight="1">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>notfound.back</t>
+          <t>login.password.placeholder</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>Go Back</t>
+          <t>Password</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Quay lại</t>
+          <t>Mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="130" ht="36" customHeight="1">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>register.confirm-password.error1</t>
+          <t>login.password.show</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Confirm password does not match password</t>
+          <t>Show password</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Mật khẩu xác nhận không khớp với mật khẩu</t>
+          <t>Hiện mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="131" ht="18" customHeight="1">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>register.confirm-password.label</t>
+          <t>login.password.hide</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>Confirm Password</t>
+          <t>Hide password</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>Xác nhận mật khẩu</t>
+          <t>Ẩn mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="132" ht="18" customHeight="1">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>register.confirm-password.placeholder</t>
+          <t>login.form.error1</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Confirm Password</t>
+          <t xml:space="preserve">Login failed. Please check your credentials </t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Xác nhận mật khẩu</t>
+          <t>Đăng nhập không thành công. Hãy kiểm tra lại</t>
         </is>
       </c>
     </row>
     <row r="133" ht="18" customHeight="1">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>register.display-name.label</t>
+          <t>login.form.forgot-password</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>Display name</t>
+          <t>Forgot password</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>Tên hiển thị</t>
+          <t>Quên mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="134" ht="18" customHeight="1">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>register.display-name.placeholder</t>
+          <t>login.form.register</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Display name</t>
+          <t>Register</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Tên hiển thị</t>
+          <t>Đăng ký</t>
         </is>
       </c>
     </row>
     <row r="135" ht="36" customHeight="1">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>register.email.error1</t>
+          <t>login.form.submit</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>Invalid email format</t>
+          <t>Login</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>Định dạng email không hợp lệ</t>
+          <t>Đăng nhập</t>
         </is>
       </c>
     </row>
     <row r="136" ht="18" customHeight="1">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>register.email.label</t>
+          <t>login.form.or</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>or</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>hoặc</t>
         </is>
       </c>
     </row>
     <row r="137" ht="18" customHeight="1">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>register.email.placeholder</t>
+          <t>login.google.load-error</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Could not load Google Sign-In</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Không tải được đăng nhập Google</t>
         </is>
       </c>
     </row>
     <row r="138" ht="18" customHeight="1">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>register.form.login</t>
+          <t>login.facebook.button</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Back to login</t>
+          <t>Sign-in with Facebook</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Về trang đăng nhập</t>
+          <t>Đăng nhập với Facebook</t>
         </is>
       </c>
     </row>
     <row r="139" ht="18" customHeight="1">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>register.form.submit</t>
+          <t>login.messages.incorrect-login</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>Register</t>
+          <t>Invalid username or password</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>Đăng ký</t>
+          <t>Tên người dùng hoặc mật khẩu không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="140" ht="18" customHeight="1">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>register.form.success</t>
+          <t>login.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Registration successful. Redirecting to login...</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Đăng ký thành công. Đang chuyển hướng...</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="141" ht="18" customHeight="1">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>register.form.title</t>
+          <t>login.messages.missing-credentials</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>Register</t>
+          <t>Username and password are required</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>Đăng ký</t>
+          <t>Tên người dùng và mật khẩu là bắt buộc</t>
         </is>
       </c>
     </row>
     <row r="142" ht="36" customHeight="1">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>register.gender.female</t>
+          <t>login.messages.success</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Login successful</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Nữ</t>
+          <t>Đăng nhập thành công</t>
         </is>
       </c>
     </row>
     <row r="143" ht="18" customHeight="1">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>register.gender.label</t>
+          <t>notfound.title</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>Gender</t>
+          <t>Page Not Found</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>Giới tính</t>
+          <t>Trang không tìm thấy</t>
         </is>
       </c>
     </row>
     <row r="144" ht="18" customHeight="1">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>register.gender.male</t>
+          <t>notfound.description</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>The page you are looking for does not exist or has been moved.</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Nam</t>
+          <t>Trang bạn tìm kiếm không tồn tại hoặc đã được di chuyển.</t>
         </is>
       </c>
     </row>
     <row r="145" ht="18" customHeight="1">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>register.gender.select</t>
+          <t>notfound.home</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>Select gender</t>
+          <t>Go to Home</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>Chọn giới tính</t>
+          <t>Về trang chủ</t>
         </is>
       </c>
     </row>
     <row r="146" ht="18" customHeight="1">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>register.page.title</t>
+          <t>notfound.back</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Register</t>
+          <t>Go Back</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Đăng ký</t>
+          <t>Quay lại</t>
         </is>
       </c>
     </row>
     <row r="147" ht="36" customHeight="1">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>register.password.error1</t>
+          <t>register.confirm-password.error1</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>Password must be at least 8 characters and contain uppercase, lowercase, number, and special character</t>
+          <t>Confirm password does not match password</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Mật khẩu phải có ít nhất 8 ký tự và chứa chữ hoa, chữ thường, số và ký tự đặc biệt</t>
+          <t>Mật khẩu xác nhận không khớp với mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="148" ht="18" customHeight="1">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>register.password.hide</t>
+          <t>register.confirm-password.label</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Hide password</t>
+          <t>Confirm Password</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Ẩn mật khẩu</t>
+          <t>Xác nhận mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="149" ht="36" customHeight="1">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>register.password.label</t>
+          <t>register.confirm-password.placeholder</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>Password</t>
+          <t>Confirm Password</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>Mật khẩu</t>
+          <t>Xác nhận mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="150" ht="18" customHeight="1">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>register.password.placeholder</t>
+          <t>register.display-name.label</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Password</t>
+          <t>Display name</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Mật khẩu</t>
+          <t>Tên hiển thị</t>
         </is>
       </c>
     </row>
     <row r="151" ht="18" customHeight="1">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>register.password.show</t>
+          <t>register.display-name.placeholder</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>Show password</t>
+          <t>Display name</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>Hiện mật khẩu</t>
+          <t>Tên hiển thị</t>
         </is>
       </c>
     </row>
     <row r="152" ht="18" customHeight="1">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>register.username.error1</t>
+          <t>register.email.error1</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>User name must contain only alphanumeric characters, underscore, and dot</t>
+          <t>Invalid email format</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>Tên người dùng chỉ chứa ký tự chữ số, dấu gạch dưới và dấu chấm</t>
+          <t>Định dạng email không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="153" ht="18" customHeight="1">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>register.username.label</t>
+          <t>register.email.label</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>User name</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>Tên người dùng</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="154" ht="18" customHeight="1">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>register.username.placeholder</t>
+          <t>register.email.placeholder</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>User name</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>Tên người dùng</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="155" ht="18" customHeight="1">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.page.title</t>
+          <t>register.form.login</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>Forgot Password</t>
+          <t>Back to login</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>Quên mật khẩu</t>
+          <t>Về trang đăng nhập</t>
         </is>
       </c>
     </row>
     <row r="156" ht="18" customHeight="1">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.form.title</t>
+          <t>register.form.submit</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>Forgot Password</t>
+          <t>Register</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Quên mật khẩu</t>
+          <t>Đăng ký</t>
         </is>
       </c>
     </row>
     <row r="157" ht="18" customHeight="1">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.form.login</t>
+          <t>register.form.success</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>Back to login</t>
+          <t>Registration successful. Redirecting to login...</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>Về trang đăng nhập</t>
+          <t>Đăng ký thành công. Đang chuyển hướng...</t>
         </is>
       </c>
     </row>
     <row r="158" ht="18" customHeight="1">
       <c r="A158" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.form.submit</t>
+          <t>register.form.title</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>Forgot password</t>
+          <t>Register</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>Quên mật khẩu</t>
+          <t>Đăng ký</t>
         </is>
       </c>
     </row>
     <row r="159" ht="36" customHeight="1">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.form.success</t>
+          <t>register.gender.female</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>Check your email for reset password details.</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>Hãy kiểm tra email để xem thông tin đặt lại mật khẩu.</t>
+          <t>Nữ</t>
         </is>
       </c>
     </row>
     <row r="160" ht="18" customHeight="1">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.form.error1</t>
+          <t>register.gender.label</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>Forgot password failed.</t>
+          <t>Gender</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Quên mật khẩu không thành công.</t>
+          <t>Giới tính</t>
         </is>
       </c>
     </row>
     <row r="161" ht="36" customHeight="1">
       <c r="A161" s="1" t="inlineStr">
         <is>
-          <t>reset-password.page.title</t>
+          <t>register.gender.male</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>Reset Password</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>Đặt lại mật khẩu</t>
+          <t>Nam</t>
         </is>
       </c>
     </row>
     <row r="162" ht="18" customHeight="1">
       <c r="A162" s="1" t="inlineStr">
         <is>
-          <t>reset-password.form.title</t>
+          <t>register.gender.select</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>Reset your password</t>
+          <t>Select gender</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Đặt lại mật khẩu của bạn</t>
+          <t>Chọn giới tính</t>
         </is>
       </c>
     </row>
     <row r="163" ht="18" customHeight="1">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t>reset-password.form.submit</t>
+          <t>register.page.title</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>Reset Password</t>
+          <t>Register</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>Đặt lại mật khẩu</t>
+          <t>Đăng ký</t>
         </is>
       </c>
     </row>
     <row r="164" ht="36" customHeight="1">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t>reset-password.form.error1</t>
+          <t>register.password.error1</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>An error occurred while resetting your password. Please try again.</t>
+          <t>Password must be at least 8 characters and contain uppercase, lowercase, number, and special character</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Có lỗi xảy ra khi đặt lại mật khẩu. Vui lòng thử lại.</t>
+          <t>Mật khẩu phải có ít nhất 8 ký tự và chứa chữ hoa, chữ thường, số và ký tự đặc biệt</t>
         </is>
       </c>
     </row>
     <row r="165" ht="18" customHeight="1">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t>reset-password.form.invalid-token</t>
+          <t>register.password.hide</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>Invalid or expired reset password token</t>
+          <t>Hide password</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>Token đặt lại mật khẩu không hợp lệ hoặc đã hết hạn</t>
+          <t>Ẩn mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="166" ht="18" customHeight="1">
       <c r="A166" s="1" t="inlineStr">
         <is>
-          <t>reset-password.form.success</t>
+          <t>register.password.label</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>Password reset successfully. Redirecting to login...</t>
+          <t>Password</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>Đặt lại mật khẩu thành công. Đang chuyển hướng đến đăng nhập...</t>
+          <t>Mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="167" ht="18" customHeight="1">
       <c r="A167" s="1" t="inlineStr">
         <is>
-          <t>reset-password.action.back-to-login</t>
+          <t>register.password.placeholder</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>Back to login</t>
+          <t>Password</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>Quay lại trang chủ</t>
+          <t>Mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="168" ht="18" customHeight="1">
       <c r="A168" s="1" t="inlineStr">
         <is>
-          <t>auth-middleware.messages.invalid-token-payload</t>
+          <t>register.password.show</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>Invalid token payload</t>
+          <t>Show password</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>Payload của token không hợp lệ</t>
+          <t>Hiện mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="169" ht="18" customHeight="1">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t>auth-middleware.messages.session-not-found</t>
+          <t>register.username.error1</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>Session not found</t>
+          <t>User name must contain only alphanumeric characters, underscore, and dot</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy phiên</t>
+          <t>Tên người dùng chỉ chứa ký tự chữ số, dấu gạch dưới và dấu chấm</t>
         </is>
       </c>
     </row>
     <row r="170" ht="18" customHeight="1">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t>auth-middleware.messages.token-expired</t>
+          <t>register.username.label</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>Token is expired</t>
+          <t>User name</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>Token đã hết hạn</t>
+          <t>Tên người dùng</t>
         </is>
       </c>
     </row>
     <row r="171" ht="18" customHeight="1">
       <c r="A171" s="1" t="inlineStr">
         <is>
-          <t>auth-middleware.messages.token-invalid</t>
+          <t>register.username.placeholder</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>Token is invalid</t>
+          <t>User name</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>Token không hợp lệ</t>
+          <t>Tên người dùng</t>
         </is>
       </c>
     </row>
     <row r="172" ht="18" customHeight="1">
       <c r="A172" s="1" t="inlineStr">
         <is>
-          <t>auth-middleware.messages.token-required</t>
+          <t>forgot-password.page.title</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>Token not provided</t>
+          <t>Forgot Password</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>Token không được cung cấp</t>
+          <t>Quên mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="173" ht="18" customHeight="1">
       <c r="A173" s="1" t="inlineStr">
         <is>
-          <t>auth-middleware.messages.token-subject-mismatch</t>
+          <t>forgot-password.form.title</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>Token subject mismatch</t>
+          <t>Forgot Password</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>Token chủ đề không khớp</t>
+          <t>Quên mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="174" ht="18" customHeight="1">
       <c r="A174" s="1" t="inlineStr">
         <is>
-          <t>auth-middleware.messages.token-validation-failed</t>
+          <t>forgot-password.form.login</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>Token validation failed</t>
+          <t>Back to login</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>Xác thực token không thành công</t>
+          <t>Về trang đăng nhập</t>
         </is>
       </c>
     </row>
     <row r="175" ht="18" customHeight="1">
       <c r="A175" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.insufficient-amount</t>
+          <t>forgot-password.form.submit</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>You do not have enough balance to create a room with this bet</t>
+          <t>Forgot password</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>Bạn không còn đủ amount để tạo phòng với mức cược này</t>
+          <t>Quên mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="176" ht="36" customHeight="1">
       <c r="A176" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.internal-server-error</t>
+          <t>forgot-password.form.success</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>Internal server error while creating room</t>
+          <t>Check your email for reset password details.</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ khi tạo phòng</t>
+          <t>Hãy kiểm tra email để xem thông tin đặt lại mật khẩu.</t>
         </is>
       </c>
     </row>
     <row r="177" ht="18" customHeight="1">
       <c r="A177" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.invalid-bet-amount</t>
+          <t>forgot-password.form.error1</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>Bet amount is required and must be one of the acceptable values</t>
+          <t>Forgot password failed.</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>Số tiền cược là bắt buộc và phải là một trong các giá trị được chấp nhận</t>
+          <t>Quên mật khẩu không thành công.</t>
         </is>
       </c>
     </row>
     <row r="178" ht="18" customHeight="1">
       <c r="A178" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.invalid-time-limit</t>
+          <t>reset-password.page.title</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>Invalid time limit</t>
+          <t>Reset Password</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>Thời gian không hợp lệ</t>
+          <t>Đặt lại mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="179" ht="18" customHeight="1">
       <c r="A179" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.invalid-redFirst</t>
+          <t>reset-password.form.title</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>'redFirst' must be a boolean</t>
+          <t>Reset your password</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>'redFirst' phải là giá trị boolean</t>
+          <t>Đặt lại mật khẩu của bạn</t>
         </is>
       </c>
     </row>
     <row r="180" ht="18" customHeight="1">
       <c r="A180" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.invalid-team-name</t>
+          <t>reset-password.form.submit</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>Team name must be either 'red', 'black', or null</t>
+          <t>Reset Password</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>Tên đội phải là 'red', 'black' hoặc null</t>
+          <t>Đặt lại mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="181" ht="18" customHeight="1">
       <c r="A181" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.name-required</t>
+          <t>reset-password.form.error1</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>Room name (tableName) is required and must not be empty</t>
+          <t>An error occurred while resetting your password. Please try again.</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>Tên phòng (tableName) là bắt buộc và không được để trống</t>
+          <t>Có lỗi xảy ra khi đặt lại mật khẩu. Vui lòng thử lại.</t>
         </is>
       </c>
     </row>
     <row r="182" ht="18" customHeight="1">
       <c r="A182" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.room-created</t>
+          <t>reset-password.form.invalid-token</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>Room created successfully</t>
+          <t>Invalid or expired reset password token</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>Phòng được tạo thành công</t>
+          <t>Token đặt lại mật khẩu không hợp lệ hoặc đã hết hạn</t>
         </is>
       </c>
     </row>
     <row r="183" ht="18" customHeight="1">
       <c r="A183" s="1" t="inlineStr">
         <is>
-          <t>fetch-rooms.messages.internal-server-error</t>
+          <t>reset-password.form.success</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Password reset successfully. Redirecting to login...</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Đặt lại mật khẩu thành công. Đang chuyển hướng đến đăng nhập...</t>
         </is>
       </c>
     </row>
     <row r="184" ht="18" customHeight="1">
       <c r="A184" s="1" t="inlineStr">
         <is>
-          <t>fetch-rooms.messages.invalid-status</t>
+          <t>reset-password.action.back-to-login</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>Query parameter 'status' must be an integer</t>
+          <t>Back to login</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>Tham số truy vấn 'status' phải là số nguyên</t>
+          <t>Quay lại trang chủ</t>
         </is>
       </c>
     </row>
     <row r="185" ht="36" customHeight="1">
       <c r="A185" s="1" t="inlineStr">
         <is>
-          <t>fetch-rooms.messages.success</t>
+          <t>auth-middleware.messages.invalid-token-payload</t>
         </is>
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>Fetch rooms successfully</t>
+          <t>Invalid token payload</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>Lấy phòng thành công</t>
+          <t>Payload của token không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="186" ht="18" customHeight="1">
       <c r="A186" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.messages.email-not-found</t>
+          <t>auth-middleware.messages.session-not-found</t>
         </is>
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>Email does not exist</t>
+          <t>Session not found</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>Email không tồn tại</t>
+          <t>Không tìm thấy phiên</t>
         </is>
       </c>
     </row>
     <row r="187" ht="36" customHeight="1">
       <c r="A187" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.messages.email-service-not-configured</t>
+          <t>auth-middleware.messages.token-expired</t>
         </is>
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>Email service is not configured</t>
+          <t>Token is expired</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>Dịch vụ email chưa được cấu hình</t>
+          <t>Token đã hết hạn</t>
         </is>
       </c>
     </row>
     <row r="188" ht="18" customHeight="1">
       <c r="A188" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.messages.internal-server-error</t>
+          <t>auth-middleware.messages.token-invalid</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Token is invalid</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Token không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="189" ht="18" customHeight="1">
       <c r="A189" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.messages.invalid-email-format</t>
+          <t>auth-middleware.messages.token-required</t>
         </is>
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>Invalid email format</t>
+          <t>Token not provided</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>Định dạng email không hợp lệ</t>
+          <t>Token không được cung cấp</t>
         </is>
       </c>
     </row>
     <row r="190" ht="18" customHeight="1">
       <c r="A190" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.messages.missing-email</t>
+          <t>auth-middleware.messages.token-subject-mismatch</t>
         </is>
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>Email is required</t>
+          <t>Token subject mismatch</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>Email là bắt buộc</t>
+          <t>Token chủ đề không khớp</t>
         </is>
       </c>
     </row>
     <row r="191" ht="18" customHeight="1">
       <c r="A191" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.messages.success</t>
+          <t>auth-middleware.messages.token-validation-failed</t>
         </is>
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>Forgot password email sent</t>
+          <t>Token validation failed</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>Email đặt lại mật khẩu đã được gửi</t>
+          <t>Xác thực token không thành công</t>
         </is>
       </c>
     </row>
     <row r="192" ht="18" customHeight="1">
       <c r="A192" s="1" t="inlineStr">
         <is>
-          <t>join-room.messages.internal-server-error</t>
+          <t>create-room.messages.insufficient-amount</t>
         </is>
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>You do not have enough balance to create a room with this bet</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Bạn không còn đủ amount để tạo phòng với mức cược này</t>
         </is>
       </c>
     </row>
     <row r="193" ht="18" customHeight="1">
       <c r="A193" s="1" t="inlineStr">
         <is>
-          <t>join-room.messages.invalid-team</t>
+          <t>create-room.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>Field 'team' must be 'red', 'black', null, or undefined</t>
+          <t>Internal server error while creating room</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>Trường 'team' phải là 'red', 'black', null hoặc không truyền</t>
+          <t>Lỗi máy chủ nội bộ khi tạo phòng</t>
         </is>
       </c>
     </row>
     <row r="194" ht="18" customHeight="1">
       <c r="A194" s="1" t="inlineStr">
         <is>
-          <t>join-room.messages.invalid-room-id</t>
+          <t>create-room.messages.invalid-bet-amount</t>
         </is>
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>Field 'id' is required and must be a positive integer</t>
+          <t>Bet amount is required and must be one of the acceptable values</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
+          <t>Số tiền cược là bắt buộc và phải là một trong các giá trị được chấp nhận</t>
         </is>
       </c>
     </row>
     <row r="195" ht="18" customHeight="1">
       <c r="A195" s="1" t="inlineStr">
         <is>
-          <t>join-room.messages.room-not-found</t>
+          <t>create-room.messages.invalid-time-limit</t>
         </is>
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>Room not found</t>
+          <t>Invalid time limit</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy phòng</t>
+          <t>Thời gian không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="196" ht="18" customHeight="1">
       <c r="A196" s="1" t="inlineStr">
         <is>
-          <t>join-room.messages.success</t>
+          <t>create-room.messages.invalid-time-increment</t>
         </is>
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>Successfully joined the room</t>
+          <t>Invalid bonus per move</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>Tham gia phòng thành công</t>
+          <t>Thời gian cộng mỗi nước không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="197" ht="18" customHeight="1">
       <c r="A197" s="1" t="inlineStr">
         <is>
-          <t>join-room.messages.team-seat-occupied</t>
+          <t>create-room.messages.invalid-time-per-move</t>
         </is>
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>Selected team seat is already occupied</t>
+          <t>Invalid time per move</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>Vị trí đội đã chọn đã có người chơi</t>
+          <t>Thời gian mỗi nước không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="198" ht="18" customHeight="1">
       <c r="A198" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.cannot-kick-self</t>
+          <t>create-room.messages.invalid-redFirst</t>
         </is>
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>You cannot kick yourself</t>
+          <t>'redFirst' must be a boolean</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>Bạn không thể kick chính mình</t>
+          <t>'redFirst' phải là giá trị boolean</t>
         </is>
       </c>
     </row>
     <row r="199" ht="18" customHeight="1">
       <c r="A199" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.forbidden</t>
+          <t>create-room.messages.invalid-team-name</t>
         </is>
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>Only the host can kick users</t>
+          <t>Team name must be either 'red', 'black', or null</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>Chỉ chủ phòng mới có thể kick người dùng</t>
+          <t>Tên đội phải là 'red', 'black' hoặc null</t>
         </is>
       </c>
     </row>
     <row r="200" ht="18" customHeight="1">
       <c r="A200" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.internal-server-error</t>
+          <t>create-room.messages.name-required</t>
         </is>
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Room name (tableName) is required and must not be empty</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Tên phòng (tableName) là bắt buộc và không được để trống</t>
         </is>
       </c>
     </row>
     <row r="201" ht="18" customHeight="1">
       <c r="A201" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.invalid-room-id</t>
+          <t>create-room.messages.room-created</t>
         </is>
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>Field 'id' is required and must be a positive integer</t>
+          <t>Room created successfully</t>
         </is>
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
+          <t>Phòng được tạo thành công</t>
         </is>
       </c>
     </row>
     <row r="202" ht="18" customHeight="1">
       <c r="A202" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.invalid-user-id</t>
+          <t>fetch-rooms.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>Field 'userId' is required and must be a positive integer</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>Trường 'userId' là bắt buộc và phải là số nguyên dương</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="203" ht="18" customHeight="1">
       <c r="A203" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.room-not-found</t>
+          <t>fetch-rooms.messages.invalid-status</t>
         </is>
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>Room not found</t>
+          <t>Query parameter 'status' must be an integer</t>
         </is>
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy phòng</t>
+          <t>Tham số truy vấn 'status' phải là số nguyên</t>
         </is>
       </c>
     </row>
     <row r="204" ht="18" customHeight="1">
       <c r="A204" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.room-not-waiting</t>
+          <t>fetch-rooms.messages.success</t>
         </is>
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>You can only kick users while the room is waiting</t>
+          <t>Fetch rooms successfully</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>Chỉ có thể kick người dùng khi phòng đang ở trạng thái chờ</t>
+          <t>Lấy phòng thành công</t>
         </is>
       </c>
     </row>
     <row r="205" ht="18" customHeight="1">
       <c r="A205" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.success</t>
+          <t>forgot-password.messages.email-not-found</t>
         </is>
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>User has been kicked</t>
+          <t>Email does not exist</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>Người dùng đã bị kick</t>
+          <t>Email không tồn tại</t>
         </is>
       </c>
     </row>
     <row r="206" ht="18" customHeight="1">
       <c r="A206" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.user-not-in-room</t>
+          <t>forgot-password.messages.email-service-not-configured</t>
         </is>
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>User is not in this room</t>
+          <t>Email service is not configured</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>Người dùng không trong phòng này</t>
+          <t>Dịch vụ email chưa được cấu hình</t>
         </is>
       </c>
     </row>
     <row r="207" ht="18" customHeight="1">
       <c r="A207" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.you-were-kicked</t>
+          <t>forgot-password.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>You have been removed from the room by the host</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>Bạn đã bị chủ phòng đưa ra khỏi phòng</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="208" ht="18" customHeight="1">
       <c r="A208" s="1" t="inlineStr">
         <is>
-          <t>leave-room.messages.internal-server-error</t>
+          <t>forgot-password.messages.invalid-email-format</t>
         </is>
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Invalid email format</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Định dạng email không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="209" ht="18" customHeight="1">
       <c r="A209" s="1" t="inlineStr">
         <is>
-          <t>leave-room.messages.invalid-room-id</t>
+          <t>forgot-password.messages.missing-email</t>
         </is>
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>Field 'id' is required and must be a positive integer</t>
+          <t>Email is required</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
+          <t>Email là bắt buộc</t>
         </is>
       </c>
     </row>
     <row r="210" ht="18" customHeight="1">
       <c r="A210" s="1" t="inlineStr">
         <is>
-          <t>leave-room.messages.player-not-in-room</t>
+          <t>forgot-password.messages.success</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>Player is not in this room</t>
+          <t>Forgot password email sent</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>Người chơi không trong phòng này</t>
+          <t>Email đặt lại mật khẩu đã được gửi</t>
         </is>
       </c>
     </row>
     <row r="211" ht="36" customHeight="1">
       <c r="A211" s="1" t="inlineStr">
         <is>
-          <t>leave-room.messages.success</t>
+          <t>join-room.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>Leave room successfully</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>Rời phòng thành công</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="212" ht="18" customHeight="1">
       <c r="A212" s="1" t="inlineStr">
         <is>
-          <t>load-room.messages.internal-server-error</t>
+          <t>join-room.messages.invalid-team</t>
         </is>
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Field 'team' must be 'red', 'black', null, or undefined</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Trường 'team' phải là 'red', 'black', null hoặc không truyền</t>
         </is>
       </c>
     </row>
     <row r="213" ht="18" customHeight="1">
       <c r="A213" s="1" t="inlineStr">
         <is>
-          <t>load-room.messages.invalid-room-id</t>
+          <t>join-room.messages.invalid-room-id</t>
         </is>
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>Room ID must be a positive integer</t>
+          <t>Field 'id' is required and must be a positive integer</t>
         </is>
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>ID phòng phải là số nguyên dương</t>
+          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
         </is>
       </c>
     </row>
     <row r="214" ht="18" customHeight="1">
       <c r="A214" s="1" t="inlineStr">
         <is>
-          <t>load-room.messages.room-not-found</t>
+          <t>join-room.messages.room-not-found</t>
         </is>
       </c>
       <c r="B214" s="2" t="inlineStr">
@@ -3974,3498 +3974,3975 @@
     <row r="215" ht="18" customHeight="1">
       <c r="A215" s="1" t="inlineStr">
         <is>
-          <t>load-room.messages.success</t>
+          <t>join-room.messages.success</t>
         </is>
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>Load room successfully</t>
+          <t>Successfully joined the room</t>
         </is>
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>Tải phòng thành công</t>
+          <t>Tham gia phòng thành công</t>
         </is>
       </c>
     </row>
     <row r="216" ht="18" customHeight="1">
       <c r="A216" s="1" t="inlineStr">
         <is>
-          <t>google-login.messages.email-not-verified</t>
+          <t>join-room.messages.team-seat-occupied</t>
         </is>
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>Your Google email is not verified</t>
+          <t>Selected team seat is already occupied</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>Email Google của bạn chưa được xác minh</t>
+          <t>Vị trí đội đã chọn đã có người chơi</t>
         </is>
       </c>
     </row>
     <row r="217" ht="18" customHeight="1">
       <c r="A217" s="1" t="inlineStr">
         <is>
-          <t>google-login.messages.failed</t>
+          <t>kick-user.messages.cannot-kick-self</t>
         </is>
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>Login failed</t>
+          <t>You cannot kick yourself</t>
         </is>
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập không thành công</t>
+          <t>Bạn không thể kick chính mình</t>
         </is>
       </c>
     </row>
     <row r="218" ht="18" customHeight="1">
       <c r="A218" s="1" t="inlineStr">
         <is>
-          <t>google-login.messages.internal-server-error</t>
+          <t>kick-user.messages.forbidden</t>
         </is>
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Only the host can kick users</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Chỉ chủ phòng mới có thể kick người dùng</t>
         </is>
       </c>
     </row>
     <row r="219" ht="18" customHeight="1">
       <c r="A219" s="1" t="inlineStr">
         <is>
-          <t>google-login.messages.invalid-token</t>
+          <t>kick-user.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>Invalid Google credential</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>Thông tin đăng nhập Google không hợp lệ</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="220" ht="18" customHeight="1">
       <c r="A220" s="1" t="inlineStr">
         <is>
-          <t>google-login.messages.missing-credential</t>
+          <t>kick-user.messages.invalid-room-id</t>
         </is>
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>Google credential is required</t>
+          <t>Field 'id' is required and must be a positive integer</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>Thiếu thông tin đăng nhập Google</t>
+          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
         </is>
       </c>
     </row>
     <row r="221" ht="18" customHeight="1">
       <c r="A221" s="1" t="inlineStr">
         <is>
-          <t>facebook-login.messages.missing-token</t>
+          <t>kick-user.messages.invalid-user-id</t>
         </is>
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>Facebook token is required</t>
+          <t>Field 'userId' is required and must be a positive integer</t>
         </is>
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>Thiếu thông tin đăng nhập Facebook</t>
+          <t>Trường 'userId' là bắt buộc và phải là số nguyên dương</t>
         </is>
       </c>
     </row>
     <row r="222" ht="18" customHeight="1">
       <c r="A222" s="1" t="inlineStr">
         <is>
-          <t>facebook-login.messages.invalid-token</t>
+          <t>kick-user.messages.room-not-found</t>
         </is>
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>Invalid Facebook token</t>
+          <t>Room not found</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>Thông tin đăng nhập Facebook không hợp lệ</t>
+          <t>Không tìm thấy phòng</t>
         </is>
       </c>
     </row>
     <row r="223" ht="18" customHeight="1">
       <c r="A223" s="1" t="inlineStr">
         <is>
-          <t>facebook-login.messages.not-linked</t>
+          <t>kick-user.messages.room-not-waiting</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>This Facebook account is not linked. Log in another way and link it in Settings</t>
+          <t>You can only kick users while the room is waiting</t>
         </is>
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản Facebook này chưa được liên kết. Hãy đăng nhập cách khác rồi liên kết trong Cài đặt</t>
+          <t>Chỉ có thể kick người dùng khi phòng đang ở trạng thái chờ</t>
         </is>
       </c>
     </row>
     <row r="224" ht="18" customHeight="1">
       <c r="A224" s="1" t="inlineStr">
         <is>
-          <t>facebook-login.messages.internal-server-error</t>
+          <t>kick-user.messages.success</t>
         </is>
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>User has been kicked</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Người dùng đã bị kick</t>
         </is>
       </c>
     </row>
     <row r="225" ht="18" customHeight="1">
       <c r="A225" s="1" t="inlineStr">
         <is>
-          <t>facebook-link.messages.missing-token</t>
+          <t>kick-user.messages.user-not-in-room</t>
         </is>
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>Facebook token is required</t>
+          <t>User is not in this room</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>Thiếu thông tin đăng nhập Facebook</t>
+          <t>Người dùng không trong phòng này</t>
         </is>
       </c>
     </row>
     <row r="226" ht="18" customHeight="1">
       <c r="A226" s="1" t="inlineStr">
         <is>
-          <t>facebook-link.messages.invalid-token</t>
+          <t>kick-user.messages.you-were-kicked</t>
         </is>
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>Invalid Facebook token</t>
+          <t>You have been removed from the room by the host</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>Thông tin đăng nhập Facebook không hợp lệ</t>
+          <t>Bạn đã bị chủ phòng đưa ra khỏi phòng</t>
         </is>
       </c>
     </row>
     <row r="227" ht="18" customHeight="1">
       <c r="A227" s="1" t="inlineStr">
         <is>
-          <t>facebook-link.messages.linked</t>
+          <t>leave-room.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>Facebook linked successfully</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>Đã liên kết Facebook</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="228" ht="18" customHeight="1">
       <c r="A228" s="1" t="inlineStr">
         <is>
-          <t>facebook-link.messages.already-linked</t>
+          <t>leave-room.messages.invalid-room-id</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>This Facebook account is already linked to your account</t>
+          <t>Field 'id' is required and must be a positive integer</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản Facebook này đã được liên kết với bạn</t>
+          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
         </is>
       </c>
     </row>
     <row r="229" ht="18" customHeight="1">
       <c r="A229" s="1" t="inlineStr">
         <is>
-          <t>facebook-link.messages.linked-to-other</t>
+          <t>leave-room.messages.player-not-in-room</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>This Facebook account is already linked to another account</t>
+          <t>Player is not in this room</t>
         </is>
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản Facebook này đã được liên kết với tài khoản khác</t>
+          <t>Người chơi không trong phòng này</t>
         </is>
       </c>
     </row>
     <row r="230" ht="18" customHeight="1">
       <c r="A230" s="1" t="inlineStr">
         <is>
-          <t>facebook-link.messages.already-has-facebook</t>
+          <t>leave-room.messages.success</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>You already linked a different Facebook account</t>
+          <t>Leave room successfully</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>Bạn đã liên kết một tài khoản Facebook khác</t>
+          <t>Rời phòng thành công</t>
         </is>
       </c>
     </row>
     <row r="231" ht="18" customHeight="1">
       <c r="A231" s="1" t="inlineStr">
         <is>
-          <t>facebook-link.messages.unlinked</t>
+          <t>load-room.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>Facebook unlinked</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>Đã huỷ liên kết Facebook</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="232" ht="18" customHeight="1">
       <c r="A232" s="1" t="inlineStr">
         <is>
-          <t>facebook-link.messages.internal-server-error</t>
+          <t>load-room.messages.invalid-room-id</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Room ID must be a positive integer</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>ID phòng phải là số nguyên dương</t>
         </is>
       </c>
     </row>
     <row r="233" ht="18" customHeight="1">
       <c r="A233" s="1" t="inlineStr">
         <is>
-          <t>logout.messages.already-inactive</t>
+          <t>load-room.messages.room-not-found</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>Session already inactive</t>
+          <t>Room not found</t>
         </is>
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>Phiên đã ngưng hoạt động</t>
+          <t>Không tìm thấy phòng</t>
         </is>
       </c>
     </row>
     <row r="234" ht="18" customHeight="1">
       <c r="A234" s="1" t="inlineStr">
         <is>
-          <t>logout.messages.internal-server-error</t>
+          <t>load-room.messages.success</t>
         </is>
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Load room successfully</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Tải phòng thành công</t>
         </is>
       </c>
     </row>
     <row r="235" ht="18" customHeight="1">
       <c r="A235" s="1" t="inlineStr">
         <is>
-          <t>logout.messages.success</t>
+          <t>google-login.messages.email-not-verified</t>
         </is>
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>Logout successful</t>
+          <t>Your Google email is not verified</t>
         </is>
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>Đăng xuất thành công</t>
+          <t>Email Google của bạn chưa được xác minh</t>
         </is>
       </c>
     </row>
     <row r="236" ht="18" customHeight="1">
       <c r="A236" s="1" t="inlineStr">
         <is>
-          <t>refresh-token.messages.missing-refresh-token</t>
+          <t>google-login.messages.failed</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>Missing refresh token cookie</t>
+          <t>Login failed</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>Thiếu cookie token làm mới</t>
+          <t>Đăng nhập không thành công</t>
         </is>
       </c>
     </row>
     <row r="237" ht="18" customHeight="1">
       <c r="A237" s="1" t="inlineStr">
         <is>
-          <t>refresh-token.messages.mismatch-or-expired</t>
+          <t>google-login.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>Refresh token mismatch or expired</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>Thiếu refresh token hoặc đã hết hạn</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="238" ht="18" customHeight="1">
       <c r="A238" s="1" t="inlineStr">
         <is>
-          <t>refresh-token.messages.success</t>
+          <t>google-login.messages.invalid-token</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>Token refreshed</t>
+          <t>Invalid Google credential</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>Token đã làm mới</t>
+          <t>Thông tin đăng nhập Google không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="239" ht="18" customHeight="1">
       <c r="A239" s="1" t="inlineStr">
         <is>
-          <t>register.messages.email-exists</t>
+          <t>google-login.messages.missing-credential</t>
         </is>
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>Email already exists</t>
+          <t>Google credential is required</t>
         </is>
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>Email đã tồn tại</t>
+          <t>Thiếu thông tin đăng nhập Google</t>
         </is>
       </c>
     </row>
     <row r="240" ht="18" customHeight="1">
       <c r="A240" s="1" t="inlineStr">
         <is>
-          <t>register.messages.internal-server-error</t>
+          <t>facebook-login.messages.missing-token</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Facebook token is required</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Thiếu thông tin đăng nhập Facebook</t>
         </is>
       </c>
     </row>
     <row r="241" ht="18" customHeight="1">
       <c r="A241" s="1" t="inlineStr">
         <is>
-          <t>register.messages.missing-fields</t>
+          <t>facebook-login.messages.invalid-token</t>
         </is>
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>Username, password, gender, displayName and email are required</t>
+          <t>Invalid Facebook token</t>
         </is>
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>Tên người dùng, mật khẩu, giới tính, tên hiển thị và email là bắt buộc</t>
+          <t>Thông tin đăng nhập Facebook không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="242" ht="18" customHeight="1">
       <c r="A242" s="1" t="inlineStr">
         <is>
-          <t>register.messages.success</t>
+          <t>facebook-login.messages.not-linked</t>
         </is>
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>User created successfully</t>
+          <t>This Facebook account is not linked. Log in another way and link it in Settings</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>Người dùng được tạo thành công</t>
+          <t>Tài khoản Facebook này chưa được liên kết. Hãy đăng nhập cách khác rồi liên kết trong Cài đặt</t>
         </is>
       </c>
     </row>
     <row r="243" ht="18" customHeight="1">
       <c r="A243" s="1" t="inlineStr">
         <is>
-          <t>register.messages.username-exists</t>
+          <t>facebook-login.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>Username already exists</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>Tên người dùng đã tồn tại</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="244" ht="18" customHeight="1">
       <c r="A244" s="1" t="inlineStr">
         <is>
-          <t>reset-password.messages.internal-server-error</t>
+          <t>facebook-link.messages.missing-token</t>
         </is>
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Facebook token is required</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Thiếu thông tin đăng nhập Facebook</t>
         </is>
       </c>
     </row>
     <row r="245" ht="18" customHeight="1">
       <c r="A245" s="1" t="inlineStr">
         <is>
-          <t>reset-password.messages.invalid-or-expired-token</t>
+          <t>facebook-link.messages.invalid-token</t>
         </is>
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>Invalid or expired reset password token</t>
+          <t>Invalid Facebook token</t>
         </is>
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>Token đặt lại mật khẩu không hợp lệ hoặc đã hết hạn</t>
+          <t>Thông tin đăng nhập Facebook không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="246" ht="18" customHeight="1">
       <c r="A246" s="1" t="inlineStr">
         <is>
-          <t>reset-password.messages.invalid-user-id</t>
+          <t>facebook-link.messages.linked</t>
         </is>
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>Invalid user id</t>
+          <t>Facebook linked successfully</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>ID người dùng không hợp lệ</t>
+          <t>Đã liên kết Facebook</t>
         </is>
       </c>
     </row>
     <row r="247" ht="18" customHeight="1">
       <c r="A247" s="1" t="inlineStr">
         <is>
-          <t>reset-password.messages.missing-id-or-token</t>
+          <t>facebook-link.messages.already-linked</t>
         </is>
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>ID and token are required</t>
+          <t>This Facebook account is already linked to your account</t>
         </is>
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>ID và token là bắt buộc</t>
+          <t>Tài khoản Facebook này đã được liên kết với bạn</t>
         </is>
       </c>
     </row>
     <row r="248" ht="18" customHeight="1">
       <c r="A248" s="1" t="inlineStr">
         <is>
-          <t>reset-password.messages.missing-userId-or-password</t>
+          <t>facebook-link.messages.linked-to-other</t>
         </is>
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>UserId and password are required</t>
+          <t>This Facebook account is already linked to another account</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>UserId và mật khẩu là bắt buộc</t>
+          <t>Tài khoản Facebook này đã được liên kết với tài khoản khác</t>
         </is>
       </c>
     </row>
     <row r="249" ht="18" customHeight="1">
       <c r="A249" s="1" t="inlineStr">
         <is>
-          <t>reset-password.messages.token-valid</t>
+          <t>facebook-link.messages.already-has-facebook</t>
         </is>
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>Reset password token is valid</t>
+          <t>You already linked a different Facebook account</t>
         </is>
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>Token đặt lại mật khẩu hợp lệ</t>
+          <t>Bạn đã liên kết một tài khoản Facebook khác</t>
         </is>
       </c>
     </row>
     <row r="250" ht="18" customHeight="1">
       <c r="A250" s="1" t="inlineStr">
         <is>
-          <t>reset-password.messages.user-not-found</t>
+          <t>facebook-link.messages.unlinked</t>
         </is>
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>User not found</t>
+          <t>Facebook unlinked</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy người dùng</t>
+          <t>Đã huỷ liên kết Facebook</t>
         </is>
       </c>
     </row>
     <row r="251" ht="18" customHeight="1">
       <c r="A251" s="1" t="inlineStr">
         <is>
-          <t>room.actions.start-room</t>
+          <t>facebook-link.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t>Start room</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>Bắt đầu chơi</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="252" ht="18" customHeight="1">
       <c r="A252" s="1" t="inlineStr">
         <is>
-          <t>room.actions.challenge</t>
+          <t>logout.messages.already-inactive</t>
         </is>
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>Challenge</t>
+          <t>Session already inactive</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>Vào chơi</t>
+          <t>Phiên đã ngưng hoạt động</t>
         </is>
       </c>
     </row>
     <row r="253" ht="18" customHeight="1">
       <c r="A253" s="1" t="inlineStr">
         <is>
-          <t>room.actions.leave-seat</t>
+          <t>logout.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>Leave seat</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>Ra xem</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="254" ht="18" customHeight="1">
       <c r="A254" s="1" t="inlineStr">
         <is>
-          <t>room.actions.undo</t>
+          <t>logout.messages.success</t>
         </is>
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>Undo</t>
+          <t>Logout successful</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>Hoán tác</t>
+          <t>Đăng xuất thành công</t>
         </is>
       </c>
     </row>
     <row r="255" ht="18" customHeight="1">
       <c r="A255" s="1" t="inlineStr">
         <is>
-          <t>room.actions.surrender</t>
+          <t>refresh-token.messages.missing-refresh-token</t>
         </is>
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>Surrender</t>
+          <t>Missing refresh token cookie</t>
         </is>
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>Đầu hàng</t>
+          <t>Thiếu cookie token làm mới</t>
         </is>
       </c>
     </row>
     <row r="256" ht="18" customHeight="1">
       <c r="A256" s="1" t="inlineStr">
         <is>
-          <t>room.actions.draw</t>
+          <t>refresh-token.messages.mismatch-or-expired</t>
         </is>
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>Draw</t>
+          <t>Refresh token mismatch or expired</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>Hòa</t>
+          <t>Thiếu refresh token hoặc đã hết hạn</t>
         </is>
       </c>
     </row>
     <row r="257" ht="18" customHeight="1">
       <c r="A257" s="1" t="inlineStr">
         <is>
-          <t>room.actions.back-home</t>
+          <t>refresh-token.messages.success</t>
         </is>
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>Back to home</t>
+          <t>Token refreshed</t>
         </is>
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>Thoát phòng</t>
+          <t>Token đã làm mới</t>
         </is>
       </c>
     </row>
     <row r="258" ht="18" customHeight="1">
       <c r="A258" s="1" t="inlineStr">
         <is>
-          <t>room.actions.flip-board</t>
+          <t>register.messages.email-exists</t>
         </is>
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>Flip board</t>
+          <t>Email already exists</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>Đảo chiều bàn cờ</t>
+          <t>Email đã tồn tại</t>
         </is>
       </c>
     </row>
     <row r="259" ht="18" customHeight="1">
       <c r="A259" s="1" t="inlineStr">
         <is>
-          <t>room.actions.accept-draw</t>
+          <t>register.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
-          <t>Accept</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>Chấp nhận</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="260" ht="36" customHeight="1">
       <c r="A260" s="1" t="inlineStr">
         <is>
-          <t>room.actions.reject-draw</t>
+          <t>register.messages.missing-fields</t>
         </is>
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>Reject</t>
+          <t>Username, password, gender, displayName and email are required</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>Từ chối</t>
+          <t>Tên người dùng, mật khẩu, giới tính, tên hiển thị và email là bắt buộc</t>
         </is>
       </c>
     </row>
     <row r="261" ht="36" customHeight="1">
       <c r="A261" s="1" t="inlineStr">
         <is>
-          <t>room.actions.send-pm</t>
+          <t>register.messages.success</t>
         </is>
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>Send PM</t>
+          <t>User created successfully</t>
         </is>
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>Chat</t>
+          <t>Người dùng được tạo thành công</t>
         </is>
       </c>
     </row>
     <row r="262" ht="18" customHeight="1">
       <c r="A262" s="1" t="inlineStr">
         <is>
-          <t>room.actions.view-history</t>
+          <t>register.messages.username-exists</t>
         </is>
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>History</t>
+          <t>Username already exists</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>Lịch sử</t>
+          <t>Tên người dùng đã tồn tại</t>
         </is>
       </c>
     </row>
     <row r="263" ht="18" customHeight="1">
       <c r="A263" s="1" t="inlineStr">
         <is>
-          <t>room.actions.kick</t>
+          <t>reset-password.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t>Kick</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>Kick</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="264" ht="18" customHeight="1">
       <c r="A264" s="1" t="inlineStr">
         <is>
-          <t>room.actions.back-to-room</t>
+          <t>reset-password.messages.invalid-or-expired-token</t>
         </is>
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>Back to room</t>
+          <t>Invalid or expired reset password token</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>Quay lại phòng chơi</t>
+          <t>Token đặt lại mật khẩu không hợp lệ hoặc đã hết hạn</t>
         </is>
       </c>
     </row>
     <row r="265" ht="17" customHeight="1">
       <c r="A265" s="1" t="inlineStr">
         <is>
-          <t>room.actions.chat</t>
+          <t>reset-password.messages.invalid-user-id</t>
         </is>
       </c>
       <c r="B265" s="1" t="inlineStr">
         <is>
-          <t>Room chat</t>
+          <t>Invalid user id</t>
         </is>
       </c>
       <c r="C265" s="1" t="inlineStr">
         <is>
-          <t>Phòng chat</t>
+          <t>ID người dùng không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="266" ht="18" customHeight="1">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>room.messages.draw-accepted</t>
+          <t>reset-password.messages.missing-id-or-token</t>
         </is>
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>Opponent accepted the draw</t>
+          <t>ID and token are required</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>Đối phương đã đồng ý hòa</t>
+          <t>ID và token là bắt buộc</t>
         </is>
       </c>
     </row>
     <row r="267" ht="18" customHeight="1">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>room.messages.draw-rejected</t>
+          <t>reset-password.messages.missing-userId-or-password</t>
         </is>
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>Opponent rejected the draw</t>
+          <t>UserId and password are required</t>
         </is>
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>Đối phương từ chối hòa</t>
+          <t>UserId và mật khẩu là bắt buộc</t>
         </is>
       </c>
     </row>
     <row r="268" ht="18" customHeight="1">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>room.messages.opponent-surrendered</t>
+          <t>reset-password.messages.token-valid</t>
         </is>
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>Opponent surrendered! You won!</t>
+          <t>Reset password token is valid</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>Đối phương đã đầu hàng! Bạn thắng!</t>
+          <t>Token đặt lại mật khẩu hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="269" ht="18" customHeight="1">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>room.messages.confirm-leave</t>
+          <t>reset-password.messages.user-not-found</t>
         </is>
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>Are you sure you want to leave room?</t>
+          <t>User not found</t>
         </is>
       </c>
       <c r="C269" s="2" t="inlineStr">
         <is>
-          <t>Bạn có chắc muốn rời bàn chơi?</t>
+          <t>Không tìm thấy người dùng</t>
         </is>
       </c>
     </row>
     <row r="270" ht="18" customHeight="1">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>room.messages.confirm-surrender</t>
+          <t>room.actions.start-room</t>
         </is>
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>Are you sure you want to surrender?</t>
+          <t>Start room</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>Bạn có chắc chắn muốn đầu hàng không?</t>
+          <t>Bắt đầu chơi</t>
         </is>
       </c>
     </row>
     <row r="271" ht="36" customHeight="1">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>room.messages.confirm-draw</t>
+          <t>room.actions.challenge</t>
         </is>
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>Are you sure you want to draw?</t>
+          <t>Challenge</t>
         </is>
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>Bạn có chắc chắn muốn hòa không?</t>
+          <t>Vào chơi</t>
         </is>
       </c>
     </row>
     <row r="272" ht="36" customHeight="1">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>room.messages.confirm-accept-draw</t>
+          <t>room.actions.leave-seat</t>
         </is>
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>Opponent has proposed a draw. Do you accept?</t>
+          <t>Leave seat</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>Đối phương đã chủ hòa, bạn có đồng ý không?</t>
+          <t>Ra xem</t>
         </is>
       </c>
     </row>
     <row r="273" ht="18" customHeight="1">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>room.messages.insufficient-amount</t>
+          <t>room.actions.undo</t>
         </is>
       </c>
       <c r="B273" s="2" t="inlineStr">
         <is>
-          <t>You do not have enough balance to join this room</t>
+          <t>Undo</t>
         </is>
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>Bạn không đủ tiền để tham gia bàn chơi này</t>
+          <t>Hoán tác</t>
         </is>
       </c>
     </row>
     <row r="274" ht="18" customHeight="1">
       <c r="A274" s="1" t="inlineStr">
         <is>
-          <t>room.messages.will-leave-current-room</t>
+          <t>room.actions.surrender</t>
         </is>
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>You are currently in another room. Joining this room will remove you from the current room</t>
+          <t>Surrender</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>Bạn đang ở trong một phòng khác. Tham gia phòng này sẽ loại bạn ra khỏi phòng hiện tại</t>
+          <t>Đầu hàng</t>
         </is>
       </c>
     </row>
     <row r="275" ht="18" customHeight="1">
       <c r="A275" s="1" t="inlineStr">
         <is>
-          <t>room.messages.all-seats-occupied</t>
+          <t>room.actions.draw</t>
         </is>
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>All player seats are occupied</t>
+          <t>Draw</t>
         </is>
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>Tất cả ghế chơi đã được chiếm</t>
+          <t>Hòa</t>
         </is>
       </c>
     </row>
     <row r="276" ht="18" customHeight="1">
       <c r="A276" s="1" t="inlineStr">
         <is>
-          <t>room.messages.game-ended</t>
+          <t>room.actions.back-home</t>
         </is>
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>Game ended</t>
+          <t>Back to home</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>Ván đấu đã kết thúc</t>
+          <t>Thoát phòng</t>
         </is>
       </c>
     </row>
     <row r="277" ht="18" customHeight="1">
       <c r="A277" s="1" t="inlineStr">
         <is>
-          <t>room.messages.you-win</t>
+          <t>room.actions.flip-board</t>
         </is>
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>You win</t>
+          <t>Flip board</t>
         </is>
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t>Bạn đã chiến thắng</t>
+          <t>Đảo chiều bàn cờ</t>
         </is>
       </c>
     </row>
     <row r="278" ht="18" customHeight="1">
       <c r="A278" s="1" t="inlineStr">
         <is>
-          <t>room.messages.you-lose</t>
+          <t>room.actions.accept-draw</t>
         </is>
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>You lose</t>
+          <t>Accept</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>Bạn đã thua</t>
+          <t>Chấp nhận</t>
         </is>
       </c>
     </row>
     <row r="279" ht="18" customHeight="1">
       <c r="A279" s="1" t="inlineStr">
         <is>
-          <t>room.messages.back-to-room</t>
+          <t>room.actions.reject-draw</t>
         </is>
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>Back to room</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="C279" s="2" t="inlineStr">
         <is>
-          <t>Quay lại phòng</t>
+          <t>Từ chối</t>
         </is>
       </c>
     </row>
     <row r="280" ht="18" customHeight="1">
       <c r="A280" s="1" t="inlineStr">
         <is>
-          <t>room.messages.auto-back-countdown</t>
+          <t>room.actions.send-pm</t>
         </is>
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>{0}. Press the back button to return to the room. You will be automatically returned in {1}s</t>
+          <t>Send PM</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>{0}. Bấm nút quay lại để quay lại room. Bạn sẽ tự động quay lại trong {1}s</t>
+          <t>Chat</t>
         </is>
       </c>
     </row>
     <row r="281" ht="18" customHeight="1">
       <c r="A281" s="1" t="inlineStr">
         <is>
-          <t>room.notifications.joined</t>
+          <t>room.actions.view-history</t>
         </is>
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>{0} joined the room</t>
+          <t>History</t>
         </is>
       </c>
       <c r="C281" s="2" t="inlineStr">
         <is>
-          <t>{0} đã vào phòng</t>
+          <t>Lịch sử</t>
         </is>
       </c>
     </row>
     <row r="282" ht="18" customHeight="1">
       <c r="A282" s="1" t="inlineStr">
         <is>
-          <t>room.notifications.left</t>
+          <t>room.actions.kick</t>
         </is>
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>{0} left the room</t>
+          <t>Kick</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>{0} đã rời phòng</t>
+          <t>Kick</t>
         </is>
       </c>
     </row>
     <row r="283" ht="18" customHeight="1">
       <c r="A283" s="1" t="inlineStr">
         <is>
-          <t>room.settings.title</t>
+          <t>room.actions.back-to-room</t>
         </is>
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>Room Settings</t>
+          <t>Back to room</t>
         </is>
       </c>
       <c r="C283" s="2" t="inlineStr">
         <is>
-          <t>Cài đặt phòng</t>
+          <t>Quay lại phòng chơi</t>
         </is>
       </c>
     </row>
     <row r="284" ht="18" customHeight="1">
       <c r="A284" s="1" t="inlineStr">
         <is>
-          <t>room.settings.room-name</t>
+          <t>room.actions.chat</t>
         </is>
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>Room name</t>
+          <t>Room chat</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>Tên phòng</t>
+          <t>Phòng chat</t>
         </is>
       </c>
     </row>
     <row r="285" ht="18" customHeight="1">
       <c r="A285" s="1" t="inlineStr">
         <is>
-          <t>room.settings.players</t>
+          <t>room.messages.draw-accepted</t>
         </is>
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>Spectators</t>
+          <t>Opponent accepted the draw</t>
         </is>
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>Người xem</t>
+          <t>Đối phương đã đồng ý hòa</t>
         </is>
       </c>
     </row>
     <row r="286" ht="18" customHeight="1">
       <c r="A286" s="1" t="inlineStr">
         <is>
-          <t>room.settings.save</t>
+          <t>room.messages.draw-rejected</t>
         </is>
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>Save</t>
+          <t>Opponent rejected the draw</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>Lưu</t>
+          <t>Đối phương từ chối hòa</t>
         </is>
       </c>
     </row>
     <row r="287" ht="18" customHeight="1">
       <c r="A287" s="1" t="inlineStr">
         <is>
-          <t>room-invite.messages.title</t>
+          <t>room.messages.opponent-surrendered</t>
         </is>
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>Room Invitation</t>
+          <t>Opponent surrendered! You won!</t>
         </is>
       </c>
       <c r="C287" s="2" t="inlineStr">
         <is>
-          <t>Lời mời vào phòng</t>
+          <t>Đối phương đã đầu hàng! Bạn thắng!</t>
         </is>
       </c>
     </row>
     <row r="288" ht="18" customHeight="1">
       <c r="A288" s="1" t="inlineStr">
         <is>
-          <t>start-game.messages.success</t>
+          <t>room.messages.confirm-leave</t>
         </is>
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>Game started successfully</t>
+          <t>Are you sure you want to leave room?</t>
         </is>
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>Bắt đầu trò chơi thành công</t>
+          <t>Bạn có chắc muốn rời bàn chơi?</t>
         </is>
       </c>
     </row>
     <row r="289" ht="18" customHeight="1">
       <c r="A289" s="1" t="inlineStr">
         <is>
-          <t>start-game.messages.internal-server-error</t>
+          <t>room.messages.confirm-surrender</t>
         </is>
       </c>
       <c r="B289" s="2" t="inlineStr">
         <is>
-          <t>Internal server error while starting game</t>
+          <t>Are you sure you want to surrender?</t>
         </is>
       </c>
       <c r="C289" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ khi bắt đầu trò chơi</t>
+          <t>Bạn có chắc chắn muốn đầu hàng không?</t>
         </is>
       </c>
     </row>
     <row r="290" ht="18" customHeight="1">
       <c r="A290" s="1" t="inlineStr">
         <is>
-          <t>start-game.messages.invalid-room-id</t>
+          <t>room.messages.confirm-draw</t>
         </is>
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>Field 'id' is required and must be a positive integer</t>
+          <t>Are you sure you want to draw?</t>
         </is>
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
+          <t>Bạn có chắc chắn muốn hòa không?</t>
         </is>
       </c>
     </row>
     <row r="291" ht="18" customHeight="1">
       <c r="A291" s="1" t="inlineStr">
         <is>
-          <t>start-game.messages.invalid-difficulty</t>
+          <t>room.messages.confirm-accept-draw</t>
         </is>
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>Bot difficulty must be between 1 and 5</t>
+          <t>Opponent has proposed a draw. Do you accept?</t>
         </is>
       </c>
       <c r="C291" s="2" t="inlineStr">
         <is>
-          <t>Độ khó của bot phải từ 1 đến 5</t>
+          <t>Đối phương đã chủ hòa, bạn có đồng ý không?</t>
         </is>
       </c>
     </row>
     <row r="292" ht="18" customHeight="1">
       <c r="A292" s="1" t="inlineStr">
         <is>
-          <t>start-game.messages.room-not-found</t>
+          <t>room.messages.insufficient-amount</t>
         </is>
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>Room not found</t>
+          <t>You do not have enough balance to join this room</t>
         </is>
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy phòng</t>
+          <t>Bạn không đủ tiền để tham gia bàn chơi này</t>
         </is>
       </c>
     </row>
     <row r="293" ht="18" customHeight="1">
       <c r="A293" s="1" t="inlineStr">
         <is>
-          <t>start-game.messages.forbidden</t>
+          <t>room.messages.will-leave-current-room</t>
         </is>
       </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t>Only the room host can start the game</t>
+          <t>You are currently in another room. Joining this room will remove you from the current room</t>
         </is>
       </c>
       <c r="C293" s="2" t="inlineStr">
         <is>
-          <t>Chỉ chủ phòng mới có thể bắt đầu trò chơi</t>
+          <t>Bạn đang ở trong một phòng khác. Tham gia phòng này sẽ loại bạn ra khỏi phòng hiện tại</t>
         </is>
       </c>
     </row>
     <row r="294" ht="18" customHeight="1">
       <c r="A294" s="1" t="inlineStr">
         <is>
-          <t>start-game.messages.insufficient-amount</t>
+          <t>room.messages.game-ended</t>
         </is>
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>You do not have enough balance to start a game with this bet</t>
+          <t>Game ended</t>
         </is>
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>Bạn không còn đủ amount để start room</t>
+          <t>Ván đấu đã kết thúc</t>
         </is>
       </c>
     </row>
     <row r="295" ht="18" customHeight="1">
       <c r="A295" s="1" t="inlineStr">
         <is>
-          <t>start-game.messages.requester-must-pick-team</t>
+          <t>room.messages.you-win</t>
         </is>
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>You must select a team before starting a game with bot</t>
+          <t>You win</t>
         </is>
       </c>
       <c r="C295" s="2" t="inlineStr">
         <is>
-          <t>Bạn phải chọn team trước khi bắt đầu trò chơi với bot</t>
+          <t>Bạn đã chiến thắng</t>
         </is>
       </c>
     </row>
     <row r="296" ht="18" customHeight="1">
       <c r="A296" s="1" t="inlineStr">
         <is>
-          <t>update-room.messages.success</t>
+          <t>room.messages.you-lose</t>
         </is>
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>Room updated successfully</t>
+          <t>You lose</t>
         </is>
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>Cập nhật phòng thành công</t>
+          <t>Bạn đã thua</t>
         </is>
       </c>
     </row>
     <row r="297" ht="18" customHeight="1">
       <c r="A297" s="1" t="inlineStr">
         <is>
-          <t>update-room.messages.internal-server-error</t>
+          <t>room.messages.you-win-perpetual-check</t>
         </is>
       </c>
       <c r="B297" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>You win — your opponent lost by perpetual check</t>
         </is>
       </c>
       <c r="C297" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Bạn thắng vì đối thủ chiếu quẩn</t>
         </is>
       </c>
     </row>
     <row r="298" ht="18" customHeight="1">
       <c r="A298" s="1" t="inlineStr">
         <is>
-          <t>update-room.messages.invalid-room-id</t>
+          <t>room.messages.you-lose-perpetual-check</t>
         </is>
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>Invalid room ID</t>
+          <t>You lose by perpetual check</t>
         </is>
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>ID phòng không hợp lệ</t>
+          <t>Bạn thua do chiếu quẩn</t>
         </is>
       </c>
     </row>
     <row r="299" ht="18" customHeight="1">
       <c r="A299" s="1" t="inlineStr">
         <is>
-          <t>update-room.messages.invalid-time-limit</t>
+          <t>room.messages.spectator-win-checkmate</t>
         </is>
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
-          <t>Invalid time limit</t>
+          <t>{0} won by checkmate</t>
         </is>
       </c>
       <c r="C299" s="2" t="inlineStr">
         <is>
-          <t>Thời gian không hợp lệ</t>
+          <t>{0} thắng do chiếu bí</t>
         </is>
       </c>
     </row>
     <row r="300" ht="18" customHeight="1">
       <c r="A300" s="1" t="inlineStr">
         <is>
-          <t>update-room.messages.name-required</t>
+          <t>room.messages.spectator-win-stalemate</t>
         </is>
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>Room name is required</t>
+          <t>{0} won — opponent had no legal moves</t>
         </is>
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>Tên phòng không được để trống</t>
+          <t>{0} thắng do đối thủ hết nước đi</t>
         </is>
       </c>
     </row>
     <row r="301" ht="18" customHeight="1">
       <c r="A301" s="1" t="inlineStr">
         <is>
-          <t>update-room.messages.room-not-found</t>
+          <t>room.messages.spectator-win-timeout</t>
         </is>
       </c>
       <c r="B301" s="2" t="inlineStr">
         <is>
-          <t>Room not found</t>
+          <t>{0} won on time</t>
         </is>
       </c>
       <c r="C301" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy phòng</t>
+          <t>{0} thắng do đối thủ hết giờ</t>
         </is>
       </c>
     </row>
     <row r="302" ht="18" customHeight="1">
       <c r="A302" s="1" t="inlineStr">
         <is>
-          <t>update-room.messages.forbidden</t>
+          <t>room.messages.spectator-win-perpetual-check</t>
         </is>
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>You are not the host of this room</t>
+          <t>{0} won — opponent lost by perpetual check</t>
         </is>
       </c>
       <c r="C302" s="2" t="inlineStr">
         <is>
-          <t>Bạn không phải chủ phòng</t>
+          <t>{0} thắng do đối thủ chiếu quẩn</t>
         </is>
       </c>
     </row>
     <row r="303" ht="18" customHeight="1">
       <c r="A303" s="1" t="inlineStr">
         <is>
-          <t>draw-game.messages.invalid-game-id</t>
+          <t>room.messages.spectator-draw</t>
         </is>
       </c>
       <c r="B303" s="2" t="inlineStr">
         <is>
-          <t>Invalid game ID</t>
+          <t>The game ended in a draw</t>
         </is>
       </c>
       <c r="C303" s="2" t="inlineStr">
         <is>
-          <t>ID trò chơi không hợp lệ</t>
+          <t>Ván đấu kết thúc với tỉ số hòa</t>
         </is>
       </c>
     </row>
     <row r="304" ht="18" customHeight="1">
       <c r="A304" s="1" t="inlineStr">
         <is>
-          <t>draw-game.messages.game-not-found</t>
+          <t>room.messages.back-to-room</t>
         </is>
       </c>
       <c r="B304" s="2" t="inlineStr">
         <is>
-          <t>Game not found</t>
+          <t>Back to room</t>
         </is>
       </c>
       <c r="C304" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy trò chơi</t>
+          <t>Quay lại phòng</t>
         </is>
       </c>
     </row>
     <row r="305" ht="18" customHeight="1">
       <c r="A305" s="1" t="inlineStr">
         <is>
-          <t>draw-game.messages.forbidden</t>
+          <t>room.messages.auto-back-countdown</t>
         </is>
       </c>
       <c r="B305" s="2" t="inlineStr">
         <is>
-          <t>You are not in this room</t>
+          <t>{0}. Press the back button to return to the room. You will be automatically returned in {1}s</t>
         </is>
       </c>
       <c r="C305" s="2" t="inlineStr">
         <is>
-          <t>Bạn không có trong phòng này</t>
+          <t>{0}. Bấm nút quay lại để quay lại room. Bạn sẽ tự động quay lại trong {1}s</t>
         </is>
       </c>
     </row>
     <row r="306" ht="90" customHeight="1">
       <c r="A306" s="1" t="inlineStr">
         <is>
-          <t>draw-game.messages.game-history-not-found</t>
+          <t>room.notifications.joined</t>
         </is>
       </c>
       <c r="B306" s="2" t="inlineStr">
         <is>
-          <t>Game history not found</t>
+          <t>{0} joined the room</t>
         </is>
       </c>
       <c r="C306" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy lịch sử trò chơi</t>
+          <t>{0} đã vào phòng</t>
         </is>
       </c>
     </row>
     <row r="307" ht="90" customHeight="1">
       <c r="A307" s="1" t="inlineStr">
         <is>
-          <t>draw-game.messages.game-already-finished</t>
+          <t>room.notifications.left</t>
         </is>
       </c>
       <c r="B307" s="2" t="inlineStr">
         <is>
-          <t>Game is already finished</t>
+          <t>{0} left the room</t>
         </is>
       </c>
       <c r="C307" s="2" t="inlineStr">
         <is>
-          <t>Trò chơi đã kết thúc</t>
+          <t>{0} đã rời phòng</t>
         </is>
       </c>
     </row>
     <row r="308" ht="18" customHeight="1">
       <c r="A308" s="1" t="inlineStr">
         <is>
-          <t>draw-game.messages.success</t>
+          <t>room.settings.title</t>
         </is>
       </c>
       <c r="B308" s="2" t="inlineStr">
         <is>
-          <t>Draw game successfully</t>
+          <t>Room Settings</t>
         </is>
       </c>
       <c r="C308" s="2" t="inlineStr">
         <is>
-          <t>Hòa cờ thành công</t>
+          <t>Cài đặt phòng</t>
         </is>
       </c>
     </row>
     <row r="309" ht="18" customHeight="1">
       <c r="A309" s="1" t="inlineStr">
         <is>
-          <t>draw-game.messages.internal-server-error</t>
+          <t>room.settings.room-name</t>
         </is>
       </c>
       <c r="B309" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Room name</t>
         </is>
       </c>
       <c r="C309" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Tên phòng</t>
         </is>
       </c>
     </row>
     <row r="310" ht="18" customHeight="1">
       <c r="A310" s="1" t="inlineStr">
         <is>
-          <t>surrender.messages.game-already-finished</t>
+          <t>room.settings.players</t>
         </is>
       </c>
       <c r="B310" s="2" t="inlineStr">
         <is>
-          <t>Game is already finished</t>
+          <t>Spectators</t>
         </is>
       </c>
       <c r="C310" s="2" t="inlineStr">
         <is>
-          <t>Trò chơi đã kết thúc</t>
+          <t>Người xem</t>
         </is>
       </c>
     </row>
     <row r="311" ht="18" customHeight="1">
       <c r="A311" s="2" t="inlineStr">
         <is>
-          <t>surrender.messages.game-history-not-found</t>
+          <t>room.settings.save</t>
         </is>
       </c>
       <c r="B311" s="2" t="inlineStr">
         <is>
-          <t>Game history not found</t>
+          <t>Save</t>
         </is>
       </c>
       <c r="C311" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy lịch sử trò chơi</t>
+          <t>Lưu</t>
         </is>
       </c>
     </row>
     <row r="312" ht="18" customHeight="1">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>surrender.messages.game-not-found</t>
+          <t>room-invite.messages.title</t>
         </is>
       </c>
       <c r="B312" s="2" t="inlineStr">
         <is>
-          <t>Game not found</t>
+          <t>Room Invitation</t>
         </is>
       </c>
       <c r="C312" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy trò chơi</t>
+          <t>Lời mời vào phòng</t>
         </is>
       </c>
     </row>
     <row r="313" ht="18" customHeight="1">
       <c r="A313" s="2" t="inlineStr">
         <is>
-          <t>surrender.messages.internal-server-error</t>
+          <t>start-game.messages.success</t>
         </is>
       </c>
       <c r="B313" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Game started successfully</t>
         </is>
       </c>
       <c r="C313" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Bắt đầu trò chơi thành công</t>
         </is>
       </c>
     </row>
     <row r="314" ht="18" customHeight="1">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>surrender.messages.invalid-game-id</t>
+          <t>start-game.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B314" s="2" t="inlineStr">
         <is>
-          <t>Invalid game ID</t>
+          <t>Internal server error while starting game</t>
         </is>
       </c>
       <c r="C314" s="2" t="inlineStr">
         <is>
-          <t>ID trò chơi không hợp lệ</t>
+          <t>Lỗi máy chủ nội bộ khi bắt đầu trò chơi</t>
         </is>
       </c>
     </row>
     <row r="315" ht="54" customHeight="1">
       <c r="A315" s="2" t="inlineStr">
         <is>
-          <t>surrender.messages.invalid-surrender-player</t>
+          <t>start-game.messages.invalid-room-id</t>
         </is>
       </c>
       <c r="B315" s="2" t="inlineStr">
         <is>
-          <t>You are not a player in this game</t>
+          <t>Field 'id' is required and must be a positive integer</t>
         </is>
       </c>
       <c r="C315" s="2" t="inlineStr">
         <is>
-          <t>Bạn không phải là người chơi trong trò chơi này</t>
+          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
         </is>
       </c>
     </row>
     <row r="316" ht="18" customHeight="1">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>surrender.messages.opponent-not-found</t>
+          <t>start-game.messages.invalid-difficulty</t>
         </is>
       </c>
       <c r="B316" s="2" t="inlineStr">
         <is>
-          <t>Opponent not found</t>
+          <t>Bot difficulty must be between 1 and 5</t>
         </is>
       </c>
       <c r="C316" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy đối thủ</t>
+          <t>Độ khó của bot phải từ 1 đến 5</t>
         </is>
       </c>
     </row>
     <row r="317" ht="90" customHeight="1">
       <c r="A317" s="2" t="inlineStr">
         <is>
-          <t>surrender.messages.success</t>
+          <t>start-game.messages.room-not-found</t>
         </is>
       </c>
       <c r="B317" s="2" t="inlineStr">
         <is>
-          <t>Surrendered</t>
+          <t>Room not found</t>
         </is>
       </c>
       <c r="C317" s="2" t="inlineStr">
         <is>
-          <t>Đã đầu hàng</t>
+          <t>Không tìm thấy phòng</t>
         </is>
       </c>
     </row>
     <row r="318" ht="18" customHeight="1">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>undo.messages.invalid-game-id</t>
+          <t>start-game.messages.forbidden</t>
         </is>
       </c>
       <c r="B318" s="2" t="inlineStr">
         <is>
-          <t>Invalid game ID</t>
+          <t>Only the room host can start the game</t>
         </is>
       </c>
       <c r="C318" s="2" t="inlineStr">
         <is>
-          <t>ID trò chơi không hợp lệ</t>
+          <t>Chỉ chủ phòng mới có thể bắt đầu trò chơi</t>
         </is>
       </c>
     </row>
     <row r="319" ht="36" customHeight="1">
       <c r="A319" s="2" t="inlineStr">
         <is>
-          <t>undo.messages.unauthorized</t>
+          <t>start-game.messages.insufficient-amount</t>
         </is>
       </c>
       <c r="B319" s="2" t="inlineStr">
         <is>
-          <t>Unauthorized</t>
+          <t>You do not have enough balance to start a game with this bet</t>
         </is>
       </c>
       <c r="C319" s="2" t="inlineStr">
         <is>
-          <t>Không được phép truy cập</t>
+          <t>Bạn không còn đủ amount để start room</t>
         </is>
       </c>
     </row>
     <row r="320" ht="18" customHeight="1">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>undo.messages.game-not-found</t>
+          <t>start-game.messages.requester-must-pick-team</t>
         </is>
       </c>
       <c r="B320" s="2" t="inlineStr">
         <is>
-          <t>Game not found</t>
+          <t>You must select a team before starting a game with bot</t>
         </is>
       </c>
       <c r="C320" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy trò chơi</t>
+          <t>Bạn phải chọn team trước khi bắt đầu trò chơi với bot</t>
         </is>
       </c>
     </row>
     <row r="321" ht="72" customHeight="1">
       <c r="A321" s="2" t="inlineStr">
         <is>
-          <t>undo.messages.not-in-game</t>
+          <t>update-room.messages.success</t>
         </is>
       </c>
       <c r="B321" s="2" t="inlineStr">
         <is>
-          <t>You are not part of this game</t>
+          <t>Room updated successfully</t>
         </is>
       </c>
       <c r="C321" s="2" t="inlineStr">
         <is>
-          <t>Bạn không phải là người chơi trong trò chơi này</t>
+          <t>Cập nhật phòng thành công</t>
         </is>
       </c>
     </row>
     <row r="322" ht="18" customHeight="1">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>undo.messages.not-in-room</t>
+          <t>update-room.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B322" s="2" t="inlineStr">
         <is>
-          <t>You are not in this room</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C322" s="2" t="inlineStr">
         <is>
-          <t>Bạn không trong phòng này</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="323" ht="54" customHeight="1">
       <c r="A323" s="2" t="inlineStr">
         <is>
-          <t>undo.messages.spectator-cannot-undo</t>
+          <t>update-room.messages.invalid-room-id</t>
         </is>
       </c>
       <c r="B323" s="2" t="inlineStr">
         <is>
-          <t>Spectators cannot undo moves</t>
+          <t>Invalid room ID</t>
         </is>
       </c>
       <c r="C323" s="2" t="inlineStr">
         <is>
-          <t>Người xem không thể hoàn tác nước đi</t>
+          <t>ID phòng không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="324" ht="18" customHeight="1">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>undo.messages.no-moves</t>
+          <t>update-room.messages.invalid-time-limit</t>
         </is>
       </c>
       <c r="B324" s="2" t="inlineStr">
         <is>
-          <t>No moves to undo</t>
+          <t>Invalid time limit</t>
         </is>
       </c>
       <c r="C324" s="2" t="inlineStr">
         <is>
-          <t>Không có nước đi để hoàn tác</t>
+          <t>Thời gian không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="325" ht="72" customHeight="1">
       <c r="A325" s="2" t="inlineStr">
         <is>
-          <t>undo.messages.delete-failed</t>
+          <t>update-room.messages.invalid-time-increment</t>
         </is>
       </c>
       <c r="B325" s="2" t="inlineStr">
         <is>
-          <t>Failed to undo move</t>
+          <t>Invalid bonus per move</t>
         </is>
       </c>
       <c r="C325" s="2" t="inlineStr">
         <is>
-          <t>Không thể hoàn tác nước đi</t>
+          <t>Thời gian cộng mỗi nước không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="326" ht="18" customHeight="1">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>undo.messages.undo-limit-exceeded</t>
+          <t>update-room.messages.invalid-time-per-move</t>
         </is>
       </c>
       <c r="B326" s="2" t="inlineStr">
         <is>
-          <t>Maximum 3 undo per game exceeded</t>
+          <t>Invalid time per move</t>
         </is>
       </c>
       <c r="C326" s="2" t="inlineStr">
         <is>
-          <t>Đã đạt tối đa 3 lần hoàn tác trong trò chơi</t>
+          <t>Thời gian mỗi nước không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="327" ht="90" customHeight="1">
       <c r="A327" s="2" t="inlineStr">
         <is>
-          <t>undo.messages.success</t>
+          <t>update-room.messages.name-required</t>
         </is>
       </c>
       <c r="B327" s="2" t="inlineStr">
         <is>
-          <t>Move undone successfully</t>
+          <t>Room name is required</t>
         </is>
       </c>
       <c r="C327" s="2" t="inlineStr">
         <is>
-          <t>Hoàn tác nước đi thành công</t>
+          <t>Tên phòng không được để trống</t>
         </is>
       </c>
     </row>
     <row r="328" ht="18" customHeight="1">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>undo.messages.internal-server-error</t>
+          <t>update-room.messages.room-not-found</t>
         </is>
       </c>
       <c r="B328" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Room not found</t>
         </is>
       </c>
       <c r="C328" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Không tìm thấy phòng</t>
         </is>
       </c>
     </row>
     <row r="329" ht="72" customHeight="1">
       <c r="A329" s="2" t="inlineStr">
         <is>
-          <t>player-history.messages.invalid-user-id</t>
+          <t>update-room.messages.forbidden</t>
         </is>
       </c>
       <c r="B329" s="2" t="inlineStr">
         <is>
-          <t>Invalid user ID</t>
+          <t>You are not the host of this room</t>
         </is>
       </c>
       <c r="C329" s="2" t="inlineStr">
         <is>
-          <t>ID người dùng không hợp lệ</t>
+          <t>Bạn không phải chủ phòng</t>
         </is>
       </c>
     </row>
     <row r="330" ht="54" customHeight="1">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>player-history.messages.success</t>
+          <t>draw-game.messages.invalid-game-id</t>
         </is>
       </c>
       <c r="B330" s="2" t="inlineStr">
         <is>
-          <t>Fetch game history successfully</t>
+          <t>Invalid game ID</t>
         </is>
       </c>
       <c r="C330" s="2" t="inlineStr">
         <is>
-          <t>Lấy lịch sử trò chơi thành công</t>
+          <t>ID trò chơi không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="331" ht="54" customHeight="1">
       <c r="A331" s="2" t="inlineStr">
         <is>
-          <t>validate-token.messages.success</t>
+          <t>draw-game.messages.game-not-found</t>
         </is>
       </c>
       <c r="B331" s="2" t="inlineStr">
         <is>
-          <t>Token is valid</t>
+          <t>Game not found</t>
         </is>
       </c>
       <c r="C331" s="2" t="inlineStr">
         <is>
-          <t>Token hợp lệ</t>
+          <t>Không tìm thấy trò chơi</t>
         </is>
       </c>
     </row>
     <row r="332" ht="54" customHeight="1">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>guide.section.objective</t>
+          <t>draw-game.messages.forbidden</t>
         </is>
       </c>
       <c r="B332" s="2" t="inlineStr">
         <is>
-          <t>Objective of the game</t>
+          <t>You are not in this room</t>
         </is>
       </c>
       <c r="C332" s="2" t="inlineStr">
         <is>
-          <t>Mục tiêu của trò chơi</t>
+          <t>Bạn không có trong phòng này</t>
         </is>
       </c>
     </row>
     <row r="333" ht="90" customHeight="1">
       <c r="A333" s="2" t="inlineStr">
         <is>
-          <t>guide.section.pieces</t>
+          <t>draw-game.messages.game-history-not-found</t>
         </is>
       </c>
       <c r="B333" s="2" t="inlineStr">
         <is>
-          <t>Pieces</t>
+          <t>Game history not found</t>
         </is>
       </c>
       <c r="C333" s="2" t="inlineStr">
         <is>
-          <t>Quân cờ</t>
+          <t>Không tìm thấy lịch sử trò chơi</t>
         </is>
       </c>
     </row>
     <row r="334" ht="54" customHeight="1">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>guide.section.moving-pieces</t>
+          <t>draw-game.messages.game-already-finished</t>
         </is>
       </c>
       <c r="B334" s="2" t="inlineStr">
         <is>
-          <t>Moving pieces</t>
+          <t>Game is already finished</t>
         </is>
       </c>
       <c r="C334" s="2" t="inlineStr">
         <is>
-          <t>Đi quân</t>
+          <t>Trò chơi đã kết thúc</t>
         </is>
       </c>
     </row>
     <row r="335" ht="36" customHeight="1">
       <c r="A335" s="2" t="inlineStr">
         <is>
-          <t>guide.section.capturing</t>
+          <t>draw-game.messages.success</t>
         </is>
       </c>
       <c r="B335" s="2" t="inlineStr">
         <is>
-          <t>Capturing</t>
+          <t>Draw game successfully</t>
         </is>
       </c>
       <c r="C335" s="2" t="inlineStr">
         <is>
-          <t>Bắt quân</t>
+          <t>Hòa cờ thành công</t>
         </is>
       </c>
     </row>
     <row r="336" ht="18" customHeight="1">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>guide.section.check</t>
+          <t>draw-game.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B336" s="2" t="inlineStr">
         <is>
-          <t>Check</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C336" s="2" t="inlineStr">
         <is>
-          <t>Chiếu tướng</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="337" ht="36" customHeight="1">
       <c r="A337" s="2" t="inlineStr">
         <is>
-          <t>guide.section.result</t>
+          <t>surrender.messages.game-already-finished</t>
         </is>
       </c>
       <c r="B337" s="2" t="inlineStr">
         <is>
-          <t>Result</t>
+          <t>Game is already finished</t>
         </is>
       </c>
       <c r="C337" s="2" t="inlineStr">
         <is>
-          <t>Kết quả</t>
+          <t>Trò chơi đã kết thúc</t>
         </is>
       </c>
     </row>
     <row r="338" ht="36" customHeight="1">
       <c r="A338" s="2" t="inlineStr">
         <is>
-          <t>guide.table.piece</t>
+          <t>surrender.messages.game-history-not-found</t>
         </is>
       </c>
       <c r="B338" s="2" t="inlineStr">
         <is>
-          <t>Piece</t>
+          <t>Game history not found</t>
         </is>
       </c>
       <c r="C338" s="2" t="inlineStr">
         <is>
-          <t>Quân</t>
+          <t>Không tìm thấy lịch sử trò chơi</t>
         </is>
       </c>
     </row>
     <row r="339" ht="72" customHeight="1">
       <c r="A339" s="2" t="inlineStr">
         <is>
-          <t>guide.table.symbol</t>
+          <t>surrender.messages.game-not-found</t>
         </is>
       </c>
       <c r="B339" s="2" t="inlineStr">
         <is>
-          <t>Symbol</t>
+          <t>Game not found</t>
         </is>
       </c>
       <c r="C339" s="2" t="inlineStr">
         <is>
-          <t>Ký hiệu</t>
+          <t>Không tìm thấy trò chơi</t>
         </is>
       </c>
     </row>
     <row r="340" ht="54" customHeight="1">
       <c r="A340" s="2" t="inlineStr">
         <is>
-          <t>guide.table.quantity</t>
+          <t>surrender.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B340" s="2" t="inlineStr">
         <is>
-          <t>Quantity</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C340" s="2" t="inlineStr">
         <is>
-          <t>Số lượng</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="341" ht="54" customHeight="1">
       <c r="A341" s="2" t="inlineStr">
         <is>
-          <t>guide.objective.paragraph1</t>
+          <t>surrender.messages.invalid-game-id</t>
         </is>
       </c>
       <c r="B341" s="2" t="inlineStr">
         <is>
-          <t>A match is played between two players: one controls the Red pieces, and the other controls the Black pieces. The objective of each player is to use their pieces on the board to &lt;b&gt;checkmate&lt;/b&gt; the opponent's General, and win the game.</t>
+          <t>Invalid game ID</t>
         </is>
       </c>
       <c r="C341" s="2" t="inlineStr">
         <is>
-          <t>Ván cờ được tiến hành giữa 2 đấu thủ, một người cầm Quân Đỏ, một người cầm Quân Đen. Mục đích của mỗi đấu thủ là tìm mọi cách sử dụng các quân trên bàn cờ để &lt;b&gt;chiếu bí Tướng&lt;/b&gt; của đối phương, giành thắng lợi.</t>
+          <t>ID trò chơi không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="342" ht="90" customHeight="1">
       <c r="A342" s="2" t="inlineStr">
         <is>
-          <t>guide.pieces.paragraph1</t>
+          <t>surrender.messages.invalid-surrender-player</t>
         </is>
       </c>
       <c r="B342" s="2" t="inlineStr">
         <is>
-          <t>At the start of each game, there must be 32 pieces in total, consisting of &lt;b&gt;7 piece types&lt;/b&gt; split evenly between both sides: 16 Red pieces and 16 Black pieces. The 7 piece types with their symbols and quantities are as follows:</t>
+          <t>You are not a player in this game</t>
         </is>
       </c>
       <c r="C342" s="2" t="inlineStr">
         <is>
-          <t>Mỗi ván cờ lúc bắt đầu phải có đủ 32 quân, gồm 7 loại chia đều cho mỗi bên gồm 16 quân Đỏ và 16 quân Đen. &lt;b&gt;7 loại quân&lt;/b&gt; có ký hiệu và số lượng như sau:</t>
+          <t>Bạn không phải là người chơi trong trò chơi này</t>
         </is>
       </c>
     </row>
     <row r="343" ht="54" customHeight="1">
       <c r="A343" s="2" t="inlineStr">
         <is>
-          <t>guide.piece.general</t>
+          <t>surrender.messages.opponent-not-found</t>
         </is>
       </c>
       <c r="B343" s="2" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Opponent not found</t>
         </is>
       </c>
       <c r="C343" s="2" t="inlineStr">
         <is>
-          <t>Tướng</t>
+          <t>Không tìm thấy đối thủ</t>
         </is>
       </c>
     </row>
     <row r="344" ht="18" customHeight="1">
       <c r="A344" s="2" t="inlineStr">
         <is>
-          <t>guide.piece.advisor</t>
+          <t>surrender.messages.success</t>
         </is>
       </c>
       <c r="B344" s="2" t="inlineStr">
         <is>
-          <t>Advisor</t>
+          <t>Surrendered</t>
         </is>
       </c>
       <c r="C344" s="2" t="inlineStr">
         <is>
-          <t>Sĩ</t>
+          <t>Đã đầu hàng</t>
         </is>
       </c>
     </row>
     <row r="345" ht="18" customHeight="1">
       <c r="A345" s="2" t="inlineStr">
         <is>
-          <t>guide.piece.elephant</t>
+          <t>undo.messages.invalid-game-id</t>
         </is>
       </c>
       <c r="B345" s="2" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Invalid game ID</t>
         </is>
       </c>
       <c r="C345" s="2" t="inlineStr">
         <is>
-          <t>Tượng</t>
+          <t>ID trò chơi không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="346" ht="36" customHeight="1">
       <c r="A346" s="2" t="inlineStr">
         <is>
-          <t>guide.piece.chariot</t>
+          <t>undo.messages.unauthorized</t>
         </is>
       </c>
       <c r="B346" s="2" t="inlineStr">
         <is>
-          <t>Chariot</t>
+          <t>Unauthorized</t>
         </is>
       </c>
       <c r="C346" s="2" t="inlineStr">
         <is>
-          <t>Xe</t>
+          <t>Không được phép truy cập</t>
         </is>
       </c>
     </row>
     <row r="347" ht="18" customHeight="1">
       <c r="A347" s="2" t="inlineStr">
         <is>
-          <t>guide.piece.horse</t>
+          <t>undo.messages.game-not-found</t>
         </is>
       </c>
       <c r="B347" s="2" t="inlineStr">
         <is>
-          <t>Horse</t>
+          <t>Game not found</t>
         </is>
       </c>
       <c r="C347" s="2" t="inlineStr">
         <is>
-          <t>Mã</t>
+          <t>Không tìm thấy trò chơi</t>
         </is>
       </c>
     </row>
     <row r="348" ht="18" customHeight="1">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>guide.piece.cannon</t>
+          <t>undo.messages.not-in-game</t>
         </is>
       </c>
       <c r="B348" s="2" t="inlineStr">
         <is>
-          <t>Cannon</t>
+          <t>You are not part of this game</t>
         </is>
       </c>
       <c r="C348" s="2" t="inlineStr">
         <is>
-          <t>Pháo</t>
+          <t>Bạn không phải là người chơi trong trò chơi này</t>
         </is>
       </c>
     </row>
     <row r="349" ht="36" customHeight="1">
       <c r="A349" s="2" t="inlineStr">
         <is>
-          <t>guide.piece.soldier</t>
+          <t>undo.messages.not-in-room</t>
         </is>
       </c>
       <c r="B349" s="2" t="inlineStr">
         <is>
-          <t>Soldier</t>
+          <t>You are not in this room</t>
         </is>
       </c>
       <c r="C349" s="2" t="inlineStr">
         <is>
-          <t>Tốt</t>
+          <t>Bạn không trong phòng này</t>
         </is>
       </c>
     </row>
     <row r="350" ht="18" customHeight="1">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>guide.moving-pieces.paragraph1</t>
+          <t>undo.messages.pve-only</t>
         </is>
       </c>
       <c r="B350" s="2" t="inlineStr">
         <is>
-          <t>On each turn, each side may move only one of its own pieces according to the rules. The movement rules are as follows:</t>
+          <t>Undo is only available in PvE rooms</t>
         </is>
       </c>
       <c r="C350" s="2" t="inlineStr">
         <is>
-          <t>Mỗi nước đi, mỗi bên chỉ được di chuyển quân của mình theo đúng quy định. Quy định di chuyển của các quân như sau:</t>
+          <t>Hoàn tác chỉ khả dụng trong phòng PvE</t>
         </is>
       </c>
     </row>
     <row r="351" ht="36" customHeight="1">
       <c r="A351" s="2" t="inlineStr">
         <is>
-          <t>guide.general.paragraph1</t>
+          <t>undo.messages.spectator-cannot-undo</t>
         </is>
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Spectators cannot undo moves</t>
         </is>
       </c>
       <c r="C351" s="2" t="inlineStr">
         <is>
-          <t>Tướng</t>
+          <t>Người xem không thể hoàn tác nước đi</t>
         </is>
       </c>
     </row>
     <row r="352" ht="18" customHeight="1">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>guide.general.paragraph2</t>
+          <t>undo.messages.no-moves</t>
         </is>
       </c>
       <c r="B352" s="2" t="inlineStr">
         <is>
-          <t>Moves one step &lt;b&gt;horizontally or vertically&lt;/b&gt; within the palace. The two Generals may not face each other directly on the same file. If they are facing each other, there must be at least one piece of either side placed between them.</t>
+          <t>No moves to undo</t>
         </is>
       </c>
       <c r="C352" s="2" t="inlineStr">
         <is>
-          <t>Mỗi nước được đi một bước &lt;b&gt;ngang hoặc dọc&lt;/b&gt; tùy ý trong cung Tướng. Hai tướng của 2 bên không được đối mặt nhau trực tiếp trên cùng một đường thẳng. Nếu đối mặt, bắt buộc phải có quân của bất kỳ bên nào đứng che mặt.</t>
+          <t>Không có nước đi để hoàn tác</t>
         </is>
       </c>
     </row>
     <row r="353" ht="18" customHeight="1">
       <c r="A353" s="2" t="inlineStr">
         <is>
-          <t>guide.advisor.paragraph1</t>
+          <t>undo.messages.delete-failed</t>
         </is>
       </c>
       <c r="B353" s="2" t="inlineStr">
         <is>
-          <t>Advisor</t>
+          <t>Failed to undo move</t>
         </is>
       </c>
       <c r="C353" s="2" t="inlineStr">
         <is>
-          <t>Sĩ</t>
+          <t>Không thể hoàn tác nước đi</t>
         </is>
       </c>
     </row>
     <row r="354" ht="18" customHeight="1">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>guide.advisor.paragraph2</t>
+          <t>undo.messages.undo-limit-exceeded</t>
         </is>
       </c>
       <c r="B354" s="2" t="inlineStr">
         <is>
-          <t>Moves one step &lt;b&gt;diagonally&lt;/b&gt; within the palace.</t>
+          <t>Maximum 3 undo per game exceeded</t>
         </is>
       </c>
       <c r="C354" s="2" t="inlineStr">
         <is>
-          <t>Mỗi nước &lt;b&gt;đi chéo một bước&lt;/b&gt; trong cung Tướng.</t>
+          <t>Đã đạt tối đa 3 lần hoàn tác trong trò chơi</t>
         </is>
       </c>
     </row>
     <row r="355" ht="18" customHeight="1">
       <c r="A355" s="2" t="inlineStr">
         <is>
-          <t>guide.elephant.paragraph1</t>
+          <t>undo.messages.success</t>
         </is>
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Move undone successfully</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
         <is>
-          <t>Tượng</t>
+          <t>Hoàn tác nước đi thành công</t>
         </is>
       </c>
     </row>
     <row r="356" ht="18" customHeight="1">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>guide.elephant.paragraph2</t>
+          <t>undo.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B356" s="2" t="inlineStr">
         <is>
-          <t>Moves &lt;b&gt;two steps diagonally&lt;/b&gt; on its own side of the board and may not cross the river. If there is another piece on the midpoint of that diagonal path, the Elephant is blocked and cannot move.</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C356" s="2" t="inlineStr">
         <is>
-          <t>Mỗi nước &lt;b&gt;đi chéo hai bước&lt;/b&gt; tại trận địa bên mình, không được qua sông. Nếu ở giữa đường chéo đó có quân khác đứng thì quân Tượng bị cản, không đi được.</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="357" ht="17" customHeight="1">
       <c r="A357" s="2" t="inlineStr">
         <is>
-          <t>guide.chariot.paragraph1</t>
+          <t>player-history.messages.invalid-user-id</t>
         </is>
       </c>
       <c r="B357" s="2" t="inlineStr">
         <is>
-          <t>Chariot</t>
+          <t>Invalid user ID</t>
         </is>
       </c>
       <c r="C357" s="2" t="inlineStr">
         <is>
-          <t>Xe</t>
+          <t>ID người dùng không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="358" ht="18" customHeight="1">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>guide.chariot.paragraph2</t>
+          <t>player-history.messages.success</t>
         </is>
       </c>
       <c r="B358" s="2" t="inlineStr">
         <is>
-          <t>Moves &lt;b&gt;horizontally or vertically&lt;/b&gt; with no limit on distance, as long as no piece blocks the path.</t>
+          <t>Fetch game history successfully</t>
         </is>
       </c>
       <c r="C358" s="2" t="inlineStr">
         <is>
-          <t>Mỗi nước được &lt;b&gt;đi dọc hoặc đi ngang&lt;/b&gt;, không hạn chế số bước đi nếu không có quân khác cản đường.</t>
+          <t>Lấy lịch sử trò chơi thành công</t>
         </is>
       </c>
     </row>
     <row r="359" ht="18" customHeight="1">
       <c r="A359" s="2" t="inlineStr">
         <is>
-          <t>guide.horse.paragraph1</t>
+          <t>validate-token.messages.success</t>
         </is>
       </c>
       <c r="B359" s="2" t="inlineStr">
         <is>
-          <t>Horse</t>
+          <t>Token is valid</t>
         </is>
       </c>
       <c r="C359" s="2" t="inlineStr">
         <is>
-          <t>Mã</t>
+          <t>Token hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="360" ht="18" customHeight="1">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>guide.horse.paragraph2</t>
+          <t>guide.section.objective</t>
         </is>
       </c>
       <c r="B360" s="2" t="inlineStr">
         <is>
-          <t>Moves in an &lt;b&gt;L-shape&lt;/b&gt; (one step orthogonally then one step diagonally outward). If the adjacent orthogonal point is occupied by any piece, the Horse is blocked and cannot move.</t>
+          <t>Objective of the game</t>
         </is>
       </c>
       <c r="C360" s="2" t="inlineStr">
         <is>
-          <t>Đi theo &lt;b&gt;đường chéo hình chữ nhật&lt;/b&gt; của hai ô vuông liền nhau. Nếu giao điểm liền kề bước thẳng dọc ngang có một quân khác đứng thì Mã bị cản, không đi được.</t>
+          <t>Mục tiêu của trò chơi</t>
         </is>
       </c>
     </row>
     <row r="361" ht="18" customHeight="1">
       <c r="A361" s="2" t="inlineStr">
         <is>
-          <t>guide.cannon.paragraph1</t>
+          <t>guide.section.pieces</t>
         </is>
       </c>
       <c r="B361" s="2" t="inlineStr">
         <is>
-          <t>Cannon</t>
+          <t>Pieces</t>
         </is>
       </c>
       <c r="C361" s="2" t="inlineStr">
         <is>
-          <t>Pháo</t>
+          <t>Quân cờ</t>
         </is>
       </c>
     </row>
     <row r="362" ht="18" customHeight="1">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>guide.cannon.paragraph2</t>
+          <t>guide.section.moving-pieces</t>
         </is>
       </c>
       <c r="B362" s="2" t="inlineStr">
         <is>
-          <t>Moves &lt;b&gt;horizontally or vertically&lt;/b&gt; like a Chariot when not capturing. To capture, it must &lt;b&gt;jump over exactly one piece&lt;/b&gt; to reach its target. If there are zero or more than one pieces between the Cannon and the target, it cannot capture.</t>
+          <t>Moving pieces</t>
         </is>
       </c>
       <c r="C362" s="2" t="inlineStr">
         <is>
-          <t>Đi ngang hoặc dọc giống Xe khi không bắt quân. Để bắt quân, nó phải &lt;b&gt;nhảy qua đúng một quân khác&lt;/b&gt; để đến mục tiêu. Nếu không có hoặc có nhiều hơn một quân giữa Pháo và mục tiêu, nó không thể bắt quân.</t>
+          <t>Đi quân</t>
         </is>
       </c>
     </row>
     <row r="363" ht="18" customHeight="1">
       <c r="A363" s="2" t="inlineStr">
         <is>
-          <t>guide.soldier.paragraph1</t>
+          <t>guide.section.capturing</t>
         </is>
       </c>
       <c r="B363" s="2" t="inlineStr">
         <is>
-          <t>Soldier</t>
+          <t>Capturing</t>
         </is>
       </c>
       <c r="C363" s="2" t="inlineStr">
         <is>
-          <t>Tốt</t>
+          <t>Bắt quân</t>
         </is>
       </c>
     </row>
     <row r="364" ht="17" customHeight="1">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>guide.soldier.paragraph2</t>
+          <t>guide.section.check</t>
         </is>
       </c>
       <c r="B364" s="2" t="inlineStr">
         <is>
-          <t>Moves &lt;b&gt;one step&lt;/b&gt; each turn. Before crossing the river, it can only move forward. After crossing the river, it may move &lt;b&gt;forward or sideways&lt;/b&gt;, but never backward.</t>
+          <t>Check</t>
         </is>
       </c>
       <c r="C364" s="2" t="inlineStr">
         <is>
-          <t>Mỗi nước đi &lt;b&gt;một bước&lt;/b&gt;. Khi chưa qua sông, Tốt chỉ được tiến. Khi Tốt đã qua sông được quyền &lt;b&gt;đi tiến và đi ngang&lt;/b&gt;, không được phép lùi.</t>
+          <t>Chiếu tướng</t>
         </is>
       </c>
     </row>
     <row r="365" ht="17" customHeight="1">
       <c r="A365" s="2" t="inlineStr">
         <is>
-          <t>guide.capturing.paragraph1</t>
+          <t>guide.section.result</t>
         </is>
       </c>
       <c r="B365" s="2" t="inlineStr">
         <is>
-          <t>When a piece moves to an intersection occupied by an opponent's piece, it may &lt;b&gt;capture that piece&lt;/b&gt; and occupy its position.</t>
+          <t>Result</t>
         </is>
       </c>
       <c r="C365" s="2" t="inlineStr">
         <is>
-          <t>Khi một quân đi tới một giao điểm khác đã có quân đối phương đứng thì được quyền &lt;b&gt;bắt quân đó&lt;/b&gt;, đồng thời chiếm giữ vị trí quân bị bắt.</t>
+          <t>Kết quả</t>
         </is>
       </c>
     </row>
     <row r="366" ht="17" customHeight="1">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>guide.capturing.paragraph2</t>
+          <t>guide.table.piece</t>
         </is>
       </c>
       <c r="B366" s="2" t="inlineStr">
         <is>
-          <t>You may not capture your own pieces. You may sacrifice your own pieces to be captured by the opponent, &lt;b&gt;except for the General&lt;/b&gt;.</t>
+          <t>Piece</t>
         </is>
       </c>
       <c r="C366" s="2" t="inlineStr">
         <is>
-          <t>Không được bắt quân bên mình. Được phép cho đối phương bắt đầu quân mình chủ động hiến mình cho đối phương, &lt;b&gt;trừ Tướng&lt;/b&gt;.</t>
+          <t>Quân</t>
         </is>
       </c>
     </row>
     <row r="367" ht="17" customHeight="1">
       <c r="A367" s="2" t="inlineStr">
         <is>
-          <t>guide.capturing.paragraph3</t>
+          <t>guide.table.symbol</t>
         </is>
       </c>
       <c r="B367" s="2" t="inlineStr">
         <is>
-          <t>A captured piece is removed from the board. &lt;b&gt;Chasing one piece for more than 6 consecutive moves is not allowed&lt;/b&gt;.</t>
+          <t>Symbol</t>
         </is>
       </c>
       <c r="C367" s="2" t="inlineStr">
         <is>
-          <t>Quân bị bắt phải bị loại và bị nhấc ra khỏi bàn cờ. &lt;b&gt;Không được đuổi 1 quân quá 6 nước cờ liên tiếp&lt;/b&gt;.</t>
+          <t>Ký hiệu</t>
         </is>
       </c>
     </row>
     <row r="368" ht="17" customHeight="1">
       <c r="A368" s="2" t="inlineStr">
         <is>
-          <t>guide.check.paragraph1</t>
+          <t>guide.table.quantity</t>
         </is>
       </c>
       <c r="B368" s="2" t="inlineStr">
         <is>
-          <t>If a player makes a move that threatens to capture the opponent's General on the next move (by the same piece or another piece), it is called a &lt;b&gt;Check&lt;/b&gt;. The checked side must respond to avoid check. Otherwise, that side loses</t>
+          <t>Quantity</t>
         </is>
       </c>
       <c r="C368" s="2" t="inlineStr">
         <is>
-          <t>Nếu người chơi thực hiện một nước đi đe dọa bắt Tướng của đối phương ở nước đi tiếp theo (bằng chính quân cờ đó hoặc một quân cờ khác), thì đó được gọi là &lt;b&gt;Chiếu&lt;/b&gt;. Bên bị chiếu phải đáp trả để tránh bị chiếu. Nếu không sẽ bị xử thua</t>
+          <t>Số lượng</t>
         </is>
       </c>
     </row>
     <row r="369" ht="17" customHeight="1">
       <c r="A369" s="2" t="inlineStr">
         <is>
-          <t>guide.check.paragraph2</t>
+          <t>guide.objective.paragraph1</t>
         </is>
       </c>
       <c r="B369" s="2" t="inlineStr">
         <is>
-          <t>When the General is checked from any direction (including from behind), the checked side may respond in one of the following ways:</t>
+          <t>A match is played between two players: one controls the Red pieces, and the other controls the Black pieces. The objective of each player is to use their pieces on the board to &lt;b&gt;checkmate&lt;/b&gt; the opponent's General, and win the game.</t>
         </is>
       </c>
       <c r="C369" s="2" t="inlineStr">
         <is>
-          <t>Tướng bị chiếu từ cả bốn hướng (bị chiếu cả từ phía sau) có thể ứng phó với nước chiếu tướng bằng một trong các cách sau:</t>
+          <t>Ván cờ được tiến hành giữa 2 đấu thủ, một người cầm Quân Đỏ, một người cầm Quân Đen. Mục đích của mỗi đấu thủ là tìm mọi cách sử dụng các quân trên bàn cờ để &lt;b&gt;chiếu bí Tướng&lt;/b&gt; của đối phương, giành thắng lợi.</t>
         </is>
       </c>
     </row>
     <row r="370" ht="17" customHeight="1">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>guide.check.paragraph3</t>
+          <t>guide.pieces.paragraph1</t>
         </is>
       </c>
       <c r="B370" s="2" t="inlineStr">
         <is>
-          <t>Move the General to another position to escape check</t>
+          <t>At the start of each game, there must be 32 pieces in total, consisting of &lt;b&gt;7 piece types&lt;/b&gt; split evenly between both sides: 16 Red pieces and 16 Black pieces. The 7 piece types with their symbols and quantities are as follows:</t>
         </is>
       </c>
       <c r="C370" s="2" t="inlineStr">
         <is>
-          <t>Di chuyển tướng sang vị trí khác để tránh nước chiếu</t>
+          <t>Mỗi ván cờ lúc bắt đầu phải có đủ 32 quân, gồm 7 loại chia đều cho mỗi bên gồm 16 quân Đỏ và 16 quân Đen. &lt;b&gt;7 loại quân&lt;/b&gt; có ký hiệu và số lượng như sau:</t>
         </is>
       </c>
     </row>
     <row r="371" ht="17" customHeight="1">
       <c r="A371" s="2" t="inlineStr">
         <is>
-          <t>guide.check.paragraph4</t>
+          <t>guide.piece.general</t>
         </is>
       </c>
       <c r="B371" s="2" t="inlineStr">
         <is>
-          <t>Capture the checking piece</t>
+          <t>General</t>
         </is>
       </c>
       <c r="C371" s="2" t="inlineStr">
         <is>
-          <t>Bắt quân đang chiếu</t>
+          <t>Tướng</t>
         </is>
       </c>
     </row>
     <row r="372" ht="17" customHeight="1">
       <c r="A372" s="2" t="inlineStr">
         <is>
-          <t>guide.check.paragraph5</t>
+          <t>guide.piece.advisor</t>
         </is>
       </c>
       <c r="B372" s="2" t="inlineStr">
         <is>
-          <t>Block the checking line with another piece to protect the General</t>
+          <t>Advisor</t>
         </is>
       </c>
       <c r="C372" s="2" t="inlineStr">
         <is>
-          <t>Dùng quân khác cản quân chiếu, đi quân che đỡ cho tướng</t>
+          <t>Sĩ</t>
         </is>
       </c>
     </row>
     <row r="373" ht="17" customHeight="1">
       <c r="A373" s="2" t="inlineStr">
         <is>
-          <t>guide.check.paragraph6</t>
+          <t>guide.piece.elephant</t>
         </is>
       </c>
       <c r="B373" s="2" t="inlineStr">
         <is>
-          <t>Repeatedly checking for more than 6 consecutive moves is not allowed</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="C373" s="2" t="inlineStr">
         <is>
-          <t>Không được chiếu tướng quá 6 nước cờ liên tiếp</t>
+          <t>Tượng</t>
         </is>
       </c>
     </row>
     <row r="374" ht="17" customHeight="1">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>guide.result.paragraph1</t>
+          <t>guide.piece.chariot</t>
         </is>
       </c>
       <c r="B374" s="2" t="inlineStr">
         <is>
-          <t>When one side gives Check and the other side has no legal way to protect the General, it is called a &lt;b&gt;Checkmate&lt;/b&gt;. The side that delivers Checkmate wins.</t>
+          <t>Chariot</t>
         </is>
       </c>
       <c r="C374" s="2" t="inlineStr">
         <is>
-          <t>Khi một bên chiếu Tướng mà bên còn lại không thể làm gì để bảo vệ Tướng thì được gọi là &lt;b&gt;Chiếu Hết&lt;/b&gt;, bên thực hiện được Chiếu Hết sẽ giành chiến thắng.</t>
+          <t>Xe</t>
         </is>
       </c>
     </row>
     <row r="375" ht="17" customHeight="1">
       <c r="A375" s="2" t="inlineStr">
         <is>
-          <t>guide.result.paragraph2</t>
+          <t>guide.piece.horse</t>
         </is>
       </c>
       <c r="B375" s="2" t="inlineStr">
         <is>
-          <t>If a player runs out of time for a single move (for example: 90s) without moving, the other side is awarded a &lt;b&gt;win&lt;/b&gt;.</t>
+          <t>Horse</t>
         </is>
       </c>
       <c r="C375" s="2" t="inlineStr">
         <is>
-          <t>Khi hết thời gian một nước đi (ví dụ: 90s) mà vẫn chưa di chuyển quân thì bên còn lại sẽ được &lt;b&gt;xử Thắng&lt;/b&gt;.</t>
+          <t>Mã</t>
         </is>
       </c>
     </row>
     <row r="376" ht="17" customHeight="1">
       <c r="A376" s="2" t="inlineStr">
         <is>
-          <t>guide.result.paragraph3</t>
+          <t>guide.piece.cannon</t>
         </is>
       </c>
       <c r="B376" s="2" t="inlineStr">
         <is>
-          <t>If a player runs out of total game time (for example: 5 minutes or 10 minutes), the other side is awarded a &lt;b&gt;win&lt;/b&gt;.</t>
+          <t>Cannon</t>
         </is>
       </c>
       <c r="C376" s="2" t="inlineStr">
         <is>
-          <t>Khi một bên hết thời gian ván đấu (ví dụ: 5 phút, 10 phút) thì bên còn lại sẽ được &lt;b&gt;xử Thắng&lt;/b&gt;.</t>
+          <t>Pháo</t>
         </is>
       </c>
     </row>
     <row r="377" ht="17" customHeight="1">
       <c r="A377" s="2" t="inlineStr">
         <is>
-          <t>guide.result.paragraph4</t>
+          <t>guide.piece.soldier</t>
         </is>
       </c>
       <c r="B377" s="2" t="inlineStr">
         <is>
-          <t>If both sides have no pieces that have crossed the river, the game is declared a &lt;b&gt;draw&lt;/b&gt;. If one side still has pieces across the river but runs out of time, while the other side still has time but has no pieces across the river, the game is declared a &lt;b&gt;draw&lt;/b&gt;.</t>
+          <t>Soldier</t>
         </is>
       </c>
       <c r="C377" s="2" t="inlineStr">
         <is>
-          <t>Khi cả 2 bên đều không còn quân qua sông, ván đấu sẽ được &lt;b&gt;xử Hòa&lt;/b&gt;. Khi một bên còn quân qua sông nhưng cạn thời gian, một bên còn thời gian nhưng hết quân qua sông, ván đấu sẽ được &lt;b&gt;xử Hòa&lt;/b&gt;.</t>
+          <t>Tốt</t>
         </is>
       </c>
     </row>
     <row r="378" ht="17" customHeight="1">
       <c r="A378" s="2" t="inlineStr">
         <is>
-          <t>guide.result.paragraph5</t>
+          <t>guide.moving-pieces.paragraph1</t>
         </is>
       </c>
       <c r="B378" s="2" t="inlineStr">
         <is>
-          <t>Within 40 moves, if there is no capture and no Soldier advances by one square, the game is declared a &lt;b&gt;draw&lt;/b&gt;.</t>
+          <t>On each turn, each side may move only one of its own pieces according to the rules. The movement rules are as follows:</t>
         </is>
       </c>
       <c r="C378" s="2" t="inlineStr">
         <is>
-          <t>Trong vòng 40 nước nếu không phát sinh nước bắt quân, Tốt không tiến 1 ô thì ván đấu sẽ được &lt;b&gt;xử Hòa&lt;/b&gt;.</t>
+          <t>Mỗi nước đi, mỗi bên chỉ được di chuyển quân của mình theo đúng quy định. Quy định di chuyển của các quân như sau:</t>
         </is>
       </c>
     </row>
     <row r="379" ht="17" customHeight="1">
       <c r="A379" s="2" t="inlineStr">
         <is>
-          <t>extra-money.title</t>
+          <t>guide.general.paragraph1</t>
         </is>
       </c>
       <c r="B379" s="2" t="inlineStr">
         <is>
-          <t>Daily tasks</t>
+          <t>General</t>
         </is>
       </c>
       <c r="C379" s="2" t="inlineStr">
         <is>
-          <t>Kiếm tiền</t>
+          <t>Tướng</t>
         </is>
       </c>
     </row>
     <row r="380" ht="17" customHeight="1">
       <c r="A380" s="2" t="inlineStr">
         <is>
-          <t>extra-money.tab.lucky-wheel</t>
+          <t>guide.general.paragraph2</t>
         </is>
       </c>
       <c r="B380" s="2" t="inlineStr">
         <is>
-          <t>Lucky Wheel</t>
+          <t>Moves one step &lt;b&gt;horizontally or vertically&lt;/b&gt; within the palace. The two Generals may not face each other directly on the same file. If they are facing each other, there must be at least one piece of either side placed between them.</t>
         </is>
       </c>
       <c r="C380" s="2" t="inlineStr">
         <is>
-          <t>Vòng Quay May Mắn</t>
+          <t>Mỗi nước được đi một bước &lt;b&gt;ngang hoặc dọc&lt;/b&gt; tùy ý trong cung Tướng. Hai tướng của 2 bên không được đối mặt nhau trực tiếp trên cùng một đường thẳng. Nếu đối mặt, bắt buộc phải có quân của bất kỳ bên nào đứng che mặt.</t>
         </is>
       </c>
     </row>
     <row r="381" ht="17" customHeight="1">
       <c r="A381" s="2" t="inlineStr">
         <is>
-          <t>extra-money.tab.bonus-coin</t>
+          <t>guide.advisor.paragraph1</t>
         </is>
       </c>
       <c r="B381" s="2" t="inlineStr">
         <is>
-          <t>Bonus Coin</t>
+          <t>Advisor</t>
         </is>
       </c>
       <c r="C381" s="2" t="inlineStr">
         <is>
-          <t>Xu Thưởng</t>
+          <t>Sĩ</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>extra-money.tab.daily-bonus</t>
+          <t>guide.advisor.paragraph2</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Daily Bonus</t>
+          <t>Moves one step &lt;b&gt;diagonally&lt;/b&gt; within the palace.</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Thưởng hàng ngày</t>
+          <t>Mỗi nước &lt;b&gt;đi chéo một bước&lt;/b&gt; trong cung Tướng.</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>extra-money.bonus-coin.subtitle</t>
+          <t>guide.elephant.paragraph1</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Watch a short video to earn free coin</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Xem video ngắn để nhận xu miễn phí</t>
+          <t>Tượng</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>extra-money.bonus-coin.next-in</t>
+          <t>guide.elephant.paragraph2</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Next in:</t>
+          <t>Moves &lt;b&gt;two steps diagonally&lt;/b&gt; on its own side of the board and may not cross the river. If there is another piece on the midpoint of that diagonal path, the Elephant is blocked and cannot move.</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Lượt kế tiếp:</t>
+          <t>Mỗi nước &lt;b&gt;đi chéo hai bước&lt;/b&gt; tại trận địa bên mình, không được qua sông. Nếu ở giữa đường chéo đó có quân khác đứng thì quân Tượng bị cản, không đi được.</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>extra-money.bonus-coin.collect</t>
+          <t>guide.chariot.paragraph1</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Collect</t>
+          <t>Chariot</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Thu thập</t>
+          <t>Xe</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>extra-money.bonus-coin.watch-video</t>
+          <t>guide.chariot.paragraph2</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Watch video</t>
+          <t>Moves &lt;b&gt;horizontally or vertically&lt;/b&gt; with no limit on distance, as long as no piece blocks the path.</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Xem video</t>
+          <t>Mỗi nước được &lt;b&gt;đi dọc hoặc đi ngang&lt;/b&gt;, không hạn chế số bước đi nếu không có quân khác cản đường.</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>extra-money.daily-bonus.subtitle</t>
+          <t>guide.horse.paragraph1</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Login 7 days in a row to earn 4000 coin</t>
+          <t>Horse</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Đăng nhập 7 ngày liên tiếp để nhận 4000 xu</t>
+          <t>Mã</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>extra-money.daily-bonus.day</t>
+          <t>guide.horse.paragraph2</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Moves in an &lt;b&gt;L-shape&lt;/b&gt; (one step orthogonally then one step diagonally outward). If the adjacent orthogonal point is occupied by any piece, the Horse is blocked and cannot move.</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Ngày</t>
+          <t>Đi theo &lt;b&gt;đường chéo hình chữ nhật&lt;/b&gt; của hai ô vuông liền nhau. Nếu giao điểm liền kề bước thẳng dọc ngang có một quân khác đứng thì Mã bị cản, không đi được.</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>extra-money.reward-ad.loading</t>
+          <t>guide.cannon.paragraph1</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Loading ad...</t>
+          <t>Cannon</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Đang tải quảng cáo...</t>
+          <t>Pháo</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>extra-money.reward-ad.error</t>
+          <t>guide.cannon.paragraph2</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Could not load the ad. Please try again.</t>
+          <t>Moves &lt;b&gt;horizontally or vertically&lt;/b&gt; like a Chariot when not capturing. To capture, it must &lt;b&gt;jump over exactly one piece&lt;/b&gt; to reach its target. If there are zero or more than one pieces between the Cannon and the target, it cannot capture.</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Không tải được quảng cáo. Vui lòng thử lại.</t>
+          <t>Đi ngang hoặc dọc giống Xe khi không bắt quân. Để bắt quân, nó phải &lt;b&gt;nhảy qua đúng một quân khác&lt;/b&gt; để đến mục tiêu. Nếu không có hoặc có nhiều hơn một quân giữa Pháo và mục tiêu, nó không thể bắt quân.</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>extra-money.reward-ad.retry</t>
+          <t>guide.soldier.paragraph1</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Try again</t>
+          <t>Soldier</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Thử lại</t>
+          <t>Tốt</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>extra-money.reward-ad.close</t>
+          <t>guide.soldier.paragraph2</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Close</t>
+          <t>Moves &lt;b&gt;one step&lt;/b&gt; each turn. Before crossing the river, it can only move forward. After crossing the river, it may move &lt;b&gt;forward or sideways&lt;/b&gt;, but never backward.</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Đóng</t>
+          <t>Mỗi nước đi &lt;b&gt;một bước&lt;/b&gt;. Khi chưa qua sông, Tốt chỉ được tiến. Khi Tốt đã qua sông được quyền &lt;b&gt;đi tiến và đi ngang&lt;/b&gt;, không được phép lùi.</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>profile.button.save</t>
+          <t>guide.capturing.paragraph1</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Save</t>
+          <t>When a piece moves to an intersection occupied by an opponent's piece, it may &lt;b&gt;capture that piece&lt;/b&gt; and occupy its position.</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Lưu</t>
+          <t>Khi một quân đi tới một giao điểm khác đã có quân đối phương đứng thì được quyền &lt;b&gt;bắt quân đó&lt;/b&gt;, đồng thời chiếm giữ vị trí quân bị bắt.</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>profile.button.cancel</t>
+          <t>guide.capturing.paragraph2</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>You may not capture your own pieces. You may sacrifice your own pieces to be captured by the opponent, &lt;b&gt;except for the General&lt;/b&gt;.</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Huỷ</t>
+          <t>Không được bắt quân bên mình. Được phép cho đối phương bắt đầu quân mình chủ động hiến mình cho đối phương, &lt;b&gt;trừ Tướng&lt;/b&gt;.</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>change-password.title</t>
+          <t>guide.capturing.paragraph3</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Change password</t>
+          <t>A captured piece is removed from the board. &lt;b&gt;Chasing one piece for more than 6 consecutive moves is not allowed&lt;/b&gt;.</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Đổi mật khẩu</t>
+          <t>Quân bị bắt phải bị loại và bị nhấc ra khỏi bàn cờ. &lt;b&gt;Không được đuổi 1 quân quá 6 nước cờ liên tiếp&lt;/b&gt;.</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>change-password.current.label</t>
+          <t>guide.check.paragraph1</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Current password</t>
+          <t>If a player makes a move that threatens to capture the opponent's General on the next move (by the same piece or another piece), it is called a &lt;b&gt;Check&lt;/b&gt;. The checked side must respond to avoid check. Otherwise, that side loses</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Mật khẩu hiện tại</t>
+          <t>Nếu người chơi thực hiện một nước đi đe dọa bắt Tướng của đối phương ở nước đi tiếp theo (bằng chính quân cờ đó hoặc một quân cờ khác), thì đó được gọi là &lt;b&gt;Chiếu&lt;/b&gt;. Bên bị chiếu phải đáp trả để tránh bị chiếu. Nếu không sẽ bị xử thua</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>change-password.current.placeholder</t>
+          <t>guide.check.paragraph2</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Enter current password</t>
+          <t>When the General is checked from any direction (including from behind), the checked side may respond in one of the following ways:</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Nhập mật khẩu hiện tại</t>
+          <t>Tướng bị chiếu từ cả bốn hướng (bị chiếu cả từ phía sau) có thể ứng phó với nước chiếu tướng bằng một trong các cách sau:</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>change-password.new.label</t>
+          <t>guide.check.paragraph3</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>New password</t>
+          <t>Move the General to another position to escape check</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Mật khẩu mới</t>
+          <t>Di chuyển tướng sang vị trí khác để tránh nước chiếu</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>change-password.new.placeholder</t>
+          <t>guide.check.paragraph4</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Enter new password</t>
+          <t>Capture the checking piece</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Nhập mật khẩu mới</t>
+          <t>Bắt quân đang chiếu</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>change-password.confirm.label</t>
+          <t>guide.check.paragraph5</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Confirm new password</t>
+          <t>Block the checking line with another piece to protect the General</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Xác nhận mật khẩu mới</t>
+          <t>Dùng quân khác cản quân chiếu, đi quân che đỡ cho tướng</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>change-password.confirm.placeholder</t>
+          <t>guide.check.paragraph6</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Re-enter new password</t>
+          <t>Repeatedly checking for more than 6 consecutive moves is not allowed</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Nhập lại mật khẩu mới</t>
+          <t>Không được chiếu tướng quá 6 nước cờ liên tiếp</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>change-password.confirm.mismatch</t>
+          <t>guide.result.paragraph1</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Passwords do not match</t>
+          <t>When one side gives Check and the other side has no legal way to protect the General, it is called a &lt;b&gt;Checkmate&lt;/b&gt;. The side that delivers Checkmate wins.</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Mật khẩu xác nhận không khớp</t>
+          <t>Khi một bên chiếu Tướng mà bên còn lại không thể làm gì để bảo vệ Tướng thì được gọi là &lt;b&gt;Chiếu Hết&lt;/b&gt;, bên thực hiện được Chiếu Hết sẽ giành chiến thắng.</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>change-password.show</t>
+          <t>guide.result.paragraph2</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Show password</t>
+          <t>If a player runs out of time for a single move (for example: 90s) without moving, the other side is awarded a &lt;b&gt;win&lt;/b&gt;.</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Hiện mật khẩu</t>
+          <t>Khi hết thời gian một nước đi (ví dụ: 90s) mà vẫn chưa di chuyển quân thì bên còn lại sẽ được &lt;b&gt;xử Thắng&lt;/b&gt;.</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>change-password.hide</t>
+          <t>guide.result.paragraph3</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Hide password</t>
+          <t>If a player runs out of total game time (for example: 5 minutes or 10 minutes), the other side is awarded a &lt;b&gt;win&lt;/b&gt;.</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Ẩn mật khẩu</t>
+          <t>Khi một bên hết thời gian ván đấu (ví dụ: 5 phút, 10 phút) thì bên còn lại sẽ được &lt;b&gt;xử Thắng&lt;/b&gt;.</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>change-password.submit</t>
+          <t>guide.result.paragraph4</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Change password</t>
+          <t>If both sides have no pieces that have crossed the river, the game is declared a &lt;b&gt;draw&lt;/b&gt;. If one side still has pieces across the river but runs out of time, while the other side still has time but has no pieces across the river, the game is declared a &lt;b&gt;draw&lt;/b&gt;.</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Đổi mật khẩu</t>
+          <t>Khi cả 2 bên đều không còn quân qua sông, ván đấu sẽ được &lt;b&gt;xử Hòa&lt;/b&gt;. Khi một bên còn quân qua sông nhưng cạn thời gian, một bên còn thời gian nhưng hết quân qua sông, ván đấu sẽ được &lt;b&gt;xử Hòa&lt;/b&gt;.</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>change-password.submitting</t>
+          <t>guide.result.paragraph5</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Changing...</t>
+          <t>Within 40 moves, if there is no capture and no Soldier advances by one square, the game is declared a &lt;b&gt;draw&lt;/b&gt;.</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Đang đổi...</t>
+          <t>Trong vòng 40 nước nếu không phát sinh nước bắt quân, Tốt không tiến 1 ô thì ván đấu sẽ được &lt;b&gt;xử Hòa&lt;/b&gt;.</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>change-password.messages.success</t>
+          <t>extra-money.title</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Password changed successfully</t>
+          <t>Daily tasks</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Đổi mật khẩu thành công</t>
+          <t>Kiếm tiền</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>change-password.messages.missing-fields</t>
+          <t>extra-money.tab.lucky-wheel</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Please fill in all fields</t>
+          <t>Lucky Wheel</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Vui lòng nhập đầy đủ thông tin</t>
+          <t>Vòng Quay May Mắn</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>change-password.messages.weak-password</t>
+          <t>extra-money.tab.bonus-coin</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>New password does not meet the requirements</t>
+          <t>Bonus Coin</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Mật khẩu mới không đạt yêu cầu</t>
+          <t>Xu Thưởng</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>change-password.messages.same-as-current</t>
+          <t>extra-money.tab.daily-bonus</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>New password must be different from the current one</t>
+          <t>Daily Bonus</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Mật khẩu mới phải khác mật khẩu hiện tại</t>
+          <t>Thưởng hàng ngày</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>change-password.messages.incorrect-current-password</t>
+          <t>extra-money.bonus-coin.subtitle</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Current password is incorrect</t>
+          <t>Watch a short video to earn free coin</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Mật khẩu hiện tại không đúng</t>
+          <t>Xem video ngắn để nhận xu miễn phí</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>change-password.messages.user-not-found</t>
+          <t>extra-money.bonus-coin.next-in</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>User not found</t>
+          <t>Next in:</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Không tìm thấy người dùng</t>
+          <t>Lượt kế tiếp:</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>change-password.messages.unauthorized</t>
+          <t>extra-money.bonus-coin.collect</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Session expired. Please sign in again.</t>
+          <t>Collect</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Phiên đăng nhập đã hết hạn. Vui lòng đăng nhập lại.</t>
+          <t>Thu thập</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
+          <t>extra-money.bonus-coin.watch-video</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Watch video</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>Xem video</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>extra-money.daily-bonus.subtitle</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Login 7 days in a row to earn 4000 coin</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>Đăng nhập 7 ngày liên tiếp để nhận 4000 xu</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>extra-money.daily-bonus.day</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>Ngày</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>extra-money.reward-ad.loading</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Loading ad...</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>Đang tải quảng cáo...</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>extra-money.reward-ad.error</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Could not load the ad. Please try again.</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>Không tải được quảng cáo. Vui lòng thử lại.</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>extra-money.reward-ad.retry</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>Try again</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>Thử lại</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>extra-money.reward-ad.close</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>Đóng</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>profile.button.save</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>Save</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>Lưu</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>profile.button.cancel</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Cancel</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>Huỷ</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>change-password.title</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>Change password</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>Đổi mật khẩu</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>change-password.current.label</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Current password</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>Mật khẩu hiện tại</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>change-password.current.placeholder</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Enter current password</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>Nhập mật khẩu hiện tại</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>change-password.new.label</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>New password</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>Mật khẩu mới</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>change-password.new.placeholder</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>Enter new password</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>Nhập mật khẩu mới</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>change-password.confirm.label</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Confirm new password</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>Xác nhận mật khẩu mới</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>change-password.confirm.placeholder</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Re-enter new password</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>Nhập lại mật khẩu mới</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>change-password.confirm.mismatch</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>Passwords do not match</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>Mật khẩu xác nhận không khớp</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>change-password.show</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>Show password</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>Hiện mật khẩu</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>change-password.hide</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>Hide password</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>Ẩn mật khẩu</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>change-password.submit</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Change password</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>Đổi mật khẩu</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>change-password.submitting</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>Changing...</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>Đang đổi...</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>change-password.messages.success</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>Password changed successfully</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>Đổi mật khẩu thành công</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>change-password.messages.missing-fields</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>Please fill in all fields</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>Vui lòng nhập đầy đủ thông tin</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>change-password.messages.weak-password</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>New password does not meet the requirements</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>Mật khẩu mới không đạt yêu cầu</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>change-password.messages.same-as-current</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>New password must be different from the current one</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>Mật khẩu mới phải khác mật khẩu hiện tại</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>change-password.messages.incorrect-current-password</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>Current password is incorrect</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>Mật khẩu hiện tại không đúng</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>change-password.messages.user-not-found</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>User not found</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>Không tìm thấy người dùng</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>change-password.messages.unauthorized</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>Session expired. Please sign in again.</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>Phiên đăng nhập đã hết hạn. Vui lòng đăng nhập lại.</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
           <t>change-password.messages.internal-server-error</t>
         </is>
       </c>
-      <c r="B414" t="inlineStr">
+      <c r="B442" t="inlineStr">
         <is>
           <t>Something went wrong. Please try again.</t>
         </is>
       </c>
-      <c r="C414" t="inlineStr">
+      <c r="C442" t="inlineStr">
         <is>
           <t>Đã có lỗi xảy ra. Vui lòng thử lại.</t>
         </is>
       </c>
     </row>
-    <row r="415">
-      <c r="A415" t="inlineStr"/>
-      <c r="B415" t="inlineStr"/>
-      <c r="C415" t="inlineStr"/>
-    </row>
-    <row r="416">
-      <c r="A416" t="inlineStr"/>
-      <c r="B416" t="inlineStr"/>
-      <c r="C416" t="inlineStr"/>
-    </row>
-    <row r="417">
-      <c r="A417" t="inlineStr"/>
-      <c r="B417" t="inlineStr"/>
-      <c r="C417" t="inlineStr"/>
-    </row>
-    <row r="418">
-      <c r="A418" t="inlineStr"/>
-      <c r="B418" t="inlineStr"/>
-      <c r="C418" t="inlineStr"/>
-    </row>
-    <row r="419">
-      <c r="A419" t="inlineStr"/>
-      <c r="B419" t="inlineStr"/>
-      <c r="C419" t="inlineStr"/>
-    </row>
-    <row r="420">
-      <c r="A420" t="inlineStr"/>
-      <c r="B420" t="inlineStr"/>
-      <c r="C420" t="inlineStr"/>
-    </row>
-    <row r="421">
-      <c r="A421" t="inlineStr"/>
-      <c r="B421" t="inlineStr"/>
-      <c r="C421" t="inlineStr"/>
-    </row>
-    <row r="422">
-      <c r="A422" t="inlineStr"/>
-      <c r="B422" t="inlineStr"/>
-      <c r="C422" t="inlineStr"/>
-    </row>
-    <row r="423">
-      <c r="A423" t="inlineStr"/>
-      <c r="B423" t="inlineStr"/>
-      <c r="C423" t="inlineStr"/>
-    </row>
-    <row r="424">
-      <c r="A424" t="inlineStr"/>
-      <c r="B424" t="inlineStr"/>
-      <c r="C424" t="inlineStr"/>
-    </row>
-    <row r="425">
-      <c r="A425" t="inlineStr"/>
-      <c r="B425" t="inlineStr"/>
-      <c r="C425" t="inlineStr"/>
-    </row>
-    <row r="426">
-      <c r="A426" t="inlineStr"/>
-      <c r="B426" t="inlineStr"/>
-      <c r="C426" t="inlineStr"/>
-    </row>
-    <row r="427">
-      <c r="A427" t="inlineStr"/>
-      <c r="B427" t="inlineStr"/>
-      <c r="C427" t="inlineStr"/>
-    </row>
-    <row r="428">
-      <c r="A428" t="inlineStr"/>
-      <c r="B428" t="inlineStr"/>
-      <c r="C428" t="inlineStr"/>
-    </row>
-    <row r="429">
-      <c r="A429" t="inlineStr"/>
-      <c r="B429" t="inlineStr"/>
-      <c r="C429" t="inlineStr"/>
-    </row>
-    <row r="430">
-      <c r="A430" t="inlineStr"/>
-      <c r="B430" t="inlineStr"/>
-      <c r="C430" t="inlineStr"/>
-    </row>
-    <row r="431">
-      <c r="A431" t="inlineStr"/>
-      <c r="B431" t="inlineStr"/>
-      <c r="C431" t="inlineStr"/>
-    </row>
-    <row r="432">
-      <c r="A432" t="inlineStr"/>
-      <c r="B432" t="inlineStr"/>
-      <c r="C432" t="inlineStr"/>
-    </row>
-    <row r="433">
-      <c r="A433" t="inlineStr"/>
-      <c r="B433" t="inlineStr"/>
-      <c r="C433" t="inlineStr"/>
-    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr"/>
+      <c r="B443" t="inlineStr"/>
+      <c r="C443" t="inlineStr"/>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr"/>
+      <c r="B444" t="inlineStr"/>
+      <c r="C444" t="inlineStr"/>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr"/>
+      <c r="B445" t="inlineStr"/>
+      <c r="C445" t="inlineStr"/>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr"/>
+      <c r="B446" t="inlineStr"/>
+      <c r="C446" t="inlineStr"/>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr"/>
+      <c r="B447" t="inlineStr"/>
+      <c r="C447" t="inlineStr"/>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr"/>
+      <c r="B448" t="inlineStr"/>
+      <c r="C448" t="inlineStr"/>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr"/>
+      <c r="B449" t="inlineStr"/>
+      <c r="C449" t="inlineStr"/>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr"/>
+      <c r="B450" t="inlineStr"/>
+      <c r="C450" t="inlineStr"/>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr"/>
+      <c r="B451" t="inlineStr"/>
+      <c r="C451" t="inlineStr"/>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr"/>
+      <c r="B452" t="inlineStr"/>
+      <c r="C452" t="inlineStr"/>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr"/>
+      <c r="B453" t="inlineStr"/>
+      <c r="C453" t="inlineStr"/>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr"/>
+      <c r="B454" t="inlineStr"/>
+      <c r="C454" t="inlineStr"/>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr"/>
+      <c r="B455" t="inlineStr"/>
+      <c r="C455" t="inlineStr"/>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr"/>
+      <c r="B456" t="inlineStr"/>
+      <c r="C456" t="inlineStr"/>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr"/>
+      <c r="B457" t="inlineStr"/>
+      <c r="C457" t="inlineStr"/>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr"/>
+      <c r="B458" t="inlineStr"/>
+      <c r="C458" t="inlineStr"/>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr"/>
+      <c r="B459" t="inlineStr"/>
+      <c r="C459" t="inlineStr"/>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr"/>
+      <c r="B460" t="inlineStr"/>
+      <c r="C460" t="inlineStr"/>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr"/>
+      <c r="B461" t="inlineStr"/>
+      <c r="C461" t="inlineStr"/>
+    </row>
+    <row r="462"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/tools/languages.xlsx
+++ b/tools/languages.xlsx
@@ -325,7 +325,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C462"/>
+  <dimension ref="A1:C471"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -851,3504 +851,3504 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>{{name}} ran out of time</t>
+          <t>{{name}} ran out of total game time</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>{{name}} đã hết giờ</t>
+          <t>{{name}} đã hết giờ cả ván</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>page.replay.reason-ended</t>
+          <t>page.replay.reason-per-move-timeout</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>The game has ended</t>
+          <t>{{name}} ran out of time for a move</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Ván đấu đã kết thúc</t>
+          <t>{{name}} đã hết giờ cho một nước đi</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>menu.app-name</t>
+          <t>page.replay.reason-ended</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Xiangqi</t>
+          <t>The game has ended</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Cờ tướng</t>
+          <t>Ván đấu đã kết thúc</t>
         </is>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>menu.profile</t>
+          <t>menu.app-name</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>Xiangqi</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Trang cá nhân</t>
+          <t>Cờ tướng</t>
         </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>menu.messages</t>
+          <t>menu.profile</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Message</t>
+          <t>Profile</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Tin nhắn</t>
+          <t>Trang cá nhân</t>
         </is>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>menu.change-password</t>
+          <t>menu.messages</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Change password</t>
+          <t>Message</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Đổi mật khẩu</t>
+          <t>Tin nhắn</t>
         </is>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>menu.guide</t>
+          <t>menu.change-password</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Guide</t>
+          <t>Change password</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Luật chơi</t>
+          <t>Đổi mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="38" ht="36" customHeight="1">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>menu.announce</t>
+          <t>menu.guide</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Announcement</t>
+          <t>Guide</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Thông báo</t>
+          <t>Luật chơi</t>
         </is>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>menu.extra</t>
+          <t>menu.announce</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Daily tasks</t>
+          <t>Announcement</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Kiếm tiền</t>
+          <t>Thông báo</t>
         </is>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>menu.setting.button</t>
+          <t>menu.extra</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Daily tasks</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Cài đặt</t>
+          <t>Kiếm tiền</t>
         </is>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>menu.app-name</t>
+          <t>menu.leaderboard</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Xiangqi</t>
+          <t>Leaderboard</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Cờ tướng</t>
+          <t>Bảng xếp hạng</t>
         </is>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>menu.home</t>
+          <t>menu.setting.button</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Trang chủ</t>
+          <t>Cài đặt</t>
         </is>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>menu.expired</t>
+          <t>menu.app-name</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Set expired</t>
+          <t>Xiangqi</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Hết hạn token</t>
+          <t>Cờ tướng</t>
         </is>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>menu.logout</t>
+          <t>menu.home</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Logout</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Đăng xuất</t>
+          <t>Trang chủ</t>
         </is>
       </c>
     </row>
     <row r="45" ht="36" customHeight="1">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>announce.title</t>
+          <t>menu.expired</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Announcement</t>
+          <t>Set expired</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Thông báo</t>
+          <t>Hết hạn token</t>
         </is>
       </c>
     </row>
     <row r="46" ht="36" customHeight="1">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>announce.placeholder</t>
+          <t>menu.logout</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Type an announcement...</t>
+          <t>Logout</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Nhập thông báo...</t>
+          <t>Đăng xuất</t>
         </is>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>announce.empty</t>
+          <t>announce.title</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>No announcements yet</t>
+          <t>Announcement</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Chưa có thông báo nào</t>
+          <t>Thông báo</t>
         </is>
       </c>
     </row>
     <row r="48" ht="36" customHeight="1">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>announce.loading-older</t>
+          <t>announce.placeholder</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Loading older announcements...</t>
+          <t>Type an announcement...</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Đang tải thông báo cũ hơn...</t>
+          <t>Nhập thông báo...</t>
         </is>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>achievement.title-01</t>
+          <t>announce.empty</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Checkmate an opponent who still has 13 or more pieces</t>
+          <t>No announcements yet</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Chiếu bí khi đối thủ vẫn còn &gt;= 13 quân</t>
+          <t>Chưa có thông báo nào</t>
         </is>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>achievement.title-02</t>
+          <t>announce.loading-older</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Win your first game</t>
+          <t>Loading older announcements...</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Thắng trận đầu khi chơi game</t>
+          <t>Đang tải thông báo cũ hơn...</t>
         </is>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>achievement.title-03</t>
+          <t>achievement.title-01</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Leave your opponent with no legal moves</t>
+          <t>Checkmate an opponent who still has 13 or more pieces</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Đánh cho đối thủ không còn nước đi</t>
+          <t>Chiếu bí khi đối thủ vẫn còn &gt;= 13 quân</t>
         </is>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>achievement.title-04</t>
+          <t>achievement.title-02</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Defeat opponents of equal or higher rank in 10 games</t>
+          <t>Win your first game</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Thắng đối thủ cùng hoặc hơn đẳng cấp 10 ván</t>
+          <t>Thắng trận đầu khi chơi game</t>
         </is>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>achievement.title-05</t>
+          <t>achievement.title-03</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Hold a draw with only your king remaining</t>
+          <t>Leave your opponent with no legal moves</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Cầm hoà đối thủ khi chỉ còn tướng</t>
+          <t>Đánh cho đối thủ không còn nước đi</t>
         </is>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>achievement.title-06</t>
+          <t>achievement.title-04</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Win 100 games</t>
+          <t>Defeat opponents of equal or higher rank in 10 games</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Thắng 100 trận</t>
+          <t>Thắng đối thủ cùng hoặc hơn đẳng cấp 10 ván</t>
         </is>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>achievement.title-07</t>
+          <t>achievement.title-05</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Draw 50 games</t>
+          <t>Hold a draw with only your king remaining</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Hoà 50 trận</t>
+          <t>Cầm hoà đối thủ khi chỉ còn tướng</t>
         </is>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>achievement.title-08</t>
+          <t>achievement.title-06</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Checkmate an opponent with only 1 attacking piece remaining</t>
+          <t>Win 100 games</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Chiếu bí khi đối thủ khi chỉ còn 1 quân tấn công</t>
+          <t>Thắng 100 trận</t>
         </is>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>achievement.title-09</t>
+          <t>achievement.title-07</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Checkmate an opponent with only a knight remaining</t>
+          <t>Draw 50 games</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Chiếu bí khi đối thủ khi chỉ còn mã</t>
+          <t>Hoà 50 trận</t>
         </is>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>achievement.title-10</t>
+          <t>achievement.title-08</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Checkmate an opponent with only a pawn remaining</t>
+          <t>Checkmate an opponent with only 1 attacking piece remaining</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Chiếu bí khi đối thủ khi chỉ còn tốt</t>
+          <t>Chiếu bí khi đối thủ khi chỉ còn 1 quân tấn công</t>
         </is>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>achievement.title-11</t>
+          <t>achievement.title-09</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Checkmate an opponent with only a cannon remaining</t>
+          <t>Checkmate an opponent with only a knight remaining</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Chiếu bí khi đối thủ khi chỉ còn pháo</t>
+          <t>Chiếu bí khi đối thủ khi chỉ còn mã</t>
         </is>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>achievement.title-12</t>
+          <t>achievement.title-10</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Defeat opponents with master rank in 50 games</t>
+          <t>Checkmate an opponent with only a pawn remaining</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Thắng đối thủ có đẳng cấp kỳ thủ 50 ván</t>
+          <t>Chiếu bí khi đối thủ khi chỉ còn tốt</t>
         </is>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>achievement.tab-title</t>
+          <t>achievement.title-11</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Achievements</t>
+          <t>Checkmate an opponent with only a cannon remaining</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Thành tựu</t>
+          <t>Chiếu bí khi đối thủ khi chỉ còn pháo</t>
         </is>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>achievement.messages.success</t>
+          <t>achievement.title-12</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Success</t>
+          <t>Defeat opponents with master rank in 50 games</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Thành công</t>
+          <t>Thắng đối thủ có đẳng cấp kỳ thủ 50 ván</t>
         </is>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>achievement.messages.invalid-user-id</t>
+          <t>achievement.tab-title</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Invalid user ID</t>
+          <t>Achievements</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>ID người dùng không hợp lệ</t>
+          <t>Thành tựu</t>
         </is>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>achievement.messages.internal-server-error</t>
+          <t>achievement.messages.success</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Success</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ</t>
+          <t>Thành công</t>
         </is>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>chat.conversation.you</t>
+          <t>achievement.messages.invalid-user-id</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>You</t>
+          <t>Invalid user ID</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Bạn</t>
+          <t>ID người dùng không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>chat.messages.unread</t>
+          <t>achievement.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Unread messages</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Tin nhắn chưa đọc</t>
+          <t>Lỗi máy chủ</t>
         </is>
       </c>
     </row>
     <row r="67" ht="18" customHeight="1">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>search.user.title</t>
+          <t>chat.conversation.you</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Search user</t>
+          <t>You</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Tìm kiếm</t>
+          <t>Bạn</t>
         </is>
       </c>
     </row>
     <row r="68" ht="18" customHeight="1">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>search.user.placeholder</t>
+          <t>chat.messages.unread</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Search user...</t>
+          <t>Unread messages</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Tìm kiếm người dùng...</t>
+          <t>Tin nhắn chưa đọc</t>
         </is>
       </c>
     </row>
     <row r="69" ht="18" customHeight="1">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>search.user.no-results</t>
+          <t>search.user.title</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>No users found</t>
+          <t>Search user</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy người dùng</t>
+          <t>Tìm kiếm</t>
         </is>
       </c>
     </row>
     <row r="70" ht="18" customHeight="1">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>search.button.search</t>
+          <t>search.user.placeholder</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>Search user...</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Tìm kiếm</t>
+          <t>Tìm kiếm người dùng...</t>
         </is>
       </c>
     </row>
     <row r="71" ht="18" customHeight="1">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>dashboard.page.title</t>
+          <t>search.user.no-results</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Room list</t>
+          <t>No users found</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Danh sách phòng</t>
+          <t>Không tìm thấy người dùng</t>
         </is>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>dashboard.filters.all</t>
+          <t>search.button.search</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Search</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Tất cả</t>
+          <t>Tìm kiếm</t>
         </is>
       </c>
     </row>
     <row r="73" ht="18" customHeight="1">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>dashboard.filters.available</t>
+          <t>leaderboard.title</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Available</t>
+          <t>Leaderboard</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>Chờ</t>
+          <t>Bảng xếp hạng</t>
         </is>
       </c>
     </row>
     <row r="74" ht="18" customHeight="1">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>dashboard.filters.playing</t>
+          <t>leaderboard.search-placeholder</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Playing</t>
+          <t>Search user...</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>Đang chơi</t>
+          <t>Tìm kiếm người dùng...</t>
         </is>
       </c>
     </row>
     <row r="75" ht="18" customHeight="1">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>dashboard.feedback.empty</t>
+          <t>leaderboard.no-results</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>No room tables match the selected filter.</t>
+          <t>No users found</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>Không có bàn chơi phù hợp với bộ lọc đã chọn.</t>
+          <t>Không tìm thấy người dùng</t>
         </is>
       </c>
     </row>
     <row r="76" ht="18" customHeight="1">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>dashboard.feedback.error</t>
+          <t>leaderboard.empty</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Unable to load room tables.</t>
+          <t>No players yet</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>Không tải được danh sách phòng chơi.</t>
+          <t>Chưa có người chơi nào</t>
         </is>
       </c>
     </row>
     <row r="77" ht="18" customHeight="1">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>dashboard.status.unknown</t>
+          <t>dashboard.page.title</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Room list</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Không xác định</t>
+          <t>Danh sách phòng</t>
         </is>
       </c>
     </row>
     <row r="78" ht="18" customHeight="1">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>dashboard.room.create</t>
+          <t>dashboard.filters.all</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Create room</t>
+          <t>All</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Tạo phòng chơi</t>
+          <t>Tất cả</t>
         </is>
       </c>
     </row>
     <row r="79" ht="18" customHeight="1">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>dashboard.popup.piece-selection</t>
+          <t>dashboard.filters.available</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Select team</t>
+          <t>Available</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Chọn quân</t>
+          <t>Chờ</t>
         </is>
       </c>
     </row>
     <row r="80" ht="18" customHeight="1">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>dashboard.popup.red-first</t>
+          <t>dashboard.filters.playing</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Red first</t>
+          <t>Playing</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Đỏ tiên</t>
+          <t>Đang chơi</t>
         </is>
       </c>
     </row>
     <row r="81" ht="18" customHeight="1">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>dashboard.popup.pve-mode</t>
+          <t>dashboard.feedback.empty</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>PVE mode</t>
+          <t>No room tables match the selected filter.</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Chơi với máy</t>
+          <t>Không có bàn chơi phù hợp với bộ lọc đã chọn.</t>
         </is>
       </c>
     </row>
     <row r="82" ht="18" customHeight="1">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>dashboard.popup.bet-amount</t>
+          <t>dashboard.feedback.error</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Bet amount</t>
+          <t>Unable to load room tables.</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Giá trị cược</t>
+          <t>Không tải được danh sách phòng chơi.</t>
         </is>
       </c>
     </row>
     <row r="83" ht="18" customHeight="1">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>dashboard.popup.time-limit</t>
+          <t>dashboard.status.unknown</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Time limit</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Giới hạn thời gian</t>
+          <t>Không xác định</t>
         </is>
       </c>
     </row>
     <row r="84" ht="18" customHeight="1">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>dashboard.popup.time-limit-per-player</t>
+          <t>dashboard.room.create</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Time per player</t>
+          <t>Create room</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Thời gian mỗi người</t>
+          <t>Tạo phòng chơi</t>
         </is>
       </c>
     </row>
     <row r="85" ht="18" customHeight="1">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>dashboard.popup.time-unlimited</t>
+          <t>dashboard.popup.piece-selection</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Unlimited</t>
+          <t>Select team</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Không giới hạn</t>
+          <t>Chọn quân</t>
         </is>
       </c>
     </row>
     <row r="86" ht="18" customHeight="1">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>dashboard.popup.time-minutes</t>
+          <t>dashboard.popup.red-first</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>{0} min</t>
+          <t>Red first</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>{0} phút</t>
+          <t>Đỏ tiên</t>
         </is>
       </c>
     </row>
     <row r="87" ht="18" customHeight="1">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>dashboard.popup.time-seconds</t>
+          <t>dashboard.popup.pve-mode</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>{0}s</t>
+          <t>PVE mode</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>{0}s</t>
+          <t>Chơi với máy</t>
         </is>
       </c>
     </row>
     <row r="88" ht="18" customHeight="1">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>dashboard.popup.time-off</t>
+          <t>dashboard.popup.bet-amount</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Off</t>
+          <t>Bet amount</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Tắt</t>
+          <t>Giá trị cược</t>
         </is>
       </c>
     </row>
     <row r="89" ht="18" customHeight="1">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>dashboard.popup.time-increment</t>
+          <t>dashboard.popup.time-limit</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Bonus per move</t>
+          <t>Time limit</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Cộng giờ mỗi nước</t>
+          <t>Giới hạn thời gian</t>
         </is>
       </c>
     </row>
     <row r="90" ht="18" customHeight="1">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>dashboard.popup.time-per-move</t>
+          <t>dashboard.popup.time-limit-per-player</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Time per move</t>
+          <t>Time per player</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Thời gian mỗi nước</t>
+          <t>Thời gian mỗi người</t>
         </is>
       </c>
     </row>
     <row r="91" ht="18" customHeight="1">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>dashboard.popup.room-name-label</t>
+          <t>dashboard.popup.time-unlimited</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Room table name</t>
+          <t>Unlimited</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Tên phòng chơi</t>
+          <t>Không giới hạn</t>
         </is>
       </c>
     </row>
     <row r="92" ht="18" customHeight="1">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>dashboard.popup.room-name-helptext</t>
+          <t>dashboard.popup.time-minutes</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>is required</t>
+          <t>{0} min</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>không được để trống</t>
+          <t>{0} phút</t>
         </is>
       </c>
     </row>
     <row r="93" ht="18" customHeight="1">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>dashboard.popup.play</t>
+          <t>dashboard.popup.time-seconds</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Play</t>
+          <t>{0}s</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Chơi</t>
+          <t>{0}s</t>
         </is>
       </c>
     </row>
     <row r="94" ht="18" customHeight="1">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>dashboard.popup.view</t>
+          <t>dashboard.popup.time-off</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>View</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Xem</t>
+          <t>Tắt</t>
         </is>
       </c>
     </row>
     <row r="95" ht="18" customHeight="1">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>settings.header</t>
+          <t>dashboard.popup.time-increment</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Bonus per move</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Cài đặt</t>
+          <t>Cộng giờ mỗi nước</t>
         </is>
       </c>
     </row>
     <row r="96" ht="18" customHeight="1">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>settings.language</t>
+          <t>dashboard.popup.time-per-move</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>Time per move</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Ngôn ngữ</t>
+          <t>Thời gian mỗi nước</t>
         </is>
       </c>
     </row>
     <row r="97" ht="18" customHeight="1">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>settings.dark-mode</t>
+          <t>dashboard.popup.room-name-label</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Dark mode</t>
+          <t>Room table name</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Chế độ tối</t>
+          <t>Tên phòng chơi</t>
         </is>
       </c>
     </row>
     <row r="98" ht="18" customHeight="1">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>settings.sound</t>
+          <t>dashboard.popup.room-name-helptext</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Sound</t>
+          <t>is required</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Âm thanh</t>
+          <t>không được để trống</t>
         </is>
       </c>
     </row>
     <row r="99" ht="18" customHeight="1">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>settings.debug-mode</t>
+          <t>dashboard.popup.play</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Debug mode</t>
+          <t>Play</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Chế độ test</t>
+          <t>Chơi</t>
         </is>
       </c>
     </row>
     <row r="100" ht="18" customHeight="1">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>settings.connected-accounts.label</t>
+          <t>dashboard.popup.view</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Connected accounts</t>
+          <t>View</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản liên kết</t>
+          <t>Xem</t>
         </is>
       </c>
     </row>
     <row r="101" ht="18" customHeight="1">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>settings.connected-accounts.link-facebook</t>
+          <t>settings.header</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Link Facebook</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Liên kết Facebook</t>
+          <t>Cài đặt</t>
         </is>
       </c>
     </row>
     <row r="102" ht="18" customHeight="1">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>settings.connected-accounts.unlink-facebook</t>
+          <t>settings.language</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Unlink Facebook</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Huỷ liên kết Facebook</t>
+          <t>Ngôn ngữ</t>
         </is>
       </c>
     </row>
     <row r="103" ht="18" customHeight="1">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>settings.connected-accounts.link-success</t>
+          <t>settings.dark-mode</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Facebook linked successfully</t>
+          <t>Dark mode</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Đã liên kết Facebook</t>
+          <t>Chế độ tối</t>
         </is>
       </c>
     </row>
     <row r="104" ht="18" customHeight="1">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>settings.connected-accounts.unlink-success</t>
+          <t>settings.sound</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Facebook unlinked</t>
+          <t>Sound</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Đã huỷ liên kết Facebook</t>
+          <t>Âm thanh</t>
         </is>
       </c>
     </row>
     <row r="105" ht="18" customHeight="1">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>settings.connected-accounts.link-error</t>
+          <t>settings.debug-mode</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Could not update Facebook link</t>
+          <t>Debug mode</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Không cập nhật được liên kết Facebook</t>
+          <t>Chế độ test</t>
         </is>
       </c>
     </row>
     <row r="106" ht="18" customHeight="1">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>settings.close</t>
+          <t>settings.connected-accounts.label</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Close</t>
+          <t>Connected accounts</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Đóng</t>
+          <t>Tài khoản liên kết</t>
         </is>
       </c>
     </row>
     <row r="107" ht="18" customHeight="1">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>popup.alert.title</t>
+          <t>settings.connected-accounts.link-facebook</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Link Facebook</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Cảnh báo</t>
+          <t>Liên kết Facebook</t>
         </is>
       </c>
     </row>
     <row r="108" ht="18" customHeight="1">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>popup.confirm.title</t>
+          <t>settings.connected-accounts.unlink-facebook</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Confirm</t>
+          <t>Unlink Facebook</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Xác nhận</t>
+          <t>Huỷ liên kết Facebook</t>
         </is>
       </c>
     </row>
     <row r="109" ht="18" customHeight="1">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>popup.confirm.ok</t>
+          <t>settings.connected-accounts.link-success</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Ok</t>
+          <t>Facebook linked successfully</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Ok</t>
+          <t>Đã liên kết Facebook</t>
         </is>
       </c>
     </row>
     <row r="110" ht="36" customHeight="1">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>popup.confirm.cancel</t>
+          <t>settings.connected-accounts.unlink-success</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Facebook unlinked</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Huỷ</t>
+          <t>Đã huỷ liên kết Facebook</t>
         </is>
       </c>
     </row>
     <row r="111" ht="18" customHeight="1">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>game.general.captured</t>
+          <t>settings.connected-accounts.link-error</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>General has been captured. Room over</t>
+          <t>Could not update Facebook link</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Tướng đã bị bắt. Game kết thúc</t>
+          <t>Không cập nhật được liên kết Facebook</t>
         </is>
       </c>
     </row>
     <row r="112" ht="18" customHeight="1">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>game.general.in-check</t>
+          <t>settings.close</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Your general is under attack</t>
+          <t>Close</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Tướng của bạn đang bị chiếu</t>
+          <t>Đóng</t>
         </is>
       </c>
     </row>
     <row r="113" ht="18" customHeight="1">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>game.perpetual-check.warning-self</t>
+          <t>popup.alert.title</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>You are perpetual checking. If you make one more repeated check, you will lose</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Bạn đang chiếu quẩn, nếu thực hiện 1 nước nữa, bạn sẽ bị xử thua</t>
+          <t>Cảnh báo</t>
         </is>
       </c>
     </row>
     <row r="114" ht="18" customHeight="1">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>game.perpetual-check.warning-sent</t>
+          <t>popup.confirm.title</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>A perpetual-check warning has been sent to your opponent</t>
+          <t>Confirm</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Đã gửi cảnh báo chiếu quẩn cho đối thủ</t>
+          <t>Xác nhận</t>
         </is>
       </c>
     </row>
     <row r="115" ht="18" customHeight="1">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>game.label.win</t>
+          <t>popup.confirm.ok</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Win</t>
+          <t>Ok</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Thắng</t>
+          <t>Ok</t>
         </is>
       </c>
     </row>
     <row r="116" ht="18" customHeight="1">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>game.label.draw</t>
+          <t>popup.confirm.cancel</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Draw</t>
+          <t>Cancel</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Hoà</t>
+          <t>Huỷ</t>
         </is>
       </c>
     </row>
     <row r="117" ht="18" customHeight="1">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>game.label.lose</t>
+          <t>game.general.captured</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Lose</t>
+          <t>General has been captured. Room over</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Thua</t>
+          <t>Tướng đã bị bắt. Game kết thúc</t>
         </is>
       </c>
     </row>
     <row r="118" ht="18" customHeight="1">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>room.bot-difficulty.title</t>
+          <t>game.general.in-check</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Select Bot Difficulty</t>
+          <t>Your general is under attack</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Chọn độ khó của Bot</t>
+          <t>Tướng của bạn đang bị chiếu</t>
         </is>
       </c>
     </row>
     <row r="119" ht="18" customHeight="1">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>room.bot-difficulty.beginner</t>
+          <t>game.perpetual-check.warning-self</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Beginner</t>
+          <t>You are perpetual checking. If you make one more repeated check, you will lose</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Mới bắt đầu</t>
+          <t>Bạn đang chiếu quẩn, nếu thực hiện 1 nước nữa, bạn sẽ bị xử thua</t>
         </is>
       </c>
     </row>
     <row r="120" ht="18" customHeight="1">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>room.bot-difficulty.amateur</t>
+          <t>game.perpetual-check.warning-sent</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Amateur</t>
+          <t>A perpetual-check warning has been sent to your opponent</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Nghiệp dư</t>
+          <t>Đã gửi cảnh báo chiếu quẩn cho đối thủ</t>
         </is>
       </c>
     </row>
     <row r="121" ht="18" customHeight="1">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>room.bot-difficulty.intermediate</t>
+          <t>game.label.win</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Intermediate</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Trung bình</t>
+          <t>Thắng</t>
         </is>
       </c>
     </row>
     <row r="122" ht="18" customHeight="1">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>room.bot-difficulty.advanced</t>
+          <t>game.label.draw</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Advanced</t>
+          <t>Draw</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Nâng cao</t>
+          <t>Hoà</t>
         </is>
       </c>
     </row>
     <row r="123" ht="18" customHeight="1">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>room.bot-difficulty.master</t>
+          <t>game.label.lose</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>Master</t>
+          <t>Lose</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>Lão luyện</t>
+          <t>Thua</t>
         </is>
       </c>
     </row>
     <row r="124" ht="18" customHeight="1">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>login.page.title</t>
+          <t>room.bot-difficulty.title</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Login</t>
+          <t>Select Bot Difficulty</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập</t>
+          <t>Chọn độ khó của Bot</t>
         </is>
       </c>
     </row>
     <row r="125" ht="18" customHeight="1">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>login.form.title</t>
+          <t>room.bot-difficulty.beginner</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>Login</t>
+          <t>Beginner</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập</t>
+          <t>Mới bắt đầu</t>
         </is>
       </c>
     </row>
     <row r="126" ht="18" customHeight="1">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>login.username.label</t>
+          <t>room.bot-difficulty.amateur</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>User name</t>
+          <t>Amateur</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Tên người dùng</t>
+          <t>Nghiệp dư</t>
         </is>
       </c>
     </row>
     <row r="127" ht="18" customHeight="1">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>login.username.placeholder</t>
+          <t>room.bot-difficulty.intermediate</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>User name</t>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Tên người dùng</t>
+          <t>Trung bình</t>
         </is>
       </c>
     </row>
     <row r="128" ht="18" customHeight="1">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>login.password.label</t>
+          <t>room.bot-difficulty.advanced</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Password</t>
+          <t>Advanced</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Mật khẩu</t>
+          <t>Nâng cao</t>
         </is>
       </c>
     </row>
     <row r="129" ht="18" customHeight="1">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>login.password.placeholder</t>
+          <t>room.bot-difficulty.master</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>Password</t>
+          <t>Master</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Mật khẩu</t>
+          <t>Lão luyện</t>
         </is>
       </c>
     </row>
     <row r="130" ht="36" customHeight="1">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>login.password.show</t>
+          <t>login.page.title</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Show password</t>
+          <t>Login</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Hiện mật khẩu</t>
+          <t>Đăng nhập</t>
         </is>
       </c>
     </row>
     <row r="131" ht="18" customHeight="1">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>login.password.hide</t>
+          <t>login.form.title</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>Hide password</t>
+          <t>Login</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>Ẩn mật khẩu</t>
+          <t>Đăng nhập</t>
         </is>
       </c>
     </row>
     <row r="132" ht="18" customHeight="1">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>login.form.error1</t>
+          <t>login.username.label</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Login failed. Please check your credentials </t>
+          <t>User name</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập không thành công. Hãy kiểm tra lại</t>
+          <t>Tên người dùng</t>
         </is>
       </c>
     </row>
     <row r="133" ht="18" customHeight="1">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>login.form.forgot-password</t>
+          <t>login.username.placeholder</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>Forgot password</t>
+          <t>User name</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>Quên mật khẩu</t>
+          <t>Tên người dùng</t>
         </is>
       </c>
     </row>
     <row r="134" ht="18" customHeight="1">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>login.form.register</t>
+          <t>login.password.label</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Register</t>
+          <t>Password</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Đăng ký</t>
+          <t>Mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="135" ht="36" customHeight="1">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>login.form.submit</t>
+          <t>login.password.placeholder</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>Login</t>
+          <t>Password</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập</t>
+          <t>Mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="136" ht="18" customHeight="1">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>login.form.or</t>
+          <t>login.password.show</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>or</t>
+          <t>Show password</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>hoặc</t>
+          <t>Hiện mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="137" ht="18" customHeight="1">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>login.google.load-error</t>
+          <t>login.password.hide</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>Could not load Google Sign-In</t>
+          <t>Hide password</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>Không tải được đăng nhập Google</t>
+          <t>Ẩn mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="138" ht="18" customHeight="1">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>login.facebook.button</t>
+          <t>login.form.error1</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Sign-in with Facebook</t>
+          <t xml:space="preserve">Login failed. Please check your credentials </t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập với Facebook</t>
+          <t>Đăng nhập không thành công. Hãy kiểm tra lại</t>
         </is>
       </c>
     </row>
     <row r="139" ht="18" customHeight="1">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>login.messages.incorrect-login</t>
+          <t>login.form.forgot-password</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>Invalid username or password</t>
+          <t>Forgot password</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>Tên người dùng hoặc mật khẩu không hợp lệ</t>
+          <t>Quên mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="140" ht="18" customHeight="1">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>login.messages.internal-server-error</t>
+          <t>login.form.register</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Register</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Đăng ký</t>
         </is>
       </c>
     </row>
     <row r="141" ht="18" customHeight="1">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>login.messages.missing-credentials</t>
+          <t>login.form.submit</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>Username and password are required</t>
+          <t>Login</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>Tên người dùng và mật khẩu là bắt buộc</t>
+          <t>Đăng nhập</t>
         </is>
       </c>
     </row>
     <row r="142" ht="36" customHeight="1">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>login.messages.success</t>
+          <t>login.form.or</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Login successful</t>
+          <t>or</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập thành công</t>
+          <t>hoặc</t>
         </is>
       </c>
     </row>
     <row r="143" ht="18" customHeight="1">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>notfound.title</t>
+          <t>login.google.load-error</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>Page Not Found</t>
+          <t>Could not load Google Sign-In</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>Trang không tìm thấy</t>
+          <t>Không tải được đăng nhập Google</t>
         </is>
       </c>
     </row>
     <row r="144" ht="18" customHeight="1">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>notfound.description</t>
+          <t>login.facebook.button</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>The page you are looking for does not exist or has been moved.</t>
+          <t>Sign-in with Facebook</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Trang bạn tìm kiếm không tồn tại hoặc đã được di chuyển.</t>
+          <t>Đăng nhập với Facebook</t>
         </is>
       </c>
     </row>
     <row r="145" ht="18" customHeight="1">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>notfound.home</t>
+          <t>login.messages.incorrect-login</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>Go to Home</t>
+          <t>Invalid username or password</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>Về trang chủ</t>
+          <t>Tên người dùng hoặc mật khẩu không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="146" ht="18" customHeight="1">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>notfound.back</t>
+          <t>login.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Go Back</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Quay lại</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="147" ht="36" customHeight="1">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>register.confirm-password.error1</t>
+          <t>login.messages.missing-credentials</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>Confirm password does not match password</t>
+          <t>Username and password are required</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Mật khẩu xác nhận không khớp với mật khẩu</t>
+          <t>Tên người dùng và mật khẩu là bắt buộc</t>
         </is>
       </c>
     </row>
     <row r="148" ht="18" customHeight="1">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>register.confirm-password.label</t>
+          <t>login.messages.success</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Confirm Password</t>
+          <t>Login successful</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Xác nhận mật khẩu</t>
+          <t>Đăng nhập thành công</t>
         </is>
       </c>
     </row>
     <row r="149" ht="36" customHeight="1">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>register.confirm-password.placeholder</t>
+          <t>notfound.title</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>Confirm Password</t>
+          <t>Page Not Found</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>Xác nhận mật khẩu</t>
+          <t>Trang không tìm thấy</t>
         </is>
       </c>
     </row>
     <row r="150" ht="18" customHeight="1">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>register.display-name.label</t>
+          <t>notfound.description</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Display name</t>
+          <t>The page you are looking for does not exist or has been moved.</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Tên hiển thị</t>
+          <t>Trang bạn tìm kiếm không tồn tại hoặc đã được di chuyển.</t>
         </is>
       </c>
     </row>
     <row r="151" ht="18" customHeight="1">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>register.display-name.placeholder</t>
+          <t>notfound.home</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>Display name</t>
+          <t>Go to Home</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>Tên hiển thị</t>
+          <t>Về trang chủ</t>
         </is>
       </c>
     </row>
     <row r="152" ht="18" customHeight="1">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>register.email.error1</t>
+          <t>notfound.back</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Invalid email format</t>
+          <t>Go Back</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>Định dạng email không hợp lệ</t>
+          <t>Quay lại</t>
         </is>
       </c>
     </row>
     <row r="153" ht="18" customHeight="1">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>register.email.label</t>
+          <t>register.confirm-password.error1</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Confirm password does not match password</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Mật khẩu xác nhận không khớp với mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="154" ht="18" customHeight="1">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>register.email.placeholder</t>
+          <t>register.confirm-password.label</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Confirm Password</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Xác nhận mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="155" ht="18" customHeight="1">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>register.form.login</t>
+          <t>register.confirm-password.placeholder</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>Back to login</t>
+          <t>Confirm Password</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>Về trang đăng nhập</t>
+          <t>Xác nhận mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="156" ht="18" customHeight="1">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>register.form.submit</t>
+          <t>register.display-name.label</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>Register</t>
+          <t>Display name</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Đăng ký</t>
+          <t>Tên hiển thị</t>
         </is>
       </c>
     </row>
     <row r="157" ht="18" customHeight="1">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t>register.form.success</t>
+          <t>register.display-name.placeholder</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>Registration successful. Redirecting to login...</t>
+          <t>Display name</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>Đăng ký thành công. Đang chuyển hướng...</t>
+          <t>Tên hiển thị</t>
         </is>
       </c>
     </row>
     <row r="158" ht="18" customHeight="1">
       <c r="A158" s="1" t="inlineStr">
         <is>
-          <t>register.form.title</t>
+          <t>register.email.error1</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>Register</t>
+          <t>Invalid email format</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>Đăng ký</t>
+          <t>Định dạng email không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="159" ht="36" customHeight="1">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t>register.gender.female</t>
+          <t>register.email.label</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>Nữ</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="160" ht="18" customHeight="1">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>register.gender.label</t>
+          <t>register.email.placeholder</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>Gender</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Giới tính</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="161" ht="36" customHeight="1">
       <c r="A161" s="1" t="inlineStr">
         <is>
-          <t>register.gender.male</t>
+          <t>register.form.login</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Back to login</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>Nam</t>
+          <t>Về trang đăng nhập</t>
         </is>
       </c>
     </row>
     <row r="162" ht="18" customHeight="1">
       <c r="A162" s="1" t="inlineStr">
         <is>
-          <t>register.gender.select</t>
+          <t>register.form.submit</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>Select gender</t>
+          <t>Register</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Chọn giới tính</t>
+          <t>Đăng ký</t>
         </is>
       </c>
     </row>
     <row r="163" ht="18" customHeight="1">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t>register.page.title</t>
+          <t>register.form.success</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>Register</t>
+          <t>Registration successful. Redirecting to login...</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>Đăng ký</t>
+          <t>Đăng ký thành công. Đang chuyển hướng...</t>
         </is>
       </c>
     </row>
     <row r="164" ht="36" customHeight="1">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t>register.password.error1</t>
+          <t>register.form.title</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>Password must be at least 8 characters and contain uppercase, lowercase, number, and special character</t>
+          <t>Register</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Mật khẩu phải có ít nhất 8 ký tự và chứa chữ hoa, chữ thường, số và ký tự đặc biệt</t>
+          <t>Đăng ký</t>
         </is>
       </c>
     </row>
     <row r="165" ht="18" customHeight="1">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t>register.password.hide</t>
+          <t>register.gender.female</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>Hide password</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>Ẩn mật khẩu</t>
+          <t>Nữ</t>
         </is>
       </c>
     </row>
     <row r="166" ht="18" customHeight="1">
       <c r="A166" s="1" t="inlineStr">
         <is>
-          <t>register.password.label</t>
+          <t>register.gender.label</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>Password</t>
+          <t>Gender</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>Mật khẩu</t>
+          <t>Giới tính</t>
         </is>
       </c>
     </row>
     <row r="167" ht="18" customHeight="1">
       <c r="A167" s="1" t="inlineStr">
         <is>
-          <t>register.password.placeholder</t>
+          <t>register.gender.male</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>Password</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>Mật khẩu</t>
+          <t>Nam</t>
         </is>
       </c>
     </row>
     <row r="168" ht="18" customHeight="1">
       <c r="A168" s="1" t="inlineStr">
         <is>
-          <t>register.password.show</t>
+          <t>register.gender.select</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>Show password</t>
+          <t>Select gender</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>Hiện mật khẩu</t>
+          <t>Chọn giới tính</t>
         </is>
       </c>
     </row>
     <row r="169" ht="18" customHeight="1">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t>register.username.error1</t>
+          <t>register.page.title</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>User name must contain only alphanumeric characters, underscore, and dot</t>
+          <t>Register</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>Tên người dùng chỉ chứa ký tự chữ số, dấu gạch dưới và dấu chấm</t>
+          <t>Đăng ký</t>
         </is>
       </c>
     </row>
     <row r="170" ht="18" customHeight="1">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t>register.username.label</t>
+          <t>register.password.error1</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>User name</t>
+          <t>Password must be at least 8 characters and contain uppercase, lowercase, number, and special character</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>Tên người dùng</t>
+          <t>Mật khẩu phải có ít nhất 8 ký tự và chứa chữ hoa, chữ thường, số và ký tự đặc biệt</t>
         </is>
       </c>
     </row>
     <row r="171" ht="18" customHeight="1">
       <c r="A171" s="1" t="inlineStr">
         <is>
-          <t>register.username.placeholder</t>
+          <t>register.password.hide</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>User name</t>
+          <t>Hide password</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>Tên người dùng</t>
+          <t>Ẩn mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="172" ht="18" customHeight="1">
       <c r="A172" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.page.title</t>
+          <t>register.password.label</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>Forgot Password</t>
+          <t>Password</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>Quên mật khẩu</t>
+          <t>Mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="173" ht="18" customHeight="1">
       <c r="A173" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.form.title</t>
+          <t>register.password.placeholder</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>Forgot Password</t>
+          <t>Password</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>Quên mật khẩu</t>
+          <t>Mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="174" ht="18" customHeight="1">
       <c r="A174" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.form.login</t>
+          <t>register.password.show</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>Back to login</t>
+          <t>Show password</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>Về trang đăng nhập</t>
+          <t>Hiện mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="175" ht="18" customHeight="1">
       <c r="A175" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.form.submit</t>
+          <t>register.username.error1</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>Forgot password</t>
+          <t>User name must contain only alphanumeric characters, underscore, and dot</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>Quên mật khẩu</t>
+          <t>Tên người dùng chỉ chứa ký tự chữ số, dấu gạch dưới và dấu chấm</t>
         </is>
       </c>
     </row>
     <row r="176" ht="36" customHeight="1">
       <c r="A176" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.form.success</t>
+          <t>register.username.label</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>Check your email for reset password details.</t>
+          <t>User name</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>Hãy kiểm tra email để xem thông tin đặt lại mật khẩu.</t>
+          <t>Tên người dùng</t>
         </is>
       </c>
     </row>
     <row r="177" ht="18" customHeight="1">
       <c r="A177" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.form.error1</t>
+          <t>register.username.placeholder</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>Forgot password failed.</t>
+          <t>User name</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>Quên mật khẩu không thành công.</t>
+          <t>Tên người dùng</t>
         </is>
       </c>
     </row>
     <row r="178" ht="18" customHeight="1">
       <c r="A178" s="1" t="inlineStr">
         <is>
-          <t>reset-password.page.title</t>
+          <t>forgot-password.page.title</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>Reset Password</t>
+          <t>Forgot Password</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>Đặt lại mật khẩu</t>
+          <t>Quên mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="179" ht="18" customHeight="1">
       <c r="A179" s="1" t="inlineStr">
         <is>
-          <t>reset-password.form.title</t>
+          <t>forgot-password.form.title</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>Reset your password</t>
+          <t>Forgot Password</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>Đặt lại mật khẩu của bạn</t>
+          <t>Quên mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="180" ht="18" customHeight="1">
       <c r="A180" s="1" t="inlineStr">
         <is>
-          <t>reset-password.form.submit</t>
+          <t>forgot-password.form.login</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>Reset Password</t>
+          <t>Back to login</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>Đặt lại mật khẩu</t>
+          <t>Về trang đăng nhập</t>
         </is>
       </c>
     </row>
     <row r="181" ht="18" customHeight="1">
       <c r="A181" s="1" t="inlineStr">
         <is>
-          <t>reset-password.form.error1</t>
+          <t>forgot-password.form.submit</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>An error occurred while resetting your password. Please try again.</t>
+          <t>Forgot password</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>Có lỗi xảy ra khi đặt lại mật khẩu. Vui lòng thử lại.</t>
+          <t>Quên mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="182" ht="18" customHeight="1">
       <c r="A182" s="1" t="inlineStr">
         <is>
-          <t>reset-password.form.invalid-token</t>
+          <t>forgot-password.form.success</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>Invalid or expired reset password token</t>
+          <t>Check your email for reset password details.</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>Token đặt lại mật khẩu không hợp lệ hoặc đã hết hạn</t>
+          <t>Hãy kiểm tra email để xem thông tin đặt lại mật khẩu.</t>
         </is>
       </c>
     </row>
     <row r="183" ht="18" customHeight="1">
       <c r="A183" s="1" t="inlineStr">
         <is>
-          <t>reset-password.form.success</t>
+          <t>forgot-password.form.error1</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>Password reset successfully. Redirecting to login...</t>
+          <t>Forgot password failed.</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>Đặt lại mật khẩu thành công. Đang chuyển hướng đến đăng nhập...</t>
+          <t>Quên mật khẩu không thành công.</t>
         </is>
       </c>
     </row>
     <row r="184" ht="18" customHeight="1">
       <c r="A184" s="1" t="inlineStr">
         <is>
-          <t>reset-password.action.back-to-login</t>
+          <t>reset-password.page.title</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>Back to login</t>
+          <t>Reset Password</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>Quay lại trang chủ</t>
+          <t>Đặt lại mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="185" ht="36" customHeight="1">
       <c r="A185" s="1" t="inlineStr">
         <is>
-          <t>auth-middleware.messages.invalid-token-payload</t>
+          <t>reset-password.form.title</t>
         </is>
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>Invalid token payload</t>
+          <t>Reset your password</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>Payload của token không hợp lệ</t>
+          <t>Đặt lại mật khẩu của bạn</t>
         </is>
       </c>
     </row>
     <row r="186" ht="18" customHeight="1">
       <c r="A186" s="1" t="inlineStr">
         <is>
-          <t>auth-middleware.messages.session-not-found</t>
+          <t>reset-password.form.submit</t>
         </is>
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>Session not found</t>
+          <t>Reset Password</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy phiên</t>
+          <t>Đặt lại mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="187" ht="36" customHeight="1">
       <c r="A187" s="1" t="inlineStr">
         <is>
-          <t>auth-middleware.messages.token-expired</t>
+          <t>reset-password.form.error1</t>
         </is>
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>Token is expired</t>
+          <t>An error occurred while resetting your password. Please try again.</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>Token đã hết hạn</t>
+          <t>Có lỗi xảy ra khi đặt lại mật khẩu. Vui lòng thử lại.</t>
         </is>
       </c>
     </row>
     <row r="188" ht="18" customHeight="1">
       <c r="A188" s="1" t="inlineStr">
         <is>
-          <t>auth-middleware.messages.token-invalid</t>
+          <t>reset-password.form.invalid-token</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>Token is invalid</t>
+          <t>Invalid or expired reset password token</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>Token không hợp lệ</t>
+          <t>Token đặt lại mật khẩu không hợp lệ hoặc đã hết hạn</t>
         </is>
       </c>
     </row>
     <row r="189" ht="18" customHeight="1">
       <c r="A189" s="1" t="inlineStr">
         <is>
-          <t>auth-middleware.messages.token-required</t>
+          <t>reset-password.form.success</t>
         </is>
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>Token not provided</t>
+          <t>Password reset successfully. Redirecting to login...</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>Token không được cung cấp</t>
+          <t>Đặt lại mật khẩu thành công. Đang chuyển hướng đến đăng nhập...</t>
         </is>
       </c>
     </row>
     <row r="190" ht="18" customHeight="1">
       <c r="A190" s="1" t="inlineStr">
         <is>
-          <t>auth-middleware.messages.token-subject-mismatch</t>
+          <t>reset-password.action.back-to-login</t>
         </is>
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>Token subject mismatch</t>
+          <t>Back to login</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>Token chủ đề không khớp</t>
+          <t>Quay lại trang chủ</t>
         </is>
       </c>
     </row>
     <row r="191" ht="18" customHeight="1">
       <c r="A191" s="1" t="inlineStr">
         <is>
-          <t>auth-middleware.messages.token-validation-failed</t>
+          <t>auth-middleware.messages.invalid-token-payload</t>
         </is>
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>Token validation failed</t>
+          <t>Invalid token payload</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>Xác thực token không thành công</t>
+          <t>Payload của token không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="192" ht="18" customHeight="1">
       <c r="A192" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.insufficient-amount</t>
+          <t>auth-middleware.messages.session-not-found</t>
         </is>
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>You do not have enough balance to create a room with this bet</t>
+          <t>Session not found</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>Bạn không còn đủ amount để tạo phòng với mức cược này</t>
+          <t>Không tìm thấy phiên</t>
         </is>
       </c>
     </row>
     <row r="193" ht="18" customHeight="1">
       <c r="A193" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.internal-server-error</t>
+          <t>auth-middleware.messages.token-expired</t>
         </is>
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>Internal server error while creating room</t>
+          <t>Token is expired</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ khi tạo phòng</t>
+          <t>Token đã hết hạn</t>
         </is>
       </c>
     </row>
     <row r="194" ht="18" customHeight="1">
       <c r="A194" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.invalid-bet-amount</t>
+          <t>auth-middleware.messages.token-invalid</t>
         </is>
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>Bet amount is required and must be one of the acceptable values</t>
+          <t>Token is invalid</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>Số tiền cược là bắt buộc và phải là một trong các giá trị được chấp nhận</t>
+          <t>Token không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="195" ht="18" customHeight="1">
       <c r="A195" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.invalid-time-limit</t>
+          <t>auth-middleware.messages.token-required</t>
         </is>
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>Invalid time limit</t>
+          <t>Token not provided</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>Thời gian không hợp lệ</t>
+          <t>Token không được cung cấp</t>
         </is>
       </c>
     </row>
     <row r="196" ht="18" customHeight="1">
       <c r="A196" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.invalid-time-increment</t>
+          <t>auth-middleware.messages.token-subject-mismatch</t>
         </is>
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>Invalid bonus per move</t>
+          <t>Token subject mismatch</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>Thời gian cộng mỗi nước không hợp lệ</t>
+          <t>Token chủ đề không khớp</t>
         </is>
       </c>
     </row>
     <row r="197" ht="18" customHeight="1">
       <c r="A197" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.invalid-time-per-move</t>
+          <t>auth-middleware.messages.token-validation-failed</t>
         </is>
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>Invalid time per move</t>
+          <t>Token validation failed</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>Thời gian mỗi nước không hợp lệ</t>
+          <t>Xác thực token không thành công</t>
         </is>
       </c>
     </row>
     <row r="198" ht="18" customHeight="1">
       <c r="A198" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.invalid-redFirst</t>
+          <t>create-room.messages.insufficient-amount</t>
         </is>
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>'redFirst' must be a boolean</t>
+          <t>You do not have enough balance to create a room with this bet</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>'redFirst' phải là giá trị boolean</t>
+          <t>Bạn không còn đủ amount để tạo phòng với mức cược này</t>
         </is>
       </c>
     </row>
     <row r="199" ht="18" customHeight="1">
       <c r="A199" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.invalid-team-name</t>
+          <t>create-room.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>Team name must be either 'red', 'black', or null</t>
+          <t>Internal server error while creating room</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>Tên đội phải là 'red', 'black' hoặc null</t>
+          <t>Lỗi máy chủ nội bộ khi tạo phòng</t>
         </is>
       </c>
     </row>
     <row r="200" ht="18" customHeight="1">
       <c r="A200" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.name-required</t>
+          <t>create-room.messages.invalid-bet-amount</t>
         </is>
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>Room name (tableName) is required and must not be empty</t>
+          <t>Bet amount is required and must be one of the acceptable values</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>Tên phòng (tableName) là bắt buộc và không được để trống</t>
+          <t>Số tiền cược là bắt buộc và phải là một trong các giá trị được chấp nhận</t>
         </is>
       </c>
     </row>
     <row r="201" ht="18" customHeight="1">
       <c r="A201" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.room-created</t>
+          <t>create-room.messages.invalid-time-limit</t>
         </is>
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>Room created successfully</t>
+          <t>Invalid time limit</t>
         </is>
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>Phòng được tạo thành công</t>
+          <t>Thời gian không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="202" ht="18" customHeight="1">
       <c r="A202" s="1" t="inlineStr">
         <is>
-          <t>fetch-rooms.messages.internal-server-error</t>
+          <t>create-room.messages.invalid-time-increment</t>
         </is>
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Invalid bonus per move</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Thời gian cộng mỗi nước không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="203" ht="18" customHeight="1">
       <c r="A203" s="1" t="inlineStr">
         <is>
-          <t>fetch-rooms.messages.invalid-status</t>
+          <t>create-room.messages.invalid-time-per-move</t>
         </is>
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>Query parameter 'status' must be an integer</t>
+          <t>Invalid time per move</t>
         </is>
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>Tham số truy vấn 'status' phải là số nguyên</t>
+          <t>Thời gian mỗi nước không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="204" ht="18" customHeight="1">
       <c r="A204" s="1" t="inlineStr">
         <is>
-          <t>fetch-rooms.messages.success</t>
+          <t>create-room.messages.invalid-redFirst</t>
         </is>
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>Fetch rooms successfully</t>
+          <t>'redFirst' must be a boolean</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>Lấy phòng thành công</t>
+          <t>'redFirst' phải là giá trị boolean</t>
         </is>
       </c>
     </row>
     <row r="205" ht="18" customHeight="1">
       <c r="A205" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.messages.email-not-found</t>
+          <t>create-room.messages.invalid-team-name</t>
         </is>
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>Email does not exist</t>
+          <t>Team name must be either 'red', 'black', or null</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>Email không tồn tại</t>
+          <t>Tên đội phải là 'red', 'black' hoặc null</t>
         </is>
       </c>
     </row>
     <row r="206" ht="18" customHeight="1">
       <c r="A206" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.messages.email-service-not-configured</t>
+          <t>create-room.messages.name-required</t>
         </is>
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>Email service is not configured</t>
+          <t>Room name (tableName) is required and must not be empty</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>Dịch vụ email chưa được cấu hình</t>
+          <t>Tên phòng (tableName) là bắt buộc và không được để trống</t>
         </is>
       </c>
     </row>
     <row r="207" ht="18" customHeight="1">
       <c r="A207" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.messages.internal-server-error</t>
+          <t>create-room.messages.room-created</t>
         </is>
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Room created successfully</t>
         </is>
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Phòng được tạo thành công</t>
         </is>
       </c>
     </row>
     <row r="208" ht="18" customHeight="1">
       <c r="A208" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.messages.invalid-email-format</t>
+          <t>fetch-rooms.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>Invalid email format</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>Định dạng email không hợp lệ</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="209" ht="18" customHeight="1">
       <c r="A209" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.messages.missing-email</t>
+          <t>fetch-rooms.messages.invalid-status</t>
         </is>
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>Email is required</t>
+          <t>Query parameter 'status' must be an integer</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>Email là bắt buộc</t>
+          <t>Tham số truy vấn 'status' phải là số nguyên</t>
         </is>
       </c>
     </row>
     <row r="210" ht="18" customHeight="1">
       <c r="A210" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.messages.success</t>
+          <t>fetch-rooms.messages.success</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>Forgot password email sent</t>
+          <t>Fetch rooms successfully</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>Email đặt lại mật khẩu đã được gửi</t>
+          <t>Lấy phòng thành công</t>
         </is>
       </c>
     </row>
     <row r="211" ht="36" customHeight="1">
       <c r="A211" s="1" t="inlineStr">
         <is>
-          <t>join-room.messages.internal-server-error</t>
+          <t>forgot-password.messages.email-not-found</t>
         </is>
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Email does not exist</t>
         </is>
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Email không tồn tại</t>
         </is>
       </c>
     </row>
     <row r="212" ht="18" customHeight="1">
       <c r="A212" s="1" t="inlineStr">
         <is>
-          <t>join-room.messages.invalid-team</t>
+          <t>forgot-password.messages.email-service-not-configured</t>
         </is>
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>Field 'team' must be 'red', 'black', null, or undefined</t>
+          <t>Email service is not configured</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>Trường 'team' phải là 'red', 'black', null hoặc không truyền</t>
+          <t>Dịch vụ email chưa được cấu hình</t>
         </is>
       </c>
     </row>
     <row r="213" ht="18" customHeight="1">
       <c r="A213" s="1" t="inlineStr">
         <is>
-          <t>join-room.messages.invalid-room-id</t>
+          <t>forgot-password.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>Field 'id' is required and must be a positive integer</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="214" ht="18" customHeight="1">
       <c r="A214" s="1" t="inlineStr">
         <is>
-          <t>join-room.messages.room-not-found</t>
+          <t>forgot-password.messages.invalid-email-format</t>
         </is>
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>Room not found</t>
+          <t>Invalid email format</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy phòng</t>
+          <t>Định dạng email không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="215" ht="18" customHeight="1">
       <c r="A215" s="1" t="inlineStr">
         <is>
-          <t>join-room.messages.success</t>
+          <t>forgot-password.messages.missing-email</t>
         </is>
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>Successfully joined the room</t>
+          <t>Email is required</t>
         </is>
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>Tham gia phòng thành công</t>
+          <t>Email là bắt buộc</t>
         </is>
       </c>
     </row>
     <row r="216" ht="18" customHeight="1">
       <c r="A216" s="1" t="inlineStr">
         <is>
-          <t>join-room.messages.team-seat-occupied</t>
+          <t>forgot-password.messages.success</t>
         </is>
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>Selected team seat is already occupied</t>
+          <t>Forgot password email sent</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>Vị trí đội đã chọn đã có người chơi</t>
+          <t>Email đặt lại mật khẩu đã được gửi</t>
         </is>
       </c>
     </row>
     <row r="217" ht="18" customHeight="1">
       <c r="A217" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.cannot-kick-self</t>
+          <t>join-room.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>You cannot kick yourself</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>Bạn không thể kick chính mình</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="218" ht="18" customHeight="1">
       <c r="A218" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.forbidden</t>
+          <t>join-room.messages.invalid-team</t>
         </is>
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>Only the host can kick users</t>
+          <t>Field 'team' must be 'red', 'black', null, or undefined</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>Chỉ chủ phòng mới có thể kick người dùng</t>
+          <t>Trường 'team' phải là 'red', 'black', null hoặc không truyền</t>
         </is>
       </c>
     </row>
     <row r="219" ht="18" customHeight="1">
       <c r="A219" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.internal-server-error</t>
+          <t>join-room.messages.invalid-room-id</t>
         </is>
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Field 'id' is required and must be a positive integer</t>
         </is>
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
         </is>
       </c>
     </row>
     <row r="220" ht="18" customHeight="1">
       <c r="A220" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.invalid-room-id</t>
+          <t>join-room.messages.room-not-found</t>
         </is>
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>Field 'id' is required and must be a positive integer</t>
+          <t>Room not found</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
+          <t>Không tìm thấy phòng</t>
         </is>
       </c>
     </row>
     <row r="221" ht="18" customHeight="1">
       <c r="A221" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.invalid-user-id</t>
+          <t>join-room.messages.success</t>
         </is>
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>Field 'userId' is required and must be a positive integer</t>
+          <t>Successfully joined the room</t>
         </is>
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>Trường 'userId' là bắt buộc và phải là số nguyên dương</t>
+          <t>Tham gia phòng thành công</t>
         </is>
       </c>
     </row>
     <row r="222" ht="18" customHeight="1">
       <c r="A222" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.room-not-found</t>
+          <t>join-room.messages.team-seat-occupied</t>
         </is>
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>Room not found</t>
+          <t>Selected team seat is already occupied</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy phòng</t>
+          <t>Vị trí đội đã chọn đã có người chơi</t>
         </is>
       </c>
     </row>
     <row r="223" ht="18" customHeight="1">
       <c r="A223" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.room-not-waiting</t>
+          <t>kick-user.messages.cannot-kick-self</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>You can only kick users while the room is waiting</t>
+          <t>You cannot kick yourself</t>
         </is>
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>Chỉ có thể kick người dùng khi phòng đang ở trạng thái chờ</t>
+          <t>Bạn không thể kick chính mình</t>
         </is>
       </c>
     </row>
     <row r="224" ht="18" customHeight="1">
       <c r="A224" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.success</t>
+          <t>kick-user.messages.forbidden</t>
         </is>
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>User has been kicked</t>
+          <t>Only the host can kick users</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>Người dùng đã bị kick</t>
+          <t>Chỉ chủ phòng mới có thể kick người dùng</t>
         </is>
       </c>
     </row>
     <row r="225" ht="18" customHeight="1">
       <c r="A225" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.user-not-in-room</t>
+          <t>kick-user.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>User is not in this room</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>Người dùng không trong phòng này</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="226" ht="18" customHeight="1">
       <c r="A226" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.you-were-kicked</t>
+          <t>kick-user.messages.invalid-room-id</t>
         </is>
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>You have been removed from the room by the host</t>
+          <t>Field 'id' is required and must be a positive integer</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>Bạn đã bị chủ phòng đưa ra khỏi phòng</t>
+          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
         </is>
       </c>
     </row>
     <row r="227" ht="18" customHeight="1">
       <c r="A227" s="1" t="inlineStr">
         <is>
-          <t>leave-room.messages.internal-server-error</t>
+          <t>kick-user.messages.invalid-user-id</t>
         </is>
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Field 'userId' is required and must be a positive integer</t>
         </is>
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Trường 'userId' là bắt buộc và phải là số nguyên dương</t>
         </is>
       </c>
     </row>
     <row r="228" ht="18" customHeight="1">
       <c r="A228" s="1" t="inlineStr">
         <is>
-          <t>leave-room.messages.invalid-room-id</t>
+          <t>kick-user.messages.room-not-found</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>Field 'id' is required and must be a positive integer</t>
+          <t>Room not found</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
+          <t>Không tìm thấy phòng</t>
         </is>
       </c>
     </row>
     <row r="229" ht="18" customHeight="1">
       <c r="A229" s="1" t="inlineStr">
         <is>
-          <t>leave-room.messages.player-not-in-room</t>
+          <t>kick-user.messages.room-not-waiting</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>Player is not in this room</t>
+          <t>You can only kick users while the room is waiting</t>
         </is>
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>Người chơi không trong phòng này</t>
+          <t>Chỉ có thể kick người dùng khi phòng đang ở trạng thái chờ</t>
         </is>
       </c>
     </row>
     <row r="230" ht="18" customHeight="1">
       <c r="A230" s="1" t="inlineStr">
         <is>
-          <t>leave-room.messages.success</t>
+          <t>kick-user.messages.success</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>Leave room successfully</t>
+          <t>User has been kicked</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>Rời phòng thành công</t>
+          <t>Người dùng đã bị kick</t>
         </is>
       </c>
     </row>
     <row r="231" ht="18" customHeight="1">
       <c r="A231" s="1" t="inlineStr">
         <is>
-          <t>load-room.messages.internal-server-error</t>
+          <t>kick-user.messages.user-not-in-room</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>User is not in this room</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Người dùng không trong phòng này</t>
         </is>
       </c>
     </row>
     <row r="232" ht="18" customHeight="1">
       <c r="A232" s="1" t="inlineStr">
         <is>
-          <t>load-room.messages.invalid-room-id</t>
+          <t>kick-user.messages.you-were-kicked</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>Room ID must be a positive integer</t>
+          <t>You have been removed from the room by the host</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>ID phòng phải là số nguyên dương</t>
+          <t>Bạn đã bị chủ phòng đưa ra khỏi phòng</t>
         </is>
       </c>
     </row>
     <row r="233" ht="18" customHeight="1">
       <c r="A233" s="1" t="inlineStr">
         <is>
-          <t>load-room.messages.room-not-found</t>
+          <t>leave-room.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>Room not found</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy phòng</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="234" ht="18" customHeight="1">
       <c r="A234" s="1" t="inlineStr">
         <is>
-          <t>load-room.messages.success</t>
+          <t>leave-room.messages.invalid-room-id</t>
         </is>
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>Load room successfully</t>
+          <t>Field 'id' is required and must be a positive integer</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>Tải phòng thành công</t>
+          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
         </is>
       </c>
     </row>
     <row r="235" ht="18" customHeight="1">
       <c r="A235" s="1" t="inlineStr">
         <is>
-          <t>google-login.messages.email-not-verified</t>
+          <t>leave-room.messages.player-not-in-room</t>
         </is>
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>Your Google email is not verified</t>
+          <t>Player is not in this room</t>
         </is>
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>Email Google của bạn chưa được xác minh</t>
+          <t>Người chơi không trong phòng này</t>
         </is>
       </c>
     </row>
     <row r="236" ht="18" customHeight="1">
       <c r="A236" s="1" t="inlineStr">
         <is>
-          <t>google-login.messages.failed</t>
+          <t>leave-room.messages.success</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>Login failed</t>
+          <t>Leave room successfully</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập không thành công</t>
+          <t>Rời phòng thành công</t>
         </is>
       </c>
     </row>
     <row r="237" ht="18" customHeight="1">
       <c r="A237" s="1" t="inlineStr">
         <is>
-          <t>google-login.messages.internal-server-error</t>
+          <t>load-room.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
@@ -4365,92 +4365,92 @@
     <row r="238" ht="18" customHeight="1">
       <c r="A238" s="1" t="inlineStr">
         <is>
-          <t>google-login.messages.invalid-token</t>
+          <t>load-room.messages.invalid-room-id</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>Invalid Google credential</t>
+          <t>Room ID must be a positive integer</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>Thông tin đăng nhập Google không hợp lệ</t>
+          <t>ID phòng phải là số nguyên dương</t>
         </is>
       </c>
     </row>
     <row r="239" ht="18" customHeight="1">
       <c r="A239" s="1" t="inlineStr">
         <is>
-          <t>google-login.messages.missing-credential</t>
+          <t>load-room.messages.room-not-found</t>
         </is>
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>Google credential is required</t>
+          <t>Room not found</t>
         </is>
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>Thiếu thông tin đăng nhập Google</t>
+          <t>Không tìm thấy phòng</t>
         </is>
       </c>
     </row>
     <row r="240" ht="18" customHeight="1">
       <c r="A240" s="1" t="inlineStr">
         <is>
-          <t>facebook-login.messages.missing-token</t>
+          <t>load-room.messages.success</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>Facebook token is required</t>
+          <t>Load room successfully</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>Thiếu thông tin đăng nhập Facebook</t>
+          <t>Tải phòng thành công</t>
         </is>
       </c>
     </row>
     <row r="241" ht="18" customHeight="1">
       <c r="A241" s="1" t="inlineStr">
         <is>
-          <t>facebook-login.messages.invalid-token</t>
+          <t>google-login.messages.email-not-verified</t>
         </is>
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>Invalid Facebook token</t>
+          <t>Your Google email is not verified</t>
         </is>
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>Thông tin đăng nhập Facebook không hợp lệ</t>
+          <t>Email Google của bạn chưa được xác minh</t>
         </is>
       </c>
     </row>
     <row r="242" ht="18" customHeight="1">
       <c r="A242" s="1" t="inlineStr">
         <is>
-          <t>facebook-login.messages.not-linked</t>
+          <t>google-login.messages.failed</t>
         </is>
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>This Facebook account is not linked. Log in another way and link it in Settings</t>
+          <t>Login failed</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản Facebook này chưa được liên kết. Hãy đăng nhập cách khác rồi liên kết trong Cài đặt</t>
+          <t>Đăng nhập không thành công</t>
         </is>
       </c>
     </row>
     <row r="243" ht="18" customHeight="1">
       <c r="A243" s="1" t="inlineStr">
         <is>
-          <t>facebook-login.messages.internal-server-error</t>
+          <t>google-login.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B243" s="2" t="inlineStr">
@@ -4467,262 +4467,262 @@
     <row r="244" ht="18" customHeight="1">
       <c r="A244" s="1" t="inlineStr">
         <is>
-          <t>facebook-link.messages.missing-token</t>
+          <t>google-login.messages.invalid-token</t>
         </is>
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>Facebook token is required</t>
+          <t>Invalid Google credential</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>Thiếu thông tin đăng nhập Facebook</t>
+          <t>Thông tin đăng nhập Google không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="245" ht="18" customHeight="1">
       <c r="A245" s="1" t="inlineStr">
         <is>
-          <t>facebook-link.messages.invalid-token</t>
+          <t>google-login.messages.missing-credential</t>
         </is>
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>Invalid Facebook token</t>
+          <t>Google credential is required</t>
         </is>
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>Thông tin đăng nhập Facebook không hợp lệ</t>
+          <t>Thiếu thông tin đăng nhập Google</t>
         </is>
       </c>
     </row>
     <row r="246" ht="18" customHeight="1">
       <c r="A246" s="1" t="inlineStr">
         <is>
-          <t>facebook-link.messages.linked</t>
+          <t>facebook-login.messages.missing-token</t>
         </is>
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>Facebook linked successfully</t>
+          <t>Facebook token is required</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>Đã liên kết Facebook</t>
+          <t>Thiếu thông tin đăng nhập Facebook</t>
         </is>
       </c>
     </row>
     <row r="247" ht="18" customHeight="1">
       <c r="A247" s="1" t="inlineStr">
         <is>
-          <t>facebook-link.messages.already-linked</t>
+          <t>facebook-login.messages.invalid-token</t>
         </is>
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>This Facebook account is already linked to your account</t>
+          <t>Invalid Facebook token</t>
         </is>
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản Facebook này đã được liên kết với bạn</t>
+          <t>Thông tin đăng nhập Facebook không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="248" ht="18" customHeight="1">
       <c r="A248" s="1" t="inlineStr">
         <is>
-          <t>facebook-link.messages.linked-to-other</t>
+          <t>facebook-login.messages.not-linked</t>
         </is>
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>This Facebook account is already linked to another account</t>
+          <t>This Facebook account is not linked. Log in another way and link it in Settings</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản Facebook này đã được liên kết với tài khoản khác</t>
+          <t>Tài khoản Facebook này chưa được liên kết. Hãy đăng nhập cách khác rồi liên kết trong Cài đặt</t>
         </is>
       </c>
     </row>
     <row r="249" ht="18" customHeight="1">
       <c r="A249" s="1" t="inlineStr">
         <is>
-          <t>facebook-link.messages.already-has-facebook</t>
+          <t>facebook-login.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>You already linked a different Facebook account</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>Bạn đã liên kết một tài khoản Facebook khác</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="250" ht="18" customHeight="1">
       <c r="A250" s="1" t="inlineStr">
         <is>
-          <t>facebook-link.messages.unlinked</t>
+          <t>facebook-link.messages.missing-token</t>
         </is>
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>Facebook unlinked</t>
+          <t>Facebook token is required</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>Đã huỷ liên kết Facebook</t>
+          <t>Thiếu thông tin đăng nhập Facebook</t>
         </is>
       </c>
     </row>
     <row r="251" ht="18" customHeight="1">
       <c r="A251" s="1" t="inlineStr">
         <is>
-          <t>facebook-link.messages.internal-server-error</t>
+          <t>facebook-link.messages.invalid-token</t>
         </is>
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Invalid Facebook token</t>
         </is>
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Thông tin đăng nhập Facebook không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="252" ht="18" customHeight=